--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EAD2FF-E8DB-4BA8-AFD3-9F0E75F6FBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79C323F-FCC3-4A22-8859-D1058807333E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$205</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="223">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,580 +45,658 @@
     <t>.</t>
   </si>
   <si>
-    <t>128804538</t>
-  </si>
-  <si>
-    <t>128819313</t>
-  </si>
-  <si>
-    <t>128828598</t>
-  </si>
-  <si>
-    <t>129109266</t>
-  </si>
-  <si>
-    <t>129166726</t>
-  </si>
-  <si>
-    <t>129529945</t>
-  </si>
-  <si>
-    <t>129643602</t>
-  </si>
-  <si>
-    <t>129765603</t>
-  </si>
-  <si>
-    <t>129779498</t>
-  </si>
-  <si>
-    <t>129907756</t>
-  </si>
-  <si>
-    <t>130383633</t>
-  </si>
-  <si>
-    <t>130400690</t>
-  </si>
-  <si>
-    <t>130656398</t>
-  </si>
-  <si>
-    <t>130740752</t>
-  </si>
-  <si>
-    <t>130823617</t>
-  </si>
-  <si>
-    <t>131096619</t>
-  </si>
-  <si>
-    <t>131258609</t>
-  </si>
-  <si>
-    <t>131726292</t>
-  </si>
-  <si>
-    <t>131757140</t>
-  </si>
-  <si>
-    <t>131907508</t>
-  </si>
-  <si>
-    <t>132182170</t>
-  </si>
-  <si>
-    <t>132270744</t>
-  </si>
-  <si>
-    <t>132322292</t>
-  </si>
-  <si>
-    <t>132573978</t>
-  </si>
-  <si>
-    <t>132686243</t>
-  </si>
-  <si>
-    <t>132787736</t>
-  </si>
-  <si>
-    <t>132910626</t>
-  </si>
-  <si>
-    <t>133046203</t>
-  </si>
-  <si>
-    <t>133308194</t>
-  </si>
-  <si>
-    <t>133338001</t>
-  </si>
-  <si>
-    <t>133338121</t>
-  </si>
-  <si>
-    <t>133338402</t>
-  </si>
-  <si>
-    <t>133338422</t>
-  </si>
-  <si>
-    <t>133338499</t>
-  </si>
-  <si>
-    <t>133338729</t>
-  </si>
-  <si>
-    <t>133338779</t>
-  </si>
-  <si>
-    <t>133338929</t>
-  </si>
-  <si>
-    <t>133338951</t>
-  </si>
-  <si>
-    <t>133339357</t>
-  </si>
-  <si>
-    <t>133339396</t>
-  </si>
-  <si>
-    <t>133339500</t>
-  </si>
-  <si>
-    <t>133339887</t>
-  </si>
-  <si>
-    <t>133340009</t>
-  </si>
-  <si>
-    <t>133340042</t>
-  </si>
-  <si>
-    <t>133340101</t>
-  </si>
-  <si>
-    <t>133340206</t>
-  </si>
-  <si>
-    <t>133340271</t>
-  </si>
-  <si>
-    <t>133340295</t>
-  </si>
-  <si>
-    <t>133340340</t>
-  </si>
-  <si>
-    <t>133340479</t>
-  </si>
-  <si>
-    <t>133340483</t>
-  </si>
-  <si>
-    <t>133340663</t>
-  </si>
-  <si>
-    <t>133341084</t>
-  </si>
-  <si>
-    <t>133341219</t>
-  </si>
-  <si>
-    <t>133341399</t>
-  </si>
-  <si>
-    <t>133341534</t>
-  </si>
-  <si>
-    <t>133341698</t>
-  </si>
-  <si>
-    <t>133341791</t>
-  </si>
-  <si>
-    <t>133341824</t>
-  </si>
-  <si>
-    <t>133341831</t>
-  </si>
-  <si>
-    <t>133342051</t>
-  </si>
-  <si>
-    <t>133342120</t>
-  </si>
-  <si>
-    <t>133342286</t>
-  </si>
-  <si>
-    <t>133342355</t>
-  </si>
-  <si>
-    <t>133342404</t>
-  </si>
-  <si>
-    <t>133342660</t>
-  </si>
-  <si>
-    <t>133343025</t>
-  </si>
-  <si>
-    <t>133343051</t>
-  </si>
-  <si>
-    <t>133343074</t>
-  </si>
-  <si>
-    <t>133343131</t>
-  </si>
-  <si>
-    <t>133343316</t>
-  </si>
-  <si>
-    <t>133343319</t>
-  </si>
-  <si>
-    <t>133343323</t>
-  </si>
-  <si>
-    <t>133343399</t>
-  </si>
-  <si>
-    <t>133343652</t>
-  </si>
-  <si>
-    <t>133343731</t>
-  </si>
-  <si>
-    <t>133343828</t>
-  </si>
-  <si>
-    <t>133343848</t>
-  </si>
-  <si>
-    <t>133343895</t>
-  </si>
-  <si>
-    <t>133343899</t>
-  </si>
-  <si>
-    <t>133343970</t>
-  </si>
-  <si>
-    <t>133344019</t>
-  </si>
-  <si>
-    <t>133344252</t>
-  </si>
-  <si>
-    <t>133344336</t>
-  </si>
-  <si>
-    <t>133344439</t>
-  </si>
-  <si>
-    <t>133344619</t>
-  </si>
-  <si>
-    <t>133344643</t>
-  </si>
-  <si>
-    <t>133344749</t>
-  </si>
-  <si>
-    <t>133344753</t>
-  </si>
-  <si>
-    <t>133345038</t>
-  </si>
-  <si>
-    <t>133345179</t>
-  </si>
-  <si>
-    <t>133345341</t>
-  </si>
-  <si>
-    <t>133345472</t>
-  </si>
-  <si>
-    <t>133346089</t>
-  </si>
-  <si>
-    <t>133346280</t>
-  </si>
-  <si>
-    <t>133346339</t>
-  </si>
-  <si>
-    <t>133346450</t>
-  </si>
-  <si>
-    <t>133346470</t>
-  </si>
-  <si>
-    <t>133346701</t>
-  </si>
-  <si>
-    <t>133346761</t>
-  </si>
-  <si>
-    <t>133347127</t>
-  </si>
-  <si>
-    <t>133347170</t>
-  </si>
-  <si>
-    <t>133347191</t>
-  </si>
-  <si>
-    <t>133347397</t>
-  </si>
-  <si>
-    <t>133347588</t>
-  </si>
-  <si>
-    <t>133347706</t>
-  </si>
-  <si>
-    <t>133347726</t>
-  </si>
-  <si>
-    <t>133347788</t>
-  </si>
-  <si>
-    <t>133347807</t>
-  </si>
-  <si>
-    <t>133347918</t>
-  </si>
-  <si>
-    <t>133348022</t>
-  </si>
-  <si>
-    <t>133348150</t>
-  </si>
-  <si>
-    <t>133348155</t>
-  </si>
-  <si>
-    <t>133348195</t>
-  </si>
-  <si>
-    <t>133348315</t>
-  </si>
-  <si>
-    <t>133348320</t>
-  </si>
-  <si>
-    <t>133348409</t>
-  </si>
-  <si>
-    <t>133348522</t>
-  </si>
-  <si>
-    <t>133348640</t>
-  </si>
-  <si>
-    <t>133348784</t>
-  </si>
-  <si>
-    <t>133348787</t>
-  </si>
-  <si>
-    <t>133348875</t>
-  </si>
-  <si>
-    <t>133348943</t>
-  </si>
-  <si>
-    <t>133349025</t>
-  </si>
-  <si>
-    <t>133349077</t>
-  </si>
-  <si>
-    <t>133349078</t>
-  </si>
-  <si>
-    <t>133349101</t>
-  </si>
-  <si>
-    <t>133349204</t>
-  </si>
-  <si>
-    <t>133349227</t>
-  </si>
-  <si>
-    <t>133349263</t>
-  </si>
-  <si>
-    <t>133349308</t>
-  </si>
-  <si>
-    <t>133349395</t>
-  </si>
-  <si>
-    <t>133349400</t>
-  </si>
-  <si>
-    <t>133349470</t>
-  </si>
-  <si>
-    <t>133349646</t>
-  </si>
-  <si>
-    <t>133349708</t>
-  </si>
-  <si>
-    <t>133349773</t>
-  </si>
-  <si>
-    <t>133349839</t>
-  </si>
-  <si>
-    <t>133349867</t>
-  </si>
-  <si>
-    <t>133349970</t>
-  </si>
-  <si>
-    <t>133349988</t>
-  </si>
-  <si>
-    <t>133349991</t>
-  </si>
-  <si>
-    <t>133350004</t>
-  </si>
-  <si>
-    <t>133350480</t>
-  </si>
-  <si>
-    <t>133350485</t>
-  </si>
-  <si>
-    <t>133350508</t>
-  </si>
-  <si>
-    <t>133350525</t>
-  </si>
-  <si>
-    <t>133350572</t>
-  </si>
-  <si>
-    <t>133350628</t>
-  </si>
-  <si>
-    <t>133350720</t>
-  </si>
-  <si>
-    <t>133350943</t>
-  </si>
-  <si>
-    <t>133351029</t>
-  </si>
-  <si>
-    <t>133351242</t>
-  </si>
-  <si>
-    <t>133351278</t>
-  </si>
-  <si>
-    <t>133351407</t>
-  </si>
-  <si>
-    <t>133351673</t>
-  </si>
-  <si>
-    <t>133351718</t>
-  </si>
-  <si>
-    <t>133351843</t>
-  </si>
-  <si>
-    <t>133351847</t>
-  </si>
-  <si>
-    <t>133351985</t>
-  </si>
-  <si>
-    <t>133352015</t>
-  </si>
-  <si>
-    <t>133352035</t>
-  </si>
-  <si>
-    <t>133352044</t>
-  </si>
-  <si>
-    <t>133352177</t>
-  </si>
-  <si>
-    <t>133352234</t>
-  </si>
-  <si>
-    <t>133352424</t>
-  </si>
-  <si>
-    <t>133352464</t>
-  </si>
-  <si>
-    <t>133352488</t>
-  </si>
-  <si>
-    <t>133352489</t>
-  </si>
-  <si>
-    <t>133352491</t>
-  </si>
-  <si>
-    <t>133352512</t>
-  </si>
-  <si>
-    <t>133352533</t>
-  </si>
-  <si>
-    <t>133352569</t>
-  </si>
-  <si>
-    <t>133352631</t>
-  </si>
-  <si>
-    <t>133352671</t>
-  </si>
-  <si>
-    <t>133352690</t>
-  </si>
-  <si>
-    <t>133352719</t>
-  </si>
-  <si>
-    <t>133352745</t>
-  </si>
-  <si>
-    <t>133352783</t>
-  </si>
-  <si>
-    <t>133352834</t>
-  </si>
-  <si>
-    <t>133353019</t>
-  </si>
-  <si>
-    <t>133353094</t>
-  </si>
-  <si>
-    <t>133353279</t>
-  </si>
-  <si>
-    <t>133353365</t>
-  </si>
-  <si>
-    <t>133353401</t>
-  </si>
-  <si>
-    <t>133353809</t>
-  </si>
-  <si>
-    <t>133353840</t>
-  </si>
-  <si>
-    <t>133354160</t>
-  </si>
-  <si>
-    <t>133354166</t>
-  </si>
-  <si>
-    <t>133354459</t>
-  </si>
-  <si>
-    <t>133354465</t>
-  </si>
-  <si>
-    <t>133354494</t>
+    <t>128653378</t>
+  </si>
+  <si>
+    <t>128661616</t>
+  </si>
+  <si>
+    <t>129541541</t>
+  </si>
+  <si>
+    <t>130034567</t>
+  </si>
+  <si>
+    <t>130172403</t>
+  </si>
+  <si>
+    <t>130503447</t>
+  </si>
+  <si>
+    <t>130560487</t>
+  </si>
+  <si>
+    <t>130582620</t>
+  </si>
+  <si>
+    <t>130606892</t>
+  </si>
+  <si>
+    <t>130813733</t>
+  </si>
+  <si>
+    <t>130844879</t>
+  </si>
+  <si>
+    <t>131183380</t>
+  </si>
+  <si>
+    <t>131297102</t>
+  </si>
+  <si>
+    <t>131450107</t>
+  </si>
+  <si>
+    <t>131587976</t>
+  </si>
+  <si>
+    <t>131610022</t>
+  </si>
+  <si>
+    <t>131619067</t>
+  </si>
+  <si>
+    <t>131907546</t>
+  </si>
+  <si>
+    <t>131940171</t>
+  </si>
+  <si>
+    <t>131943658</t>
+  </si>
+  <si>
+    <t>132233129</t>
+  </si>
+  <si>
+    <t>132343404</t>
+  </si>
+  <si>
+    <t>132390396</t>
+  </si>
+  <si>
+    <t>132495323</t>
+  </si>
+  <si>
+    <t>132524254</t>
+  </si>
+  <si>
+    <t>132744340</t>
+  </si>
+  <si>
+    <t>132843449</t>
+  </si>
+  <si>
+    <t>132868658</t>
+  </si>
+  <si>
+    <t>132979293</t>
+  </si>
+  <si>
+    <t>133057623</t>
+  </si>
+  <si>
+    <t>133108599</t>
+  </si>
+  <si>
+    <t>133354703</t>
+  </si>
+  <si>
+    <t>133354966</t>
+  </si>
+  <si>
+    <t>133355270</t>
+  </si>
+  <si>
+    <t>133355464</t>
+  </si>
+  <si>
+    <t>133355593</t>
+  </si>
+  <si>
+    <t>133355764</t>
+  </si>
+  <si>
+    <t>133355907</t>
+  </si>
+  <si>
+    <t>133355982</t>
+  </si>
+  <si>
+    <t>133356055</t>
+  </si>
+  <si>
+    <t>133356092</t>
+  </si>
+  <si>
+    <t>133356293</t>
+  </si>
+  <si>
+    <t>133356315</t>
+  </si>
+  <si>
+    <t>133356512</t>
+  </si>
+  <si>
+    <t>133356635</t>
+  </si>
+  <si>
+    <t>133356831</t>
+  </si>
+  <si>
+    <t>133356979</t>
+  </si>
+  <si>
+    <t>133357003</t>
+  </si>
+  <si>
+    <t>133357224</t>
+  </si>
+  <si>
+    <t>133357246</t>
+  </si>
+  <si>
+    <t>133357551</t>
+  </si>
+  <si>
+    <t>133357847</t>
+  </si>
+  <si>
+    <t>133357923</t>
+  </si>
+  <si>
+    <t>133357993</t>
+  </si>
+  <si>
+    <t>133358201</t>
+  </si>
+  <si>
+    <t>133358317</t>
+  </si>
+  <si>
+    <t>133358367</t>
+  </si>
+  <si>
+    <t>133358467</t>
+  </si>
+  <si>
+    <t>133358891</t>
+  </si>
+  <si>
+    <t>133358893</t>
+  </si>
+  <si>
+    <t>133358897</t>
+  </si>
+  <si>
+    <t>133358999</t>
+  </si>
+  <si>
+    <t>133359008</t>
+  </si>
+  <si>
+    <t>133359088</t>
+  </si>
+  <si>
+    <t>133359595</t>
+  </si>
+  <si>
+    <t>133359768</t>
+  </si>
+  <si>
+    <t>133359865</t>
+  </si>
+  <si>
+    <t>133359907</t>
+  </si>
+  <si>
+    <t>133359916</t>
+  </si>
+  <si>
+    <t>133359934</t>
+  </si>
+  <si>
+    <t>133360185</t>
+  </si>
+  <si>
+    <t>133360217</t>
+  </si>
+  <si>
+    <t>133360316</t>
+  </si>
+  <si>
+    <t>133360369</t>
+  </si>
+  <si>
+    <t>133360532</t>
+  </si>
+  <si>
+    <t>133360981</t>
+  </si>
+  <si>
+    <t>133361215</t>
+  </si>
+  <si>
+    <t>133361434</t>
+  </si>
+  <si>
+    <t>133361499</t>
+  </si>
+  <si>
+    <t>133361666</t>
+  </si>
+  <si>
+    <t>133361769</t>
+  </si>
+  <si>
+    <t>133361939</t>
+  </si>
+  <si>
+    <t>133361997</t>
+  </si>
+  <si>
+    <t>133362275</t>
+  </si>
+  <si>
+    <t>133362341</t>
+  </si>
+  <si>
+    <t>133362560</t>
+  </si>
+  <si>
+    <t>133362962</t>
+  </si>
+  <si>
+    <t>133363256</t>
+  </si>
+  <si>
+    <t>133363323</t>
+  </si>
+  <si>
+    <t>133363396</t>
+  </si>
+  <si>
+    <t>133363825</t>
+  </si>
+  <si>
+    <t>133363948</t>
+  </si>
+  <si>
+    <t>133364008</t>
+  </si>
+  <si>
+    <t>133364267</t>
+  </si>
+  <si>
+    <t>133364540</t>
+  </si>
+  <si>
+    <t>133364686</t>
+  </si>
+  <si>
+    <t>133364879</t>
+  </si>
+  <si>
+    <t>133364947</t>
+  </si>
+  <si>
+    <t>133365045</t>
+  </si>
+  <si>
+    <t>133365241</t>
+  </si>
+  <si>
+    <t>133365332</t>
+  </si>
+  <si>
+    <t>133365396</t>
+  </si>
+  <si>
+    <t>133365545</t>
+  </si>
+  <si>
+    <t>133365662</t>
+  </si>
+  <si>
+    <t>133365693</t>
+  </si>
+  <si>
+    <t>133365763</t>
+  </si>
+  <si>
+    <t>133365837</t>
+  </si>
+  <si>
+    <t>133366192</t>
+  </si>
+  <si>
+    <t>133366197</t>
+  </si>
+  <si>
+    <t>133366312</t>
+  </si>
+  <si>
+    <t>133366327</t>
+  </si>
+  <si>
+    <t>133366339</t>
+  </si>
+  <si>
+    <t>133366369</t>
+  </si>
+  <si>
+    <t>133366468</t>
+  </si>
+  <si>
+    <t>133366483</t>
+  </si>
+  <si>
+    <t>133366528</t>
+  </si>
+  <si>
+    <t>133366701</t>
+  </si>
+  <si>
+    <t>133366783</t>
+  </si>
+  <si>
+    <t>133366936</t>
+  </si>
+  <si>
+    <t>133366979</t>
+  </si>
+  <si>
+    <t>133367025</t>
+  </si>
+  <si>
+    <t>133367251</t>
+  </si>
+  <si>
+    <t>133367344</t>
+  </si>
+  <si>
+    <t>133367389</t>
+  </si>
+  <si>
+    <t>133367639</t>
+  </si>
+  <si>
+    <t>133367731</t>
+  </si>
+  <si>
+    <t>133367775</t>
+  </si>
+  <si>
+    <t>133367776</t>
+  </si>
+  <si>
+    <t>133367896</t>
+  </si>
+  <si>
+    <t>133367998</t>
+  </si>
+  <si>
+    <t>133368140</t>
+  </si>
+  <si>
+    <t>133368176</t>
+  </si>
+  <si>
+    <t>133368185</t>
+  </si>
+  <si>
+    <t>133368544</t>
+  </si>
+  <si>
+    <t>133368638</t>
+  </si>
+  <si>
+    <t>133368854</t>
+  </si>
+  <si>
+    <t>133368875</t>
+  </si>
+  <si>
+    <t>133368968</t>
+  </si>
+  <si>
+    <t>133369040</t>
+  </si>
+  <si>
+    <t>133369264</t>
+  </si>
+  <si>
+    <t>133369314</t>
+  </si>
+  <si>
+    <t>133369595</t>
+  </si>
+  <si>
+    <t>133369620</t>
+  </si>
+  <si>
+    <t>133369748</t>
+  </si>
+  <si>
+    <t>133369856</t>
+  </si>
+  <si>
+    <t>133369917</t>
+  </si>
+  <si>
+    <t>133369947</t>
+  </si>
+  <si>
+    <t>133370166</t>
+  </si>
+  <si>
+    <t>133370222</t>
+  </si>
+  <si>
+    <t>133370234</t>
+  </si>
+  <si>
+    <t>133370377</t>
+  </si>
+  <si>
+    <t>133370449</t>
+  </si>
+  <si>
+    <t>133370513</t>
+  </si>
+  <si>
+    <t>133370540</t>
+  </si>
+  <si>
+    <t>133370669</t>
+  </si>
+  <si>
+    <t>133370788</t>
+  </si>
+  <si>
+    <t>133370811</t>
+  </si>
+  <si>
+    <t>133371244</t>
+  </si>
+  <si>
+    <t>133371300</t>
+  </si>
+  <si>
+    <t>133371365</t>
+  </si>
+  <si>
+    <t>133371613</t>
+  </si>
+  <si>
+    <t>133371707</t>
+  </si>
+  <si>
+    <t>133371708</t>
+  </si>
+  <si>
+    <t>133371751</t>
+  </si>
+  <si>
+    <t>133371858</t>
+  </si>
+  <si>
+    <t>133372265</t>
+  </si>
+  <si>
+    <t>133372370</t>
+  </si>
+  <si>
+    <t>133372378</t>
+  </si>
+  <si>
+    <t>133372422</t>
+  </si>
+  <si>
+    <t>133372433</t>
+  </si>
+  <si>
+    <t>133372461</t>
+  </si>
+  <si>
+    <t>133372513</t>
+  </si>
+  <si>
+    <t>133372612</t>
+  </si>
+  <si>
+    <t>133372619</t>
+  </si>
+  <si>
+    <t>133372625</t>
+  </si>
+  <si>
+    <t>133372638</t>
+  </si>
+  <si>
+    <t>133372717</t>
+  </si>
+  <si>
+    <t>133372747</t>
+  </si>
+  <si>
+    <t>133372808</t>
+  </si>
+  <si>
+    <t>133372818</t>
+  </si>
+  <si>
+    <t>133372833</t>
+  </si>
+  <si>
+    <t>133372920</t>
+  </si>
+  <si>
+    <t>133372952</t>
+  </si>
+  <si>
+    <t>133373094</t>
+  </si>
+  <si>
+    <t>133373215</t>
+  </si>
+  <si>
+    <t>133373234</t>
+  </si>
+  <si>
+    <t>133373236</t>
+  </si>
+  <si>
+    <t>133373368</t>
+  </si>
+  <si>
+    <t>133373499</t>
+  </si>
+  <si>
+    <t>133373627</t>
+  </si>
+  <si>
+    <t>133373720</t>
+  </si>
+  <si>
+    <t>133373806</t>
+  </si>
+  <si>
+    <t>133373870</t>
+  </si>
+  <si>
+    <t>133374014</t>
+  </si>
+  <si>
+    <t>133374238</t>
+  </si>
+  <si>
+    <t>133374243</t>
+  </si>
+  <si>
+    <t>133374399</t>
+  </si>
+  <si>
+    <t>133374424</t>
+  </si>
+  <si>
+    <t>133374489</t>
+  </si>
+  <si>
+    <t>133374522</t>
+  </si>
+  <si>
+    <t>133374529</t>
+  </si>
+  <si>
+    <t>133374862</t>
+  </si>
+  <si>
+    <t>133374940</t>
+  </si>
+  <si>
+    <t>133375356</t>
+  </si>
+  <si>
+    <t>133375387</t>
+  </si>
+  <si>
+    <t>133375395</t>
+  </si>
+  <si>
+    <t>133375471</t>
+  </si>
+  <si>
+    <t>133375499</t>
+  </si>
+  <si>
+    <t>133375520</t>
+  </si>
+  <si>
+    <t>133375521</t>
+  </si>
+  <si>
+    <t>133376093</t>
+  </si>
+  <si>
+    <t>133376331</t>
+  </si>
+  <si>
+    <t>133376479</t>
+  </si>
+  <si>
+    <t>133376575</t>
+  </si>
+  <si>
+    <t>133377125</t>
+  </si>
+  <si>
+    <t>133377185</t>
+  </si>
+  <si>
+    <t>133377200</t>
+  </si>
+  <si>
+    <t>133377268</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C193"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3155,8 +3233,294 @@
         <v>4</v>
       </c>
     </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C193" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33360396-0BB3-432C-8D67-4D0E348157C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BFE05B-8DFC-4E5B-BC34-FAE2370F2154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$178</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="182">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,709 +45,535 @@
     <t>.</t>
   </si>
   <si>
-    <t>129845174</t>
-  </si>
-  <si>
-    <t>129989880</t>
-  </si>
-  <si>
-    <t>130487849</t>
-  </si>
-  <si>
-    <t>130544584</t>
-  </si>
-  <si>
-    <t>130569548</t>
-  </si>
-  <si>
-    <t>130667559</t>
-  </si>
-  <si>
-    <t>130789878</t>
-  </si>
-  <si>
-    <t>130846036</t>
-  </si>
-  <si>
-    <t>130938488</t>
-  </si>
-  <si>
-    <t>131112325</t>
-  </si>
-  <si>
-    <t>131192428</t>
-  </si>
-  <si>
-    <t>131270606</t>
-  </si>
-  <si>
-    <t>131768719</t>
-  </si>
-  <si>
-    <t>131941453</t>
-  </si>
-  <si>
-    <t>131994067</t>
-  </si>
-  <si>
-    <t>132136061</t>
-  </si>
-  <si>
-    <t>132385330</t>
-  </si>
-  <si>
-    <t>132829489</t>
-  </si>
-  <si>
-    <t>133110635</t>
-  </si>
-  <si>
-    <t>133328334</t>
-  </si>
-  <si>
-    <t>133398408</t>
-  </si>
-  <si>
-    <t>133429216</t>
-  </si>
-  <si>
-    <t>133429247</t>
-  </si>
-  <si>
-    <t>133429290</t>
-  </si>
-  <si>
-    <t>133429298</t>
-  </si>
-  <si>
-    <t>133429367</t>
-  </si>
-  <si>
-    <t>133429373</t>
-  </si>
-  <si>
-    <t>133429396</t>
-  </si>
-  <si>
-    <t>133429397</t>
-  </si>
-  <si>
-    <t>133429449</t>
-  </si>
-  <si>
-    <t>133429499</t>
-  </si>
-  <si>
-    <t>133429582</t>
-  </si>
-  <si>
-    <t>133429716</t>
-  </si>
-  <si>
-    <t>133430198</t>
-  </si>
-  <si>
-    <t>133430287</t>
-  </si>
-  <si>
-    <t>133430391</t>
-  </si>
-  <si>
-    <t>133430503</t>
-  </si>
-  <si>
-    <t>133430672</t>
-  </si>
-  <si>
-    <t>133430771</t>
-  </si>
-  <si>
-    <t>133430976</t>
-  </si>
-  <si>
-    <t>133431061</t>
-  </si>
-  <si>
-    <t>133431104</t>
-  </si>
-  <si>
-    <t>133431245</t>
-  </si>
-  <si>
-    <t>133431265</t>
-  </si>
-  <si>
-    <t>133431275</t>
-  </si>
-  <si>
-    <t>133431410</t>
-  </si>
-  <si>
-    <t>133431638</t>
-  </si>
-  <si>
-    <t>133431666</t>
-  </si>
-  <si>
-    <t>133431738</t>
-  </si>
-  <si>
-    <t>133431801</t>
-  </si>
-  <si>
-    <t>133431919</t>
-  </si>
-  <si>
-    <t>133432111</t>
-  </si>
-  <si>
-    <t>133432129</t>
-  </si>
-  <si>
-    <t>133432141</t>
-  </si>
-  <si>
-    <t>133432176</t>
-  </si>
-  <si>
-    <t>133432299</t>
-  </si>
-  <si>
-    <t>133432526</t>
-  </si>
-  <si>
-    <t>133432787</t>
-  </si>
-  <si>
-    <t>133433168</t>
-  </si>
-  <si>
-    <t>133433261</t>
-  </si>
-  <si>
-    <t>133433378</t>
-  </si>
-  <si>
-    <t>133433708</t>
-  </si>
-  <si>
-    <t>133433770</t>
-  </si>
-  <si>
-    <t>133433985</t>
-  </si>
-  <si>
-    <t>133434393</t>
-  </si>
-  <si>
-    <t>133434416</t>
-  </si>
-  <si>
-    <t>133434438</t>
-  </si>
-  <si>
-    <t>133434546</t>
-  </si>
-  <si>
-    <t>133434682</t>
-  </si>
-  <si>
-    <t>133434789</t>
-  </si>
-  <si>
-    <t>133434803</t>
-  </si>
-  <si>
-    <t>133434973</t>
-  </si>
-  <si>
-    <t>133435628</t>
-  </si>
-  <si>
-    <t>133435677</t>
-  </si>
-  <si>
-    <t>133435717</t>
-  </si>
-  <si>
-    <t>133435777</t>
-  </si>
-  <si>
-    <t>133436007</t>
-  </si>
-  <si>
-    <t>133436186</t>
-  </si>
-  <si>
-    <t>133436240</t>
-  </si>
-  <si>
-    <t>133436271</t>
-  </si>
-  <si>
-    <t>133436344</t>
-  </si>
-  <si>
-    <t>133436382</t>
-  </si>
-  <si>
-    <t>133436626</t>
-  </si>
-  <si>
-    <t>133436790</t>
-  </si>
-  <si>
-    <t>133437022</t>
-  </si>
-  <si>
-    <t>133437067</t>
-  </si>
-  <si>
-    <t>133437178</t>
-  </si>
-  <si>
-    <t>133437266</t>
-  </si>
-  <si>
-    <t>133437334</t>
-  </si>
-  <si>
-    <t>133437397</t>
-  </si>
-  <si>
-    <t>133437596</t>
-  </si>
-  <si>
-    <t>133437820</t>
-  </si>
-  <si>
-    <t>133437823</t>
-  </si>
-  <si>
-    <t>133437831</t>
-  </si>
-  <si>
-    <t>133438020</t>
-  </si>
-  <si>
-    <t>133438092</t>
-  </si>
-  <si>
-    <t>133438096</t>
-  </si>
-  <si>
-    <t>133438180</t>
-  </si>
-  <si>
-    <t>133438299</t>
-  </si>
-  <si>
-    <t>133438492</t>
-  </si>
-  <si>
-    <t>133438528</t>
-  </si>
-  <si>
-    <t>133438543</t>
-  </si>
-  <si>
-    <t>133438626</t>
-  </si>
-  <si>
-    <t>133438635</t>
-  </si>
-  <si>
-    <t>133438730</t>
-  </si>
-  <si>
-    <t>133438848</t>
-  </si>
-  <si>
-    <t>133438949</t>
-  </si>
-  <si>
-    <t>133439001</t>
-  </si>
-  <si>
-    <t>133439059</t>
-  </si>
-  <si>
-    <t>133439123</t>
-  </si>
-  <si>
-    <t>133439368</t>
-  </si>
-  <si>
-    <t>133439570</t>
-  </si>
-  <si>
-    <t>133439641</t>
-  </si>
-  <si>
-    <t>133439711</t>
-  </si>
-  <si>
-    <t>133439799</t>
-  </si>
-  <si>
-    <t>133440234</t>
-  </si>
-  <si>
-    <t>133440240</t>
-  </si>
-  <si>
-    <t>133440275</t>
-  </si>
-  <si>
-    <t>133440293</t>
-  </si>
-  <si>
-    <t>133440385</t>
-  </si>
-  <si>
-    <t>133440527</t>
-  </si>
-  <si>
-    <t>133440638</t>
-  </si>
-  <si>
-    <t>133440684</t>
-  </si>
-  <si>
-    <t>133440737</t>
-  </si>
-  <si>
-    <t>133440753</t>
-  </si>
-  <si>
-    <t>133440821</t>
-  </si>
-  <si>
-    <t>133441245</t>
-  </si>
-  <si>
-    <t>133441410</t>
-  </si>
-  <si>
-    <t>133441471</t>
-  </si>
-  <si>
-    <t>133441484</t>
-  </si>
-  <si>
-    <t>133441515</t>
-  </si>
-  <si>
-    <t>133441611</t>
-  </si>
-  <si>
-    <t>133441635</t>
-  </si>
-  <si>
-    <t>133441819</t>
-  </si>
-  <si>
-    <t>133441863</t>
-  </si>
-  <si>
-    <t>133441989</t>
-  </si>
-  <si>
-    <t>133441993</t>
-  </si>
-  <si>
-    <t>133442140</t>
-  </si>
-  <si>
-    <t>133442155</t>
-  </si>
-  <si>
-    <t>133442210</t>
-  </si>
-  <si>
-    <t>133442238</t>
-  </si>
-  <si>
-    <t>133442252</t>
-  </si>
-  <si>
-    <t>133442301</t>
-  </si>
-  <si>
-    <t>133442432</t>
-  </si>
-  <si>
-    <t>133442442</t>
-  </si>
-  <si>
-    <t>133442495</t>
-  </si>
-  <si>
-    <t>133442515</t>
-  </si>
-  <si>
-    <t>133442793</t>
-  </si>
-  <si>
-    <t>133442827</t>
-  </si>
-  <si>
-    <t>133442846</t>
-  </si>
-  <si>
-    <t>133443016</t>
-  </si>
-  <si>
-    <t>133443190</t>
-  </si>
-  <si>
-    <t>133443734</t>
-  </si>
-  <si>
-    <t>133443888</t>
-  </si>
-  <si>
-    <t>133443956</t>
-  </si>
-  <si>
-    <t>133444019</t>
-  </si>
-  <si>
-    <t>133444021</t>
-  </si>
-  <si>
-    <t>133444053</t>
-  </si>
-  <si>
-    <t>133444063</t>
-  </si>
-  <si>
-    <t>133444103</t>
-  </si>
-  <si>
-    <t>133444120</t>
-  </si>
-  <si>
-    <t>133444598</t>
-  </si>
-  <si>
-    <t>133444654</t>
-  </si>
-  <si>
-    <t>133444656</t>
-  </si>
-  <si>
-    <t>133444733</t>
-  </si>
-  <si>
-    <t>133444768</t>
-  </si>
-  <si>
-    <t>133444832</t>
-  </si>
-  <si>
-    <t>133444888</t>
-  </si>
-  <si>
-    <t>133444917</t>
-  </si>
-  <si>
-    <t>133444953</t>
-  </si>
-  <si>
-    <t>133445033</t>
-  </si>
-  <si>
-    <t>133445047</t>
-  </si>
-  <si>
-    <t>133445211</t>
-  </si>
-  <si>
-    <t>133445250</t>
-  </si>
-  <si>
-    <t>133445325</t>
-  </si>
-  <si>
-    <t>133445477</t>
-  </si>
-  <si>
-    <t>133445521</t>
-  </si>
-  <si>
-    <t>133445597</t>
-  </si>
-  <si>
-    <t>133445690</t>
-  </si>
-  <si>
-    <t>133445784</t>
-  </si>
-  <si>
-    <t>133445788</t>
-  </si>
-  <si>
-    <t>133445795</t>
-  </si>
-  <si>
-    <t>133445800</t>
-  </si>
-  <si>
-    <t>133445908</t>
-  </si>
-  <si>
-    <t>133445911</t>
-  </si>
-  <si>
-    <t>133445916</t>
-  </si>
-  <si>
-    <t>133446130</t>
-  </si>
-  <si>
-    <t>133446166</t>
-  </si>
-  <si>
-    <t>133446481</t>
-  </si>
-  <si>
-    <t>133446620</t>
-  </si>
-  <si>
-    <t>133446701</t>
-  </si>
-  <si>
-    <t>133446914</t>
-  </si>
-  <si>
-    <t>133446980</t>
-  </si>
-  <si>
-    <t>133447104</t>
-  </si>
-  <si>
-    <t>133447129</t>
-  </si>
-  <si>
-    <t>133447132</t>
-  </si>
-  <si>
-    <t>133447397</t>
-  </si>
-  <si>
-    <t>133447767</t>
-  </si>
-  <si>
-    <t>133447812</t>
-  </si>
-  <si>
-    <t>133447905</t>
-  </si>
-  <si>
-    <t>133448039</t>
-  </si>
-  <si>
-    <t>133448289</t>
-  </si>
-  <si>
-    <t>133448435</t>
-  </si>
-  <si>
-    <t>133448480</t>
-  </si>
-  <si>
-    <t>133448584</t>
-  </si>
-  <si>
-    <t>133448714</t>
-  </si>
-  <si>
-    <t>133448730</t>
-  </si>
-  <si>
-    <t>133448734</t>
-  </si>
-  <si>
-    <t>133448869</t>
-  </si>
-  <si>
-    <t>133448872</t>
-  </si>
-  <si>
-    <t>133448999</t>
-  </si>
-  <si>
-    <t>133449007</t>
-  </si>
-  <si>
-    <t>133449051</t>
-  </si>
-  <si>
-    <t>133449087</t>
-  </si>
-  <si>
-    <t>133449430</t>
-  </si>
-  <si>
-    <t>133449537</t>
-  </si>
-  <si>
-    <t>133449664</t>
-  </si>
-  <si>
-    <t>133449684</t>
-  </si>
-  <si>
-    <t>133449685</t>
-  </si>
-  <si>
-    <t>133449704</t>
-  </si>
-  <si>
-    <t>133449744</t>
-  </si>
-  <si>
-    <t>133449886</t>
-  </si>
-  <si>
-    <t>133450081</t>
-  </si>
-  <si>
-    <t>133450083</t>
-  </si>
-  <si>
-    <t>133450210</t>
-  </si>
-  <si>
-    <t>133450311</t>
-  </si>
-  <si>
-    <t>133450358</t>
-  </si>
-  <si>
-    <t>133450408</t>
-  </si>
-  <si>
-    <t>133450450</t>
-  </si>
-  <si>
-    <t>133450942</t>
-  </si>
-  <si>
-    <t>133451496</t>
-  </si>
-  <si>
-    <t>133451734</t>
-  </si>
-  <si>
-    <t>133451763</t>
-  </si>
-  <si>
-    <t>133451958</t>
-  </si>
-  <si>
-    <t>133452205</t>
+    <t>128918011</t>
+  </si>
+  <si>
+    <t>129138010</t>
+  </si>
+  <si>
+    <t>129583154</t>
+  </si>
+  <si>
+    <t>129791922</t>
+  </si>
+  <si>
+    <t>129823846</t>
+  </si>
+  <si>
+    <t>129824309</t>
+  </si>
+  <si>
+    <t>130660161</t>
+  </si>
+  <si>
+    <t>130866480</t>
+  </si>
+  <si>
+    <t>130967631</t>
+  </si>
+  <si>
+    <t>130999601</t>
+  </si>
+  <si>
+    <t>131107827</t>
+  </si>
+  <si>
+    <t>131346259</t>
+  </si>
+  <si>
+    <t>131424584</t>
+  </si>
+  <si>
+    <t>131795185</t>
+  </si>
+  <si>
+    <t>132108008</t>
+  </si>
+  <si>
+    <t>132199784</t>
+  </si>
+  <si>
+    <t>132395686</t>
+  </si>
+  <si>
+    <t>132683497</t>
+  </si>
+  <si>
+    <t>132955608</t>
+  </si>
+  <si>
+    <t>133452580</t>
+  </si>
+  <si>
+    <t>133452601</t>
+  </si>
+  <si>
+    <t>133452626</t>
+  </si>
+  <si>
+    <t>133452657</t>
+  </si>
+  <si>
+    <t>133452913</t>
+  </si>
+  <si>
+    <t>133453387</t>
+  </si>
+  <si>
+    <t>133453500</t>
+  </si>
+  <si>
+    <t>133453538</t>
+  </si>
+  <si>
+    <t>133453673</t>
+  </si>
+  <si>
+    <t>133453692</t>
+  </si>
+  <si>
+    <t>133453894</t>
+  </si>
+  <si>
+    <t>133454104</t>
+  </si>
+  <si>
+    <t>133454182</t>
+  </si>
+  <si>
+    <t>133454480</t>
+  </si>
+  <si>
+    <t>133454569</t>
+  </si>
+  <si>
+    <t>133454662</t>
+  </si>
+  <si>
+    <t>133454913</t>
+  </si>
+  <si>
+    <t>133455117</t>
+  </si>
+  <si>
+    <t>133455284</t>
+  </si>
+  <si>
+    <t>133455835</t>
+  </si>
+  <si>
+    <t>133455944</t>
+  </si>
+  <si>
+    <t>133456185</t>
+  </si>
+  <si>
+    <t>133456228</t>
+  </si>
+  <si>
+    <t>133456231</t>
+  </si>
+  <si>
+    <t>133456440</t>
+  </si>
+  <si>
+    <t>133456533</t>
+  </si>
+  <si>
+    <t>133456693</t>
+  </si>
+  <si>
+    <t>133456721</t>
+  </si>
+  <si>
+    <t>133456807</t>
+  </si>
+  <si>
+    <t>133456825</t>
+  </si>
+  <si>
+    <t>133456896</t>
+  </si>
+  <si>
+    <t>133456971</t>
+  </si>
+  <si>
+    <t>133456982</t>
+  </si>
+  <si>
+    <t>133457105</t>
+  </si>
+  <si>
+    <t>133457125</t>
+  </si>
+  <si>
+    <t>133457515</t>
+  </si>
+  <si>
+    <t>133457558</t>
+  </si>
+  <si>
+    <t>133457599</t>
+  </si>
+  <si>
+    <t>133457689</t>
+  </si>
+  <si>
+    <t>133457756</t>
+  </si>
+  <si>
+    <t>133458032</t>
+  </si>
+  <si>
+    <t>133458157</t>
+  </si>
+  <si>
+    <t>133458183</t>
+  </si>
+  <si>
+    <t>133458209</t>
+  </si>
+  <si>
+    <t>133458521</t>
+  </si>
+  <si>
+    <t>133458636</t>
+  </si>
+  <si>
+    <t>133458855</t>
+  </si>
+  <si>
+    <t>133459145</t>
+  </si>
+  <si>
+    <t>133459228</t>
+  </si>
+  <si>
+    <t>133459349</t>
+  </si>
+  <si>
+    <t>133459498</t>
+  </si>
+  <si>
+    <t>133459504</t>
+  </si>
+  <si>
+    <t>133459648</t>
+  </si>
+  <si>
+    <t>133459783</t>
+  </si>
+  <si>
+    <t>133459923</t>
+  </si>
+  <si>
+    <t>133460459</t>
+  </si>
+  <si>
+    <t>133460460</t>
+  </si>
+  <si>
+    <t>133460515</t>
+  </si>
+  <si>
+    <t>133460778</t>
+  </si>
+  <si>
+    <t>133460927</t>
+  </si>
+  <si>
+    <t>133461005</t>
+  </si>
+  <si>
+    <t>133461007</t>
+  </si>
+  <si>
+    <t>133461046</t>
+  </si>
+  <si>
+    <t>133461114</t>
+  </si>
+  <si>
+    <t>133461193</t>
+  </si>
+  <si>
+    <t>133461532</t>
+  </si>
+  <si>
+    <t>133461831</t>
+  </si>
+  <si>
+    <t>133462246</t>
+  </si>
+  <si>
+    <t>133462294</t>
+  </si>
+  <si>
+    <t>133462361</t>
+  </si>
+  <si>
+    <t>133462463</t>
+  </si>
+  <si>
+    <t>133462516</t>
+  </si>
+  <si>
+    <t>133462558</t>
+  </si>
+  <si>
+    <t>133462719</t>
+  </si>
+  <si>
+    <t>133462842</t>
+  </si>
+  <si>
+    <t>133462874</t>
+  </si>
+  <si>
+    <t>133463006</t>
+  </si>
+  <si>
+    <t>133463021</t>
+  </si>
+  <si>
+    <t>133463041</t>
+  </si>
+  <si>
+    <t>133463125</t>
+  </si>
+  <si>
+    <t>133463133</t>
+  </si>
+  <si>
+    <t>133463331</t>
+  </si>
+  <si>
+    <t>133463778</t>
+  </si>
+  <si>
+    <t>133463971</t>
+  </si>
+  <si>
+    <t>133464153</t>
+  </si>
+  <si>
+    <t>133464195</t>
+  </si>
+  <si>
+    <t>133464292</t>
+  </si>
+  <si>
+    <t>133464344</t>
+  </si>
+  <si>
+    <t>133464355</t>
+  </si>
+  <si>
+    <t>133464541</t>
+  </si>
+  <si>
+    <t>133464654</t>
+  </si>
+  <si>
+    <t>133464680</t>
+  </si>
+  <si>
+    <t>133464793</t>
+  </si>
+  <si>
+    <t>133465004</t>
+  </si>
+  <si>
+    <t>133465201</t>
+  </si>
+  <si>
+    <t>133465283</t>
+  </si>
+  <si>
+    <t>133465379</t>
+  </si>
+  <si>
+    <t>133466077</t>
+  </si>
+  <si>
+    <t>133466352</t>
+  </si>
+  <si>
+    <t>133466517</t>
+  </si>
+  <si>
+    <t>133466562</t>
+  </si>
+  <si>
+    <t>133466577</t>
+  </si>
+  <si>
+    <t>133466729</t>
+  </si>
+  <si>
+    <t>133466798</t>
+  </si>
+  <si>
+    <t>133466895</t>
+  </si>
+  <si>
+    <t>133466903</t>
+  </si>
+  <si>
+    <t>133466976</t>
+  </si>
+  <si>
+    <t>133467174</t>
+  </si>
+  <si>
+    <t>133467194</t>
+  </si>
+  <si>
+    <t>133467266</t>
+  </si>
+  <si>
+    <t>133467556</t>
+  </si>
+  <si>
+    <t>133467572</t>
+  </si>
+  <si>
+    <t>133467643</t>
+  </si>
+  <si>
+    <t>133467800</t>
+  </si>
+  <si>
+    <t>133467875</t>
+  </si>
+  <si>
+    <t>133468052</t>
+  </si>
+  <si>
+    <t>133468709</t>
+  </si>
+  <si>
+    <t>133468764</t>
+  </si>
+  <si>
+    <t>133468809</t>
+  </si>
+  <si>
+    <t>133468881</t>
+  </si>
+  <si>
+    <t>133468962</t>
+  </si>
+  <si>
+    <t>133469184</t>
+  </si>
+  <si>
+    <t>133469199</t>
+  </si>
+  <si>
+    <t>133469277</t>
+  </si>
+  <si>
+    <t>133469490</t>
+  </si>
+  <si>
+    <t>133469496</t>
+  </si>
+  <si>
+    <t>133469608</t>
+  </si>
+  <si>
+    <t>133469657</t>
+  </si>
+  <si>
+    <t>133469732</t>
+  </si>
+  <si>
+    <t>133469842</t>
+  </si>
+  <si>
+    <t>133469850</t>
+  </si>
+  <si>
+    <t>133469887</t>
+  </si>
+  <si>
+    <t>133470163</t>
+  </si>
+  <si>
+    <t>133470186</t>
+  </si>
+  <si>
+    <t>133470286</t>
+  </si>
+  <si>
+    <t>133470318</t>
+  </si>
+  <si>
+    <t>133470834</t>
+  </si>
+  <si>
+    <t>133470839</t>
+  </si>
+  <si>
+    <t>133470840</t>
+  </si>
+  <si>
+    <t>133471037</t>
+  </si>
+  <si>
+    <t>133471180</t>
+  </si>
+  <si>
+    <t>133471310</t>
+  </si>
+  <si>
+    <t>133471332</t>
+  </si>
+  <si>
+    <t>133471364</t>
+  </si>
+  <si>
+    <t>133471379</t>
+  </si>
+  <si>
+    <t>133471387</t>
+  </si>
+  <si>
+    <t>133471604</t>
+  </si>
+  <si>
+    <t>133471731</t>
+  </si>
+  <si>
+    <t>133471962</t>
+  </si>
+  <si>
+    <t>133471992</t>
+  </si>
+  <si>
+    <t>133472010</t>
+  </si>
+  <si>
+    <t>133472093</t>
+  </si>
+  <si>
+    <t>133472117</t>
+  </si>
+  <si>
+    <t>133472827</t>
+  </si>
+  <si>
+    <t>133472836</t>
+  </si>
+  <si>
+    <t>133473127</t>
+  </si>
+  <si>
+    <t>133473160</t>
+  </si>
+  <si>
+    <t>133473646</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3119,646 +2945,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B200" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B213" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B214" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C214" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B215" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B216" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B220" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B223" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C178" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33690C86-4F55-4A36-9E00-024873F16917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C96D49B-8D19-45D3-8B5F-AE1BE7FAFB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$185</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="189">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,526 +45,556 @@
     <t>.</t>
   </si>
   <si>
-    <t>129133275</t>
-  </si>
-  <si>
-    <t>129743881</t>
-  </si>
-  <si>
-    <t>130028274</t>
-  </si>
-  <si>
-    <t>130187373</t>
-  </si>
-  <si>
-    <t>130423302</t>
-  </si>
-  <si>
-    <t>130581473</t>
-  </si>
-  <si>
-    <t>130691761</t>
-  </si>
-  <si>
-    <t>130724946</t>
-  </si>
-  <si>
-    <t>130767356</t>
-  </si>
-  <si>
-    <t>130857815</t>
-  </si>
-  <si>
-    <t>131265508</t>
-  </si>
-  <si>
-    <t>131276622</t>
-  </si>
-  <si>
-    <t>131490925</t>
-  </si>
-  <si>
-    <t>131525510</t>
-  </si>
-  <si>
-    <t>131555519</t>
-  </si>
-  <si>
-    <t>131669074</t>
-  </si>
-  <si>
-    <t>132674364</t>
-  </si>
-  <si>
-    <t>132774618</t>
-  </si>
-  <si>
-    <t>133474296</t>
-  </si>
-  <si>
-    <t>133474631</t>
-  </si>
-  <si>
-    <t>133474650</t>
-  </si>
-  <si>
-    <t>133474667</t>
-  </si>
-  <si>
-    <t>133474698</t>
-  </si>
-  <si>
-    <t>133475035</t>
-  </si>
-  <si>
-    <t>133475052</t>
-  </si>
-  <si>
-    <t>133475179</t>
-  </si>
-  <si>
-    <t>133475186</t>
-  </si>
-  <si>
-    <t>133475783</t>
-  </si>
-  <si>
-    <t>133475895</t>
-  </si>
-  <si>
-    <t>133476031</t>
-  </si>
-  <si>
-    <t>133476396</t>
-  </si>
-  <si>
-    <t>133476433</t>
-  </si>
-  <si>
-    <t>133476468</t>
-  </si>
-  <si>
-    <t>133476484</t>
-  </si>
-  <si>
-    <t>133476650</t>
-  </si>
-  <si>
-    <t>133476857</t>
-  </si>
-  <si>
-    <t>133476914</t>
-  </si>
-  <si>
-    <t>133476972</t>
-  </si>
-  <si>
-    <t>133477010</t>
-  </si>
-  <si>
-    <t>133477013</t>
-  </si>
-  <si>
-    <t>133477023</t>
-  </si>
-  <si>
-    <t>133477282</t>
-  </si>
-  <si>
-    <t>133477330</t>
-  </si>
-  <si>
-    <t>133477490</t>
-  </si>
-  <si>
-    <t>133477623</t>
-  </si>
-  <si>
-    <t>133477717</t>
-  </si>
-  <si>
-    <t>133477750</t>
-  </si>
-  <si>
-    <t>133477994</t>
-  </si>
-  <si>
-    <t>133478228</t>
-  </si>
-  <si>
-    <t>133478359</t>
-  </si>
-  <si>
-    <t>133478502</t>
-  </si>
-  <si>
-    <t>133478613</t>
-  </si>
-  <si>
-    <t>133478620</t>
-  </si>
-  <si>
-    <t>133479077</t>
-  </si>
-  <si>
-    <t>133479247</t>
-  </si>
-  <si>
-    <t>133479430</t>
-  </si>
-  <si>
-    <t>133479528</t>
-  </si>
-  <si>
-    <t>133479943</t>
-  </si>
-  <si>
-    <t>133480166</t>
-  </si>
-  <si>
-    <t>133480356</t>
-  </si>
-  <si>
-    <t>133480358</t>
-  </si>
-  <si>
-    <t>133480418</t>
-  </si>
-  <si>
-    <t>133480457</t>
-  </si>
-  <si>
-    <t>133480527</t>
-  </si>
-  <si>
-    <t>133480760</t>
-  </si>
-  <si>
-    <t>133480810</t>
-  </si>
-  <si>
-    <t>133481024</t>
-  </si>
-  <si>
-    <t>133481159</t>
-  </si>
-  <si>
-    <t>133481399</t>
-  </si>
-  <si>
-    <t>133481549</t>
-  </si>
-  <si>
-    <t>133481617</t>
-  </si>
-  <si>
-    <t>133481744</t>
-  </si>
-  <si>
-    <t>133481896</t>
-  </si>
-  <si>
-    <t>133481981</t>
-  </si>
-  <si>
-    <t>133481998</t>
-  </si>
-  <si>
-    <t>133482003</t>
-  </si>
-  <si>
-    <t>133482048</t>
-  </si>
-  <si>
-    <t>133482154</t>
-  </si>
-  <si>
-    <t>133482263</t>
-  </si>
-  <si>
-    <t>133482428</t>
-  </si>
-  <si>
-    <t>133482671</t>
-  </si>
-  <si>
-    <t>133482714</t>
-  </si>
-  <si>
-    <t>133482725</t>
-  </si>
-  <si>
-    <t>133482813</t>
-  </si>
-  <si>
-    <t>133482991</t>
-  </si>
-  <si>
-    <t>133483003</t>
-  </si>
-  <si>
-    <t>133483056</t>
-  </si>
-  <si>
-    <t>133483115</t>
-  </si>
-  <si>
-    <t>133483183</t>
-  </si>
-  <si>
-    <t>133483282</t>
-  </si>
-  <si>
-    <t>133483385</t>
-  </si>
-  <si>
-    <t>133483414</t>
-  </si>
-  <si>
-    <t>133483589</t>
-  </si>
-  <si>
-    <t>133483723</t>
-  </si>
-  <si>
-    <t>133484173</t>
-  </si>
-  <si>
-    <t>133484358</t>
-  </si>
-  <si>
-    <t>133484454</t>
-  </si>
-  <si>
-    <t>133484466</t>
-  </si>
-  <si>
-    <t>133484500</t>
-  </si>
-  <si>
-    <t>133484549</t>
-  </si>
-  <si>
-    <t>133484657</t>
-  </si>
-  <si>
-    <t>133484751</t>
-  </si>
-  <si>
-    <t>133484831</t>
-  </si>
-  <si>
-    <t>133485005</t>
-  </si>
-  <si>
-    <t>133485664</t>
-  </si>
-  <si>
-    <t>133486075</t>
-  </si>
-  <si>
-    <t>133486130</t>
-  </si>
-  <si>
-    <t>133486367</t>
-  </si>
-  <si>
-    <t>133486551</t>
-  </si>
-  <si>
-    <t>133486631</t>
-  </si>
-  <si>
-    <t>133486668</t>
-  </si>
-  <si>
-    <t>133486974</t>
-  </si>
-  <si>
-    <t>133487059</t>
-  </si>
-  <si>
-    <t>133487088</t>
-  </si>
-  <si>
-    <t>133487301</t>
-  </si>
-  <si>
-    <t>133487501</t>
-  </si>
-  <si>
-    <t>133487690</t>
-  </si>
-  <si>
-    <t>133487801</t>
-  </si>
-  <si>
-    <t>133487932</t>
-  </si>
-  <si>
-    <t>133487933</t>
-  </si>
-  <si>
-    <t>133487972</t>
-  </si>
-  <si>
-    <t>133488001</t>
-  </si>
-  <si>
-    <t>133488003</t>
-  </si>
-  <si>
-    <t>133488008</t>
-  </si>
-  <si>
-    <t>133488122</t>
-  </si>
-  <si>
-    <t>133488461</t>
-  </si>
-  <si>
-    <t>133488499</t>
-  </si>
-  <si>
-    <t>133488688</t>
-  </si>
-  <si>
-    <t>133488722</t>
-  </si>
-  <si>
-    <t>133488808</t>
-  </si>
-  <si>
-    <t>133489043</t>
-  </si>
-  <si>
-    <t>133489136</t>
-  </si>
-  <si>
-    <t>133489202</t>
-  </si>
-  <si>
-    <t>133489203</t>
-  </si>
-  <si>
-    <t>133489435</t>
-  </si>
-  <si>
-    <t>133489455</t>
-  </si>
-  <si>
-    <t>133489689</t>
-  </si>
-  <si>
-    <t>133489819</t>
-  </si>
-  <si>
-    <t>133490301</t>
-  </si>
-  <si>
-    <t>133490636</t>
-  </si>
-  <si>
-    <t>133490813</t>
-  </si>
-  <si>
-    <t>133490941</t>
-  </si>
-  <si>
-    <t>133491007</t>
-  </si>
-  <si>
-    <t>133491014</t>
-  </si>
-  <si>
-    <t>133491047</t>
-  </si>
-  <si>
-    <t>133491304</t>
-  </si>
-  <si>
-    <t>133491642</t>
-  </si>
-  <si>
-    <t>133491663</t>
-  </si>
-  <si>
-    <t>133491818</t>
-  </si>
-  <si>
-    <t>133491852</t>
-  </si>
-  <si>
-    <t>133491868</t>
-  </si>
-  <si>
-    <t>133491931</t>
-  </si>
-  <si>
-    <t>133492019</t>
-  </si>
-  <si>
-    <t>133492044</t>
-  </si>
-  <si>
-    <t>133492243</t>
-  </si>
-  <si>
-    <t>133492418</t>
-  </si>
-  <si>
-    <t>133492495</t>
-  </si>
-  <si>
-    <t>133492655</t>
-  </si>
-  <si>
-    <t>133492775</t>
-  </si>
-  <si>
-    <t>133492952</t>
-  </si>
-  <si>
-    <t>133493022</t>
-  </si>
-  <si>
-    <t>133493063</t>
-  </si>
-  <si>
-    <t>133493303</t>
-  </si>
-  <si>
-    <t>133493592</t>
-  </si>
-  <si>
-    <t>133493802</t>
-  </si>
-  <si>
-    <t>133493839</t>
-  </si>
-  <si>
-    <t>133493911</t>
-  </si>
-  <si>
-    <t>133494057</t>
-  </si>
-  <si>
-    <t>133494096</t>
-  </si>
-  <si>
-    <t>133494278</t>
-  </si>
-  <si>
-    <t>133494454</t>
-  </si>
-  <si>
-    <t>133494499</t>
-  </si>
-  <si>
-    <t>133494646</t>
-  </si>
-  <si>
-    <t>133495927</t>
+    <t>129136705</t>
+  </si>
+  <si>
+    <t>129389753</t>
+  </si>
+  <si>
+    <t>129476140</t>
+  </si>
+  <si>
+    <t>129572959</t>
+  </si>
+  <si>
+    <t>129654819</t>
+  </si>
+  <si>
+    <t>129764998</t>
+  </si>
+  <si>
+    <t>130028459</t>
+  </si>
+  <si>
+    <t>130109355</t>
+  </si>
+  <si>
+    <t>130162820</t>
+  </si>
+  <si>
+    <t>130302954</t>
+  </si>
+  <si>
+    <t>130725583</t>
+  </si>
+  <si>
+    <t>131577416</t>
+  </si>
+  <si>
+    <t>131693335</t>
+  </si>
+  <si>
+    <t>132082254</t>
+  </si>
+  <si>
+    <t>132433268</t>
+  </si>
+  <si>
+    <t>132620076</t>
+  </si>
+  <si>
+    <t>132849476</t>
+  </si>
+  <si>
+    <t>132877909</t>
+  </si>
+  <si>
+    <t>133335332</t>
+  </si>
+  <si>
+    <t>133403303</t>
+  </si>
+  <si>
+    <t>133520636</t>
+  </si>
+  <si>
+    <t>133520645</t>
+  </si>
+  <si>
+    <t>133520676</t>
+  </si>
+  <si>
+    <t>133520692</t>
+  </si>
+  <si>
+    <t>133521208</t>
+  </si>
+  <si>
+    <t>133521321</t>
+  </si>
+  <si>
+    <t>133521666</t>
+  </si>
+  <si>
+    <t>133521675</t>
+  </si>
+  <si>
+    <t>133521974</t>
+  </si>
+  <si>
+    <t>133522094</t>
+  </si>
+  <si>
+    <t>133522139</t>
+  </si>
+  <si>
+    <t>133522380</t>
+  </si>
+  <si>
+    <t>133522525</t>
+  </si>
+  <si>
+    <t>133522603</t>
+  </si>
+  <si>
+    <t>133522613</t>
+  </si>
+  <si>
+    <t>133522630</t>
+  </si>
+  <si>
+    <t>133522724</t>
+  </si>
+  <si>
+    <t>133522761</t>
+  </si>
+  <si>
+    <t>133522822</t>
+  </si>
+  <si>
+    <t>133522858</t>
+  </si>
+  <si>
+    <t>133523010</t>
+  </si>
+  <si>
+    <t>133523909</t>
+  </si>
+  <si>
+    <t>133523953</t>
+  </si>
+  <si>
+    <t>133524004</t>
+  </si>
+  <si>
+    <t>133524286</t>
+  </si>
+  <si>
+    <t>133524688</t>
+  </si>
+  <si>
+    <t>133525002</t>
+  </si>
+  <si>
+    <t>133525069</t>
+  </si>
+  <si>
+    <t>133525139</t>
+  </si>
+  <si>
+    <t>133525144</t>
+  </si>
+  <si>
+    <t>133525236</t>
+  </si>
+  <si>
+    <t>133525705</t>
+  </si>
+  <si>
+    <t>133526005</t>
+  </si>
+  <si>
+    <t>133526112</t>
+  </si>
+  <si>
+    <t>133526211</t>
+  </si>
+  <si>
+    <t>133526617</t>
+  </si>
+  <si>
+    <t>133526689</t>
+  </si>
+  <si>
+    <t>133526981</t>
+  </si>
+  <si>
+    <t>133527423</t>
+  </si>
+  <si>
+    <t>133527474</t>
+  </si>
+  <si>
+    <t>133527700</t>
+  </si>
+  <si>
+    <t>133527815</t>
+  </si>
+  <si>
+    <t>133528222</t>
+  </si>
+  <si>
+    <t>133528389</t>
+  </si>
+  <si>
+    <t>133528485</t>
+  </si>
+  <si>
+    <t>133528549</t>
+  </si>
+  <si>
+    <t>133528787</t>
+  </si>
+  <si>
+    <t>133528879</t>
+  </si>
+  <si>
+    <t>133529169</t>
+  </si>
+  <si>
+    <t>133529377</t>
+  </si>
+  <si>
+    <t>133529957</t>
+  </si>
+  <si>
+    <t>133530076</t>
+  </si>
+  <si>
+    <t>133530195</t>
+  </si>
+  <si>
+    <t>133530602</t>
+  </si>
+  <si>
+    <t>133530801</t>
+  </si>
+  <si>
+    <t>133530889</t>
+  </si>
+  <si>
+    <t>133530913</t>
+  </si>
+  <si>
+    <t>133530955</t>
+  </si>
+  <si>
+    <t>133530959</t>
+  </si>
+  <si>
+    <t>133531209</t>
+  </si>
+  <si>
+    <t>133531405</t>
+  </si>
+  <si>
+    <t>133531484</t>
+  </si>
+  <si>
+    <t>133531931</t>
+  </si>
+  <si>
+    <t>133531949</t>
+  </si>
+  <si>
+    <t>133532143</t>
+  </si>
+  <si>
+    <t>133532164</t>
+  </si>
+  <si>
+    <t>133532177</t>
+  </si>
+  <si>
+    <t>133532863</t>
+  </si>
+  <si>
+    <t>133533076</t>
+  </si>
+  <si>
+    <t>133533176</t>
+  </si>
+  <si>
+    <t>133533314</t>
+  </si>
+  <si>
+    <t>133533383</t>
+  </si>
+  <si>
+    <t>133533502</t>
+  </si>
+  <si>
+    <t>133533863</t>
+  </si>
+  <si>
+    <t>133534060</t>
+  </si>
+  <si>
+    <t>133534098</t>
+  </si>
+  <si>
+    <t>133534216</t>
+  </si>
+  <si>
+    <t>133534309</t>
+  </si>
+  <si>
+    <t>133534439</t>
+  </si>
+  <si>
+    <t>133534511</t>
+  </si>
+  <si>
+    <t>133534554</t>
+  </si>
+  <si>
+    <t>133534625</t>
+  </si>
+  <si>
+    <t>133534684</t>
+  </si>
+  <si>
+    <t>133534690</t>
+  </si>
+  <si>
+    <t>133534732</t>
+  </si>
+  <si>
+    <t>133535336</t>
+  </si>
+  <si>
+    <t>133535602</t>
+  </si>
+  <si>
+    <t>133535965</t>
+  </si>
+  <si>
+    <t>133535977</t>
+  </si>
+  <si>
+    <t>133536002</t>
+  </si>
+  <si>
+    <t>133536206</t>
+  </si>
+  <si>
+    <t>133536793</t>
+  </si>
+  <si>
+    <t>133536889</t>
+  </si>
+  <si>
+    <t>133536901</t>
+  </si>
+  <si>
+    <t>133536979</t>
+  </si>
+  <si>
+    <t>133537034</t>
+  </si>
+  <si>
+    <t>133537542</t>
+  </si>
+  <si>
+    <t>133537615</t>
+  </si>
+  <si>
+    <t>133537849</t>
+  </si>
+  <si>
+    <t>133537980</t>
+  </si>
+  <si>
+    <t>133538091</t>
+  </si>
+  <si>
+    <t>133538170</t>
+  </si>
+  <si>
+    <t>133538562</t>
+  </si>
+  <si>
+    <t>133538715</t>
+  </si>
+  <si>
+    <t>133538718</t>
+  </si>
+  <si>
+    <t>133538924</t>
+  </si>
+  <si>
+    <t>133539007</t>
+  </si>
+  <si>
+    <t>133539024</t>
+  </si>
+  <si>
+    <t>133539082</t>
+  </si>
+  <si>
+    <t>133539175</t>
+  </si>
+  <si>
+    <t>133539207</t>
+  </si>
+  <si>
+    <t>133539507</t>
+  </si>
+  <si>
+    <t>133539518</t>
+  </si>
+  <si>
+    <t>133539655</t>
+  </si>
+  <si>
+    <t>133539797</t>
+  </si>
+  <si>
+    <t>133539835</t>
+  </si>
+  <si>
+    <t>133539850</t>
+  </si>
+  <si>
+    <t>133540013</t>
+  </si>
+  <si>
+    <t>133540076</t>
+  </si>
+  <si>
+    <t>133540408</t>
+  </si>
+  <si>
+    <t>133540538</t>
+  </si>
+  <si>
+    <t>133540555</t>
+  </si>
+  <si>
+    <t>133540582</t>
+  </si>
+  <si>
+    <t>133540641</t>
+  </si>
+  <si>
+    <t>133540714</t>
+  </si>
+  <si>
+    <t>133540910</t>
+  </si>
+  <si>
+    <t>133540957</t>
+  </si>
+  <si>
+    <t>133541074</t>
+  </si>
+  <si>
+    <t>133541170</t>
+  </si>
+  <si>
+    <t>133541273</t>
+  </si>
+  <si>
+    <t>133541353</t>
+  </si>
+  <si>
+    <t>133541440</t>
+  </si>
+  <si>
+    <t>133541441</t>
+  </si>
+  <si>
+    <t>133541799</t>
+  </si>
+  <si>
+    <t>133541860</t>
+  </si>
+  <si>
+    <t>133541870</t>
+  </si>
+  <si>
+    <t>133541882</t>
+  </si>
+  <si>
+    <t>133542025</t>
+  </si>
+  <si>
+    <t>133542149</t>
+  </si>
+  <si>
+    <t>133542591</t>
+  </si>
+  <si>
+    <t>133542691</t>
+  </si>
+  <si>
+    <t>133542697</t>
+  </si>
+  <si>
+    <t>133543190</t>
+  </si>
+  <si>
+    <t>133543343</t>
+  </si>
+  <si>
+    <t>133543422</t>
+  </si>
+  <si>
+    <t>133543702</t>
+  </si>
+  <si>
+    <t>133543844</t>
+  </si>
+  <si>
+    <t>133543872</t>
+  </si>
+  <si>
+    <t>133543955</t>
+  </si>
+  <si>
+    <t>133543957</t>
+  </si>
+  <si>
+    <t>133544086</t>
+  </si>
+  <si>
+    <t>133544181</t>
+  </si>
+  <si>
+    <t>133544186</t>
+  </si>
+  <si>
+    <t>133544187</t>
+  </si>
+  <si>
+    <t>133544216</t>
+  </si>
+  <si>
+    <t>133544258</t>
+  </si>
+  <si>
+    <t>133544325</t>
+  </si>
+  <si>
+    <t>133544371</t>
+  </si>
+  <si>
+    <t>133544451</t>
+  </si>
+  <si>
+    <t>133544575</t>
+  </si>
+  <si>
+    <t>133546013</t>
+  </si>
+  <si>
+    <t>133546107</t>
+  </si>
+  <si>
+    <t>133546161</t>
+  </si>
+  <si>
+    <t>133546621</t>
   </si>
 </sst>
 </file>
@@ -969,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C175"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2903,8 +2933,118 @@
         <v>4</v>
       </c>
     </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C175" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C185" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C96D49B-8D19-45D3-8B5F-AE1BE7FAFB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA5B8A3-307E-450A-8790-0819E7764044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="186">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,556 +45,547 @@
     <t>.</t>
   </si>
   <si>
-    <t>129136705</t>
-  </si>
-  <si>
-    <t>129389753</t>
-  </si>
-  <si>
-    <t>129476140</t>
-  </si>
-  <si>
-    <t>129572959</t>
-  </si>
-  <si>
-    <t>129654819</t>
-  </si>
-  <si>
-    <t>129764998</t>
-  </si>
-  <si>
-    <t>130028459</t>
-  </si>
-  <si>
-    <t>130109355</t>
-  </si>
-  <si>
-    <t>130162820</t>
-  </si>
-  <si>
-    <t>130302954</t>
-  </si>
-  <si>
-    <t>130725583</t>
-  </si>
-  <si>
-    <t>131577416</t>
-  </si>
-  <si>
-    <t>131693335</t>
-  </si>
-  <si>
-    <t>132082254</t>
-  </si>
-  <si>
-    <t>132433268</t>
-  </si>
-  <si>
-    <t>132620076</t>
-  </si>
-  <si>
-    <t>132849476</t>
-  </si>
-  <si>
-    <t>132877909</t>
-  </si>
-  <si>
-    <t>133335332</t>
-  </si>
-  <si>
-    <t>133403303</t>
-  </si>
-  <si>
-    <t>133520636</t>
-  </si>
-  <si>
-    <t>133520645</t>
-  </si>
-  <si>
-    <t>133520676</t>
-  </si>
-  <si>
-    <t>133520692</t>
-  </si>
-  <si>
-    <t>133521208</t>
-  </si>
-  <si>
-    <t>133521321</t>
-  </si>
-  <si>
-    <t>133521666</t>
-  </si>
-  <si>
-    <t>133521675</t>
-  </si>
-  <si>
-    <t>133521974</t>
-  </si>
-  <si>
-    <t>133522094</t>
-  </si>
-  <si>
-    <t>133522139</t>
-  </si>
-  <si>
-    <t>133522380</t>
-  </si>
-  <si>
-    <t>133522525</t>
-  </si>
-  <si>
-    <t>133522603</t>
-  </si>
-  <si>
-    <t>133522613</t>
-  </si>
-  <si>
-    <t>133522630</t>
-  </si>
-  <si>
-    <t>133522724</t>
-  </si>
-  <si>
-    <t>133522761</t>
-  </si>
-  <si>
-    <t>133522822</t>
-  </si>
-  <si>
-    <t>133522858</t>
-  </si>
-  <si>
-    <t>133523010</t>
-  </si>
-  <si>
-    <t>133523909</t>
-  </si>
-  <si>
-    <t>133523953</t>
-  </si>
-  <si>
-    <t>133524004</t>
-  </si>
-  <si>
-    <t>133524286</t>
-  </si>
-  <si>
-    <t>133524688</t>
-  </si>
-  <si>
-    <t>133525002</t>
-  </si>
-  <si>
-    <t>133525069</t>
-  </si>
-  <si>
-    <t>133525139</t>
-  </si>
-  <si>
-    <t>133525144</t>
-  </si>
-  <si>
-    <t>133525236</t>
-  </si>
-  <si>
-    <t>133525705</t>
-  </si>
-  <si>
-    <t>133526005</t>
-  </si>
-  <si>
-    <t>133526112</t>
-  </si>
-  <si>
-    <t>133526211</t>
-  </si>
-  <si>
-    <t>133526617</t>
-  </si>
-  <si>
-    <t>133526689</t>
-  </si>
-  <si>
-    <t>133526981</t>
-  </si>
-  <si>
-    <t>133527423</t>
-  </si>
-  <si>
-    <t>133527474</t>
-  </si>
-  <si>
-    <t>133527700</t>
-  </si>
-  <si>
-    <t>133527815</t>
-  </si>
-  <si>
-    <t>133528222</t>
-  </si>
-  <si>
-    <t>133528389</t>
-  </si>
-  <si>
-    <t>133528485</t>
-  </si>
-  <si>
-    <t>133528549</t>
-  </si>
-  <si>
-    <t>133528787</t>
-  </si>
-  <si>
-    <t>133528879</t>
-  </si>
-  <si>
-    <t>133529169</t>
-  </si>
-  <si>
-    <t>133529377</t>
-  </si>
-  <si>
-    <t>133529957</t>
-  </si>
-  <si>
-    <t>133530076</t>
-  </si>
-  <si>
-    <t>133530195</t>
-  </si>
-  <si>
-    <t>133530602</t>
-  </si>
-  <si>
-    <t>133530801</t>
-  </si>
-  <si>
-    <t>133530889</t>
-  </si>
-  <si>
-    <t>133530913</t>
-  </si>
-  <si>
-    <t>133530955</t>
-  </si>
-  <si>
-    <t>133530959</t>
-  </si>
-  <si>
-    <t>133531209</t>
-  </si>
-  <si>
-    <t>133531405</t>
-  </si>
-  <si>
-    <t>133531484</t>
-  </si>
-  <si>
-    <t>133531931</t>
-  </si>
-  <si>
-    <t>133531949</t>
-  </si>
-  <si>
-    <t>133532143</t>
-  </si>
-  <si>
-    <t>133532164</t>
-  </si>
-  <si>
-    <t>133532177</t>
-  </si>
-  <si>
-    <t>133532863</t>
-  </si>
-  <si>
-    <t>133533076</t>
-  </si>
-  <si>
-    <t>133533176</t>
-  </si>
-  <si>
-    <t>133533314</t>
-  </si>
-  <si>
-    <t>133533383</t>
-  </si>
-  <si>
-    <t>133533502</t>
-  </si>
-  <si>
-    <t>133533863</t>
-  </si>
-  <si>
-    <t>133534060</t>
-  </si>
-  <si>
-    <t>133534098</t>
-  </si>
-  <si>
-    <t>133534216</t>
-  </si>
-  <si>
-    <t>133534309</t>
-  </si>
-  <si>
-    <t>133534439</t>
-  </si>
-  <si>
-    <t>133534511</t>
-  </si>
-  <si>
-    <t>133534554</t>
-  </si>
-  <si>
-    <t>133534625</t>
-  </si>
-  <si>
-    <t>133534684</t>
-  </si>
-  <si>
-    <t>133534690</t>
-  </si>
-  <si>
-    <t>133534732</t>
-  </si>
-  <si>
-    <t>133535336</t>
-  </si>
-  <si>
-    <t>133535602</t>
-  </si>
-  <si>
-    <t>133535965</t>
-  </si>
-  <si>
-    <t>133535977</t>
-  </si>
-  <si>
-    <t>133536002</t>
-  </si>
-  <si>
-    <t>133536206</t>
-  </si>
-  <si>
-    <t>133536793</t>
-  </si>
-  <si>
-    <t>133536889</t>
-  </si>
-  <si>
-    <t>133536901</t>
-  </si>
-  <si>
-    <t>133536979</t>
-  </si>
-  <si>
-    <t>133537034</t>
-  </si>
-  <si>
-    <t>133537542</t>
-  </si>
-  <si>
-    <t>133537615</t>
-  </si>
-  <si>
-    <t>133537849</t>
-  </si>
-  <si>
-    <t>133537980</t>
-  </si>
-  <si>
-    <t>133538091</t>
-  </si>
-  <si>
-    <t>133538170</t>
-  </si>
-  <si>
-    <t>133538562</t>
-  </si>
-  <si>
-    <t>133538715</t>
-  </si>
-  <si>
-    <t>133538718</t>
-  </si>
-  <si>
-    <t>133538924</t>
-  </si>
-  <si>
-    <t>133539007</t>
-  </si>
-  <si>
-    <t>133539024</t>
-  </si>
-  <si>
-    <t>133539082</t>
-  </si>
-  <si>
-    <t>133539175</t>
-  </si>
-  <si>
-    <t>133539207</t>
-  </si>
-  <si>
-    <t>133539507</t>
-  </si>
-  <si>
-    <t>133539518</t>
-  </si>
-  <si>
-    <t>133539655</t>
-  </si>
-  <si>
-    <t>133539797</t>
-  </si>
-  <si>
-    <t>133539835</t>
-  </si>
-  <si>
-    <t>133539850</t>
-  </si>
-  <si>
-    <t>133540013</t>
-  </si>
-  <si>
-    <t>133540076</t>
-  </si>
-  <si>
-    <t>133540408</t>
-  </si>
-  <si>
-    <t>133540538</t>
-  </si>
-  <si>
-    <t>133540555</t>
-  </si>
-  <si>
-    <t>133540582</t>
-  </si>
-  <si>
-    <t>133540641</t>
-  </si>
-  <si>
-    <t>133540714</t>
-  </si>
-  <si>
-    <t>133540910</t>
-  </si>
-  <si>
-    <t>133540957</t>
-  </si>
-  <si>
-    <t>133541074</t>
-  </si>
-  <si>
-    <t>133541170</t>
-  </si>
-  <si>
-    <t>133541273</t>
-  </si>
-  <si>
-    <t>133541353</t>
-  </si>
-  <si>
-    <t>133541440</t>
-  </si>
-  <si>
-    <t>133541441</t>
-  </si>
-  <si>
-    <t>133541799</t>
-  </si>
-  <si>
-    <t>133541860</t>
-  </si>
-  <si>
-    <t>133541870</t>
-  </si>
-  <si>
-    <t>133541882</t>
-  </si>
-  <si>
-    <t>133542025</t>
-  </si>
-  <si>
-    <t>133542149</t>
-  </si>
-  <si>
-    <t>133542591</t>
-  </si>
-  <si>
-    <t>133542691</t>
-  </si>
-  <si>
-    <t>133542697</t>
-  </si>
-  <si>
-    <t>133543190</t>
-  </si>
-  <si>
-    <t>133543343</t>
-  </si>
-  <si>
-    <t>133543422</t>
-  </si>
-  <si>
-    <t>133543702</t>
-  </si>
-  <si>
-    <t>133543844</t>
-  </si>
-  <si>
-    <t>133543872</t>
-  </si>
-  <si>
-    <t>133543955</t>
-  </si>
-  <si>
-    <t>133543957</t>
-  </si>
-  <si>
-    <t>133544086</t>
-  </si>
-  <si>
-    <t>133544181</t>
-  </si>
-  <si>
-    <t>133544186</t>
-  </si>
-  <si>
-    <t>133544187</t>
-  </si>
-  <si>
-    <t>133544216</t>
-  </si>
-  <si>
-    <t>133544258</t>
-  </si>
-  <si>
-    <t>133544325</t>
-  </si>
-  <si>
-    <t>133544371</t>
-  </si>
-  <si>
-    <t>133544451</t>
-  </si>
-  <si>
-    <t>133544575</t>
-  </si>
-  <si>
-    <t>133546013</t>
-  </si>
-  <si>
-    <t>133546107</t>
-  </si>
-  <si>
-    <t>133546161</t>
-  </si>
-  <si>
-    <t>133546621</t>
+    <t>129038793</t>
+  </si>
+  <si>
+    <t>129159559</t>
+  </si>
+  <si>
+    <t>129233118</t>
+  </si>
+  <si>
+    <t>129269930</t>
+  </si>
+  <si>
+    <t>129502263</t>
+  </si>
+  <si>
+    <t>129539345</t>
+  </si>
+  <si>
+    <t>130381673</t>
+  </si>
+  <si>
+    <t>130650855</t>
+  </si>
+  <si>
+    <t>130730026</t>
+  </si>
+  <si>
+    <t>130761498</t>
+  </si>
+  <si>
+    <t>130779495</t>
+  </si>
+  <si>
+    <t>131006200</t>
+  </si>
+  <si>
+    <t>131720376</t>
+  </si>
+  <si>
+    <t>132237794</t>
+  </si>
+  <si>
+    <t>132279831</t>
+  </si>
+  <si>
+    <t>132660941</t>
+  </si>
+  <si>
+    <t>133422208</t>
+  </si>
+  <si>
+    <t>133547693</t>
+  </si>
+  <si>
+    <t>133547754</t>
+  </si>
+  <si>
+    <t>133547826</t>
+  </si>
+  <si>
+    <t>133547839</t>
+  </si>
+  <si>
+    <t>133547863</t>
+  </si>
+  <si>
+    <t>133548063</t>
+  </si>
+  <si>
+    <t>133548694</t>
+  </si>
+  <si>
+    <t>133548812</t>
+  </si>
+  <si>
+    <t>133549209</t>
+  </si>
+  <si>
+    <t>133549235</t>
+  </si>
+  <si>
+    <t>133549471</t>
+  </si>
+  <si>
+    <t>133549591</t>
+  </si>
+  <si>
+    <t>133549598</t>
+  </si>
+  <si>
+    <t>133550294</t>
+  </si>
+  <si>
+    <t>133550634</t>
+  </si>
+  <si>
+    <t>133550698</t>
+  </si>
+  <si>
+    <t>133550930</t>
+  </si>
+  <si>
+    <t>133551125</t>
+  </si>
+  <si>
+    <t>133551207</t>
+  </si>
+  <si>
+    <t>133551226</t>
+  </si>
+  <si>
+    <t>133551261</t>
+  </si>
+  <si>
+    <t>133551479</t>
+  </si>
+  <si>
+    <t>133551701</t>
+  </si>
+  <si>
+    <t>133551734</t>
+  </si>
+  <si>
+    <t>133551903</t>
+  </si>
+  <si>
+    <t>133552135</t>
+  </si>
+  <si>
+    <t>133552264</t>
+  </si>
+  <si>
+    <t>133552421</t>
+  </si>
+  <si>
+    <t>133552562</t>
+  </si>
+  <si>
+    <t>133552768</t>
+  </si>
+  <si>
+    <t>133553118</t>
+  </si>
+  <si>
+    <t>133553321</t>
+  </si>
+  <si>
+    <t>133553350</t>
+  </si>
+  <si>
+    <t>133553638</t>
+  </si>
+  <si>
+    <t>133553708</t>
+  </si>
+  <si>
+    <t>133553905</t>
+  </si>
+  <si>
+    <t>133554292</t>
+  </si>
+  <si>
+    <t>133554460</t>
+  </si>
+  <si>
+    <t>133554606</t>
+  </si>
+  <si>
+    <t>133554629</t>
+  </si>
+  <si>
+    <t>133554643</t>
+  </si>
+  <si>
+    <t>133554673</t>
+  </si>
+  <si>
+    <t>133554718</t>
+  </si>
+  <si>
+    <t>133554789</t>
+  </si>
+  <si>
+    <t>133554868</t>
+  </si>
+  <si>
+    <t>133554985</t>
+  </si>
+  <si>
+    <t>133555160</t>
+  </si>
+  <si>
+    <t>133555247</t>
+  </si>
+  <si>
+    <t>133555256</t>
+  </si>
+  <si>
+    <t>133555345</t>
+  </si>
+  <si>
+    <t>133555564</t>
+  </si>
+  <si>
+    <t>133555675</t>
+  </si>
+  <si>
+    <t>133555809</t>
+  </si>
+  <si>
+    <t>133555840</t>
+  </si>
+  <si>
+    <t>133555841</t>
+  </si>
+  <si>
+    <t>133555881</t>
+  </si>
+  <si>
+    <t>133556282</t>
+  </si>
+  <si>
+    <t>133556375</t>
+  </si>
+  <si>
+    <t>133556669</t>
+  </si>
+  <si>
+    <t>133556720</t>
+  </si>
+  <si>
+    <t>133556757</t>
+  </si>
+  <si>
+    <t>133556915</t>
+  </si>
+  <si>
+    <t>133556955</t>
+  </si>
+  <si>
+    <t>133557099</t>
+  </si>
+  <si>
+    <t>133557647</t>
+  </si>
+  <si>
+    <t>133557714</t>
+  </si>
+  <si>
+    <t>133557924</t>
+  </si>
+  <si>
+    <t>133558070</t>
+  </si>
+  <si>
+    <t>133558344</t>
+  </si>
+  <si>
+    <t>133558410</t>
+  </si>
+  <si>
+    <t>133558423</t>
+  </si>
+  <si>
+    <t>133558520</t>
+  </si>
+  <si>
+    <t>133558807</t>
+  </si>
+  <si>
+    <t>133558860</t>
+  </si>
+  <si>
+    <t>133558863</t>
+  </si>
+  <si>
+    <t>133558985</t>
+  </si>
+  <si>
+    <t>133559073</t>
+  </si>
+  <si>
+    <t>133559324</t>
+  </si>
+  <si>
+    <t>133559345</t>
+  </si>
+  <si>
+    <t>133559433</t>
+  </si>
+  <si>
+    <t>133559466</t>
+  </si>
+  <si>
+    <t>133559533</t>
+  </si>
+  <si>
+    <t>133559730</t>
+  </si>
+  <si>
+    <t>133559784</t>
+  </si>
+  <si>
+    <t>133559890</t>
+  </si>
+  <si>
+    <t>133560108</t>
+  </si>
+  <si>
+    <t>133560182</t>
+  </si>
+  <si>
+    <t>133560191</t>
+  </si>
+  <si>
+    <t>133560254</t>
+  </si>
+  <si>
+    <t>133560591</t>
+  </si>
+  <si>
+    <t>133560709</t>
+  </si>
+  <si>
+    <t>133560730</t>
+  </si>
+  <si>
+    <t>133560780</t>
+  </si>
+  <si>
+    <t>133560850</t>
+  </si>
+  <si>
+    <t>133561233</t>
+  </si>
+  <si>
+    <t>133561262</t>
+  </si>
+  <si>
+    <t>133561272</t>
+  </si>
+  <si>
+    <t>133561303</t>
+  </si>
+  <si>
+    <t>133561463</t>
+  </si>
+  <si>
+    <t>133561537</t>
+  </si>
+  <si>
+    <t>133561824</t>
+  </si>
+  <si>
+    <t>133561927</t>
+  </si>
+  <si>
+    <t>133562069</t>
+  </si>
+  <si>
+    <t>133562077</t>
+  </si>
+  <si>
+    <t>133562122</t>
+  </si>
+  <si>
+    <t>133562145</t>
+  </si>
+  <si>
+    <t>133562188</t>
+  </si>
+  <si>
+    <t>133562403</t>
+  </si>
+  <si>
+    <t>133562413</t>
+  </si>
+  <si>
+    <t>133562524</t>
+  </si>
+  <si>
+    <t>133562542</t>
+  </si>
+  <si>
+    <t>133562550</t>
+  </si>
+  <si>
+    <t>133562736</t>
+  </si>
+  <si>
+    <t>133562827</t>
+  </si>
+  <si>
+    <t>133562885</t>
+  </si>
+  <si>
+    <t>133562897</t>
+  </si>
+  <si>
+    <t>133563111</t>
+  </si>
+  <si>
+    <t>133563217</t>
+  </si>
+  <si>
+    <t>133563397</t>
+  </si>
+  <si>
+    <t>133563403</t>
+  </si>
+  <si>
+    <t>133563621</t>
+  </si>
+  <si>
+    <t>133563683</t>
+  </si>
+  <si>
+    <t>133563878</t>
+  </si>
+  <si>
+    <t>133564008</t>
+  </si>
+  <si>
+    <t>133564136</t>
+  </si>
+  <si>
+    <t>133564269</t>
+  </si>
+  <si>
+    <t>133564314</t>
+  </si>
+  <si>
+    <t>133564334</t>
+  </si>
+  <si>
+    <t>133564400</t>
+  </si>
+  <si>
+    <t>133564412</t>
+  </si>
+  <si>
+    <t>133564478</t>
+  </si>
+  <si>
+    <t>133564547</t>
+  </si>
+  <si>
+    <t>133564599</t>
+  </si>
+  <si>
+    <t>133564606</t>
+  </si>
+  <si>
+    <t>133564730</t>
+  </si>
+  <si>
+    <t>133564887</t>
+  </si>
+  <si>
+    <t>133564968</t>
+  </si>
+  <si>
+    <t>133565026</t>
+  </si>
+  <si>
+    <t>133565161</t>
+  </si>
+  <si>
+    <t>133565512</t>
+  </si>
+  <si>
+    <t>133565625</t>
+  </si>
+  <si>
+    <t>133565785</t>
+  </si>
+  <si>
+    <t>133565853</t>
+  </si>
+  <si>
+    <t>133565905</t>
+  </si>
+  <si>
+    <t>133566127</t>
+  </si>
+  <si>
+    <t>133566217</t>
+  </si>
+  <si>
+    <t>133566243</t>
+  </si>
+  <si>
+    <t>133566316</t>
+  </si>
+  <si>
+    <t>133566414</t>
+  </si>
+  <si>
+    <t>133566466</t>
+  </si>
+  <si>
+    <t>133566478</t>
+  </si>
+  <si>
+    <t>133566485</t>
+  </si>
+  <si>
+    <t>133566522</t>
+  </si>
+  <si>
+    <t>133566562</t>
+  </si>
+  <si>
+    <t>133566679</t>
+  </si>
+  <si>
+    <t>133566837</t>
+  </si>
+  <si>
+    <t>133566945</t>
+  </si>
+  <si>
+    <t>133566971</t>
+  </si>
+  <si>
+    <t>133567097</t>
+  </si>
+  <si>
+    <t>133567328</t>
+  </si>
+  <si>
+    <t>133567713</t>
+  </si>
+  <si>
+    <t>133568382</t>
+  </si>
+  <si>
+    <t>133568464</t>
+  </si>
+  <si>
+    <t>133568507</t>
   </si>
 </sst>
 </file>
@@ -999,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3010,41 +3001,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C185" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C182" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E1BEE8-7422-4B9C-8B95-D3BB014DCFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA36EC8-4317-4EBA-869B-AB51D0DFCC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$205</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="244">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,517 +45,721 @@
     <t>.</t>
   </si>
   <si>
-    <t>128887754</t>
-  </si>
-  <si>
-    <t>129256925</t>
-  </si>
-  <si>
-    <t>129876001</t>
-  </si>
-  <si>
-    <t>130066663</t>
-  </si>
-  <si>
-    <t>130183522</t>
-  </si>
-  <si>
-    <t>130199589</t>
-  </si>
-  <si>
-    <t>130423275</t>
-  </si>
-  <si>
-    <t>130505289</t>
-  </si>
-  <si>
-    <t>130579055</t>
-  </si>
-  <si>
-    <t>130696802</t>
-  </si>
-  <si>
-    <t>131066352</t>
-  </si>
-  <si>
-    <t>131082708</t>
-  </si>
-  <si>
-    <t>131106543</t>
-  </si>
-  <si>
-    <t>131177411</t>
-  </si>
-  <si>
-    <t>131207287</t>
-  </si>
-  <si>
-    <t>131585057</t>
-  </si>
-  <si>
-    <t>131692915</t>
-  </si>
-  <si>
-    <t>131719817</t>
-  </si>
-  <si>
-    <t>131972051</t>
-  </si>
-  <si>
-    <t>132240564</t>
-  </si>
-  <si>
-    <t>132289910</t>
-  </si>
-  <si>
-    <t>132411676</t>
-  </si>
-  <si>
-    <t>132576659</t>
-  </si>
-  <si>
-    <t>132670756</t>
-  </si>
-  <si>
-    <t>132775968</t>
-  </si>
-  <si>
-    <t>132979293</t>
-  </si>
-  <si>
-    <t>133312003</t>
-  </si>
-  <si>
-    <t>133386466</t>
-  </si>
-  <si>
-    <t>133590236</t>
-  </si>
-  <si>
-    <t>133590276</t>
-  </si>
-  <si>
-    <t>133590290</t>
-  </si>
-  <si>
-    <t>133590601</t>
-  </si>
-  <si>
-    <t>133590718</t>
-  </si>
-  <si>
-    <t>133591055</t>
-  </si>
-  <si>
-    <t>133591122</t>
-  </si>
-  <si>
-    <t>133591140</t>
-  </si>
-  <si>
-    <t>133591384</t>
-  </si>
-  <si>
-    <t>133591583</t>
-  </si>
-  <si>
-    <t>133591990</t>
-  </si>
-  <si>
-    <t>133592001</t>
-  </si>
-  <si>
-    <t>133592274</t>
-  </si>
-  <si>
-    <t>133592394</t>
-  </si>
-  <si>
-    <t>133592570</t>
-  </si>
-  <si>
-    <t>133592670</t>
-  </si>
-  <si>
-    <t>133593098</t>
-  </si>
-  <si>
-    <t>133593154</t>
-  </si>
-  <si>
-    <t>133593319</t>
-  </si>
-  <si>
-    <t>133593597</t>
-  </si>
-  <si>
-    <t>133594248</t>
-  </si>
-  <si>
-    <t>133595009</t>
-  </si>
-  <si>
-    <t>133595033</t>
-  </si>
-  <si>
-    <t>133595038</t>
-  </si>
-  <si>
-    <t>133595752</t>
-  </si>
-  <si>
-    <t>133596067</t>
-  </si>
-  <si>
-    <t>133596152</t>
-  </si>
-  <si>
-    <t>133596309</t>
-  </si>
-  <si>
-    <t>133596540</t>
-  </si>
-  <si>
-    <t>133596590</t>
-  </si>
-  <si>
-    <t>133596712</t>
-  </si>
-  <si>
-    <t>133596738</t>
-  </si>
-  <si>
-    <t>133597043</t>
-  </si>
-  <si>
-    <t>133597553</t>
-  </si>
-  <si>
-    <t>133597580</t>
-  </si>
-  <si>
-    <t>133597679</t>
-  </si>
-  <si>
-    <t>133597995</t>
-  </si>
-  <si>
-    <t>133598154</t>
-  </si>
-  <si>
-    <t>133598331</t>
-  </si>
-  <si>
-    <t>133598436</t>
-  </si>
-  <si>
-    <t>133598451</t>
-  </si>
-  <si>
-    <t>133598592</t>
-  </si>
-  <si>
-    <t>133598719</t>
-  </si>
-  <si>
-    <t>133598940</t>
-  </si>
-  <si>
-    <t>133599010</t>
-  </si>
-  <si>
-    <t>133599132</t>
-  </si>
-  <si>
-    <t>133599345</t>
-  </si>
-  <si>
-    <t>133599577</t>
-  </si>
-  <si>
-    <t>133599579</t>
-  </si>
-  <si>
-    <t>133599592</t>
-  </si>
-  <si>
-    <t>133599664</t>
-  </si>
-  <si>
-    <t>133599691</t>
-  </si>
-  <si>
-    <t>133599750</t>
-  </si>
-  <si>
-    <t>133599934</t>
-  </si>
-  <si>
-    <t>133600029</t>
-  </si>
-  <si>
-    <t>133600033</t>
-  </si>
-  <si>
-    <t>133600352</t>
-  </si>
-  <si>
-    <t>133600843</t>
-  </si>
-  <si>
-    <t>133600907</t>
-  </si>
-  <si>
-    <t>133600987</t>
-  </si>
-  <si>
-    <t>133601002</t>
-  </si>
-  <si>
-    <t>133601324</t>
-  </si>
-  <si>
-    <t>133601342</t>
-  </si>
-  <si>
-    <t>133601429</t>
-  </si>
-  <si>
-    <t>133601584</t>
-  </si>
-  <si>
-    <t>133601599</t>
-  </si>
-  <si>
-    <t>133601852</t>
-  </si>
-  <si>
-    <t>133601972</t>
-  </si>
-  <si>
-    <t>133602000</t>
-  </si>
-  <si>
-    <t>133602095</t>
-  </si>
-  <si>
-    <t>133602096</t>
-  </si>
-  <si>
-    <t>133602129</t>
-  </si>
-  <si>
-    <t>133602188</t>
-  </si>
-  <si>
-    <t>133602234</t>
-  </si>
-  <si>
-    <t>133602301</t>
-  </si>
-  <si>
-    <t>133602594</t>
-  </si>
-  <si>
-    <t>133602703</t>
-  </si>
-  <si>
-    <t>133602755</t>
-  </si>
-  <si>
-    <t>133602936</t>
-  </si>
-  <si>
-    <t>133603027</t>
-  </si>
-  <si>
-    <t>133603097</t>
-  </si>
-  <si>
-    <t>133603149</t>
-  </si>
-  <si>
-    <t>133603267</t>
-  </si>
-  <si>
-    <t>133603348</t>
-  </si>
-  <si>
-    <t>133603508</t>
-  </si>
-  <si>
-    <t>133603549</t>
-  </si>
-  <si>
-    <t>133603570</t>
-  </si>
-  <si>
-    <t>133603608</t>
-  </si>
-  <si>
-    <t>133603622</t>
-  </si>
-  <si>
-    <t>133603717</t>
-  </si>
-  <si>
-    <t>133603856</t>
-  </si>
-  <si>
-    <t>133604072</t>
-  </si>
-  <si>
-    <t>133604252</t>
-  </si>
-  <si>
-    <t>133604485</t>
-  </si>
-  <si>
-    <t>133604502</t>
-  </si>
-  <si>
-    <t>133604505</t>
-  </si>
-  <si>
-    <t>133604526</t>
-  </si>
-  <si>
-    <t>133604603</t>
-  </si>
-  <si>
-    <t>133604745</t>
-  </si>
-  <si>
-    <t>133604903</t>
-  </si>
-  <si>
-    <t>133605325</t>
-  </si>
-  <si>
-    <t>133605335</t>
-  </si>
-  <si>
-    <t>133605384</t>
-  </si>
-  <si>
-    <t>133605432</t>
-  </si>
-  <si>
-    <t>133605583</t>
-  </si>
-  <si>
-    <t>133605837</t>
-  </si>
-  <si>
-    <t>133605966</t>
-  </si>
-  <si>
-    <t>133606239</t>
-  </si>
-  <si>
-    <t>133606525</t>
-  </si>
-  <si>
-    <t>133606603</t>
-  </si>
-  <si>
-    <t>133606826</t>
-  </si>
-  <si>
-    <t>133606970</t>
-  </si>
-  <si>
-    <t>133607195</t>
-  </si>
-  <si>
-    <t>133607244</t>
-  </si>
-  <si>
-    <t>133607356</t>
-  </si>
-  <si>
-    <t>133607462</t>
-  </si>
-  <si>
-    <t>133607528</t>
-  </si>
-  <si>
-    <t>133607530</t>
-  </si>
-  <si>
-    <t>133607546</t>
-  </si>
-  <si>
-    <t>133607704</t>
-  </si>
-  <si>
-    <t>133608011</t>
-  </si>
-  <si>
-    <t>133608059</t>
-  </si>
-  <si>
-    <t>133608216</t>
-  </si>
-  <si>
-    <t>133608251</t>
-  </si>
-  <si>
-    <t>133608331</t>
-  </si>
-  <si>
-    <t>133608558</t>
-  </si>
-  <si>
-    <t>133608579</t>
-  </si>
-  <si>
-    <t>133608692</t>
-  </si>
-  <si>
-    <t>133608864</t>
-  </si>
-  <si>
-    <t>133609058</t>
-  </si>
-  <si>
-    <t>133609086</t>
-  </si>
-  <si>
-    <t>133609098</t>
-  </si>
-  <si>
-    <t>133609230</t>
-  </si>
-  <si>
-    <t>133609287</t>
-  </si>
-  <si>
-    <t>133609410</t>
-  </si>
-  <si>
-    <t>133609537</t>
-  </si>
-  <si>
-    <t>133609681</t>
-  </si>
-  <si>
-    <t>133609766</t>
-  </si>
-  <si>
-    <t>133609832</t>
-  </si>
-  <si>
-    <t>133609949</t>
-  </si>
-  <si>
-    <t>133609998</t>
-  </si>
-  <si>
-    <t>133610153</t>
-  </si>
-  <si>
-    <t>133610675</t>
+    <t>128748899</t>
+  </si>
+  <si>
+    <t>129094845</t>
+  </si>
+  <si>
+    <t>129484119</t>
+  </si>
+  <si>
+    <t>129573061</t>
+  </si>
+  <si>
+    <t>130059412</t>
+  </si>
+  <si>
+    <t>130084769</t>
+  </si>
+  <si>
+    <t>130202354</t>
+  </si>
+  <si>
+    <t>130352033</t>
+  </si>
+  <si>
+    <t>130469555</t>
+  </si>
+  <si>
+    <t>130530810</t>
+  </si>
+  <si>
+    <t>130559298</t>
+  </si>
+  <si>
+    <t>130561482</t>
+  </si>
+  <si>
+    <t>130803316</t>
+  </si>
+  <si>
+    <t>130889256</t>
+  </si>
+  <si>
+    <t>131166641</t>
+  </si>
+  <si>
+    <t>131181173</t>
+  </si>
+  <si>
+    <t>131705945</t>
+  </si>
+  <si>
+    <t>131832231</t>
+  </si>
+  <si>
+    <t>132065340</t>
+  </si>
+  <si>
+    <t>132210670</t>
+  </si>
+  <si>
+    <t>132456524</t>
+  </si>
+  <si>
+    <t>132617840</t>
+  </si>
+  <si>
+    <t>133007971</t>
+  </si>
+  <si>
+    <t>133373013</t>
+  </si>
+  <si>
+    <t>133408272</t>
+  </si>
+  <si>
+    <t>133612179</t>
+  </si>
+  <si>
+    <t>133612260</t>
+  </si>
+  <si>
+    <t>133612696</t>
+  </si>
+  <si>
+    <t>133613082</t>
+  </si>
+  <si>
+    <t>133613216</t>
+  </si>
+  <si>
+    <t>133613362</t>
+  </si>
+  <si>
+    <t>133613427</t>
+  </si>
+  <si>
+    <t>133613465</t>
+  </si>
+  <si>
+    <t>133613475</t>
+  </si>
+  <si>
+    <t>133613813</t>
+  </si>
+  <si>
+    <t>133613919</t>
+  </si>
+  <si>
+    <t>133613976</t>
+  </si>
+  <si>
+    <t>133613992</t>
+  </si>
+  <si>
+    <t>133614327</t>
+  </si>
+  <si>
+    <t>133614364</t>
+  </si>
+  <si>
+    <t>133614593</t>
+  </si>
+  <si>
+    <t>133614739</t>
+  </si>
+  <si>
+    <t>133615006</t>
+  </si>
+  <si>
+    <t>133615315</t>
+  </si>
+  <si>
+    <t>133615484</t>
+  </si>
+  <si>
+    <t>133615501</t>
+  </si>
+  <si>
+    <t>133615503</t>
+  </si>
+  <si>
+    <t>133615504</t>
+  </si>
+  <si>
+    <t>133615563</t>
+  </si>
+  <si>
+    <t>133616109</t>
+  </si>
+  <si>
+    <t>133616119</t>
+  </si>
+  <si>
+    <t>133616228</t>
+  </si>
+  <si>
+    <t>133616425</t>
+  </si>
+  <si>
+    <t>133616483</t>
+  </si>
+  <si>
+    <t>133616562</t>
+  </si>
+  <si>
+    <t>133616687</t>
+  </si>
+  <si>
+    <t>133616759</t>
+  </si>
+  <si>
+    <t>133616821</t>
+  </si>
+  <si>
+    <t>133616960</t>
+  </si>
+  <si>
+    <t>133617577</t>
+  </si>
+  <si>
+    <t>133617872</t>
+  </si>
+  <si>
+    <t>133618110</t>
+  </si>
+  <si>
+    <t>133618292</t>
+  </si>
+  <si>
+    <t>133618297</t>
+  </si>
+  <si>
+    <t>133618299</t>
+  </si>
+  <si>
+    <t>133618335</t>
+  </si>
+  <si>
+    <t>133618631</t>
+  </si>
+  <si>
+    <t>133618708</t>
+  </si>
+  <si>
+    <t>133618906</t>
+  </si>
+  <si>
+    <t>133618908</t>
+  </si>
+  <si>
+    <t>133618963</t>
+  </si>
+  <si>
+    <t>133619012</t>
+  </si>
+  <si>
+    <t>133619109</t>
+  </si>
+  <si>
+    <t>133619290</t>
+  </si>
+  <si>
+    <t>133619293</t>
+  </si>
+  <si>
+    <t>133619480</t>
+  </si>
+  <si>
+    <t>133619664</t>
+  </si>
+  <si>
+    <t>133619702</t>
+  </si>
+  <si>
+    <t>133619737</t>
+  </si>
+  <si>
+    <t>133620004</t>
+  </si>
+  <si>
+    <t>133620025</t>
+  </si>
+  <si>
+    <t>133620190</t>
+  </si>
+  <si>
+    <t>133620490</t>
+  </si>
+  <si>
+    <t>133620546</t>
+  </si>
+  <si>
+    <t>133620704</t>
+  </si>
+  <si>
+    <t>133620809</t>
+  </si>
+  <si>
+    <t>133620812</t>
+  </si>
+  <si>
+    <t>133620818</t>
+  </si>
+  <si>
+    <t>133621053</t>
+  </si>
+  <si>
+    <t>133621099</t>
+  </si>
+  <si>
+    <t>133621134</t>
+  </si>
+  <si>
+    <t>133621135</t>
+  </si>
+  <si>
+    <t>133621229</t>
+  </si>
+  <si>
+    <t>133621578</t>
+  </si>
+  <si>
+    <t>133621666</t>
+  </si>
+  <si>
+    <t>133621798</t>
+  </si>
+  <si>
+    <t>133622230</t>
+  </si>
+  <si>
+    <t>133622332</t>
+  </si>
+  <si>
+    <t>133622403</t>
+  </si>
+  <si>
+    <t>133622580</t>
+  </si>
+  <si>
+    <t>133622609</t>
+  </si>
+  <si>
+    <t>133622703</t>
+  </si>
+  <si>
+    <t>133622850</t>
+  </si>
+  <si>
+    <t>133622957</t>
+  </si>
+  <si>
+    <t>133623069</t>
+  </si>
+  <si>
+    <t>133623405</t>
+  </si>
+  <si>
+    <t>133623533</t>
+  </si>
+  <si>
+    <t>133623994</t>
+  </si>
+  <si>
+    <t>133624195</t>
+  </si>
+  <si>
+    <t>133624244</t>
+  </si>
+  <si>
+    <t>133624356</t>
+  </si>
+  <si>
+    <t>133624376</t>
+  </si>
+  <si>
+    <t>133624469</t>
+  </si>
+  <si>
+    <t>133624566</t>
+  </si>
+  <si>
+    <t>133624755</t>
+  </si>
+  <si>
+    <t>133625045</t>
+  </si>
+  <si>
+    <t>133625094</t>
+  </si>
+  <si>
+    <t>133625116</t>
+  </si>
+  <si>
+    <t>133625257</t>
+  </si>
+  <si>
+    <t>133625462</t>
+  </si>
+  <si>
+    <t>133625917</t>
+  </si>
+  <si>
+    <t>133626065</t>
+  </si>
+  <si>
+    <t>133626191</t>
+  </si>
+  <si>
+    <t>133626399</t>
+  </si>
+  <si>
+    <t>133626629</t>
+  </si>
+  <si>
+    <t>133626683</t>
+  </si>
+  <si>
+    <t>133626770</t>
+  </si>
+  <si>
+    <t>133627073</t>
+  </si>
+  <si>
+    <t>133627371</t>
+  </si>
+  <si>
+    <t>133627374</t>
+  </si>
+  <si>
+    <t>133627409</t>
+  </si>
+  <si>
+    <t>133627426</t>
+  </si>
+  <si>
+    <t>133627461</t>
+  </si>
+  <si>
+    <t>133627732</t>
+  </si>
+  <si>
+    <t>133627796</t>
+  </si>
+  <si>
+    <t>133627821</t>
+  </si>
+  <si>
+    <t>133628106</t>
+  </si>
+  <si>
+    <t>133628195</t>
+  </si>
+  <si>
+    <t>133628230</t>
+  </si>
+  <si>
+    <t>133628387</t>
+  </si>
+  <si>
+    <t>133628437</t>
+  </si>
+  <si>
+    <t>133628464</t>
+  </si>
+  <si>
+    <t>133628528</t>
+  </si>
+  <si>
+    <t>133628753</t>
+  </si>
+  <si>
+    <t>133628789</t>
+  </si>
+  <si>
+    <t>133628985</t>
+  </si>
+  <si>
+    <t>133629352</t>
+  </si>
+  <si>
+    <t>133629369</t>
+  </si>
+  <si>
+    <t>133629544</t>
+  </si>
+  <si>
+    <t>133629632</t>
+  </si>
+  <si>
+    <t>133629717</t>
+  </si>
+  <si>
+    <t>133629762</t>
+  </si>
+  <si>
+    <t>133630014</t>
+  </si>
+  <si>
+    <t>133630052</t>
+  </si>
+  <si>
+    <t>133630090</t>
+  </si>
+  <si>
+    <t>133630273</t>
+  </si>
+  <si>
+    <t>133630326</t>
+  </si>
+  <si>
+    <t>133630358</t>
+  </si>
+  <si>
+    <t>133630440</t>
+  </si>
+  <si>
+    <t>133630513</t>
+  </si>
+  <si>
+    <t>133630563</t>
+  </si>
+  <si>
+    <t>133630609</t>
+  </si>
+  <si>
+    <t>133630656</t>
+  </si>
+  <si>
+    <t>133630725</t>
+  </si>
+  <si>
+    <t>133630779</t>
+  </si>
+  <si>
+    <t>133631012</t>
+  </si>
+  <si>
+    <t>133631318</t>
+  </si>
+  <si>
+    <t>133631520</t>
+  </si>
+  <si>
+    <t>133631522</t>
+  </si>
+  <si>
+    <t>133631581</t>
+  </si>
+  <si>
+    <t>133631665</t>
+  </si>
+  <si>
+    <t>133631738</t>
+  </si>
+  <si>
+    <t>133631836</t>
+  </si>
+  <si>
+    <t>133631843</t>
+  </si>
+  <si>
+    <t>133631950</t>
+  </si>
+  <si>
+    <t>133632006</t>
+  </si>
+  <si>
+    <t>133632043</t>
+  </si>
+  <si>
+    <t>133632259</t>
+  </si>
+  <si>
+    <t>133632308</t>
+  </si>
+  <si>
+    <t>133632309</t>
+  </si>
+  <si>
+    <t>133632327</t>
+  </si>
+  <si>
+    <t>133632356</t>
+  </si>
+  <si>
+    <t>133632426</t>
+  </si>
+  <si>
+    <t>133632485</t>
+  </si>
+  <si>
+    <t>133632572</t>
+  </si>
+  <si>
+    <t>133632743</t>
+  </si>
+  <si>
+    <t>133632899</t>
+  </si>
+  <si>
+    <t>133632932</t>
+  </si>
+  <si>
+    <t>133632971</t>
+  </si>
+  <si>
+    <t>133633048</t>
+  </si>
+  <si>
+    <t>133633072</t>
+  </si>
+  <si>
+    <t>133633148</t>
+  </si>
+  <si>
+    <t>133633177</t>
+  </si>
+  <si>
+    <t>133633334</t>
+  </si>
+  <si>
+    <t>133633360</t>
+  </si>
+  <si>
+    <t>133633364</t>
+  </si>
+  <si>
+    <t>133633489</t>
+  </si>
+  <si>
+    <t>133633514</t>
+  </si>
+  <si>
+    <t>133633578</t>
+  </si>
+  <si>
+    <t>133633698</t>
+  </si>
+  <si>
+    <t>133633778</t>
+  </si>
+  <si>
+    <t>133633908</t>
+  </si>
+  <si>
+    <t>133633923</t>
+  </si>
+  <si>
+    <t>133633964</t>
+  </si>
+  <si>
+    <t>133633971</t>
+  </si>
+  <si>
+    <t>133634013</t>
+  </si>
+  <si>
+    <t>133634087</t>
+  </si>
+  <si>
+    <t>133634160</t>
+  </si>
+  <si>
+    <t>133634193</t>
+  </si>
+  <si>
+    <t>133634369</t>
+  </si>
+  <si>
+    <t>133634409</t>
+  </si>
+  <si>
+    <t>133634459</t>
+  </si>
+  <si>
+    <t>133634460</t>
+  </si>
+  <si>
+    <t>133634703</t>
+  </si>
+  <si>
+    <t>133634709</t>
+  </si>
+  <si>
+    <t>133634725</t>
+  </si>
+  <si>
+    <t>133634808</t>
+  </si>
+  <si>
+    <t>133634845</t>
+  </si>
+  <si>
+    <t>133634857</t>
+  </si>
+  <si>
+    <t>133634868</t>
+  </si>
+  <si>
+    <t>133634886</t>
+  </si>
+  <si>
+    <t>133634926</t>
+  </si>
+  <si>
+    <t>133635052</t>
+  </si>
+  <si>
+    <t>133635110</t>
+  </si>
+  <si>
+    <t>133635137</t>
+  </si>
+  <si>
+    <t>133635154</t>
+  </si>
+  <si>
+    <t>133635247</t>
+  </si>
+  <si>
+    <t>133635250</t>
+  </si>
+  <si>
+    <t>133635271</t>
+  </si>
+  <si>
+    <t>133635307</t>
+  </si>
+  <si>
+    <t>133635419</t>
+  </si>
+  <si>
+    <t>133635421</t>
+  </si>
+  <si>
+    <t>133635724</t>
+  </si>
+  <si>
+    <t>133635781</t>
+  </si>
+  <si>
+    <t>133635876</t>
+  </si>
+  <si>
+    <t>133635878</t>
+  </si>
+  <si>
+    <t>133635911</t>
+  </si>
+  <si>
+    <t>133636122</t>
+  </si>
+  <si>
+    <t>133636230</t>
   </si>
 </sst>
 </file>
@@ -960,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:C240"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2861,8 +3065,756 @@
         <v>4</v>
       </c>
     </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C172" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819EC75F-B78D-4EE9-834D-D05E7A448D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACF0657-58B9-489C-A5CE-1BDD6FB0A0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$167</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="171">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,382 +45,502 @@
     <t>.</t>
   </si>
   <si>
-    <t>129643602</t>
-  </si>
-  <si>
-    <t>129798122</t>
-  </si>
-  <si>
-    <t>129966162</t>
-  </si>
-  <si>
-    <t>130248417</t>
-  </si>
-  <si>
-    <t>130624120</t>
-  </si>
-  <si>
-    <t>130646486</t>
-  </si>
-  <si>
-    <t>130649677</t>
-  </si>
-  <si>
-    <t>130670716</t>
-  </si>
-  <si>
-    <t>130815059</t>
-  </si>
-  <si>
-    <t>130821989</t>
-  </si>
-  <si>
-    <t>131194268</t>
-  </si>
-  <si>
-    <t>131605817</t>
-  </si>
-  <si>
-    <t>131715967</t>
-  </si>
-  <si>
-    <t>132357062</t>
-  </si>
-  <si>
-    <t>132401670</t>
-  </si>
-  <si>
-    <t>132557745</t>
-  </si>
-  <si>
-    <t>132577528</t>
-  </si>
-  <si>
-    <t>132715379</t>
-  </si>
-  <si>
-    <t>132801404</t>
-  </si>
-  <si>
-    <t>132872047</t>
-  </si>
-  <si>
-    <t>132980693</t>
-  </si>
-  <si>
-    <t>133636937</t>
-  </si>
-  <si>
-    <t>133636970</t>
-  </si>
-  <si>
-    <t>133637445</t>
-  </si>
-  <si>
-    <t>133637783</t>
-  </si>
-  <si>
-    <t>133637794</t>
-  </si>
-  <si>
-    <t>133638587</t>
-  </si>
-  <si>
-    <t>133638627</t>
-  </si>
-  <si>
-    <t>133639210</t>
-  </si>
-  <si>
-    <t>133639305</t>
-  </si>
-  <si>
-    <t>133639580</t>
-  </si>
-  <si>
-    <t>133639700</t>
-  </si>
-  <si>
-    <t>133639725</t>
-  </si>
-  <si>
-    <t>133639744</t>
-  </si>
-  <si>
-    <t>133639773</t>
-  </si>
-  <si>
-    <t>133639781</t>
-  </si>
-  <si>
-    <t>133639832</t>
-  </si>
-  <si>
-    <t>133640146</t>
-  </si>
-  <si>
-    <t>133640147</t>
-  </si>
-  <si>
-    <t>133640359</t>
-  </si>
-  <si>
-    <t>133641204</t>
-  </si>
-  <si>
-    <t>133641286</t>
-  </si>
-  <si>
-    <t>133641551</t>
-  </si>
-  <si>
-    <t>133641818</t>
-  </si>
-  <si>
-    <t>133641872</t>
-  </si>
-  <si>
-    <t>133642390</t>
-  </si>
-  <si>
-    <t>133642503</t>
-  </si>
-  <si>
-    <t>133642605</t>
-  </si>
-  <si>
-    <t>133642992</t>
-  </si>
-  <si>
-    <t>133643103</t>
-  </si>
-  <si>
-    <t>133643170</t>
-  </si>
-  <si>
-    <t>133643247</t>
-  </si>
-  <si>
-    <t>133643596</t>
-  </si>
-  <si>
-    <t>133643946</t>
-  </si>
-  <si>
-    <t>133644036</t>
-  </si>
-  <si>
-    <t>133644178</t>
-  </si>
-  <si>
-    <t>133644271</t>
-  </si>
-  <si>
-    <t>133644304</t>
-  </si>
-  <si>
-    <t>133644876</t>
-  </si>
-  <si>
-    <t>133644926</t>
-  </si>
-  <si>
-    <t>133645352</t>
-  </si>
-  <si>
-    <t>133645642</t>
-  </si>
-  <si>
-    <t>133646117</t>
-  </si>
-  <si>
-    <t>133646785</t>
-  </si>
-  <si>
-    <t>133646825</t>
-  </si>
-  <si>
-    <t>133647362</t>
-  </si>
-  <si>
-    <t>133647549</t>
-  </si>
-  <si>
-    <t>133647558</t>
-  </si>
-  <si>
-    <t>133647921</t>
-  </si>
-  <si>
-    <t>133648070</t>
-  </si>
-  <si>
-    <t>133648190</t>
-  </si>
-  <si>
-    <t>133648216</t>
-  </si>
-  <si>
-    <t>133648261</t>
-  </si>
-  <si>
-    <t>133648391</t>
-  </si>
-  <si>
-    <t>133648416</t>
-  </si>
-  <si>
-    <t>133648480</t>
-  </si>
-  <si>
-    <t>133648923</t>
-  </si>
-  <si>
-    <t>133649037</t>
-  </si>
-  <si>
-    <t>133649145</t>
-  </si>
-  <si>
-    <t>133649211</t>
-  </si>
-  <si>
-    <t>133649388</t>
-  </si>
-  <si>
-    <t>133649713</t>
-  </si>
-  <si>
-    <t>133649932</t>
-  </si>
-  <si>
-    <t>133650130</t>
-  </si>
-  <si>
-    <t>133650136</t>
-  </si>
-  <si>
-    <t>133650536</t>
-  </si>
-  <si>
-    <t>133650995</t>
-  </si>
-  <si>
-    <t>133650998</t>
-  </si>
-  <si>
-    <t>133651104</t>
-  </si>
-  <si>
-    <t>133651381</t>
-  </si>
-  <si>
-    <t>133651417</t>
-  </si>
-  <si>
-    <t>133651547</t>
-  </si>
-  <si>
-    <t>133651717</t>
-  </si>
-  <si>
-    <t>133651761</t>
-  </si>
-  <si>
-    <t>133651776</t>
-  </si>
-  <si>
-    <t>133651818</t>
-  </si>
-  <si>
-    <t>133652210</t>
-  </si>
-  <si>
-    <t>133652550</t>
-  </si>
-  <si>
-    <t>133652661</t>
-  </si>
-  <si>
-    <t>133652724</t>
-  </si>
-  <si>
-    <t>133652817</t>
-  </si>
-  <si>
-    <t>133652947</t>
-  </si>
-  <si>
-    <t>133653057</t>
-  </si>
-  <si>
-    <t>133653295</t>
-  </si>
-  <si>
-    <t>133653316</t>
-  </si>
-  <si>
-    <t>133653367</t>
-  </si>
-  <si>
-    <t>133653584</t>
-  </si>
-  <si>
-    <t>133653610</t>
-  </si>
-  <si>
-    <t>133653699</t>
-  </si>
-  <si>
-    <t>133653713</t>
-  </si>
-  <si>
-    <t>133653732</t>
-  </si>
-  <si>
-    <t>133653865</t>
-  </si>
-  <si>
-    <t>133653956</t>
-  </si>
-  <si>
-    <t>133653974</t>
-  </si>
-  <si>
-    <t>133654153</t>
-  </si>
-  <si>
-    <t>133654183</t>
-  </si>
-  <si>
-    <t>133654302</t>
-  </si>
-  <si>
-    <t>133654340</t>
-  </si>
-  <si>
-    <t>133654520</t>
-  </si>
-  <si>
-    <t>133654531</t>
-  </si>
-  <si>
-    <t>133654888</t>
-  </si>
-  <si>
-    <t>133655194</t>
-  </si>
-  <si>
-    <t>133655245</t>
-  </si>
-  <si>
-    <t>133655777</t>
-  </si>
-  <si>
-    <t>133655962</t>
-  </si>
-  <si>
-    <t>133655974</t>
+    <t>129470361</t>
+  </si>
+  <si>
+    <t>129476650</t>
+  </si>
+  <si>
+    <t>129515359</t>
+  </si>
+  <si>
+    <t>129574441</t>
+  </si>
+  <si>
+    <t>130084596</t>
+  </si>
+  <si>
+    <t>130175145</t>
+  </si>
+  <si>
+    <t>130244254</t>
+  </si>
+  <si>
+    <t>130722221</t>
+  </si>
+  <si>
+    <t>130858567</t>
+  </si>
+  <si>
+    <t>130929145</t>
+  </si>
+  <si>
+    <t>131077160</t>
+  </si>
+  <si>
+    <t>131158298</t>
+  </si>
+  <si>
+    <t>131268501</t>
+  </si>
+  <si>
+    <t>131282851</t>
+  </si>
+  <si>
+    <t>131798304</t>
+  </si>
+  <si>
+    <t>131852594</t>
+  </si>
+  <si>
+    <t>131905435</t>
+  </si>
+  <si>
+    <t>132169500</t>
+  </si>
+  <si>
+    <t>132238779</t>
+  </si>
+  <si>
+    <t>132349984</t>
+  </si>
+  <si>
+    <t>132531467</t>
+  </si>
+  <si>
+    <t>133024778</t>
+  </si>
+  <si>
+    <t>133157387</t>
+  </si>
+  <si>
+    <t>133462601</t>
+  </si>
+  <si>
+    <t>133500424</t>
+  </si>
+  <si>
+    <t>133656232</t>
+  </si>
+  <si>
+    <t>133656443</t>
+  </si>
+  <si>
+    <t>133656528</t>
+  </si>
+  <si>
+    <t>133656602</t>
+  </si>
+  <si>
+    <t>133656670</t>
+  </si>
+  <si>
+    <t>133656875</t>
+  </si>
+  <si>
+    <t>133656890</t>
+  </si>
+  <si>
+    <t>133656964</t>
+  </si>
+  <si>
+    <t>133657151</t>
+  </si>
+  <si>
+    <t>133657260</t>
+  </si>
+  <si>
+    <t>133657495</t>
+  </si>
+  <si>
+    <t>133657516</t>
+  </si>
+  <si>
+    <t>133657724</t>
+  </si>
+  <si>
+    <t>133657838</t>
+  </si>
+  <si>
+    <t>133657966</t>
+  </si>
+  <si>
+    <t>133658783</t>
+  </si>
+  <si>
+    <t>133659263</t>
+  </si>
+  <si>
+    <t>133659630</t>
+  </si>
+  <si>
+    <t>133659701</t>
+  </si>
+  <si>
+    <t>133659833</t>
+  </si>
+  <si>
+    <t>133659972</t>
+  </si>
+  <si>
+    <t>133660323</t>
+  </si>
+  <si>
+    <t>133660462</t>
+  </si>
+  <si>
+    <t>133660641</t>
+  </si>
+  <si>
+    <t>133660749</t>
+  </si>
+  <si>
+    <t>133660757</t>
+  </si>
+  <si>
+    <t>133661144</t>
+  </si>
+  <si>
+    <t>133661199</t>
+  </si>
+  <si>
+    <t>133661217</t>
+  </si>
+  <si>
+    <t>133661278</t>
+  </si>
+  <si>
+    <t>133661314</t>
+  </si>
+  <si>
+    <t>133661367</t>
+  </si>
+  <si>
+    <t>133661408</t>
+  </si>
+  <si>
+    <t>133661480</t>
+  </si>
+  <si>
+    <t>133661501</t>
+  </si>
+  <si>
+    <t>133661607</t>
+  </si>
+  <si>
+    <t>133661609</t>
+  </si>
+  <si>
+    <t>133661661</t>
+  </si>
+  <si>
+    <t>133661683</t>
+  </si>
+  <si>
+    <t>133661925</t>
+  </si>
+  <si>
+    <t>133662257</t>
+  </si>
+  <si>
+    <t>133662424</t>
+  </si>
+  <si>
+    <t>133662472</t>
+  </si>
+  <si>
+    <t>133662597</t>
+  </si>
+  <si>
+    <t>133662702</t>
+  </si>
+  <si>
+    <t>133662786</t>
+  </si>
+  <si>
+    <t>133662817</t>
+  </si>
+  <si>
+    <t>133662893</t>
+  </si>
+  <si>
+    <t>133663091</t>
+  </si>
+  <si>
+    <t>133663799</t>
+  </si>
+  <si>
+    <t>133664038</t>
+  </si>
+  <si>
+    <t>133664128</t>
+  </si>
+  <si>
+    <t>133664132</t>
+  </si>
+  <si>
+    <t>133664446</t>
+  </si>
+  <si>
+    <t>133664465</t>
+  </si>
+  <si>
+    <t>133664730</t>
+  </si>
+  <si>
+    <t>133664918</t>
+  </si>
+  <si>
+    <t>133664991</t>
+  </si>
+  <si>
+    <t>133665053</t>
+  </si>
+  <si>
+    <t>133665361</t>
+  </si>
+  <si>
+    <t>133665568</t>
+  </si>
+  <si>
+    <t>133665699</t>
+  </si>
+  <si>
+    <t>133666005</t>
+  </si>
+  <si>
+    <t>133666327</t>
+  </si>
+  <si>
+    <t>133666388</t>
+  </si>
+  <si>
+    <t>133666597</t>
+  </si>
+  <si>
+    <t>133667435</t>
+  </si>
+  <si>
+    <t>133667453</t>
+  </si>
+  <si>
+    <t>133667865</t>
+  </si>
+  <si>
+    <t>133668217</t>
+  </si>
+  <si>
+    <t>133668251</t>
+  </si>
+  <si>
+    <t>133668311</t>
+  </si>
+  <si>
+    <t>133668475</t>
+  </si>
+  <si>
+    <t>133668943</t>
+  </si>
+  <si>
+    <t>133669004</t>
+  </si>
+  <si>
+    <t>133669156</t>
+  </si>
+  <si>
+    <t>133669415</t>
+  </si>
+  <si>
+    <t>133669484</t>
+  </si>
+  <si>
+    <t>133669502</t>
+  </si>
+  <si>
+    <t>133669544</t>
+  </si>
+  <si>
+    <t>133669553</t>
+  </si>
+  <si>
+    <t>133669583</t>
+  </si>
+  <si>
+    <t>133669586</t>
+  </si>
+  <si>
+    <t>133669732</t>
+  </si>
+  <si>
+    <t>133669756</t>
+  </si>
+  <si>
+    <t>133669993</t>
+  </si>
+  <si>
+    <t>133670196</t>
+  </si>
+  <si>
+    <t>133670337</t>
+  </si>
+  <si>
+    <t>133670576</t>
+  </si>
+  <si>
+    <t>133670904</t>
+  </si>
+  <si>
+    <t>133671002</t>
+  </si>
+  <si>
+    <t>133671006</t>
+  </si>
+  <si>
+    <t>133671037</t>
+  </si>
+  <si>
+    <t>133671123</t>
+  </si>
+  <si>
+    <t>133671295</t>
+  </si>
+  <si>
+    <t>133671420</t>
+  </si>
+  <si>
+    <t>133671483</t>
+  </si>
+  <si>
+    <t>133671489</t>
+  </si>
+  <si>
+    <t>133671569</t>
+  </si>
+  <si>
+    <t>133671659</t>
+  </si>
+  <si>
+    <t>133671761</t>
+  </si>
+  <si>
+    <t>133671936</t>
+  </si>
+  <si>
+    <t>133671940</t>
+  </si>
+  <si>
+    <t>133672251</t>
+  </si>
+  <si>
+    <t>133672297</t>
+  </si>
+  <si>
+    <t>133672365</t>
+  </si>
+  <si>
+    <t>133672398</t>
+  </si>
+  <si>
+    <t>133672435</t>
+  </si>
+  <si>
+    <t>133672589</t>
+  </si>
+  <si>
+    <t>133672648</t>
+  </si>
+  <si>
+    <t>133672752</t>
+  </si>
+  <si>
+    <t>133672946</t>
+  </si>
+  <si>
+    <t>133673115</t>
+  </si>
+  <si>
+    <t>133673174</t>
+  </si>
+  <si>
+    <t>133673333</t>
+  </si>
+  <si>
+    <t>133673604</t>
+  </si>
+  <si>
+    <t>133673675</t>
+  </si>
+  <si>
+    <t>133673737</t>
+  </si>
+  <si>
+    <t>133673861</t>
+  </si>
+  <si>
+    <t>133673890</t>
+  </si>
+  <si>
+    <t>133674241</t>
+  </si>
+  <si>
+    <t>133674242</t>
+  </si>
+  <si>
+    <t>133674287</t>
+  </si>
+  <si>
+    <t>133674418</t>
+  </si>
+  <si>
+    <t>133674659</t>
+  </si>
+  <si>
+    <t>133674688</t>
+  </si>
+  <si>
+    <t>133674754</t>
+  </si>
+  <si>
+    <t>133674989</t>
+  </si>
+  <si>
+    <t>133675040</t>
+  </si>
+  <si>
+    <t>133675042</t>
+  </si>
+  <si>
+    <t>133675107</t>
+  </si>
+  <si>
+    <t>133675209</t>
+  </si>
+  <si>
+    <t>133675211</t>
+  </si>
+  <si>
+    <t>133675306</t>
+  </si>
+  <si>
+    <t>133675797</t>
+  </si>
+  <si>
+    <t>133675908</t>
+  </si>
+  <si>
+    <t>133676306</t>
+  </si>
+  <si>
+    <t>133676818</t>
+  </si>
+  <si>
+    <t>133676851</t>
+  </si>
+  <si>
+    <t>133676905</t>
+  </si>
+  <si>
+    <t>133676938</t>
   </si>
 </sst>
 </file>
@@ -825,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2231,8 +2351,448 @@
         <v>4</v>
       </c>
     </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C127" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C167" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9753344-9192-4B6E-97D8-C16A97CE4527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F7BE22-8E8B-4C7D-BC92-7A1F20A47A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$184</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="188">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,802 +45,553 @@
     <t>.</t>
   </si>
   <si>
-    <t>129476650</t>
-  </si>
-  <si>
-    <t>129481808</t>
-  </si>
-  <si>
-    <t>129799952</t>
-  </si>
-  <si>
-    <t>130068346</t>
-  </si>
-  <si>
-    <t>130337739</t>
-  </si>
-  <si>
-    <t>130343530</t>
-  </si>
-  <si>
-    <t>130728175</t>
-  </si>
-  <si>
-    <t>130876290</t>
-  </si>
-  <si>
-    <t>130938939</t>
-  </si>
-  <si>
-    <t>130954816</t>
-  </si>
-  <si>
-    <t>131236814</t>
-  </si>
-  <si>
-    <t>131282996</t>
-  </si>
-  <si>
-    <t>131458095</t>
-  </si>
-  <si>
-    <t>131527040</t>
-  </si>
-  <si>
-    <t>131852795</t>
-  </si>
-  <si>
-    <t>132066327</t>
-  </si>
-  <si>
-    <t>132121257</t>
-  </si>
-  <si>
-    <t>132351897</t>
-  </si>
-  <si>
-    <t>132399107</t>
-  </si>
-  <si>
-    <t>132453385</t>
-  </si>
-  <si>
-    <t>132541002</t>
-  </si>
-  <si>
-    <t>133011346</t>
-  </si>
-  <si>
-    <t>133106881</t>
-  </si>
-  <si>
-    <t>133193928</t>
-  </si>
-  <si>
-    <t>133465940</t>
-  </si>
-  <si>
-    <t>133762431</t>
-  </si>
-  <si>
-    <t>133835025</t>
-  </si>
-  <si>
-    <t>133835081</t>
-  </si>
-  <si>
-    <t>133835122</t>
-  </si>
-  <si>
-    <t>133835144</t>
-  </si>
-  <si>
-    <t>133835187</t>
-  </si>
-  <si>
-    <t>133835267</t>
-  </si>
-  <si>
-    <t>133835657</t>
-  </si>
-  <si>
-    <t>133835986</t>
-  </si>
-  <si>
-    <t>133836325</t>
-  </si>
-  <si>
-    <t>133836336</t>
-  </si>
-  <si>
-    <t>133836552</t>
-  </si>
-  <si>
-    <t>133836727</t>
-  </si>
-  <si>
-    <t>133836828</t>
-  </si>
-  <si>
-    <t>133836911</t>
-  </si>
-  <si>
-    <t>133836912</t>
-  </si>
-  <si>
-    <t>133836968</t>
-  </si>
-  <si>
-    <t>133836999</t>
-  </si>
-  <si>
-    <t>133837198</t>
-  </si>
-  <si>
-    <t>133837370</t>
-  </si>
-  <si>
-    <t>133837454</t>
-  </si>
-  <si>
-    <t>133837504</t>
-  </si>
-  <si>
-    <t>133837527</t>
-  </si>
-  <si>
-    <t>133837714</t>
-  </si>
-  <si>
-    <t>133838040</t>
-  </si>
-  <si>
-    <t>133838260</t>
-  </si>
-  <si>
-    <t>133838644</t>
-  </si>
-  <si>
-    <t>133839162</t>
-  </si>
-  <si>
-    <t>133839188</t>
-  </si>
-  <si>
-    <t>133839597</t>
-  </si>
-  <si>
-    <t>133839687</t>
-  </si>
-  <si>
-    <t>133839729</t>
-  </si>
-  <si>
-    <t>133839905</t>
-  </si>
-  <si>
-    <t>133839982</t>
-  </si>
-  <si>
-    <t>133839996</t>
-  </si>
-  <si>
-    <t>133840038</t>
-  </si>
-  <si>
-    <t>133840095</t>
-  </si>
-  <si>
-    <t>133840123</t>
-  </si>
-  <si>
-    <t>133840251</t>
-  </si>
-  <si>
-    <t>133840290</t>
-  </si>
-  <si>
-    <t>133840379</t>
-  </si>
-  <si>
-    <t>133840382</t>
-  </si>
-  <si>
-    <t>133840747</t>
-  </si>
-  <si>
-    <t>133840821</t>
-  </si>
-  <si>
-    <t>133840864</t>
-  </si>
-  <si>
-    <t>133841135</t>
-  </si>
-  <si>
-    <t>133841166</t>
-  </si>
-  <si>
-    <t>133841281</t>
-  </si>
-  <si>
-    <t>133841386</t>
-  </si>
-  <si>
-    <t>133841390</t>
-  </si>
-  <si>
-    <t>133841502</t>
-  </si>
-  <si>
-    <t>133841573</t>
-  </si>
-  <si>
-    <t>133841686</t>
-  </si>
-  <si>
-    <t>133841756</t>
-  </si>
-  <si>
-    <t>133841791</t>
-  </si>
-  <si>
-    <t>133842224</t>
-  </si>
-  <si>
-    <t>133842288</t>
-  </si>
-  <si>
-    <t>133842290</t>
-  </si>
-  <si>
-    <t>133842344</t>
-  </si>
-  <si>
-    <t>133842346</t>
-  </si>
-  <si>
-    <t>133842558</t>
-  </si>
-  <si>
-    <t>133842793</t>
-  </si>
-  <si>
-    <t>133842903</t>
-  </si>
-  <si>
-    <t>133843065</t>
-  </si>
-  <si>
-    <t>133843177</t>
-  </si>
-  <si>
-    <t>133843511</t>
-  </si>
-  <si>
-    <t>133843546</t>
-  </si>
-  <si>
-    <t>133843657</t>
-  </si>
-  <si>
-    <t>133844516</t>
-  </si>
-  <si>
-    <t>133844533</t>
-  </si>
-  <si>
-    <t>133844566</t>
-  </si>
-  <si>
-    <t>133844880</t>
-  </si>
-  <si>
-    <t>133844999</t>
-  </si>
-  <si>
-    <t>133845051</t>
-  </si>
-  <si>
-    <t>133845271</t>
-  </si>
-  <si>
-    <t>133845334</t>
-  </si>
-  <si>
-    <t>133845390</t>
-  </si>
-  <si>
-    <t>133845796</t>
-  </si>
-  <si>
-    <t>133845801</t>
-  </si>
-  <si>
-    <t>133846095</t>
-  </si>
-  <si>
-    <t>133846194</t>
-  </si>
-  <si>
-    <t>133846476</t>
-  </si>
-  <si>
-    <t>133846522</t>
-  </si>
-  <si>
-    <t>133846577</t>
-  </si>
-  <si>
-    <t>133846836</t>
-  </si>
-  <si>
-    <t>133846845</t>
-  </si>
-  <si>
-    <t>133846936</t>
-  </si>
-  <si>
-    <t>133847042</t>
-  </si>
-  <si>
-    <t>133847230</t>
-  </si>
-  <si>
-    <t>133847231</t>
-  </si>
-  <si>
-    <t>133847234</t>
-  </si>
-  <si>
-    <t>133847302</t>
-  </si>
-  <si>
-    <t>133847310</t>
-  </si>
-  <si>
-    <t>133847315</t>
-  </si>
-  <si>
-    <t>133847482</t>
-  </si>
-  <si>
-    <t>133847547</t>
-  </si>
-  <si>
-    <t>133847708</t>
-  </si>
-  <si>
-    <t>133847963</t>
-  </si>
-  <si>
-    <t>133848784</t>
-  </si>
-  <si>
-    <t>133848878</t>
-  </si>
-  <si>
-    <t>133848943</t>
-  </si>
-  <si>
-    <t>133848977</t>
-  </si>
-  <si>
-    <t>133849162</t>
-  </si>
-  <si>
-    <t>133849202</t>
-  </si>
-  <si>
-    <t>133849309</t>
-  </si>
-  <si>
-    <t>133849486</t>
-  </si>
-  <si>
-    <t>133849538</t>
-  </si>
-  <si>
-    <t>133849592</t>
-  </si>
-  <si>
-    <t>133849644</t>
-  </si>
-  <si>
-    <t>133849844</t>
-  </si>
-  <si>
-    <t>133849919</t>
-  </si>
-  <si>
-    <t>133850148</t>
-  </si>
-  <si>
-    <t>133850215</t>
-  </si>
-  <si>
-    <t>133850262</t>
-  </si>
-  <si>
-    <t>133850264</t>
-  </si>
-  <si>
-    <t>133850327</t>
-  </si>
-  <si>
-    <t>133850522</t>
-  </si>
-  <si>
-    <t>133850682</t>
-  </si>
-  <si>
-    <t>133850786</t>
-  </si>
-  <si>
-    <t>133850810</t>
-  </si>
-  <si>
-    <t>133850911</t>
-  </si>
-  <si>
-    <t>133851015</t>
-  </si>
-  <si>
-    <t>133851065</t>
-  </si>
-  <si>
-    <t>133851275</t>
-  </si>
-  <si>
-    <t>133851427</t>
-  </si>
-  <si>
-    <t>133851542</t>
-  </si>
-  <si>
-    <t>133851577</t>
-  </si>
-  <si>
-    <t>133851660</t>
-  </si>
-  <si>
-    <t>133851851</t>
-  </si>
-  <si>
-    <t>133851905</t>
-  </si>
-  <si>
-    <t>133851962</t>
-  </si>
-  <si>
-    <t>133852044</t>
-  </si>
-  <si>
-    <t>133852072</t>
-  </si>
-  <si>
-    <t>133852144</t>
-  </si>
-  <si>
-    <t>133852150</t>
-  </si>
-  <si>
-    <t>133852304</t>
-  </si>
-  <si>
-    <t>133852339</t>
-  </si>
-  <si>
-    <t>133852393</t>
-  </si>
-  <si>
-    <t>133852443</t>
-  </si>
-  <si>
-    <t>133852579</t>
-  </si>
-  <si>
-    <t>133852620</t>
-  </si>
-  <si>
-    <t>133852648</t>
-  </si>
-  <si>
-    <t>133852709</t>
-  </si>
-  <si>
-    <t>133852715</t>
-  </si>
-  <si>
-    <t>133852745</t>
-  </si>
-  <si>
-    <t>133852746</t>
-  </si>
-  <si>
-    <t>133852758</t>
-  </si>
-  <si>
-    <t>133852831</t>
-  </si>
-  <si>
-    <t>133852997</t>
-  </si>
-  <si>
-    <t>133853107</t>
-  </si>
-  <si>
-    <t>133853183</t>
-  </si>
-  <si>
-    <t>133853259</t>
-  </si>
-  <si>
-    <t>133853476</t>
-  </si>
-  <si>
-    <t>133853561</t>
-  </si>
-  <si>
-    <t>133853753</t>
-  </si>
-  <si>
-    <t>133853882</t>
-  </si>
-  <si>
-    <t>133853915</t>
-  </si>
-  <si>
-    <t>133854010</t>
-  </si>
-  <si>
-    <t>133854335</t>
-  </si>
-  <si>
-    <t>133854342</t>
-  </si>
-  <si>
-    <t>133854530</t>
-  </si>
-  <si>
-    <t>133854560</t>
-  </si>
-  <si>
-    <t>133854641</t>
-  </si>
-  <si>
-    <t>133854654</t>
-  </si>
-  <si>
-    <t>133854689</t>
-  </si>
-  <si>
-    <t>133854699</t>
-  </si>
-  <si>
-    <t>133854812</t>
-  </si>
-  <si>
-    <t>133854825</t>
-  </si>
-  <si>
-    <t>133854852</t>
-  </si>
-  <si>
-    <t>133854858</t>
-  </si>
-  <si>
-    <t>133854921</t>
-  </si>
-  <si>
-    <t>133854956</t>
-  </si>
-  <si>
-    <t>133854986</t>
-  </si>
-  <si>
-    <t>133855033</t>
-  </si>
-  <si>
-    <t>133855142</t>
-  </si>
-  <si>
-    <t>133855148</t>
-  </si>
-  <si>
-    <t>133855274</t>
-  </si>
-  <si>
-    <t>133855283</t>
-  </si>
-  <si>
-    <t>133855343</t>
-  </si>
-  <si>
-    <t>133855357</t>
-  </si>
-  <si>
-    <t>133855392</t>
-  </si>
-  <si>
-    <t>133855435</t>
-  </si>
-  <si>
-    <t>133855488</t>
-  </si>
-  <si>
-    <t>133855540</t>
-  </si>
-  <si>
-    <t>133855601</t>
-  </si>
-  <si>
-    <t>133855675</t>
-  </si>
-  <si>
-    <t>133855689</t>
-  </si>
-  <si>
-    <t>133855793</t>
-  </si>
-  <si>
-    <t>133855797</t>
-  </si>
-  <si>
-    <t>133855800</t>
-  </si>
-  <si>
-    <t>133855942</t>
-  </si>
-  <si>
-    <t>133856003</t>
-  </si>
-  <si>
-    <t>133856634</t>
-  </si>
-  <si>
-    <t>133856703</t>
-  </si>
-  <si>
-    <t>133856754</t>
-  </si>
-  <si>
-    <t>133856845</t>
-  </si>
-  <si>
-    <t>133857057</t>
-  </si>
-  <si>
-    <t>133857097</t>
-  </si>
-  <si>
-    <t>133857112</t>
-  </si>
-  <si>
-    <t>133857492</t>
-  </si>
-  <si>
-    <t>133857531</t>
-  </si>
-  <si>
-    <t>133857656</t>
-  </si>
-  <si>
-    <t>133857935</t>
-  </si>
-  <si>
-    <t>133858002</t>
-  </si>
-  <si>
-    <t>133858004</t>
-  </si>
-  <si>
-    <t>133858031</t>
-  </si>
-  <si>
-    <t>133858068</t>
-  </si>
-  <si>
-    <t>133858180</t>
-  </si>
-  <si>
-    <t>133858230</t>
-  </si>
-  <si>
-    <t>133858235</t>
-  </si>
-  <si>
-    <t>133858257</t>
-  </si>
-  <si>
-    <t>133858328</t>
-  </si>
-  <si>
-    <t>133858333</t>
-  </si>
-  <si>
-    <t>133858431</t>
-  </si>
-  <si>
-    <t>133858440</t>
-  </si>
-  <si>
-    <t>133858521</t>
-  </si>
-  <si>
-    <t>133858576</t>
-  </si>
-  <si>
-    <t>133858595</t>
-  </si>
-  <si>
-    <t>133858638</t>
-  </si>
-  <si>
-    <t>133858697</t>
-  </si>
-  <si>
-    <t>133858785</t>
-  </si>
-  <si>
-    <t>133858800</t>
-  </si>
-  <si>
-    <t>133858875</t>
-  </si>
-  <si>
-    <t>133858901</t>
-  </si>
-  <si>
-    <t>133858910</t>
-  </si>
-  <si>
-    <t>133858911</t>
-  </si>
-  <si>
-    <t>133858935</t>
-  </si>
-  <si>
-    <t>133859062</t>
-  </si>
-  <si>
-    <t>133859289</t>
-  </si>
-  <si>
-    <t>133859356</t>
-  </si>
-  <si>
-    <t>133859440</t>
-  </si>
-  <si>
-    <t>133859472</t>
-  </si>
-  <si>
-    <t>133859520</t>
-  </si>
-  <si>
-    <t>133859614</t>
-  </si>
-  <si>
-    <t>133859717</t>
-  </si>
-  <si>
-    <t>133859971</t>
-  </si>
-  <si>
-    <t>133860141</t>
-  </si>
-  <si>
-    <t>133860147</t>
-  </si>
-  <si>
-    <t>133860187</t>
-  </si>
-  <si>
-    <t>133860450</t>
-  </si>
-  <si>
-    <t>133860604</t>
+    <t>129182400</t>
+  </si>
+  <si>
+    <t>129239378</t>
+  </si>
+  <si>
+    <t>129303120</t>
+  </si>
+  <si>
+    <t>129849582</t>
+  </si>
+  <si>
+    <t>129961283</t>
+  </si>
+  <si>
+    <t>130418823</t>
+  </si>
+  <si>
+    <t>130635961</t>
+  </si>
+  <si>
+    <t>131171668</t>
+  </si>
+  <si>
+    <t>131220959</t>
+  </si>
+  <si>
+    <t>131799946</t>
+  </si>
+  <si>
+    <t>131853712</t>
+  </si>
+  <si>
+    <t>131902700</t>
+  </si>
+  <si>
+    <t>131905435</t>
+  </si>
+  <si>
+    <t>132168558</t>
+  </si>
+  <si>
+    <t>132241243</t>
+  </si>
+  <si>
+    <t>132247090</t>
+  </si>
+  <si>
+    <t>132349984</t>
+  </si>
+  <si>
+    <t>132425535</t>
+  </si>
+  <si>
+    <t>132772383</t>
+  </si>
+  <si>
+    <t>132799079</t>
+  </si>
+  <si>
+    <t>132829489</t>
+  </si>
+  <si>
+    <t>132927678</t>
+  </si>
+  <si>
+    <t>133041270</t>
+  </si>
+  <si>
+    <t>133370526</t>
+  </si>
+  <si>
+    <t>133463849</t>
+  </si>
+  <si>
+    <t>133853076</t>
+  </si>
+  <si>
+    <t>133860954</t>
+  </si>
+  <si>
+    <t>133861062</t>
+  </si>
+  <si>
+    <t>133861099</t>
+  </si>
+  <si>
+    <t>133861148</t>
+  </si>
+  <si>
+    <t>133861151</t>
+  </si>
+  <si>
+    <t>133861256</t>
+  </si>
+  <si>
+    <t>133861268</t>
+  </si>
+  <si>
+    <t>133861461</t>
+  </si>
+  <si>
+    <t>133861530</t>
+  </si>
+  <si>
+    <t>133862319</t>
+  </si>
+  <si>
+    <t>133862333</t>
+  </si>
+  <si>
+    <t>133862539</t>
+  </si>
+  <si>
+    <t>133862734</t>
+  </si>
+  <si>
+    <t>133862951</t>
+  </si>
+  <si>
+    <t>133863174</t>
+  </si>
+  <si>
+    <t>133863401</t>
+  </si>
+  <si>
+    <t>133863740</t>
+  </si>
+  <si>
+    <t>133864073</t>
+  </si>
+  <si>
+    <t>133864075</t>
+  </si>
+  <si>
+    <t>133864097</t>
+  </si>
+  <si>
+    <t>133864174</t>
+  </si>
+  <si>
+    <t>133864385</t>
+  </si>
+  <si>
+    <t>133864644</t>
+  </si>
+  <si>
+    <t>133865015</t>
+  </si>
+  <si>
+    <t>133865028</t>
+  </si>
+  <si>
+    <t>133865520</t>
+  </si>
+  <si>
+    <t>133865787</t>
+  </si>
+  <si>
+    <t>133865799</t>
+  </si>
+  <si>
+    <t>133866069</t>
+  </si>
+  <si>
+    <t>133866087</t>
+  </si>
+  <si>
+    <t>133866293</t>
+  </si>
+  <si>
+    <t>133866326</t>
+  </si>
+  <si>
+    <t>133866373</t>
+  </si>
+  <si>
+    <t>133866437</t>
+  </si>
+  <si>
+    <t>133866477</t>
+  </si>
+  <si>
+    <t>133866482</t>
+  </si>
+  <si>
+    <t>133866612</t>
+  </si>
+  <si>
+    <t>133866716</t>
+  </si>
+  <si>
+    <t>133866781</t>
+  </si>
+  <si>
+    <t>133866886</t>
+  </si>
+  <si>
+    <t>133867026</t>
+  </si>
+  <si>
+    <t>133867114</t>
+  </si>
+  <si>
+    <t>133867518</t>
+  </si>
+  <si>
+    <t>133867535</t>
+  </si>
+  <si>
+    <t>133867667</t>
+  </si>
+  <si>
+    <t>133867891</t>
+  </si>
+  <si>
+    <t>133867927</t>
+  </si>
+  <si>
+    <t>133868104</t>
+  </si>
+  <si>
+    <t>133868309</t>
+  </si>
+  <si>
+    <t>133868654</t>
+  </si>
+  <si>
+    <t>133868656</t>
+  </si>
+  <si>
+    <t>133868677</t>
+  </si>
+  <si>
+    <t>133868830</t>
+  </si>
+  <si>
+    <t>133868992</t>
+  </si>
+  <si>
+    <t>133869062</t>
+  </si>
+  <si>
+    <t>133869105</t>
+  </si>
+  <si>
+    <t>133869433</t>
+  </si>
+  <si>
+    <t>133869524</t>
+  </si>
+  <si>
+    <t>133869625</t>
+  </si>
+  <si>
+    <t>133869674</t>
+  </si>
+  <si>
+    <t>133869684</t>
+  </si>
+  <si>
+    <t>133870073</t>
+  </si>
+  <si>
+    <t>133870129</t>
+  </si>
+  <si>
+    <t>133870219</t>
+  </si>
+  <si>
+    <t>133870244</t>
+  </si>
+  <si>
+    <t>133870282</t>
+  </si>
+  <si>
+    <t>133870389</t>
+  </si>
+  <si>
+    <t>133870532</t>
+  </si>
+  <si>
+    <t>133870627</t>
+  </si>
+  <si>
+    <t>133870852</t>
+  </si>
+  <si>
+    <t>133870924</t>
+  </si>
+  <si>
+    <t>133871022</t>
+  </si>
+  <si>
+    <t>133871171</t>
+  </si>
+  <si>
+    <t>133871240</t>
+  </si>
+  <si>
+    <t>133871543</t>
+  </si>
+  <si>
+    <t>133871837</t>
+  </si>
+  <si>
+    <t>133871874</t>
+  </si>
+  <si>
+    <t>133871983</t>
+  </si>
+  <si>
+    <t>133871993</t>
+  </si>
+  <si>
+    <t>133872254</t>
+  </si>
+  <si>
+    <t>133872675</t>
+  </si>
+  <si>
+    <t>133872682</t>
+  </si>
+  <si>
+    <t>133872990</t>
+  </si>
+  <si>
+    <t>133873123</t>
+  </si>
+  <si>
+    <t>133873226</t>
+  </si>
+  <si>
+    <t>133873348</t>
+  </si>
+  <si>
+    <t>133873638</t>
+  </si>
+  <si>
+    <t>133873753</t>
+  </si>
+  <si>
+    <t>133873854</t>
+  </si>
+  <si>
+    <t>133873870</t>
+  </si>
+  <si>
+    <t>133873889</t>
+  </si>
+  <si>
+    <t>133873972</t>
+  </si>
+  <si>
+    <t>133873991</t>
+  </si>
+  <si>
+    <t>133874132</t>
+  </si>
+  <si>
+    <t>133874146</t>
+  </si>
+  <si>
+    <t>133874234</t>
+  </si>
+  <si>
+    <t>133874411</t>
+  </si>
+  <si>
+    <t>133874558</t>
+  </si>
+  <si>
+    <t>133874778</t>
+  </si>
+  <si>
+    <t>133875051</t>
+  </si>
+  <si>
+    <t>133875272</t>
+  </si>
+  <si>
+    <t>133875344</t>
+  </si>
+  <si>
+    <t>133875420</t>
+  </si>
+  <si>
+    <t>133875560</t>
+  </si>
+  <si>
+    <t>133875580</t>
+  </si>
+  <si>
+    <t>133875631</t>
+  </si>
+  <si>
+    <t>133875632</t>
+  </si>
+  <si>
+    <t>133876005</t>
+  </si>
+  <si>
+    <t>133876009</t>
+  </si>
+  <si>
+    <t>133876127</t>
+  </si>
+  <si>
+    <t>133876185</t>
+  </si>
+  <si>
+    <t>133876250</t>
+  </si>
+  <si>
+    <t>133876269</t>
+  </si>
+  <si>
+    <t>133876306</t>
+  </si>
+  <si>
+    <t>133876571</t>
+  </si>
+  <si>
+    <t>133876627</t>
+  </si>
+  <si>
+    <t>133876723</t>
+  </si>
+  <si>
+    <t>133876760</t>
+  </si>
+  <si>
+    <t>133876920</t>
+  </si>
+  <si>
+    <t>133877059</t>
+  </si>
+  <si>
+    <t>133877230</t>
+  </si>
+  <si>
+    <t>133877272</t>
+  </si>
+  <si>
+    <t>133877358</t>
+  </si>
+  <si>
+    <t>133877396</t>
+  </si>
+  <si>
+    <t>133877557</t>
+  </si>
+  <si>
+    <t>133877786</t>
+  </si>
+  <si>
+    <t>133877964</t>
+  </si>
+  <si>
+    <t>133878008</t>
+  </si>
+  <si>
+    <t>133878260</t>
+  </si>
+  <si>
+    <t>133878312</t>
+  </si>
+  <si>
+    <t>133878416</t>
+  </si>
+  <si>
+    <t>133878610</t>
+  </si>
+  <si>
+    <t>133878615</t>
+  </si>
+  <si>
+    <t>133878775</t>
+  </si>
+  <si>
+    <t>133878793</t>
+  </si>
+  <si>
+    <t>133878957</t>
+  </si>
+  <si>
+    <t>133878986</t>
+  </si>
+  <si>
+    <t>133879112</t>
+  </si>
+  <si>
+    <t>133879298</t>
+  </si>
+  <si>
+    <t>133879322</t>
+  </si>
+  <si>
+    <t>133879327</t>
+  </si>
+  <si>
+    <t>133879342</t>
+  </si>
+  <si>
+    <t>133879362</t>
+  </si>
+  <si>
+    <t>133879365</t>
+  </si>
+  <si>
+    <t>133879417</t>
+  </si>
+  <si>
+    <t>133879501</t>
+  </si>
+  <si>
+    <t>133879524</t>
+  </si>
+  <si>
+    <t>133879528</t>
+  </si>
+  <si>
+    <t>133880014</t>
+  </si>
+  <si>
+    <t>133880078</t>
+  </si>
+  <si>
+    <t>133880378</t>
+  </si>
+  <si>
+    <t>133880525</t>
+  </si>
+  <si>
+    <t>133880526</t>
+  </si>
+  <si>
+    <t>133880760</t>
+  </si>
+  <si>
+    <t>133881218</t>
+  </si>
+  <si>
+    <t>133881287</t>
+  </si>
+  <si>
+    <t>133881288</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C267"/>
+  <dimension ref="A1:C184"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3278,921 +3029,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B200" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B213" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B214" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C214" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B215" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B216" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B220" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B223" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B237" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B239" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B242" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B243" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B245" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B246" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B247" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B248" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C250" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B251" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C256" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B257" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B258" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B261" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B262" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C262" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B263" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C264" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C266" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B267" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C184" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB70498F-FEC1-476E-B814-2D0F7F15AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01FC5C3-8E46-4413-BDF3-900A28DECB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="256">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,688 +45,757 @@
     <t>.</t>
   </si>
   <si>
-    <t>129341811</t>
-  </si>
-  <si>
-    <t>129378562</t>
-  </si>
-  <si>
-    <t>129579544</t>
-  </si>
-  <si>
-    <t>129638630</t>
-  </si>
-  <si>
-    <t>129642946</t>
-  </si>
-  <si>
-    <t>129873946</t>
-  </si>
-  <si>
-    <t>130185701</t>
-  </si>
-  <si>
-    <t>130334054</t>
-  </si>
-  <si>
-    <t>130389229</t>
-  </si>
-  <si>
-    <t>130535012</t>
-  </si>
-  <si>
-    <t>130572982</t>
-  </si>
-  <si>
-    <t>130626810</t>
-  </si>
-  <si>
-    <t>130681727</t>
-  </si>
-  <si>
-    <t>130976646</t>
-  </si>
-  <si>
-    <t>131004512</t>
-  </si>
-  <si>
-    <t>131033039</t>
-  </si>
-  <si>
-    <t>131063254</t>
-  </si>
-  <si>
-    <t>131361595</t>
-  </si>
-  <si>
-    <t>131394205</t>
-  </si>
-  <si>
-    <t>131485067</t>
-  </si>
-  <si>
-    <t>131526580</t>
-  </si>
-  <si>
-    <t>131528344</t>
-  </si>
-  <si>
-    <t>131741299</t>
-  </si>
-  <si>
-    <t>132063096</t>
-  </si>
-  <si>
-    <t>132083918</t>
-  </si>
-  <si>
-    <t>132132049</t>
-  </si>
-  <si>
-    <t>132591772</t>
-  </si>
-  <si>
-    <t>132659865</t>
-  </si>
-  <si>
-    <t>132785100</t>
-  </si>
-  <si>
-    <t>132884230</t>
-  </si>
-  <si>
-    <t>133260135</t>
-  </si>
-  <si>
-    <t>133324758</t>
-  </si>
-  <si>
-    <t>133333399</t>
-  </si>
-  <si>
-    <t>133764646</t>
-  </si>
-  <si>
-    <t>133903563</t>
-  </si>
-  <si>
-    <t>133903565</t>
-  </si>
-  <si>
-    <t>133903728</t>
-  </si>
-  <si>
-    <t>133903883</t>
-  </si>
-  <si>
-    <t>133903993</t>
-  </si>
-  <si>
-    <t>133904254</t>
-  </si>
-  <si>
-    <t>133904268</t>
-  </si>
-  <si>
-    <t>133904506</t>
-  </si>
-  <si>
-    <t>133904782</t>
-  </si>
-  <si>
-    <t>133904959</t>
-  </si>
-  <si>
-    <t>133904960</t>
-  </si>
-  <si>
-    <t>133905114</t>
-  </si>
-  <si>
-    <t>133905256</t>
-  </si>
-  <si>
-    <t>133905268</t>
-  </si>
-  <si>
-    <t>133905399</t>
-  </si>
-  <si>
-    <t>133905503</t>
-  </si>
-  <si>
-    <t>133905545</t>
-  </si>
-  <si>
-    <t>133905743</t>
-  </si>
-  <si>
-    <t>133905813</t>
-  </si>
-  <si>
-    <t>133906171</t>
-  </si>
-  <si>
-    <t>133906293</t>
-  </si>
-  <si>
-    <t>133906296</t>
-  </si>
-  <si>
-    <t>133906372</t>
-  </si>
-  <si>
-    <t>133906861</t>
-  </si>
-  <si>
-    <t>133906922</t>
-  </si>
-  <si>
-    <t>133906961</t>
-  </si>
-  <si>
-    <t>133907106</t>
-  </si>
-  <si>
-    <t>133907119</t>
-  </si>
-  <si>
-    <t>133907749</t>
-  </si>
-  <si>
-    <t>133907804</t>
-  </si>
-  <si>
-    <t>133907806</t>
-  </si>
-  <si>
-    <t>133907925</t>
-  </si>
-  <si>
-    <t>133908113</t>
-  </si>
-  <si>
-    <t>133908240</t>
-  </si>
-  <si>
-    <t>133908282</t>
-  </si>
-  <si>
-    <t>133908966</t>
-  </si>
-  <si>
-    <t>133908976</t>
-  </si>
-  <si>
-    <t>133909010</t>
-  </si>
-  <si>
-    <t>133909100</t>
-  </si>
-  <si>
-    <t>133909112</t>
-  </si>
-  <si>
-    <t>133909508</t>
-  </si>
-  <si>
-    <t>133909633</t>
-  </si>
-  <si>
-    <t>133909703</t>
-  </si>
-  <si>
-    <t>133909802</t>
-  </si>
-  <si>
-    <t>133909892</t>
-  </si>
-  <si>
-    <t>133909902</t>
-  </si>
-  <si>
-    <t>133909908</t>
-  </si>
-  <si>
-    <t>133910106</t>
-  </si>
-  <si>
-    <t>133910133</t>
-  </si>
-  <si>
-    <t>133910289</t>
-  </si>
-  <si>
-    <t>133910395</t>
-  </si>
-  <si>
-    <t>133910688</t>
-  </si>
-  <si>
-    <t>133910834</t>
-  </si>
-  <si>
-    <t>133910841</t>
-  </si>
-  <si>
-    <t>133910892</t>
-  </si>
-  <si>
-    <t>133911213</t>
-  </si>
-  <si>
-    <t>133911420</t>
-  </si>
-  <si>
-    <t>133911444</t>
-  </si>
-  <si>
-    <t>133911459</t>
-  </si>
-  <si>
-    <t>133911633</t>
-  </si>
-  <si>
-    <t>133911733</t>
-  </si>
-  <si>
-    <t>133912040</t>
-  </si>
-  <si>
-    <t>133912129</t>
-  </si>
-  <si>
-    <t>133912158</t>
-  </si>
-  <si>
-    <t>133912174</t>
-  </si>
-  <si>
-    <t>133912253</t>
-  </si>
-  <si>
-    <t>133912340</t>
-  </si>
-  <si>
-    <t>133912381</t>
-  </si>
-  <si>
-    <t>133912396</t>
-  </si>
-  <si>
-    <t>133912574</t>
-  </si>
-  <si>
-    <t>133912629</t>
-  </si>
-  <si>
-    <t>133912813</t>
-  </si>
-  <si>
-    <t>133912841</t>
-  </si>
-  <si>
-    <t>133912977</t>
-  </si>
-  <si>
-    <t>133913114</t>
-  </si>
-  <si>
-    <t>133913389</t>
-  </si>
-  <si>
-    <t>133913877</t>
-  </si>
-  <si>
-    <t>133913992</t>
-  </si>
-  <si>
-    <t>133914119</t>
-  </si>
-  <si>
-    <t>133914234</t>
-  </si>
-  <si>
-    <t>133914307</t>
-  </si>
-  <si>
-    <t>133914311</t>
-  </si>
-  <si>
-    <t>133914336</t>
-  </si>
-  <si>
-    <t>133914399</t>
-  </si>
-  <si>
-    <t>133914655</t>
-  </si>
-  <si>
-    <t>133914763</t>
-  </si>
-  <si>
-    <t>133914786</t>
-  </si>
-  <si>
-    <t>133915346</t>
-  </si>
-  <si>
-    <t>133915714</t>
-  </si>
-  <si>
-    <t>133915726</t>
-  </si>
-  <si>
-    <t>133915933</t>
-  </si>
-  <si>
-    <t>133916173</t>
-  </si>
-  <si>
-    <t>133916220</t>
-  </si>
-  <si>
-    <t>133916374</t>
-  </si>
-  <si>
-    <t>133916387</t>
-  </si>
-  <si>
-    <t>133916407</t>
-  </si>
-  <si>
-    <t>133916595</t>
-  </si>
-  <si>
-    <t>133916625</t>
-  </si>
-  <si>
-    <t>133916748</t>
-  </si>
-  <si>
-    <t>133916805</t>
-  </si>
-  <si>
-    <t>133917001</t>
-  </si>
-  <si>
-    <t>133917048</t>
-  </si>
-  <si>
-    <t>133917155</t>
-  </si>
-  <si>
-    <t>133917304</t>
-  </si>
-  <si>
-    <t>133917592</t>
-  </si>
-  <si>
-    <t>133917854</t>
-  </si>
-  <si>
-    <t>133917862</t>
-  </si>
-  <si>
-    <t>133917949</t>
-  </si>
-  <si>
-    <t>133918029</t>
-  </si>
-  <si>
-    <t>133918110</t>
-  </si>
-  <si>
-    <t>133918205</t>
-  </si>
-  <si>
-    <t>133918277</t>
-  </si>
-  <si>
-    <t>133918359</t>
-  </si>
-  <si>
-    <t>133918760</t>
-  </si>
-  <si>
-    <t>133918841</t>
-  </si>
-  <si>
-    <t>133918968</t>
-  </si>
-  <si>
-    <t>133919056</t>
-  </si>
-  <si>
-    <t>133919095</t>
-  </si>
-  <si>
-    <t>133919114</t>
-  </si>
-  <si>
-    <t>133919203</t>
-  </si>
-  <si>
-    <t>133919246</t>
-  </si>
-  <si>
-    <t>133919270</t>
-  </si>
-  <si>
-    <t>133919310</t>
-  </si>
-  <si>
-    <t>133919347</t>
-  </si>
-  <si>
-    <t>133919361</t>
-  </si>
-  <si>
-    <t>133919448</t>
-  </si>
-  <si>
-    <t>133919464</t>
-  </si>
-  <si>
-    <t>133919515</t>
-  </si>
-  <si>
-    <t>133919780</t>
-  </si>
-  <si>
-    <t>133919878</t>
-  </si>
-  <si>
-    <t>133919955</t>
-  </si>
-  <si>
-    <t>133920065</t>
-  </si>
-  <si>
-    <t>133920143</t>
-  </si>
-  <si>
-    <t>133920214</t>
-  </si>
-  <si>
-    <t>133920239</t>
-  </si>
-  <si>
-    <t>133920287</t>
-  </si>
-  <si>
-    <t>133920638</t>
-  </si>
-  <si>
-    <t>133920646</t>
-  </si>
-  <si>
-    <t>133920780</t>
-  </si>
-  <si>
-    <t>133920974</t>
-  </si>
-  <si>
-    <t>133921236</t>
-  </si>
-  <si>
-    <t>133921268</t>
-  </si>
-  <si>
-    <t>133921342</t>
-  </si>
-  <si>
-    <t>133921374</t>
-  </si>
-  <si>
-    <t>133921401</t>
-  </si>
-  <si>
-    <t>133921555</t>
-  </si>
-  <si>
-    <t>133921622</t>
-  </si>
-  <si>
-    <t>133921759</t>
-  </si>
-  <si>
-    <t>133921817</t>
-  </si>
-  <si>
-    <t>133921903</t>
-  </si>
-  <si>
-    <t>133921939</t>
-  </si>
-  <si>
-    <t>133922111</t>
-  </si>
-  <si>
-    <t>133922157</t>
-  </si>
-  <si>
-    <t>133922170</t>
-  </si>
-  <si>
-    <t>133922264</t>
-  </si>
-  <si>
-    <t>133922340</t>
-  </si>
-  <si>
-    <t>133922417</t>
-  </si>
-  <si>
-    <t>133922444</t>
-  </si>
-  <si>
-    <t>133922445</t>
-  </si>
-  <si>
-    <t>133922451</t>
-  </si>
-  <si>
-    <t>133922484</t>
-  </si>
-  <si>
-    <t>133922532</t>
-  </si>
-  <si>
-    <t>133922652</t>
-  </si>
-  <si>
-    <t>133922661</t>
-  </si>
-  <si>
-    <t>133922730</t>
-  </si>
-  <si>
-    <t>133922818</t>
-  </si>
-  <si>
-    <t>133922844</t>
-  </si>
-  <si>
-    <t>133922846</t>
-  </si>
-  <si>
-    <t>133922918</t>
-  </si>
-  <si>
-    <t>133922969</t>
-  </si>
-  <si>
-    <t>133923031</t>
-  </si>
-  <si>
-    <t>133923034</t>
-  </si>
-  <si>
-    <t>133923062</t>
-  </si>
-  <si>
-    <t>133923112</t>
-  </si>
-  <si>
-    <t>133923161</t>
-  </si>
-  <si>
-    <t>133923251</t>
-  </si>
-  <si>
-    <t>133923266</t>
-  </si>
-  <si>
-    <t>133923386</t>
-  </si>
-  <si>
-    <t>133923601</t>
-  </si>
-  <si>
-    <t>133923679</t>
-  </si>
-  <si>
-    <t>133923708</t>
-  </si>
-  <si>
-    <t>133923725</t>
-  </si>
-  <si>
-    <t>133923795</t>
-  </si>
-  <si>
-    <t>133923846</t>
-  </si>
-  <si>
-    <t>133923925</t>
-  </si>
-  <si>
-    <t>133924153</t>
-  </si>
-  <si>
-    <t>133924362</t>
-  </si>
-  <si>
-    <t>133924364</t>
-  </si>
-  <si>
-    <t>133924388</t>
-  </si>
-  <si>
-    <t>133924469</t>
-  </si>
-  <si>
-    <t>133925032</t>
-  </si>
-  <si>
-    <t>133925360</t>
-  </si>
-  <si>
-    <t>133925361</t>
-  </si>
-  <si>
-    <t>133925520</t>
+    <t>129650217</t>
+  </si>
+  <si>
+    <t>129890146</t>
+  </si>
+  <si>
+    <t>130011181</t>
+  </si>
+  <si>
+    <t>130032913</t>
+  </si>
+  <si>
+    <t>130138854</t>
+  </si>
+  <si>
+    <t>130142458</t>
+  </si>
+  <si>
+    <t>130160209</t>
+  </si>
+  <si>
+    <t>130325864</t>
+  </si>
+  <si>
+    <t>130564867</t>
+  </si>
+  <si>
+    <t>130725639</t>
+  </si>
+  <si>
+    <t>130846095</t>
+  </si>
+  <si>
+    <t>130949349</t>
+  </si>
+  <si>
+    <t>130957266</t>
+  </si>
+  <si>
+    <t>131392569</t>
+  </si>
+  <si>
+    <t>131557327</t>
+  </si>
+  <si>
+    <t>132064131</t>
+  </si>
+  <si>
+    <t>132161695</t>
+  </si>
+  <si>
+    <t>132190020</t>
+  </si>
+  <si>
+    <t>132211597</t>
+  </si>
+  <si>
+    <t>132310468</t>
+  </si>
+  <si>
+    <t>132607866</t>
+  </si>
+  <si>
+    <t>132657985</t>
+  </si>
+  <si>
+    <t>133138526</t>
+  </si>
+  <si>
+    <t>133469726</t>
+  </si>
+  <si>
+    <t>133531756</t>
+  </si>
+  <si>
+    <t>133648523</t>
+  </si>
+  <si>
+    <t>133739414</t>
+  </si>
+  <si>
+    <t>133742966</t>
+  </si>
+  <si>
+    <t>133925626</t>
+  </si>
+  <si>
+    <t>133925628</t>
+  </si>
+  <si>
+    <t>133925715</t>
+  </si>
+  <si>
+    <t>133925809</t>
+  </si>
+  <si>
+    <t>133925817</t>
+  </si>
+  <si>
+    <t>133925826</t>
+  </si>
+  <si>
+    <t>133926044</t>
+  </si>
+  <si>
+    <t>133926111</t>
+  </si>
+  <si>
+    <t>133926154</t>
+  </si>
+  <si>
+    <t>133926255</t>
+  </si>
+  <si>
+    <t>133926296</t>
+  </si>
+  <si>
+    <t>133926341</t>
+  </si>
+  <si>
+    <t>133926458</t>
+  </si>
+  <si>
+    <t>133926851</t>
+  </si>
+  <si>
+    <t>133926939</t>
+  </si>
+  <si>
+    <t>133926979</t>
+  </si>
+  <si>
+    <t>133927032</t>
+  </si>
+  <si>
+    <t>133927112</t>
+  </si>
+  <si>
+    <t>133927122</t>
+  </si>
+  <si>
+    <t>133927467</t>
+  </si>
+  <si>
+    <t>133927468</t>
+  </si>
+  <si>
+    <t>133927546</t>
+  </si>
+  <si>
+    <t>133928061</t>
+  </si>
+  <si>
+    <t>133928223</t>
+  </si>
+  <si>
+    <t>133928279</t>
+  </si>
+  <si>
+    <t>133928831</t>
+  </si>
+  <si>
+    <t>133928915</t>
+  </si>
+  <si>
+    <t>133928933</t>
+  </si>
+  <si>
+    <t>133928965</t>
+  </si>
+  <si>
+    <t>133929110</t>
+  </si>
+  <si>
+    <t>133929112</t>
+  </si>
+  <si>
+    <t>133929250</t>
+  </si>
+  <si>
+    <t>133929520</t>
+  </si>
+  <si>
+    <t>133929534</t>
+  </si>
+  <si>
+    <t>133929806</t>
+  </si>
+  <si>
+    <t>133929935</t>
+  </si>
+  <si>
+    <t>133930034</t>
+  </si>
+  <si>
+    <t>133930097</t>
+  </si>
+  <si>
+    <t>133930249</t>
+  </si>
+  <si>
+    <t>133930428</t>
+  </si>
+  <si>
+    <t>133930555</t>
+  </si>
+  <si>
+    <t>133930672</t>
+  </si>
+  <si>
+    <t>133930898</t>
+  </si>
+  <si>
+    <t>133930922</t>
+  </si>
+  <si>
+    <t>133930943</t>
+  </si>
+  <si>
+    <t>133931160</t>
+  </si>
+  <si>
+    <t>133931249</t>
+  </si>
+  <si>
+    <t>133931884</t>
+  </si>
+  <si>
+    <t>133931980</t>
+  </si>
+  <si>
+    <t>133932044</t>
+  </si>
+  <si>
+    <t>133932142</t>
+  </si>
+  <si>
+    <t>133932155</t>
+  </si>
+  <si>
+    <t>133932469</t>
+  </si>
+  <si>
+    <t>133932587</t>
+  </si>
+  <si>
+    <t>133932814</t>
+  </si>
+  <si>
+    <t>133932915</t>
+  </si>
+  <si>
+    <t>133932916</t>
+  </si>
+  <si>
+    <t>133932968</t>
+  </si>
+  <si>
+    <t>133933114</t>
+  </si>
+  <si>
+    <t>133933157</t>
+  </si>
+  <si>
+    <t>133933262</t>
+  </si>
+  <si>
+    <t>133933400</t>
+  </si>
+  <si>
+    <t>133933460</t>
+  </si>
+  <si>
+    <t>133933473</t>
+  </si>
+  <si>
+    <t>133933654</t>
+  </si>
+  <si>
+    <t>133933677</t>
+  </si>
+  <si>
+    <t>133933745</t>
+  </si>
+  <si>
+    <t>133933751</t>
+  </si>
+  <si>
+    <t>133933754</t>
+  </si>
+  <si>
+    <t>133933965</t>
+  </si>
+  <si>
+    <t>133933990</t>
+  </si>
+  <si>
+    <t>133934159</t>
+  </si>
+  <si>
+    <t>133934373</t>
+  </si>
+  <si>
+    <t>133934573</t>
+  </si>
+  <si>
+    <t>133934872</t>
+  </si>
+  <si>
+    <t>133934876</t>
+  </si>
+  <si>
+    <t>133935055</t>
+  </si>
+  <si>
+    <t>133935148</t>
+  </si>
+  <si>
+    <t>133935564</t>
+  </si>
+  <si>
+    <t>133935599</t>
+  </si>
+  <si>
+    <t>133935834</t>
+  </si>
+  <si>
+    <t>133935889</t>
+  </si>
+  <si>
+    <t>133936159</t>
+  </si>
+  <si>
+    <t>133936276</t>
+  </si>
+  <si>
+    <t>133936352</t>
+  </si>
+  <si>
+    <t>133936438</t>
+  </si>
+  <si>
+    <t>133936507</t>
+  </si>
+  <si>
+    <t>133936852</t>
+  </si>
+  <si>
+    <t>133937373</t>
+  </si>
+  <si>
+    <t>133937435</t>
+  </si>
+  <si>
+    <t>133937572</t>
+  </si>
+  <si>
+    <t>133937751</t>
+  </si>
+  <si>
+    <t>133937843</t>
+  </si>
+  <si>
+    <t>133937902</t>
+  </si>
+  <si>
+    <t>133937909</t>
+  </si>
+  <si>
+    <t>133937928</t>
+  </si>
+  <si>
+    <t>133938063</t>
+  </si>
+  <si>
+    <t>133938331</t>
+  </si>
+  <si>
+    <t>133938526</t>
+  </si>
+  <si>
+    <t>133938998</t>
+  </si>
+  <si>
+    <t>133939111</t>
+  </si>
+  <si>
+    <t>133939136</t>
+  </si>
+  <si>
+    <t>133939346</t>
+  </si>
+  <si>
+    <t>133939373</t>
+  </si>
+  <si>
+    <t>133939448</t>
+  </si>
+  <si>
+    <t>133939690</t>
+  </si>
+  <si>
+    <t>133939899</t>
+  </si>
+  <si>
+    <t>133939940</t>
+  </si>
+  <si>
+    <t>133939986</t>
+  </si>
+  <si>
+    <t>133940047</t>
+  </si>
+  <si>
+    <t>133940105</t>
+  </si>
+  <si>
+    <t>133940123</t>
+  </si>
+  <si>
+    <t>133940245</t>
+  </si>
+  <si>
+    <t>133940341</t>
+  </si>
+  <si>
+    <t>133940398</t>
+  </si>
+  <si>
+    <t>133940409</t>
+  </si>
+  <si>
+    <t>133940533</t>
+  </si>
+  <si>
+    <t>133940538</t>
+  </si>
+  <si>
+    <t>133940561</t>
+  </si>
+  <si>
+    <t>133940651</t>
+  </si>
+  <si>
+    <t>133940676</t>
+  </si>
+  <si>
+    <t>133940698</t>
+  </si>
+  <si>
+    <t>133940713</t>
+  </si>
+  <si>
+    <t>133940900</t>
+  </si>
+  <si>
+    <t>133940934</t>
+  </si>
+  <si>
+    <t>133941149</t>
+  </si>
+  <si>
+    <t>133941190</t>
+  </si>
+  <si>
+    <t>133941240</t>
+  </si>
+  <si>
+    <t>133941590</t>
+  </si>
+  <si>
+    <t>133941604</t>
+  </si>
+  <si>
+    <t>133941656</t>
+  </si>
+  <si>
+    <t>133941672</t>
+  </si>
+  <si>
+    <t>133941751</t>
+  </si>
+  <si>
+    <t>133941846</t>
+  </si>
+  <si>
+    <t>133942041</t>
+  </si>
+  <si>
+    <t>133942163</t>
+  </si>
+  <si>
+    <t>133942254</t>
+  </si>
+  <si>
+    <t>133943002</t>
+  </si>
+  <si>
+    <t>133943087</t>
+  </si>
+  <si>
+    <t>133943105</t>
+  </si>
+  <si>
+    <t>133943156</t>
+  </si>
+  <si>
+    <t>133943216</t>
+  </si>
+  <si>
+    <t>133943610</t>
+  </si>
+  <si>
+    <t>133943613</t>
+  </si>
+  <si>
+    <t>133943699</t>
+  </si>
+  <si>
+    <t>133943715</t>
+  </si>
+  <si>
+    <t>133943824</t>
+  </si>
+  <si>
+    <t>133943853</t>
+  </si>
+  <si>
+    <t>133944014</t>
+  </si>
+  <si>
+    <t>133944050</t>
+  </si>
+  <si>
+    <t>133944170</t>
+  </si>
+  <si>
+    <t>133944218</t>
+  </si>
+  <si>
+    <t>133944288</t>
+  </si>
+  <si>
+    <t>133944333</t>
+  </si>
+  <si>
+    <t>133944384</t>
+  </si>
+  <si>
+    <t>133944416</t>
+  </si>
+  <si>
+    <t>133944531</t>
+  </si>
+  <si>
+    <t>133944537</t>
+  </si>
+  <si>
+    <t>133944600</t>
+  </si>
+  <si>
+    <t>133944603</t>
+  </si>
+  <si>
+    <t>133944621</t>
+  </si>
+  <si>
+    <t>133944655</t>
+  </si>
+  <si>
+    <t>133944699</t>
+  </si>
+  <si>
+    <t>133944719</t>
+  </si>
+  <si>
+    <t>133944732</t>
+  </si>
+  <si>
+    <t>133944834</t>
+  </si>
+  <si>
+    <t>133944838</t>
+  </si>
+  <si>
+    <t>133944846</t>
+  </si>
+  <si>
+    <t>133944881</t>
+  </si>
+  <si>
+    <t>133944905</t>
+  </si>
+  <si>
+    <t>133944909</t>
+  </si>
+  <si>
+    <t>133945024</t>
+  </si>
+  <si>
+    <t>133945181</t>
+  </si>
+  <si>
+    <t>133945215</t>
+  </si>
+  <si>
+    <t>133945253</t>
+  </si>
+  <si>
+    <t>133945254</t>
+  </si>
+  <si>
+    <t>133945326</t>
+  </si>
+  <si>
+    <t>133945388</t>
+  </si>
+  <si>
+    <t>133945392</t>
+  </si>
+  <si>
+    <t>133945423</t>
+  </si>
+  <si>
+    <t>133945447</t>
+  </si>
+  <si>
+    <t>133945486</t>
+  </si>
+  <si>
+    <t>133945490</t>
+  </si>
+  <si>
+    <t>133945536</t>
+  </si>
+  <si>
+    <t>133945542</t>
+  </si>
+  <si>
+    <t>133945591</t>
+  </si>
+  <si>
+    <t>133945619</t>
+  </si>
+  <si>
+    <t>133945663</t>
+  </si>
+  <si>
+    <t>133945756</t>
+  </si>
+  <si>
+    <t>133945826</t>
+  </si>
+  <si>
+    <t>133945872</t>
+  </si>
+  <si>
+    <t>133945875</t>
+  </si>
+  <si>
+    <t>133945919</t>
+  </si>
+  <si>
+    <t>133945943</t>
+  </si>
+  <si>
+    <t>133946024</t>
+  </si>
+  <si>
+    <t>133946052</t>
+  </si>
+  <si>
+    <t>133946111</t>
+  </si>
+  <si>
+    <t>133946178</t>
+  </si>
+  <si>
+    <t>133946251</t>
+  </si>
+  <si>
+    <t>133946306</t>
+  </si>
+  <si>
+    <t>133946373</t>
+  </si>
+  <si>
+    <t>133946375</t>
+  </si>
+  <si>
+    <t>133946502</t>
+  </si>
+  <si>
+    <t>133946515</t>
+  </si>
+  <si>
+    <t>133946546</t>
+  </si>
+  <si>
+    <t>133946662</t>
+  </si>
+  <si>
+    <t>133946829</t>
+  </si>
+  <si>
+    <t>133946880</t>
+  </si>
+  <si>
+    <t>133946924</t>
+  </si>
+  <si>
+    <t>133947045</t>
+  </si>
+  <si>
+    <t>133947073</t>
+  </si>
+  <si>
+    <t>133947348</t>
+  </si>
+  <si>
+    <t>133947376</t>
+  </si>
+  <si>
+    <t>133947475</t>
+  </si>
+  <si>
+    <t>133947555</t>
+  </si>
+  <si>
+    <t>133947606</t>
+  </si>
+  <si>
+    <t>133947713</t>
+  </si>
+  <si>
+    <t>133947737</t>
+  </si>
+  <si>
+    <t>133947792</t>
+  </si>
+  <si>
+    <t>133948202</t>
+  </si>
+  <si>
+    <t>133948433</t>
+  </si>
+  <si>
+    <t>133948640</t>
+  </si>
+  <si>
+    <t>133948717</t>
   </si>
 </sst>
 </file>
@@ -3660,162 +3729,277 @@
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B230" s="6"/>
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C230" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B231" s="6"/>
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C231" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B232" s="6"/>
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C232" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B233" s="6"/>
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C233" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B234" s="6"/>
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C234" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B235" s="6"/>
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C235" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B236" s="6"/>
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C236" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B237" s="6"/>
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C237" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B238" s="6"/>
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C238" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B239" s="6"/>
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C239" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B240" s="6"/>
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C240" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B241" s="6"/>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C241" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B242" s="6"/>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C242" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B243" s="6"/>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C243" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B244" s="6"/>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C244" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B245" s="6"/>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C245" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B246" s="6"/>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C246" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B247" s="6"/>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C247" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B248" s="6"/>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C248" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B249" s="6"/>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C249" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B250" s="6"/>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C250" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B251" s="6"/>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C251" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B252" s="6"/>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C252" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B253" s="6"/>
       <c r="C253" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B254" s="6"/>
       <c r="C254" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B255" s="6"/>
       <c r="C255" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B256" s="6"/>
       <c r="C256" s="5" t="s">
         <v>4</v>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB45296-FB2A-4833-9686-D79F625BB9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE89F36-91AC-4516-A4F5-A2B309AFDA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="224">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,781 +45,661 @@
     <t>.</t>
   </si>
   <si>
-    <t>129350848</t>
-  </si>
-  <si>
-    <t>129380249</t>
-  </si>
-  <si>
-    <t>129511219</t>
-  </si>
-  <si>
-    <t>129642070</t>
-  </si>
-  <si>
-    <t>129712889</t>
-  </si>
-  <si>
-    <t>130065654</t>
-  </si>
-  <si>
-    <t>130220372</t>
-  </si>
-  <si>
-    <t>130275574</t>
-  </si>
-  <si>
-    <t>130344727</t>
-  </si>
-  <si>
-    <t>130576763</t>
-  </si>
-  <si>
-    <t>130664580</t>
-  </si>
-  <si>
-    <t>130910976</t>
-  </si>
-  <si>
-    <t>131051529</t>
-  </si>
-  <si>
-    <t>131167884</t>
-  </si>
-  <si>
-    <t>131231594</t>
-  </si>
-  <si>
-    <t>131300340</t>
-  </si>
-  <si>
-    <t>131547360</t>
-  </si>
-  <si>
-    <t>131584840</t>
-  </si>
-  <si>
-    <t>131888920</t>
-  </si>
-  <si>
-    <t>132121170</t>
-  </si>
-  <si>
-    <t>132511672</t>
-  </si>
-  <si>
-    <t>132565265</t>
-  </si>
-  <si>
-    <t>132686493</t>
-  </si>
-  <si>
-    <t>132824045</t>
-  </si>
-  <si>
-    <t>133019624</t>
-  </si>
-  <si>
-    <t>133041042</t>
-  </si>
-  <si>
-    <t>133143509</t>
-  </si>
-  <si>
-    <t>133192684</t>
-  </si>
-  <si>
-    <t>133331726</t>
-  </si>
-  <si>
-    <t>133394297</t>
-  </si>
-  <si>
-    <t>133408803</t>
-  </si>
-  <si>
-    <t>133566895</t>
-  </si>
-  <si>
-    <t>133740542</t>
-  </si>
-  <si>
-    <t>133831222</t>
-  </si>
-  <si>
-    <t>133948789</t>
-  </si>
-  <si>
-    <t>133948915</t>
-  </si>
-  <si>
-    <t>133948963</t>
-  </si>
-  <si>
-    <t>133949189</t>
-  </si>
-  <si>
-    <t>133949394</t>
-  </si>
-  <si>
-    <t>133949633</t>
-  </si>
-  <si>
-    <t>133949785</t>
-  </si>
-  <si>
-    <t>133949831</t>
-  </si>
-  <si>
-    <t>133949836</t>
-  </si>
-  <si>
-    <t>133949839</t>
-  </si>
-  <si>
-    <t>133950038</t>
-  </si>
-  <si>
-    <t>133950342</t>
-  </si>
-  <si>
-    <t>133950619</t>
-  </si>
-  <si>
-    <t>133950847</t>
-  </si>
-  <si>
-    <t>133951231</t>
-  </si>
-  <si>
-    <t>133951237</t>
-  </si>
-  <si>
-    <t>133951384</t>
-  </si>
-  <si>
-    <t>133951398</t>
-  </si>
-  <si>
-    <t>133951481</t>
-  </si>
-  <si>
-    <t>133951577</t>
-  </si>
-  <si>
-    <t>133951650</t>
-  </si>
-  <si>
-    <t>133951772</t>
-  </si>
-  <si>
-    <t>133951953</t>
-  </si>
-  <si>
-    <t>133952043</t>
-  </si>
-  <si>
-    <t>133952098</t>
-  </si>
-  <si>
-    <t>133952106</t>
-  </si>
-  <si>
-    <t>133952192</t>
-  </si>
-  <si>
-    <t>133952413</t>
-  </si>
-  <si>
-    <t>133952649</t>
-  </si>
-  <si>
-    <t>133952749</t>
-  </si>
-  <si>
-    <t>133952751</t>
-  </si>
-  <si>
-    <t>133953149</t>
-  </si>
-  <si>
-    <t>133953204</t>
-  </si>
-  <si>
-    <t>133953243</t>
-  </si>
-  <si>
-    <t>133953586</t>
-  </si>
-  <si>
-    <t>133953600</t>
-  </si>
-  <si>
-    <t>133953755</t>
-  </si>
-  <si>
-    <t>133953765</t>
-  </si>
-  <si>
-    <t>133954071</t>
-  </si>
-  <si>
-    <t>133954148</t>
-  </si>
-  <si>
-    <t>133954202</t>
-  </si>
-  <si>
-    <t>133954307</t>
-  </si>
-  <si>
-    <t>133954318</t>
-  </si>
-  <si>
-    <t>133954346</t>
-  </si>
-  <si>
-    <t>133954516</t>
-  </si>
-  <si>
-    <t>133954629</t>
-  </si>
-  <si>
-    <t>133954650</t>
-  </si>
-  <si>
-    <t>133954717</t>
-  </si>
-  <si>
-    <t>133954745</t>
-  </si>
-  <si>
-    <t>133954766</t>
-  </si>
-  <si>
-    <t>133954888</t>
-  </si>
-  <si>
-    <t>133954976</t>
-  </si>
-  <si>
-    <t>133955031</t>
-  </si>
-  <si>
-    <t>133955239</t>
-  </si>
-  <si>
-    <t>133955421</t>
-  </si>
-  <si>
-    <t>133955570</t>
-  </si>
-  <si>
-    <t>133956230</t>
-  </si>
-  <si>
-    <t>133956260</t>
-  </si>
-  <si>
-    <t>133956387</t>
-  </si>
-  <si>
-    <t>133956737</t>
-  </si>
-  <si>
-    <t>133957004</t>
-  </si>
-  <si>
-    <t>133957093</t>
-  </si>
-  <si>
-    <t>133957095</t>
-  </si>
-  <si>
-    <t>133957382</t>
-  </si>
-  <si>
-    <t>133957479</t>
-  </si>
-  <si>
-    <t>133957496</t>
-  </si>
-  <si>
-    <t>133957735</t>
-  </si>
-  <si>
-    <t>133957797</t>
-  </si>
-  <si>
-    <t>133957846</t>
-  </si>
-  <si>
-    <t>133957994</t>
-  </si>
-  <si>
-    <t>133958141</t>
-  </si>
-  <si>
-    <t>133958216</t>
-  </si>
-  <si>
-    <t>133958544</t>
-  </si>
-  <si>
-    <t>133959070</t>
-  </si>
-  <si>
-    <t>133959115</t>
-  </si>
-  <si>
-    <t>133959233</t>
-  </si>
-  <si>
-    <t>133959303</t>
-  </si>
-  <si>
-    <t>133959343</t>
-  </si>
-  <si>
-    <t>133959436</t>
-  </si>
-  <si>
-    <t>133959683</t>
-  </si>
-  <si>
-    <t>133959849</t>
-  </si>
-  <si>
-    <t>133959993</t>
-  </si>
-  <si>
-    <t>133960055</t>
-  </si>
-  <si>
-    <t>133960077</t>
-  </si>
-  <si>
-    <t>133960171</t>
-  </si>
-  <si>
-    <t>133960299</t>
-  </si>
-  <si>
-    <t>133960323</t>
-  </si>
-  <si>
-    <t>133960372</t>
-  </si>
-  <si>
-    <t>133960399</t>
-  </si>
-  <si>
-    <t>133960435</t>
-  </si>
-  <si>
-    <t>133960700</t>
-  </si>
-  <si>
-    <t>133960845</t>
-  </si>
-  <si>
-    <t>133960867</t>
-  </si>
-  <si>
-    <t>133960883</t>
-  </si>
-  <si>
-    <t>133961012</t>
-  </si>
-  <si>
-    <t>133961038</t>
-  </si>
-  <si>
-    <t>133961122</t>
-  </si>
-  <si>
-    <t>133961145</t>
-  </si>
-  <si>
-    <t>133961496</t>
-  </si>
-  <si>
-    <t>133961642</t>
-  </si>
-  <si>
-    <t>133961724</t>
-  </si>
-  <si>
-    <t>133961746</t>
-  </si>
-  <si>
-    <t>133961898</t>
-  </si>
-  <si>
-    <t>133962059</t>
-  </si>
-  <si>
-    <t>133962240</t>
-  </si>
-  <si>
-    <t>133962260</t>
-  </si>
-  <si>
-    <t>133962472</t>
-  </si>
-  <si>
-    <t>133962687</t>
-  </si>
-  <si>
-    <t>133962750</t>
-  </si>
-  <si>
-    <t>133962800</t>
-  </si>
-  <si>
-    <t>133962869</t>
-  </si>
-  <si>
-    <t>133962906</t>
-  </si>
-  <si>
-    <t>133963079</t>
-  </si>
-  <si>
-    <t>133963188</t>
-  </si>
-  <si>
-    <t>133963432</t>
-  </si>
-  <si>
-    <t>133963436</t>
-  </si>
-  <si>
-    <t>133963461</t>
-  </si>
-  <si>
-    <t>133963495</t>
-  </si>
-  <si>
-    <t>133963510</t>
-  </si>
-  <si>
-    <t>133963543</t>
-  </si>
-  <si>
-    <t>133963569</t>
-  </si>
-  <si>
-    <t>133963790</t>
-  </si>
-  <si>
-    <t>133963814</t>
-  </si>
-  <si>
-    <t>133964073</t>
-  </si>
-  <si>
-    <t>133964091</t>
-  </si>
-  <si>
-    <t>133964148</t>
-  </si>
-  <si>
-    <t>133964156</t>
-  </si>
-  <si>
-    <t>133964207</t>
-  </si>
-  <si>
-    <t>133964240</t>
-  </si>
-  <si>
-    <t>133964246</t>
-  </si>
-  <si>
-    <t>133964294</t>
-  </si>
-  <si>
-    <t>133964487</t>
-  </si>
-  <si>
-    <t>133964568</t>
-  </si>
-  <si>
-    <t>133964590</t>
-  </si>
-  <si>
-    <t>133964668</t>
-  </si>
-  <si>
-    <t>133964670</t>
-  </si>
-  <si>
-    <t>133964747</t>
-  </si>
-  <si>
-    <t>133965118</t>
-  </si>
-  <si>
-    <t>133965159</t>
-  </si>
-  <si>
-    <t>133965177</t>
-  </si>
-  <si>
-    <t>133965262</t>
-  </si>
-  <si>
-    <t>133965276</t>
-  </si>
-  <si>
-    <t>133965440</t>
-  </si>
-  <si>
-    <t>133965454</t>
-  </si>
-  <si>
-    <t>133965530</t>
-  </si>
-  <si>
-    <t>133965660</t>
-  </si>
-  <si>
-    <t>133965689</t>
-  </si>
-  <si>
-    <t>133966017</t>
-  </si>
-  <si>
-    <t>133966162</t>
-  </si>
-  <si>
-    <t>133966257</t>
-  </si>
-  <si>
-    <t>133966261</t>
-  </si>
-  <si>
-    <t>133966350</t>
-  </si>
-  <si>
-    <t>133966357</t>
-  </si>
-  <si>
-    <t>133966406</t>
-  </si>
-  <si>
-    <t>133966426</t>
-  </si>
-  <si>
-    <t>133966430</t>
-  </si>
-  <si>
-    <t>133966492</t>
-  </si>
-  <si>
-    <t>133966515</t>
-  </si>
-  <si>
-    <t>133966545</t>
-  </si>
-  <si>
-    <t>133966554</t>
-  </si>
-  <si>
-    <t>133966664</t>
-  </si>
-  <si>
-    <t>133966747</t>
-  </si>
-  <si>
-    <t>133966875</t>
-  </si>
-  <si>
-    <t>133966957</t>
-  </si>
-  <si>
-    <t>133966979</t>
-  </si>
-  <si>
-    <t>133967085</t>
-  </si>
-  <si>
-    <t>133967104</t>
-  </si>
-  <si>
-    <t>133967305</t>
-  </si>
-  <si>
-    <t>133967342</t>
-  </si>
-  <si>
-    <t>133967360</t>
-  </si>
-  <si>
-    <t>133967394</t>
-  </si>
-  <si>
-    <t>133967408</t>
-  </si>
-  <si>
-    <t>133967435</t>
-  </si>
-  <si>
-    <t>133967485</t>
-  </si>
-  <si>
-    <t>133967502</t>
-  </si>
-  <si>
-    <t>133967598</t>
-  </si>
-  <si>
-    <t>133967762</t>
-  </si>
-  <si>
-    <t>133967777</t>
-  </si>
-  <si>
-    <t>133967874</t>
-  </si>
-  <si>
-    <t>133967897</t>
-  </si>
-  <si>
-    <t>133967948</t>
-  </si>
-  <si>
-    <t>133967967</t>
-  </si>
-  <si>
-    <t>133967991</t>
-  </si>
-  <si>
-    <t>133968006</t>
-  </si>
-  <si>
-    <t>133968009</t>
-  </si>
-  <si>
-    <t>133968246</t>
-  </si>
-  <si>
-    <t>133968261</t>
-  </si>
-  <si>
-    <t>133968283</t>
-  </si>
-  <si>
-    <t>133968318</t>
-  </si>
-  <si>
-    <t>133968321</t>
-  </si>
-  <si>
-    <t>133968763</t>
-  </si>
-  <si>
-    <t>133968964</t>
-  </si>
-  <si>
-    <t>133969323</t>
-  </si>
-  <si>
-    <t>133969355</t>
-  </si>
-  <si>
-    <t>133969801</t>
-  </si>
-  <si>
-    <t>133970171</t>
-  </si>
-  <si>
-    <t>133970200</t>
-  </si>
-  <si>
-    <t>133970204</t>
-  </si>
-  <si>
-    <t>133970256</t>
-  </si>
-  <si>
-    <t>133970266</t>
-  </si>
-  <si>
-    <t>133970276</t>
-  </si>
-  <si>
-    <t>133970385</t>
-  </si>
-  <si>
-    <t>133970471</t>
-  </si>
-  <si>
-    <t>133970670</t>
-  </si>
-  <si>
-    <t>133970703</t>
-  </si>
-  <si>
-    <t>133970744</t>
-  </si>
-  <si>
-    <t>133970801</t>
-  </si>
-  <si>
-    <t>133970805</t>
-  </si>
-  <si>
-    <t>133970821</t>
-  </si>
-  <si>
-    <t>133970851</t>
-  </si>
-  <si>
-    <t>133970953</t>
-  </si>
-  <si>
-    <t>133970990</t>
-  </si>
-  <si>
-    <t>133971050</t>
-  </si>
-  <si>
-    <t>133971191</t>
-  </si>
-  <si>
-    <t>133971202</t>
-  </si>
-  <si>
-    <t>133971452</t>
-  </si>
-  <si>
-    <t>133971558</t>
-  </si>
-  <si>
-    <t>133971704</t>
-  </si>
-  <si>
-    <t>133971816</t>
-  </si>
-  <si>
-    <t>133972088</t>
-  </si>
-  <si>
-    <t>133972406</t>
-  </si>
-  <si>
-    <t>133972721</t>
-  </si>
-  <si>
-    <t>133972858</t>
-  </si>
-  <si>
-    <t>133973005</t>
-  </si>
-  <si>
-    <t>133973124</t>
+    <t>129688972</t>
+  </si>
+  <si>
+    <t>129697414</t>
+  </si>
+  <si>
+    <t>129717161</t>
+  </si>
+  <si>
+    <t>129952716</t>
+  </si>
+  <si>
+    <t>130197674</t>
+  </si>
+  <si>
+    <t>130333056</t>
+  </si>
+  <si>
+    <t>130493804</t>
+  </si>
+  <si>
+    <t>130568607</t>
+  </si>
+  <si>
+    <t>130650561</t>
+  </si>
+  <si>
+    <t>130661380</t>
+  </si>
+  <si>
+    <t>130841644</t>
+  </si>
+  <si>
+    <t>130906366</t>
+  </si>
+  <si>
+    <t>131329973</t>
+  </si>
+  <si>
+    <t>131435324</t>
+  </si>
+  <si>
+    <t>131459283</t>
+  </si>
+  <si>
+    <t>131572651</t>
+  </si>
+  <si>
+    <t>131918223</t>
+  </si>
+  <si>
+    <t>131924732</t>
+  </si>
+  <si>
+    <t>132030599</t>
+  </si>
+  <si>
+    <t>132101005</t>
+  </si>
+  <si>
+    <t>132564389</t>
+  </si>
+  <si>
+    <t>132613299</t>
+  </si>
+  <si>
+    <t>132929514</t>
+  </si>
+  <si>
+    <t>133027143</t>
+  </si>
+  <si>
+    <t>133276708</t>
+  </si>
+  <si>
+    <t>133776353</t>
+  </si>
+  <si>
+    <t>133973408</t>
+  </si>
+  <si>
+    <t>133973615</t>
+  </si>
+  <si>
+    <t>133973663</t>
+  </si>
+  <si>
+    <t>133973729</t>
+  </si>
+  <si>
+    <t>133973836</t>
+  </si>
+  <si>
+    <t>133973927</t>
+  </si>
+  <si>
+    <t>133974117</t>
+  </si>
+  <si>
+    <t>133974231</t>
+  </si>
+  <si>
+    <t>133974238</t>
+  </si>
+  <si>
+    <t>133974603</t>
+  </si>
+  <si>
+    <t>133974738</t>
+  </si>
+  <si>
+    <t>133974758</t>
+  </si>
+  <si>
+    <t>133974816</t>
+  </si>
+  <si>
+    <t>133974835</t>
+  </si>
+  <si>
+    <t>133975403</t>
+  </si>
+  <si>
+    <t>133975435</t>
+  </si>
+  <si>
+    <t>133975456</t>
+  </si>
+  <si>
+    <t>133975478</t>
+  </si>
+  <si>
+    <t>133975598</t>
+  </si>
+  <si>
+    <t>133975625</t>
+  </si>
+  <si>
+    <t>133975853</t>
+  </si>
+  <si>
+    <t>133975998</t>
+  </si>
+  <si>
+    <t>133976181</t>
+  </si>
+  <si>
+    <t>133976286</t>
+  </si>
+  <si>
+    <t>133976340</t>
+  </si>
+  <si>
+    <t>133976697</t>
+  </si>
+  <si>
+    <t>133976744</t>
+  </si>
+  <si>
+    <t>133976771</t>
+  </si>
+  <si>
+    <t>133976857</t>
+  </si>
+  <si>
+    <t>133976873</t>
+  </si>
+  <si>
+    <t>133976902</t>
+  </si>
+  <si>
+    <t>133977085</t>
+  </si>
+  <si>
+    <t>133977314</t>
+  </si>
+  <si>
+    <t>133977403</t>
+  </si>
+  <si>
+    <t>133977430</t>
+  </si>
+  <si>
+    <t>133977781</t>
+  </si>
+  <si>
+    <t>133977789</t>
+  </si>
+  <si>
+    <t>133977809</t>
+  </si>
+  <si>
+    <t>133977888</t>
+  </si>
+  <si>
+    <t>133977931</t>
+  </si>
+  <si>
+    <t>133977966</t>
+  </si>
+  <si>
+    <t>133977981</t>
+  </si>
+  <si>
+    <t>133978116</t>
+  </si>
+  <si>
+    <t>133978126</t>
+  </si>
+  <si>
+    <t>133978142</t>
+  </si>
+  <si>
+    <t>133978332</t>
+  </si>
+  <si>
+    <t>133978377</t>
+  </si>
+  <si>
+    <t>133978502</t>
+  </si>
+  <si>
+    <t>133978547</t>
+  </si>
+  <si>
+    <t>133978563</t>
+  </si>
+  <si>
+    <t>133978689</t>
+  </si>
+  <si>
+    <t>133978727</t>
+  </si>
+  <si>
+    <t>133978767</t>
+  </si>
+  <si>
+    <t>133978866</t>
+  </si>
+  <si>
+    <t>133978998</t>
+  </si>
+  <si>
+    <t>133979179</t>
+  </si>
+  <si>
+    <t>133979423</t>
+  </si>
+  <si>
+    <t>133979441</t>
+  </si>
+  <si>
+    <t>133979919</t>
+  </si>
+  <si>
+    <t>133980027</t>
+  </si>
+  <si>
+    <t>133980052</t>
+  </si>
+  <si>
+    <t>133980100</t>
+  </si>
+  <si>
+    <t>133980124</t>
+  </si>
+  <si>
+    <t>133980247</t>
+  </si>
+  <si>
+    <t>133980285</t>
+  </si>
+  <si>
+    <t>133980373</t>
+  </si>
+  <si>
+    <t>133980382</t>
+  </si>
+  <si>
+    <t>133980996</t>
+  </si>
+  <si>
+    <t>133981234</t>
+  </si>
+  <si>
+    <t>133981246</t>
+  </si>
+  <si>
+    <t>133981251</t>
+  </si>
+  <si>
+    <t>133981283</t>
+  </si>
+  <si>
+    <t>133981445</t>
+  </si>
+  <si>
+    <t>133981548</t>
+  </si>
+  <si>
+    <t>133981561</t>
+  </si>
+  <si>
+    <t>133981928</t>
+  </si>
+  <si>
+    <t>133981938</t>
+  </si>
+  <si>
+    <t>133982224</t>
+  </si>
+  <si>
+    <t>133982257</t>
+  </si>
+  <si>
+    <t>133982277</t>
+  </si>
+  <si>
+    <t>133982313</t>
+  </si>
+  <si>
+    <t>133982650</t>
+  </si>
+  <si>
+    <t>133982713</t>
+  </si>
+  <si>
+    <t>133982789</t>
+  </si>
+  <si>
+    <t>133982879</t>
+  </si>
+  <si>
+    <t>133983151</t>
+  </si>
+  <si>
+    <t>133983185</t>
+  </si>
+  <si>
+    <t>133983243</t>
+  </si>
+  <si>
+    <t>133983311</t>
+  </si>
+  <si>
+    <t>133983467</t>
+  </si>
+  <si>
+    <t>133983548</t>
+  </si>
+  <si>
+    <t>133983635</t>
+  </si>
+  <si>
+    <t>133983640</t>
+  </si>
+  <si>
+    <t>133983868</t>
+  </si>
+  <si>
+    <t>133983955</t>
+  </si>
+  <si>
+    <t>133984081</t>
+  </si>
+  <si>
+    <t>133984199</t>
+  </si>
+  <si>
+    <t>133984234</t>
+  </si>
+  <si>
+    <t>133984459</t>
+  </si>
+  <si>
+    <t>133984490</t>
+  </si>
+  <si>
+    <t>133984707</t>
+  </si>
+  <si>
+    <t>133984811</t>
+  </si>
+  <si>
+    <t>133985210</t>
+  </si>
+  <si>
+    <t>133985312</t>
+  </si>
+  <si>
+    <t>133985361</t>
+  </si>
+  <si>
+    <t>133985535</t>
+  </si>
+  <si>
+    <t>133985537</t>
+  </si>
+  <si>
+    <t>133985679</t>
+  </si>
+  <si>
+    <t>133985758</t>
+  </si>
+  <si>
+    <t>133986217</t>
+  </si>
+  <si>
+    <t>133986218</t>
+  </si>
+  <si>
+    <t>133986219</t>
+  </si>
+  <si>
+    <t>133986313</t>
+  </si>
+  <si>
+    <t>133986332</t>
+  </si>
+  <si>
+    <t>133986483</t>
+  </si>
+  <si>
+    <t>133986604</t>
+  </si>
+  <si>
+    <t>133986608</t>
+  </si>
+  <si>
+    <t>133986612</t>
+  </si>
+  <si>
+    <t>133986769</t>
+  </si>
+  <si>
+    <t>133986983</t>
+  </si>
+  <si>
+    <t>133987339</t>
+  </si>
+  <si>
+    <t>133987397</t>
+  </si>
+  <si>
+    <t>133987531</t>
+  </si>
+  <si>
+    <t>133987812</t>
+  </si>
+  <si>
+    <t>133987885</t>
+  </si>
+  <si>
+    <t>133987942</t>
+  </si>
+  <si>
+    <t>133987970</t>
+  </si>
+  <si>
+    <t>133988112</t>
+  </si>
+  <si>
+    <t>133988160</t>
+  </si>
+  <si>
+    <t>133988210</t>
+  </si>
+  <si>
+    <t>133988414</t>
+  </si>
+  <si>
+    <t>133988501</t>
+  </si>
+  <si>
+    <t>133988895</t>
+  </si>
+  <si>
+    <t>133988930</t>
+  </si>
+  <si>
+    <t>133988960</t>
+  </si>
+  <si>
+    <t>133989083</t>
+  </si>
+  <si>
+    <t>133989145</t>
+  </si>
+  <si>
+    <t>133989275</t>
+  </si>
+  <si>
+    <t>133989292</t>
+  </si>
+  <si>
+    <t>133989461</t>
+  </si>
+  <si>
+    <t>133989543</t>
+  </si>
+  <si>
+    <t>133989544</t>
+  </si>
+  <si>
+    <t>133989569</t>
+  </si>
+  <si>
+    <t>133989643</t>
+  </si>
+  <si>
+    <t>133989657</t>
+  </si>
+  <si>
+    <t>133989678</t>
+  </si>
+  <si>
+    <t>133989768</t>
+  </si>
+  <si>
+    <t>133989793</t>
+  </si>
+  <si>
+    <t>133989900</t>
+  </si>
+  <si>
+    <t>133989975</t>
+  </si>
+  <si>
+    <t>133990068</t>
+  </si>
+  <si>
+    <t>133990148</t>
+  </si>
+  <si>
+    <t>133990160</t>
+  </si>
+  <si>
+    <t>133990227</t>
+  </si>
+  <si>
+    <t>133990278</t>
+  </si>
+  <si>
+    <t>133990323</t>
+  </si>
+  <si>
+    <t>133990351</t>
+  </si>
+  <si>
+    <t>133990460</t>
+  </si>
+  <si>
+    <t>133990467</t>
+  </si>
+  <si>
+    <t>133990500</t>
+  </si>
+  <si>
+    <t>133990516</t>
+  </si>
+  <si>
+    <t>133990560</t>
+  </si>
+  <si>
+    <t>133990572</t>
+  </si>
+  <si>
+    <t>133990665</t>
+  </si>
+  <si>
+    <t>133990695</t>
+  </si>
+  <si>
+    <t>133990741</t>
+  </si>
+  <si>
+    <t>133990747</t>
+  </si>
+  <si>
+    <t>133990875</t>
+  </si>
+  <si>
+    <t>133990907</t>
+  </si>
+  <si>
+    <t>133990923</t>
+  </si>
+  <si>
+    <t>133991154</t>
+  </si>
+  <si>
+    <t>133991184</t>
+  </si>
+  <si>
+    <t>133991201</t>
+  </si>
+  <si>
+    <t>133991251</t>
+  </si>
+  <si>
+    <t>133991261</t>
+  </si>
+  <si>
+    <t>133991274</t>
+  </si>
+  <si>
+    <t>133991290</t>
+  </si>
+  <si>
+    <t>133991388</t>
+  </si>
+  <si>
+    <t>133991408</t>
+  </si>
+  <si>
+    <t>133991427</t>
+  </si>
+  <si>
+    <t>133991518</t>
+  </si>
+  <si>
+    <t>133991527</t>
+  </si>
+  <si>
+    <t>133991721</t>
+  </si>
+  <si>
+    <t>133991881</t>
+  </si>
+  <si>
+    <t>133992128</t>
+  </si>
+  <si>
+    <t>133992577</t>
+  </si>
+  <si>
+    <t>133992684</t>
+  </si>
+  <si>
+    <t>133992702</t>
+  </si>
+  <si>
+    <t>133992770</t>
+  </si>
+  <si>
+    <t>133993351</t>
+  </si>
+  <si>
+    <t>133993709</t>
+  </si>
+  <si>
+    <t>133993813</t>
+  </si>
+  <si>
+    <t>133993936</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C260"/>
+  <dimension ref="A1:C220"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3653,446 +3533,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B223" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B237" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B239" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B242" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B243" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B245" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B246" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B247" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B248" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C250" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B251" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C256" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B257" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B258" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45139B92-2B50-44AD-B024-641B1D442A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A531139-879F-4465-8289-14281A517F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="331">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,673 +45,982 @@
     <t>.</t>
   </si>
   <si>
-    <t>129747433</t>
-  </si>
-  <si>
-    <t>129802129</t>
-  </si>
-  <si>
-    <t>130144379</t>
-  </si>
-  <si>
-    <t>130244300</t>
-  </si>
-  <si>
-    <t>130430780</t>
-  </si>
-  <si>
-    <t>130457650</t>
-  </si>
-  <si>
-    <t>130481342</t>
-  </si>
-  <si>
-    <t>130664193</t>
-  </si>
-  <si>
-    <t>130872171</t>
-  </si>
-  <si>
-    <t>130917854</t>
-  </si>
-  <si>
-    <t>131738740</t>
-  </si>
-  <si>
-    <t>131929643</t>
-  </si>
-  <si>
-    <t>132100309</t>
-  </si>
-  <si>
-    <t>132170609</t>
-  </si>
-  <si>
-    <t>132511672</t>
-  </si>
-  <si>
-    <t>132604695</t>
-  </si>
-  <si>
-    <t>133566895</t>
-  </si>
-  <si>
-    <t>133633616</t>
-  </si>
-  <si>
-    <t>133713911</t>
-  </si>
-  <si>
-    <t>133777761</t>
-  </si>
-  <si>
-    <t>134161553</t>
-  </si>
-  <si>
-    <t>134161572</t>
-  </si>
-  <si>
-    <t>134161577</t>
-  </si>
-  <si>
-    <t>134161925</t>
-  </si>
-  <si>
-    <t>134162012</t>
-  </si>
-  <si>
-    <t>134162070</t>
-  </si>
-  <si>
-    <t>134162312</t>
-  </si>
-  <si>
-    <t>134162340</t>
-  </si>
-  <si>
-    <t>134162361</t>
-  </si>
-  <si>
-    <t>134162609</t>
-  </si>
-  <si>
-    <t>134162657</t>
-  </si>
-  <si>
-    <t>134162690</t>
-  </si>
-  <si>
-    <t>134162801</t>
-  </si>
-  <si>
-    <t>134162927</t>
-  </si>
-  <si>
-    <t>134163042</t>
-  </si>
-  <si>
-    <t>134163128</t>
-  </si>
-  <si>
-    <t>134163284</t>
-  </si>
-  <si>
-    <t>134163433</t>
-  </si>
-  <si>
-    <t>134163639</t>
-  </si>
-  <si>
-    <t>134163876</t>
-  </si>
-  <si>
-    <t>134164222</t>
-  </si>
-  <si>
-    <t>134164276</t>
-  </si>
-  <si>
-    <t>134164498</t>
-  </si>
-  <si>
-    <t>134164610</t>
-  </si>
-  <si>
-    <t>134164623</t>
-  </si>
-  <si>
-    <t>134164677</t>
-  </si>
-  <si>
-    <t>134164763</t>
-  </si>
-  <si>
-    <t>134164883</t>
-  </si>
-  <si>
-    <t>134164930</t>
-  </si>
-  <si>
-    <t>134164975</t>
-  </si>
-  <si>
-    <t>134165025</t>
-  </si>
-  <si>
-    <t>134165044</t>
-  </si>
-  <si>
-    <t>134165135</t>
-  </si>
-  <si>
-    <t>134165175</t>
-  </si>
-  <si>
-    <t>134165324</t>
-  </si>
-  <si>
-    <t>134165432</t>
-  </si>
-  <si>
-    <t>134165571</t>
-  </si>
-  <si>
-    <t>134165630</t>
-  </si>
-  <si>
-    <t>134165897</t>
-  </si>
-  <si>
-    <t>134165926</t>
-  </si>
-  <si>
-    <t>134165952</t>
-  </si>
-  <si>
-    <t>134166038</t>
-  </si>
-  <si>
-    <t>134166102</t>
-  </si>
-  <si>
-    <t>134166156</t>
-  </si>
-  <si>
-    <t>134166268</t>
-  </si>
-  <si>
-    <t>134166290</t>
-  </si>
-  <si>
-    <t>134166496</t>
-  </si>
-  <si>
-    <t>134166565</t>
-  </si>
-  <si>
-    <t>134166594</t>
-  </si>
-  <si>
-    <t>134166656</t>
-  </si>
-  <si>
-    <t>134166723</t>
-  </si>
-  <si>
-    <t>134166875</t>
-  </si>
-  <si>
-    <t>134167078</t>
-  </si>
-  <si>
-    <t>134167202</t>
-  </si>
-  <si>
-    <t>134167289</t>
-  </si>
-  <si>
-    <t>134167349</t>
-  </si>
-  <si>
-    <t>134168082</t>
-  </si>
-  <si>
-    <t>134168126</t>
-  </si>
-  <si>
-    <t>134168478</t>
-  </si>
-  <si>
-    <t>134168562</t>
-  </si>
-  <si>
-    <t>134168692</t>
-  </si>
-  <si>
-    <t>134168701</t>
-  </si>
-  <si>
-    <t>134169182</t>
-  </si>
-  <si>
-    <t>134169561</t>
-  </si>
-  <si>
-    <t>134169769</t>
-  </si>
-  <si>
-    <t>134169791</t>
-  </si>
-  <si>
-    <t>134169815</t>
-  </si>
-  <si>
-    <t>134169949</t>
-  </si>
-  <si>
-    <t>134169958</t>
-  </si>
-  <si>
-    <t>134169989</t>
-  </si>
-  <si>
-    <t>134170052</t>
-  </si>
-  <si>
-    <t>134170148</t>
-  </si>
-  <si>
-    <t>134170221</t>
-  </si>
-  <si>
-    <t>134170237</t>
-  </si>
-  <si>
-    <t>134170595</t>
-  </si>
-  <si>
-    <t>134170741</t>
-  </si>
-  <si>
-    <t>134170747</t>
-  </si>
-  <si>
-    <t>134170780</t>
-  </si>
-  <si>
-    <t>134170865</t>
-  </si>
-  <si>
-    <t>134171037</t>
-  </si>
-  <si>
-    <t>134171657</t>
-  </si>
-  <si>
-    <t>134171883</t>
-  </si>
-  <si>
-    <t>134172333</t>
-  </si>
-  <si>
-    <t>134172715</t>
-  </si>
-  <si>
-    <t>134172777</t>
-  </si>
-  <si>
-    <t>134172868</t>
-  </si>
-  <si>
-    <t>134172892</t>
-  </si>
-  <si>
-    <t>134173005</t>
-  </si>
-  <si>
-    <t>134173201</t>
-  </si>
-  <si>
-    <t>134173263</t>
-  </si>
-  <si>
-    <t>134173645</t>
-  </si>
-  <si>
-    <t>134173649</t>
-  </si>
-  <si>
-    <t>134173797</t>
-  </si>
-  <si>
-    <t>134173872</t>
-  </si>
-  <si>
-    <t>134173909</t>
-  </si>
-  <si>
-    <t>134174015</t>
-  </si>
-  <si>
-    <t>134174029</t>
-  </si>
-  <si>
-    <t>134174576</t>
-  </si>
-  <si>
-    <t>134174611</t>
-  </si>
-  <si>
-    <t>134174996</t>
-  </si>
-  <si>
-    <t>134175142</t>
-  </si>
-  <si>
-    <t>134175153</t>
-  </si>
-  <si>
-    <t>134175752</t>
-  </si>
-  <si>
-    <t>134175821</t>
-  </si>
-  <si>
-    <t>134175865</t>
-  </si>
-  <si>
-    <t>134175866</t>
-  </si>
-  <si>
-    <t>134175881</t>
-  </si>
-  <si>
-    <t>134175897</t>
-  </si>
-  <si>
-    <t>134176042</t>
-  </si>
-  <si>
-    <t>134176076</t>
-  </si>
-  <si>
-    <t>134176146</t>
-  </si>
-  <si>
-    <t>134176406</t>
-  </si>
-  <si>
-    <t>134176425</t>
-  </si>
-  <si>
-    <t>134176442</t>
-  </si>
-  <si>
-    <t>134176505</t>
-  </si>
-  <si>
-    <t>134176594</t>
-  </si>
-  <si>
-    <t>134176646</t>
-  </si>
-  <si>
-    <t>134176871</t>
-  </si>
-  <si>
-    <t>134176980</t>
-  </si>
-  <si>
-    <t>134177178</t>
-  </si>
-  <si>
-    <t>134177281</t>
-  </si>
-  <si>
-    <t>134177289</t>
-  </si>
-  <si>
-    <t>134177568</t>
-  </si>
-  <si>
-    <t>134177699</t>
-  </si>
-  <si>
-    <t>134177849</t>
-  </si>
-  <si>
-    <t>134178123</t>
-  </si>
-  <si>
-    <t>134178173</t>
-  </si>
-  <si>
-    <t>134178214</t>
-  </si>
-  <si>
-    <t>134178343</t>
-  </si>
-  <si>
-    <t>134178347</t>
-  </si>
-  <si>
-    <t>134178451</t>
-  </si>
-  <si>
-    <t>134179042</t>
-  </si>
-  <si>
-    <t>134179135</t>
-  </si>
-  <si>
-    <t>134179176</t>
-  </si>
-  <si>
-    <t>134179272</t>
-  </si>
-  <si>
-    <t>134179346</t>
-  </si>
-  <si>
-    <t>134179417</t>
-  </si>
-  <si>
-    <t>134179524</t>
-  </si>
-  <si>
-    <t>134179544</t>
-  </si>
-  <si>
-    <t>134179551</t>
-  </si>
-  <si>
-    <t>134179577</t>
-  </si>
-  <si>
-    <t>134179594</t>
-  </si>
-  <si>
-    <t>134179634</t>
-  </si>
-  <si>
-    <t>134179644</t>
-  </si>
-  <si>
-    <t>134179690</t>
-  </si>
-  <si>
-    <t>134179819</t>
-  </si>
-  <si>
-    <t>134179834</t>
-  </si>
-  <si>
-    <t>134179858</t>
-  </si>
-  <si>
-    <t>134179969</t>
-  </si>
-  <si>
-    <t>134180008</t>
-  </si>
-  <si>
-    <t>134180238</t>
-  </si>
-  <si>
-    <t>134180317</t>
-  </si>
-  <si>
-    <t>134180482</t>
-  </si>
-  <si>
-    <t>134180487</t>
-  </si>
-  <si>
-    <t>134180556</t>
-  </si>
-  <si>
-    <t>134180683</t>
-  </si>
-  <si>
-    <t>134180798</t>
-  </si>
-  <si>
-    <t>134180955</t>
-  </si>
-  <si>
-    <t>134180977</t>
-  </si>
-  <si>
-    <t>134180990</t>
-  </si>
-  <si>
-    <t>134181169</t>
-  </si>
-  <si>
-    <t>134181173</t>
-  </si>
-  <si>
-    <t>134181181</t>
-  </si>
-  <si>
-    <t>134181183</t>
-  </si>
-  <si>
-    <t>134181213</t>
-  </si>
-  <si>
-    <t>134181254</t>
-  </si>
-  <si>
-    <t>134181317</t>
-  </si>
-  <si>
-    <t>134181363</t>
-  </si>
-  <si>
-    <t>134181474</t>
-  </si>
-  <si>
-    <t>134181526</t>
-  </si>
-  <si>
-    <t>134181577</t>
-  </si>
-  <si>
-    <t>134181711</t>
-  </si>
-  <si>
-    <t>134181872</t>
-  </si>
-  <si>
-    <t>134181932</t>
-  </si>
-  <si>
-    <t>134182035</t>
-  </si>
-  <si>
-    <t>134182130</t>
-  </si>
-  <si>
-    <t>134182171</t>
-  </si>
-  <si>
-    <t>134182250</t>
-  </si>
-  <si>
-    <t>134182334</t>
-  </si>
-  <si>
-    <t>134182341</t>
-  </si>
-  <si>
-    <t>134182447</t>
-  </si>
-  <si>
-    <t>134182558</t>
-  </si>
-  <si>
-    <t>134182617</t>
-  </si>
-  <si>
-    <t>134182822</t>
-  </si>
-  <si>
-    <t>134182909</t>
-  </si>
-  <si>
-    <t>134183024</t>
-  </si>
-  <si>
-    <t>134183375</t>
-  </si>
-  <si>
-    <t>134183386</t>
-  </si>
-  <si>
-    <t>134183403</t>
-  </si>
-  <si>
-    <t>134183419</t>
-  </si>
-  <si>
-    <t>134183516</t>
-  </si>
-  <si>
-    <t>134183528</t>
-  </si>
-  <si>
-    <t>134183769</t>
-  </si>
-  <si>
-    <t>134184079</t>
-  </si>
-  <si>
-    <t>134184112</t>
-  </si>
-  <si>
-    <t>134184496</t>
-  </si>
-  <si>
-    <t>134184764</t>
-  </si>
-  <si>
-    <t>134185045</t>
-  </si>
-  <si>
-    <t>134185363</t>
-  </si>
-  <si>
-    <t>134185567</t>
-  </si>
-  <si>
-    <t>134185571</t>
-  </si>
-  <si>
-    <t>134185575</t>
-  </si>
-  <si>
-    <t>134185623</t>
+    <t>129315423</t>
+  </si>
+  <si>
+    <t>129647275</t>
+  </si>
+  <si>
+    <t>129974883</t>
+  </si>
+  <si>
+    <t>129977860</t>
+  </si>
+  <si>
+    <t>130183532</t>
+  </si>
+  <si>
+    <t>130457524</t>
+  </si>
+  <si>
+    <t>130993542</t>
+  </si>
+  <si>
+    <t>131106543</t>
+  </si>
+  <si>
+    <t>131171668</t>
+  </si>
+  <si>
+    <t>131624462</t>
+  </si>
+  <si>
+    <t>131765978</t>
+  </si>
+  <si>
+    <t>131810911</t>
+  </si>
+  <si>
+    <t>131843371</t>
+  </si>
+  <si>
+    <t>131920268</t>
+  </si>
+  <si>
+    <t>132017763</t>
+  </si>
+  <si>
+    <t>132274247</t>
+  </si>
+  <si>
+    <t>132350461</t>
+  </si>
+  <si>
+    <t>132447136</t>
+  </si>
+  <si>
+    <t>132776417</t>
+  </si>
+  <si>
+    <t>132829489</t>
+  </si>
+  <si>
+    <t>132936812</t>
+  </si>
+  <si>
+    <t>132943478</t>
+  </si>
+  <si>
+    <t>133132812</t>
+  </si>
+  <si>
+    <t>133720155</t>
+  </si>
+  <si>
+    <t>133730594</t>
+  </si>
+  <si>
+    <t>133763806</t>
+  </si>
+  <si>
+    <t>133872566</t>
+  </si>
+  <si>
+    <t>133906515</t>
+  </si>
+  <si>
+    <t>133968196</t>
+  </si>
+  <si>
+    <t>134185917</t>
+  </si>
+  <si>
+    <t>134185921</t>
+  </si>
+  <si>
+    <t>134186125</t>
+  </si>
+  <si>
+    <t>134186237</t>
+  </si>
+  <si>
+    <t>134186459</t>
+  </si>
+  <si>
+    <t>134186509</t>
+  </si>
+  <si>
+    <t>134186521</t>
+  </si>
+  <si>
+    <t>134186694</t>
+  </si>
+  <si>
+    <t>134186993</t>
+  </si>
+  <si>
+    <t>134187012</t>
+  </si>
+  <si>
+    <t>134187066</t>
+  </si>
+  <si>
+    <t>134187183</t>
+  </si>
+  <si>
+    <t>134187339</t>
+  </si>
+  <si>
+    <t>134187563</t>
+  </si>
+  <si>
+    <t>134187673</t>
+  </si>
+  <si>
+    <t>134187719</t>
+  </si>
+  <si>
+    <t>134187749</t>
+  </si>
+  <si>
+    <t>134187930</t>
+  </si>
+  <si>
+    <t>134187933</t>
+  </si>
+  <si>
+    <t>134188025</t>
+  </si>
+  <si>
+    <t>134188043</t>
+  </si>
+  <si>
+    <t>134188164</t>
+  </si>
+  <si>
+    <t>134188292</t>
+  </si>
+  <si>
+    <t>134188321</t>
+  </si>
+  <si>
+    <t>134188338</t>
+  </si>
+  <si>
+    <t>134188409</t>
+  </si>
+  <si>
+    <t>134188648</t>
+  </si>
+  <si>
+    <t>134188922</t>
+  </si>
+  <si>
+    <t>134188937</t>
+  </si>
+  <si>
+    <t>134188990</t>
+  </si>
+  <si>
+    <t>134189187</t>
+  </si>
+  <si>
+    <t>134189453</t>
+  </si>
+  <si>
+    <t>134189532</t>
+  </si>
+  <si>
+    <t>134189799</t>
+  </si>
+  <si>
+    <t>134189902</t>
+  </si>
+  <si>
+    <t>134189970</t>
+  </si>
+  <si>
+    <t>134190143</t>
+  </si>
+  <si>
+    <t>134190161</t>
+  </si>
+  <si>
+    <t>134190258</t>
+  </si>
+  <si>
+    <t>134190401</t>
+  </si>
+  <si>
+    <t>134190445</t>
+  </si>
+  <si>
+    <t>134190802</t>
+  </si>
+  <si>
+    <t>134190824</t>
+  </si>
+  <si>
+    <t>134190841</t>
+  </si>
+  <si>
+    <t>134190862</t>
+  </si>
+  <si>
+    <t>134190893</t>
+  </si>
+  <si>
+    <t>134190896</t>
+  </si>
+  <si>
+    <t>134190996</t>
+  </si>
+  <si>
+    <t>134191030</t>
+  </si>
+  <si>
+    <t>134191040</t>
+  </si>
+  <si>
+    <t>134191056</t>
+  </si>
+  <si>
+    <t>134191266</t>
+  </si>
+  <si>
+    <t>134191270</t>
+  </si>
+  <si>
+    <t>134191389</t>
+  </si>
+  <si>
+    <t>134191494</t>
+  </si>
+  <si>
+    <t>134191647</t>
+  </si>
+  <si>
+    <t>134191688</t>
+  </si>
+  <si>
+    <t>134191689</t>
+  </si>
+  <si>
+    <t>134191741</t>
+  </si>
+  <si>
+    <t>134192170</t>
+  </si>
+  <si>
+    <t>134192184</t>
+  </si>
+  <si>
+    <t>134192439</t>
+  </si>
+  <si>
+    <t>134192511</t>
+  </si>
+  <si>
+    <t>134192561</t>
+  </si>
+  <si>
+    <t>134192639</t>
+  </si>
+  <si>
+    <t>134192733</t>
+  </si>
+  <si>
+    <t>134192757</t>
+  </si>
+  <si>
+    <t>134192795</t>
+  </si>
+  <si>
+    <t>134192826</t>
+  </si>
+  <si>
+    <t>134192840</t>
+  </si>
+  <si>
+    <t>134192880</t>
+  </si>
+  <si>
+    <t>134192894</t>
+  </si>
+  <si>
+    <t>134193006</t>
+  </si>
+  <si>
+    <t>134193014</t>
+  </si>
+  <si>
+    <t>134193074</t>
+  </si>
+  <si>
+    <t>134193364</t>
+  </si>
+  <si>
+    <t>134193370</t>
+  </si>
+  <si>
+    <t>134193444</t>
+  </si>
+  <si>
+    <t>134193561</t>
+  </si>
+  <si>
+    <t>134193608</t>
+  </si>
+  <si>
+    <t>134193749</t>
+  </si>
+  <si>
+    <t>134193789</t>
+  </si>
+  <si>
+    <t>134193814</t>
+  </si>
+  <si>
+    <t>134193846</t>
+  </si>
+  <si>
+    <t>134193921</t>
+  </si>
+  <si>
+    <t>134194000</t>
+  </si>
+  <si>
+    <t>134194097</t>
+  </si>
+  <si>
+    <t>134194130</t>
+  </si>
+  <si>
+    <t>134194352</t>
+  </si>
+  <si>
+    <t>134194453</t>
+  </si>
+  <si>
+    <t>134194526</t>
+  </si>
+  <si>
+    <t>134194557</t>
+  </si>
+  <si>
+    <t>134194562</t>
+  </si>
+  <si>
+    <t>134194759</t>
+  </si>
+  <si>
+    <t>134194760</t>
+  </si>
+  <si>
+    <t>134194771</t>
+  </si>
+  <si>
+    <t>134194819</t>
+  </si>
+  <si>
+    <t>134194867</t>
+  </si>
+  <si>
+    <t>134195109</t>
+  </si>
+  <si>
+    <t>134195275</t>
+  </si>
+  <si>
+    <t>134195281</t>
+  </si>
+  <si>
+    <t>134195357</t>
+  </si>
+  <si>
+    <t>134195399</t>
+  </si>
+  <si>
+    <t>134195403</t>
+  </si>
+  <si>
+    <t>134195469</t>
+  </si>
+  <si>
+    <t>134195629</t>
+  </si>
+  <si>
+    <t>134195642</t>
+  </si>
+  <si>
+    <t>134195681</t>
+  </si>
+  <si>
+    <t>134195723</t>
+  </si>
+  <si>
+    <t>134195749</t>
+  </si>
+  <si>
+    <t>134195766</t>
+  </si>
+  <si>
+    <t>134195871</t>
+  </si>
+  <si>
+    <t>134196227</t>
+  </si>
+  <si>
+    <t>134196243</t>
+  </si>
+  <si>
+    <t>134196299</t>
+  </si>
+  <si>
+    <t>134196342</t>
+  </si>
+  <si>
+    <t>134196613</t>
+  </si>
+  <si>
+    <t>134197036</t>
+  </si>
+  <si>
+    <t>134197131</t>
+  </si>
+  <si>
+    <t>134197236</t>
+  </si>
+  <si>
+    <t>134197241</t>
+  </si>
+  <si>
+    <t>134197529</t>
+  </si>
+  <si>
+    <t>134197852</t>
+  </si>
+  <si>
+    <t>134197853</t>
+  </si>
+  <si>
+    <t>134197957</t>
+  </si>
+  <si>
+    <t>134197979</t>
+  </si>
+  <si>
+    <t>134198142</t>
+  </si>
+  <si>
+    <t>134198416</t>
+  </si>
+  <si>
+    <t>134198426</t>
+  </si>
+  <si>
+    <t>134198786</t>
+  </si>
+  <si>
+    <t>134198876</t>
+  </si>
+  <si>
+    <t>134198945</t>
+  </si>
+  <si>
+    <t>134199180</t>
+  </si>
+  <si>
+    <t>134199249</t>
+  </si>
+  <si>
+    <t>134199304</t>
+  </si>
+  <si>
+    <t>134199317</t>
+  </si>
+  <si>
+    <t>134199527</t>
+  </si>
+  <si>
+    <t>134199689</t>
+  </si>
+  <si>
+    <t>134199697</t>
+  </si>
+  <si>
+    <t>134199896</t>
+  </si>
+  <si>
+    <t>134199911</t>
+  </si>
+  <si>
+    <t>134199944</t>
+  </si>
+  <si>
+    <t>134199955</t>
+  </si>
+  <si>
+    <t>134200032</t>
+  </si>
+  <si>
+    <t>134200325</t>
+  </si>
+  <si>
+    <t>134200360</t>
+  </si>
+  <si>
+    <t>134200366</t>
+  </si>
+  <si>
+    <t>134200564</t>
+  </si>
+  <si>
+    <t>134200585</t>
+  </si>
+  <si>
+    <t>134200663</t>
+  </si>
+  <si>
+    <t>134200827</t>
+  </si>
+  <si>
+    <t>134200857</t>
+  </si>
+  <si>
+    <t>134201161</t>
+  </si>
+  <si>
+    <t>134201314</t>
+  </si>
+  <si>
+    <t>134201496</t>
+  </si>
+  <si>
+    <t>134201505</t>
+  </si>
+  <si>
+    <t>134201552</t>
+  </si>
+  <si>
+    <t>134201573</t>
+  </si>
+  <si>
+    <t>134201912</t>
+  </si>
+  <si>
+    <t>134202021</t>
+  </si>
+  <si>
+    <t>134202101</t>
+  </si>
+  <si>
+    <t>134202140</t>
+  </si>
+  <si>
+    <t>134202251</t>
+  </si>
+  <si>
+    <t>134202259</t>
+  </si>
+  <si>
+    <t>134202273</t>
+  </si>
+  <si>
+    <t>134202349</t>
+  </si>
+  <si>
+    <t>134202389</t>
+  </si>
+  <si>
+    <t>134202432</t>
+  </si>
+  <si>
+    <t>134202519</t>
+  </si>
+  <si>
+    <t>134202813</t>
+  </si>
+  <si>
+    <t>134202866</t>
+  </si>
+  <si>
+    <t>134202875</t>
+  </si>
+  <si>
+    <t>134203270</t>
+  </si>
+  <si>
+    <t>134203302</t>
+  </si>
+  <si>
+    <t>134203413</t>
+  </si>
+  <si>
+    <t>134203522</t>
+  </si>
+  <si>
+    <t>134203536</t>
+  </si>
+  <si>
+    <t>134203678</t>
+  </si>
+  <si>
+    <t>134204141</t>
+  </si>
+  <si>
+    <t>134204180</t>
+  </si>
+  <si>
+    <t>134204253</t>
+  </si>
+  <si>
+    <t>134204335</t>
+  </si>
+  <si>
+    <t>134204341</t>
+  </si>
+  <si>
+    <t>134204496</t>
+  </si>
+  <si>
+    <t>134204824</t>
+  </si>
+  <si>
+    <t>134204900</t>
+  </si>
+  <si>
+    <t>134204931</t>
+  </si>
+  <si>
+    <t>134204990</t>
+  </si>
+  <si>
+    <t>134205000</t>
+  </si>
+  <si>
+    <t>134205006</t>
+  </si>
+  <si>
+    <t>134205113</t>
+  </si>
+  <si>
+    <t>134205366</t>
+  </si>
+  <si>
+    <t>134205375</t>
+  </si>
+  <si>
+    <t>134205457</t>
+  </si>
+  <si>
+    <t>134205572</t>
+  </si>
+  <si>
+    <t>134205789</t>
+  </si>
+  <si>
+    <t>134205801</t>
+  </si>
+  <si>
+    <t>134205836</t>
+  </si>
+  <si>
+    <t>134205953</t>
+  </si>
+  <si>
+    <t>134206060</t>
+  </si>
+  <si>
+    <t>134206080</t>
+  </si>
+  <si>
+    <t>134206248</t>
+  </si>
+  <si>
+    <t>134206251</t>
+  </si>
+  <si>
+    <t>134206282</t>
+  </si>
+  <si>
+    <t>134206306</t>
+  </si>
+  <si>
+    <t>134206386</t>
+  </si>
+  <si>
+    <t>134206455</t>
+  </si>
+  <si>
+    <t>134206582</t>
+  </si>
+  <si>
+    <t>134206623</t>
+  </si>
+  <si>
+    <t>134206780</t>
+  </si>
+  <si>
+    <t>134206810</t>
+  </si>
+  <si>
+    <t>134207088</t>
+  </si>
+  <si>
+    <t>134207215</t>
+  </si>
+  <si>
+    <t>134207331</t>
+  </si>
+  <si>
+    <t>134207350</t>
+  </si>
+  <si>
+    <t>134207393</t>
+  </si>
+  <si>
+    <t>134207411</t>
+  </si>
+  <si>
+    <t>134207431</t>
+  </si>
+  <si>
+    <t>134207457</t>
+  </si>
+  <si>
+    <t>134207534</t>
+  </si>
+  <si>
+    <t>134207753</t>
+  </si>
+  <si>
+    <t>134207810</t>
+  </si>
+  <si>
+    <t>134207823</t>
+  </si>
+  <si>
+    <t>134207825</t>
+  </si>
+  <si>
+    <t>134207961</t>
+  </si>
+  <si>
+    <t>134208023</t>
+  </si>
+  <si>
+    <t>134208072</t>
+  </si>
+  <si>
+    <t>134208154</t>
+  </si>
+  <si>
+    <t>134208210</t>
+  </si>
+  <si>
+    <t>134208381</t>
+  </si>
+  <si>
+    <t>134208407</t>
+  </si>
+  <si>
+    <t>134208431</t>
+  </si>
+  <si>
+    <t>134208447</t>
+  </si>
+  <si>
+    <t>134208500</t>
+  </si>
+  <si>
+    <t>134208529</t>
+  </si>
+  <si>
+    <t>134208536</t>
+  </si>
+  <si>
+    <t>134208570</t>
+  </si>
+  <si>
+    <t>134208613</t>
+  </si>
+  <si>
+    <t>134208669</t>
+  </si>
+  <si>
+    <t>134208723</t>
+  </si>
+  <si>
+    <t>134208742</t>
+  </si>
+  <si>
+    <t>134208754</t>
+  </si>
+  <si>
+    <t>134208891</t>
+  </si>
+  <si>
+    <t>134208957</t>
+  </si>
+  <si>
+    <t>134209024</t>
+  </si>
+  <si>
+    <t>134209125</t>
+  </si>
+  <si>
+    <t>134209193</t>
+  </si>
+  <si>
+    <t>134209663</t>
+  </si>
+  <si>
+    <t>134209727</t>
+  </si>
+  <si>
+    <t>134209750</t>
+  </si>
+  <si>
+    <t>134210663</t>
+  </si>
+  <si>
+    <t>134210717</t>
+  </si>
+  <si>
+    <t>134210719</t>
+  </si>
+  <si>
+    <t>134210769</t>
+  </si>
+  <si>
+    <t>134210811</t>
+  </si>
+  <si>
+    <t>134211034</t>
+  </si>
+  <si>
+    <t>134211057</t>
+  </si>
+  <si>
+    <t>134211096</t>
+  </si>
+  <si>
+    <t>134211127</t>
+  </si>
+  <si>
+    <t>134211153</t>
+  </si>
+  <si>
+    <t>134211159</t>
+  </si>
+  <si>
+    <t>134211434</t>
+  </si>
+  <si>
+    <t>134211552</t>
+  </si>
+  <si>
+    <t>134211611</t>
+  </si>
+  <si>
+    <t>134211651</t>
+  </si>
+  <si>
+    <t>134211689</t>
+  </si>
+  <si>
+    <t>134211770</t>
+  </si>
+  <si>
+    <t>134211777</t>
+  </si>
+  <si>
+    <t>134211807</t>
+  </si>
+  <si>
+    <t>134211841</t>
+  </si>
+  <si>
+    <t>134211920</t>
+  </si>
+  <si>
+    <t>134212108</t>
+  </si>
+  <si>
+    <t>134212180</t>
+  </si>
+  <si>
+    <t>134212293</t>
+  </si>
+  <si>
+    <t>134212310</t>
+  </si>
+  <si>
+    <t>134212320</t>
+  </si>
+  <si>
+    <t>134212342</t>
+  </si>
+  <si>
+    <t>134212358</t>
+  </si>
+  <si>
+    <t>134212397</t>
+  </si>
+  <si>
+    <t>134212403</t>
+  </si>
+  <si>
+    <t>134212420</t>
+  </si>
+  <si>
+    <t>134212538</t>
+  </si>
+  <si>
+    <t>134212578</t>
+  </si>
+  <si>
+    <t>134212609</t>
+  </si>
+  <si>
+    <t>134212611</t>
+  </si>
+  <si>
+    <t>134212646</t>
+  </si>
+  <si>
+    <t>134212773</t>
+  </si>
+  <si>
+    <t>134212783</t>
+  </si>
+  <si>
+    <t>134212852</t>
+  </si>
+  <si>
+    <t>134212863</t>
+  </si>
+  <si>
+    <t>134212888</t>
+  </si>
+  <si>
+    <t>134213085</t>
+  </si>
+  <si>
+    <t>134213578</t>
+  </si>
+  <si>
+    <t>134213818</t>
+  </si>
+  <si>
+    <t>134213927</t>
+  </si>
+  <si>
+    <t>134214141</t>
+  </si>
+  <si>
+    <t>134214230</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C224"/>
+  <dimension ref="A1:C333"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3589,6 +3898,1163 @@
         <v>4</v>
       </c>
     </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B328" s="6"/>
+      <c r="C328" s="5"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B329" s="6"/>
+      <c r="C329" s="5"/>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B330" s="6"/>
+      <c r="C330" s="5"/>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B331" s="6"/>
+      <c r="C331" s="5"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B332" s="6"/>
+      <c r="C332" s="5"/>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B333" s="6"/>
+      <c r="C333" s="5"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC18EC9B-ED32-4952-93DB-52F57E12EE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4858E2-9D69-4F34-A9E9-45BDC6787084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$205</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="212">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,610 +45,625 @@
     <t>.</t>
   </si>
   <si>
-    <t>130094967</t>
-  </si>
-  <si>
-    <t>130312912</t>
-  </si>
-  <si>
-    <t>130317752</t>
-  </si>
-  <si>
-    <t>130610156</t>
-  </si>
-  <si>
-    <t>130622368</t>
-  </si>
-  <si>
-    <t>130648170</t>
-  </si>
-  <si>
-    <t>130950538</t>
-  </si>
-  <si>
-    <t>131190618</t>
-  </si>
-  <si>
-    <t>131194704</t>
-  </si>
-  <si>
-    <t>131392834</t>
-  </si>
-  <si>
-    <t>131543735</t>
-  </si>
-  <si>
-    <t>131577582</t>
-  </si>
-  <si>
-    <t>131610534</t>
-  </si>
-  <si>
-    <t>131642673</t>
-  </si>
-  <si>
-    <t>132049632</t>
-  </si>
-  <si>
-    <t>132275206</t>
-  </si>
-  <si>
-    <t>132453385</t>
-  </si>
-  <si>
-    <t>132486022</t>
-  </si>
-  <si>
-    <t>132624685</t>
-  </si>
-  <si>
-    <t>133077517</t>
-  </si>
-  <si>
-    <t>133106191</t>
-  </si>
-  <si>
-    <t>133392099</t>
-  </si>
-  <si>
-    <t>133527541</t>
-  </si>
-  <si>
-    <t>133596773</t>
-  </si>
-  <si>
-    <t>133668898</t>
-  </si>
-  <si>
-    <t>133690758</t>
-  </si>
-  <si>
-    <t>133958563</t>
-  </si>
-  <si>
-    <t>134256212</t>
-  </si>
-  <si>
-    <t>134256261</t>
-  </si>
-  <si>
-    <t>134256885</t>
-  </si>
-  <si>
-    <t>134256900</t>
-  </si>
-  <si>
-    <t>134256973</t>
-  </si>
-  <si>
-    <t>134257213</t>
-  </si>
-  <si>
-    <t>134257341</t>
-  </si>
-  <si>
-    <t>134257352</t>
-  </si>
-  <si>
-    <t>134257436</t>
-  </si>
-  <si>
-    <t>134257478</t>
-  </si>
-  <si>
-    <t>134257515</t>
-  </si>
-  <si>
-    <t>134258094</t>
-  </si>
-  <si>
-    <t>134258249</t>
-  </si>
-  <si>
-    <t>134258441</t>
-  </si>
-  <si>
-    <t>134258471</t>
-  </si>
-  <si>
-    <t>134258509</t>
-  </si>
-  <si>
-    <t>134258704</t>
-  </si>
-  <si>
-    <t>134258827</t>
-  </si>
-  <si>
-    <t>134259166</t>
-  </si>
-  <si>
-    <t>134259385</t>
-  </si>
-  <si>
-    <t>134259393</t>
-  </si>
-  <si>
-    <t>134259498</t>
-  </si>
-  <si>
-    <t>134259684</t>
-  </si>
-  <si>
-    <t>134259694</t>
-  </si>
-  <si>
-    <t>134259893</t>
-  </si>
-  <si>
-    <t>134260057</t>
-  </si>
-  <si>
-    <t>134260172</t>
-  </si>
-  <si>
-    <t>134260281</t>
-  </si>
-  <si>
-    <t>134260322</t>
-  </si>
-  <si>
-    <t>134260490</t>
-  </si>
-  <si>
-    <t>134260716</t>
-  </si>
-  <si>
-    <t>134260886</t>
-  </si>
-  <si>
-    <t>134261126</t>
-  </si>
-  <si>
-    <t>134261198</t>
-  </si>
-  <si>
-    <t>134261243</t>
-  </si>
-  <si>
-    <t>134261391</t>
-  </si>
-  <si>
-    <t>134261638</t>
-  </si>
-  <si>
-    <t>134261747</t>
-  </si>
-  <si>
-    <t>134261818</t>
-  </si>
-  <si>
-    <t>134261833</t>
-  </si>
-  <si>
-    <t>134261983</t>
-  </si>
-  <si>
-    <t>134262306</t>
-  </si>
-  <si>
-    <t>134262337</t>
-  </si>
-  <si>
-    <t>134262605</t>
-  </si>
-  <si>
-    <t>134262606</t>
-  </si>
-  <si>
-    <t>134262627</t>
-  </si>
-  <si>
-    <t>134262652</t>
-  </si>
-  <si>
-    <t>134262825</t>
-  </si>
-  <si>
-    <t>134262839</t>
-  </si>
-  <si>
-    <t>134263094</t>
-  </si>
-  <si>
-    <t>134263121</t>
-  </si>
-  <si>
-    <t>134263367</t>
-  </si>
-  <si>
-    <t>134263451</t>
-  </si>
-  <si>
-    <t>134263482</t>
-  </si>
-  <si>
-    <t>134263492</t>
-  </si>
-  <si>
-    <t>134263497</t>
-  </si>
-  <si>
-    <t>134263558</t>
-  </si>
-  <si>
-    <t>134263677</t>
-  </si>
-  <si>
-    <t>134263738</t>
-  </si>
-  <si>
-    <t>134263812</t>
-  </si>
-  <si>
-    <t>134264094</t>
-  </si>
-  <si>
-    <t>134264220</t>
-  </si>
-  <si>
-    <t>134264459</t>
-  </si>
-  <si>
-    <t>134264658</t>
-  </si>
-  <si>
-    <t>134264696</t>
-  </si>
-  <si>
-    <t>134264775</t>
-  </si>
-  <si>
-    <t>134264898</t>
-  </si>
-  <si>
-    <t>134265186</t>
-  </si>
-  <si>
-    <t>134265388</t>
-  </si>
-  <si>
-    <t>134265552</t>
-  </si>
-  <si>
-    <t>134265561</t>
-  </si>
-  <si>
-    <t>134265564</t>
-  </si>
-  <si>
-    <t>134265582</t>
-  </si>
-  <si>
-    <t>134265724</t>
-  </si>
-  <si>
-    <t>134265755</t>
-  </si>
-  <si>
-    <t>134265775</t>
-  </si>
-  <si>
-    <t>134266062</t>
-  </si>
-  <si>
-    <t>134266198</t>
-  </si>
-  <si>
-    <t>134266450</t>
-  </si>
-  <si>
-    <t>134266492</t>
-  </si>
-  <si>
-    <t>134266698</t>
-  </si>
-  <si>
-    <t>134266845</t>
-  </si>
-  <si>
-    <t>134266848</t>
-  </si>
-  <si>
-    <t>134266934</t>
-  </si>
-  <si>
-    <t>134267141</t>
-  </si>
-  <si>
-    <t>134267187</t>
-  </si>
-  <si>
-    <t>134267282</t>
-  </si>
-  <si>
-    <t>134267363</t>
-  </si>
-  <si>
-    <t>134267441</t>
-  </si>
-  <si>
-    <t>134267571</t>
-  </si>
-  <si>
-    <t>134267657</t>
-  </si>
-  <si>
-    <t>134267731</t>
-  </si>
-  <si>
-    <t>134267833</t>
-  </si>
-  <si>
-    <t>134268052</t>
-  </si>
-  <si>
-    <t>134268235</t>
-  </si>
-  <si>
-    <t>134268468</t>
-  </si>
-  <si>
-    <t>134268804</t>
-  </si>
-  <si>
-    <t>134268884</t>
-  </si>
-  <si>
-    <t>134268958</t>
-  </si>
-  <si>
-    <t>134269373</t>
-  </si>
-  <si>
-    <t>134269453</t>
-  </si>
-  <si>
-    <t>134269545</t>
-  </si>
-  <si>
-    <t>134269579</t>
-  </si>
-  <si>
-    <t>134269736</t>
-  </si>
-  <si>
-    <t>134269841</t>
-  </si>
-  <si>
-    <t>134269843</t>
-  </si>
-  <si>
-    <t>134269852</t>
-  </si>
-  <si>
-    <t>134270175</t>
-  </si>
-  <si>
-    <t>134270681</t>
-  </si>
-  <si>
-    <t>134271186</t>
-  </si>
-  <si>
-    <t>134271199</t>
-  </si>
-  <si>
-    <t>134271727</t>
-  </si>
-  <si>
-    <t>134271861</t>
-  </si>
-  <si>
-    <t>134271999</t>
-  </si>
-  <si>
-    <t>134272028</t>
-  </si>
-  <si>
-    <t>134272053</t>
-  </si>
-  <si>
-    <t>134272154</t>
-  </si>
-  <si>
-    <t>134272243</t>
-  </si>
-  <si>
-    <t>134272312</t>
-  </si>
-  <si>
-    <t>134272354</t>
-  </si>
-  <si>
-    <t>134272395</t>
-  </si>
-  <si>
-    <t>134272529</t>
-  </si>
-  <si>
-    <t>134272643</t>
-  </si>
-  <si>
-    <t>134272702</t>
-  </si>
-  <si>
-    <t>134272705</t>
-  </si>
-  <si>
-    <t>134273102</t>
-  </si>
-  <si>
-    <t>134273173</t>
-  </si>
-  <si>
-    <t>134273235</t>
-  </si>
-  <si>
-    <t>134273302</t>
-  </si>
-  <si>
-    <t>134273306</t>
-  </si>
-  <si>
-    <t>134273322</t>
-  </si>
-  <si>
-    <t>134273362</t>
-  </si>
-  <si>
-    <t>134273448</t>
-  </si>
-  <si>
-    <t>134273453</t>
-  </si>
-  <si>
-    <t>134273537</t>
-  </si>
-  <si>
-    <t>134273696</t>
-  </si>
-  <si>
-    <t>134273789</t>
-  </si>
-  <si>
-    <t>134273829</t>
-  </si>
-  <si>
-    <t>134273943</t>
-  </si>
-  <si>
-    <t>134273999</t>
-  </si>
-  <si>
-    <t>134274040</t>
-  </si>
-  <si>
-    <t>134274049</t>
-  </si>
-  <si>
-    <t>134274153</t>
-  </si>
-  <si>
-    <t>134274234</t>
-  </si>
-  <si>
-    <t>134274382</t>
-  </si>
-  <si>
-    <t>134274558</t>
-  </si>
-  <si>
-    <t>134274591</t>
-  </si>
-  <si>
-    <t>134274763</t>
-  </si>
-  <si>
-    <t>134274783</t>
-  </si>
-  <si>
-    <t>134274813</t>
-  </si>
-  <si>
-    <t>134274889</t>
-  </si>
-  <si>
-    <t>134274997</t>
-  </si>
-  <si>
-    <t>134275097</t>
-  </si>
-  <si>
-    <t>134275129</t>
-  </si>
-  <si>
-    <t>134275281</t>
-  </si>
-  <si>
-    <t>134275284</t>
-  </si>
-  <si>
-    <t>134275373</t>
-  </si>
-  <si>
-    <t>134275468</t>
-  </si>
-  <si>
-    <t>134275525</t>
-  </si>
-  <si>
-    <t>134275735</t>
-  </si>
-  <si>
-    <t>134275814</t>
-  </si>
-  <si>
-    <t>134275892</t>
-  </si>
-  <si>
-    <t>134275951</t>
-  </si>
-  <si>
-    <t>134275979</t>
-  </si>
-  <si>
-    <t>134276082</t>
-  </si>
-  <si>
-    <t>134276143</t>
-  </si>
-  <si>
-    <t>134276275</t>
-  </si>
-  <si>
-    <t>134276748</t>
-  </si>
-  <si>
-    <t>134277024</t>
-  </si>
-  <si>
-    <t>134277361</t>
-  </si>
-  <si>
-    <t>134277942</t>
-  </si>
-  <si>
-    <t>134277950</t>
-  </si>
-  <si>
-    <t>134277974</t>
-  </si>
-  <si>
-    <t>134279263</t>
-  </si>
-  <si>
-    <t>134279440</t>
+    <t>129551118</t>
+  </si>
+  <si>
+    <t>129589860</t>
+  </si>
+  <si>
+    <t>130000505</t>
+  </si>
+  <si>
+    <t>130086787</t>
+  </si>
+  <si>
+    <t>130104207</t>
+  </si>
+  <si>
+    <t>130568697</t>
+  </si>
+  <si>
+    <t>130638485</t>
+  </si>
+  <si>
+    <t>130906729</t>
+  </si>
+  <si>
+    <t>131031574</t>
+  </si>
+  <si>
+    <t>131513808</t>
+  </si>
+  <si>
+    <t>132143955</t>
+  </si>
+  <si>
+    <t>132594332</t>
+  </si>
+  <si>
+    <t>133027143</t>
+  </si>
+  <si>
+    <t>133039439</t>
+  </si>
+  <si>
+    <t>133886402</t>
+  </si>
+  <si>
+    <t>133983147</t>
+  </si>
+  <si>
+    <t>134125164</t>
+  </si>
+  <si>
+    <t>134279756</t>
+  </si>
+  <si>
+    <t>134279849</t>
+  </si>
+  <si>
+    <t>134279975</t>
+  </si>
+  <si>
+    <t>134280002</t>
+  </si>
+  <si>
+    <t>134280023</t>
+  </si>
+  <si>
+    <t>134280083</t>
+  </si>
+  <si>
+    <t>134280176</t>
+  </si>
+  <si>
+    <t>134280248</t>
+  </si>
+  <si>
+    <t>134280255</t>
+  </si>
+  <si>
+    <t>134280268</t>
+  </si>
+  <si>
+    <t>134280535</t>
+  </si>
+  <si>
+    <t>134280562</t>
+  </si>
+  <si>
+    <t>134280566</t>
+  </si>
+  <si>
+    <t>134280660</t>
+  </si>
+  <si>
+    <t>134280690</t>
+  </si>
+  <si>
+    <t>134280760</t>
+  </si>
+  <si>
+    <t>134280897</t>
+  </si>
+  <si>
+    <t>134280914</t>
+  </si>
+  <si>
+    <t>134280961</t>
+  </si>
+  <si>
+    <t>134280971</t>
+  </si>
+  <si>
+    <t>134281009</t>
+  </si>
+  <si>
+    <t>134281300</t>
+  </si>
+  <si>
+    <t>134281320</t>
+  </si>
+  <si>
+    <t>134281326</t>
+  </si>
+  <si>
+    <t>134281404</t>
+  </si>
+  <si>
+    <t>134281469</t>
+  </si>
+  <si>
+    <t>134281580</t>
+  </si>
+  <si>
+    <t>134281740</t>
+  </si>
+  <si>
+    <t>134281952</t>
+  </si>
+  <si>
+    <t>134282142</t>
+  </si>
+  <si>
+    <t>134282439</t>
+  </si>
+  <si>
+    <t>134282565</t>
+  </si>
+  <si>
+    <t>134282645</t>
+  </si>
+  <si>
+    <t>134282816</t>
+  </si>
+  <si>
+    <t>134282910</t>
+  </si>
+  <si>
+    <t>134283083</t>
+  </si>
+  <si>
+    <t>134283115</t>
+  </si>
+  <si>
+    <t>134283318</t>
+  </si>
+  <si>
+    <t>134283326</t>
+  </si>
+  <si>
+    <t>134283727</t>
+  </si>
+  <si>
+    <t>134283796</t>
+  </si>
+  <si>
+    <t>134283843</t>
+  </si>
+  <si>
+    <t>134283897</t>
+  </si>
+  <si>
+    <t>134284167</t>
+  </si>
+  <si>
+    <t>134284194</t>
+  </si>
+  <si>
+    <t>134284285</t>
+  </si>
+  <si>
+    <t>134284321</t>
+  </si>
+  <si>
+    <t>134284445</t>
+  </si>
+  <si>
+    <t>134284477</t>
+  </si>
+  <si>
+    <t>134284618</t>
+  </si>
+  <si>
+    <t>134284680</t>
+  </si>
+  <si>
+    <t>134284919</t>
+  </si>
+  <si>
+    <t>134284997</t>
+  </si>
+  <si>
+    <t>134285027</t>
+  </si>
+  <si>
+    <t>134285062</t>
+  </si>
+  <si>
+    <t>134285248</t>
+  </si>
+  <si>
+    <t>134285690</t>
+  </si>
+  <si>
+    <t>134285882</t>
+  </si>
+  <si>
+    <t>134286106</t>
+  </si>
+  <si>
+    <t>134286447</t>
+  </si>
+  <si>
+    <t>134286507</t>
+  </si>
+  <si>
+    <t>134286515</t>
+  </si>
+  <si>
+    <t>134286811</t>
+  </si>
+  <si>
+    <t>134286843</t>
+  </si>
+  <si>
+    <t>134286893</t>
+  </si>
+  <si>
+    <t>134286913</t>
+  </si>
+  <si>
+    <t>134287055</t>
+  </si>
+  <si>
+    <t>134287574</t>
+  </si>
+  <si>
+    <t>134287619</t>
+  </si>
+  <si>
+    <t>134287636</t>
+  </si>
+  <si>
+    <t>134287724</t>
+  </si>
+  <si>
+    <t>134287772</t>
+  </si>
+  <si>
+    <t>134287831</t>
+  </si>
+  <si>
+    <t>134287832</t>
+  </si>
+  <si>
+    <t>134287890</t>
+  </si>
+  <si>
+    <t>134287909</t>
+  </si>
+  <si>
+    <t>134288011</t>
+  </si>
+  <si>
+    <t>134288224</t>
+  </si>
+  <si>
+    <t>134288387</t>
+  </si>
+  <si>
+    <t>134288429</t>
+  </si>
+  <si>
+    <t>134288479</t>
+  </si>
+  <si>
+    <t>134288561</t>
+  </si>
+  <si>
+    <t>134288728</t>
+  </si>
+  <si>
+    <t>134288883</t>
+  </si>
+  <si>
+    <t>134288907</t>
+  </si>
+  <si>
+    <t>134288908</t>
+  </si>
+  <si>
+    <t>134288972</t>
+  </si>
+  <si>
+    <t>134289096</t>
+  </si>
+  <si>
+    <t>134289173</t>
+  </si>
+  <si>
+    <t>134289192</t>
+  </si>
+  <si>
+    <t>134289194</t>
+  </si>
+  <si>
+    <t>134289266</t>
+  </si>
+  <si>
+    <t>134289481</t>
+  </si>
+  <si>
+    <t>134289489</t>
+  </si>
+  <si>
+    <t>134289493</t>
+  </si>
+  <si>
+    <t>134289691</t>
+  </si>
+  <si>
+    <t>134289791</t>
+  </si>
+  <si>
+    <t>134289895</t>
+  </si>
+  <si>
+    <t>134289926</t>
+  </si>
+  <si>
+    <t>134290101</t>
+  </si>
+  <si>
+    <t>134290271</t>
+  </si>
+  <si>
+    <t>134290502</t>
+  </si>
+  <si>
+    <t>134290898</t>
+  </si>
+  <si>
+    <t>134290941</t>
+  </si>
+  <si>
+    <t>134291065</t>
+  </si>
+  <si>
+    <t>134291640</t>
+  </si>
+  <si>
+    <t>134291732</t>
+  </si>
+  <si>
+    <t>134291770</t>
+  </si>
+  <si>
+    <t>134292031</t>
+  </si>
+  <si>
+    <t>134292267</t>
+  </si>
+  <si>
+    <t>134292307</t>
+  </si>
+  <si>
+    <t>134292594</t>
+  </si>
+  <si>
+    <t>134292626</t>
+  </si>
+  <si>
+    <t>134292632</t>
+  </si>
+  <si>
+    <t>134292762</t>
+  </si>
+  <si>
+    <t>134292787</t>
+  </si>
+  <si>
+    <t>134292888</t>
+  </si>
+  <si>
+    <t>134293154</t>
+  </si>
+  <si>
+    <t>134293260</t>
+  </si>
+  <si>
+    <t>134293418</t>
+  </si>
+  <si>
+    <t>134293455</t>
+  </si>
+  <si>
+    <t>134293604</t>
+  </si>
+  <si>
+    <t>134293663</t>
+  </si>
+  <si>
+    <t>134293702</t>
+  </si>
+  <si>
+    <t>134293745</t>
+  </si>
+  <si>
+    <t>134293848</t>
+  </si>
+  <si>
+    <t>134293849</t>
+  </si>
+  <si>
+    <t>134294082</t>
+  </si>
+  <si>
+    <t>134294235</t>
+  </si>
+  <si>
+    <t>134294489</t>
+  </si>
+  <si>
+    <t>134294584</t>
+  </si>
+  <si>
+    <t>134294591</t>
+  </si>
+  <si>
+    <t>134294738</t>
+  </si>
+  <si>
+    <t>134294748</t>
+  </si>
+  <si>
+    <t>134294832</t>
+  </si>
+  <si>
+    <t>134295175</t>
+  </si>
+  <si>
+    <t>134295854</t>
+  </si>
+  <si>
+    <t>134295908</t>
+  </si>
+  <si>
+    <t>134295972</t>
+  </si>
+  <si>
+    <t>134296056</t>
+  </si>
+  <si>
+    <t>134296242</t>
+  </si>
+  <si>
+    <t>134296724</t>
+  </si>
+  <si>
+    <t>134296780</t>
+  </si>
+  <si>
+    <t>134296882</t>
+  </si>
+  <si>
+    <t>134296888</t>
+  </si>
+  <si>
+    <t>134296902</t>
+  </si>
+  <si>
+    <t>134296981</t>
+  </si>
+  <si>
+    <t>134296983</t>
+  </si>
+  <si>
+    <t>134297066</t>
+  </si>
+  <si>
+    <t>134297096</t>
+  </si>
+  <si>
+    <t>134297217</t>
+  </si>
+  <si>
+    <t>134297501</t>
+  </si>
+  <si>
+    <t>134297592</t>
+  </si>
+  <si>
+    <t>134297625</t>
+  </si>
+  <si>
+    <t>134297773</t>
+  </si>
+  <si>
+    <t>134297869</t>
+  </si>
+  <si>
+    <t>134297951</t>
+  </si>
+  <si>
+    <t>134297999</t>
+  </si>
+  <si>
+    <t>134298042</t>
+  </si>
+  <si>
+    <t>134298082</t>
+  </si>
+  <si>
+    <t>134298144</t>
+  </si>
+  <si>
+    <t>134298165</t>
+  </si>
+  <si>
+    <t>134298168</t>
+  </si>
+  <si>
+    <t>134298360</t>
+  </si>
+  <si>
+    <t>134298396</t>
+  </si>
+  <si>
+    <t>134298443</t>
+  </si>
+  <si>
+    <t>134298444</t>
+  </si>
+  <si>
+    <t>134298521</t>
+  </si>
+  <si>
+    <t>134298732</t>
+  </si>
+  <si>
+    <t>134298749</t>
+  </si>
+  <si>
+    <t>134298936</t>
+  </si>
+  <si>
+    <t>134298986</t>
+  </si>
+  <si>
+    <t>134299012</t>
+  </si>
+  <si>
+    <t>134299074</t>
+  </si>
+  <si>
+    <t>134299102</t>
+  </si>
+  <si>
+    <t>134299203</t>
+  </si>
+  <si>
+    <t>134299333</t>
+  </si>
+  <si>
+    <t>134299506</t>
+  </si>
+  <si>
+    <t>134299610</t>
+  </si>
+  <si>
+    <t>134299666</t>
+  </si>
+  <si>
+    <t>134299822</t>
+  </si>
+  <si>
+    <t>134300008</t>
+  </si>
+  <si>
+    <t>134300093</t>
+  </si>
+  <si>
+    <t>134300111</t>
+  </si>
+  <si>
+    <t>134300209</t>
+  </si>
+  <si>
+    <t>134300789</t>
+  </si>
+  <si>
+    <t>134300951</t>
+  </si>
+  <si>
+    <t>134301175</t>
+  </si>
+  <si>
+    <t>134302099</t>
+  </si>
+  <si>
+    <t>134302254</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C203"/>
+  <dimension ref="A1:C208"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3295,8 +3310,63 @@
         <v>4</v>
       </c>
     </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C203" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4858E2-9D69-4F34-A9E9-45BDC6787084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1429D7-B1D3-48B0-B26F-76E85D8ECBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="343">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,625 +45,1018 @@
     <t>.</t>
   </si>
   <si>
-    <t>129551118</t>
-  </si>
-  <si>
-    <t>129589860</t>
-  </si>
-  <si>
-    <t>130000505</t>
-  </si>
-  <si>
-    <t>130086787</t>
-  </si>
-  <si>
-    <t>130104207</t>
-  </si>
-  <si>
-    <t>130568697</t>
-  </si>
-  <si>
-    <t>130638485</t>
-  </si>
-  <si>
-    <t>130906729</t>
-  </si>
-  <si>
-    <t>131031574</t>
-  </si>
-  <si>
-    <t>131513808</t>
-  </si>
-  <si>
-    <t>132143955</t>
-  </si>
-  <si>
-    <t>132594332</t>
-  </si>
-  <si>
-    <t>133027143</t>
-  </si>
-  <si>
-    <t>133039439</t>
-  </si>
-  <si>
-    <t>133886402</t>
-  </si>
-  <si>
-    <t>133983147</t>
-  </si>
-  <si>
-    <t>134125164</t>
-  </si>
-  <si>
-    <t>134279756</t>
-  </si>
-  <si>
-    <t>134279849</t>
-  </si>
-  <si>
-    <t>134279975</t>
-  </si>
-  <si>
-    <t>134280002</t>
-  </si>
-  <si>
-    <t>134280023</t>
-  </si>
-  <si>
-    <t>134280083</t>
-  </si>
-  <si>
-    <t>134280176</t>
-  </si>
-  <si>
-    <t>134280248</t>
-  </si>
-  <si>
-    <t>134280255</t>
-  </si>
-  <si>
-    <t>134280268</t>
-  </si>
-  <si>
-    <t>134280535</t>
-  </si>
-  <si>
-    <t>134280562</t>
-  </si>
-  <si>
-    <t>134280566</t>
-  </si>
-  <si>
-    <t>134280660</t>
-  </si>
-  <si>
-    <t>134280690</t>
-  </si>
-  <si>
-    <t>134280760</t>
-  </si>
-  <si>
-    <t>134280897</t>
-  </si>
-  <si>
-    <t>134280914</t>
-  </si>
-  <si>
-    <t>134280961</t>
-  </si>
-  <si>
-    <t>134280971</t>
-  </si>
-  <si>
-    <t>134281009</t>
-  </si>
-  <si>
-    <t>134281300</t>
-  </si>
-  <si>
-    <t>134281320</t>
-  </si>
-  <si>
-    <t>134281326</t>
-  </si>
-  <si>
-    <t>134281404</t>
-  </si>
-  <si>
-    <t>134281469</t>
-  </si>
-  <si>
-    <t>134281580</t>
-  </si>
-  <si>
-    <t>134281740</t>
-  </si>
-  <si>
-    <t>134281952</t>
-  </si>
-  <si>
-    <t>134282142</t>
-  </si>
-  <si>
-    <t>134282439</t>
-  </si>
-  <si>
-    <t>134282565</t>
-  </si>
-  <si>
-    <t>134282645</t>
-  </si>
-  <si>
-    <t>134282816</t>
-  </si>
-  <si>
-    <t>134282910</t>
-  </si>
-  <si>
-    <t>134283083</t>
-  </si>
-  <si>
-    <t>134283115</t>
-  </si>
-  <si>
-    <t>134283318</t>
-  </si>
-  <si>
-    <t>134283326</t>
-  </si>
-  <si>
-    <t>134283727</t>
-  </si>
-  <si>
-    <t>134283796</t>
-  </si>
-  <si>
-    <t>134283843</t>
-  </si>
-  <si>
-    <t>134283897</t>
-  </si>
-  <si>
-    <t>134284167</t>
-  </si>
-  <si>
-    <t>134284194</t>
-  </si>
-  <si>
-    <t>134284285</t>
-  </si>
-  <si>
-    <t>134284321</t>
-  </si>
-  <si>
-    <t>134284445</t>
-  </si>
-  <si>
-    <t>134284477</t>
-  </si>
-  <si>
-    <t>134284618</t>
-  </si>
-  <si>
-    <t>134284680</t>
-  </si>
-  <si>
-    <t>134284919</t>
-  </si>
-  <si>
-    <t>134284997</t>
-  </si>
-  <si>
-    <t>134285027</t>
-  </si>
-  <si>
-    <t>134285062</t>
-  </si>
-  <si>
-    <t>134285248</t>
-  </si>
-  <si>
-    <t>134285690</t>
-  </si>
-  <si>
-    <t>134285882</t>
-  </si>
-  <si>
-    <t>134286106</t>
-  </si>
-  <si>
-    <t>134286447</t>
-  </si>
-  <si>
-    <t>134286507</t>
-  </si>
-  <si>
-    <t>134286515</t>
-  </si>
-  <si>
-    <t>134286811</t>
-  </si>
-  <si>
-    <t>134286843</t>
-  </si>
-  <si>
-    <t>134286893</t>
-  </si>
-  <si>
-    <t>134286913</t>
-  </si>
-  <si>
-    <t>134287055</t>
-  </si>
-  <si>
-    <t>134287574</t>
-  </si>
-  <si>
-    <t>134287619</t>
-  </si>
-  <si>
-    <t>134287636</t>
-  </si>
-  <si>
-    <t>134287724</t>
-  </si>
-  <si>
-    <t>134287772</t>
-  </si>
-  <si>
-    <t>134287831</t>
-  </si>
-  <si>
-    <t>134287832</t>
-  </si>
-  <si>
-    <t>134287890</t>
-  </si>
-  <si>
-    <t>134287909</t>
-  </si>
-  <si>
-    <t>134288011</t>
-  </si>
-  <si>
-    <t>134288224</t>
-  </si>
-  <si>
-    <t>134288387</t>
-  </si>
-  <si>
-    <t>134288429</t>
-  </si>
-  <si>
-    <t>134288479</t>
-  </si>
-  <si>
-    <t>134288561</t>
-  </si>
-  <si>
-    <t>134288728</t>
-  </si>
-  <si>
-    <t>134288883</t>
-  </si>
-  <si>
-    <t>134288907</t>
-  </si>
-  <si>
-    <t>134288908</t>
-  </si>
-  <si>
-    <t>134288972</t>
-  </si>
-  <si>
-    <t>134289096</t>
-  </si>
-  <si>
-    <t>134289173</t>
-  </si>
-  <si>
-    <t>134289192</t>
-  </si>
-  <si>
-    <t>134289194</t>
-  </si>
-  <si>
-    <t>134289266</t>
-  </si>
-  <si>
-    <t>134289481</t>
-  </si>
-  <si>
-    <t>134289489</t>
-  </si>
-  <si>
-    <t>134289493</t>
-  </si>
-  <si>
-    <t>134289691</t>
-  </si>
-  <si>
-    <t>134289791</t>
-  </si>
-  <si>
-    <t>134289895</t>
-  </si>
-  <si>
-    <t>134289926</t>
-  </si>
-  <si>
-    <t>134290101</t>
-  </si>
-  <si>
-    <t>134290271</t>
-  </si>
-  <si>
-    <t>134290502</t>
-  </si>
-  <si>
-    <t>134290898</t>
-  </si>
-  <si>
-    <t>134290941</t>
-  </si>
-  <si>
-    <t>134291065</t>
-  </si>
-  <si>
-    <t>134291640</t>
-  </si>
-  <si>
-    <t>134291732</t>
-  </si>
-  <si>
-    <t>134291770</t>
-  </si>
-  <si>
-    <t>134292031</t>
-  </si>
-  <si>
-    <t>134292267</t>
-  </si>
-  <si>
-    <t>134292307</t>
-  </si>
-  <si>
-    <t>134292594</t>
-  </si>
-  <si>
-    <t>134292626</t>
-  </si>
-  <si>
-    <t>134292632</t>
-  </si>
-  <si>
-    <t>134292762</t>
-  </si>
-  <si>
-    <t>134292787</t>
-  </si>
-  <si>
-    <t>134292888</t>
-  </si>
-  <si>
-    <t>134293154</t>
-  </si>
-  <si>
-    <t>134293260</t>
-  </si>
-  <si>
-    <t>134293418</t>
-  </si>
-  <si>
-    <t>134293455</t>
-  </si>
-  <si>
-    <t>134293604</t>
-  </si>
-  <si>
-    <t>134293663</t>
-  </si>
-  <si>
-    <t>134293702</t>
-  </si>
-  <si>
-    <t>134293745</t>
-  </si>
-  <si>
-    <t>134293848</t>
-  </si>
-  <si>
-    <t>134293849</t>
-  </si>
-  <si>
-    <t>134294082</t>
-  </si>
-  <si>
-    <t>134294235</t>
-  </si>
-  <si>
-    <t>134294489</t>
-  </si>
-  <si>
-    <t>134294584</t>
-  </si>
-  <si>
-    <t>134294591</t>
-  </si>
-  <si>
-    <t>134294738</t>
-  </si>
-  <si>
-    <t>134294748</t>
-  </si>
-  <si>
-    <t>134294832</t>
-  </si>
-  <si>
-    <t>134295175</t>
-  </si>
-  <si>
-    <t>134295854</t>
-  </si>
-  <si>
-    <t>134295908</t>
-  </si>
-  <si>
-    <t>134295972</t>
-  </si>
-  <si>
-    <t>134296056</t>
-  </si>
-  <si>
-    <t>134296242</t>
-  </si>
-  <si>
-    <t>134296724</t>
-  </si>
-  <si>
-    <t>134296780</t>
-  </si>
-  <si>
-    <t>134296882</t>
-  </si>
-  <si>
-    <t>134296888</t>
-  </si>
-  <si>
-    <t>134296902</t>
-  </si>
-  <si>
-    <t>134296981</t>
-  </si>
-  <si>
-    <t>134296983</t>
-  </si>
-  <si>
-    <t>134297066</t>
-  </si>
-  <si>
-    <t>134297096</t>
-  </si>
-  <si>
-    <t>134297217</t>
-  </si>
-  <si>
-    <t>134297501</t>
-  </si>
-  <si>
-    <t>134297592</t>
-  </si>
-  <si>
-    <t>134297625</t>
-  </si>
-  <si>
-    <t>134297773</t>
-  </si>
-  <si>
-    <t>134297869</t>
-  </si>
-  <si>
-    <t>134297951</t>
-  </si>
-  <si>
-    <t>134297999</t>
-  </si>
-  <si>
-    <t>134298042</t>
-  </si>
-  <si>
-    <t>134298082</t>
-  </si>
-  <si>
-    <t>134298144</t>
-  </si>
-  <si>
-    <t>134298165</t>
-  </si>
-  <si>
-    <t>134298168</t>
-  </si>
-  <si>
-    <t>134298360</t>
-  </si>
-  <si>
-    <t>134298396</t>
-  </si>
-  <si>
-    <t>134298443</t>
-  </si>
-  <si>
-    <t>134298444</t>
-  </si>
-  <si>
-    <t>134298521</t>
-  </si>
-  <si>
-    <t>134298732</t>
-  </si>
-  <si>
-    <t>134298749</t>
-  </si>
-  <si>
-    <t>134298936</t>
-  </si>
-  <si>
-    <t>134298986</t>
-  </si>
-  <si>
-    <t>134299012</t>
-  </si>
-  <si>
-    <t>134299074</t>
-  </si>
-  <si>
-    <t>134299102</t>
-  </si>
-  <si>
-    <t>134299203</t>
-  </si>
-  <si>
-    <t>134299333</t>
-  </si>
-  <si>
-    <t>134299506</t>
-  </si>
-  <si>
-    <t>134299610</t>
-  </si>
-  <si>
-    <t>134299666</t>
-  </si>
-  <si>
-    <t>134299822</t>
-  </si>
-  <si>
-    <t>134300008</t>
-  </si>
-  <si>
-    <t>134300093</t>
-  </si>
-  <si>
-    <t>134300111</t>
-  </si>
-  <si>
-    <t>134300209</t>
-  </si>
-  <si>
-    <t>134300789</t>
-  </si>
-  <si>
-    <t>134300951</t>
-  </si>
-  <si>
-    <t>134301175</t>
-  </si>
-  <si>
-    <t>134302099</t>
-  </si>
-  <si>
-    <t>134302254</t>
+    <t>129336516</t>
+  </si>
+  <si>
+    <t>129603445</t>
+  </si>
+  <si>
+    <t>129808260</t>
+  </si>
+  <si>
+    <t>129851345</t>
+  </si>
+  <si>
+    <t>129999408</t>
+  </si>
+  <si>
+    <t>130001866</t>
+  </si>
+  <si>
+    <t>130076020</t>
+  </si>
+  <si>
+    <t>130208262</t>
+  </si>
+  <si>
+    <t>130328967</t>
+  </si>
+  <si>
+    <t>130507834</t>
+  </si>
+  <si>
+    <t>130565732</t>
+  </si>
+  <si>
+    <t>131042353</t>
+  </si>
+  <si>
+    <t>131050273</t>
+  </si>
+  <si>
+    <t>131484365</t>
+  </si>
+  <si>
+    <t>131585392</t>
+  </si>
+  <si>
+    <t>131735440</t>
+  </si>
+  <si>
+    <t>131853654</t>
+  </si>
+  <si>
+    <t>131878282</t>
+  </si>
+  <si>
+    <t>132066400</t>
+  </si>
+  <si>
+    <t>132112028</t>
+  </si>
+  <si>
+    <t>132410794</t>
+  </si>
+  <si>
+    <t>132483104</t>
+  </si>
+  <si>
+    <t>132686493</t>
+  </si>
+  <si>
+    <t>132767120</t>
+  </si>
+  <si>
+    <t>132819065</t>
+  </si>
+  <si>
+    <t>132878294</t>
+  </si>
+  <si>
+    <t>132948298</t>
+  </si>
+  <si>
+    <t>132977418</t>
+  </si>
+  <si>
+    <t>133066678</t>
+  </si>
+  <si>
+    <t>133114941</t>
+  </si>
+  <si>
+    <t>133197954</t>
+  </si>
+  <si>
+    <t>133245760</t>
+  </si>
+  <si>
+    <t>133280809</t>
+  </si>
+  <si>
+    <t>133394297</t>
+  </si>
+  <si>
+    <t>133502403</t>
+  </si>
+  <si>
+    <t>133519136</t>
+  </si>
+  <si>
+    <t>133675202</t>
+  </si>
+  <si>
+    <t>133780926</t>
+  </si>
+  <si>
+    <t>133922751</t>
+  </si>
+  <si>
+    <t>133952377</t>
+  </si>
+  <si>
+    <t>134085225</t>
+  </si>
+  <si>
+    <t>134284134</t>
+  </si>
+  <si>
+    <t>134302355</t>
+  </si>
+  <si>
+    <t>134302483</t>
+  </si>
+  <si>
+    <t>134302593</t>
+  </si>
+  <si>
+    <t>134302701</t>
+  </si>
+  <si>
+    <t>134302848</t>
+  </si>
+  <si>
+    <t>134303218</t>
+  </si>
+  <si>
+    <t>134303290</t>
+  </si>
+  <si>
+    <t>134303291</t>
+  </si>
+  <si>
+    <t>134303298</t>
+  </si>
+  <si>
+    <t>134303395</t>
+  </si>
+  <si>
+    <t>134303428</t>
+  </si>
+  <si>
+    <t>134303542</t>
+  </si>
+  <si>
+    <t>134303575</t>
+  </si>
+  <si>
+    <t>134303739</t>
+  </si>
+  <si>
+    <t>134303742</t>
+  </si>
+  <si>
+    <t>134303784</t>
+  </si>
+  <si>
+    <t>134303800</t>
+  </si>
+  <si>
+    <t>134303877</t>
+  </si>
+  <si>
+    <t>134303918</t>
+  </si>
+  <si>
+    <t>134303978</t>
+  </si>
+  <si>
+    <t>134304093</t>
+  </si>
+  <si>
+    <t>134304127</t>
+  </si>
+  <si>
+    <t>134304284</t>
+  </si>
+  <si>
+    <t>134304584</t>
+  </si>
+  <si>
+    <t>134304665</t>
+  </si>
+  <si>
+    <t>134304725</t>
+  </si>
+  <si>
+    <t>134304923</t>
+  </si>
+  <si>
+    <t>134305125</t>
+  </si>
+  <si>
+    <t>134305155</t>
+  </si>
+  <si>
+    <t>134305157</t>
+  </si>
+  <si>
+    <t>134305170</t>
+  </si>
+  <si>
+    <t>134305200</t>
+  </si>
+  <si>
+    <t>134305201</t>
+  </si>
+  <si>
+    <t>134305224</t>
+  </si>
+  <si>
+    <t>134305346</t>
+  </si>
+  <si>
+    <t>134305362</t>
+  </si>
+  <si>
+    <t>134305587</t>
+  </si>
+  <si>
+    <t>134305637</t>
+  </si>
+  <si>
+    <t>134305758</t>
+  </si>
+  <si>
+    <t>134305800</t>
+  </si>
+  <si>
+    <t>134305807</t>
+  </si>
+  <si>
+    <t>134306124</t>
+  </si>
+  <si>
+    <t>134306141</t>
+  </si>
+  <si>
+    <t>134306327</t>
+  </si>
+  <si>
+    <t>134306426</t>
+  </si>
+  <si>
+    <t>134306510</t>
+  </si>
+  <si>
+    <t>134306592</t>
+  </si>
+  <si>
+    <t>134306808</t>
+  </si>
+  <si>
+    <t>134306919</t>
+  </si>
+  <si>
+    <t>134307039</t>
+  </si>
+  <si>
+    <t>134307198</t>
+  </si>
+  <si>
+    <t>134307439</t>
+  </si>
+  <si>
+    <t>134307896</t>
+  </si>
+  <si>
+    <t>134307986</t>
+  </si>
+  <si>
+    <t>134308110</t>
+  </si>
+  <si>
+    <t>134308112</t>
+  </si>
+  <si>
+    <t>134308199</t>
+  </si>
+  <si>
+    <t>134308236</t>
+  </si>
+  <si>
+    <t>134308534</t>
+  </si>
+  <si>
+    <t>134308612</t>
+  </si>
+  <si>
+    <t>134308712</t>
+  </si>
+  <si>
+    <t>134308881</t>
+  </si>
+  <si>
+    <t>134308933</t>
+  </si>
+  <si>
+    <t>134309004</t>
+  </si>
+  <si>
+    <t>134309184</t>
+  </si>
+  <si>
+    <t>134309187</t>
+  </si>
+  <si>
+    <t>134309269</t>
+  </si>
+  <si>
+    <t>134309436</t>
+  </si>
+  <si>
+    <t>134309485</t>
+  </si>
+  <si>
+    <t>134309536</t>
+  </si>
+  <si>
+    <t>134309591</t>
+  </si>
+  <si>
+    <t>134309655</t>
+  </si>
+  <si>
+    <t>134309786</t>
+  </si>
+  <si>
+    <t>134309802</t>
+  </si>
+  <si>
+    <t>134309964</t>
+  </si>
+  <si>
+    <t>134310263</t>
+  </si>
+  <si>
+    <t>134310339</t>
+  </si>
+  <si>
+    <t>134310397</t>
+  </si>
+  <si>
+    <t>134310407</t>
+  </si>
+  <si>
+    <t>134310782</t>
+  </si>
+  <si>
+    <t>134310783</t>
+  </si>
+  <si>
+    <t>134310846</t>
+  </si>
+  <si>
+    <t>134310849</t>
+  </si>
+  <si>
+    <t>134310868</t>
+  </si>
+  <si>
+    <t>134310887</t>
+  </si>
+  <si>
+    <t>134311056</t>
+  </si>
+  <si>
+    <t>134311361</t>
+  </si>
+  <si>
+    <t>134311376</t>
+  </si>
+  <si>
+    <t>134311503</t>
+  </si>
+  <si>
+    <t>134311510</t>
+  </si>
+  <si>
+    <t>134311587</t>
+  </si>
+  <si>
+    <t>134311595</t>
+  </si>
+  <si>
+    <t>134311626</t>
+  </si>
+  <si>
+    <t>134311693</t>
+  </si>
+  <si>
+    <t>134311755</t>
+  </si>
+  <si>
+    <t>134311873</t>
+  </si>
+  <si>
+    <t>134311938</t>
+  </si>
+  <si>
+    <t>134311991</t>
+  </si>
+  <si>
+    <t>134312157</t>
+  </si>
+  <si>
+    <t>134312471</t>
+  </si>
+  <si>
+    <t>134312499</t>
+  </si>
+  <si>
+    <t>134312614</t>
+  </si>
+  <si>
+    <t>134312828</t>
+  </si>
+  <si>
+    <t>134312994</t>
+  </si>
+  <si>
+    <t>134313071</t>
+  </si>
+  <si>
+    <t>134313232</t>
+  </si>
+  <si>
+    <t>134313349</t>
+  </si>
+  <si>
+    <t>134313427</t>
+  </si>
+  <si>
+    <t>134313472</t>
+  </si>
+  <si>
+    <t>134313587</t>
+  </si>
+  <si>
+    <t>134313615</t>
+  </si>
+  <si>
+    <t>134313674</t>
+  </si>
+  <si>
+    <t>134313695</t>
+  </si>
+  <si>
+    <t>134313740</t>
+  </si>
+  <si>
+    <t>134313845</t>
+  </si>
+  <si>
+    <t>134313850</t>
+  </si>
+  <si>
+    <t>134313865</t>
+  </si>
+  <si>
+    <t>134313939</t>
+  </si>
+  <si>
+    <t>134314025</t>
+  </si>
+  <si>
+    <t>134314259</t>
+  </si>
+  <si>
+    <t>134314267</t>
+  </si>
+  <si>
+    <t>134314292</t>
+  </si>
+  <si>
+    <t>134314303</t>
+  </si>
+  <si>
+    <t>134314607</t>
+  </si>
+  <si>
+    <t>134314615</t>
+  </si>
+  <si>
+    <t>134314777</t>
+  </si>
+  <si>
+    <t>134314790</t>
+  </si>
+  <si>
+    <t>134314836</t>
+  </si>
+  <si>
+    <t>134314901</t>
+  </si>
+  <si>
+    <t>134314994</t>
+  </si>
+  <si>
+    <t>134315041</t>
+  </si>
+  <si>
+    <t>134315169</t>
+  </si>
+  <si>
+    <t>134315171</t>
+  </si>
+  <si>
+    <t>134315318</t>
+  </si>
+  <si>
+    <t>134315383</t>
+  </si>
+  <si>
+    <t>134315551</t>
+  </si>
+  <si>
+    <t>134315619</t>
+  </si>
+  <si>
+    <t>134315664</t>
+  </si>
+  <si>
+    <t>134315824</t>
+  </si>
+  <si>
+    <t>134316030</t>
+  </si>
+  <si>
+    <t>134316037</t>
+  </si>
+  <si>
+    <t>134316062</t>
+  </si>
+  <si>
+    <t>134316167</t>
+  </si>
+  <si>
+    <t>134316269</t>
+  </si>
+  <si>
+    <t>134316819</t>
+  </si>
+  <si>
+    <t>134317018</t>
+  </si>
+  <si>
+    <t>134317031</t>
+  </si>
+  <si>
+    <t>134317066</t>
+  </si>
+  <si>
+    <t>134317121</t>
+  </si>
+  <si>
+    <t>134317223</t>
+  </si>
+  <si>
+    <t>134317254</t>
+  </si>
+  <si>
+    <t>134317330</t>
+  </si>
+  <si>
+    <t>134317364</t>
+  </si>
+  <si>
+    <t>134317441</t>
+  </si>
+  <si>
+    <t>134317506</t>
+  </si>
+  <si>
+    <t>134317561</t>
+  </si>
+  <si>
+    <t>134317644</t>
+  </si>
+  <si>
+    <t>134317715</t>
+  </si>
+  <si>
+    <t>134317785</t>
+  </si>
+  <si>
+    <t>134317811</t>
+  </si>
+  <si>
+    <t>134317859</t>
+  </si>
+  <si>
+    <t>134317885</t>
+  </si>
+  <si>
+    <t>134318033</t>
+  </si>
+  <si>
+    <t>134318147</t>
+  </si>
+  <si>
+    <t>134318202</t>
+  </si>
+  <si>
+    <t>134318241</t>
+  </si>
+  <si>
+    <t>134318382</t>
+  </si>
+  <si>
+    <t>134318437</t>
+  </si>
+  <si>
+    <t>134318576</t>
+  </si>
+  <si>
+    <t>134318616</t>
+  </si>
+  <si>
+    <t>134318617</t>
+  </si>
+  <si>
+    <t>134318630</t>
+  </si>
+  <si>
+    <t>134318638</t>
+  </si>
+  <si>
+    <t>134318755</t>
+  </si>
+  <si>
+    <t>134318813</t>
+  </si>
+  <si>
+    <t>134318850</t>
+  </si>
+  <si>
+    <t>134318945</t>
+  </si>
+  <si>
+    <t>134319024</t>
+  </si>
+  <si>
+    <t>134319055</t>
+  </si>
+  <si>
+    <t>134319058</t>
+  </si>
+  <si>
+    <t>134319069</t>
+  </si>
+  <si>
+    <t>134319091</t>
+  </si>
+  <si>
+    <t>134319108</t>
+  </si>
+  <si>
+    <t>134319172</t>
+  </si>
+  <si>
+    <t>134319361</t>
+  </si>
+  <si>
+    <t>134319501</t>
+  </si>
+  <si>
+    <t>134319648</t>
+  </si>
+  <si>
+    <t>134319676</t>
+  </si>
+  <si>
+    <t>134319723</t>
+  </si>
+  <si>
+    <t>134320064</t>
+  </si>
+  <si>
+    <t>134320120</t>
+  </si>
+  <si>
+    <t>134320197</t>
+  </si>
+  <si>
+    <t>134320284</t>
+  </si>
+  <si>
+    <t>134320304</t>
+  </si>
+  <si>
+    <t>134320354</t>
+  </si>
+  <si>
+    <t>134320435</t>
+  </si>
+  <si>
+    <t>134320531</t>
+  </si>
+  <si>
+    <t>134320534</t>
+  </si>
+  <si>
+    <t>134320545</t>
+  </si>
+  <si>
+    <t>134320554</t>
+  </si>
+  <si>
+    <t>134320879</t>
+  </si>
+  <si>
+    <t>134320964</t>
+  </si>
+  <si>
+    <t>134320973</t>
+  </si>
+  <si>
+    <t>134320981</t>
+  </si>
+  <si>
+    <t>134321004</t>
+  </si>
+  <si>
+    <t>134321079</t>
+  </si>
+  <si>
+    <t>134321149</t>
+  </si>
+  <si>
+    <t>134321264</t>
+  </si>
+  <si>
+    <t>134321301</t>
+  </si>
+  <si>
+    <t>134321350</t>
+  </si>
+  <si>
+    <t>134321351</t>
+  </si>
+  <si>
+    <t>134321805</t>
+  </si>
+  <si>
+    <t>134321829</t>
+  </si>
+  <si>
+    <t>134321853</t>
+  </si>
+  <si>
+    <t>134321869</t>
+  </si>
+  <si>
+    <t>134321897</t>
+  </si>
+  <si>
+    <t>134321919</t>
+  </si>
+  <si>
+    <t>134321943</t>
+  </si>
+  <si>
+    <t>134321971</t>
+  </si>
+  <si>
+    <t>134322013</t>
+  </si>
+  <si>
+    <t>134322065</t>
+  </si>
+  <si>
+    <t>134322090</t>
+  </si>
+  <si>
+    <t>134322106</t>
+  </si>
+  <si>
+    <t>134322361</t>
+  </si>
+  <si>
+    <t>134322390</t>
+  </si>
+  <si>
+    <t>134322415</t>
+  </si>
+  <si>
+    <t>134322494</t>
+  </si>
+  <si>
+    <t>134322591</t>
+  </si>
+  <si>
+    <t>134322664</t>
+  </si>
+  <si>
+    <t>134322682</t>
+  </si>
+  <si>
+    <t>134322725</t>
+  </si>
+  <si>
+    <t>134322753</t>
+  </si>
+  <si>
+    <t>134322760</t>
+  </si>
+  <si>
+    <t>134322819</t>
+  </si>
+  <si>
+    <t>134322833</t>
+  </si>
+  <si>
+    <t>134322875</t>
+  </si>
+  <si>
+    <t>134322969</t>
+  </si>
+  <si>
+    <t>134323144</t>
+  </si>
+  <si>
+    <t>134323327</t>
+  </si>
+  <si>
+    <t>134323397</t>
+  </si>
+  <si>
+    <t>134323418</t>
+  </si>
+  <si>
+    <t>134323433</t>
+  </si>
+  <si>
+    <t>134323456</t>
+  </si>
+  <si>
+    <t>134323518</t>
+  </si>
+  <si>
+    <t>134323546</t>
+  </si>
+  <si>
+    <t>134323556</t>
+  </si>
+  <si>
+    <t>134323647</t>
+  </si>
+  <si>
+    <t>134323675</t>
+  </si>
+  <si>
+    <t>134323747</t>
+  </si>
+  <si>
+    <t>134323761</t>
+  </si>
+  <si>
+    <t>134324327</t>
+  </si>
+  <si>
+    <t>134324495</t>
+  </si>
+  <si>
+    <t>134324499</t>
+  </si>
+  <si>
+    <t>134324573</t>
+  </si>
+  <si>
+    <t>134325031</t>
+  </si>
+  <si>
+    <t>134325142</t>
+  </si>
+  <si>
+    <t>134325439</t>
+  </si>
+  <si>
+    <t>134325535</t>
+  </si>
+  <si>
+    <t>134325611</t>
+  </si>
+  <si>
+    <t>134325779</t>
+  </si>
+  <si>
+    <t>134325785</t>
+  </si>
+  <si>
+    <t>134325800</t>
+  </si>
+  <si>
+    <t>134325824</t>
+  </si>
+  <si>
+    <t>134325846</t>
+  </si>
+  <si>
+    <t>134325852</t>
+  </si>
+  <si>
+    <t>134325899</t>
+  </si>
+  <si>
+    <t>134325947</t>
+  </si>
+  <si>
+    <t>134325955</t>
+  </si>
+  <si>
+    <t>134325963</t>
+  </si>
+  <si>
+    <t>134326122</t>
+  </si>
+  <si>
+    <t>134326151</t>
+  </si>
+  <si>
+    <t>134326183</t>
+  </si>
+  <si>
+    <t>134326216</t>
+  </si>
+  <si>
+    <t>134326262</t>
+  </si>
+  <si>
+    <t>134326442</t>
+  </si>
+  <si>
+    <t>134326474</t>
+  </si>
+  <si>
+    <t>134326507</t>
+  </si>
+  <si>
+    <t>134326517</t>
+  </si>
+  <si>
+    <t>134326558</t>
+  </si>
+  <si>
+    <t>134326677</t>
+  </si>
+  <si>
+    <t>134326686</t>
+  </si>
+  <si>
+    <t>134326790</t>
+  </si>
+  <si>
+    <t>134326827</t>
+  </si>
+  <si>
+    <t>134327035</t>
+  </si>
+  <si>
+    <t>134327058</t>
+  </si>
+  <si>
+    <t>134327170</t>
+  </si>
+  <si>
+    <t>134327210</t>
+  </si>
+  <si>
+    <t>134327404</t>
+  </si>
+  <si>
+    <t>134327464</t>
+  </si>
+  <si>
+    <t>134327658</t>
+  </si>
+  <si>
+    <t>134327686</t>
+  </si>
+  <si>
+    <t>134327693</t>
+  </si>
+  <si>
+    <t>134327755</t>
+  </si>
+  <si>
+    <t>134327887</t>
+  </si>
+  <si>
+    <t>134327988</t>
+  </si>
+  <si>
+    <t>134328433</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C208"/>
+  <dimension ref="A1:C339"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3365,6 +3758,1429 @@
         <v>4</v>
       </c>
     </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8796FB-8D23-46F6-8EBC-7E3B236C01D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADA59C3-D141-4FAC-9B3A-A33EE28FB814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="259">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,628 +45,766 @@
     <t>.</t>
   </si>
   <si>
-    <t>130056514</t>
-  </si>
-  <si>
-    <t>130423275</t>
-  </si>
-  <si>
-    <t>130766198</t>
-  </si>
-  <si>
-    <t>130872171</t>
-  </si>
-  <si>
-    <t>130980129</t>
-  </si>
-  <si>
-    <t>131067864</t>
-  </si>
-  <si>
-    <t>131290629</t>
-  </si>
-  <si>
-    <t>131398393</t>
-  </si>
-  <si>
-    <t>131743694</t>
-  </si>
-  <si>
-    <t>131786558</t>
-  </si>
-  <si>
-    <t>131809525</t>
-  </si>
-  <si>
-    <t>132013412</t>
-  </si>
-  <si>
-    <t>132293302</t>
-  </si>
-  <si>
-    <t>132347110</t>
-  </si>
-  <si>
-    <t>132498414</t>
-  </si>
-  <si>
-    <t>132842786</t>
-  </si>
-  <si>
-    <t>132856012</t>
-  </si>
-  <si>
-    <t>132882574</t>
-  </si>
-  <si>
-    <t>133024483</t>
-  </si>
-  <si>
-    <t>133777761</t>
-  </si>
-  <si>
-    <t>134120071</t>
-  </si>
-  <si>
-    <t>134329037</t>
-  </si>
-  <si>
-    <t>134329083</t>
-  </si>
-  <si>
-    <t>134329286</t>
-  </si>
-  <si>
-    <t>134329362</t>
-  </si>
-  <si>
-    <t>134329395</t>
-  </si>
-  <si>
-    <t>134329512</t>
-  </si>
-  <si>
-    <t>134329853</t>
-  </si>
-  <si>
-    <t>134330007</t>
-  </si>
-  <si>
-    <t>134330019</t>
-  </si>
-  <si>
-    <t>134330051</t>
-  </si>
-  <si>
-    <t>134330080</t>
-  </si>
-  <si>
-    <t>134330299</t>
-  </si>
-  <si>
-    <t>134330424</t>
-  </si>
-  <si>
-    <t>134330615</t>
-  </si>
-  <si>
-    <t>134330660</t>
-  </si>
-  <si>
-    <t>134330700</t>
-  </si>
-  <si>
-    <t>134330711</t>
-  </si>
-  <si>
-    <t>134331324</t>
-  </si>
-  <si>
-    <t>134331355</t>
-  </si>
-  <si>
-    <t>134331365</t>
-  </si>
-  <si>
-    <t>134331436</t>
-  </si>
-  <si>
-    <t>134331732</t>
-  </si>
-  <si>
-    <t>134331788</t>
-  </si>
-  <si>
-    <t>134331976</t>
-  </si>
-  <si>
-    <t>134332077</t>
-  </si>
-  <si>
-    <t>134332135</t>
-  </si>
-  <si>
-    <t>134332386</t>
-  </si>
-  <si>
-    <t>134332403</t>
-  </si>
-  <si>
-    <t>134332453</t>
-  </si>
-  <si>
-    <t>134332506</t>
-  </si>
-  <si>
-    <t>134332532</t>
-  </si>
-  <si>
-    <t>134332570</t>
-  </si>
-  <si>
-    <t>134332669</t>
-  </si>
-  <si>
-    <t>134332797</t>
-  </si>
-  <si>
-    <t>134332859</t>
-  </si>
-  <si>
-    <t>134333015</t>
-  </si>
-  <si>
-    <t>134333024</t>
-  </si>
-  <si>
-    <t>134333028</t>
-  </si>
-  <si>
-    <t>134333090</t>
-  </si>
-  <si>
-    <t>134333345</t>
-  </si>
-  <si>
-    <t>134333587</t>
-  </si>
-  <si>
-    <t>134333613</t>
-  </si>
-  <si>
-    <t>134333678</t>
-  </si>
-  <si>
-    <t>134333717</t>
-  </si>
-  <si>
-    <t>134333758</t>
-  </si>
-  <si>
-    <t>134333805</t>
-  </si>
-  <si>
-    <t>134333847</t>
-  </si>
-  <si>
-    <t>134333895</t>
-  </si>
-  <si>
-    <t>134333955</t>
-  </si>
-  <si>
-    <t>134334089</t>
-  </si>
-  <si>
-    <t>134334099</t>
-  </si>
-  <si>
-    <t>134334347</t>
-  </si>
-  <si>
-    <t>134334507</t>
-  </si>
-  <si>
-    <t>134334594</t>
-  </si>
-  <si>
-    <t>134334598</t>
-  </si>
-  <si>
-    <t>134335158</t>
-  </si>
-  <si>
-    <t>134335169</t>
-  </si>
-  <si>
-    <t>134335280</t>
-  </si>
-  <si>
-    <t>134335332</t>
-  </si>
-  <si>
-    <t>134335351</t>
-  </si>
-  <si>
-    <t>134335445</t>
-  </si>
-  <si>
-    <t>134335514</t>
-  </si>
-  <si>
-    <t>134335631</t>
-  </si>
-  <si>
-    <t>134335688</t>
-  </si>
-  <si>
-    <t>134335809</t>
-  </si>
-  <si>
-    <t>134335868</t>
-  </si>
-  <si>
-    <t>134335959</t>
-  </si>
-  <si>
-    <t>134336125</t>
-  </si>
-  <si>
-    <t>134336157</t>
-  </si>
-  <si>
-    <t>134336181</t>
-  </si>
-  <si>
-    <t>134336197</t>
-  </si>
-  <si>
-    <t>134336364</t>
-  </si>
-  <si>
-    <t>134336379</t>
-  </si>
-  <si>
-    <t>134336419</t>
-  </si>
-  <si>
-    <t>134336539</t>
-  </si>
-  <si>
-    <t>134336602</t>
-  </si>
-  <si>
-    <t>134336668</t>
-  </si>
-  <si>
-    <t>134336735</t>
-  </si>
-  <si>
-    <t>134337086</t>
-  </si>
-  <si>
-    <t>134337098</t>
-  </si>
-  <si>
-    <t>134337399</t>
-  </si>
-  <si>
-    <t>134338259</t>
-  </si>
-  <si>
-    <t>134338264</t>
-  </si>
-  <si>
-    <t>134338630</t>
-  </si>
-  <si>
-    <t>134338642</t>
-  </si>
-  <si>
-    <t>134339175</t>
-  </si>
-  <si>
-    <t>134339367</t>
-  </si>
-  <si>
-    <t>134339411</t>
-  </si>
-  <si>
-    <t>134339584</t>
-  </si>
-  <si>
-    <t>134339815</t>
-  </si>
-  <si>
-    <t>134339881</t>
-  </si>
-  <si>
-    <t>134339902</t>
-  </si>
-  <si>
-    <t>134340054</t>
-  </si>
-  <si>
-    <t>134340118</t>
-  </si>
-  <si>
-    <t>134340119</t>
-  </si>
-  <si>
-    <t>134340148</t>
-  </si>
-  <si>
-    <t>134340296</t>
-  </si>
-  <si>
-    <t>134340297</t>
-  </si>
-  <si>
-    <t>134340335</t>
-  </si>
-  <si>
-    <t>134340394</t>
-  </si>
-  <si>
-    <t>134340585</t>
-  </si>
-  <si>
-    <t>134340821</t>
-  </si>
-  <si>
-    <t>134341085</t>
-  </si>
-  <si>
-    <t>134341183</t>
-  </si>
-  <si>
-    <t>134341263</t>
-  </si>
-  <si>
-    <t>134341499</t>
-  </si>
-  <si>
-    <t>134341589</t>
-  </si>
-  <si>
-    <t>134341611</t>
-  </si>
-  <si>
-    <t>134341840</t>
-  </si>
-  <si>
-    <t>134341871</t>
-  </si>
-  <si>
-    <t>134341895</t>
-  </si>
-  <si>
-    <t>134342334</t>
-  </si>
-  <si>
-    <t>134342382</t>
-  </si>
-  <si>
-    <t>134342475</t>
-  </si>
-  <si>
-    <t>134342486</t>
-  </si>
-  <si>
-    <t>134342701</t>
-  </si>
-  <si>
-    <t>134342752</t>
-  </si>
-  <si>
-    <t>134342955</t>
-  </si>
-  <si>
-    <t>134342973</t>
-  </si>
-  <si>
-    <t>134343342</t>
-  </si>
-  <si>
-    <t>134343347</t>
-  </si>
-  <si>
-    <t>134343358</t>
-  </si>
-  <si>
-    <t>134343374</t>
-  </si>
-  <si>
-    <t>134343728</t>
-  </si>
-  <si>
-    <t>134343739</t>
-  </si>
-  <si>
-    <t>134343758</t>
-  </si>
-  <si>
-    <t>134343770</t>
-  </si>
-  <si>
-    <t>134343828</t>
-  </si>
-  <si>
-    <t>134343909</t>
-  </si>
-  <si>
-    <t>134344017</t>
-  </si>
-  <si>
-    <t>134344018</t>
-  </si>
-  <si>
-    <t>134344108</t>
-  </si>
-  <si>
-    <t>134344138</t>
-  </si>
-  <si>
-    <t>134344526</t>
-  </si>
-  <si>
-    <t>134344528</t>
-  </si>
-  <si>
-    <t>134344554</t>
-  </si>
-  <si>
-    <t>134344876</t>
-  </si>
-  <si>
-    <t>134344963</t>
-  </si>
-  <si>
-    <t>134345246</t>
-  </si>
-  <si>
-    <t>134345466</t>
-  </si>
-  <si>
-    <t>134345481</t>
-  </si>
-  <si>
-    <t>134345489</t>
-  </si>
-  <si>
-    <t>134345497</t>
-  </si>
-  <si>
-    <t>134345519</t>
-  </si>
-  <si>
-    <t>134345529</t>
-  </si>
-  <si>
-    <t>134345650</t>
-  </si>
-  <si>
-    <t>134345745</t>
-  </si>
-  <si>
-    <t>134345802</t>
-  </si>
-  <si>
-    <t>134345838</t>
-  </si>
-  <si>
-    <t>134345901</t>
-  </si>
-  <si>
-    <t>134345930</t>
-  </si>
-  <si>
-    <t>134346112</t>
-  </si>
-  <si>
-    <t>134346355</t>
-  </si>
-  <si>
-    <t>134346359</t>
-  </si>
-  <si>
-    <t>134346455</t>
-  </si>
-  <si>
-    <t>134346553</t>
-  </si>
-  <si>
-    <t>134346630</t>
-  </si>
-  <si>
-    <t>134346670</t>
-  </si>
-  <si>
-    <t>134346692</t>
-  </si>
-  <si>
-    <t>134346700</t>
-  </si>
-  <si>
-    <t>134346754</t>
-  </si>
-  <si>
-    <t>134346768</t>
-  </si>
-  <si>
-    <t>134346802</t>
-  </si>
-  <si>
-    <t>134346840</t>
-  </si>
-  <si>
-    <t>134346858</t>
-  </si>
-  <si>
-    <t>134346871</t>
-  </si>
-  <si>
-    <t>134346907</t>
-  </si>
-  <si>
-    <t>134346914</t>
-  </si>
-  <si>
-    <t>134347100</t>
-  </si>
-  <si>
-    <t>134347144</t>
-  </si>
-  <si>
-    <t>134347230</t>
-  </si>
-  <si>
-    <t>134347242</t>
-  </si>
-  <si>
-    <t>134347359</t>
-  </si>
-  <si>
-    <t>134347375</t>
-  </si>
-  <si>
-    <t>134347405</t>
-  </si>
-  <si>
-    <t>134347478</t>
-  </si>
-  <si>
-    <t>134348009</t>
-  </si>
-  <si>
-    <t>134348099</t>
-  </si>
-  <si>
-    <t>134348368</t>
-  </si>
-  <si>
-    <t>134348646</t>
-  </si>
-  <si>
-    <t>134348866</t>
-  </si>
-  <si>
-    <t>134349257</t>
-  </si>
-  <si>
-    <t>134349314</t>
-  </si>
-  <si>
-    <t>134349445</t>
-  </si>
-  <si>
-    <t>134349465</t>
-  </si>
-  <si>
-    <t>134349535</t>
-  </si>
-  <si>
-    <t>134349536</t>
+    <t>129734695</t>
+  </si>
+  <si>
+    <t>129736922</t>
+  </si>
+  <si>
+    <t>129899738</t>
+  </si>
+  <si>
+    <t>130037183</t>
+  </si>
+  <si>
+    <t>130248016</t>
+  </si>
+  <si>
+    <t>130282600</t>
+  </si>
+  <si>
+    <t>130457650</t>
+  </si>
+  <si>
+    <t>130569739</t>
+  </si>
+  <si>
+    <t>130674338</t>
+  </si>
+  <si>
+    <t>130767718</t>
+  </si>
+  <si>
+    <t>130805562</t>
+  </si>
+  <si>
+    <t>130808132</t>
+  </si>
+  <si>
+    <t>131084902</t>
+  </si>
+  <si>
+    <t>131159429</t>
+  </si>
+  <si>
+    <t>131283053</t>
+  </si>
+  <si>
+    <t>131450066</t>
+  </si>
+  <si>
+    <t>131465789</t>
+  </si>
+  <si>
+    <t>131484346</t>
+  </si>
+  <si>
+    <t>131669074</t>
+  </si>
+  <si>
+    <t>132000459</t>
+  </si>
+  <si>
+    <t>132210108</t>
+  </si>
+  <si>
+    <t>132365210</t>
+  </si>
+  <si>
+    <t>132377990</t>
+  </si>
+  <si>
+    <t>132465678</t>
+  </si>
+  <si>
+    <t>132477849</t>
+  </si>
+  <si>
+    <t>132776262</t>
+  </si>
+  <si>
+    <t>132803557</t>
+  </si>
+  <si>
+    <t>132943478</t>
+  </si>
+  <si>
+    <t>132978979</t>
+  </si>
+  <si>
+    <t>133160042</t>
+  </si>
+  <si>
+    <t>133285103</t>
+  </si>
+  <si>
+    <t>133570861</t>
+  </si>
+  <si>
+    <t>133596623</t>
+  </si>
+  <si>
+    <t>133854520</t>
+  </si>
+  <si>
+    <t>134271114</t>
+  </si>
+  <si>
+    <t>134349559</t>
+  </si>
+  <si>
+    <t>134349601</t>
+  </si>
+  <si>
+    <t>134349675</t>
+  </si>
+  <si>
+    <t>134349725</t>
+  </si>
+  <si>
+    <t>134349822</t>
+  </si>
+  <si>
+    <t>134349889</t>
+  </si>
+  <si>
+    <t>134349890</t>
+  </si>
+  <si>
+    <t>134350188</t>
+  </si>
+  <si>
+    <t>134350225</t>
+  </si>
+  <si>
+    <t>134350451</t>
+  </si>
+  <si>
+    <t>134350570</t>
+  </si>
+  <si>
+    <t>134350768</t>
+  </si>
+  <si>
+    <t>134350787</t>
+  </si>
+  <si>
+    <t>134350839</t>
+  </si>
+  <si>
+    <t>134350857</t>
+  </si>
+  <si>
+    <t>134351107</t>
+  </si>
+  <si>
+    <t>134351117</t>
+  </si>
+  <si>
+    <t>134351393</t>
+  </si>
+  <si>
+    <t>134351497</t>
+  </si>
+  <si>
+    <t>134351712</t>
+  </si>
+  <si>
+    <t>134351738</t>
+  </si>
+  <si>
+    <t>134351827</t>
+  </si>
+  <si>
+    <t>134351853</t>
+  </si>
+  <si>
+    <t>134351886</t>
+  </si>
+  <si>
+    <t>134351933</t>
+  </si>
+  <si>
+    <t>134352249</t>
+  </si>
+  <si>
+    <t>134352292</t>
+  </si>
+  <si>
+    <t>134352346</t>
+  </si>
+  <si>
+    <t>134352386</t>
+  </si>
+  <si>
+    <t>134352419</t>
+  </si>
+  <si>
+    <t>134352581</t>
+  </si>
+  <si>
+    <t>134352587</t>
+  </si>
+  <si>
+    <t>134352609</t>
+  </si>
+  <si>
+    <t>134352798</t>
+  </si>
+  <si>
+    <t>134352833</t>
+  </si>
+  <si>
+    <t>134353721</t>
+  </si>
+  <si>
+    <t>134353841</t>
+  </si>
+  <si>
+    <t>134353962</t>
+  </si>
+  <si>
+    <t>134353987</t>
+  </si>
+  <si>
+    <t>134354206</t>
+  </si>
+  <si>
+    <t>134354255</t>
+  </si>
+  <si>
+    <t>134354512</t>
+  </si>
+  <si>
+    <t>134354776</t>
+  </si>
+  <si>
+    <t>134354813</t>
+  </si>
+  <si>
+    <t>134354899</t>
+  </si>
+  <si>
+    <t>134354902</t>
+  </si>
+  <si>
+    <t>134354910</t>
+  </si>
+  <si>
+    <t>134354931</t>
+  </si>
+  <si>
+    <t>134355029</t>
+  </si>
+  <si>
+    <t>134355231</t>
+  </si>
+  <si>
+    <t>134355390</t>
+  </si>
+  <si>
+    <t>134355524</t>
+  </si>
+  <si>
+    <t>134355551</t>
+  </si>
+  <si>
+    <t>134355628</t>
+  </si>
+  <si>
+    <t>134356009</t>
+  </si>
+  <si>
+    <t>134356069</t>
+  </si>
+  <si>
+    <t>134356223</t>
+  </si>
+  <si>
+    <t>134356353</t>
+  </si>
+  <si>
+    <t>134356386</t>
+  </si>
+  <si>
+    <t>134356463</t>
+  </si>
+  <si>
+    <t>134356565</t>
+  </si>
+  <si>
+    <t>134356588</t>
+  </si>
+  <si>
+    <t>134356607</t>
+  </si>
+  <si>
+    <t>134356723</t>
+  </si>
+  <si>
+    <t>134356725</t>
+  </si>
+  <si>
+    <t>134356807</t>
+  </si>
+  <si>
+    <t>134356829</t>
+  </si>
+  <si>
+    <t>134356844</t>
+  </si>
+  <si>
+    <t>134356941</t>
+  </si>
+  <si>
+    <t>134357181</t>
+  </si>
+  <si>
+    <t>134357390</t>
+  </si>
+  <si>
+    <t>134357397</t>
+  </si>
+  <si>
+    <t>134357442</t>
+  </si>
+  <si>
+    <t>134357591</t>
+  </si>
+  <si>
+    <t>134357731</t>
+  </si>
+  <si>
+    <t>134357842</t>
+  </si>
+  <si>
+    <t>134357856</t>
+  </si>
+  <si>
+    <t>134357867</t>
+  </si>
+  <si>
+    <t>134357895</t>
+  </si>
+  <si>
+    <t>134357937</t>
+  </si>
+  <si>
+    <t>134358119</t>
+  </si>
+  <si>
+    <t>134358204</t>
+  </si>
+  <si>
+    <t>134358258</t>
+  </si>
+  <si>
+    <t>134358289</t>
+  </si>
+  <si>
+    <t>134358361</t>
+  </si>
+  <si>
+    <t>134358381</t>
+  </si>
+  <si>
+    <t>134358422</t>
+  </si>
+  <si>
+    <t>134358432</t>
+  </si>
+  <si>
+    <t>134358437</t>
+  </si>
+  <si>
+    <t>134358662</t>
+  </si>
+  <si>
+    <t>134358668</t>
+  </si>
+  <si>
+    <t>134358722</t>
+  </si>
+  <si>
+    <t>134358794</t>
+  </si>
+  <si>
+    <t>134358827</t>
+  </si>
+  <si>
+    <t>134358865</t>
+  </si>
+  <si>
+    <t>134358917</t>
+  </si>
+  <si>
+    <t>134358986</t>
+  </si>
+  <si>
+    <t>134359262</t>
+  </si>
+  <si>
+    <t>134359272</t>
+  </si>
+  <si>
+    <t>134359345</t>
+  </si>
+  <si>
+    <t>134359458</t>
+  </si>
+  <si>
+    <t>134359478</t>
+  </si>
+  <si>
+    <t>134359484</t>
+  </si>
+  <si>
+    <t>134359554</t>
+  </si>
+  <si>
+    <t>134359588</t>
+  </si>
+  <si>
+    <t>134359699</t>
+  </si>
+  <si>
+    <t>134359713</t>
+  </si>
+  <si>
+    <t>134359924</t>
+  </si>
+  <si>
+    <t>134360389</t>
+  </si>
+  <si>
+    <t>134360711</t>
+  </si>
+  <si>
+    <t>134360734</t>
+  </si>
+  <si>
+    <t>134360765</t>
+  </si>
+  <si>
+    <t>134360844</t>
+  </si>
+  <si>
+    <t>134360874</t>
+  </si>
+  <si>
+    <t>134360876</t>
+  </si>
+  <si>
+    <t>134360919</t>
+  </si>
+  <si>
+    <t>134360923</t>
+  </si>
+  <si>
+    <t>134361141</t>
+  </si>
+  <si>
+    <t>134361266</t>
+  </si>
+  <si>
+    <t>134361299</t>
+  </si>
+  <si>
+    <t>134361380</t>
+  </si>
+  <si>
+    <t>134361383</t>
+  </si>
+  <si>
+    <t>134361527</t>
+  </si>
+  <si>
+    <t>134361558</t>
+  </si>
+  <si>
+    <t>134361588</t>
+  </si>
+  <si>
+    <t>134361630</t>
+  </si>
+  <si>
+    <t>134362040</t>
+  </si>
+  <si>
+    <t>134362061</t>
+  </si>
+  <si>
+    <t>134362352</t>
+  </si>
+  <si>
+    <t>134362562</t>
+  </si>
+  <si>
+    <t>134362763</t>
+  </si>
+  <si>
+    <t>134363127</t>
+  </si>
+  <si>
+    <t>134363146</t>
+  </si>
+  <si>
+    <t>134363398</t>
+  </si>
+  <si>
+    <t>134363478</t>
+  </si>
+  <si>
+    <t>134363585</t>
+  </si>
+  <si>
+    <t>134363716</t>
+  </si>
+  <si>
+    <t>134363851</t>
+  </si>
+  <si>
+    <t>134364012</t>
+  </si>
+  <si>
+    <t>134364482</t>
+  </si>
+  <si>
+    <t>134364513</t>
+  </si>
+  <si>
+    <t>134364534</t>
+  </si>
+  <si>
+    <t>134364699</t>
+  </si>
+  <si>
+    <t>134364836</t>
+  </si>
+  <si>
+    <t>134365208</t>
+  </si>
+  <si>
+    <t>134365727</t>
+  </si>
+  <si>
+    <t>134365859</t>
+  </si>
+  <si>
+    <t>134365922</t>
+  </si>
+  <si>
+    <t>134365923</t>
+  </si>
+  <si>
+    <t>134365952</t>
+  </si>
+  <si>
+    <t>134366057</t>
+  </si>
+  <si>
+    <t>134366109</t>
+  </si>
+  <si>
+    <t>134366170</t>
+  </si>
+  <si>
+    <t>134366202</t>
+  </si>
+  <si>
+    <t>134366777</t>
+  </si>
+  <si>
+    <t>134366793</t>
+  </si>
+  <si>
+    <t>134366868</t>
+  </si>
+  <si>
+    <t>134366967</t>
+  </si>
+  <si>
+    <t>134367069</t>
+  </si>
+  <si>
+    <t>134367104</t>
+  </si>
+  <si>
+    <t>134367117</t>
+  </si>
+  <si>
+    <t>134367136</t>
+  </si>
+  <si>
+    <t>134367336</t>
+  </si>
+  <si>
+    <t>134367388</t>
+  </si>
+  <si>
+    <t>134367395</t>
+  </si>
+  <si>
+    <t>134367442</t>
+  </si>
+  <si>
+    <t>134367548</t>
+  </si>
+  <si>
+    <t>134367613</t>
+  </si>
+  <si>
+    <t>134367628</t>
+  </si>
+  <si>
+    <t>134367758</t>
+  </si>
+  <si>
+    <t>134367797</t>
+  </si>
+  <si>
+    <t>134367878</t>
+  </si>
+  <si>
+    <t>134367911</t>
+  </si>
+  <si>
+    <t>134367927</t>
+  </si>
+  <si>
+    <t>134368073</t>
+  </si>
+  <si>
+    <t>134368094</t>
+  </si>
+  <si>
+    <t>134368160</t>
+  </si>
+  <si>
+    <t>134368163</t>
+  </si>
+  <si>
+    <t>134368178</t>
+  </si>
+  <si>
+    <t>134368215</t>
+  </si>
+  <si>
+    <t>134368364</t>
+  </si>
+  <si>
+    <t>134368470</t>
+  </si>
+  <si>
+    <t>134368504</t>
+  </si>
+  <si>
+    <t>134368506</t>
+  </si>
+  <si>
+    <t>134368604</t>
+  </si>
+  <si>
+    <t>134368607</t>
+  </si>
+  <si>
+    <t>134368647</t>
+  </si>
+  <si>
+    <t>134368650</t>
+  </si>
+  <si>
+    <t>134368716</t>
+  </si>
+  <si>
+    <t>134368744</t>
+  </si>
+  <si>
+    <t>134368768</t>
+  </si>
+  <si>
+    <t>134368808</t>
+  </si>
+  <si>
+    <t>134368843</t>
+  </si>
+  <si>
+    <t>134368879</t>
+  </si>
+  <si>
+    <t>134368889</t>
+  </si>
+  <si>
+    <t>134368915</t>
+  </si>
+  <si>
+    <t>134368940</t>
+  </si>
+  <si>
+    <t>134368954</t>
+  </si>
+  <si>
+    <t>134369010</t>
+  </si>
+  <si>
+    <t>134369042</t>
+  </si>
+  <si>
+    <t>134369224</t>
+  </si>
+  <si>
+    <t>134369304</t>
+  </si>
+  <si>
+    <t>134369345</t>
+  </si>
+  <si>
+    <t>134369361</t>
+  </si>
+  <si>
+    <t>134369370</t>
+  </si>
+  <si>
+    <t>134369459</t>
+  </si>
+  <si>
+    <t>134369481</t>
+  </si>
+  <si>
+    <t>134369639</t>
+  </si>
+  <si>
+    <t>134369825</t>
+  </si>
+  <si>
+    <t>134369943</t>
+  </si>
+  <si>
+    <t>134370033</t>
+  </si>
+  <si>
+    <t>134370306</t>
+  </si>
+  <si>
+    <t>134371127</t>
+  </si>
+  <si>
+    <t>134371361</t>
+  </si>
+  <si>
+    <t>134371638</t>
+  </si>
+  <si>
+    <t>134371685</t>
+  </si>
+  <si>
+    <t>134371797</t>
+  </si>
+  <si>
+    <t>134371801</t>
+  </si>
+  <si>
+    <t>134371913</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C255"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3379,6 +3517,374 @@
         <v>4</v>
       </c>
     </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADA59C3-D141-4FAC-9B3A-A33EE28FB814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242ABFB7-19B0-448C-A1E5-487E95FF6C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="221">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,766 +45,652 @@
     <t>.</t>
   </si>
   <si>
-    <t>129734695</t>
-  </si>
-  <si>
-    <t>129736922</t>
-  </si>
-  <si>
-    <t>129899738</t>
-  </si>
-  <si>
-    <t>130037183</t>
-  </si>
-  <si>
-    <t>130248016</t>
-  </si>
-  <si>
-    <t>130282600</t>
-  </si>
-  <si>
-    <t>130457650</t>
-  </si>
-  <si>
-    <t>130569739</t>
-  </si>
-  <si>
-    <t>130674338</t>
-  </si>
-  <si>
-    <t>130767718</t>
-  </si>
-  <si>
-    <t>130805562</t>
-  </si>
-  <si>
-    <t>130808132</t>
-  </si>
-  <si>
-    <t>131084902</t>
-  </si>
-  <si>
-    <t>131159429</t>
-  </si>
-  <si>
-    <t>131283053</t>
-  </si>
-  <si>
-    <t>131450066</t>
-  </si>
-  <si>
-    <t>131465789</t>
-  </si>
-  <si>
-    <t>131484346</t>
-  </si>
-  <si>
-    <t>131669074</t>
-  </si>
-  <si>
-    <t>132000459</t>
-  </si>
-  <si>
-    <t>132210108</t>
-  </si>
-  <si>
-    <t>132365210</t>
-  </si>
-  <si>
-    <t>132377990</t>
-  </si>
-  <si>
-    <t>132465678</t>
-  </si>
-  <si>
-    <t>132477849</t>
-  </si>
-  <si>
-    <t>132776262</t>
-  </si>
-  <si>
-    <t>132803557</t>
-  </si>
-  <si>
-    <t>132943478</t>
-  </si>
-  <si>
-    <t>132978979</t>
-  </si>
-  <si>
-    <t>133160042</t>
-  </si>
-  <si>
-    <t>133285103</t>
-  </si>
-  <si>
-    <t>133570861</t>
-  </si>
-  <si>
-    <t>133596623</t>
-  </si>
-  <si>
-    <t>133854520</t>
-  </si>
-  <si>
-    <t>134271114</t>
-  </si>
-  <si>
-    <t>134349559</t>
-  </si>
-  <si>
-    <t>134349601</t>
-  </si>
-  <si>
-    <t>134349675</t>
-  </si>
-  <si>
-    <t>134349725</t>
-  </si>
-  <si>
-    <t>134349822</t>
-  </si>
-  <si>
-    <t>134349889</t>
-  </si>
-  <si>
-    <t>134349890</t>
-  </si>
-  <si>
-    <t>134350188</t>
-  </si>
-  <si>
-    <t>134350225</t>
-  </si>
-  <si>
-    <t>134350451</t>
-  </si>
-  <si>
-    <t>134350570</t>
-  </si>
-  <si>
-    <t>134350768</t>
-  </si>
-  <si>
-    <t>134350787</t>
-  </si>
-  <si>
-    <t>134350839</t>
-  </si>
-  <si>
-    <t>134350857</t>
-  </si>
-  <si>
-    <t>134351107</t>
-  </si>
-  <si>
-    <t>134351117</t>
-  </si>
-  <si>
-    <t>134351393</t>
-  </si>
-  <si>
-    <t>134351497</t>
-  </si>
-  <si>
-    <t>134351712</t>
-  </si>
-  <si>
-    <t>134351738</t>
-  </si>
-  <si>
-    <t>134351827</t>
-  </si>
-  <si>
-    <t>134351853</t>
-  </si>
-  <si>
-    <t>134351886</t>
-  </si>
-  <si>
-    <t>134351933</t>
-  </si>
-  <si>
-    <t>134352249</t>
-  </si>
-  <si>
-    <t>134352292</t>
-  </si>
-  <si>
-    <t>134352346</t>
-  </si>
-  <si>
-    <t>134352386</t>
-  </si>
-  <si>
-    <t>134352419</t>
-  </si>
-  <si>
-    <t>134352581</t>
-  </si>
-  <si>
-    <t>134352587</t>
-  </si>
-  <si>
-    <t>134352609</t>
-  </si>
-  <si>
-    <t>134352798</t>
-  </si>
-  <si>
-    <t>134352833</t>
-  </si>
-  <si>
-    <t>134353721</t>
-  </si>
-  <si>
-    <t>134353841</t>
-  </si>
-  <si>
-    <t>134353962</t>
-  </si>
-  <si>
-    <t>134353987</t>
-  </si>
-  <si>
-    <t>134354206</t>
-  </si>
-  <si>
-    <t>134354255</t>
-  </si>
-  <si>
-    <t>134354512</t>
-  </si>
-  <si>
-    <t>134354776</t>
-  </si>
-  <si>
-    <t>134354813</t>
-  </si>
-  <si>
-    <t>134354899</t>
-  </si>
-  <si>
-    <t>134354902</t>
-  </si>
-  <si>
-    <t>134354910</t>
-  </si>
-  <si>
-    <t>134354931</t>
-  </si>
-  <si>
-    <t>134355029</t>
-  </si>
-  <si>
-    <t>134355231</t>
-  </si>
-  <si>
-    <t>134355390</t>
-  </si>
-  <si>
-    <t>134355524</t>
-  </si>
-  <si>
-    <t>134355551</t>
-  </si>
-  <si>
-    <t>134355628</t>
-  </si>
-  <si>
-    <t>134356009</t>
-  </si>
-  <si>
-    <t>134356069</t>
-  </si>
-  <si>
-    <t>134356223</t>
-  </si>
-  <si>
-    <t>134356353</t>
-  </si>
-  <si>
-    <t>134356386</t>
-  </si>
-  <si>
-    <t>134356463</t>
-  </si>
-  <si>
-    <t>134356565</t>
-  </si>
-  <si>
-    <t>134356588</t>
-  </si>
-  <si>
-    <t>134356607</t>
-  </si>
-  <si>
-    <t>134356723</t>
-  </si>
-  <si>
-    <t>134356725</t>
-  </si>
-  <si>
-    <t>134356807</t>
-  </si>
-  <si>
-    <t>134356829</t>
-  </si>
-  <si>
-    <t>134356844</t>
-  </si>
-  <si>
-    <t>134356941</t>
-  </si>
-  <si>
-    <t>134357181</t>
-  </si>
-  <si>
-    <t>134357390</t>
-  </si>
-  <si>
-    <t>134357397</t>
-  </si>
-  <si>
-    <t>134357442</t>
-  </si>
-  <si>
-    <t>134357591</t>
-  </si>
-  <si>
-    <t>134357731</t>
-  </si>
-  <si>
-    <t>134357842</t>
-  </si>
-  <si>
-    <t>134357856</t>
-  </si>
-  <si>
-    <t>134357867</t>
-  </si>
-  <si>
-    <t>134357895</t>
-  </si>
-  <si>
-    <t>134357937</t>
-  </si>
-  <si>
-    <t>134358119</t>
-  </si>
-  <si>
-    <t>134358204</t>
-  </si>
-  <si>
-    <t>134358258</t>
-  </si>
-  <si>
-    <t>134358289</t>
-  </si>
-  <si>
-    <t>134358361</t>
-  </si>
-  <si>
-    <t>134358381</t>
-  </si>
-  <si>
-    <t>134358422</t>
-  </si>
-  <si>
-    <t>134358432</t>
-  </si>
-  <si>
-    <t>134358437</t>
-  </si>
-  <si>
-    <t>134358662</t>
-  </si>
-  <si>
-    <t>134358668</t>
-  </si>
-  <si>
-    <t>134358722</t>
-  </si>
-  <si>
-    <t>134358794</t>
-  </si>
-  <si>
-    <t>134358827</t>
-  </si>
-  <si>
-    <t>134358865</t>
-  </si>
-  <si>
-    <t>134358917</t>
-  </si>
-  <si>
-    <t>134358986</t>
-  </si>
-  <si>
-    <t>134359262</t>
-  </si>
-  <si>
-    <t>134359272</t>
-  </si>
-  <si>
-    <t>134359345</t>
-  </si>
-  <si>
-    <t>134359458</t>
-  </si>
-  <si>
-    <t>134359478</t>
-  </si>
-  <si>
-    <t>134359484</t>
-  </si>
-  <si>
-    <t>134359554</t>
-  </si>
-  <si>
-    <t>134359588</t>
-  </si>
-  <si>
-    <t>134359699</t>
-  </si>
-  <si>
-    <t>134359713</t>
-  </si>
-  <si>
-    <t>134359924</t>
-  </si>
-  <si>
-    <t>134360389</t>
-  </si>
-  <si>
-    <t>134360711</t>
-  </si>
-  <si>
-    <t>134360734</t>
-  </si>
-  <si>
-    <t>134360765</t>
-  </si>
-  <si>
-    <t>134360844</t>
-  </si>
-  <si>
-    <t>134360874</t>
-  </si>
-  <si>
-    <t>134360876</t>
-  </si>
-  <si>
-    <t>134360919</t>
-  </si>
-  <si>
-    <t>134360923</t>
-  </si>
-  <si>
-    <t>134361141</t>
-  </si>
-  <si>
-    <t>134361266</t>
-  </si>
-  <si>
-    <t>134361299</t>
-  </si>
-  <si>
-    <t>134361380</t>
-  </si>
-  <si>
-    <t>134361383</t>
-  </si>
-  <si>
-    <t>134361527</t>
-  </si>
-  <si>
-    <t>134361558</t>
-  </si>
-  <si>
-    <t>134361588</t>
-  </si>
-  <si>
-    <t>134361630</t>
-  </si>
-  <si>
-    <t>134362040</t>
-  </si>
-  <si>
-    <t>134362061</t>
-  </si>
-  <si>
-    <t>134362352</t>
-  </si>
-  <si>
-    <t>134362562</t>
-  </si>
-  <si>
-    <t>134362763</t>
-  </si>
-  <si>
-    <t>134363127</t>
-  </si>
-  <si>
-    <t>134363146</t>
-  </si>
-  <si>
-    <t>134363398</t>
-  </si>
-  <si>
-    <t>134363478</t>
-  </si>
-  <si>
-    <t>134363585</t>
-  </si>
-  <si>
-    <t>134363716</t>
-  </si>
-  <si>
-    <t>134363851</t>
-  </si>
-  <si>
-    <t>134364012</t>
-  </si>
-  <si>
-    <t>134364482</t>
-  </si>
-  <si>
-    <t>134364513</t>
-  </si>
-  <si>
-    <t>134364534</t>
-  </si>
-  <si>
-    <t>134364699</t>
-  </si>
-  <si>
-    <t>134364836</t>
-  </si>
-  <si>
-    <t>134365208</t>
-  </si>
-  <si>
-    <t>134365727</t>
-  </si>
-  <si>
-    <t>134365859</t>
-  </si>
-  <si>
-    <t>134365922</t>
-  </si>
-  <si>
-    <t>134365923</t>
-  </si>
-  <si>
-    <t>134365952</t>
-  </si>
-  <si>
-    <t>134366057</t>
-  </si>
-  <si>
-    <t>134366109</t>
-  </si>
-  <si>
-    <t>134366170</t>
-  </si>
-  <si>
-    <t>134366202</t>
-  </si>
-  <si>
-    <t>134366777</t>
-  </si>
-  <si>
-    <t>134366793</t>
-  </si>
-  <si>
-    <t>134366868</t>
-  </si>
-  <si>
-    <t>134366967</t>
-  </si>
-  <si>
-    <t>134367069</t>
-  </si>
-  <si>
-    <t>134367104</t>
-  </si>
-  <si>
-    <t>134367117</t>
-  </si>
-  <si>
-    <t>134367136</t>
-  </si>
-  <si>
-    <t>134367336</t>
-  </si>
-  <si>
-    <t>134367388</t>
-  </si>
-  <si>
-    <t>134367395</t>
-  </si>
-  <si>
-    <t>134367442</t>
-  </si>
-  <si>
-    <t>134367548</t>
-  </si>
-  <si>
-    <t>134367613</t>
-  </si>
-  <si>
-    <t>134367628</t>
-  </si>
-  <si>
-    <t>134367758</t>
-  </si>
-  <si>
-    <t>134367797</t>
-  </si>
-  <si>
-    <t>134367878</t>
-  </si>
-  <si>
-    <t>134367911</t>
-  </si>
-  <si>
-    <t>134367927</t>
-  </si>
-  <si>
-    <t>134368073</t>
-  </si>
-  <si>
-    <t>134368094</t>
-  </si>
-  <si>
-    <t>134368160</t>
-  </si>
-  <si>
-    <t>134368163</t>
-  </si>
-  <si>
-    <t>134368178</t>
-  </si>
-  <si>
-    <t>134368215</t>
-  </si>
-  <si>
-    <t>134368364</t>
-  </si>
-  <si>
-    <t>134368470</t>
-  </si>
-  <si>
-    <t>134368504</t>
-  </si>
-  <si>
-    <t>134368506</t>
-  </si>
-  <si>
-    <t>134368604</t>
-  </si>
-  <si>
-    <t>134368607</t>
-  </si>
-  <si>
-    <t>134368647</t>
-  </si>
-  <si>
-    <t>134368650</t>
-  </si>
-  <si>
-    <t>134368716</t>
-  </si>
-  <si>
-    <t>134368744</t>
-  </si>
-  <si>
-    <t>134368768</t>
-  </si>
-  <si>
-    <t>134368808</t>
-  </si>
-  <si>
-    <t>134368843</t>
-  </si>
-  <si>
-    <t>134368879</t>
-  </si>
-  <si>
-    <t>134368889</t>
-  </si>
-  <si>
-    <t>134368915</t>
-  </si>
-  <si>
-    <t>134368940</t>
-  </si>
-  <si>
-    <t>134368954</t>
-  </si>
-  <si>
-    <t>134369010</t>
-  </si>
-  <si>
-    <t>134369042</t>
-  </si>
-  <si>
-    <t>134369224</t>
-  </si>
-  <si>
-    <t>134369304</t>
-  </si>
-  <si>
-    <t>134369345</t>
-  </si>
-  <si>
-    <t>134369361</t>
-  </si>
-  <si>
-    <t>134369370</t>
-  </si>
-  <si>
-    <t>134369459</t>
-  </si>
-  <si>
-    <t>134369481</t>
-  </si>
-  <si>
-    <t>134369639</t>
-  </si>
-  <si>
-    <t>134369825</t>
-  </si>
-  <si>
-    <t>134369943</t>
-  </si>
-  <si>
-    <t>134370033</t>
-  </si>
-  <si>
-    <t>134370306</t>
-  </si>
-  <si>
-    <t>134371127</t>
-  </si>
-  <si>
-    <t>134371361</t>
-  </si>
-  <si>
-    <t>134371638</t>
-  </si>
-  <si>
-    <t>134371685</t>
-  </si>
-  <si>
-    <t>134371797</t>
-  </si>
-  <si>
-    <t>134371801</t>
-  </si>
-  <si>
-    <t>134371913</t>
+    <t>129712727</t>
+  </si>
+  <si>
+    <t>130105440</t>
+  </si>
+  <si>
+    <t>130119469</t>
+  </si>
+  <si>
+    <t>130259685</t>
+  </si>
+  <si>
+    <t>130350183</t>
+  </si>
+  <si>
+    <t>130457524</t>
+  </si>
+  <si>
+    <t>130975754</t>
+  </si>
+  <si>
+    <t>131008597</t>
+  </si>
+  <si>
+    <t>131590511</t>
+  </si>
+  <si>
+    <t>131663382</t>
+  </si>
+  <si>
+    <t>131912186</t>
+  </si>
+  <si>
+    <t>132049028</t>
+  </si>
+  <si>
+    <t>132171398</t>
+  </si>
+  <si>
+    <t>132428960</t>
+  </si>
+  <si>
+    <t>132636776</t>
+  </si>
+  <si>
+    <t>133025384</t>
+  </si>
+  <si>
+    <t>133368850</t>
+  </si>
+  <si>
+    <t>133665150</t>
+  </si>
+  <si>
+    <t>133704093</t>
+  </si>
+  <si>
+    <t>133941065</t>
+  </si>
+  <si>
+    <t>133963056</t>
+  </si>
+  <si>
+    <t>134060157</t>
+  </si>
+  <si>
+    <t>134209978</t>
+  </si>
+  <si>
+    <t>134287323</t>
+  </si>
+  <si>
+    <t>134371966</t>
+  </si>
+  <si>
+    <t>134372043</t>
+  </si>
+  <si>
+    <t>134372522</t>
+  </si>
+  <si>
+    <t>134372583</t>
+  </si>
+  <si>
+    <t>134372768</t>
+  </si>
+  <si>
+    <t>134372888</t>
+  </si>
+  <si>
+    <t>134373011</t>
+  </si>
+  <si>
+    <t>134373087</t>
+  </si>
+  <si>
+    <t>134373252</t>
+  </si>
+  <si>
+    <t>134373253</t>
+  </si>
+  <si>
+    <t>134373254</t>
+  </si>
+  <si>
+    <t>134373270</t>
+  </si>
+  <si>
+    <t>134373468</t>
+  </si>
+  <si>
+    <t>134373533</t>
+  </si>
+  <si>
+    <t>134373558</t>
+  </si>
+  <si>
+    <t>134373721</t>
+  </si>
+  <si>
+    <t>134373857</t>
+  </si>
+  <si>
+    <t>134373928</t>
+  </si>
+  <si>
+    <t>134374074</t>
+  </si>
+  <si>
+    <t>134374247</t>
+  </si>
+  <si>
+    <t>134374304</t>
+  </si>
+  <si>
+    <t>134374401</t>
+  </si>
+  <si>
+    <t>134374668</t>
+  </si>
+  <si>
+    <t>134374721</t>
+  </si>
+  <si>
+    <t>134374739</t>
+  </si>
+  <si>
+    <t>134374819</t>
+  </si>
+  <si>
+    <t>134374854</t>
+  </si>
+  <si>
+    <t>134374980</t>
+  </si>
+  <si>
+    <t>134375053</t>
+  </si>
+  <si>
+    <t>134375117</t>
+  </si>
+  <si>
+    <t>134375131</t>
+  </si>
+  <si>
+    <t>134375365</t>
+  </si>
+  <si>
+    <t>134375457</t>
+  </si>
+  <si>
+    <t>134375856</t>
+  </si>
+  <si>
+    <t>134376163</t>
+  </si>
+  <si>
+    <t>134376359</t>
+  </si>
+  <si>
+    <t>134376372</t>
+  </si>
+  <si>
+    <t>134376485</t>
+  </si>
+  <si>
+    <t>134376609</t>
+  </si>
+  <si>
+    <t>134376617</t>
+  </si>
+  <si>
+    <t>134376747</t>
+  </si>
+  <si>
+    <t>134376988</t>
+  </si>
+  <si>
+    <t>134377111</t>
+  </si>
+  <si>
+    <t>134377132</t>
+  </si>
+  <si>
+    <t>134377223</t>
+  </si>
+  <si>
+    <t>134377528</t>
+  </si>
+  <si>
+    <t>134377562</t>
+  </si>
+  <si>
+    <t>134377563</t>
+  </si>
+  <si>
+    <t>134377692</t>
+  </si>
+  <si>
+    <t>134377784</t>
+  </si>
+  <si>
+    <t>134377899</t>
+  </si>
+  <si>
+    <t>134377900</t>
+  </si>
+  <si>
+    <t>134377916</t>
+  </si>
+  <si>
+    <t>134377990</t>
+  </si>
+  <si>
+    <t>134378089</t>
+  </si>
+  <si>
+    <t>134378215</t>
+  </si>
+  <si>
+    <t>134378245</t>
+  </si>
+  <si>
+    <t>134378252</t>
+  </si>
+  <si>
+    <t>134378348</t>
+  </si>
+  <si>
+    <t>134378387</t>
+  </si>
+  <si>
+    <t>134378477</t>
+  </si>
+  <si>
+    <t>134378489</t>
+  </si>
+  <si>
+    <t>134378509</t>
+  </si>
+  <si>
+    <t>134378688</t>
+  </si>
+  <si>
+    <t>134378716</t>
+  </si>
+  <si>
+    <t>134378870</t>
+  </si>
+  <si>
+    <t>134378949</t>
+  </si>
+  <si>
+    <t>134379305</t>
+  </si>
+  <si>
+    <t>134379415</t>
+  </si>
+  <si>
+    <t>134379508</t>
+  </si>
+  <si>
+    <t>134379592</t>
+  </si>
+  <si>
+    <t>134379757</t>
+  </si>
+  <si>
+    <t>134379890</t>
+  </si>
+  <si>
+    <t>134380281</t>
+  </si>
+  <si>
+    <t>134380372</t>
+  </si>
+  <si>
+    <t>134380671</t>
+  </si>
+  <si>
+    <t>134380793</t>
+  </si>
+  <si>
+    <t>134380978</t>
+  </si>
+  <si>
+    <t>134381027</t>
+  </si>
+  <si>
+    <t>134381196</t>
+  </si>
+  <si>
+    <t>134381268</t>
+  </si>
+  <si>
+    <t>134381321</t>
+  </si>
+  <si>
+    <t>134381323</t>
+  </si>
+  <si>
+    <t>134381513</t>
+  </si>
+  <si>
+    <t>134381671</t>
+  </si>
+  <si>
+    <t>134381694</t>
+  </si>
+  <si>
+    <t>134381763</t>
+  </si>
+  <si>
+    <t>134381821</t>
+  </si>
+  <si>
+    <t>134381992</t>
+  </si>
+  <si>
+    <t>134382233</t>
+  </si>
+  <si>
+    <t>134382270</t>
+  </si>
+  <si>
+    <t>134382759</t>
+  </si>
+  <si>
+    <t>134382820</t>
+  </si>
+  <si>
+    <t>134382879</t>
+  </si>
+  <si>
+    <t>134382896</t>
+  </si>
+  <si>
+    <t>134382933</t>
+  </si>
+  <si>
+    <t>134382968</t>
+  </si>
+  <si>
+    <t>134383266</t>
+  </si>
+  <si>
+    <t>134383521</t>
+  </si>
+  <si>
+    <t>134383694</t>
+  </si>
+  <si>
+    <t>134383735</t>
+  </si>
+  <si>
+    <t>134383864</t>
+  </si>
+  <si>
+    <t>134383939</t>
+  </si>
+  <si>
+    <t>134384068</t>
+  </si>
+  <si>
+    <t>134384123</t>
+  </si>
+  <si>
+    <t>134384252</t>
+  </si>
+  <si>
+    <t>134384306</t>
+  </si>
+  <si>
+    <t>134384530</t>
+  </si>
+  <si>
+    <t>134384626</t>
+  </si>
+  <si>
+    <t>134384663</t>
+  </si>
+  <si>
+    <t>134384760</t>
+  </si>
+  <si>
+    <t>134384853</t>
+  </si>
+  <si>
+    <t>134384861</t>
+  </si>
+  <si>
+    <t>134385081</t>
+  </si>
+  <si>
+    <t>134385539</t>
+  </si>
+  <si>
+    <t>134385551</t>
+  </si>
+  <si>
+    <t>134385562</t>
+  </si>
+  <si>
+    <t>134385576</t>
+  </si>
+  <si>
+    <t>134385589</t>
+  </si>
+  <si>
+    <t>134385718</t>
+  </si>
+  <si>
+    <t>134385964</t>
+  </si>
+  <si>
+    <t>134385988</t>
+  </si>
+  <si>
+    <t>134386066</t>
+  </si>
+  <si>
+    <t>134386093</t>
+  </si>
+  <si>
+    <t>134386304</t>
+  </si>
+  <si>
+    <t>134386921</t>
+  </si>
+  <si>
+    <t>134386985</t>
+  </si>
+  <si>
+    <t>134387009</t>
+  </si>
+  <si>
+    <t>134387097</t>
+  </si>
+  <si>
+    <t>134387104</t>
+  </si>
+  <si>
+    <t>134387165</t>
+  </si>
+  <si>
+    <t>134387393</t>
+  </si>
+  <si>
+    <t>134387624</t>
+  </si>
+  <si>
+    <t>134387779</t>
+  </si>
+  <si>
+    <t>134387834</t>
+  </si>
+  <si>
+    <t>134388093</t>
+  </si>
+  <si>
+    <t>134388104</t>
+  </si>
+  <si>
+    <t>134388168</t>
+  </si>
+  <si>
+    <t>134388256</t>
+  </si>
+  <si>
+    <t>134388257</t>
+  </si>
+  <si>
+    <t>134388311</t>
+  </si>
+  <si>
+    <t>134388388</t>
+  </si>
+  <si>
+    <t>134388426</t>
+  </si>
+  <si>
+    <t>134388455</t>
+  </si>
+  <si>
+    <t>134388458</t>
+  </si>
+  <si>
+    <t>134388485</t>
+  </si>
+  <si>
+    <t>134388533</t>
+  </si>
+  <si>
+    <t>134388711</t>
+  </si>
+  <si>
+    <t>134388747</t>
+  </si>
+  <si>
+    <t>134388803</t>
+  </si>
+  <si>
+    <t>134388832</t>
+  </si>
+  <si>
+    <t>134389012</t>
+  </si>
+  <si>
+    <t>134389022</t>
+  </si>
+  <si>
+    <t>134389119</t>
+  </si>
+  <si>
+    <t>134389210</t>
+  </si>
+  <si>
+    <t>134389418</t>
+  </si>
+  <si>
+    <t>134389458</t>
+  </si>
+  <si>
+    <t>134389467</t>
+  </si>
+  <si>
+    <t>134389645</t>
+  </si>
+  <si>
+    <t>134389785</t>
+  </si>
+  <si>
+    <t>134389823</t>
+  </si>
+  <si>
+    <t>134390132</t>
+  </si>
+  <si>
+    <t>134390206</t>
+  </si>
+  <si>
+    <t>134390215</t>
+  </si>
+  <si>
+    <t>134390237</t>
+  </si>
+  <si>
+    <t>134390242</t>
+  </si>
+  <si>
+    <t>134390356</t>
+  </si>
+  <si>
+    <t>134390410</t>
+  </si>
+  <si>
+    <t>134390415</t>
+  </si>
+  <si>
+    <t>134390434</t>
+  </si>
+  <si>
+    <t>134390576</t>
+  </si>
+  <si>
+    <t>134390637</t>
+  </si>
+  <si>
+    <t>134390654</t>
+  </si>
+  <si>
+    <t>134390658</t>
+  </si>
+  <si>
+    <t>134390679</t>
+  </si>
+  <si>
+    <t>134390715</t>
+  </si>
+  <si>
+    <t>134390781</t>
+  </si>
+  <si>
+    <t>134390963</t>
+  </si>
+  <si>
+    <t>134391210</t>
+  </si>
+  <si>
+    <t>134391306</t>
+  </si>
+  <si>
+    <t>134391339</t>
+  </si>
+  <si>
+    <t>134391510</t>
+  </si>
+  <si>
+    <t>134391663</t>
+  </si>
+  <si>
+    <t>134391698</t>
+  </si>
+  <si>
+    <t>134392076</t>
+  </si>
+  <si>
+    <t>134392214</t>
+  </si>
+  <si>
+    <t>134392643</t>
+  </si>
+  <si>
+    <t>134393236</t>
+  </si>
+  <si>
+    <t>134393407</t>
+  </si>
+  <si>
+    <t>134393462</t>
+  </si>
+  <si>
+    <t>134393471</t>
+  </si>
+  <si>
+    <t>134393544</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C255"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3524,6 +3410,9 @@
       <c r="B210" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
@@ -3532,6 +3421,9 @@
       <c r="B211" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
@@ -3540,6 +3432,9 @@
       <c r="B212" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
@@ -3548,6 +3443,9 @@
       <c r="B213" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
@@ -3556,6 +3454,9 @@
       <c r="B214" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
@@ -3564,6 +3465,9 @@
       <c r="B215" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
@@ -3572,6 +3476,9 @@
       <c r="B216" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
@@ -3580,309 +3487,8 @@
       <c r="B217" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B220" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B223" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B237" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B239" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B242" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B243" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B245" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A246" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B246" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A247" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B247" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B248" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A251" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B251" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A252" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A254" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A255" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>3</v>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242ABFB7-19B0-448C-A1E5-487E95FF6C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7759502-7552-4AC3-8162-7C4F92C0AB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="236">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,652 +45,697 @@
     <t>.</t>
   </si>
   <si>
-    <t>129712727</t>
-  </si>
-  <si>
-    <t>130105440</t>
-  </si>
-  <si>
-    <t>130119469</t>
-  </si>
-  <si>
-    <t>130259685</t>
-  </si>
-  <si>
-    <t>130350183</t>
-  </si>
-  <si>
-    <t>130457524</t>
-  </si>
-  <si>
-    <t>130975754</t>
-  </si>
-  <si>
-    <t>131008597</t>
-  </si>
-  <si>
-    <t>131590511</t>
-  </si>
-  <si>
-    <t>131663382</t>
-  </si>
-  <si>
-    <t>131912186</t>
-  </si>
-  <si>
-    <t>132049028</t>
-  </si>
-  <si>
-    <t>132171398</t>
-  </si>
-  <si>
-    <t>132428960</t>
-  </si>
-  <si>
-    <t>132636776</t>
-  </si>
-  <si>
-    <t>133025384</t>
-  </si>
-  <si>
-    <t>133368850</t>
-  </si>
-  <si>
-    <t>133665150</t>
-  </si>
-  <si>
-    <t>133704093</t>
-  </si>
-  <si>
-    <t>133941065</t>
-  </si>
-  <si>
-    <t>133963056</t>
-  </si>
-  <si>
-    <t>134060157</t>
-  </si>
-  <si>
-    <t>134209978</t>
-  </si>
-  <si>
-    <t>134287323</t>
-  </si>
-  <si>
-    <t>134371966</t>
-  </si>
-  <si>
-    <t>134372043</t>
-  </si>
-  <si>
-    <t>134372522</t>
-  </si>
-  <si>
-    <t>134372583</t>
-  </si>
-  <si>
-    <t>134372768</t>
-  </si>
-  <si>
-    <t>134372888</t>
-  </si>
-  <si>
-    <t>134373011</t>
-  </si>
-  <si>
-    <t>134373087</t>
-  </si>
-  <si>
-    <t>134373252</t>
-  </si>
-  <si>
-    <t>134373253</t>
-  </si>
-  <si>
-    <t>134373254</t>
-  </si>
-  <si>
-    <t>134373270</t>
-  </si>
-  <si>
-    <t>134373468</t>
-  </si>
-  <si>
-    <t>134373533</t>
-  </si>
-  <si>
-    <t>134373558</t>
-  </si>
-  <si>
-    <t>134373721</t>
-  </si>
-  <si>
-    <t>134373857</t>
-  </si>
-  <si>
-    <t>134373928</t>
-  </si>
-  <si>
-    <t>134374074</t>
-  </si>
-  <si>
-    <t>134374247</t>
-  </si>
-  <si>
-    <t>134374304</t>
-  </si>
-  <si>
-    <t>134374401</t>
-  </si>
-  <si>
-    <t>134374668</t>
-  </si>
-  <si>
-    <t>134374721</t>
-  </si>
-  <si>
-    <t>134374739</t>
-  </si>
-  <si>
-    <t>134374819</t>
-  </si>
-  <si>
-    <t>134374854</t>
-  </si>
-  <si>
-    <t>134374980</t>
-  </si>
-  <si>
-    <t>134375053</t>
-  </si>
-  <si>
-    <t>134375117</t>
-  </si>
-  <si>
-    <t>134375131</t>
-  </si>
-  <si>
-    <t>134375365</t>
-  </si>
-  <si>
-    <t>134375457</t>
-  </si>
-  <si>
-    <t>134375856</t>
-  </si>
-  <si>
-    <t>134376163</t>
-  </si>
-  <si>
-    <t>134376359</t>
-  </si>
-  <si>
-    <t>134376372</t>
-  </si>
-  <si>
-    <t>134376485</t>
-  </si>
-  <si>
-    <t>134376609</t>
-  </si>
-  <si>
-    <t>134376617</t>
-  </si>
-  <si>
-    <t>134376747</t>
-  </si>
-  <si>
-    <t>134376988</t>
-  </si>
-  <si>
-    <t>134377111</t>
-  </si>
-  <si>
-    <t>134377132</t>
-  </si>
-  <si>
-    <t>134377223</t>
-  </si>
-  <si>
-    <t>134377528</t>
-  </si>
-  <si>
-    <t>134377562</t>
-  </si>
-  <si>
-    <t>134377563</t>
-  </si>
-  <si>
-    <t>134377692</t>
-  </si>
-  <si>
-    <t>134377784</t>
-  </si>
-  <si>
-    <t>134377899</t>
-  </si>
-  <si>
-    <t>134377900</t>
-  </si>
-  <si>
-    <t>134377916</t>
-  </si>
-  <si>
-    <t>134377990</t>
-  </si>
-  <si>
-    <t>134378089</t>
-  </si>
-  <si>
-    <t>134378215</t>
-  </si>
-  <si>
-    <t>134378245</t>
-  </si>
-  <si>
-    <t>134378252</t>
-  </si>
-  <si>
-    <t>134378348</t>
-  </si>
-  <si>
-    <t>134378387</t>
-  </si>
-  <si>
-    <t>134378477</t>
-  </si>
-  <si>
-    <t>134378489</t>
-  </si>
-  <si>
-    <t>134378509</t>
-  </si>
-  <si>
-    <t>134378688</t>
-  </si>
-  <si>
-    <t>134378716</t>
-  </si>
-  <si>
-    <t>134378870</t>
-  </si>
-  <si>
-    <t>134378949</t>
-  </si>
-  <si>
-    <t>134379305</t>
-  </si>
-  <si>
-    <t>134379415</t>
-  </si>
-  <si>
-    <t>134379508</t>
-  </si>
-  <si>
-    <t>134379592</t>
-  </si>
-  <si>
-    <t>134379757</t>
-  </si>
-  <si>
-    <t>134379890</t>
-  </si>
-  <si>
-    <t>134380281</t>
-  </si>
-  <si>
-    <t>134380372</t>
-  </si>
-  <si>
-    <t>134380671</t>
-  </si>
-  <si>
-    <t>134380793</t>
-  </si>
-  <si>
-    <t>134380978</t>
-  </si>
-  <si>
-    <t>134381027</t>
-  </si>
-  <si>
-    <t>134381196</t>
-  </si>
-  <si>
-    <t>134381268</t>
-  </si>
-  <si>
-    <t>134381321</t>
-  </si>
-  <si>
-    <t>134381323</t>
-  </si>
-  <si>
-    <t>134381513</t>
-  </si>
-  <si>
-    <t>134381671</t>
-  </si>
-  <si>
-    <t>134381694</t>
-  </si>
-  <si>
-    <t>134381763</t>
-  </si>
-  <si>
-    <t>134381821</t>
-  </si>
-  <si>
-    <t>134381992</t>
-  </si>
-  <si>
-    <t>134382233</t>
-  </si>
-  <si>
-    <t>134382270</t>
-  </si>
-  <si>
-    <t>134382759</t>
-  </si>
-  <si>
-    <t>134382820</t>
-  </si>
-  <si>
-    <t>134382879</t>
-  </si>
-  <si>
-    <t>134382896</t>
-  </si>
-  <si>
-    <t>134382933</t>
-  </si>
-  <si>
-    <t>134382968</t>
-  </si>
-  <si>
-    <t>134383266</t>
-  </si>
-  <si>
-    <t>134383521</t>
-  </si>
-  <si>
-    <t>134383694</t>
-  </si>
-  <si>
-    <t>134383735</t>
-  </si>
-  <si>
-    <t>134383864</t>
-  </si>
-  <si>
-    <t>134383939</t>
-  </si>
-  <si>
-    <t>134384068</t>
-  </si>
-  <si>
-    <t>134384123</t>
-  </si>
-  <si>
-    <t>134384252</t>
-  </si>
-  <si>
-    <t>134384306</t>
-  </si>
-  <si>
-    <t>134384530</t>
-  </si>
-  <si>
-    <t>134384626</t>
-  </si>
-  <si>
-    <t>134384663</t>
-  </si>
-  <si>
-    <t>134384760</t>
-  </si>
-  <si>
-    <t>134384853</t>
-  </si>
-  <si>
-    <t>134384861</t>
-  </si>
-  <si>
-    <t>134385081</t>
-  </si>
-  <si>
-    <t>134385539</t>
-  </si>
-  <si>
-    <t>134385551</t>
-  </si>
-  <si>
-    <t>134385562</t>
-  </si>
-  <si>
-    <t>134385576</t>
-  </si>
-  <si>
-    <t>134385589</t>
-  </si>
-  <si>
-    <t>134385718</t>
-  </si>
-  <si>
-    <t>134385964</t>
-  </si>
-  <si>
-    <t>134385988</t>
-  </si>
-  <si>
-    <t>134386066</t>
-  </si>
-  <si>
-    <t>134386093</t>
-  </si>
-  <si>
-    <t>134386304</t>
-  </si>
-  <si>
-    <t>134386921</t>
-  </si>
-  <si>
-    <t>134386985</t>
-  </si>
-  <si>
-    <t>134387009</t>
-  </si>
-  <si>
-    <t>134387097</t>
-  </si>
-  <si>
-    <t>134387104</t>
-  </si>
-  <si>
-    <t>134387165</t>
-  </si>
-  <si>
-    <t>134387393</t>
-  </si>
-  <si>
-    <t>134387624</t>
-  </si>
-  <si>
-    <t>134387779</t>
-  </si>
-  <si>
-    <t>134387834</t>
-  </si>
-  <si>
-    <t>134388093</t>
-  </si>
-  <si>
-    <t>134388104</t>
-  </si>
-  <si>
-    <t>134388168</t>
-  </si>
-  <si>
-    <t>134388256</t>
-  </si>
-  <si>
-    <t>134388257</t>
-  </si>
-  <si>
-    <t>134388311</t>
-  </si>
-  <si>
-    <t>134388388</t>
-  </si>
-  <si>
-    <t>134388426</t>
-  </si>
-  <si>
-    <t>134388455</t>
-  </si>
-  <si>
-    <t>134388458</t>
-  </si>
-  <si>
-    <t>134388485</t>
-  </si>
-  <si>
-    <t>134388533</t>
-  </si>
-  <si>
-    <t>134388711</t>
-  </si>
-  <si>
-    <t>134388747</t>
-  </si>
-  <si>
-    <t>134388803</t>
-  </si>
-  <si>
-    <t>134388832</t>
-  </si>
-  <si>
-    <t>134389012</t>
-  </si>
-  <si>
-    <t>134389022</t>
-  </si>
-  <si>
-    <t>134389119</t>
-  </si>
-  <si>
-    <t>134389210</t>
-  </si>
-  <si>
-    <t>134389418</t>
-  </si>
-  <si>
-    <t>134389458</t>
-  </si>
-  <si>
-    <t>134389467</t>
-  </si>
-  <si>
-    <t>134389645</t>
-  </si>
-  <si>
-    <t>134389785</t>
-  </si>
-  <si>
-    <t>134389823</t>
-  </si>
-  <si>
-    <t>134390132</t>
-  </si>
-  <si>
-    <t>134390206</t>
-  </si>
-  <si>
-    <t>134390215</t>
-  </si>
-  <si>
-    <t>134390237</t>
-  </si>
-  <si>
-    <t>134390242</t>
-  </si>
-  <si>
-    <t>134390356</t>
-  </si>
-  <si>
-    <t>134390410</t>
-  </si>
-  <si>
-    <t>134390415</t>
-  </si>
-  <si>
-    <t>134390434</t>
-  </si>
-  <si>
-    <t>134390576</t>
-  </si>
-  <si>
-    <t>134390637</t>
-  </si>
-  <si>
-    <t>134390654</t>
-  </si>
-  <si>
-    <t>134390658</t>
-  </si>
-  <si>
-    <t>134390679</t>
-  </si>
-  <si>
-    <t>134390715</t>
-  </si>
-  <si>
-    <t>134390781</t>
-  </si>
-  <si>
-    <t>134390963</t>
-  </si>
-  <si>
-    <t>134391210</t>
-  </si>
-  <si>
-    <t>134391306</t>
-  </si>
-  <si>
-    <t>134391339</t>
-  </si>
-  <si>
-    <t>134391510</t>
-  </si>
-  <si>
-    <t>134391663</t>
-  </si>
-  <si>
-    <t>134391698</t>
-  </si>
-  <si>
-    <t>134392076</t>
-  </si>
-  <si>
-    <t>134392214</t>
-  </si>
-  <si>
-    <t>134392643</t>
-  </si>
-  <si>
-    <t>134393236</t>
-  </si>
-  <si>
-    <t>134393407</t>
-  </si>
-  <si>
-    <t>134393462</t>
-  </si>
-  <si>
-    <t>134393471</t>
-  </si>
-  <si>
-    <t>134393544</t>
+    <t>129704175</t>
+  </si>
+  <si>
+    <t>129887952</t>
+  </si>
+  <si>
+    <t>129913252</t>
+  </si>
+  <si>
+    <t>130073415</t>
+  </si>
+  <si>
+    <t>130293095</t>
+  </si>
+  <si>
+    <t>130505714</t>
+  </si>
+  <si>
+    <t>130774500</t>
+  </si>
+  <si>
+    <t>131106543</t>
+  </si>
+  <si>
+    <t>131738740</t>
+  </si>
+  <si>
+    <t>131817351</t>
+  </si>
+  <si>
+    <t>131839485</t>
+  </si>
+  <si>
+    <t>131845289</t>
+  </si>
+  <si>
+    <t>131995280</t>
+  </si>
+  <si>
+    <t>132544112</t>
+  </si>
+  <si>
+    <t>132587720</t>
+  </si>
+  <si>
+    <t>132854698</t>
+  </si>
+  <si>
+    <t>133086649</t>
+  </si>
+  <si>
+    <t>133192684</t>
+  </si>
+  <si>
+    <t>133369567</t>
+  </si>
+  <si>
+    <t>133373983</t>
+  </si>
+  <si>
+    <t>133459264</t>
+  </si>
+  <si>
+    <t>133487089</t>
+  </si>
+  <si>
+    <t>133958845</t>
+  </si>
+  <si>
+    <t>134199031</t>
+  </si>
+  <si>
+    <t>134393725</t>
+  </si>
+  <si>
+    <t>134393747</t>
+  </si>
+  <si>
+    <t>134393774</t>
+  </si>
+  <si>
+    <t>134394204</t>
+  </si>
+  <si>
+    <t>134394228</t>
+  </si>
+  <si>
+    <t>134394422</t>
+  </si>
+  <si>
+    <t>134394533</t>
+  </si>
+  <si>
+    <t>134394657</t>
+  </si>
+  <si>
+    <t>134394733</t>
+  </si>
+  <si>
+    <t>134395741</t>
+  </si>
+  <si>
+    <t>134395814</t>
+  </si>
+  <si>
+    <t>134395861</t>
+  </si>
+  <si>
+    <t>134395980</t>
+  </si>
+  <si>
+    <t>134396400</t>
+  </si>
+  <si>
+    <t>134396527</t>
+  </si>
+  <si>
+    <t>134396688</t>
+  </si>
+  <si>
+    <t>134397191</t>
+  </si>
+  <si>
+    <t>134397212</t>
+  </si>
+  <si>
+    <t>134397263</t>
+  </si>
+  <si>
+    <t>134397327</t>
+  </si>
+  <si>
+    <t>134397495</t>
+  </si>
+  <si>
+    <t>134397555</t>
+  </si>
+  <si>
+    <t>134397585</t>
+  </si>
+  <si>
+    <t>134397702</t>
+  </si>
+  <si>
+    <t>134397743</t>
+  </si>
+  <si>
+    <t>134397902</t>
+  </si>
+  <si>
+    <t>134397933</t>
+  </si>
+  <si>
+    <t>134398173</t>
+  </si>
+  <si>
+    <t>134398271</t>
+  </si>
+  <si>
+    <t>134398308</t>
+  </si>
+  <si>
+    <t>134398325</t>
+  </si>
+  <si>
+    <t>134398326</t>
+  </si>
+  <si>
+    <t>134398802</t>
+  </si>
+  <si>
+    <t>134398838</t>
+  </si>
+  <si>
+    <t>134398890</t>
+  </si>
+  <si>
+    <t>134399075</t>
+  </si>
+  <si>
+    <t>134399147</t>
+  </si>
+  <si>
+    <t>134399287</t>
+  </si>
+  <si>
+    <t>134399294</t>
+  </si>
+  <si>
+    <t>134399320</t>
+  </si>
+  <si>
+    <t>134399380</t>
+  </si>
+  <si>
+    <t>134399560</t>
+  </si>
+  <si>
+    <t>134399918</t>
+  </si>
+  <si>
+    <t>134399997</t>
+  </si>
+  <si>
+    <t>134400221</t>
+  </si>
+  <si>
+    <t>134400255</t>
+  </si>
+  <si>
+    <t>134400266</t>
+  </si>
+  <si>
+    <t>134400509</t>
+  </si>
+  <si>
+    <t>134400790</t>
+  </si>
+  <si>
+    <t>134400810</t>
+  </si>
+  <si>
+    <t>134400882</t>
+  </si>
+  <si>
+    <t>134401003</t>
+  </si>
+  <si>
+    <t>134401233</t>
+  </si>
+  <si>
+    <t>134401360</t>
+  </si>
+  <si>
+    <t>134401386</t>
+  </si>
+  <si>
+    <t>134401659</t>
+  </si>
+  <si>
+    <t>134401673</t>
+  </si>
+  <si>
+    <t>134401709</t>
+  </si>
+  <si>
+    <t>134401780</t>
+  </si>
+  <si>
+    <t>134401816</t>
+  </si>
+  <si>
+    <t>134402000</t>
+  </si>
+  <si>
+    <t>134402084</t>
+  </si>
+  <si>
+    <t>134402138</t>
+  </si>
+  <si>
+    <t>134402391</t>
+  </si>
+  <si>
+    <t>134402449</t>
+  </si>
+  <si>
+    <t>134402553</t>
+  </si>
+  <si>
+    <t>134402571</t>
+  </si>
+  <si>
+    <t>134402581</t>
+  </si>
+  <si>
+    <t>134402632</t>
+  </si>
+  <si>
+    <t>134402798</t>
+  </si>
+  <si>
+    <t>134402801</t>
+  </si>
+  <si>
+    <t>134402900</t>
+  </si>
+  <si>
+    <t>134402930</t>
+  </si>
+  <si>
+    <t>134402967</t>
+  </si>
+  <si>
+    <t>134403334</t>
+  </si>
+  <si>
+    <t>134403351</t>
+  </si>
+  <si>
+    <t>134403488</t>
+  </si>
+  <si>
+    <t>134403519</t>
+  </si>
+  <si>
+    <t>134403544</t>
+  </si>
+  <si>
+    <t>134403640</t>
+  </si>
+  <si>
+    <t>134403662</t>
+  </si>
+  <si>
+    <t>134403668</t>
+  </si>
+  <si>
+    <t>134403702</t>
+  </si>
+  <si>
+    <t>134403726</t>
+  </si>
+  <si>
+    <t>134403805</t>
+  </si>
+  <si>
+    <t>134403815</t>
+  </si>
+  <si>
+    <t>134403833</t>
+  </si>
+  <si>
+    <t>134403879</t>
+  </si>
+  <si>
+    <t>134403978</t>
+  </si>
+  <si>
+    <t>134404237</t>
+  </si>
+  <si>
+    <t>134404302</t>
+  </si>
+  <si>
+    <t>134404350</t>
+  </si>
+  <si>
+    <t>134404443</t>
+  </si>
+  <si>
+    <t>134404708</t>
+  </si>
+  <si>
+    <t>134404855</t>
+  </si>
+  <si>
+    <t>134405230</t>
+  </si>
+  <si>
+    <t>134405775</t>
+  </si>
+  <si>
+    <t>134405801</t>
+  </si>
+  <si>
+    <t>134406110</t>
+  </si>
+  <si>
+    <t>134406147</t>
+  </si>
+  <si>
+    <t>134406241</t>
+  </si>
+  <si>
+    <t>134406314</t>
+  </si>
+  <si>
+    <t>134406499</t>
+  </si>
+  <si>
+    <t>134406562</t>
+  </si>
+  <si>
+    <t>134406675</t>
+  </si>
+  <si>
+    <t>134406687</t>
+  </si>
+  <si>
+    <t>134406777</t>
+  </si>
+  <si>
+    <t>134406955</t>
+  </si>
+  <si>
+    <t>134407185</t>
+  </si>
+  <si>
+    <t>134407300</t>
+  </si>
+  <si>
+    <t>134407484</t>
+  </si>
+  <si>
+    <t>134407575</t>
+  </si>
+  <si>
+    <t>134407588</t>
+  </si>
+  <si>
+    <t>134407598</t>
+  </si>
+  <si>
+    <t>134407754</t>
+  </si>
+  <si>
+    <t>134407771</t>
+  </si>
+  <si>
+    <t>134407854</t>
+  </si>
+  <si>
+    <t>134407994</t>
+  </si>
+  <si>
+    <t>134408383</t>
+  </si>
+  <si>
+    <t>134408437</t>
+  </si>
+  <si>
+    <t>134408525</t>
+  </si>
+  <si>
+    <t>134408598</t>
+  </si>
+  <si>
+    <t>134408613</t>
+  </si>
+  <si>
+    <t>134408659</t>
+  </si>
+  <si>
+    <t>134408661</t>
+  </si>
+  <si>
+    <t>134408839</t>
+  </si>
+  <si>
+    <t>134408866</t>
+  </si>
+  <si>
+    <t>134408949</t>
+  </si>
+  <si>
+    <t>134409107</t>
+  </si>
+  <si>
+    <t>134409161</t>
+  </si>
+  <si>
+    <t>134409181</t>
+  </si>
+  <si>
+    <t>134409217</t>
+  </si>
+  <si>
+    <t>134409337</t>
+  </si>
+  <si>
+    <t>134409391</t>
+  </si>
+  <si>
+    <t>134409400</t>
+  </si>
+  <si>
+    <t>134409481</t>
+  </si>
+  <si>
+    <t>134409584</t>
+  </si>
+  <si>
+    <t>134409693</t>
+  </si>
+  <si>
+    <t>134409711</t>
+  </si>
+  <si>
+    <t>134409733</t>
+  </si>
+  <si>
+    <t>134409822</t>
+  </si>
+  <si>
+    <t>134409848</t>
+  </si>
+  <si>
+    <t>134410068</t>
+  </si>
+  <si>
+    <t>134410073</t>
+  </si>
+  <si>
+    <t>134410169</t>
+  </si>
+  <si>
+    <t>134410180</t>
+  </si>
+  <si>
+    <t>134410207</t>
+  </si>
+  <si>
+    <t>134410485</t>
+  </si>
+  <si>
+    <t>134410507</t>
+  </si>
+  <si>
+    <t>134410680</t>
+  </si>
+  <si>
+    <t>134410702</t>
+  </si>
+  <si>
+    <t>134410813</t>
+  </si>
+  <si>
+    <t>134410814</t>
+  </si>
+  <si>
+    <t>134410842</t>
+  </si>
+  <si>
+    <t>134410861</t>
+  </si>
+  <si>
+    <t>134410891</t>
+  </si>
+  <si>
+    <t>134410935</t>
+  </si>
+  <si>
+    <t>134410955</t>
+  </si>
+  <si>
+    <t>134410972</t>
+  </si>
+  <si>
+    <t>134411000</t>
+  </si>
+  <si>
+    <t>134411072</t>
+  </si>
+  <si>
+    <t>134411165</t>
+  </si>
+  <si>
+    <t>134411220</t>
+  </si>
+  <si>
+    <t>134411328</t>
+  </si>
+  <si>
+    <t>134411382</t>
+  </si>
+  <si>
+    <t>134411421</t>
+  </si>
+  <si>
+    <t>134411477</t>
+  </si>
+  <si>
+    <t>134411525</t>
+  </si>
+  <si>
+    <t>134411537</t>
+  </si>
+  <si>
+    <t>134411588</t>
+  </si>
+  <si>
+    <t>134411605</t>
+  </si>
+  <si>
+    <t>134411670</t>
+  </si>
+  <si>
+    <t>134411713</t>
+  </si>
+  <si>
+    <t>134411762</t>
+  </si>
+  <si>
+    <t>134411944</t>
+  </si>
+  <si>
+    <t>134412030</t>
+  </si>
+  <si>
+    <t>134412067</t>
+  </si>
+  <si>
+    <t>134412105</t>
+  </si>
+  <si>
+    <t>134412134</t>
+  </si>
+  <si>
+    <t>134412191</t>
+  </si>
+  <si>
+    <t>134412244</t>
+  </si>
+  <si>
+    <t>134412412</t>
+  </si>
+  <si>
+    <t>134412419</t>
+  </si>
+  <si>
+    <t>134412422</t>
+  </si>
+  <si>
+    <t>134412429</t>
+  </si>
+  <si>
+    <t>134412432</t>
+  </si>
+  <si>
+    <t>134412541</t>
+  </si>
+  <si>
+    <t>134412724</t>
+  </si>
+  <si>
+    <t>134412923</t>
+  </si>
+  <si>
+    <t>134412981</t>
+  </si>
+  <si>
+    <t>134413032</t>
+  </si>
+  <si>
+    <t>134413079</t>
+  </si>
+  <si>
+    <t>134413250</t>
+  </si>
+  <si>
+    <t>134413262</t>
+  </si>
+  <si>
+    <t>134413536</t>
+  </si>
+  <si>
+    <t>134413542</t>
+  </si>
+  <si>
+    <t>134413592</t>
+  </si>
+  <si>
+    <t>134413813</t>
+  </si>
+  <si>
+    <t>134413909</t>
+  </si>
+  <si>
+    <t>134414066</t>
+  </si>
+  <si>
+    <t>134414071</t>
+  </si>
+  <si>
+    <t>134414543</t>
+  </si>
+  <si>
+    <t>134414565</t>
+  </si>
+  <si>
+    <t>134414567</t>
+  </si>
+  <si>
+    <t>134414594</t>
+  </si>
+  <si>
+    <t>134414650</t>
+  </si>
+  <si>
+    <t>134415534</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3491,6 +3536,126 @@
         <v>4</v>
       </c>
     </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E0FE67-E24C-449C-959E-59B6A20589CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580CC4EC-A70A-4198-9625-7F19E0F6AC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="218">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,574 +45,643 @@
     <t>.</t>
   </si>
   <si>
-    <t>129712827</t>
-  </si>
-  <si>
-    <t>129764998</t>
-  </si>
-  <si>
-    <t>129819143</t>
-  </si>
-  <si>
-    <t>130086787</t>
-  </si>
-  <si>
-    <t>130345885</t>
-  </si>
-  <si>
-    <t>130637868</t>
-  </si>
-  <si>
-    <t>130646974</t>
-  </si>
-  <si>
-    <t>130741141</t>
-  </si>
-  <si>
-    <t>130856750</t>
-  </si>
-  <si>
-    <t>130883370</t>
-  </si>
-  <si>
-    <t>130884494</t>
-  </si>
-  <si>
-    <t>130906283</t>
-  </si>
-  <si>
-    <t>130941673</t>
-  </si>
-  <si>
-    <t>131194704</t>
-  </si>
-  <si>
-    <t>131290365</t>
-  </si>
-  <si>
-    <t>131837828</t>
-  </si>
-  <si>
-    <t>131928127</t>
-  </si>
-  <si>
-    <t>132493844</t>
-  </si>
-  <si>
-    <t>133037286</t>
-  </si>
-  <si>
-    <t>133422011</t>
-  </si>
-  <si>
-    <t>133685649</t>
-  </si>
-  <si>
-    <t>133901570</t>
-  </si>
-  <si>
-    <t>134374440</t>
-  </si>
-  <si>
-    <t>134443005</t>
-  </si>
-  <si>
-    <t>134443263</t>
-  </si>
-  <si>
-    <t>134443364</t>
-  </si>
-  <si>
-    <t>134443657</t>
-  </si>
-  <si>
-    <t>134443708</t>
-  </si>
-  <si>
-    <t>134444121</t>
-  </si>
-  <si>
-    <t>134444226</t>
-  </si>
-  <si>
-    <t>134444292</t>
-  </si>
-  <si>
-    <t>134444696</t>
-  </si>
-  <si>
-    <t>134444701</t>
-  </si>
-  <si>
-    <t>134444754</t>
-  </si>
-  <si>
-    <t>134444788</t>
-  </si>
-  <si>
-    <t>134444834</t>
-  </si>
-  <si>
-    <t>134444865</t>
-  </si>
-  <si>
-    <t>134445486</t>
-  </si>
-  <si>
-    <t>134445488</t>
-  </si>
-  <si>
-    <t>134445544</t>
-  </si>
-  <si>
-    <t>134445813</t>
-  </si>
-  <si>
-    <t>134445886</t>
-  </si>
-  <si>
-    <t>134446261</t>
-  </si>
-  <si>
-    <t>134446280</t>
-  </si>
-  <si>
-    <t>134446331</t>
-  </si>
-  <si>
-    <t>134446356</t>
-  </si>
-  <si>
-    <t>134446394</t>
-  </si>
-  <si>
-    <t>134446466</t>
-  </si>
-  <si>
-    <t>134446485</t>
-  </si>
-  <si>
-    <t>134446541</t>
-  </si>
-  <si>
-    <t>134446594</t>
-  </si>
-  <si>
-    <t>134446742</t>
-  </si>
-  <si>
-    <t>134446864</t>
-  </si>
-  <si>
-    <t>134446865</t>
-  </si>
-  <si>
-    <t>134447077</t>
-  </si>
-  <si>
-    <t>134447184</t>
-  </si>
-  <si>
-    <t>134447238</t>
-  </si>
-  <si>
-    <t>134447383</t>
-  </si>
-  <si>
-    <t>134447471</t>
-  </si>
-  <si>
-    <t>134447520</t>
-  </si>
-  <si>
-    <t>134447927</t>
-  </si>
-  <si>
-    <t>134448216</t>
-  </si>
-  <si>
-    <t>134448318</t>
-  </si>
-  <si>
-    <t>134448510</t>
-  </si>
-  <si>
-    <t>134448589</t>
-  </si>
-  <si>
-    <t>134448876</t>
-  </si>
-  <si>
-    <t>134449011</t>
-  </si>
-  <si>
-    <t>134449118</t>
-  </si>
-  <si>
-    <t>134449696</t>
-  </si>
-  <si>
-    <t>134449937</t>
-  </si>
-  <si>
-    <t>134449964</t>
-  </si>
-  <si>
-    <t>134450174</t>
-  </si>
-  <si>
-    <t>134450191</t>
-  </si>
-  <si>
-    <t>134450689</t>
-  </si>
-  <si>
-    <t>134450716</t>
-  </si>
-  <si>
-    <t>134451029</t>
-  </si>
-  <si>
-    <t>134451057</t>
-  </si>
-  <si>
-    <t>134451099</t>
-  </si>
-  <si>
-    <t>134451172</t>
-  </si>
-  <si>
-    <t>134451365</t>
-  </si>
-  <si>
-    <t>134451753</t>
-  </si>
-  <si>
-    <t>134451954</t>
-  </si>
-  <si>
-    <t>134452066</t>
-  </si>
-  <si>
-    <t>134452141</t>
-  </si>
-  <si>
-    <t>134452372</t>
-  </si>
-  <si>
-    <t>134452390</t>
-  </si>
-  <si>
-    <t>134452649</t>
-  </si>
-  <si>
-    <t>134452712</t>
-  </si>
-  <si>
-    <t>134452714</t>
-  </si>
-  <si>
-    <t>134452792</t>
-  </si>
-  <si>
-    <t>134452800</t>
-  </si>
-  <si>
-    <t>134452829</t>
-  </si>
-  <si>
-    <t>134453330</t>
-  </si>
-  <si>
-    <t>134453455</t>
-  </si>
-  <si>
-    <t>134453854</t>
-  </si>
-  <si>
-    <t>134453911</t>
-  </si>
-  <si>
-    <t>134453941</t>
-  </si>
-  <si>
-    <t>134454101</t>
-  </si>
-  <si>
-    <t>134454298</t>
-  </si>
-  <si>
-    <t>134454383</t>
-  </si>
-  <si>
-    <t>134454608</t>
-  </si>
-  <si>
-    <t>134454783</t>
-  </si>
-  <si>
-    <t>134454849</t>
-  </si>
-  <si>
-    <t>134454921</t>
-  </si>
-  <si>
-    <t>134454926</t>
-  </si>
-  <si>
-    <t>134454990</t>
-  </si>
-  <si>
-    <t>134455011</t>
-  </si>
-  <si>
-    <t>134455092</t>
-  </si>
-  <si>
-    <t>134455166</t>
-  </si>
-  <si>
-    <t>134455356</t>
-  </si>
-  <si>
-    <t>134455359</t>
-  </si>
-  <si>
-    <t>134455689</t>
-  </si>
-  <si>
-    <t>134456023</t>
-  </si>
-  <si>
-    <t>134456032</t>
-  </si>
-  <si>
-    <t>134456049</t>
-  </si>
-  <si>
-    <t>134456363</t>
-  </si>
-  <si>
-    <t>134456403</t>
-  </si>
-  <si>
-    <t>134456552</t>
-  </si>
-  <si>
-    <t>134456597</t>
-  </si>
-  <si>
-    <t>134456742</t>
-  </si>
-  <si>
-    <t>134456743</t>
-  </si>
-  <si>
-    <t>134456759</t>
-  </si>
-  <si>
-    <t>134457027</t>
-  </si>
-  <si>
-    <t>134457196</t>
-  </si>
-  <si>
-    <t>134457366</t>
-  </si>
-  <si>
-    <t>134457571</t>
-  </si>
-  <si>
-    <t>134457596</t>
-  </si>
-  <si>
-    <t>134457871</t>
-  </si>
-  <si>
-    <t>134457919</t>
-  </si>
-  <si>
-    <t>134458133</t>
-  </si>
-  <si>
-    <t>134458352</t>
-  </si>
-  <si>
-    <t>134458555</t>
-  </si>
-  <si>
-    <t>134458643</t>
-  </si>
-  <si>
-    <t>134458683</t>
-  </si>
-  <si>
-    <t>134458744</t>
-  </si>
-  <si>
-    <t>134458809</t>
-  </si>
-  <si>
-    <t>134458876</t>
-  </si>
-  <si>
-    <t>134459292</t>
-  </si>
-  <si>
-    <t>134459637</t>
-  </si>
-  <si>
-    <t>134459642</t>
-  </si>
-  <si>
-    <t>134459736</t>
-  </si>
-  <si>
-    <t>134459827</t>
-  </si>
-  <si>
-    <t>134459932</t>
-  </si>
-  <si>
-    <t>134460086</t>
-  </si>
-  <si>
-    <t>134460094</t>
-  </si>
-  <si>
-    <t>134460217</t>
-  </si>
-  <si>
-    <t>134460323</t>
-  </si>
-  <si>
-    <t>134460328</t>
-  </si>
-  <si>
-    <t>134460410</t>
-  </si>
-  <si>
-    <t>134460493</t>
-  </si>
-  <si>
-    <t>134460660</t>
-  </si>
-  <si>
-    <t>134460706</t>
-  </si>
-  <si>
-    <t>134460803</t>
-  </si>
-  <si>
-    <t>134460810</t>
-  </si>
-  <si>
-    <t>134460811</t>
-  </si>
-  <si>
-    <t>134460865</t>
-  </si>
-  <si>
-    <t>134460960</t>
-  </si>
-  <si>
-    <t>134461002</t>
-  </si>
-  <si>
-    <t>134461020</t>
-  </si>
-  <si>
-    <t>134461194</t>
-  </si>
-  <si>
-    <t>134461306</t>
-  </si>
-  <si>
-    <t>134461325</t>
-  </si>
-  <si>
-    <t>134461327</t>
-  </si>
-  <si>
-    <t>134461480</t>
-  </si>
-  <si>
-    <t>134461542</t>
-  </si>
-  <si>
-    <t>134461693</t>
-  </si>
-  <si>
-    <t>134461772</t>
-  </si>
-  <si>
-    <t>134461930</t>
-  </si>
-  <si>
-    <t>134461971</t>
-  </si>
-  <si>
-    <t>134462039</t>
-  </si>
-  <si>
-    <t>134462269</t>
-  </si>
-  <si>
-    <t>134462330</t>
-  </si>
-  <si>
-    <t>134462378</t>
-  </si>
-  <si>
-    <t>134462489</t>
-  </si>
-  <si>
-    <t>134462520</t>
-  </si>
-  <si>
-    <t>134462585</t>
-  </si>
-  <si>
-    <t>134462676</t>
-  </si>
-  <si>
-    <t>134462693</t>
-  </si>
-  <si>
-    <t>134462755</t>
-  </si>
-  <si>
-    <t>134462766</t>
-  </si>
-  <si>
-    <t>134462891</t>
-  </si>
-  <si>
-    <t>134463374</t>
-  </si>
-  <si>
-    <t>134463399</t>
-  </si>
-  <si>
-    <t>134463477</t>
-  </si>
-  <si>
-    <t>134463486</t>
-  </si>
-  <si>
-    <t>134463900</t>
-  </si>
-  <si>
-    <t>134463992</t>
-  </si>
-  <si>
-    <t>134464141</t>
-  </si>
-  <si>
-    <t>134464664</t>
-  </si>
-  <si>
-    <t>134465004</t>
+    <t>129803867</t>
+  </si>
+  <si>
+    <t>130085298</t>
+  </si>
+  <si>
+    <t>130328230</t>
+  </si>
+  <si>
+    <t>130361963</t>
+  </si>
+  <si>
+    <t>130395476</t>
+  </si>
+  <si>
+    <t>130680182</t>
+  </si>
+  <si>
+    <t>130785598</t>
+  </si>
+  <si>
+    <t>131281345</t>
+  </si>
+  <si>
+    <t>131298298</t>
+  </si>
+  <si>
+    <t>131470156</t>
+  </si>
+  <si>
+    <t>131484293</t>
+  </si>
+  <si>
+    <t>131640533</t>
+  </si>
+  <si>
+    <t>131878282</t>
+  </si>
+  <si>
+    <t>131951122</t>
+  </si>
+  <si>
+    <t>132040510</t>
+  </si>
+  <si>
+    <t>132112028</t>
+  </si>
+  <si>
+    <t>132168011</t>
+  </si>
+  <si>
+    <t>132364310</t>
+  </si>
+  <si>
+    <t>132395912</t>
+  </si>
+  <si>
+    <t>132661870</t>
+  </si>
+  <si>
+    <t>132777487</t>
+  </si>
+  <si>
+    <t>132829489</t>
+  </si>
+  <si>
+    <t>133060437</t>
+  </si>
+  <si>
+    <t>133210770</t>
+  </si>
+  <si>
+    <t>133737515</t>
+  </si>
+  <si>
+    <t>133865395</t>
+  </si>
+  <si>
+    <t>133877028</t>
+  </si>
+  <si>
+    <t>133901105</t>
+  </si>
+  <si>
+    <t>134465138</t>
+  </si>
+  <si>
+    <t>134465202</t>
+  </si>
+  <si>
+    <t>134465263</t>
+  </si>
+  <si>
+    <t>134465483</t>
+  </si>
+  <si>
+    <t>134465542</t>
+  </si>
+  <si>
+    <t>134465660</t>
+  </si>
+  <si>
+    <t>134465757</t>
+  </si>
+  <si>
+    <t>134465919</t>
+  </si>
+  <si>
+    <t>134466008</t>
+  </si>
+  <si>
+    <t>134466034</t>
+  </si>
+  <si>
+    <t>134466142</t>
+  </si>
+  <si>
+    <t>134466246</t>
+  </si>
+  <si>
+    <t>134466455</t>
+  </si>
+  <si>
+    <t>134466498</t>
+  </si>
+  <si>
+    <t>134466577</t>
+  </si>
+  <si>
+    <t>134466768</t>
+  </si>
+  <si>
+    <t>134466954</t>
+  </si>
+  <si>
+    <t>134467161</t>
+  </si>
+  <si>
+    <t>134467497</t>
+  </si>
+  <si>
+    <t>134467621</t>
+  </si>
+  <si>
+    <t>134467824</t>
+  </si>
+  <si>
+    <t>134467844</t>
+  </si>
+  <si>
+    <t>134467872</t>
+  </si>
+  <si>
+    <t>134467942</t>
+  </si>
+  <si>
+    <t>134467976</t>
+  </si>
+  <si>
+    <t>134468064</t>
+  </si>
+  <si>
+    <t>134468170</t>
+  </si>
+  <si>
+    <t>134468287</t>
+  </si>
+  <si>
+    <t>134468430</t>
+  </si>
+  <si>
+    <t>134468472</t>
+  </si>
+  <si>
+    <t>134468480</t>
+  </si>
+  <si>
+    <t>134468506</t>
+  </si>
+  <si>
+    <t>134468699</t>
+  </si>
+  <si>
+    <t>134468713</t>
+  </si>
+  <si>
+    <t>134468718</t>
+  </si>
+  <si>
+    <t>134468982</t>
+  </si>
+  <si>
+    <t>134469092</t>
+  </si>
+  <si>
+    <t>134469227</t>
+  </si>
+  <si>
+    <t>134469267</t>
+  </si>
+  <si>
+    <t>134469290</t>
+  </si>
+  <si>
+    <t>134469318</t>
+  </si>
+  <si>
+    <t>134469329</t>
+  </si>
+  <si>
+    <t>134469377</t>
+  </si>
+  <si>
+    <t>134469467</t>
+  </si>
+  <si>
+    <t>134470205</t>
+  </si>
+  <si>
+    <t>134470210</t>
+  </si>
+  <si>
+    <t>134470437</t>
+  </si>
+  <si>
+    <t>134470744</t>
+  </si>
+  <si>
+    <t>134471057</t>
+  </si>
+  <si>
+    <t>134471122</t>
+  </si>
+  <si>
+    <t>134471152</t>
+  </si>
+  <si>
+    <t>134471308</t>
+  </si>
+  <si>
+    <t>134471359</t>
+  </si>
+  <si>
+    <t>134471695</t>
+  </si>
+  <si>
+    <t>134471841</t>
+  </si>
+  <si>
+    <t>134471893</t>
+  </si>
+  <si>
+    <t>134472359</t>
+  </si>
+  <si>
+    <t>134472680</t>
+  </si>
+  <si>
+    <t>134472712</t>
+  </si>
+  <si>
+    <t>134472769</t>
+  </si>
+  <si>
+    <t>134472853</t>
+  </si>
+  <si>
+    <t>134472971</t>
+  </si>
+  <si>
+    <t>134473259</t>
+  </si>
+  <si>
+    <t>134473376</t>
+  </si>
+  <si>
+    <t>134473442</t>
+  </si>
+  <si>
+    <t>134473447</t>
+  </si>
+  <si>
+    <t>134473463</t>
+  </si>
+  <si>
+    <t>134473470</t>
+  </si>
+  <si>
+    <t>134473484</t>
+  </si>
+  <si>
+    <t>134473502</t>
+  </si>
+  <si>
+    <t>134473614</t>
+  </si>
+  <si>
+    <t>134473692</t>
+  </si>
+  <si>
+    <t>134473702</t>
+  </si>
+  <si>
+    <t>134473797</t>
+  </si>
+  <si>
+    <t>134473852</t>
+  </si>
+  <si>
+    <t>134473911</t>
+  </si>
+  <si>
+    <t>134474029</t>
+  </si>
+  <si>
+    <t>134474114</t>
+  </si>
+  <si>
+    <t>134474219</t>
+  </si>
+  <si>
+    <t>134474264</t>
+  </si>
+  <si>
+    <t>134474345</t>
+  </si>
+  <si>
+    <t>134474351</t>
+  </si>
+  <si>
+    <t>134474382</t>
+  </si>
+  <si>
+    <t>134474505</t>
+  </si>
+  <si>
+    <t>134474619</t>
+  </si>
+  <si>
+    <t>134474789</t>
+  </si>
+  <si>
+    <t>134474821</t>
+  </si>
+  <si>
+    <t>134474867</t>
+  </si>
+  <si>
+    <t>134474914</t>
+  </si>
+  <si>
+    <t>134475213</t>
+  </si>
+  <si>
+    <t>134475316</t>
+  </si>
+  <si>
+    <t>134475334</t>
+  </si>
+  <si>
+    <t>134475494</t>
+  </si>
+  <si>
+    <t>134475602</t>
+  </si>
+  <si>
+    <t>134475752</t>
+  </si>
+  <si>
+    <t>134475899</t>
+  </si>
+  <si>
+    <t>134476116</t>
+  </si>
+  <si>
+    <t>134476331</t>
+  </si>
+  <si>
+    <t>134476447</t>
+  </si>
+  <si>
+    <t>134476674</t>
+  </si>
+  <si>
+    <t>134476767</t>
+  </si>
+  <si>
+    <t>134476848</t>
+  </si>
+  <si>
+    <t>134477279</t>
+  </si>
+  <si>
+    <t>134477282</t>
+  </si>
+  <si>
+    <t>134477649</t>
+  </si>
+  <si>
+    <t>134477781</t>
+  </si>
+  <si>
+    <t>134477892</t>
+  </si>
+  <si>
+    <t>134477896</t>
+  </si>
+  <si>
+    <t>134478265</t>
+  </si>
+  <si>
+    <t>134478289</t>
+  </si>
+  <si>
+    <t>134478290</t>
+  </si>
+  <si>
+    <t>134478482</t>
+  </si>
+  <si>
+    <t>134478532</t>
+  </si>
+  <si>
+    <t>134478584</t>
+  </si>
+  <si>
+    <t>134478747</t>
+  </si>
+  <si>
+    <t>134478856</t>
+  </si>
+  <si>
+    <t>134479113</t>
+  </si>
+  <si>
+    <t>134479181</t>
+  </si>
+  <si>
+    <t>134479299</t>
+  </si>
+  <si>
+    <t>134479704</t>
+  </si>
+  <si>
+    <t>134479769</t>
+  </si>
+  <si>
+    <t>134479858</t>
+  </si>
+  <si>
+    <t>134479869</t>
+  </si>
+  <si>
+    <t>134479941</t>
+  </si>
+  <si>
+    <t>134479990</t>
+  </si>
+  <si>
+    <t>134480003</t>
+  </si>
+  <si>
+    <t>134480290</t>
+  </si>
+  <si>
+    <t>134480439</t>
+  </si>
+  <si>
+    <t>134480517</t>
+  </si>
+  <si>
+    <t>134480548</t>
+  </si>
+  <si>
+    <t>134480555</t>
+  </si>
+  <si>
+    <t>134480576</t>
+  </si>
+  <si>
+    <t>134480630</t>
+  </si>
+  <si>
+    <t>134480669</t>
+  </si>
+  <si>
+    <t>134480863</t>
+  </si>
+  <si>
+    <t>134480995</t>
+  </si>
+  <si>
+    <t>134481415</t>
+  </si>
+  <si>
+    <t>134481474</t>
+  </si>
+  <si>
+    <t>134481622</t>
+  </si>
+  <si>
+    <t>134481642</t>
+  </si>
+  <si>
+    <t>134481748</t>
+  </si>
+  <si>
+    <t>134481778</t>
+  </si>
+  <si>
+    <t>134481793</t>
+  </si>
+  <si>
+    <t>134481861</t>
+  </si>
+  <si>
+    <t>134482166</t>
+  </si>
+  <si>
+    <t>134482236</t>
+  </si>
+  <si>
+    <t>134482430</t>
+  </si>
+  <si>
+    <t>134483061</t>
+  </si>
+  <si>
+    <t>134483225</t>
+  </si>
+  <si>
+    <t>134483238</t>
+  </si>
+  <si>
+    <t>134483240</t>
+  </si>
+  <si>
+    <t>134483331</t>
+  </si>
+  <si>
+    <t>134483335</t>
+  </si>
+  <si>
+    <t>134483421</t>
+  </si>
+  <si>
+    <t>134483515</t>
+  </si>
+  <si>
+    <t>134483704</t>
+  </si>
+  <si>
+    <t>134483853</t>
+  </si>
+  <si>
+    <t>134484101</t>
+  </si>
+  <si>
+    <t>134484305</t>
+  </si>
+  <si>
+    <t>134484372</t>
+  </si>
+  <si>
+    <t>134484497</t>
+  </si>
+  <si>
+    <t>134484507</t>
+  </si>
+  <si>
+    <t>134484517</t>
+  </si>
+  <si>
+    <t>134484734</t>
+  </si>
+  <si>
+    <t>134484891</t>
+  </si>
+  <si>
+    <t>134485043</t>
+  </si>
+  <si>
+    <t>134485103</t>
+  </si>
+  <si>
+    <t>134485142</t>
+  </si>
+  <si>
+    <t>134485410</t>
+  </si>
+  <si>
+    <t>134485428</t>
+  </si>
+  <si>
+    <t>134485449</t>
+  </si>
+  <si>
+    <t>134485453</t>
+  </si>
+  <si>
+    <t>134485489</t>
+  </si>
+  <si>
+    <t>134485603</t>
+  </si>
+  <si>
+    <t>134485642</t>
+  </si>
+  <si>
+    <t>134485726</t>
+  </si>
+  <si>
+    <t>134485808</t>
+  </si>
+  <si>
+    <t>134485948</t>
+  </si>
+  <si>
+    <t>134486228</t>
+  </si>
+  <si>
+    <t>134486503</t>
+  </si>
+  <si>
+    <t>134486608</t>
+  </si>
+  <si>
+    <t>134486611</t>
+  </si>
+  <si>
+    <t>134486621</t>
+  </si>
+  <si>
+    <t>134487071</t>
+  </si>
+  <si>
+    <t>134487695</t>
   </si>
 </sst>
 </file>
@@ -3128,867 +3197,1206 @@
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="4"/>
-      <c r="B192" s="6"/>
+      <c r="A192" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C192" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="4"/>
-      <c r="B193" s="6"/>
+      <c r="A193" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C193" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="4"/>
-      <c r="B194" s="6"/>
+      <c r="A194" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C194" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="4"/>
-      <c r="B195" s="6"/>
+      <c r="A195" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C195" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="4"/>
-      <c r="B196" s="6"/>
+      <c r="A196" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C196" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="4"/>
-      <c r="B197" s="6"/>
+      <c r="A197" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C197" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="4"/>
-      <c r="B198" s="6"/>
+      <c r="A198" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C198" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="4"/>
-      <c r="B199" s="6"/>
+      <c r="A199" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C199" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="4"/>
-      <c r="B200" s="6"/>
+      <c r="A200" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C200" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="4"/>
-      <c r="B201" s="6"/>
+      <c r="A201" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C201" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="4"/>
-      <c r="B202" s="6"/>
+      <c r="A202" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C202" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="4"/>
-      <c r="B203" s="6"/>
+      <c r="A203" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C203" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="4"/>
-      <c r="B204" s="6"/>
+      <c r="A204" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C204" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="4"/>
-      <c r="B205" s="6"/>
+      <c r="A205" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C205" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B206" s="6"/>
+      <c r="A206" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C206" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B207" s="6"/>
+      <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C207" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B208" s="6"/>
+      <c r="A208" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C208" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B209" s="6"/>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C209" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B210" s="6"/>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C210" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B211" s="6"/>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C211" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B212" s="6"/>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C212" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B213" s="6"/>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C213" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B214" s="6"/>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C214" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B215" s="6"/>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C215" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B216" s="6"/>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C216" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B217" s="6"/>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C217" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B218" s="6"/>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C218" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B219" s="6"/>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C219" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B220" s="6"/>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C220" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B221" s="6"/>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C221" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B222" s="6"/>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C222" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B223" s="6"/>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C223" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B224" s="6"/>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C224" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B225" s="6"/>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C225" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B226" s="6"/>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C226" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B227" s="6"/>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C227" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B228" s="6"/>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C228" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B229" s="6"/>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C229" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B230" s="6"/>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C230" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B231" s="6"/>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C231" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B232" s="6"/>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C232" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B233" s="6"/>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C233" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B234" s="6"/>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C234" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B235" s="6"/>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C235" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B236" s="6"/>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C236" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B237" s="6"/>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C237" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B238" s="6"/>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C238" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B239" s="6"/>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C239" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="240" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B240" s="6"/>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C240" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B241" s="6"/>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C241" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B242" s="6"/>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C242" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="243" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B243" s="6"/>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C243" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="244" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B244" s="6"/>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C244" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="245" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B245" s="6"/>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C245" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="246" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B246" s="6"/>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C246" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="247" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B247" s="6"/>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C247" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="248" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B248" s="6"/>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C248" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="249" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B249" s="6"/>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C249" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="250" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B250" s="6"/>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C250" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="251" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B251" s="6"/>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C251" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="252" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B252" s="6"/>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C252" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="253" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B253" s="6"/>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C253" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="254" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B254" s="6"/>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C254" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="255" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B255" s="6"/>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C255" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="256" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B256" s="6"/>
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C256" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="257" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B257" s="6"/>
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C257" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="258" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B258" s="6"/>
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C258" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="259" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B259" s="6"/>
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C259" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="260" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B260" s="6"/>
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C260" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="261" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B261" s="6"/>
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C261" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="262" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B262" s="6"/>
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C262" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="263" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B263" s="6"/>
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C263" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="264" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B264" s="6"/>
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C264" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="265" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B265" s="6"/>
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C265" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="266" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B266" s="6"/>
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C266" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="267" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B267" s="6"/>
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C267" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="268" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B268" s="6"/>
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C268" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="269" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B269" s="6"/>
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C269" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="270" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B270" s="6"/>
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C270" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="271" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B271" s="6"/>
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C271" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="272" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B272" s="6"/>
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C272" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="273" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B273" s="6"/>
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C273" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="274" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B274" s="6"/>
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C274" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="275" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B275" s="6"/>
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C275" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="276" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B276" s="6"/>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C276" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="277" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B277" s="6"/>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C277" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="278" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B278" s="6"/>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C278" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="279" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B279" s="6"/>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C279" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="280" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B280" s="6"/>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C280" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="281" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B281" s="6"/>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C281" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="282" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B282" s="6"/>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C282" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="283" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B283" s="6"/>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C283" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="284" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B284" s="6"/>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C284" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="285" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B285" s="6"/>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C285" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="286" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B286" s="6"/>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C286" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="287" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B287" s="6"/>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C287" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="288" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B288" s="6"/>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C288" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="289" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B289" s="6"/>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C289" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="290" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B290" s="6"/>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C290" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="291" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B291" s="6"/>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C291" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="292" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B292" s="6"/>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C292" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="293" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B293" s="6"/>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C293" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="294" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B294" s="6"/>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C294" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="295" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B295" s="6"/>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C295" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="296" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B296" s="6"/>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C296" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="297" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B297" s="6"/>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C297" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="298" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B298" s="6"/>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C298" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="299" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B299" s="6"/>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C299" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="300" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B300" s="6"/>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C300" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="301" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B301" s="6"/>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C301" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="302" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B302" s="6"/>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C302" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="303" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B303" s="6"/>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C303" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="304" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B304" s="6"/>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C304" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="305" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B305" s="6"/>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C305" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="306" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B306" s="6"/>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C306" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="307" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B307" s="6"/>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C307" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="308" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B308" s="6"/>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C308" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="309" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B309" s="6"/>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C309" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="310" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B310" s="6"/>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C310" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="311" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B311" s="6"/>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C311" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="312" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B312" s="6"/>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C312" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="313" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B313" s="6"/>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C313" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="314" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B314" s="6"/>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C314" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="315" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B315" s="6"/>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C315" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="316" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B316" s="6"/>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C316" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="317" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B317" s="6"/>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C317" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="318" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B318" s="6"/>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C318" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="319" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B319" s="6"/>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C319" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="320" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B320" s="6"/>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C320" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="321" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B321" s="6"/>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C321" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="322" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B322" s="6"/>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C322" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="323" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B323" s="6"/>
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C323" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="324" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B324" s="6"/>
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C324" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="325" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B325" s="6"/>
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C325" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="326" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B326" s="6"/>
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C326" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="327" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B327" s="6"/>
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C327" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="328" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B328" s="6"/>
+      <c r="B328" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C328" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="329" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B329" s="6"/>
+      <c r="B329" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C329" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="330" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B330" s="6"/>
+      <c r="B330" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C330" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="331" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B331" s="6"/>
+      <c r="B331" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C331" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="332" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B332" s="6"/>
+      <c r="B332" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C332" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="333" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B333" s="6"/>
+      <c r="B333" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C333" s="5" t="s">
         <v>4</v>
       </c>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580CC4EC-A70A-4198-9625-7F19E0F6AC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAB78F7-D6EE-42E5-8FE8-94A70B80DEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="279">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,643 +45,826 @@
     <t>.</t>
   </si>
   <si>
-    <t>129803867</t>
-  </si>
-  <si>
-    <t>130085298</t>
-  </si>
-  <si>
-    <t>130328230</t>
-  </si>
-  <si>
-    <t>130361963</t>
-  </si>
-  <si>
-    <t>130395476</t>
-  </si>
-  <si>
-    <t>130680182</t>
-  </si>
-  <si>
-    <t>130785598</t>
-  </si>
-  <si>
-    <t>131281345</t>
-  </si>
-  <si>
-    <t>131298298</t>
-  </si>
-  <si>
-    <t>131470156</t>
-  </si>
-  <si>
-    <t>131484293</t>
-  </si>
-  <si>
-    <t>131640533</t>
-  </si>
-  <si>
-    <t>131878282</t>
-  </si>
-  <si>
-    <t>131951122</t>
-  </si>
-  <si>
-    <t>132040510</t>
-  </si>
-  <si>
-    <t>132112028</t>
-  </si>
-  <si>
-    <t>132168011</t>
-  </si>
-  <si>
-    <t>132364310</t>
-  </si>
-  <si>
-    <t>132395912</t>
-  </si>
-  <si>
-    <t>132661870</t>
-  </si>
-  <si>
-    <t>132777487</t>
-  </si>
-  <si>
-    <t>132829489</t>
-  </si>
-  <si>
-    <t>133060437</t>
-  </si>
-  <si>
-    <t>133210770</t>
-  </si>
-  <si>
-    <t>133737515</t>
-  </si>
-  <si>
-    <t>133865395</t>
-  </si>
-  <si>
-    <t>133877028</t>
-  </si>
-  <si>
-    <t>133901105</t>
-  </si>
-  <si>
-    <t>134465138</t>
-  </si>
-  <si>
-    <t>134465202</t>
-  </si>
-  <si>
-    <t>134465263</t>
-  </si>
-  <si>
-    <t>134465483</t>
-  </si>
-  <si>
-    <t>134465542</t>
-  </si>
-  <si>
-    <t>134465660</t>
-  </si>
-  <si>
-    <t>134465757</t>
-  </si>
-  <si>
-    <t>134465919</t>
-  </si>
-  <si>
-    <t>134466008</t>
-  </si>
-  <si>
-    <t>134466034</t>
-  </si>
-  <si>
-    <t>134466142</t>
-  </si>
-  <si>
-    <t>134466246</t>
-  </si>
-  <si>
-    <t>134466455</t>
-  </si>
-  <si>
-    <t>134466498</t>
-  </si>
-  <si>
-    <t>134466577</t>
-  </si>
-  <si>
-    <t>134466768</t>
-  </si>
-  <si>
-    <t>134466954</t>
-  </si>
-  <si>
-    <t>134467161</t>
-  </si>
-  <si>
-    <t>134467497</t>
-  </si>
-  <si>
-    <t>134467621</t>
-  </si>
-  <si>
-    <t>134467824</t>
-  </si>
-  <si>
-    <t>134467844</t>
-  </si>
-  <si>
-    <t>134467872</t>
-  </si>
-  <si>
-    <t>134467942</t>
-  </si>
-  <si>
-    <t>134467976</t>
-  </si>
-  <si>
-    <t>134468064</t>
-  </si>
-  <si>
-    <t>134468170</t>
-  </si>
-  <si>
-    <t>134468287</t>
-  </si>
-  <si>
-    <t>134468430</t>
-  </si>
-  <si>
-    <t>134468472</t>
-  </si>
-  <si>
-    <t>134468480</t>
-  </si>
-  <si>
-    <t>134468506</t>
-  </si>
-  <si>
-    <t>134468699</t>
-  </si>
-  <si>
-    <t>134468713</t>
-  </si>
-  <si>
-    <t>134468718</t>
-  </si>
-  <si>
-    <t>134468982</t>
-  </si>
-  <si>
-    <t>134469092</t>
-  </si>
-  <si>
-    <t>134469227</t>
-  </si>
-  <si>
-    <t>134469267</t>
-  </si>
-  <si>
-    <t>134469290</t>
-  </si>
-  <si>
-    <t>134469318</t>
-  </si>
-  <si>
-    <t>134469329</t>
-  </si>
-  <si>
-    <t>134469377</t>
-  </si>
-  <si>
-    <t>134469467</t>
-  </si>
-  <si>
-    <t>134470205</t>
-  </si>
-  <si>
-    <t>134470210</t>
-  </si>
-  <si>
-    <t>134470437</t>
-  </si>
-  <si>
-    <t>134470744</t>
-  </si>
-  <si>
-    <t>134471057</t>
-  </si>
-  <si>
-    <t>134471122</t>
-  </si>
-  <si>
-    <t>134471152</t>
-  </si>
-  <si>
-    <t>134471308</t>
-  </si>
-  <si>
-    <t>134471359</t>
-  </si>
-  <si>
-    <t>134471695</t>
-  </si>
-  <si>
-    <t>134471841</t>
-  </si>
-  <si>
-    <t>134471893</t>
-  </si>
-  <si>
-    <t>134472359</t>
-  </si>
-  <si>
-    <t>134472680</t>
-  </si>
-  <si>
-    <t>134472712</t>
-  </si>
-  <si>
-    <t>134472769</t>
-  </si>
-  <si>
-    <t>134472853</t>
-  </si>
-  <si>
-    <t>134472971</t>
-  </si>
-  <si>
-    <t>134473259</t>
-  </si>
-  <si>
-    <t>134473376</t>
-  </si>
-  <si>
-    <t>134473442</t>
-  </si>
-  <si>
-    <t>134473447</t>
-  </si>
-  <si>
-    <t>134473463</t>
-  </si>
-  <si>
-    <t>134473470</t>
-  </si>
-  <si>
-    <t>134473484</t>
-  </si>
-  <si>
-    <t>134473502</t>
-  </si>
-  <si>
-    <t>134473614</t>
-  </si>
-  <si>
-    <t>134473692</t>
-  </si>
-  <si>
-    <t>134473702</t>
-  </si>
-  <si>
-    <t>134473797</t>
-  </si>
-  <si>
-    <t>134473852</t>
-  </si>
-  <si>
-    <t>134473911</t>
-  </si>
-  <si>
-    <t>134474029</t>
-  </si>
-  <si>
-    <t>134474114</t>
-  </si>
-  <si>
-    <t>134474219</t>
-  </si>
-  <si>
-    <t>134474264</t>
-  </si>
-  <si>
-    <t>134474345</t>
-  </si>
-  <si>
-    <t>134474351</t>
-  </si>
-  <si>
-    <t>134474382</t>
-  </si>
-  <si>
-    <t>134474505</t>
-  </si>
-  <si>
-    <t>134474619</t>
-  </si>
-  <si>
-    <t>134474789</t>
-  </si>
-  <si>
-    <t>134474821</t>
-  </si>
-  <si>
-    <t>134474867</t>
-  </si>
-  <si>
-    <t>134474914</t>
-  </si>
-  <si>
-    <t>134475213</t>
-  </si>
-  <si>
-    <t>134475316</t>
-  </si>
-  <si>
-    <t>134475334</t>
-  </si>
-  <si>
-    <t>134475494</t>
-  </si>
-  <si>
-    <t>134475602</t>
-  </si>
-  <si>
-    <t>134475752</t>
-  </si>
-  <si>
-    <t>134475899</t>
-  </si>
-  <si>
-    <t>134476116</t>
-  </si>
-  <si>
-    <t>134476331</t>
-  </si>
-  <si>
-    <t>134476447</t>
-  </si>
-  <si>
-    <t>134476674</t>
-  </si>
-  <si>
-    <t>134476767</t>
-  </si>
-  <si>
-    <t>134476848</t>
-  </si>
-  <si>
-    <t>134477279</t>
-  </si>
-  <si>
-    <t>134477282</t>
-  </si>
-  <si>
-    <t>134477649</t>
-  </si>
-  <si>
-    <t>134477781</t>
-  </si>
-  <si>
-    <t>134477892</t>
-  </si>
-  <si>
-    <t>134477896</t>
-  </si>
-  <si>
-    <t>134478265</t>
-  </si>
-  <si>
-    <t>134478289</t>
-  </si>
-  <si>
-    <t>134478290</t>
-  </si>
-  <si>
-    <t>134478482</t>
-  </si>
-  <si>
-    <t>134478532</t>
-  </si>
-  <si>
-    <t>134478584</t>
-  </si>
-  <si>
-    <t>134478747</t>
-  </si>
-  <si>
-    <t>134478856</t>
-  </si>
-  <si>
-    <t>134479113</t>
-  </si>
-  <si>
-    <t>134479181</t>
-  </si>
-  <si>
-    <t>134479299</t>
-  </si>
-  <si>
-    <t>134479704</t>
-  </si>
-  <si>
-    <t>134479769</t>
-  </si>
-  <si>
-    <t>134479858</t>
-  </si>
-  <si>
-    <t>134479869</t>
-  </si>
-  <si>
-    <t>134479941</t>
-  </si>
-  <si>
-    <t>134479990</t>
-  </si>
-  <si>
-    <t>134480003</t>
-  </si>
-  <si>
-    <t>134480290</t>
-  </si>
-  <si>
-    <t>134480439</t>
-  </si>
-  <si>
-    <t>134480517</t>
-  </si>
-  <si>
-    <t>134480548</t>
-  </si>
-  <si>
-    <t>134480555</t>
-  </si>
-  <si>
-    <t>134480576</t>
-  </si>
-  <si>
-    <t>134480630</t>
-  </si>
-  <si>
-    <t>134480669</t>
-  </si>
-  <si>
-    <t>134480863</t>
-  </si>
-  <si>
-    <t>134480995</t>
-  </si>
-  <si>
-    <t>134481415</t>
-  </si>
-  <si>
-    <t>134481474</t>
-  </si>
-  <si>
-    <t>134481622</t>
-  </si>
-  <si>
-    <t>134481642</t>
-  </si>
-  <si>
-    <t>134481748</t>
-  </si>
-  <si>
-    <t>134481778</t>
-  </si>
-  <si>
-    <t>134481793</t>
-  </si>
-  <si>
-    <t>134481861</t>
-  </si>
-  <si>
-    <t>134482166</t>
-  </si>
-  <si>
-    <t>134482236</t>
-  </si>
-  <si>
-    <t>134482430</t>
-  </si>
-  <si>
-    <t>134483061</t>
-  </si>
-  <si>
-    <t>134483225</t>
-  </si>
-  <si>
-    <t>134483238</t>
-  </si>
-  <si>
-    <t>134483240</t>
-  </si>
-  <si>
-    <t>134483331</t>
-  </si>
-  <si>
-    <t>134483335</t>
-  </si>
-  <si>
-    <t>134483421</t>
-  </si>
-  <si>
-    <t>134483515</t>
-  </si>
-  <si>
-    <t>134483704</t>
-  </si>
-  <si>
-    <t>134483853</t>
-  </si>
-  <si>
-    <t>134484101</t>
-  </si>
-  <si>
-    <t>134484305</t>
-  </si>
-  <si>
-    <t>134484372</t>
-  </si>
-  <si>
-    <t>134484497</t>
-  </si>
-  <si>
-    <t>134484507</t>
-  </si>
-  <si>
-    <t>134484517</t>
-  </si>
-  <si>
-    <t>134484734</t>
-  </si>
-  <si>
-    <t>134484891</t>
-  </si>
-  <si>
-    <t>134485043</t>
-  </si>
-  <si>
-    <t>134485103</t>
-  </si>
-  <si>
-    <t>134485142</t>
-  </si>
-  <si>
-    <t>134485410</t>
-  </si>
-  <si>
-    <t>134485428</t>
-  </si>
-  <si>
-    <t>134485449</t>
-  </si>
-  <si>
-    <t>134485453</t>
-  </si>
-  <si>
-    <t>134485489</t>
-  </si>
-  <si>
-    <t>134485603</t>
-  </si>
-  <si>
-    <t>134485642</t>
-  </si>
-  <si>
-    <t>134485726</t>
-  </si>
-  <si>
-    <t>134485808</t>
-  </si>
-  <si>
-    <t>134485948</t>
-  </si>
-  <si>
-    <t>134486228</t>
-  </si>
-  <si>
-    <t>134486503</t>
-  </si>
-  <si>
-    <t>134486608</t>
-  </si>
-  <si>
-    <t>134486611</t>
-  </si>
-  <si>
-    <t>134486621</t>
-  </si>
-  <si>
-    <t>134487071</t>
-  </si>
-  <si>
-    <t>134487695</t>
+    <t>129634207</t>
+  </si>
+  <si>
+    <t>129647419</t>
+  </si>
+  <si>
+    <t>129780471</t>
+  </si>
+  <si>
+    <t>130156772</t>
+  </si>
+  <si>
+    <t>130257066</t>
+  </si>
+  <si>
+    <t>130490145</t>
+  </si>
+  <si>
+    <t>130507834</t>
+  </si>
+  <si>
+    <t>130564660</t>
+  </si>
+  <si>
+    <t>130589990</t>
+  </si>
+  <si>
+    <t>130598503</t>
+  </si>
+  <si>
+    <t>130657700</t>
+  </si>
+  <si>
+    <t>130676188</t>
+  </si>
+  <si>
+    <t>130821566</t>
+  </si>
+  <si>
+    <t>130826255</t>
+  </si>
+  <si>
+    <t>131193969</t>
+  </si>
+  <si>
+    <t>131378646</t>
+  </si>
+  <si>
+    <t>131385177</t>
+  </si>
+  <si>
+    <t>131392548</t>
+  </si>
+  <si>
+    <t>131515151</t>
+  </si>
+  <si>
+    <t>131840814</t>
+  </si>
+  <si>
+    <t>131921390</t>
+  </si>
+  <si>
+    <t>131947144</t>
+  </si>
+  <si>
+    <t>132135647</t>
+  </si>
+  <si>
+    <t>132329989</t>
+  </si>
+  <si>
+    <t>132610255</t>
+  </si>
+  <si>
+    <t>132722981</t>
+  </si>
+  <si>
+    <t>132930749</t>
+  </si>
+  <si>
+    <t>132936692</t>
+  </si>
+  <si>
+    <t>133170528</t>
+  </si>
+  <si>
+    <t>133303504</t>
+  </si>
+  <si>
+    <t>133326695</t>
+  </si>
+  <si>
+    <t>134198392</t>
+  </si>
+  <si>
+    <t>134262785</t>
+  </si>
+  <si>
+    <t>134488185</t>
+  </si>
+  <si>
+    <t>134488434</t>
+  </si>
+  <si>
+    <t>134488451</t>
+  </si>
+  <si>
+    <t>134488474</t>
+  </si>
+  <si>
+    <t>134488789</t>
+  </si>
+  <si>
+    <t>134488878</t>
+  </si>
+  <si>
+    <t>134488910</t>
+  </si>
+  <si>
+    <t>134488974</t>
+  </si>
+  <si>
+    <t>134489065</t>
+  </si>
+  <si>
+    <t>134489155</t>
+  </si>
+  <si>
+    <t>134489202</t>
+  </si>
+  <si>
+    <t>134489243</t>
+  </si>
+  <si>
+    <t>134489252</t>
+  </si>
+  <si>
+    <t>134489288</t>
+  </si>
+  <si>
+    <t>134489399</t>
+  </si>
+  <si>
+    <t>134489614</t>
+  </si>
+  <si>
+    <t>134489736</t>
+  </si>
+  <si>
+    <t>134489903</t>
+  </si>
+  <si>
+    <t>134489976</t>
+  </si>
+  <si>
+    <t>134490057</t>
+  </si>
+  <si>
+    <t>134490089</t>
+  </si>
+  <si>
+    <t>134490097</t>
+  </si>
+  <si>
+    <t>134490119</t>
+  </si>
+  <si>
+    <t>134490252</t>
+  </si>
+  <si>
+    <t>134490307</t>
+  </si>
+  <si>
+    <t>134490326</t>
+  </si>
+  <si>
+    <t>134490385</t>
+  </si>
+  <si>
+    <t>134490399</t>
+  </si>
+  <si>
+    <t>134490562</t>
+  </si>
+  <si>
+    <t>134490623</t>
+  </si>
+  <si>
+    <t>134490712</t>
+  </si>
+  <si>
+    <t>134490946</t>
+  </si>
+  <si>
+    <t>134491005</t>
+  </si>
+  <si>
+    <t>134491134</t>
+  </si>
+  <si>
+    <t>134491370</t>
+  </si>
+  <si>
+    <t>134491486</t>
+  </si>
+  <si>
+    <t>134491614</t>
+  </si>
+  <si>
+    <t>134491815</t>
+  </si>
+  <si>
+    <t>134491848</t>
+  </si>
+  <si>
+    <t>134491889</t>
+  </si>
+  <si>
+    <t>134491916</t>
+  </si>
+  <si>
+    <t>134492162</t>
+  </si>
+  <si>
+    <t>134492265</t>
+  </si>
+  <si>
+    <t>134492333</t>
+  </si>
+  <si>
+    <t>134492387</t>
+  </si>
+  <si>
+    <t>134492586</t>
+  </si>
+  <si>
+    <t>134492851</t>
+  </si>
+  <si>
+    <t>134492918</t>
+  </si>
+  <si>
+    <t>134492981</t>
+  </si>
+  <si>
+    <t>134492996</t>
+  </si>
+  <si>
+    <t>134493041</t>
+  </si>
+  <si>
+    <t>134493100</t>
+  </si>
+  <si>
+    <t>134493128</t>
+  </si>
+  <si>
+    <t>134493211</t>
+  </si>
+  <si>
+    <t>134493280</t>
+  </si>
+  <si>
+    <t>134493339</t>
+  </si>
+  <si>
+    <t>134493343</t>
+  </si>
+  <si>
+    <t>134493550</t>
+  </si>
+  <si>
+    <t>134493695</t>
+  </si>
+  <si>
+    <t>134493782</t>
+  </si>
+  <si>
+    <t>134493842</t>
+  </si>
+  <si>
+    <t>134493945</t>
+  </si>
+  <si>
+    <t>134494077</t>
+  </si>
+  <si>
+    <t>134494138</t>
+  </si>
+  <si>
+    <t>134494168</t>
+  </si>
+  <si>
+    <t>134494335</t>
+  </si>
+  <si>
+    <t>134494479</t>
+  </si>
+  <si>
+    <t>134494594</t>
+  </si>
+  <si>
+    <t>134494803</t>
+  </si>
+  <si>
+    <t>134495287</t>
+  </si>
+  <si>
+    <t>134495364</t>
+  </si>
+  <si>
+    <t>134495483</t>
+  </si>
+  <si>
+    <t>134495706</t>
+  </si>
+  <si>
+    <t>134495922</t>
+  </si>
+  <si>
+    <t>134495935</t>
+  </si>
+  <si>
+    <t>134496011</t>
+  </si>
+  <si>
+    <t>134496062</t>
+  </si>
+  <si>
+    <t>134496117</t>
+  </si>
+  <si>
+    <t>134496260</t>
+  </si>
+  <si>
+    <t>134496349</t>
+  </si>
+  <si>
+    <t>134496352</t>
+  </si>
+  <si>
+    <t>134496358</t>
+  </si>
+  <si>
+    <t>134496484</t>
+  </si>
+  <si>
+    <t>134496531</t>
+  </si>
+  <si>
+    <t>134496575</t>
+  </si>
+  <si>
+    <t>134496634</t>
+  </si>
+  <si>
+    <t>134496726</t>
+  </si>
+  <si>
+    <t>134496733</t>
+  </si>
+  <si>
+    <t>134496760</t>
+  </si>
+  <si>
+    <t>134496888</t>
+  </si>
+  <si>
+    <t>134496889</t>
+  </si>
+  <si>
+    <t>134496971</t>
+  </si>
+  <si>
+    <t>134497055</t>
+  </si>
+  <si>
+    <t>134497074</t>
+  </si>
+  <si>
+    <t>134497184</t>
+  </si>
+  <si>
+    <t>134497220</t>
+  </si>
+  <si>
+    <t>134497264</t>
+  </si>
+  <si>
+    <t>134497441</t>
+  </si>
+  <si>
+    <t>134497460</t>
+  </si>
+  <si>
+    <t>134497562</t>
+  </si>
+  <si>
+    <t>134497563</t>
+  </si>
+  <si>
+    <t>134497701</t>
+  </si>
+  <si>
+    <t>134497807</t>
+  </si>
+  <si>
+    <t>134497881</t>
+  </si>
+  <si>
+    <t>134497922</t>
+  </si>
+  <si>
+    <t>134497980</t>
+  </si>
+  <si>
+    <t>134498004</t>
+  </si>
+  <si>
+    <t>134498274</t>
+  </si>
+  <si>
+    <t>134498290</t>
+  </si>
+  <si>
+    <t>134498296</t>
+  </si>
+  <si>
+    <t>134498316</t>
+  </si>
+  <si>
+    <t>134498385</t>
+  </si>
+  <si>
+    <t>134498398</t>
+  </si>
+  <si>
+    <t>134498471</t>
+  </si>
+  <si>
+    <t>134498604</t>
+  </si>
+  <si>
+    <t>134498644</t>
+  </si>
+  <si>
+    <t>134498688</t>
+  </si>
+  <si>
+    <t>134498707</t>
+  </si>
+  <si>
+    <t>134498852</t>
+  </si>
+  <si>
+    <t>134498896</t>
+  </si>
+  <si>
+    <t>134499011</t>
+  </si>
+  <si>
+    <t>134499235</t>
+  </si>
+  <si>
+    <t>134499522</t>
+  </si>
+  <si>
+    <t>134499535</t>
+  </si>
+  <si>
+    <t>134499648</t>
+  </si>
+  <si>
+    <t>134499756</t>
+  </si>
+  <si>
+    <t>134499781</t>
+  </si>
+  <si>
+    <t>134499795</t>
+  </si>
+  <si>
+    <t>134499901</t>
+  </si>
+  <si>
+    <t>134499946</t>
+  </si>
+  <si>
+    <t>134499950</t>
+  </si>
+  <si>
+    <t>134500134</t>
+  </si>
+  <si>
+    <t>134500140</t>
+  </si>
+  <si>
+    <t>134500167</t>
+  </si>
+  <si>
+    <t>134500183</t>
+  </si>
+  <si>
+    <t>134500265</t>
+  </si>
+  <si>
+    <t>134500339</t>
+  </si>
+  <si>
+    <t>134500434</t>
+  </si>
+  <si>
+    <t>134500594</t>
+  </si>
+  <si>
+    <t>134500930</t>
+  </si>
+  <si>
+    <t>134501034</t>
+  </si>
+  <si>
+    <t>134501037</t>
+  </si>
+  <si>
+    <t>134501071</t>
+  </si>
+  <si>
+    <t>134501183</t>
+  </si>
+  <si>
+    <t>134501188</t>
+  </si>
+  <si>
+    <t>134501223</t>
+  </si>
+  <si>
+    <t>134501238</t>
+  </si>
+  <si>
+    <t>134501346</t>
+  </si>
+  <si>
+    <t>134501465</t>
+  </si>
+  <si>
+    <t>134501483</t>
+  </si>
+  <si>
+    <t>134501529</t>
+  </si>
+  <si>
+    <t>134501633</t>
+  </si>
+  <si>
+    <t>134501781</t>
+  </si>
+  <si>
+    <t>134502008</t>
+  </si>
+  <si>
+    <t>134502221</t>
+  </si>
+  <si>
+    <t>134502354</t>
+  </si>
+  <si>
+    <t>134502606</t>
+  </si>
+  <si>
+    <t>134502616</t>
+  </si>
+  <si>
+    <t>134503007</t>
+  </si>
+  <si>
+    <t>134503013</t>
+  </si>
+  <si>
+    <t>134503110</t>
+  </si>
+  <si>
+    <t>134503253</t>
+  </si>
+  <si>
+    <t>134503272</t>
+  </si>
+  <si>
+    <t>134503306</t>
+  </si>
+  <si>
+    <t>134503362</t>
+  </si>
+  <si>
+    <t>134503508</t>
+  </si>
+  <si>
+    <t>134503603</t>
+  </si>
+  <si>
+    <t>134503638</t>
+  </si>
+  <si>
+    <t>134503739</t>
+  </si>
+  <si>
+    <t>134503798</t>
+  </si>
+  <si>
+    <t>134503841</t>
+  </si>
+  <si>
+    <t>134503847</t>
+  </si>
+  <si>
+    <t>134503899</t>
+  </si>
+  <si>
+    <t>134503905</t>
+  </si>
+  <si>
+    <t>134503931</t>
+  </si>
+  <si>
+    <t>134503946</t>
+  </si>
+  <si>
+    <t>134504034</t>
+  </si>
+  <si>
+    <t>134504044</t>
+  </si>
+  <si>
+    <t>134504083</t>
+  </si>
+  <si>
+    <t>134504215</t>
+  </si>
+  <si>
+    <t>134504253</t>
+  </si>
+  <si>
+    <t>134504705</t>
+  </si>
+  <si>
+    <t>134504721</t>
+  </si>
+  <si>
+    <t>134504755</t>
+  </si>
+  <si>
+    <t>134504820</t>
+  </si>
+  <si>
+    <t>134504892</t>
+  </si>
+  <si>
+    <t>134505167</t>
+  </si>
+  <si>
+    <t>134505248</t>
+  </si>
+  <si>
+    <t>134505382</t>
+  </si>
+  <si>
+    <t>134505427</t>
+  </si>
+  <si>
+    <t>134505550</t>
+  </si>
+  <si>
+    <t>134505588</t>
+  </si>
+  <si>
+    <t>134505606</t>
+  </si>
+  <si>
+    <t>134505607</t>
+  </si>
+  <si>
+    <t>134505619</t>
+  </si>
+  <si>
+    <t>134505623</t>
+  </si>
+  <si>
+    <t>134505747</t>
+  </si>
+  <si>
+    <t>134505848</t>
+  </si>
+  <si>
+    <t>134505850</t>
+  </si>
+  <si>
+    <t>134505852</t>
+  </si>
+  <si>
+    <t>134506141</t>
+  </si>
+  <si>
+    <t>134506146</t>
+  </si>
+  <si>
+    <t>134506219</t>
+  </si>
+  <si>
+    <t>134506311</t>
+  </si>
+  <si>
+    <t>134506381</t>
+  </si>
+  <si>
+    <t>134506620</t>
+  </si>
+  <si>
+    <t>134506658</t>
+  </si>
+  <si>
+    <t>134506841</t>
+  </si>
+  <si>
+    <t>134506891</t>
+  </si>
+  <si>
+    <t>134506993</t>
+  </si>
+  <si>
+    <t>134507001</t>
+  </si>
+  <si>
+    <t>134507085</t>
+  </si>
+  <si>
+    <t>134507100</t>
+  </si>
+  <si>
+    <t>134507185</t>
+  </si>
+  <si>
+    <t>134507254</t>
+  </si>
+  <si>
+    <t>134507268</t>
+  </si>
+  <si>
+    <t>134507324</t>
+  </si>
+  <si>
+    <t>134507573</t>
+  </si>
+  <si>
+    <t>134507780</t>
+  </si>
+  <si>
+    <t>134507991</t>
+  </si>
+  <si>
+    <t>134508012</t>
+  </si>
+  <si>
+    <t>134508177</t>
+  </si>
+  <si>
+    <t>134508178</t>
+  </si>
+  <si>
+    <t>134508229</t>
+  </si>
+  <si>
+    <t>134508264</t>
+  </si>
+  <si>
+    <t>134508339</t>
+  </si>
+  <si>
+    <t>134508394</t>
+  </si>
+  <si>
+    <t>134508456</t>
+  </si>
+  <si>
+    <t>134508527</t>
+  </si>
+  <si>
+    <t>134508764</t>
+  </si>
+  <si>
+    <t>134508798</t>
+  </si>
+  <si>
+    <t>134508858</t>
+  </si>
+  <si>
+    <t>134508937</t>
+  </si>
+  <si>
+    <t>134508940</t>
+  </si>
+  <si>
+    <t>134509735</t>
+  </si>
+  <si>
+    <t>134509852</t>
+  </si>
+  <si>
+    <t>134509876</t>
+  </si>
+  <si>
+    <t>134510018</t>
+  </si>
+  <si>
+    <t>134510610</t>
+  </si>
+  <si>
+    <t>134510829</t>
+  </si>
+  <si>
+    <t>134510850</t>
   </si>
 </sst>
 </file>
@@ -3450,6 +3633,9 @@
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="B215" s="6" t="s">
         <v>3</v>
       </c>
@@ -3458,6 +3644,9 @@
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="B216" s="6" t="s">
         <v>3</v>
       </c>
@@ -3466,6 +3655,9 @@
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="B217" s="6" t="s">
         <v>3</v>
       </c>
@@ -3474,6 +3666,9 @@
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="B218" s="6" t="s">
         <v>3</v>
       </c>
@@ -3482,6 +3677,9 @@
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="B219" s="6" t="s">
         <v>3</v>
       </c>
@@ -3490,6 +3688,9 @@
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
       <c r="B220" s="6" t="s">
         <v>3</v>
       </c>
@@ -3498,6 +3699,9 @@
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="B221" s="6" t="s">
         <v>3</v>
       </c>
@@ -3506,6 +3710,9 @@
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="B222" s="6" t="s">
         <v>3</v>
       </c>
@@ -3514,6 +3721,9 @@
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="B223" s="6" t="s">
         <v>3</v>
       </c>
@@ -3522,6 +3732,9 @@
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="B224" s="6" t="s">
         <v>3</v>
       </c>
@@ -3529,7 +3742,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
       <c r="B225" s="6" t="s">
         <v>3</v>
       </c>
@@ -3537,7 +3753,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
       <c r="B226" s="6" t="s">
         <v>3</v>
       </c>
@@ -3545,7 +3764,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
       <c r="B227" s="6" t="s">
         <v>3</v>
       </c>
@@ -3553,7 +3775,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="B228" s="6" t="s">
         <v>3</v>
       </c>
@@ -3561,7 +3786,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="B229" s="6" t="s">
         <v>3</v>
       </c>
@@ -3569,7 +3797,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="B230" s="6" t="s">
         <v>3</v>
       </c>
@@ -3577,7 +3808,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="B231" s="6" t="s">
         <v>3</v>
       </c>
@@ -3585,7 +3819,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
       <c r="B232" s="6" t="s">
         <v>3</v>
       </c>
@@ -3593,7 +3830,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="B233" s="6" t="s">
         <v>3</v>
       </c>
@@ -3601,7 +3841,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
       <c r="B234" s="6" t="s">
         <v>3</v>
       </c>
@@ -3609,7 +3852,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="B235" s="6" t="s">
         <v>3</v>
       </c>
@@ -3617,7 +3863,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="B236" s="6" t="s">
         <v>3</v>
       </c>
@@ -3625,7 +3874,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="B237" s="6" t="s">
         <v>3</v>
       </c>
@@ -3633,7 +3885,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="B238" s="6" t="s">
         <v>3</v>
       </c>
@@ -3641,7 +3896,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="B239" s="6" t="s">
         <v>3</v>
       </c>
@@ -3649,7 +3907,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
       <c r="B240" s="6" t="s">
         <v>3</v>
       </c>
@@ -3657,7 +3918,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
       <c r="B241" s="6" t="s">
         <v>3</v>
       </c>
@@ -3665,7 +3929,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
       <c r="B242" s="6" t="s">
         <v>3</v>
       </c>
@@ -3673,7 +3940,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
       <c r="B243" s="6" t="s">
         <v>3</v>
       </c>
@@ -3681,7 +3951,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="B244" s="6" t="s">
         <v>3</v>
       </c>
@@ -3689,7 +3962,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="B245" s="6" t="s">
         <v>3</v>
       </c>
@@ -3697,7 +3973,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
       <c r="B246" s="6" t="s">
         <v>3</v>
       </c>
@@ -3705,7 +3984,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="B247" s="6" t="s">
         <v>3</v>
       </c>
@@ -3713,7 +3995,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="B248" s="6" t="s">
         <v>3</v>
       </c>
@@ -3721,7 +4006,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="B249" s="6" t="s">
         <v>3</v>
       </c>
@@ -3729,7 +4017,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
       <c r="B250" s="6" t="s">
         <v>3</v>
       </c>
@@ -3737,7 +4028,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="B251" s="6" t="s">
         <v>3</v>
       </c>
@@ -3745,7 +4039,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
       <c r="B252" s="6" t="s">
         <v>3</v>
       </c>
@@ -3753,7 +4050,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="B253" s="6" t="s">
         <v>3</v>
       </c>
@@ -3761,7 +4061,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="B254" s="6" t="s">
         <v>3</v>
       </c>
@@ -3769,7 +4072,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="B255" s="6" t="s">
         <v>3</v>
       </c>
@@ -3777,7 +4083,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="B256" s="6" t="s">
         <v>3</v>
       </c>
@@ -3785,7 +4094,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>260</v>
+      </c>
       <c r="B257" s="6" t="s">
         <v>3</v>
       </c>
@@ -3793,7 +4105,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="B258" s="6" t="s">
         <v>3</v>
       </c>
@@ -3801,7 +4116,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>262</v>
+      </c>
       <c r="B259" s="6" t="s">
         <v>3</v>
       </c>
@@ -3809,7 +4127,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="B260" s="6" t="s">
         <v>3</v>
       </c>
@@ -3817,7 +4138,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="B261" s="6" t="s">
         <v>3</v>
       </c>
@@ -3825,7 +4149,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="B262" s="6" t="s">
         <v>3</v>
       </c>
@@ -3833,7 +4160,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>266</v>
+      </c>
       <c r="B263" s="6" t="s">
         <v>3</v>
       </c>
@@ -3841,7 +4171,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="B264" s="6" t="s">
         <v>3</v>
       </c>
@@ -3849,7 +4182,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="B265" s="6" t="s">
         <v>3</v>
       </c>
@@ -3857,7 +4193,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="B266" s="6" t="s">
         <v>3</v>
       </c>
@@ -3865,7 +4204,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="B267" s="6" t="s">
         <v>3</v>
       </c>
@@ -3873,7 +4215,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="B268" s="6" t="s">
         <v>3</v>
       </c>
@@ -3881,7 +4226,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="B269" s="6" t="s">
         <v>3</v>
       </c>
@@ -3889,7 +4237,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="B270" s="6" t="s">
         <v>3</v>
       </c>
@@ -3897,7 +4248,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="B271" s="6" t="s">
         <v>3</v>
       </c>
@@ -3905,7 +4259,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>275</v>
+      </c>
       <c r="B272" s="6" t="s">
         <v>3</v>
       </c>
@@ -3913,7 +4270,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="B273" s="6" t="s">
         <v>3</v>
       </c>
@@ -3921,7 +4281,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="B274" s="6" t="s">
         <v>3</v>
       </c>
@@ -3929,7 +4292,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="B275" s="6" t="s">
         <v>3</v>
       </c>
@@ -3937,466 +4303,350 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B276" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B276" s="6"/>
       <c r="C276" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B277" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B277" s="6"/>
       <c r="C277" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B278" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B278" s="6"/>
       <c r="C278" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B279" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B279" s="6"/>
       <c r="C279" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B280" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B280" s="6"/>
       <c r="C280" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B281" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B281" s="6"/>
       <c r="C281" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B282" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B282" s="6"/>
       <c r="C282" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B283" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B283" s="6"/>
       <c r="C283" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B284" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B284" s="6"/>
       <c r="C284" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B285" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B285" s="6"/>
       <c r="C285" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B286" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B286" s="6"/>
       <c r="C286" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B287" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B287" s="6"/>
       <c r="C287" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B288" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B288" s="6"/>
       <c r="C288" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="289" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B289" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B289" s="6"/>
       <c r="C289" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="290" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B290" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B290" s="6"/>
       <c r="C290" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="291" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B291" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B291" s="6"/>
       <c r="C291" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="292" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B292" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B292" s="6"/>
       <c r="C292" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="293" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B293" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B293" s="6"/>
       <c r="C293" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="294" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B294" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B294" s="6"/>
       <c r="C294" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="295" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B295" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B295" s="6"/>
       <c r="C295" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="296" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B296" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B296" s="6"/>
       <c r="C296" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="297" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B297" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B297" s="6"/>
       <c r="C297" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="298" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B298" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B298" s="6"/>
       <c r="C298" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="299" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B299" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B299" s="6"/>
       <c r="C299" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="300" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B300" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B300" s="6"/>
       <c r="C300" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="301" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B301" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B301" s="6"/>
       <c r="C301" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="302" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B302" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B302" s="6"/>
       <c r="C302" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="303" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B303" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B303" s="6"/>
       <c r="C303" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="304" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B304" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B304" s="6"/>
       <c r="C304" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="305" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B305" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B305" s="6"/>
       <c r="C305" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="306" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B306" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B306" s="6"/>
       <c r="C306" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="307" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B307" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B307" s="6"/>
       <c r="C307" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="308" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B308" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B308" s="6"/>
       <c r="C308" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="309" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B309" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B309" s="6"/>
       <c r="C309" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="310" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B310" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B310" s="6"/>
       <c r="C310" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="311" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B311" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B311" s="6"/>
       <c r="C311" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="312" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B312" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B312" s="6"/>
       <c r="C312" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="313" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B313" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B313" s="6"/>
       <c r="C313" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="314" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B314" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B314" s="6"/>
       <c r="C314" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="315" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B315" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B315" s="6"/>
       <c r="C315" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="316" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B316" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B316" s="6"/>
       <c r="C316" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="317" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B317" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B317" s="6"/>
       <c r="C317" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="318" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B318" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B318" s="6"/>
       <c r="C318" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="319" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B319" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B319" s="6"/>
       <c r="C319" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="320" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B320" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B320" s="6"/>
       <c r="C320" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="321" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B321" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B321" s="6"/>
       <c r="C321" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="322" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B322" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B322" s="6"/>
       <c r="C322" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="323" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B323" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B323" s="6"/>
       <c r="C323" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="324" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B324" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B324" s="6"/>
       <c r="C324" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="325" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B325" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B325" s="6"/>
       <c r="C325" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="326" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B326" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B326" s="6"/>
       <c r="C326" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="327" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B327" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B327" s="6"/>
       <c r="C327" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="328" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B328" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B328" s="6"/>
       <c r="C328" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="329" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B329" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B329" s="6"/>
       <c r="C329" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="330" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B330" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B330" s="6"/>
       <c r="C330" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="331" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B331" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B331" s="6"/>
       <c r="C331" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="332" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B332" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B332" s="6"/>
       <c r="C332" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="333" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B333" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B333" s="6"/>
       <c r="C333" s="5" t="s">
         <v>4</v>
       </c>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAB78F7-D6EE-42E5-8FE8-94A70B80DEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC4C25D-2244-4BB0-91ED-AEFC3E958BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="385">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,826 +45,1144 @@
     <t>.</t>
   </si>
   <si>
-    <t>129634207</t>
-  </si>
-  <si>
-    <t>129647419</t>
-  </si>
-  <si>
-    <t>129780471</t>
-  </si>
-  <si>
-    <t>130156772</t>
-  </si>
-  <si>
-    <t>130257066</t>
-  </si>
-  <si>
-    <t>130490145</t>
-  </si>
-  <si>
     <t>130507834</t>
   </si>
   <si>
-    <t>130564660</t>
-  </si>
-  <si>
-    <t>130589990</t>
-  </si>
-  <si>
-    <t>130598503</t>
-  </si>
-  <si>
-    <t>130657700</t>
-  </si>
-  <si>
-    <t>130676188</t>
-  </si>
-  <si>
-    <t>130821566</t>
-  </si>
-  <si>
-    <t>130826255</t>
-  </si>
-  <si>
-    <t>131193969</t>
-  </si>
-  <si>
-    <t>131378646</t>
-  </si>
-  <si>
-    <t>131385177</t>
-  </si>
-  <si>
-    <t>131392548</t>
-  </si>
-  <si>
-    <t>131515151</t>
-  </si>
-  <si>
-    <t>131840814</t>
-  </si>
-  <si>
-    <t>131921390</t>
-  </si>
-  <si>
     <t>131947144</t>
   </si>
   <si>
-    <t>132135647</t>
-  </si>
-  <si>
-    <t>132329989</t>
-  </si>
-  <si>
-    <t>132610255</t>
-  </si>
-  <si>
-    <t>132722981</t>
-  </si>
-  <si>
-    <t>132930749</t>
-  </si>
-  <si>
-    <t>132936692</t>
-  </si>
-  <si>
-    <t>133170528</t>
-  </si>
-  <si>
-    <t>133303504</t>
-  </si>
-  <si>
-    <t>133326695</t>
-  </si>
-  <si>
-    <t>134198392</t>
-  </si>
-  <si>
-    <t>134262785</t>
-  </si>
-  <si>
-    <t>134488185</t>
-  </si>
-  <si>
-    <t>134488434</t>
-  </si>
-  <si>
-    <t>134488451</t>
-  </si>
-  <si>
-    <t>134488474</t>
-  </si>
-  <si>
-    <t>134488789</t>
-  </si>
-  <si>
-    <t>134488878</t>
-  </si>
-  <si>
-    <t>134488910</t>
-  </si>
-  <si>
-    <t>134488974</t>
-  </si>
-  <si>
-    <t>134489065</t>
-  </si>
-  <si>
-    <t>134489155</t>
-  </si>
-  <si>
-    <t>134489202</t>
-  </si>
-  <si>
-    <t>134489243</t>
-  </si>
-  <si>
-    <t>134489252</t>
-  </si>
-  <si>
-    <t>134489288</t>
-  </si>
-  <si>
-    <t>134489399</t>
-  </si>
-  <si>
-    <t>134489614</t>
-  </si>
-  <si>
-    <t>134489736</t>
-  </si>
-  <si>
-    <t>134489903</t>
-  </si>
-  <si>
-    <t>134489976</t>
-  </si>
-  <si>
-    <t>134490057</t>
-  </si>
-  <si>
-    <t>134490089</t>
-  </si>
-  <si>
-    <t>134490097</t>
-  </si>
-  <si>
-    <t>134490119</t>
-  </si>
-  <si>
-    <t>134490252</t>
-  </si>
-  <si>
-    <t>134490307</t>
-  </si>
-  <si>
-    <t>134490326</t>
-  </si>
-  <si>
-    <t>134490385</t>
-  </si>
-  <si>
-    <t>134490399</t>
-  </si>
-  <si>
-    <t>134490562</t>
-  </si>
-  <si>
-    <t>134490623</t>
-  </si>
-  <si>
-    <t>134490712</t>
-  </si>
-  <si>
-    <t>134490946</t>
-  </si>
-  <si>
-    <t>134491005</t>
-  </si>
-  <si>
-    <t>134491134</t>
-  </si>
-  <si>
-    <t>134491370</t>
-  </si>
-  <si>
-    <t>134491486</t>
-  </si>
-  <si>
-    <t>134491614</t>
-  </si>
-  <si>
-    <t>134491815</t>
-  </si>
-  <si>
-    <t>134491848</t>
-  </si>
-  <si>
-    <t>134491889</t>
-  </si>
-  <si>
-    <t>134491916</t>
-  </si>
-  <si>
-    <t>134492162</t>
-  </si>
-  <si>
-    <t>134492265</t>
-  </si>
-  <si>
-    <t>134492333</t>
-  </si>
-  <si>
-    <t>134492387</t>
-  </si>
-  <si>
-    <t>134492586</t>
-  </si>
-  <si>
-    <t>134492851</t>
-  </si>
-  <si>
-    <t>134492918</t>
-  </si>
-  <si>
-    <t>134492981</t>
-  </si>
-  <si>
-    <t>134492996</t>
-  </si>
-  <si>
-    <t>134493041</t>
-  </si>
-  <si>
-    <t>134493100</t>
-  </si>
-  <si>
-    <t>134493128</t>
-  </si>
-  <si>
-    <t>134493211</t>
-  </si>
-  <si>
-    <t>134493280</t>
-  </si>
-  <si>
-    <t>134493339</t>
-  </si>
-  <si>
-    <t>134493343</t>
-  </si>
-  <si>
-    <t>134493550</t>
-  </si>
-  <si>
-    <t>134493695</t>
-  </si>
-  <si>
-    <t>134493782</t>
-  </si>
-  <si>
-    <t>134493842</t>
-  </si>
-  <si>
-    <t>134493945</t>
-  </si>
-  <si>
-    <t>134494077</t>
-  </si>
-  <si>
-    <t>134494138</t>
-  </si>
-  <si>
-    <t>134494168</t>
-  </si>
-  <si>
-    <t>134494335</t>
-  </si>
-  <si>
-    <t>134494479</t>
-  </si>
-  <si>
-    <t>134494594</t>
-  </si>
-  <si>
-    <t>134494803</t>
-  </si>
-  <si>
-    <t>134495287</t>
-  </si>
-  <si>
-    <t>134495364</t>
-  </si>
-  <si>
-    <t>134495483</t>
-  </si>
-  <si>
-    <t>134495706</t>
-  </si>
-  <si>
-    <t>134495922</t>
-  </si>
-  <si>
-    <t>134495935</t>
-  </si>
-  <si>
-    <t>134496011</t>
-  </si>
-  <si>
-    <t>134496062</t>
-  </si>
-  <si>
-    <t>134496117</t>
-  </si>
-  <si>
-    <t>134496260</t>
-  </si>
-  <si>
-    <t>134496349</t>
-  </si>
-  <si>
-    <t>134496352</t>
-  </si>
-  <si>
-    <t>134496358</t>
-  </si>
-  <si>
-    <t>134496484</t>
-  </si>
-  <si>
-    <t>134496531</t>
-  </si>
-  <si>
-    <t>134496575</t>
-  </si>
-  <si>
-    <t>134496634</t>
-  </si>
-  <si>
-    <t>134496726</t>
-  </si>
-  <si>
-    <t>134496733</t>
-  </si>
-  <si>
-    <t>134496760</t>
-  </si>
-  <si>
-    <t>134496888</t>
-  </si>
-  <si>
-    <t>134496889</t>
-  </si>
-  <si>
-    <t>134496971</t>
-  </si>
-  <si>
-    <t>134497055</t>
-  </si>
-  <si>
-    <t>134497074</t>
-  </si>
-  <si>
-    <t>134497184</t>
-  </si>
-  <si>
-    <t>134497220</t>
-  </si>
-  <si>
-    <t>134497264</t>
-  </si>
-  <si>
-    <t>134497441</t>
-  </si>
-  <si>
-    <t>134497460</t>
-  </si>
-  <si>
-    <t>134497562</t>
-  </si>
-  <si>
-    <t>134497563</t>
-  </si>
-  <si>
-    <t>134497701</t>
-  </si>
-  <si>
-    <t>134497807</t>
-  </si>
-  <si>
-    <t>134497881</t>
-  </si>
-  <si>
-    <t>134497922</t>
-  </si>
-  <si>
-    <t>134497980</t>
-  </si>
-  <si>
-    <t>134498004</t>
-  </si>
-  <si>
-    <t>134498274</t>
-  </si>
-  <si>
-    <t>134498290</t>
-  </si>
-  <si>
-    <t>134498296</t>
-  </si>
-  <si>
-    <t>134498316</t>
-  </si>
-  <si>
-    <t>134498385</t>
-  </si>
-  <si>
-    <t>134498398</t>
-  </si>
-  <si>
-    <t>134498471</t>
-  </si>
-  <si>
-    <t>134498604</t>
-  </si>
-  <si>
-    <t>134498644</t>
-  </si>
-  <si>
-    <t>134498688</t>
-  </si>
-  <si>
-    <t>134498707</t>
-  </si>
-  <si>
-    <t>134498852</t>
-  </si>
-  <si>
-    <t>134498896</t>
-  </si>
-  <si>
-    <t>134499011</t>
-  </si>
-  <si>
-    <t>134499235</t>
-  </si>
-  <si>
-    <t>134499522</t>
-  </si>
-  <si>
-    <t>134499535</t>
-  </si>
-  <si>
-    <t>134499648</t>
-  </si>
-  <si>
-    <t>134499756</t>
-  </si>
-  <si>
-    <t>134499781</t>
-  </si>
-  <si>
-    <t>134499795</t>
-  </si>
-  <si>
-    <t>134499901</t>
-  </si>
-  <si>
-    <t>134499946</t>
-  </si>
-  <si>
-    <t>134499950</t>
-  </si>
-  <si>
-    <t>134500134</t>
-  </si>
-  <si>
-    <t>134500140</t>
-  </si>
-  <si>
-    <t>134500167</t>
-  </si>
-  <si>
-    <t>134500183</t>
-  </si>
-  <si>
-    <t>134500265</t>
-  </si>
-  <si>
-    <t>134500339</t>
-  </si>
-  <si>
-    <t>134500434</t>
-  </si>
-  <si>
-    <t>134500594</t>
-  </si>
-  <si>
-    <t>134500930</t>
-  </si>
-  <si>
-    <t>134501034</t>
-  </si>
-  <si>
-    <t>134501037</t>
-  </si>
-  <si>
-    <t>134501071</t>
-  </si>
-  <si>
-    <t>134501183</t>
-  </si>
-  <si>
-    <t>134501188</t>
-  </si>
-  <si>
-    <t>134501223</t>
-  </si>
-  <si>
-    <t>134501238</t>
-  </si>
-  <si>
-    <t>134501346</t>
-  </si>
-  <si>
-    <t>134501465</t>
-  </si>
-  <si>
-    <t>134501483</t>
-  </si>
-  <si>
-    <t>134501529</t>
-  </si>
-  <si>
-    <t>134501633</t>
-  </si>
-  <si>
-    <t>134501781</t>
-  </si>
-  <si>
-    <t>134502008</t>
-  </si>
-  <si>
-    <t>134502221</t>
-  </si>
-  <si>
-    <t>134502354</t>
-  </si>
-  <si>
-    <t>134502606</t>
-  </si>
-  <si>
-    <t>134502616</t>
-  </si>
-  <si>
-    <t>134503007</t>
-  </si>
-  <si>
-    <t>134503013</t>
-  </si>
-  <si>
-    <t>134503110</t>
-  </si>
-  <si>
-    <t>134503253</t>
-  </si>
-  <si>
-    <t>134503272</t>
-  </si>
-  <si>
-    <t>134503306</t>
-  </si>
-  <si>
-    <t>134503362</t>
-  </si>
-  <si>
-    <t>134503508</t>
-  </si>
-  <si>
-    <t>134503603</t>
-  </si>
-  <si>
-    <t>134503638</t>
-  </si>
-  <si>
-    <t>134503739</t>
-  </si>
-  <si>
-    <t>134503798</t>
-  </si>
-  <si>
-    <t>134503841</t>
-  </si>
-  <si>
-    <t>134503847</t>
-  </si>
-  <si>
-    <t>134503899</t>
-  </si>
-  <si>
-    <t>134503905</t>
-  </si>
-  <si>
-    <t>134503931</t>
-  </si>
-  <si>
-    <t>134503946</t>
-  </si>
-  <si>
-    <t>134504034</t>
-  </si>
-  <si>
-    <t>134504044</t>
-  </si>
-  <si>
-    <t>134504083</t>
-  </si>
-  <si>
-    <t>134504215</t>
-  </si>
-  <si>
-    <t>134504253</t>
-  </si>
-  <si>
-    <t>134504705</t>
-  </si>
-  <si>
-    <t>134504721</t>
-  </si>
-  <si>
-    <t>134504755</t>
-  </si>
-  <si>
-    <t>134504820</t>
-  </si>
-  <si>
-    <t>134504892</t>
-  </si>
-  <si>
-    <t>134505167</t>
-  </si>
-  <si>
-    <t>134505248</t>
-  </si>
-  <si>
-    <t>134505382</t>
-  </si>
-  <si>
-    <t>134505427</t>
-  </si>
-  <si>
-    <t>134505550</t>
-  </si>
-  <si>
-    <t>134505588</t>
-  </si>
-  <si>
-    <t>134505606</t>
-  </si>
-  <si>
-    <t>134505607</t>
-  </si>
-  <si>
-    <t>134505619</t>
-  </si>
-  <si>
-    <t>134505623</t>
-  </si>
-  <si>
-    <t>134505747</t>
-  </si>
-  <si>
-    <t>134505848</t>
-  </si>
-  <si>
-    <t>134505850</t>
-  </si>
-  <si>
-    <t>134505852</t>
-  </si>
-  <si>
-    <t>134506141</t>
-  </si>
-  <si>
-    <t>134506146</t>
-  </si>
-  <si>
-    <t>134506219</t>
-  </si>
-  <si>
-    <t>134506311</t>
-  </si>
-  <si>
-    <t>134506381</t>
-  </si>
-  <si>
-    <t>134506620</t>
-  </si>
-  <si>
-    <t>134506658</t>
-  </si>
-  <si>
-    <t>134506841</t>
-  </si>
-  <si>
-    <t>134506891</t>
-  </si>
-  <si>
-    <t>134506993</t>
-  </si>
-  <si>
-    <t>134507001</t>
-  </si>
-  <si>
-    <t>134507085</t>
-  </si>
-  <si>
-    <t>134507100</t>
-  </si>
-  <si>
-    <t>134507185</t>
-  </si>
-  <si>
-    <t>134507254</t>
-  </si>
-  <si>
-    <t>134507268</t>
-  </si>
-  <si>
-    <t>134507324</t>
-  </si>
-  <si>
-    <t>134507573</t>
-  </si>
-  <si>
-    <t>134507780</t>
-  </si>
-  <si>
-    <t>134507991</t>
-  </si>
-  <si>
-    <t>134508012</t>
-  </si>
-  <si>
-    <t>134508177</t>
-  </si>
-  <si>
-    <t>134508178</t>
-  </si>
-  <si>
-    <t>134508229</t>
-  </si>
-  <si>
-    <t>134508264</t>
-  </si>
-  <si>
-    <t>134508339</t>
-  </si>
-  <si>
-    <t>134508394</t>
-  </si>
-  <si>
-    <t>134508456</t>
-  </si>
-  <si>
-    <t>134508527</t>
-  </si>
-  <si>
-    <t>134508764</t>
-  </si>
-  <si>
-    <t>134508798</t>
-  </si>
-  <si>
-    <t>134508858</t>
-  </si>
-  <si>
-    <t>134508937</t>
-  </si>
-  <si>
-    <t>134508940</t>
-  </si>
-  <si>
-    <t>134509735</t>
-  </si>
-  <si>
-    <t>134509852</t>
-  </si>
-  <si>
-    <t>134509876</t>
-  </si>
-  <si>
-    <t>134510018</t>
-  </si>
-  <si>
-    <t>134510610</t>
-  </si>
-  <si>
-    <t>134510829</t>
-  </si>
-  <si>
-    <t>134510850</t>
+    <t>129596093</t>
+  </si>
+  <si>
+    <t>129926812</t>
+  </si>
+  <si>
+    <t>129941882</t>
+  </si>
+  <si>
+    <t>130027162</t>
+  </si>
+  <si>
+    <t>130110913</t>
+  </si>
+  <si>
+    <t>130114312</t>
+  </si>
+  <si>
+    <t>130307681</t>
+  </si>
+  <si>
+    <t>130474919</t>
+  </si>
+  <si>
+    <t>130571245</t>
+  </si>
+  <si>
+    <t>130579392</t>
+  </si>
+  <si>
+    <t>130591700</t>
+  </si>
+  <si>
+    <t>130714405</t>
+  </si>
+  <si>
+    <t>130876046</t>
+  </si>
+  <si>
+    <t>130973138</t>
+  </si>
+  <si>
+    <t>130975014</t>
+  </si>
+  <si>
+    <t>131109254</t>
+  </si>
+  <si>
+    <t>131147003</t>
+  </si>
+  <si>
+    <t>131161736</t>
+  </si>
+  <si>
+    <t>131201532</t>
+  </si>
+  <si>
+    <t>131386954</t>
+  </si>
+  <si>
+    <t>131413385</t>
+  </si>
+  <si>
+    <t>131645383</t>
+  </si>
+  <si>
+    <t>131746019</t>
+  </si>
+  <si>
+    <t>131766858</t>
+  </si>
+  <si>
+    <t>131803718</t>
+  </si>
+  <si>
+    <t>131827439</t>
+  </si>
+  <si>
+    <t>131843371</t>
+  </si>
+  <si>
+    <t>131858762</t>
+  </si>
+  <si>
+    <t>131882384</t>
+  </si>
+  <si>
+    <t>131970942</t>
+  </si>
+  <si>
+    <t>132062837</t>
+  </si>
+  <si>
+    <t>132138957</t>
+  </si>
+  <si>
+    <t>132144178</t>
+  </si>
+  <si>
+    <t>132218551</t>
+  </si>
+  <si>
+    <t>132284151</t>
+  </si>
+  <si>
+    <t>132292522</t>
+  </si>
+  <si>
+    <t>132386442</t>
+  </si>
+  <si>
+    <t>132453385</t>
+  </si>
+  <si>
+    <t>132651220</t>
+  </si>
+  <si>
+    <t>132739850</t>
+  </si>
+  <si>
+    <t>133110231</t>
+  </si>
+  <si>
+    <t>133189280</t>
+  </si>
+  <si>
+    <t>133478322</t>
+  </si>
+  <si>
+    <t>133492078</t>
+  </si>
+  <si>
+    <t>133500353</t>
+  </si>
+  <si>
+    <t>133628000</t>
+  </si>
+  <si>
+    <t>133737515</t>
+  </si>
+  <si>
+    <t>133905880</t>
+  </si>
+  <si>
+    <t>133929895</t>
+  </si>
+  <si>
+    <t>134038379</t>
+  </si>
+  <si>
+    <t>134209978</t>
+  </si>
+  <si>
+    <t>134277580</t>
+  </si>
+  <si>
+    <t>134302385</t>
+  </si>
+  <si>
+    <t>134322375</t>
+  </si>
+  <si>
+    <t>134351976</t>
+  </si>
+  <si>
+    <t>134526227</t>
+  </si>
+  <si>
+    <t>134635835</t>
+  </si>
+  <si>
+    <t>134675222</t>
+  </si>
+  <si>
+    <t>134675372</t>
+  </si>
+  <si>
+    <t>134675373</t>
+  </si>
+  <si>
+    <t>134675399</t>
+  </si>
+  <si>
+    <t>134675423</t>
+  </si>
+  <si>
+    <t>134675458</t>
+  </si>
+  <si>
+    <t>134675667</t>
+  </si>
+  <si>
+    <t>134675712</t>
+  </si>
+  <si>
+    <t>134675765</t>
+  </si>
+  <si>
+    <t>134675780</t>
+  </si>
+  <si>
+    <t>134675860</t>
+  </si>
+  <si>
+    <t>134676104</t>
+  </si>
+  <si>
+    <t>134676254</t>
+  </si>
+  <si>
+    <t>134676322</t>
+  </si>
+  <si>
+    <t>134676324</t>
+  </si>
+  <si>
+    <t>134676441</t>
+  </si>
+  <si>
+    <t>134676499</t>
+  </si>
+  <si>
+    <t>134676833</t>
+  </si>
+  <si>
+    <t>134676848</t>
+  </si>
+  <si>
+    <t>134676910</t>
+  </si>
+  <si>
+    <t>134677034</t>
+  </si>
+  <si>
+    <t>134677176</t>
+  </si>
+  <si>
+    <t>134677389</t>
+  </si>
+  <si>
+    <t>134677448</t>
+  </si>
+  <si>
+    <t>134677513</t>
+  </si>
+  <si>
+    <t>134677540</t>
+  </si>
+  <si>
+    <t>134677599</t>
+  </si>
+  <si>
+    <t>134677605</t>
+  </si>
+  <si>
+    <t>134677614</t>
+  </si>
+  <si>
+    <t>134677653</t>
+  </si>
+  <si>
+    <t>134677702</t>
+  </si>
+  <si>
+    <t>134677794</t>
+  </si>
+  <si>
+    <t>134677841</t>
+  </si>
+  <si>
+    <t>134677935</t>
+  </si>
+  <si>
+    <t>134678080</t>
+  </si>
+  <si>
+    <t>134678110</t>
+  </si>
+  <si>
+    <t>134678188</t>
+  </si>
+  <si>
+    <t>134678211</t>
+  </si>
+  <si>
+    <t>134678564</t>
+  </si>
+  <si>
+    <t>134678720</t>
+  </si>
+  <si>
+    <t>134678736</t>
+  </si>
+  <si>
+    <t>134678745</t>
+  </si>
+  <si>
+    <t>134678751</t>
+  </si>
+  <si>
+    <t>134678765</t>
+  </si>
+  <si>
+    <t>134678774</t>
+  </si>
+  <si>
+    <t>134678780</t>
+  </si>
+  <si>
+    <t>134678859</t>
+  </si>
+  <si>
+    <t>134678912</t>
+  </si>
+  <si>
+    <t>134678976</t>
+  </si>
+  <si>
+    <t>134678982</t>
+  </si>
+  <si>
+    <t>134679064</t>
+  </si>
+  <si>
+    <t>134679276</t>
+  </si>
+  <si>
+    <t>134679317</t>
+  </si>
+  <si>
+    <t>134679333</t>
+  </si>
+  <si>
+    <t>134679395</t>
+  </si>
+  <si>
+    <t>134679397</t>
+  </si>
+  <si>
+    <t>134679431</t>
+  </si>
+  <si>
+    <t>134679457</t>
+  </si>
+  <si>
+    <t>134679727</t>
+  </si>
+  <si>
+    <t>134679799</t>
+  </si>
+  <si>
+    <t>134679876</t>
+  </si>
+  <si>
+    <t>134679934</t>
+  </si>
+  <si>
+    <t>134679980</t>
+  </si>
+  <si>
+    <t>134680059</t>
+  </si>
+  <si>
+    <t>134680072</t>
+  </si>
+  <si>
+    <t>134680134</t>
+  </si>
+  <si>
+    <t>134680220</t>
+  </si>
+  <si>
+    <t>134680225</t>
+  </si>
+  <si>
+    <t>134680301</t>
+  </si>
+  <si>
+    <t>134680333</t>
+  </si>
+  <si>
+    <t>134680703</t>
+  </si>
+  <si>
+    <t>134680753</t>
+  </si>
+  <si>
+    <t>134680754</t>
+  </si>
+  <si>
+    <t>134680770</t>
+  </si>
+  <si>
+    <t>134680812</t>
+  </si>
+  <si>
+    <t>134680848</t>
+  </si>
+  <si>
+    <t>134680858</t>
+  </si>
+  <si>
+    <t>134680931</t>
+  </si>
+  <si>
+    <t>134680934</t>
+  </si>
+  <si>
+    <t>134680989</t>
+  </si>
+  <si>
+    <t>134681055</t>
+  </si>
+  <si>
+    <t>134681098</t>
+  </si>
+  <si>
+    <t>134681206</t>
+  </si>
+  <si>
+    <t>134681211</t>
+  </si>
+  <si>
+    <t>134681332</t>
+  </si>
+  <si>
+    <t>134681396</t>
+  </si>
+  <si>
+    <t>134681499</t>
+  </si>
+  <si>
+    <t>134681507</t>
+  </si>
+  <si>
+    <t>134681724</t>
+  </si>
+  <si>
+    <t>134681935</t>
+  </si>
+  <si>
+    <t>134682012</t>
+  </si>
+  <si>
+    <t>134682106</t>
+  </si>
+  <si>
+    <t>134682187</t>
+  </si>
+  <si>
+    <t>134682190</t>
+  </si>
+  <si>
+    <t>134682380</t>
+  </si>
+  <si>
+    <t>134682390</t>
+  </si>
+  <si>
+    <t>134682416</t>
+  </si>
+  <si>
+    <t>134682490</t>
+  </si>
+  <si>
+    <t>134682606</t>
+  </si>
+  <si>
+    <t>134682607</t>
+  </si>
+  <si>
+    <t>134682805</t>
+  </si>
+  <si>
+    <t>134682828</t>
+  </si>
+  <si>
+    <t>134682847</t>
+  </si>
+  <si>
+    <t>134682935</t>
+  </si>
+  <si>
+    <t>134682963</t>
+  </si>
+  <si>
+    <t>134683003</t>
+  </si>
+  <si>
+    <t>134683159</t>
+  </si>
+  <si>
+    <t>134683171</t>
+  </si>
+  <si>
+    <t>134683243</t>
+  </si>
+  <si>
+    <t>134683270</t>
+  </si>
+  <si>
+    <t>134683355</t>
+  </si>
+  <si>
+    <t>134683357</t>
+  </si>
+  <si>
+    <t>134683463</t>
+  </si>
+  <si>
+    <t>134683488</t>
+  </si>
+  <si>
+    <t>134683615</t>
+  </si>
+  <si>
+    <t>134683746</t>
+  </si>
+  <si>
+    <t>134683814</t>
+  </si>
+  <si>
+    <t>134683864</t>
+  </si>
+  <si>
+    <t>134683866</t>
+  </si>
+  <si>
+    <t>134684060</t>
+  </si>
+  <si>
+    <t>134684240</t>
+  </si>
+  <si>
+    <t>134684432</t>
+  </si>
+  <si>
+    <t>134684436</t>
+  </si>
+  <si>
+    <t>134684441</t>
+  </si>
+  <si>
+    <t>134684475</t>
+  </si>
+  <si>
+    <t>134684641</t>
+  </si>
+  <si>
+    <t>134684657</t>
+  </si>
+  <si>
+    <t>134684696</t>
+  </si>
+  <si>
+    <t>134684719</t>
+  </si>
+  <si>
+    <t>134684742</t>
+  </si>
+  <si>
+    <t>134684781</t>
+  </si>
+  <si>
+    <t>134684798</t>
+  </si>
+  <si>
+    <t>134684949</t>
+  </si>
+  <si>
+    <t>134684957</t>
+  </si>
+  <si>
+    <t>134684996</t>
+  </si>
+  <si>
+    <t>134685001</t>
+  </si>
+  <si>
+    <t>134685008</t>
+  </si>
+  <si>
+    <t>134685016</t>
+  </si>
+  <si>
+    <t>134685018</t>
+  </si>
+  <si>
+    <t>134685033</t>
+  </si>
+  <si>
+    <t>134685097</t>
+  </si>
+  <si>
+    <t>134685182</t>
+  </si>
+  <si>
+    <t>134685315</t>
+  </si>
+  <si>
+    <t>134685479</t>
+  </si>
+  <si>
+    <t>134685498</t>
+  </si>
+  <si>
+    <t>134685851</t>
+  </si>
+  <si>
+    <t>134686075</t>
+  </si>
+  <si>
+    <t>134686326</t>
+  </si>
+  <si>
+    <t>134686353</t>
+  </si>
+  <si>
+    <t>134686485</t>
+  </si>
+  <si>
+    <t>134686494</t>
+  </si>
+  <si>
+    <t>134686633</t>
+  </si>
+  <si>
+    <t>134686673</t>
+  </si>
+  <si>
+    <t>134686686</t>
+  </si>
+  <si>
+    <t>134686805</t>
+  </si>
+  <si>
+    <t>134686928</t>
+  </si>
+  <si>
+    <t>134686938</t>
+  </si>
+  <si>
+    <t>134686945</t>
+  </si>
+  <si>
+    <t>134686960</t>
+  </si>
+  <si>
+    <t>134687019</t>
+  </si>
+  <si>
+    <t>134687085</t>
+  </si>
+  <si>
+    <t>134687107</t>
+  </si>
+  <si>
+    <t>134687135</t>
+  </si>
+  <si>
+    <t>134687165</t>
+  </si>
+  <si>
+    <t>134687171</t>
+  </si>
+  <si>
+    <t>134687213</t>
+  </si>
+  <si>
+    <t>134687260</t>
+  </si>
+  <si>
+    <t>134687290</t>
+  </si>
+  <si>
+    <t>134687301</t>
+  </si>
+  <si>
+    <t>134687322</t>
+  </si>
+  <si>
+    <t>134687385</t>
+  </si>
+  <si>
+    <t>134687474</t>
+  </si>
+  <si>
+    <t>134687631</t>
+  </si>
+  <si>
+    <t>134687639</t>
+  </si>
+  <si>
+    <t>134687744</t>
+  </si>
+  <si>
+    <t>134687757</t>
+  </si>
+  <si>
+    <t>134687902</t>
+  </si>
+  <si>
+    <t>134687908</t>
+  </si>
+  <si>
+    <t>134687936</t>
+  </si>
+  <si>
+    <t>134687979</t>
+  </si>
+  <si>
+    <t>134688008</t>
+  </si>
+  <si>
+    <t>134688045</t>
+  </si>
+  <si>
+    <t>134688052</t>
+  </si>
+  <si>
+    <t>134688136</t>
+  </si>
+  <si>
+    <t>134688236</t>
+  </si>
+  <si>
+    <t>134688273</t>
+  </si>
+  <si>
+    <t>134688278</t>
+  </si>
+  <si>
+    <t>134688362</t>
+  </si>
+  <si>
+    <t>134688473</t>
+  </si>
+  <si>
+    <t>134688573</t>
+  </si>
+  <si>
+    <t>134688695</t>
+  </si>
+  <si>
+    <t>134688730</t>
+  </si>
+  <si>
+    <t>134688811</t>
+  </si>
+  <si>
+    <t>134688869</t>
+  </si>
+  <si>
+    <t>134688909</t>
+  </si>
+  <si>
+    <t>134688982</t>
+  </si>
+  <si>
+    <t>134689030</t>
+  </si>
+  <si>
+    <t>134689146</t>
+  </si>
+  <si>
+    <t>134689189</t>
+  </si>
+  <si>
+    <t>134689302</t>
+  </si>
+  <si>
+    <t>134689356</t>
+  </si>
+  <si>
+    <t>134689383</t>
+  </si>
+  <si>
+    <t>134689520</t>
+  </si>
+  <si>
+    <t>134689676</t>
+  </si>
+  <si>
+    <t>134689719</t>
+  </si>
+  <si>
+    <t>134689748</t>
+  </si>
+  <si>
+    <t>134689787</t>
+  </si>
+  <si>
+    <t>134689813</t>
+  </si>
+  <si>
+    <t>134689874</t>
+  </si>
+  <si>
+    <t>134689915</t>
+  </si>
+  <si>
+    <t>134689978</t>
+  </si>
+  <si>
+    <t>134689979</t>
+  </si>
+  <si>
+    <t>134690080</t>
+  </si>
+  <si>
+    <t>134690132</t>
+  </si>
+  <si>
+    <t>134690147</t>
+  </si>
+  <si>
+    <t>134690328</t>
+  </si>
+  <si>
+    <t>134690358</t>
+  </si>
+  <si>
+    <t>134690365</t>
+  </si>
+  <si>
+    <t>134690366</t>
+  </si>
+  <si>
+    <t>134690418</t>
+  </si>
+  <si>
+    <t>134690452</t>
+  </si>
+  <si>
+    <t>134690489</t>
+  </si>
+  <si>
+    <t>134690505</t>
+  </si>
+  <si>
+    <t>134690653</t>
+  </si>
+  <si>
+    <t>134690688</t>
+  </si>
+  <si>
+    <t>134690740</t>
+  </si>
+  <si>
+    <t>134690754</t>
+  </si>
+  <si>
+    <t>134690838</t>
+  </si>
+  <si>
+    <t>134690904</t>
+  </si>
+  <si>
+    <t>134690928</t>
+  </si>
+  <si>
+    <t>134691004</t>
+  </si>
+  <si>
+    <t>134691013</t>
+  </si>
+  <si>
+    <t>134691034</t>
+  </si>
+  <si>
+    <t>134691041</t>
+  </si>
+  <si>
+    <t>134691112</t>
+  </si>
+  <si>
+    <t>134691122</t>
+  </si>
+  <si>
+    <t>134691177</t>
+  </si>
+  <si>
+    <t>134691236</t>
+  </si>
+  <si>
+    <t>134691356</t>
+  </si>
+  <si>
+    <t>134691360</t>
+  </si>
+  <si>
+    <t>134691403</t>
+  </si>
+  <si>
+    <t>134691483</t>
+  </si>
+  <si>
+    <t>134691492</t>
+  </si>
+  <si>
+    <t>134691511</t>
+  </si>
+  <si>
+    <t>134691645</t>
+  </si>
+  <si>
+    <t>134691667</t>
+  </si>
+  <si>
+    <t>134691736</t>
+  </si>
+  <si>
+    <t>134691773</t>
+  </si>
+  <si>
+    <t>134691825</t>
+  </si>
+  <si>
+    <t>134691892</t>
+  </si>
+  <si>
+    <t>134691931</t>
+  </si>
+  <si>
+    <t>134691958</t>
+  </si>
+  <si>
+    <t>134692074</t>
+  </si>
+  <si>
+    <t>134692159</t>
+  </si>
+  <si>
+    <t>134692177</t>
+  </si>
+  <si>
+    <t>134692186</t>
+  </si>
+  <si>
+    <t>134692265</t>
+  </si>
+  <si>
+    <t>134692290</t>
+  </si>
+  <si>
+    <t>134692367</t>
+  </si>
+  <si>
+    <t>134692385</t>
+  </si>
+  <si>
+    <t>134692405</t>
+  </si>
+  <si>
+    <t>134692425</t>
+  </si>
+  <si>
+    <t>134692469</t>
+  </si>
+  <si>
+    <t>134692480</t>
+  </si>
+  <si>
+    <t>134692565</t>
+  </si>
+  <si>
+    <t>134692600</t>
+  </si>
+  <si>
+    <t>134692605</t>
+  </si>
+  <si>
+    <t>134692686</t>
+  </si>
+  <si>
+    <t>134692699</t>
+  </si>
+  <si>
+    <t>134692730</t>
+  </si>
+  <si>
+    <t>134692808</t>
+  </si>
+  <si>
+    <t>134692817</t>
+  </si>
+  <si>
+    <t>134692835</t>
+  </si>
+  <si>
+    <t>134692885</t>
+  </si>
+  <si>
+    <t>134692952</t>
+  </si>
+  <si>
+    <t>134693022</t>
+  </si>
+  <si>
+    <t>134693051</t>
+  </si>
+  <si>
+    <t>134693137</t>
+  </si>
+  <si>
+    <t>134693163</t>
+  </si>
+  <si>
+    <t>134693169</t>
+  </si>
+  <si>
+    <t>134693170</t>
+  </si>
+  <si>
+    <t>134693181</t>
+  </si>
+  <si>
+    <t>134693212</t>
+  </si>
+  <si>
+    <t>134693286</t>
+  </si>
+  <si>
+    <t>134693396</t>
+  </si>
+  <si>
+    <t>134693418</t>
+  </si>
+  <si>
+    <t>134693434</t>
+  </si>
+  <si>
+    <t>134693482</t>
+  </si>
+  <si>
+    <t>134693495</t>
+  </si>
+  <si>
+    <t>134693508</t>
+  </si>
+  <si>
+    <t>134693532</t>
+  </si>
+  <si>
+    <t>134693609</t>
+  </si>
+  <si>
+    <t>134693625</t>
+  </si>
+  <si>
+    <t>134693626</t>
+  </si>
+  <si>
+    <t>134693727</t>
+  </si>
+  <si>
+    <t>134693749</t>
+  </si>
+  <si>
+    <t>134693837</t>
+  </si>
+  <si>
+    <t>134693885</t>
+  </si>
+  <si>
+    <t>134693932</t>
+  </si>
+  <si>
+    <t>134694003</t>
+  </si>
+  <si>
+    <t>134694084</t>
+  </si>
+  <si>
+    <t>134694107</t>
+  </si>
+  <si>
+    <t>134694147</t>
+  </si>
+  <si>
+    <t>134694208</t>
+  </si>
+  <si>
+    <t>134694280</t>
+  </si>
+  <si>
+    <t>134694370</t>
+  </si>
+  <si>
+    <t>134694372</t>
+  </si>
+  <si>
+    <t>134694402</t>
+  </si>
+  <si>
+    <t>134694441</t>
+  </si>
+  <si>
+    <t>134694721</t>
+  </si>
+  <si>
+    <t>134694828</t>
+  </si>
+  <si>
+    <t>134694961</t>
+  </si>
+  <si>
+    <t>134694963</t>
+  </si>
+  <si>
+    <t>134694986</t>
+  </si>
+  <si>
+    <t>134695130</t>
+  </si>
+  <si>
+    <t>134695488</t>
+  </si>
+  <si>
+    <t>134695984</t>
+  </si>
+  <si>
+    <t>134696079</t>
+  </si>
+  <si>
+    <t>134696090</t>
+  </si>
+  <si>
+    <t>134696100</t>
+  </si>
+  <si>
+    <t>134696145</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C333"/>
+  <dimension ref="A1:C381"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1291,7 +1609,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>3</v>
@@ -1302,7 +1620,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>3</v>
@@ -1313,7 +1631,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>3</v>
@@ -1324,7 +1642,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>3</v>
@@ -1335,7 +1653,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>3</v>
@@ -1346,7 +1664,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>3</v>
@@ -1357,7 +1675,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
@@ -1368,7 +1686,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>3</v>
@@ -1379,7 +1697,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>3</v>
@@ -1390,7 +1708,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>3</v>
@@ -1401,7 +1719,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>3</v>
@@ -1412,7 +1730,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>3</v>
@@ -1423,7 +1741,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>3</v>
@@ -1434,7 +1752,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>3</v>
@@ -1445,7 +1763,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>3</v>
@@ -1456,7 +1774,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>3</v>
@@ -1467,7 +1785,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>3</v>
@@ -1478,7 +1796,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>3</v>
@@ -1489,7 +1807,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>3</v>
@@ -1500,7 +1818,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>3</v>
@@ -1511,7 +1829,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>3</v>
@@ -1522,7 +1840,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>3</v>
@@ -1533,7 +1851,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>3</v>
@@ -1544,7 +1862,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>3</v>
@@ -1555,7 +1873,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>3</v>
@@ -1566,7 +1884,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>3</v>
@@ -1577,7 +1895,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>3</v>
@@ -1588,7 +1906,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>3</v>
@@ -1599,7 +1917,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>3</v>
@@ -1610,7 +1928,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>3</v>
@@ -1621,7 +1939,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>3</v>
@@ -4304,351 +4622,1025 @@
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B276" s="6"/>
+      <c r="A276" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C276" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B277" s="6"/>
+      <c r="A277" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C277" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B278" s="6"/>
+      <c r="A278" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C278" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B279" s="6"/>
+      <c r="A279" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C279" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B280" s="6"/>
+      <c r="A280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C280" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B281" s="6"/>
+      <c r="A281" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C281" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B282" s="6"/>
+      <c r="A282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C282" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B283" s="6"/>
+      <c r="A283" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C283" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B284" s="6"/>
+      <c r="A284" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C284" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B285" s="6"/>
+      <c r="A285" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C285" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B286" s="6"/>
+      <c r="A286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C286" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B287" s="6"/>
+      <c r="A287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C287" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B288" s="6"/>
+      <c r="A288" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C288" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B289" s="6"/>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C289" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B290" s="6"/>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C290" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B291" s="6"/>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C291" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B292" s="6"/>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C292" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B293" s="6"/>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C293" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B294" s="6"/>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C294" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B295" s="6"/>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C295" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B296" s="6"/>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C296" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B297" s="6"/>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C297" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B298" s="6"/>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C298" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B299" s="6"/>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C299" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B300" s="6"/>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C300" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B301" s="6"/>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C301" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B302" s="6"/>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C302" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B303" s="6"/>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C303" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B304" s="6"/>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C304" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B305" s="6"/>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C305" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B306" s="6"/>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C306" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B307" s="6"/>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C307" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B308" s="6"/>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C308" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B309" s="6"/>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C309" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B310" s="6"/>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C310" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B311" s="6"/>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C311" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B312" s="6"/>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C312" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B313" s="6"/>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C313" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B314" s="6"/>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C314" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B315" s="6"/>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C315" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B316" s="6"/>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C316" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B317" s="6"/>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C317" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B318" s="6"/>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C318" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B319" s="6"/>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C319" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B320" s="6"/>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C320" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B321" s="6"/>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C321" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B322" s="6"/>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C322" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B323" s="6"/>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C323" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B324" s="6"/>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C324" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B325" s="6"/>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C325" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B326" s="6"/>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C326" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B327" s="6"/>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C327" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B328" s="6"/>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C328" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B329" s="6"/>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C329" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B330" s="6"/>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C330" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B331" s="6"/>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C331" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B332" s="6"/>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C332" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B333" s="6"/>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C333" s="5" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B340" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B353" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B364" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B367" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B369" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B370" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B372" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B373" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B375" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D82966E-8DD4-4A94-894B-A6C0C8E0D1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C02AC38-933A-4F70-ABF3-B930C02C7D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="324">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,1012 +45,961 @@
     <t>.</t>
   </si>
   <si>
-    <t>130033158</t>
-  </si>
-  <si>
-    <t>130038275</t>
-  </si>
-  <si>
-    <t>130080229</t>
-  </si>
-  <si>
-    <t>130201120</t>
-  </si>
-  <si>
-    <t>130292420</t>
-  </si>
-  <si>
-    <t>130459049</t>
-  </si>
-  <si>
-    <t>130490145</t>
-  </si>
-  <si>
-    <t>130668575</t>
-  </si>
-  <si>
-    <t>130669432</t>
-  </si>
-  <si>
-    <t>130764110</t>
-  </si>
-  <si>
-    <t>130841536</t>
-  </si>
-  <si>
-    <t>130924980</t>
-  </si>
-  <si>
-    <t>131064720</t>
-  </si>
-  <si>
-    <t>131089027</t>
-  </si>
-  <si>
-    <t>131463581</t>
-  </si>
-  <si>
-    <t>131470062</t>
-  </si>
-  <si>
-    <t>131716429</t>
-  </si>
-  <si>
-    <t>131747131</t>
-  </si>
-  <si>
-    <t>131800496</t>
-  </si>
-  <si>
-    <t>131904301</t>
-  </si>
-  <si>
-    <t>132051407</t>
-  </si>
-  <si>
-    <t>132087920</t>
-  </si>
-  <si>
-    <t>132493844</t>
-  </si>
-  <si>
-    <t>132990746</t>
-  </si>
-  <si>
-    <t>133060437</t>
-  </si>
-  <si>
-    <t>133066678</t>
-  </si>
-  <si>
-    <t>133083179</t>
-  </si>
-  <si>
-    <t>133344847</t>
-  </si>
-  <si>
-    <t>133512934</t>
-  </si>
-  <si>
-    <t>133677614</t>
-  </si>
-  <si>
-    <t>133687665</t>
-  </si>
-  <si>
-    <t>133728808</t>
-  </si>
-  <si>
-    <t>133794072</t>
-  </si>
-  <si>
-    <t>133909717</t>
-  </si>
-  <si>
-    <t>133953433</t>
-  </si>
-  <si>
-    <t>134154359</t>
-  </si>
-  <si>
-    <t>134156730</t>
-  </si>
-  <si>
-    <t>134318934</t>
-  </si>
-  <si>
-    <t>134418400</t>
-  </si>
-  <si>
-    <t>134424954</t>
-  </si>
-  <si>
-    <t>134696534</t>
-  </si>
-  <si>
-    <t>134696628</t>
-  </si>
-  <si>
-    <t>134696691</t>
-  </si>
-  <si>
-    <t>134696810</t>
-  </si>
-  <si>
-    <t>134697056</t>
-  </si>
-  <si>
-    <t>134697097</t>
-  </si>
-  <si>
-    <t>134697217</t>
-  </si>
-  <si>
-    <t>134697399</t>
-  </si>
-  <si>
-    <t>134697417</t>
-  </si>
-  <si>
-    <t>134697476</t>
-  </si>
-  <si>
-    <t>134697658</t>
-  </si>
-  <si>
-    <t>134697673</t>
-  </si>
-  <si>
-    <t>134697849</t>
-  </si>
-  <si>
-    <t>134697864</t>
-  </si>
-  <si>
-    <t>134697889</t>
-  </si>
-  <si>
-    <t>134697904</t>
-  </si>
-  <si>
-    <t>134697915</t>
-  </si>
-  <si>
-    <t>134698048</t>
-  </si>
-  <si>
-    <t>134698124</t>
-  </si>
-  <si>
-    <t>134698198</t>
-  </si>
-  <si>
-    <t>134698243</t>
-  </si>
-  <si>
-    <t>134698277</t>
-  </si>
-  <si>
-    <t>134698282</t>
-  </si>
-  <si>
-    <t>134698293</t>
-  </si>
-  <si>
-    <t>134698398</t>
-  </si>
-  <si>
-    <t>134698478</t>
-  </si>
-  <si>
-    <t>134698542</t>
-  </si>
-  <si>
-    <t>134698556</t>
-  </si>
-  <si>
-    <t>134698568</t>
-  </si>
-  <si>
-    <t>134698592</t>
-  </si>
-  <si>
-    <t>134698678</t>
-  </si>
-  <si>
-    <t>134698730</t>
-  </si>
-  <si>
-    <t>134698899</t>
-  </si>
-  <si>
-    <t>134698944</t>
-  </si>
-  <si>
-    <t>134699118</t>
-  </si>
-  <si>
-    <t>134699150</t>
-  </si>
-  <si>
-    <t>134699179</t>
-  </si>
-  <si>
-    <t>134699249</t>
-  </si>
-  <si>
-    <t>134699316</t>
-  </si>
-  <si>
-    <t>134699362</t>
-  </si>
-  <si>
-    <t>134699368</t>
-  </si>
-  <si>
-    <t>134699433</t>
-  </si>
-  <si>
-    <t>134699520</t>
-  </si>
-  <si>
-    <t>134699736</t>
-  </si>
-  <si>
-    <t>134699986</t>
-  </si>
-  <si>
-    <t>134700129</t>
-  </si>
-  <si>
-    <t>134700131</t>
-  </si>
-  <si>
-    <t>134700232</t>
-  </si>
-  <si>
-    <t>134700240</t>
-  </si>
-  <si>
-    <t>134700248</t>
-  </si>
-  <si>
-    <t>134700263</t>
-  </si>
-  <si>
-    <t>134700273</t>
-  </si>
-  <si>
-    <t>134700418</t>
-  </si>
-  <si>
-    <t>134700580</t>
-  </si>
-  <si>
-    <t>134700624</t>
-  </si>
-  <si>
-    <t>134700667</t>
-  </si>
-  <si>
-    <t>134700832</t>
-  </si>
-  <si>
-    <t>134700854</t>
-  </si>
-  <si>
-    <t>134700922</t>
-  </si>
-  <si>
-    <t>134701193</t>
-  </si>
-  <si>
-    <t>134701209</t>
-  </si>
-  <si>
-    <t>134701236</t>
-  </si>
-  <si>
-    <t>134701447</t>
-  </si>
-  <si>
-    <t>134701456</t>
-  </si>
-  <si>
-    <t>134701599</t>
-  </si>
-  <si>
-    <t>134701648</t>
-  </si>
-  <si>
-    <t>134701828</t>
-  </si>
-  <si>
-    <t>134701829</t>
-  </si>
-  <si>
-    <t>134701869</t>
-  </si>
-  <si>
-    <t>134701905</t>
-  </si>
-  <si>
-    <t>134701925</t>
-  </si>
-  <si>
-    <t>134702041</t>
-  </si>
-  <si>
-    <t>134702042</t>
-  </si>
-  <si>
-    <t>134702149</t>
-  </si>
-  <si>
-    <t>134702162</t>
-  </si>
-  <si>
-    <t>134702184</t>
-  </si>
-  <si>
-    <t>134702244</t>
-  </si>
-  <si>
-    <t>134702284</t>
-  </si>
-  <si>
-    <t>134702322</t>
-  </si>
-  <si>
-    <t>134702457</t>
-  </si>
-  <si>
-    <t>134702464</t>
-  </si>
-  <si>
-    <t>134702570</t>
-  </si>
-  <si>
-    <t>134702687</t>
-  </si>
-  <si>
-    <t>134702710</t>
-  </si>
-  <si>
-    <t>134702759</t>
-  </si>
-  <si>
-    <t>134703023</t>
-  </si>
-  <si>
-    <t>134703094</t>
-  </si>
-  <si>
-    <t>134703158</t>
-  </si>
-  <si>
-    <t>134703241</t>
-  </si>
-  <si>
-    <t>134703341</t>
-  </si>
-  <si>
-    <t>134703374</t>
-  </si>
-  <si>
-    <t>134703508</t>
-  </si>
-  <si>
-    <t>134703555</t>
-  </si>
-  <si>
-    <t>134703560</t>
-  </si>
-  <si>
-    <t>134703708</t>
-  </si>
-  <si>
-    <t>134703718</t>
-  </si>
-  <si>
-    <t>134703788</t>
-  </si>
-  <si>
-    <t>134703859</t>
-  </si>
-  <si>
-    <t>134703911</t>
-  </si>
-  <si>
-    <t>134704005</t>
-  </si>
-  <si>
-    <t>134704154</t>
-  </si>
-  <si>
-    <t>134704194</t>
-  </si>
-  <si>
-    <t>134704437</t>
-  </si>
-  <si>
-    <t>134704471</t>
-  </si>
-  <si>
-    <t>134704602</t>
-  </si>
-  <si>
-    <t>134704620</t>
-  </si>
-  <si>
-    <t>134704659</t>
-  </si>
-  <si>
-    <t>134704709</t>
-  </si>
-  <si>
-    <t>134704735</t>
-  </si>
-  <si>
-    <t>134704740</t>
-  </si>
-  <si>
-    <t>134704767</t>
-  </si>
-  <si>
-    <t>134704840</t>
-  </si>
-  <si>
-    <t>134704934</t>
-  </si>
-  <si>
-    <t>134705129</t>
-  </si>
-  <si>
-    <t>134705160</t>
-  </si>
-  <si>
-    <t>134705178</t>
-  </si>
-  <si>
-    <t>134705214</t>
-  </si>
-  <si>
-    <t>134705393</t>
-  </si>
-  <si>
-    <t>134705558</t>
-  </si>
-  <si>
-    <t>134705705</t>
-  </si>
-  <si>
-    <t>134705802</t>
-  </si>
-  <si>
-    <t>134705830</t>
-  </si>
-  <si>
-    <t>134705963</t>
-  </si>
-  <si>
-    <t>134705965</t>
-  </si>
-  <si>
-    <t>134705973</t>
-  </si>
-  <si>
-    <t>134706001</t>
-  </si>
-  <si>
-    <t>134706064</t>
-  </si>
-  <si>
-    <t>134706140</t>
-  </si>
-  <si>
-    <t>134706403</t>
-  </si>
-  <si>
-    <t>134706578</t>
-  </si>
-  <si>
-    <t>134706658</t>
-  </si>
-  <si>
-    <t>134706692</t>
-  </si>
-  <si>
-    <t>134706758</t>
-  </si>
-  <si>
-    <t>134706800</t>
-  </si>
-  <si>
-    <t>134706806</t>
-  </si>
-  <si>
-    <t>134706922</t>
-  </si>
-  <si>
-    <t>134707034</t>
-  </si>
-  <si>
-    <t>134707045</t>
-  </si>
-  <si>
-    <t>134707055</t>
-  </si>
-  <si>
-    <t>134707464</t>
-  </si>
-  <si>
-    <t>134707627</t>
-  </si>
-  <si>
-    <t>134707658</t>
-  </si>
-  <si>
-    <t>134707685</t>
-  </si>
-  <si>
-    <t>134707736</t>
-  </si>
-  <si>
-    <t>134707749</t>
-  </si>
-  <si>
-    <t>134707976</t>
-  </si>
-  <si>
-    <t>134708036</t>
-  </si>
-  <si>
-    <t>134708092</t>
-  </si>
-  <si>
-    <t>134708219</t>
-  </si>
-  <si>
-    <t>134708273</t>
-  </si>
-  <si>
-    <t>134708302</t>
-  </si>
-  <si>
-    <t>134708350</t>
-  </si>
-  <si>
-    <t>134708381</t>
-  </si>
-  <si>
-    <t>134708395</t>
-  </si>
-  <si>
-    <t>134708462</t>
-  </si>
-  <si>
-    <t>134708524</t>
-  </si>
-  <si>
-    <t>134708607</t>
-  </si>
-  <si>
-    <t>134708678</t>
-  </si>
-  <si>
-    <t>134708989</t>
-  </si>
-  <si>
-    <t>134709009</t>
-  </si>
-  <si>
-    <t>134709137</t>
-  </si>
-  <si>
-    <t>134709174</t>
-  </si>
-  <si>
-    <t>134709321</t>
-  </si>
-  <si>
-    <t>134709337</t>
-  </si>
-  <si>
-    <t>134709355</t>
-  </si>
-  <si>
-    <t>134709424</t>
-  </si>
-  <si>
-    <t>134709479</t>
-  </si>
-  <si>
-    <t>134709484</t>
-  </si>
-  <si>
-    <t>134709626</t>
-  </si>
-  <si>
-    <t>134709632</t>
-  </si>
-  <si>
-    <t>134709672</t>
-  </si>
-  <si>
-    <t>134709764</t>
-  </si>
-  <si>
-    <t>134710021</t>
-  </si>
-  <si>
-    <t>134710322</t>
-  </si>
-  <si>
-    <t>134710352</t>
-  </si>
-  <si>
-    <t>134710481</t>
-  </si>
-  <si>
-    <t>134710715</t>
-  </si>
-  <si>
-    <t>134710734</t>
-  </si>
-  <si>
-    <t>134710752</t>
-  </si>
-  <si>
-    <t>134710776</t>
-  </si>
-  <si>
-    <t>134710837</t>
-  </si>
-  <si>
-    <t>134710859</t>
-  </si>
-  <si>
-    <t>134710861</t>
-  </si>
-  <si>
-    <t>134710928</t>
-  </si>
-  <si>
-    <t>134710958</t>
-  </si>
-  <si>
-    <t>134711163</t>
-  </si>
-  <si>
-    <t>134711197</t>
-  </si>
-  <si>
-    <t>134711304</t>
-  </si>
-  <si>
-    <t>134711320</t>
-  </si>
-  <si>
-    <t>134711547</t>
-  </si>
-  <si>
-    <t>134711548</t>
-  </si>
-  <si>
-    <t>134711662</t>
-  </si>
-  <si>
-    <t>134711717</t>
-  </si>
-  <si>
-    <t>134711761</t>
-  </si>
-  <si>
-    <t>134711784</t>
-  </si>
-  <si>
-    <t>134711824</t>
-  </si>
-  <si>
-    <t>134711858</t>
-  </si>
-  <si>
-    <t>134711889</t>
-  </si>
-  <si>
-    <t>134711937</t>
-  </si>
-  <si>
-    <t>134711939</t>
-  </si>
-  <si>
-    <t>134712152</t>
-  </si>
-  <si>
-    <t>134712206</t>
-  </si>
-  <si>
-    <t>134712248</t>
-  </si>
-  <si>
-    <t>134712395</t>
-  </si>
-  <si>
-    <t>134712402</t>
-  </si>
-  <si>
-    <t>134712455</t>
-  </si>
-  <si>
-    <t>134712513</t>
-  </si>
-  <si>
-    <t>134712544</t>
-  </si>
-  <si>
-    <t>134712597</t>
-  </si>
-  <si>
-    <t>134712612</t>
-  </si>
-  <si>
-    <t>134712857</t>
-  </si>
-  <si>
-    <t>134712996</t>
-  </si>
-  <si>
-    <t>134713054</t>
-  </si>
-  <si>
-    <t>134713157</t>
-  </si>
-  <si>
-    <t>134713194</t>
-  </si>
-  <si>
-    <t>134713216</t>
-  </si>
-  <si>
-    <t>134713464</t>
-  </si>
-  <si>
-    <t>134713489</t>
-  </si>
-  <si>
-    <t>134713506</t>
-  </si>
-  <si>
-    <t>134713541</t>
-  </si>
-  <si>
-    <t>134713580</t>
-  </si>
-  <si>
-    <t>134713747</t>
-  </si>
-  <si>
-    <t>134713751</t>
-  </si>
-  <si>
-    <t>134713834</t>
-  </si>
-  <si>
-    <t>134713926</t>
-  </si>
-  <si>
-    <t>134713970</t>
-  </si>
-  <si>
-    <t>134714162</t>
-  </si>
-  <si>
-    <t>134714189</t>
-  </si>
-  <si>
-    <t>134714273</t>
-  </si>
-  <si>
-    <t>134714296</t>
-  </si>
-  <si>
-    <t>134714302</t>
-  </si>
-  <si>
-    <t>134714325</t>
-  </si>
-  <si>
-    <t>134714329</t>
-  </si>
-  <si>
-    <t>134714335</t>
-  </si>
-  <si>
-    <t>134714393</t>
-  </si>
-  <si>
-    <t>134714456</t>
-  </si>
-  <si>
-    <t>134714544</t>
-  </si>
-  <si>
-    <t>134714566</t>
-  </si>
-  <si>
-    <t>134714627</t>
-  </si>
-  <si>
-    <t>134714628</t>
-  </si>
-  <si>
-    <t>134714660</t>
-  </si>
-  <si>
-    <t>134714684</t>
-  </si>
-  <si>
-    <t>134714692</t>
-  </si>
-  <si>
-    <t>134714730</t>
-  </si>
-  <si>
-    <t>134714736</t>
-  </si>
-  <si>
-    <t>134714812</t>
-  </si>
-  <si>
-    <t>134714850</t>
-  </si>
-  <si>
-    <t>134714881</t>
-  </si>
-  <si>
-    <t>134714887</t>
-  </si>
-  <si>
-    <t>134714904</t>
-  </si>
-  <si>
-    <t>134714958</t>
-  </si>
-  <si>
-    <t>134714993</t>
-  </si>
-  <si>
-    <t>134715030</t>
-  </si>
-  <si>
-    <t>134715112</t>
-  </si>
-  <si>
-    <t>134715172</t>
-  </si>
-  <si>
-    <t>134715211</t>
-  </si>
-  <si>
-    <t>134715302</t>
-  </si>
-  <si>
-    <t>134715446</t>
-  </si>
-  <si>
-    <t>134715526</t>
-  </si>
-  <si>
-    <t>134715541</t>
-  </si>
-  <si>
-    <t>134715578</t>
-  </si>
-  <si>
-    <t>134715606</t>
-  </si>
-  <si>
-    <t>134715732</t>
-  </si>
-  <si>
-    <t>134715792</t>
-  </si>
-  <si>
-    <t>134715856</t>
-  </si>
-  <si>
-    <t>134715922</t>
-  </si>
-  <si>
-    <t>134715961</t>
-  </si>
-  <si>
-    <t>134716111</t>
-  </si>
-  <si>
-    <t>134716192</t>
-  </si>
-  <si>
-    <t>134716264</t>
-  </si>
-  <si>
-    <t>134716294</t>
-  </si>
-  <si>
-    <t>134716305</t>
-  </si>
-  <si>
-    <t>134716340</t>
-  </si>
-  <si>
-    <t>134716403</t>
-  </si>
-  <si>
-    <t>134716459</t>
-  </si>
-  <si>
-    <t>134716478</t>
-  </si>
-  <si>
-    <t>134716480</t>
-  </si>
-  <si>
-    <t>134716511</t>
-  </si>
-  <si>
-    <t>134716526</t>
-  </si>
-  <si>
-    <t>134716534</t>
-  </si>
-  <si>
-    <t>134716555</t>
-  </si>
-  <si>
-    <t>134716568</t>
-  </si>
-  <si>
-    <t>134716590</t>
-  </si>
-  <si>
-    <t>134716819</t>
-  </si>
-  <si>
-    <t>134716994</t>
-  </si>
-  <si>
-    <t>134717315</t>
-  </si>
-  <si>
-    <t>134717434</t>
-  </si>
-  <si>
-    <t>134717588</t>
-  </si>
-  <si>
-    <t>134717802</t>
-  </si>
-  <si>
-    <t>134717865</t>
-  </si>
-  <si>
-    <t>134718347</t>
-  </si>
-  <si>
-    <t>134718390</t>
-  </si>
-  <si>
-    <t>134718542</t>
-  </si>
-  <si>
-    <t>134718640</t>
-  </si>
-  <si>
-    <t>134718649</t>
-  </si>
-  <si>
-    <t>134718680</t>
+    <t>129634207</t>
+  </si>
+  <si>
+    <t>129860972</t>
+  </si>
+  <si>
+    <t>129884071</t>
+  </si>
+  <si>
+    <t>130422239</t>
+  </si>
+  <si>
+    <t>130496860</t>
+  </si>
+  <si>
+    <t>130611515</t>
+  </si>
+  <si>
+    <t>130872171</t>
+  </si>
+  <si>
+    <t>131044037</t>
+  </si>
+  <si>
+    <t>131320718</t>
+  </si>
+  <si>
+    <t>131575786</t>
+  </si>
+  <si>
+    <t>131768677</t>
+  </si>
+  <si>
+    <t>131812037</t>
+  </si>
+  <si>
+    <t>132039770</t>
+  </si>
+  <si>
+    <t>132061814</t>
+  </si>
+  <si>
+    <t>132068986</t>
+  </si>
+  <si>
+    <t>132140894</t>
+  </si>
+  <si>
+    <t>132322101</t>
+  </si>
+  <si>
+    <t>132487983</t>
+  </si>
+  <si>
+    <t>132732192</t>
+  </si>
+  <si>
+    <t>133207605</t>
+  </si>
+  <si>
+    <t>133421596</t>
+  </si>
+  <si>
+    <t>133457684</t>
+  </si>
+  <si>
+    <t>133478627</t>
+  </si>
+  <si>
+    <t>133848890</t>
+  </si>
+  <si>
+    <t>134168588</t>
+  </si>
+  <si>
+    <t>134718730</t>
+  </si>
+  <si>
+    <t>134718765</t>
+  </si>
+  <si>
+    <t>134718935</t>
+  </si>
+  <si>
+    <t>134718950</t>
+  </si>
+  <si>
+    <t>134719001</t>
+  </si>
+  <si>
+    <t>134719033</t>
+  </si>
+  <si>
+    <t>134719396</t>
+  </si>
+  <si>
+    <t>134719523</t>
+  </si>
+  <si>
+    <t>134719879</t>
+  </si>
+  <si>
+    <t>134720011</t>
+  </si>
+  <si>
+    <t>134720239</t>
+  </si>
+  <si>
+    <t>134720289</t>
+  </si>
+  <si>
+    <t>134720422</t>
+  </si>
+  <si>
+    <t>134720514</t>
+  </si>
+  <si>
+    <t>134720521</t>
+  </si>
+  <si>
+    <t>134720724</t>
+  </si>
+  <si>
+    <t>134720790</t>
+  </si>
+  <si>
+    <t>134720805</t>
+  </si>
+  <si>
+    <t>134720960</t>
+  </si>
+  <si>
+    <t>134721001</t>
+  </si>
+  <si>
+    <t>134721048</t>
+  </si>
+  <si>
+    <t>134721132</t>
+  </si>
+  <si>
+    <t>134721171</t>
+  </si>
+  <si>
+    <t>134721252</t>
+  </si>
+  <si>
+    <t>134721590</t>
+  </si>
+  <si>
+    <t>134721603</t>
+  </si>
+  <si>
+    <t>134721714</t>
+  </si>
+  <si>
+    <t>134721872</t>
+  </si>
+  <si>
+    <t>134721890</t>
+  </si>
+  <si>
+    <t>134721892</t>
+  </si>
+  <si>
+    <t>134722018</t>
+  </si>
+  <si>
+    <t>134722124</t>
+  </si>
+  <si>
+    <t>134722366</t>
+  </si>
+  <si>
+    <t>134722389</t>
+  </si>
+  <si>
+    <t>134722462</t>
+  </si>
+  <si>
+    <t>134722573</t>
+  </si>
+  <si>
+    <t>134722908</t>
+  </si>
+  <si>
+    <t>134722954</t>
+  </si>
+  <si>
+    <t>134722957</t>
+  </si>
+  <si>
+    <t>134723018</t>
+  </si>
+  <si>
+    <t>134723054</t>
+  </si>
+  <si>
+    <t>134723077</t>
+  </si>
+  <si>
+    <t>134723343</t>
+  </si>
+  <si>
+    <t>134723368</t>
+  </si>
+  <si>
+    <t>134723425</t>
+  </si>
+  <si>
+    <t>134723613</t>
+  </si>
+  <si>
+    <t>134723821</t>
+  </si>
+  <si>
+    <t>134723863</t>
+  </si>
+  <si>
+    <t>134723894</t>
+  </si>
+  <si>
+    <t>134723922</t>
+  </si>
+  <si>
+    <t>134723923</t>
+  </si>
+  <si>
+    <t>134723993</t>
+  </si>
+  <si>
+    <t>134724022</t>
+  </si>
+  <si>
+    <t>134724143</t>
+  </si>
+  <si>
+    <t>134724226</t>
+  </si>
+  <si>
+    <t>134724351</t>
+  </si>
+  <si>
+    <t>134724610</t>
+  </si>
+  <si>
+    <t>134724835</t>
+  </si>
+  <si>
+    <t>134725174</t>
+  </si>
+  <si>
+    <t>134725466</t>
+  </si>
+  <si>
+    <t>134725472</t>
+  </si>
+  <si>
+    <t>134725622</t>
+  </si>
+  <si>
+    <t>134725664</t>
+  </si>
+  <si>
+    <t>134725915</t>
+  </si>
+  <si>
+    <t>134725929</t>
+  </si>
+  <si>
+    <t>134725938</t>
+  </si>
+  <si>
+    <t>134725955</t>
+  </si>
+  <si>
+    <t>134726107</t>
+  </si>
+  <si>
+    <t>134726130</t>
+  </si>
+  <si>
+    <t>134726169</t>
+  </si>
+  <si>
+    <t>134726289</t>
+  </si>
+  <si>
+    <t>134726297</t>
+  </si>
+  <si>
+    <t>134726300</t>
+  </si>
+  <si>
+    <t>134726364</t>
+  </si>
+  <si>
+    <t>134726366</t>
+  </si>
+  <si>
+    <t>134726390</t>
+  </si>
+  <si>
+    <t>134726413</t>
+  </si>
+  <si>
+    <t>134726565</t>
+  </si>
+  <si>
+    <t>134726584</t>
+  </si>
+  <si>
+    <t>134726628</t>
+  </si>
+  <si>
+    <t>134726676</t>
+  </si>
+  <si>
+    <t>134726750</t>
+  </si>
+  <si>
+    <t>134726816</t>
+  </si>
+  <si>
+    <t>134726892</t>
+  </si>
+  <si>
+    <t>134726916</t>
+  </si>
+  <si>
+    <t>134727035</t>
+  </si>
+  <si>
+    <t>134727086</t>
+  </si>
+  <si>
+    <t>134727121</t>
+  </si>
+  <si>
+    <t>134727207</t>
+  </si>
+  <si>
+    <t>134727291</t>
+  </si>
+  <si>
+    <t>134727296</t>
+  </si>
+  <si>
+    <t>134727302</t>
+  </si>
+  <si>
+    <t>134727387</t>
+  </si>
+  <si>
+    <t>134727457</t>
+  </si>
+  <si>
+    <t>134727484</t>
+  </si>
+  <si>
+    <t>134727575</t>
+  </si>
+  <si>
+    <t>134727605</t>
+  </si>
+  <si>
+    <t>134727654</t>
+  </si>
+  <si>
+    <t>134727680</t>
+  </si>
+  <si>
+    <t>134727726</t>
+  </si>
+  <si>
+    <t>134727765</t>
+  </si>
+  <si>
+    <t>134727850</t>
+  </si>
+  <si>
+    <t>134727883</t>
+  </si>
+  <si>
+    <t>134727933</t>
+  </si>
+  <si>
+    <t>134727972</t>
+  </si>
+  <si>
+    <t>134727976</t>
+  </si>
+  <si>
+    <t>134728010</t>
+  </si>
+  <si>
+    <t>134728030</t>
+  </si>
+  <si>
+    <t>134728071</t>
+  </si>
+  <si>
+    <t>134728365</t>
+  </si>
+  <si>
+    <t>134728432</t>
+  </si>
+  <si>
+    <t>134728460</t>
+  </si>
+  <si>
+    <t>134728509</t>
+  </si>
+  <si>
+    <t>134728588</t>
+  </si>
+  <si>
+    <t>134728608</t>
+  </si>
+  <si>
+    <t>134728609</t>
+  </si>
+  <si>
+    <t>134728668</t>
+  </si>
+  <si>
+    <t>134728674</t>
+  </si>
+  <si>
+    <t>134728904</t>
+  </si>
+  <si>
+    <t>134729042</t>
+  </si>
+  <si>
+    <t>134729101</t>
+  </si>
+  <si>
+    <t>134729263</t>
+  </si>
+  <si>
+    <t>134729375</t>
+  </si>
+  <si>
+    <t>134729398</t>
+  </si>
+  <si>
+    <t>134729543</t>
+  </si>
+  <si>
+    <t>134729614</t>
+  </si>
+  <si>
+    <t>134729690</t>
+  </si>
+  <si>
+    <t>134729770</t>
+  </si>
+  <si>
+    <t>134730021</t>
+  </si>
+  <si>
+    <t>134730038</t>
+  </si>
+  <si>
+    <t>134730069</t>
+  </si>
+  <si>
+    <t>134730093</t>
+  </si>
+  <si>
+    <t>134730160</t>
+  </si>
+  <si>
+    <t>134730190</t>
+  </si>
+  <si>
+    <t>134730355</t>
+  </si>
+  <si>
+    <t>134730432</t>
+  </si>
+  <si>
+    <t>134730451</t>
+  </si>
+  <si>
+    <t>134730676</t>
+  </si>
+  <si>
+    <t>134730739</t>
+  </si>
+  <si>
+    <t>134730750</t>
+  </si>
+  <si>
+    <t>134730901</t>
+  </si>
+  <si>
+    <t>134731051</t>
+  </si>
+  <si>
+    <t>134731091</t>
+  </si>
+  <si>
+    <t>134731096</t>
+  </si>
+  <si>
+    <t>134731126</t>
+  </si>
+  <si>
+    <t>134731170</t>
+  </si>
+  <si>
+    <t>134731194</t>
+  </si>
+  <si>
+    <t>134731215</t>
+  </si>
+  <si>
+    <t>134731279</t>
+  </si>
+  <si>
+    <t>134731406</t>
+  </si>
+  <si>
+    <t>134731459</t>
+  </si>
+  <si>
+    <t>134731526</t>
+  </si>
+  <si>
+    <t>134731599</t>
+  </si>
+  <si>
+    <t>134731694</t>
+  </si>
+  <si>
+    <t>134731758</t>
+  </si>
+  <si>
+    <t>134731773</t>
+  </si>
+  <si>
+    <t>134731832</t>
+  </si>
+  <si>
+    <t>134731834</t>
+  </si>
+  <si>
+    <t>134731930</t>
+  </si>
+  <si>
+    <t>134732077</t>
+  </si>
+  <si>
+    <t>134732087</t>
+  </si>
+  <si>
+    <t>134732167</t>
+  </si>
+  <si>
+    <t>134732239</t>
+  </si>
+  <si>
+    <t>134732265</t>
+  </si>
+  <si>
+    <t>134732310</t>
+  </si>
+  <si>
+    <t>134732349</t>
+  </si>
+  <si>
+    <t>134732356</t>
+  </si>
+  <si>
+    <t>134732368</t>
+  </si>
+  <si>
+    <t>134732519</t>
+  </si>
+  <si>
+    <t>134732628</t>
+  </si>
+  <si>
+    <t>134732752</t>
+  </si>
+  <si>
+    <t>134732841</t>
+  </si>
+  <si>
+    <t>134732861</t>
+  </si>
+  <si>
+    <t>134732959</t>
+  </si>
+  <si>
+    <t>134732971</t>
+  </si>
+  <si>
+    <t>134733083</t>
+  </si>
+  <si>
+    <t>134733160</t>
+  </si>
+  <si>
+    <t>134733177</t>
+  </si>
+  <si>
+    <t>134733190</t>
+  </si>
+  <si>
+    <t>134733214</t>
+  </si>
+  <si>
+    <t>134733232</t>
+  </si>
+  <si>
+    <t>134733447</t>
+  </si>
+  <si>
+    <t>134733460</t>
+  </si>
+  <si>
+    <t>134733482</t>
+  </si>
+  <si>
+    <t>134733563</t>
+  </si>
+  <si>
+    <t>134733675</t>
+  </si>
+  <si>
+    <t>134733676</t>
+  </si>
+  <si>
+    <t>134733692</t>
+  </si>
+  <si>
+    <t>134733778</t>
+  </si>
+  <si>
+    <t>134733782</t>
+  </si>
+  <si>
+    <t>134733874</t>
+  </si>
+  <si>
+    <t>134733880</t>
+  </si>
+  <si>
+    <t>134733886</t>
+  </si>
+  <si>
+    <t>134733961</t>
+  </si>
+  <si>
+    <t>134733979</t>
+  </si>
+  <si>
+    <t>134734053</t>
+  </si>
+  <si>
+    <t>134734104</t>
+  </si>
+  <si>
+    <t>134734108</t>
+  </si>
+  <si>
+    <t>134734201</t>
+  </si>
+  <si>
+    <t>134734231</t>
+  </si>
+  <si>
+    <t>134734251</t>
+  </si>
+  <si>
+    <t>134734290</t>
+  </si>
+  <si>
+    <t>134734410</t>
+  </si>
+  <si>
+    <t>134734447</t>
+  </si>
+  <si>
+    <t>134734482</t>
+  </si>
+  <si>
+    <t>134734505</t>
+  </si>
+  <si>
+    <t>134734595</t>
+  </si>
+  <si>
+    <t>134734765</t>
+  </si>
+  <si>
+    <t>134734782</t>
+  </si>
+  <si>
+    <t>134734802</t>
+  </si>
+  <si>
+    <t>134734826</t>
+  </si>
+  <si>
+    <t>134734905</t>
+  </si>
+  <si>
+    <t>134734934</t>
+  </si>
+  <si>
+    <t>134734990</t>
+  </si>
+  <si>
+    <t>134735175</t>
+  </si>
+  <si>
+    <t>134735215</t>
+  </si>
+  <si>
+    <t>134735331</t>
+  </si>
+  <si>
+    <t>134735439</t>
+  </si>
+  <si>
+    <t>134735572</t>
+  </si>
+  <si>
+    <t>134735741</t>
+  </si>
+  <si>
+    <t>134735825</t>
+  </si>
+  <si>
+    <t>134735885</t>
+  </si>
+  <si>
+    <t>134735890</t>
+  </si>
+  <si>
+    <t>134735925</t>
+  </si>
+  <si>
+    <t>134735996</t>
+  </si>
+  <si>
+    <t>134736046</t>
+  </si>
+  <si>
+    <t>134736061</t>
+  </si>
+  <si>
+    <t>134736197</t>
+  </si>
+  <si>
+    <t>134736219</t>
+  </si>
+  <si>
+    <t>134736226</t>
+  </si>
+  <si>
+    <t>134736399</t>
+  </si>
+  <si>
+    <t>134736441</t>
+  </si>
+  <si>
+    <t>134736470</t>
+  </si>
+  <si>
+    <t>134736479</t>
+  </si>
+  <si>
+    <t>134736644</t>
+  </si>
+  <si>
+    <t>134736646</t>
+  </si>
+  <si>
+    <t>134736730</t>
+  </si>
+  <si>
+    <t>134736737</t>
+  </si>
+  <si>
+    <t>134736854</t>
+  </si>
+  <si>
+    <t>134736872</t>
+  </si>
+  <si>
+    <t>134736905</t>
+  </si>
+  <si>
+    <t>134736910</t>
+  </si>
+  <si>
+    <t>134737072</t>
+  </si>
+  <si>
+    <t>134737120</t>
+  </si>
+  <si>
+    <t>134737141</t>
+  </si>
+  <si>
+    <t>134737181</t>
+  </si>
+  <si>
+    <t>134737182</t>
+  </si>
+  <si>
+    <t>134737196</t>
+  </si>
+  <si>
+    <t>134737307</t>
+  </si>
+  <si>
+    <t>134737314</t>
+  </si>
+  <si>
+    <t>134737406</t>
+  </si>
+  <si>
+    <t>134737492</t>
+  </si>
+  <si>
+    <t>134737510</t>
+  </si>
+  <si>
+    <t>134737513</t>
+  </si>
+  <si>
+    <t>134737517</t>
+  </si>
+  <si>
+    <t>134737564</t>
+  </si>
+  <si>
+    <t>134737570</t>
+  </si>
+  <si>
+    <t>134737597</t>
+  </si>
+  <si>
+    <t>134737643</t>
+  </si>
+  <si>
+    <t>134737663</t>
+  </si>
+  <si>
+    <t>134737689</t>
+  </si>
+  <si>
+    <t>134737745</t>
+  </si>
+  <si>
+    <t>134737902</t>
+  </si>
+  <si>
+    <t>134737903</t>
+  </si>
+  <si>
+    <t>134737931</t>
+  </si>
+  <si>
+    <t>134737964</t>
+  </si>
+  <si>
+    <t>134737968</t>
+  </si>
+  <si>
+    <t>134737984</t>
+  </si>
+  <si>
+    <t>134738024</t>
+  </si>
+  <si>
+    <t>134738134</t>
+  </si>
+  <si>
+    <t>134738143</t>
+  </si>
+  <si>
+    <t>134738187</t>
+  </si>
+  <si>
+    <t>134738189</t>
+  </si>
+  <si>
+    <t>134738196</t>
+  </si>
+  <si>
+    <t>134738553</t>
+  </si>
+  <si>
+    <t>134738652</t>
+  </si>
+  <si>
+    <t>134738727</t>
+  </si>
+  <si>
+    <t>134738796</t>
+  </si>
+  <si>
+    <t>134738811</t>
+  </si>
+  <si>
+    <t>134738812</t>
+  </si>
+  <si>
+    <t>134738928</t>
+  </si>
+  <si>
+    <t>134738991</t>
+  </si>
+  <si>
+    <t>134738998</t>
+  </si>
+  <si>
+    <t>134739126</t>
+  </si>
+  <si>
+    <t>134739253</t>
+  </si>
+  <si>
+    <t>134739254</t>
+  </si>
+  <si>
+    <t>134739299</t>
+  </si>
+  <si>
+    <t>134739360</t>
+  </si>
+  <si>
+    <t>134739454</t>
+  </si>
+  <si>
+    <t>134739488</t>
+  </si>
+  <si>
+    <t>134739556</t>
+  </si>
+  <si>
+    <t>134739964</t>
+  </si>
+  <si>
+    <t>134740030</t>
+  </si>
+  <si>
+    <t>134740049</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C340"/>
+  <dimension ref="A1:C333"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1510,7 +1459,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>3</v>
@@ -1521,7 +1470,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>3</v>
@@ -1532,7 +1481,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>3</v>
@@ -1543,7 +1492,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
@@ -1554,7 +1503,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>3</v>
@@ -1565,7 +1514,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>3</v>
@@ -1576,7 +1525,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>3</v>
@@ -1587,7 +1536,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>3</v>
@@ -1598,7 +1547,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>3</v>
@@ -1609,7 +1558,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>3</v>
@@ -1620,7 +1569,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>3</v>
@@ -1631,7 +1580,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>3</v>
@@ -1642,7 +1591,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>3</v>
@@ -1653,7 +1602,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>3</v>
@@ -1664,7 +1613,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>3</v>
@@ -1675,7 +1624,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>3</v>
@@ -1686,7 +1635,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>3</v>
@@ -1697,7 +1646,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>3</v>
@@ -1708,7 +1657,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>3</v>
@@ -1719,7 +1668,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>3</v>
@@ -1730,7 +1679,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>3</v>
@@ -1741,7 +1690,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>3</v>
@@ -1752,7 +1701,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>3</v>
@@ -1763,7 +1712,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>3</v>
@@ -1774,7 +1723,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>3</v>
@@ -1785,7 +1734,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>3</v>
@@ -1796,7 +1745,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>3</v>
@@ -1807,7 +1756,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>3</v>
@@ -1818,7 +1767,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>3</v>
@@ -1829,7 +1778,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>3</v>
@@ -1840,7 +1789,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>3</v>
@@ -1851,7 +1800,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>3</v>
@@ -1862,7 +1811,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>3</v>
@@ -1873,7 +1822,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>3</v>
@@ -1884,7 +1833,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>3</v>
@@ -1895,7 +1844,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>3</v>
@@ -1906,7 +1855,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>3</v>
@@ -1917,7 +1866,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>3</v>
@@ -1928,7 +1877,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>3</v>
@@ -1939,7 +1888,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>3</v>
@@ -1950,7 +1899,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>3</v>
@@ -1961,7 +1910,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>3</v>
@@ -1972,7 +1921,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>3</v>
@@ -1983,7 +1932,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>3</v>
@@ -1994,7 +1943,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>3</v>
@@ -2005,7 +1954,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>3</v>
@@ -2016,7 +1965,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>3</v>
@@ -2027,7 +1976,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>3</v>
@@ -2038,7 +1987,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>3</v>
@@ -2049,7 +1998,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>3</v>
@@ -2060,7 +2009,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>3</v>
@@ -2071,7 +2020,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>3</v>
@@ -2082,7 +2031,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>3</v>
@@ -2093,7 +2042,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>3</v>
@@ -2104,7 +2053,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>3</v>
@@ -2115,7 +2064,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>3</v>
@@ -2126,7 +2075,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>3</v>
@@ -2137,7 +2086,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>3</v>
@@ -2148,7 +2097,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>3</v>
@@ -2159,7 +2108,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>3</v>
@@ -2170,7 +2119,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>3</v>
@@ -2181,7 +2130,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>3</v>
@@ -2192,7 +2141,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>3</v>
@@ -2203,7 +2152,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>3</v>
@@ -2214,7 +2163,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>3</v>
@@ -2225,7 +2174,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>3</v>
@@ -2236,7 +2185,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>3</v>
@@ -2247,7 +2196,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>3</v>
@@ -2258,7 +2207,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>3</v>
@@ -2269,7 +2218,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>3</v>
@@ -2280,7 +2229,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>3</v>
@@ -2291,7 +2240,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>3</v>
@@ -2302,7 +2251,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>3</v>
@@ -2313,7 +2262,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>3</v>
@@ -2324,7 +2273,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>3</v>
@@ -2335,7 +2284,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>3</v>
@@ -2346,7 +2295,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>3</v>
@@ -2357,7 +2306,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>3</v>
@@ -2368,7 +2317,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>3</v>
@@ -2379,7 +2328,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>3</v>
@@ -2390,7 +2339,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>3</v>
@@ -2401,7 +2350,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>3</v>
@@ -2412,7 +2361,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>3</v>
@@ -2423,7 +2372,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>3</v>
@@ -2434,7 +2383,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>3</v>
@@ -2445,7 +2394,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>3</v>
@@ -2456,7 +2405,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>3</v>
@@ -2467,7 +2416,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>3</v>
@@ -2478,7 +2427,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>3</v>
@@ -2489,7 +2438,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>3</v>
@@ -2500,7 +2449,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>3</v>
@@ -2511,7 +2460,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>3</v>
@@ -2522,7 +2471,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>3</v>
@@ -2533,7 +2482,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>3</v>
@@ -2544,7 +2493,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>3</v>
@@ -2555,7 +2504,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>3</v>
@@ -2566,7 +2515,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>3</v>
@@ -2577,7 +2526,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>3</v>
@@ -2588,7 +2537,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>3</v>
@@ -2599,7 +2548,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>3</v>
@@ -2610,7 +2559,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>3</v>
@@ -2621,7 +2570,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>3</v>
@@ -2632,7 +2581,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>3</v>
@@ -2643,7 +2592,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>3</v>
@@ -2654,7 +2603,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>3</v>
@@ -2665,7 +2614,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>3</v>
@@ -2676,7 +2625,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>3</v>
@@ -2687,7 +2636,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>3</v>
@@ -2698,7 +2647,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>3</v>
@@ -2709,7 +2658,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>3</v>
@@ -2720,7 +2669,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>3</v>
@@ -2731,7 +2680,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>3</v>
@@ -2742,7 +2691,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>3</v>
@@ -2753,7 +2702,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>3</v>
@@ -2764,7 +2713,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>3</v>
@@ -2775,7 +2724,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>3</v>
@@ -2786,7 +2735,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>3</v>
@@ -2797,7 +2746,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>3</v>
@@ -2808,7 +2757,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>3</v>
@@ -2819,7 +2768,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>3</v>
@@ -2830,7 +2779,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>3</v>
@@ -2841,7 +2790,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>3</v>
@@ -2852,7 +2801,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>3</v>
@@ -2863,7 +2812,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>3</v>
@@ -2874,7 +2823,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>3</v>
@@ -2885,7 +2834,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>3</v>
@@ -2896,7 +2845,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>3</v>
@@ -2907,7 +2856,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>3</v>
@@ -2918,7 +2867,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>3</v>
@@ -2929,7 +2878,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>3</v>
@@ -2940,7 +2889,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>3</v>
@@ -2951,7 +2900,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>3</v>
@@ -2962,7 +2911,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>3</v>
@@ -2973,7 +2922,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>3</v>
@@ -2984,7 +2933,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>3</v>
@@ -2995,7 +2944,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>3</v>
@@ -3006,7 +2955,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>3</v>
@@ -3017,7 +2966,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>3</v>
@@ -3028,7 +2977,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>3</v>
@@ -3039,7 +2988,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>3</v>
@@ -3050,7 +2999,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>3</v>
@@ -3061,7 +3010,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>3</v>
@@ -3072,7 +3021,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>3</v>
@@ -3083,7 +3032,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>3</v>
@@ -3094,7 +3043,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>3</v>
@@ -3105,7 +3054,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>3</v>
@@ -3116,7 +3065,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>3</v>
@@ -3127,7 +3076,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>3</v>
@@ -3138,7 +3087,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>3</v>
@@ -3149,7 +3098,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>3</v>
@@ -3160,7 +3109,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>3</v>
@@ -3171,7 +3120,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>3</v>
@@ -3182,7 +3131,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>3</v>
@@ -3193,7 +3142,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>3</v>
@@ -3204,7 +3153,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>3</v>
@@ -3215,7 +3164,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>3</v>
@@ -3226,7 +3175,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>3</v>
@@ -3237,7 +3186,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>3</v>
@@ -3248,7 +3197,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>3</v>
@@ -3259,7 +3208,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>3</v>
@@ -3270,7 +3219,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>3</v>
@@ -3281,7 +3230,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>3</v>
@@ -3292,7 +3241,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>3</v>
@@ -3303,7 +3252,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>3</v>
@@ -3314,7 +3263,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>3</v>
@@ -3325,7 +3274,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>3</v>
@@ -3336,7 +3285,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>3</v>
@@ -3347,7 +3296,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>3</v>
@@ -3358,7 +3307,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>3</v>
@@ -3369,7 +3318,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>3</v>
@@ -3380,7 +3329,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>3</v>
@@ -3391,7 +3340,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>3</v>
@@ -3402,7 +3351,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>3</v>
@@ -3413,7 +3362,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>3</v>
@@ -3424,7 +3373,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>3</v>
@@ -3435,7 +3384,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>3</v>
@@ -3446,7 +3395,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>3</v>
@@ -3457,7 +3406,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>3</v>
@@ -3468,7 +3417,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>3</v>
@@ -3479,7 +3428,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>3</v>
@@ -3490,7 +3439,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>3</v>
@@ -3501,7 +3450,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>3</v>
@@ -3512,7 +3461,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>3</v>
@@ -3523,7 +3472,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>3</v>
@@ -3534,7 +3483,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>3</v>
@@ -3545,7 +3494,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>3</v>
@@ -3556,7 +3505,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>3</v>
@@ -3567,7 +3516,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>3</v>
@@ -3578,7 +3527,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>3</v>
@@ -3589,7 +3538,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>3</v>
@@ -3600,7 +3549,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>3</v>
@@ -3611,7 +3560,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>3</v>
@@ -3622,7 +3571,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>3</v>
@@ -3633,7 +3582,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>3</v>
@@ -3644,7 +3593,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>3</v>
@@ -3655,7 +3604,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>3</v>
@@ -3666,7 +3615,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>3</v>
@@ -3677,7 +3626,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>3</v>
@@ -3688,7 +3637,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>3</v>
@@ -3699,7 +3648,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>3</v>
@@ -3710,7 +3659,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>3</v>
@@ -3721,7 +3670,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>3</v>
@@ -3732,7 +3681,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>3</v>
@@ -3743,7 +3692,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>3</v>
@@ -3754,7 +3703,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>3</v>
@@ -3765,7 +3714,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>3</v>
@@ -3776,7 +3725,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>3</v>
@@ -3787,7 +3736,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>3</v>
@@ -3798,7 +3747,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>3</v>
@@ -3809,7 +3758,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B214" s="6" t="s">
         <v>3</v>
@@ -3820,7 +3769,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>3</v>
@@ -3831,7 +3780,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>3</v>
@@ -3842,7 +3791,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B217" s="6" t="s">
         <v>3</v>
@@ -3853,7 +3802,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>3</v>
@@ -3864,7 +3813,7 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>3</v>
@@ -3875,7 +3824,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>3</v>
@@ -3886,7 +3835,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>3</v>
@@ -3897,7 +3846,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>3</v>
@@ -3908,7 +3857,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>3</v>
@@ -3919,7 +3868,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>3</v>
@@ -3930,7 +3879,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>3</v>
@@ -3941,7 +3890,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>3</v>
@@ -3952,7 +3901,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>3</v>
@@ -3963,7 +3912,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>3</v>
@@ -3974,7 +3923,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>3</v>
@@ -3985,7 +3934,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>3</v>
@@ -3996,7 +3945,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>3</v>
@@ -4007,7 +3956,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>3</v>
@@ -4018,7 +3967,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>3</v>
@@ -4029,7 +3978,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>3</v>
@@ -4040,7 +3989,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>3</v>
@@ -4051,7 +4000,7 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>3</v>
@@ -4062,7 +4011,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>3</v>
@@ -4073,7 +4022,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>3</v>
@@ -4084,7 +4033,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>3</v>
@@ -4095,7 +4044,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>3</v>
@@ -4106,7 +4055,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>3</v>
@@ -4117,7 +4066,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>3</v>
@@ -4128,7 +4077,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>3</v>
@@ -4139,7 +4088,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>3</v>
@@ -4150,7 +4099,7 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>3</v>
@@ -4161,7 +4110,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>3</v>
@@ -4172,7 +4121,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>3</v>
@@ -4183,7 +4132,7 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>3</v>
@@ -4194,7 +4143,7 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>3</v>
@@ -4205,7 +4154,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>3</v>
@@ -4216,7 +4165,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>3</v>
@@ -4227,7 +4176,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>3</v>
@@ -4238,7 +4187,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>3</v>
@@ -4249,7 +4198,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>3</v>
@@ -4260,7 +4209,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>3</v>
@@ -4271,7 +4220,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>3</v>
@@ -4282,7 +4231,7 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>3</v>
@@ -4293,7 +4242,7 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>3</v>
@@ -4304,7 +4253,7 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>3</v>
@@ -4315,7 +4264,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>3</v>
@@ -4326,7 +4275,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>3</v>
@@ -4337,7 +4286,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>3</v>
@@ -4348,7 +4297,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>3</v>
@@ -4359,7 +4308,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>3</v>
@@ -4370,7 +4319,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>3</v>
@@ -4381,7 +4330,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>3</v>
@@ -4392,7 +4341,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>3</v>
@@ -4403,7 +4352,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>3</v>
@@ -4414,7 +4363,7 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>3</v>
@@ -4425,7 +4374,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>3</v>
@@ -4436,7 +4385,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>3</v>
@@ -4447,7 +4396,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>3</v>
@@ -4458,7 +4407,7 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>3</v>
@@ -4469,7 +4418,7 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>3</v>
@@ -4480,7 +4429,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>3</v>
@@ -4491,7 +4440,7 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>3</v>
@@ -4502,7 +4451,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>3</v>
@@ -4513,7 +4462,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>3</v>
@@ -4524,7 +4473,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>3</v>
@@ -4535,7 +4484,7 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>3</v>
@@ -4546,7 +4495,7 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>3</v>
@@ -4557,7 +4506,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>3</v>
@@ -4568,7 +4517,7 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B283" s="6" t="s">
         <v>3</v>
@@ -4579,7 +4528,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>3</v>
@@ -4590,7 +4539,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>3</v>
@@ -4601,7 +4550,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>3</v>
@@ -4612,7 +4561,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>3</v>
@@ -4623,7 +4572,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>3</v>
@@ -4634,7 +4583,7 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>3</v>
@@ -4645,7 +4594,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>3</v>
@@ -4656,7 +4605,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>3</v>
@@ -4667,7 +4616,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>3</v>
@@ -4678,7 +4627,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>3</v>
@@ -4689,7 +4638,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>3</v>
@@ -4700,7 +4649,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>3</v>
@@ -4711,7 +4660,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B296" s="6" t="s">
         <v>3</v>
@@ -4722,7 +4671,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>3</v>
@@ -4733,7 +4682,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B298" s="6" t="s">
         <v>3</v>
@@ -4744,7 +4693,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>3</v>
@@ -4755,7 +4704,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>3</v>
@@ -4766,7 +4715,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>3</v>
@@ -4777,7 +4726,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B302" s="6" t="s">
         <v>3</v>
@@ -4788,7 +4737,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B303" s="6" t="s">
         <v>3</v>
@@ -4799,7 +4748,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B304" s="6" t="s">
         <v>3</v>
@@ -4810,7 +4759,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B305" s="6" t="s">
         <v>3</v>
@@ -4821,7 +4770,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B306" s="6" t="s">
         <v>3</v>
@@ -4832,7 +4781,7 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B307" s="6" t="s">
         <v>3</v>
@@ -4843,7 +4792,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B308" s="6" t="s">
         <v>3</v>
@@ -4854,7 +4803,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B309" s="6" t="s">
         <v>3</v>
@@ -4865,7 +4814,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B310" s="6" t="s">
         <v>3</v>
@@ -4876,7 +4825,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B311" s="6" t="s">
         <v>3</v>
@@ -4887,7 +4836,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B312" s="6" t="s">
         <v>3</v>
@@ -4898,7 +4847,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B313" s="6" t="s">
         <v>3</v>
@@ -4909,7 +4858,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B314" s="6" t="s">
         <v>3</v>
@@ -4920,7 +4869,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B315" s="6" t="s">
         <v>3</v>
@@ -4931,7 +4880,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B316" s="6" t="s">
         <v>3</v>
@@ -4942,7 +4891,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B317" s="6" t="s">
         <v>3</v>
@@ -4953,7 +4902,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B318" s="6" t="s">
         <v>3</v>
@@ -4964,7 +4913,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B319" s="6" t="s">
         <v>3</v>
@@ -4975,7 +4924,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B320" s="6" t="s">
         <v>3</v>
@@ -4984,203 +4933,82 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B321" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B321" s="6"/>
       <c r="C321" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B322" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B322" s="6"/>
       <c r="C322" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B323" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B323" s="6"/>
       <c r="C323" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B324" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B324" s="6"/>
       <c r="C324" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B325" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B325" s="6"/>
       <c r="C325" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B326" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B326" s="6"/>
       <c r="C326" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B327" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B327" s="6"/>
       <c r="C327" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B328" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B328" s="6"/>
       <c r="C328" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B329" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B329" s="6"/>
       <c r="C329" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B330" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="330" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B330" s="6"/>
       <c r="C330" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B331" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="331" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B331" s="6"/>
       <c r="C331" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B332" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="332" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B332" s="6"/>
       <c r="C332" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B333" s="6" t="s">
-        <v>3</v>
-      </c>
+    <row r="333" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B333" s="6"/>
       <c r="C333" s="5" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B334" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B335" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B336" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B337" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B338" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B339" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B340" s="6" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C02AC38-933A-4F70-ABF3-B930C02C7D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F03561F-563A-4FCF-A54E-214EEDD64F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="292">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,961 +45,865 @@
     <t>.</t>
   </si>
   <si>
-    <t>129634207</t>
-  </si>
-  <si>
-    <t>129860972</t>
-  </si>
-  <si>
-    <t>129884071</t>
-  </si>
-  <si>
-    <t>130422239</t>
-  </si>
-  <si>
-    <t>130496860</t>
-  </si>
-  <si>
-    <t>130611515</t>
-  </si>
-  <si>
-    <t>130872171</t>
-  </si>
-  <si>
-    <t>131044037</t>
-  </si>
-  <si>
-    <t>131320718</t>
-  </si>
-  <si>
-    <t>131575786</t>
-  </si>
-  <si>
-    <t>131768677</t>
-  </si>
-  <si>
-    <t>131812037</t>
-  </si>
-  <si>
-    <t>132039770</t>
-  </si>
-  <si>
-    <t>132061814</t>
-  </si>
-  <si>
-    <t>132068986</t>
-  </si>
-  <si>
-    <t>132140894</t>
-  </si>
-  <si>
-    <t>132322101</t>
-  </si>
-  <si>
-    <t>132487983</t>
-  </si>
-  <si>
-    <t>132732192</t>
-  </si>
-  <si>
-    <t>133207605</t>
-  </si>
-  <si>
-    <t>133421596</t>
-  </si>
-  <si>
-    <t>133457684</t>
-  </si>
-  <si>
-    <t>133478627</t>
-  </si>
-  <si>
-    <t>133848890</t>
-  </si>
-  <si>
-    <t>134168588</t>
-  </si>
-  <si>
-    <t>134718730</t>
-  </si>
-  <si>
-    <t>134718765</t>
-  </si>
-  <si>
-    <t>134718935</t>
-  </si>
-  <si>
-    <t>134718950</t>
-  </si>
-  <si>
-    <t>134719001</t>
-  </si>
-  <si>
-    <t>134719033</t>
-  </si>
-  <si>
-    <t>134719396</t>
-  </si>
-  <si>
-    <t>134719523</t>
-  </si>
-  <si>
-    <t>134719879</t>
-  </si>
-  <si>
-    <t>134720011</t>
-  </si>
-  <si>
-    <t>134720239</t>
-  </si>
-  <si>
-    <t>134720289</t>
-  </si>
-  <si>
-    <t>134720422</t>
-  </si>
-  <si>
-    <t>134720514</t>
-  </si>
-  <si>
-    <t>134720521</t>
-  </si>
-  <si>
-    <t>134720724</t>
-  </si>
-  <si>
-    <t>134720790</t>
-  </si>
-  <si>
-    <t>134720805</t>
-  </si>
-  <si>
-    <t>134720960</t>
-  </si>
-  <si>
-    <t>134721001</t>
-  </si>
-  <si>
-    <t>134721048</t>
-  </si>
-  <si>
-    <t>134721132</t>
-  </si>
-  <si>
-    <t>134721171</t>
-  </si>
-  <si>
-    <t>134721252</t>
-  </si>
-  <si>
-    <t>134721590</t>
-  </si>
-  <si>
-    <t>134721603</t>
-  </si>
-  <si>
-    <t>134721714</t>
-  </si>
-  <si>
-    <t>134721872</t>
-  </si>
-  <si>
-    <t>134721890</t>
-  </si>
-  <si>
-    <t>134721892</t>
-  </si>
-  <si>
-    <t>134722018</t>
-  </si>
-  <si>
-    <t>134722124</t>
-  </si>
-  <si>
-    <t>134722366</t>
-  </si>
-  <si>
-    <t>134722389</t>
-  </si>
-  <si>
-    <t>134722462</t>
-  </si>
-  <si>
-    <t>134722573</t>
-  </si>
-  <si>
-    <t>134722908</t>
-  </si>
-  <si>
-    <t>134722954</t>
-  </si>
-  <si>
-    <t>134722957</t>
-  </si>
-  <si>
-    <t>134723018</t>
-  </si>
-  <si>
-    <t>134723054</t>
-  </si>
-  <si>
-    <t>134723077</t>
-  </si>
-  <si>
-    <t>134723343</t>
-  </si>
-  <si>
-    <t>134723368</t>
-  </si>
-  <si>
-    <t>134723425</t>
-  </si>
-  <si>
-    <t>134723613</t>
-  </si>
-  <si>
-    <t>134723821</t>
-  </si>
-  <si>
-    <t>134723863</t>
-  </si>
-  <si>
-    <t>134723894</t>
-  </si>
-  <si>
-    <t>134723922</t>
-  </si>
-  <si>
-    <t>134723923</t>
-  </si>
-  <si>
-    <t>134723993</t>
-  </si>
-  <si>
-    <t>134724022</t>
-  </si>
-  <si>
-    <t>134724143</t>
-  </si>
-  <si>
-    <t>134724226</t>
-  </si>
-  <si>
-    <t>134724351</t>
-  </si>
-  <si>
-    <t>134724610</t>
-  </si>
-  <si>
-    <t>134724835</t>
-  </si>
-  <si>
-    <t>134725174</t>
-  </si>
-  <si>
-    <t>134725466</t>
-  </si>
-  <si>
-    <t>134725472</t>
-  </si>
-  <si>
-    <t>134725622</t>
-  </si>
-  <si>
-    <t>134725664</t>
-  </si>
-  <si>
-    <t>134725915</t>
-  </si>
-  <si>
-    <t>134725929</t>
-  </si>
-  <si>
-    <t>134725938</t>
-  </si>
-  <si>
-    <t>134725955</t>
-  </si>
-  <si>
-    <t>134726107</t>
-  </si>
-  <si>
-    <t>134726130</t>
-  </si>
-  <si>
-    <t>134726169</t>
-  </si>
-  <si>
-    <t>134726289</t>
-  </si>
-  <si>
-    <t>134726297</t>
-  </si>
-  <si>
-    <t>134726300</t>
-  </si>
-  <si>
-    <t>134726364</t>
-  </si>
-  <si>
-    <t>134726366</t>
-  </si>
-  <si>
-    <t>134726390</t>
-  </si>
-  <si>
-    <t>134726413</t>
-  </si>
-  <si>
-    <t>134726565</t>
-  </si>
-  <si>
-    <t>134726584</t>
-  </si>
-  <si>
-    <t>134726628</t>
-  </si>
-  <si>
-    <t>134726676</t>
-  </si>
-  <si>
-    <t>134726750</t>
-  </si>
-  <si>
-    <t>134726816</t>
-  </si>
-  <si>
-    <t>134726892</t>
-  </si>
-  <si>
-    <t>134726916</t>
-  </si>
-  <si>
-    <t>134727035</t>
-  </si>
-  <si>
-    <t>134727086</t>
-  </si>
-  <si>
-    <t>134727121</t>
-  </si>
-  <si>
-    <t>134727207</t>
-  </si>
-  <si>
-    <t>134727291</t>
-  </si>
-  <si>
-    <t>134727296</t>
-  </si>
-  <si>
-    <t>134727302</t>
-  </si>
-  <si>
-    <t>134727387</t>
-  </si>
-  <si>
-    <t>134727457</t>
-  </si>
-  <si>
-    <t>134727484</t>
-  </si>
-  <si>
-    <t>134727575</t>
-  </si>
-  <si>
-    <t>134727605</t>
-  </si>
-  <si>
-    <t>134727654</t>
-  </si>
-  <si>
-    <t>134727680</t>
-  </si>
-  <si>
-    <t>134727726</t>
-  </si>
-  <si>
-    <t>134727765</t>
-  </si>
-  <si>
-    <t>134727850</t>
-  </si>
-  <si>
-    <t>134727883</t>
-  </si>
-  <si>
-    <t>134727933</t>
-  </si>
-  <si>
-    <t>134727972</t>
-  </si>
-  <si>
-    <t>134727976</t>
-  </si>
-  <si>
-    <t>134728010</t>
-  </si>
-  <si>
-    <t>134728030</t>
-  </si>
-  <si>
-    <t>134728071</t>
-  </si>
-  <si>
-    <t>134728365</t>
-  </si>
-  <si>
-    <t>134728432</t>
-  </si>
-  <si>
-    <t>134728460</t>
-  </si>
-  <si>
-    <t>134728509</t>
-  </si>
-  <si>
-    <t>134728588</t>
-  </si>
-  <si>
-    <t>134728608</t>
-  </si>
-  <si>
-    <t>134728609</t>
-  </si>
-  <si>
-    <t>134728668</t>
-  </si>
-  <si>
-    <t>134728674</t>
-  </si>
-  <si>
-    <t>134728904</t>
-  </si>
-  <si>
-    <t>134729042</t>
-  </si>
-  <si>
-    <t>134729101</t>
-  </si>
-  <si>
-    <t>134729263</t>
-  </si>
-  <si>
-    <t>134729375</t>
-  </si>
-  <si>
-    <t>134729398</t>
-  </si>
-  <si>
-    <t>134729543</t>
-  </si>
-  <si>
-    <t>134729614</t>
-  </si>
-  <si>
-    <t>134729690</t>
-  </si>
-  <si>
-    <t>134729770</t>
-  </si>
-  <si>
-    <t>134730021</t>
-  </si>
-  <si>
-    <t>134730038</t>
-  </si>
-  <si>
-    <t>134730069</t>
-  </si>
-  <si>
-    <t>134730093</t>
-  </si>
-  <si>
-    <t>134730160</t>
-  </si>
-  <si>
-    <t>134730190</t>
-  </si>
-  <si>
-    <t>134730355</t>
-  </si>
-  <si>
-    <t>134730432</t>
-  </si>
-  <si>
-    <t>134730451</t>
-  </si>
-  <si>
-    <t>134730676</t>
-  </si>
-  <si>
-    <t>134730739</t>
-  </si>
-  <si>
-    <t>134730750</t>
-  </si>
-  <si>
-    <t>134730901</t>
-  </si>
-  <si>
-    <t>134731051</t>
-  </si>
-  <si>
-    <t>134731091</t>
-  </si>
-  <si>
-    <t>134731096</t>
-  </si>
-  <si>
-    <t>134731126</t>
-  </si>
-  <si>
-    <t>134731170</t>
-  </si>
-  <si>
-    <t>134731194</t>
-  </si>
-  <si>
-    <t>134731215</t>
-  </si>
-  <si>
-    <t>134731279</t>
-  </si>
-  <si>
-    <t>134731406</t>
-  </si>
-  <si>
-    <t>134731459</t>
-  </si>
-  <si>
-    <t>134731526</t>
-  </si>
-  <si>
-    <t>134731599</t>
-  </si>
-  <si>
-    <t>134731694</t>
-  </si>
-  <si>
-    <t>134731758</t>
-  </si>
-  <si>
-    <t>134731773</t>
-  </si>
-  <si>
-    <t>134731832</t>
-  </si>
-  <si>
-    <t>134731834</t>
-  </si>
-  <si>
-    <t>134731930</t>
-  </si>
-  <si>
-    <t>134732077</t>
-  </si>
-  <si>
-    <t>134732087</t>
-  </si>
-  <si>
-    <t>134732167</t>
-  </si>
-  <si>
-    <t>134732239</t>
-  </si>
-  <si>
-    <t>134732265</t>
-  </si>
-  <si>
-    <t>134732310</t>
-  </si>
-  <si>
-    <t>134732349</t>
-  </si>
-  <si>
-    <t>134732356</t>
-  </si>
-  <si>
-    <t>134732368</t>
-  </si>
-  <si>
-    <t>134732519</t>
-  </si>
-  <si>
-    <t>134732628</t>
-  </si>
-  <si>
-    <t>134732752</t>
-  </si>
-  <si>
-    <t>134732841</t>
-  </si>
-  <si>
-    <t>134732861</t>
-  </si>
-  <si>
-    <t>134732959</t>
-  </si>
-  <si>
-    <t>134732971</t>
-  </si>
-  <si>
-    <t>134733083</t>
-  </si>
-  <si>
-    <t>134733160</t>
-  </si>
-  <si>
-    <t>134733177</t>
-  </si>
-  <si>
-    <t>134733190</t>
-  </si>
-  <si>
-    <t>134733214</t>
-  </si>
-  <si>
-    <t>134733232</t>
-  </si>
-  <si>
-    <t>134733447</t>
-  </si>
-  <si>
-    <t>134733460</t>
-  </si>
-  <si>
-    <t>134733482</t>
-  </si>
-  <si>
-    <t>134733563</t>
-  </si>
-  <si>
-    <t>134733675</t>
-  </si>
-  <si>
-    <t>134733676</t>
-  </si>
-  <si>
-    <t>134733692</t>
-  </si>
-  <si>
-    <t>134733778</t>
-  </si>
-  <si>
-    <t>134733782</t>
-  </si>
-  <si>
-    <t>134733874</t>
-  </si>
-  <si>
-    <t>134733880</t>
-  </si>
-  <si>
-    <t>134733886</t>
-  </si>
-  <si>
-    <t>134733961</t>
-  </si>
-  <si>
-    <t>134733979</t>
-  </si>
-  <si>
-    <t>134734053</t>
-  </si>
-  <si>
-    <t>134734104</t>
-  </si>
-  <si>
-    <t>134734108</t>
-  </si>
-  <si>
-    <t>134734201</t>
-  </si>
-  <si>
-    <t>134734231</t>
-  </si>
-  <si>
-    <t>134734251</t>
-  </si>
-  <si>
-    <t>134734290</t>
-  </si>
-  <si>
-    <t>134734410</t>
-  </si>
-  <si>
-    <t>134734447</t>
-  </si>
-  <si>
-    <t>134734482</t>
-  </si>
-  <si>
-    <t>134734505</t>
-  </si>
-  <si>
-    <t>134734595</t>
-  </si>
-  <si>
-    <t>134734765</t>
-  </si>
-  <si>
-    <t>134734782</t>
-  </si>
-  <si>
-    <t>134734802</t>
-  </si>
-  <si>
-    <t>134734826</t>
-  </si>
-  <si>
-    <t>134734905</t>
-  </si>
-  <si>
-    <t>134734934</t>
-  </si>
-  <si>
-    <t>134734990</t>
-  </si>
-  <si>
-    <t>134735175</t>
-  </si>
-  <si>
-    <t>134735215</t>
-  </si>
-  <si>
-    <t>134735331</t>
-  </si>
-  <si>
-    <t>134735439</t>
-  </si>
-  <si>
-    <t>134735572</t>
-  </si>
-  <si>
-    <t>134735741</t>
-  </si>
-  <si>
-    <t>134735825</t>
-  </si>
-  <si>
-    <t>134735885</t>
-  </si>
-  <si>
-    <t>134735890</t>
-  </si>
-  <si>
-    <t>134735925</t>
-  </si>
-  <si>
-    <t>134735996</t>
-  </si>
-  <si>
-    <t>134736046</t>
-  </si>
-  <si>
-    <t>134736061</t>
-  </si>
-  <si>
-    <t>134736197</t>
-  </si>
-  <si>
-    <t>134736219</t>
-  </si>
-  <si>
-    <t>134736226</t>
-  </si>
-  <si>
-    <t>134736399</t>
-  </si>
-  <si>
-    <t>134736441</t>
-  </si>
-  <si>
-    <t>134736470</t>
-  </si>
-  <si>
-    <t>134736479</t>
-  </si>
-  <si>
-    <t>134736644</t>
-  </si>
-  <si>
-    <t>134736646</t>
-  </si>
-  <si>
-    <t>134736730</t>
-  </si>
-  <si>
-    <t>134736737</t>
-  </si>
-  <si>
-    <t>134736854</t>
-  </si>
-  <si>
-    <t>134736872</t>
-  </si>
-  <si>
-    <t>134736905</t>
-  </si>
-  <si>
-    <t>134736910</t>
-  </si>
-  <si>
-    <t>134737072</t>
-  </si>
-  <si>
-    <t>134737120</t>
-  </si>
-  <si>
-    <t>134737141</t>
-  </si>
-  <si>
-    <t>134737181</t>
-  </si>
-  <si>
-    <t>134737182</t>
-  </si>
-  <si>
-    <t>134737196</t>
-  </si>
-  <si>
-    <t>134737307</t>
-  </si>
-  <si>
-    <t>134737314</t>
-  </si>
-  <si>
-    <t>134737406</t>
-  </si>
-  <si>
-    <t>134737492</t>
-  </si>
-  <si>
-    <t>134737510</t>
-  </si>
-  <si>
-    <t>134737513</t>
-  </si>
-  <si>
-    <t>134737517</t>
-  </si>
-  <si>
-    <t>134737564</t>
-  </si>
-  <si>
-    <t>134737570</t>
-  </si>
-  <si>
-    <t>134737597</t>
-  </si>
-  <si>
-    <t>134737643</t>
-  </si>
-  <si>
-    <t>134737663</t>
-  </si>
-  <si>
-    <t>134737689</t>
-  </si>
-  <si>
-    <t>134737745</t>
-  </si>
-  <si>
-    <t>134737902</t>
-  </si>
-  <si>
-    <t>134737903</t>
-  </si>
-  <si>
-    <t>134737931</t>
-  </si>
-  <si>
-    <t>134737964</t>
-  </si>
-  <si>
-    <t>134737968</t>
-  </si>
-  <si>
-    <t>134737984</t>
-  </si>
-  <si>
-    <t>134738024</t>
-  </si>
-  <si>
-    <t>134738134</t>
-  </si>
-  <si>
-    <t>134738143</t>
-  </si>
-  <si>
-    <t>134738187</t>
-  </si>
-  <si>
-    <t>134738189</t>
-  </si>
-  <si>
-    <t>134738196</t>
-  </si>
-  <si>
-    <t>134738553</t>
-  </si>
-  <si>
-    <t>134738652</t>
-  </si>
-  <si>
-    <t>134738727</t>
-  </si>
-  <si>
-    <t>134738796</t>
-  </si>
-  <si>
-    <t>134738811</t>
-  </si>
-  <si>
-    <t>134738812</t>
-  </si>
-  <si>
-    <t>134738928</t>
-  </si>
-  <si>
-    <t>134738991</t>
-  </si>
-  <si>
-    <t>134738998</t>
-  </si>
-  <si>
-    <t>134739126</t>
-  </si>
-  <si>
-    <t>134739253</t>
-  </si>
-  <si>
-    <t>134739254</t>
-  </si>
-  <si>
-    <t>134739299</t>
-  </si>
-  <si>
-    <t>134739360</t>
-  </si>
-  <si>
-    <t>134739454</t>
-  </si>
-  <si>
-    <t>134739488</t>
-  </si>
-  <si>
-    <t>134739556</t>
-  </si>
-  <si>
-    <t>134739964</t>
-  </si>
-  <si>
-    <t>134740030</t>
-  </si>
-  <si>
-    <t>134740049</t>
+    <t>129852142</t>
+  </si>
+  <si>
+    <t>130065654</t>
+  </si>
+  <si>
+    <t>130265467</t>
+  </si>
+  <si>
+    <t>130474419</t>
+  </si>
+  <si>
+    <t>130740978</t>
+  </si>
+  <si>
+    <t>130782004</t>
+  </si>
+  <si>
+    <t>130835101</t>
+  </si>
+  <si>
+    <t>131037550</t>
+  </si>
+  <si>
+    <t>131099868</t>
+  </si>
+  <si>
+    <t>131335775</t>
+  </si>
+  <si>
+    <t>131361581</t>
+  </si>
+  <si>
+    <t>131403608</t>
+  </si>
+  <si>
+    <t>131777870</t>
+  </si>
+  <si>
+    <t>131839463</t>
+  </si>
+  <si>
+    <t>132117770</t>
+  </si>
+  <si>
+    <t>132253527</t>
+  </si>
+  <si>
+    <t>132327895</t>
+  </si>
+  <si>
+    <t>132483088</t>
+  </si>
+  <si>
+    <t>132495868</t>
+  </si>
+  <si>
+    <t>132632998</t>
+  </si>
+  <si>
+    <t>132816951</t>
+  </si>
+  <si>
+    <t>133106191</t>
+  </si>
+  <si>
+    <t>133233450</t>
+  </si>
+  <si>
+    <t>133286186</t>
+  </si>
+  <si>
+    <t>133313508</t>
+  </si>
+  <si>
+    <t>133374570</t>
+  </si>
+  <si>
+    <t>133391518</t>
+  </si>
+  <si>
+    <t>133507725</t>
+  </si>
+  <si>
+    <t>133510114</t>
+  </si>
+  <si>
+    <t>133559881</t>
+  </si>
+  <si>
+    <t>133653543</t>
+  </si>
+  <si>
+    <t>133770708</t>
+  </si>
+  <si>
+    <t>133918353</t>
+  </si>
+  <si>
+    <t>134057108</t>
+  </si>
+  <si>
+    <t>134440991</t>
+  </si>
+  <si>
+    <t>134454208</t>
+  </si>
+  <si>
+    <t>134467234</t>
+  </si>
+  <si>
+    <t>134672507</t>
+  </si>
+  <si>
+    <t>134740298</t>
+  </si>
+  <si>
+    <t>134740327</t>
+  </si>
+  <si>
+    <t>134740379</t>
+  </si>
+  <si>
+    <t>134740414</t>
+  </si>
+  <si>
+    <t>134740570</t>
+  </si>
+  <si>
+    <t>134741190</t>
+  </si>
+  <si>
+    <t>134741206</t>
+  </si>
+  <si>
+    <t>134741265</t>
+  </si>
+  <si>
+    <t>134741310</t>
+  </si>
+  <si>
+    <t>134741311</t>
+  </si>
+  <si>
+    <t>134741424</t>
+  </si>
+  <si>
+    <t>134741489</t>
+  </si>
+  <si>
+    <t>134741517</t>
+  </si>
+  <si>
+    <t>134741726</t>
+  </si>
+  <si>
+    <t>134741929</t>
+  </si>
+  <si>
+    <t>134741979</t>
+  </si>
+  <si>
+    <t>134742186</t>
+  </si>
+  <si>
+    <t>134742217</t>
+  </si>
+  <si>
+    <t>134742657</t>
+  </si>
+  <si>
+    <t>134742891</t>
+  </si>
+  <si>
+    <t>134742893</t>
+  </si>
+  <si>
+    <t>134742907</t>
+  </si>
+  <si>
+    <t>134742910</t>
+  </si>
+  <si>
+    <t>134742994</t>
+  </si>
+  <si>
+    <t>134742998</t>
+  </si>
+  <si>
+    <t>134743024</t>
+  </si>
+  <si>
+    <t>134743066</t>
+  </si>
+  <si>
+    <t>134743100</t>
+  </si>
+  <si>
+    <t>134743204</t>
+  </si>
+  <si>
+    <t>134743272</t>
+  </si>
+  <si>
+    <t>134743312</t>
+  </si>
+  <si>
+    <t>134743459</t>
+  </si>
+  <si>
+    <t>134743475</t>
+  </si>
+  <si>
+    <t>134743490</t>
+  </si>
+  <si>
+    <t>134743503</t>
+  </si>
+  <si>
+    <t>134743626</t>
+  </si>
+  <si>
+    <t>134743854</t>
+  </si>
+  <si>
+    <t>134743936</t>
+  </si>
+  <si>
+    <t>134744010</t>
+  </si>
+  <si>
+    <t>134744064</t>
+  </si>
+  <si>
+    <t>134744301</t>
+  </si>
+  <si>
+    <t>134744345</t>
+  </si>
+  <si>
+    <t>134744369</t>
+  </si>
+  <si>
+    <t>134744471</t>
+  </si>
+  <si>
+    <t>134744591</t>
+  </si>
+  <si>
+    <t>134744628</t>
+  </si>
+  <si>
+    <t>134744727</t>
+  </si>
+  <si>
+    <t>134744803</t>
+  </si>
+  <si>
+    <t>134744899</t>
+  </si>
+  <si>
+    <t>134745010</t>
+  </si>
+  <si>
+    <t>134745291</t>
+  </si>
+  <si>
+    <t>134745306</t>
+  </si>
+  <si>
+    <t>134745333</t>
+  </si>
+  <si>
+    <t>134745337</t>
+  </si>
+  <si>
+    <t>134745338</t>
+  </si>
+  <si>
+    <t>134745471</t>
+  </si>
+  <si>
+    <t>134745539</t>
+  </si>
+  <si>
+    <t>134745613</t>
+  </si>
+  <si>
+    <t>134745631</t>
+  </si>
+  <si>
+    <t>134745785</t>
+  </si>
+  <si>
+    <t>134745881</t>
+  </si>
+  <si>
+    <t>134745899</t>
+  </si>
+  <si>
+    <t>134745903</t>
+  </si>
+  <si>
+    <t>134745946</t>
+  </si>
+  <si>
+    <t>134746255</t>
+  </si>
+  <si>
+    <t>134746333</t>
+  </si>
+  <si>
+    <t>134746513</t>
+  </si>
+  <si>
+    <t>134746525</t>
+  </si>
+  <si>
+    <t>134746701</t>
+  </si>
+  <si>
+    <t>134746768</t>
+  </si>
+  <si>
+    <t>134746780</t>
+  </si>
+  <si>
+    <t>134747137</t>
+  </si>
+  <si>
+    <t>134747203</t>
+  </si>
+  <si>
+    <t>134747229</t>
+  </si>
+  <si>
+    <t>134747272</t>
+  </si>
+  <si>
+    <t>134747295</t>
+  </si>
+  <si>
+    <t>134747381</t>
+  </si>
+  <si>
+    <t>134747413</t>
+  </si>
+  <si>
+    <t>134747445</t>
+  </si>
+  <si>
+    <t>134747487</t>
+  </si>
+  <si>
+    <t>134747548</t>
+  </si>
+  <si>
+    <t>134747602</t>
+  </si>
+  <si>
+    <t>134747639</t>
+  </si>
+  <si>
+    <t>134747811</t>
+  </si>
+  <si>
+    <t>134748080</t>
+  </si>
+  <si>
+    <t>134748111</t>
+  </si>
+  <si>
+    <t>134748210</t>
+  </si>
+  <si>
+    <t>134748296</t>
+  </si>
+  <si>
+    <t>134748304</t>
+  </si>
+  <si>
+    <t>134748357</t>
+  </si>
+  <si>
+    <t>134748392</t>
+  </si>
+  <si>
+    <t>134748464</t>
+  </si>
+  <si>
+    <t>134748622</t>
+  </si>
+  <si>
+    <t>134748670</t>
+  </si>
+  <si>
+    <t>134748680</t>
+  </si>
+  <si>
+    <t>134748737</t>
+  </si>
+  <si>
+    <t>134748853</t>
+  </si>
+  <si>
+    <t>134748934</t>
+  </si>
+  <si>
+    <t>134749144</t>
+  </si>
+  <si>
+    <t>134749198</t>
+  </si>
+  <si>
+    <t>134749273</t>
+  </si>
+  <si>
+    <t>134749444</t>
+  </si>
+  <si>
+    <t>134749799</t>
+  </si>
+  <si>
+    <t>134749859</t>
+  </si>
+  <si>
+    <t>134750015</t>
+  </si>
+  <si>
+    <t>134750097</t>
+  </si>
+  <si>
+    <t>134750289</t>
+  </si>
+  <si>
+    <t>134750311</t>
+  </si>
+  <si>
+    <t>134750346</t>
+  </si>
+  <si>
+    <t>134750573</t>
+  </si>
+  <si>
+    <t>134750590</t>
+  </si>
+  <si>
+    <t>134750715</t>
+  </si>
+  <si>
+    <t>134750786</t>
+  </si>
+  <si>
+    <t>134750790</t>
+  </si>
+  <si>
+    <t>134750805</t>
+  </si>
+  <si>
+    <t>134750850</t>
+  </si>
+  <si>
+    <t>134750883</t>
+  </si>
+  <si>
+    <t>134750932</t>
+  </si>
+  <si>
+    <t>134750982</t>
+  </si>
+  <si>
+    <t>134751080</t>
+  </si>
+  <si>
+    <t>134751082</t>
+  </si>
+  <si>
+    <t>134751221</t>
+  </si>
+  <si>
+    <t>134751482</t>
+  </si>
+  <si>
+    <t>134751506</t>
+  </si>
+  <si>
+    <t>134751535</t>
+  </si>
+  <si>
+    <t>134751634</t>
+  </si>
+  <si>
+    <t>134751769</t>
+  </si>
+  <si>
+    <t>134751865</t>
+  </si>
+  <si>
+    <t>134752085</t>
+  </si>
+  <si>
+    <t>134752117</t>
+  </si>
+  <si>
+    <t>134752265</t>
+  </si>
+  <si>
+    <t>134752458</t>
+  </si>
+  <si>
+    <t>134752478</t>
+  </si>
+  <si>
+    <t>134752516</t>
+  </si>
+  <si>
+    <t>134752521</t>
+  </si>
+  <si>
+    <t>134752621</t>
+  </si>
+  <si>
+    <t>134752874</t>
+  </si>
+  <si>
+    <t>134752919</t>
+  </si>
+  <si>
+    <t>134752955</t>
+  </si>
+  <si>
+    <t>134753016</t>
+  </si>
+  <si>
+    <t>134753023</t>
+  </si>
+  <si>
+    <t>134753099</t>
+  </si>
+  <si>
+    <t>134753181</t>
+  </si>
+  <si>
+    <t>134753424</t>
+  </si>
+  <si>
+    <t>134753427</t>
+  </si>
+  <si>
+    <t>134753432</t>
+  </si>
+  <si>
+    <t>134753494</t>
+  </si>
+  <si>
+    <t>134753526</t>
+  </si>
+  <si>
+    <t>134753614</t>
+  </si>
+  <si>
+    <t>134753808</t>
+  </si>
+  <si>
+    <t>134753873</t>
+  </si>
+  <si>
+    <t>134753889</t>
+  </si>
+  <si>
+    <t>134753938</t>
+  </si>
+  <si>
+    <t>134753990</t>
+  </si>
+  <si>
+    <t>134754173</t>
+  </si>
+  <si>
+    <t>134754290</t>
+  </si>
+  <si>
+    <t>134754322</t>
+  </si>
+  <si>
+    <t>134754358</t>
+  </si>
+  <si>
+    <t>134754550</t>
+  </si>
+  <si>
+    <t>134754557</t>
+  </si>
+  <si>
+    <t>134754570</t>
+  </si>
+  <si>
+    <t>134754669</t>
+  </si>
+  <si>
+    <t>134754713</t>
+  </si>
+  <si>
+    <t>134754907</t>
+  </si>
+  <si>
+    <t>134754922</t>
+  </si>
+  <si>
+    <t>134755011</t>
+  </si>
+  <si>
+    <t>134755061</t>
+  </si>
+  <si>
+    <t>134755304</t>
+  </si>
+  <si>
+    <t>134755358</t>
+  </si>
+  <si>
+    <t>134755438</t>
+  </si>
+  <si>
+    <t>134755521</t>
+  </si>
+  <si>
+    <t>134755524</t>
+  </si>
+  <si>
+    <t>134755664</t>
+  </si>
+  <si>
+    <t>134755686</t>
+  </si>
+  <si>
+    <t>134755703</t>
+  </si>
+  <si>
+    <t>134755767</t>
+  </si>
+  <si>
+    <t>134755776</t>
+  </si>
+  <si>
+    <t>134755806</t>
+  </si>
+  <si>
+    <t>134755955</t>
+  </si>
+  <si>
+    <t>134755966</t>
+  </si>
+  <si>
+    <t>134755978</t>
+  </si>
+  <si>
+    <t>134755988</t>
+  </si>
+  <si>
+    <t>134756002</t>
+  </si>
+  <si>
+    <t>134756049</t>
+  </si>
+  <si>
+    <t>134756242</t>
+  </si>
+  <si>
+    <t>134756268</t>
+  </si>
+  <si>
+    <t>134756349</t>
+  </si>
+  <si>
+    <t>134756365</t>
+  </si>
+  <si>
+    <t>134756370</t>
+  </si>
+  <si>
+    <t>134756385</t>
+  </si>
+  <si>
+    <t>134756415</t>
+  </si>
+  <si>
+    <t>134756476</t>
+  </si>
+  <si>
+    <t>134756504</t>
+  </si>
+  <si>
+    <t>134756573</t>
+  </si>
+  <si>
+    <t>134756582</t>
+  </si>
+  <si>
+    <t>134756642</t>
+  </si>
+  <si>
+    <t>134756660</t>
+  </si>
+  <si>
+    <t>134756730</t>
+  </si>
+  <si>
+    <t>134756752</t>
+  </si>
+  <si>
+    <t>134756781</t>
+  </si>
+  <si>
+    <t>134756795</t>
+  </si>
+  <si>
+    <t>134756865</t>
+  </si>
+  <si>
+    <t>134756891</t>
+  </si>
+  <si>
+    <t>134756951</t>
+  </si>
+  <si>
+    <t>134756982</t>
+  </si>
+  <si>
+    <t>134757113</t>
+  </si>
+  <si>
+    <t>134757149</t>
+  </si>
+  <si>
+    <t>134757420</t>
+  </si>
+  <si>
+    <t>134757462</t>
+  </si>
+  <si>
+    <t>134757645</t>
+  </si>
+  <si>
+    <t>134757674</t>
+  </si>
+  <si>
+    <t>134757690</t>
+  </si>
+  <si>
+    <t>134757710</t>
+  </si>
+  <si>
+    <t>134757757</t>
+  </si>
+  <si>
+    <t>134757771</t>
+  </si>
+  <si>
+    <t>134757899</t>
+  </si>
+  <si>
+    <t>134757942</t>
+  </si>
+  <si>
+    <t>134757943</t>
+  </si>
+  <si>
+    <t>134758393</t>
+  </si>
+  <si>
+    <t>134758420</t>
+  </si>
+  <si>
+    <t>134758505</t>
+  </si>
+  <si>
+    <t>134758520</t>
+  </si>
+  <si>
+    <t>134758555</t>
+  </si>
+  <si>
+    <t>134758635</t>
+  </si>
+  <si>
+    <t>134758646</t>
+  </si>
+  <si>
+    <t>134758703</t>
+  </si>
+  <si>
+    <t>134758707</t>
+  </si>
+  <si>
+    <t>134758720</t>
+  </si>
+  <si>
+    <t>134758846</t>
+  </si>
+  <si>
+    <t>134758948</t>
+  </si>
+  <si>
+    <t>134758954</t>
+  </si>
+  <si>
+    <t>134758960</t>
+  </si>
+  <si>
+    <t>134759043</t>
+  </si>
+  <si>
+    <t>134759165</t>
+  </si>
+  <si>
+    <t>134759199</t>
+  </si>
+  <si>
+    <t>134759493</t>
+  </si>
+  <si>
+    <t>134759496</t>
+  </si>
+  <si>
+    <t>134759730</t>
+  </si>
+  <si>
+    <t>134759806</t>
+  </si>
+  <si>
+    <t>134759892</t>
+  </si>
+  <si>
+    <t>134760142</t>
+  </si>
+  <si>
+    <t>134760244</t>
+  </si>
+  <si>
+    <t>134760383</t>
+  </si>
+  <si>
+    <t>134760396</t>
+  </si>
+  <si>
+    <t>134760403</t>
+  </si>
+  <si>
+    <t>134760520</t>
+  </si>
+  <si>
+    <t>134760690</t>
+  </si>
+  <si>
+    <t>134760730</t>
+  </si>
+  <si>
+    <t>134760755</t>
   </si>
 </sst>
 </file>
@@ -4581,357 +4485,133 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C289" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C290" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B292" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C292" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C293" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C294" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B295" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C295" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B296" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C296" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B298" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C298" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B299" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C299" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B300" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C300" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B301" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C301" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B302" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C302" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B303" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C303" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B304" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C304" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B305" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C305" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B306" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C306" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B307" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B308" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B309" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C309" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B310" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C310" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B311" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C311" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B312" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C312" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B313" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C313" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B314" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C314" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B315" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C315" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B316" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C316" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B317" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C317" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B318" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C318" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B319" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C319" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B320" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C320" s="5" t="s">
-        <v>4</v>
-      </c>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B289" s="6"/>
+      <c r="C289" s="5"/>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B290" s="6"/>
+      <c r="C290" s="5"/>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B291" s="6"/>
+      <c r="C291" s="5"/>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B292" s="6"/>
+      <c r="C292" s="5"/>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B293" s="6"/>
+      <c r="C293" s="5"/>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B294" s="6"/>
+      <c r="C294" s="5"/>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B295" s="6"/>
+      <c r="C295" s="5"/>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B296" s="6"/>
+      <c r="C296" s="5"/>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B297" s="6"/>
+      <c r="C297" s="5"/>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B298" s="6"/>
+      <c r="C298" s="5"/>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B299" s="6"/>
+      <c r="C299" s="5"/>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B300" s="6"/>
+      <c r="C300" s="5"/>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B301" s="6"/>
+      <c r="C301" s="5"/>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B302" s="6"/>
+      <c r="C302" s="5"/>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B303" s="6"/>
+      <c r="C303" s="5"/>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B304" s="6"/>
+      <c r="C304" s="5"/>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B305" s="6"/>
+      <c r="C305" s="5"/>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B306" s="6"/>
+      <c r="C306" s="5"/>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B307" s="6"/>
+      <c r="C307" s="5"/>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B308" s="6"/>
+      <c r="C308" s="5"/>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B309" s="6"/>
+      <c r="C309" s="5"/>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B310" s="6"/>
+      <c r="C310" s="5"/>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B311" s="6"/>
+      <c r="C311" s="5"/>
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B312" s="6"/>
+      <c r="C312" s="5"/>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B313" s="6"/>
+      <c r="C313" s="5"/>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B314" s="6"/>
+      <c r="C314" s="5"/>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B315" s="6"/>
+      <c r="C315" s="5"/>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B316" s="6"/>
+      <c r="C316" s="5"/>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B317" s="6"/>
+      <c r="C317" s="5"/>
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B318" s="6"/>
+      <c r="C318" s="5"/>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B319" s="6"/>
+      <c r="C319" s="5"/>
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B320" s="6"/>
+      <c r="C320" s="5"/>
     </row>
     <row r="321" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B321" s="6"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F03561F-563A-4FCF-A54E-214EEDD64F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E920386-0383-4C5D-B0FA-2D7C1F3E48FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="350">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,865 +45,1039 @@
     <t>.</t>
   </si>
   <si>
-    <t>129852142</t>
-  </si>
-  <si>
-    <t>130065654</t>
-  </si>
-  <si>
-    <t>130265467</t>
-  </si>
-  <si>
-    <t>130474419</t>
-  </si>
-  <si>
-    <t>130740978</t>
-  </si>
-  <si>
-    <t>130782004</t>
-  </si>
-  <si>
-    <t>130835101</t>
-  </si>
-  <si>
-    <t>131037550</t>
-  </si>
-  <si>
-    <t>131099868</t>
-  </si>
-  <si>
-    <t>131335775</t>
-  </si>
-  <si>
-    <t>131361581</t>
-  </si>
-  <si>
-    <t>131403608</t>
-  </si>
-  <si>
-    <t>131777870</t>
-  </si>
-  <si>
-    <t>131839463</t>
-  </si>
-  <si>
-    <t>132117770</t>
-  </si>
-  <si>
-    <t>132253527</t>
-  </si>
-  <si>
-    <t>132327895</t>
-  </si>
-  <si>
-    <t>132483088</t>
-  </si>
-  <si>
-    <t>132495868</t>
-  </si>
-  <si>
-    <t>132632998</t>
-  </si>
-  <si>
-    <t>132816951</t>
-  </si>
-  <si>
-    <t>133106191</t>
-  </si>
-  <si>
-    <t>133233450</t>
-  </si>
-  <si>
-    <t>133286186</t>
-  </si>
-  <si>
-    <t>133313508</t>
-  </si>
-  <si>
-    <t>133374570</t>
-  </si>
-  <si>
-    <t>133391518</t>
-  </si>
-  <si>
-    <t>133507725</t>
-  </si>
-  <si>
-    <t>133510114</t>
-  </si>
-  <si>
-    <t>133559881</t>
-  </si>
-  <si>
-    <t>133653543</t>
-  </si>
-  <si>
-    <t>133770708</t>
-  </si>
-  <si>
-    <t>133918353</t>
-  </si>
-  <si>
-    <t>134057108</t>
-  </si>
-  <si>
-    <t>134440991</t>
-  </si>
-  <si>
-    <t>134454208</t>
-  </si>
-  <si>
-    <t>134467234</t>
-  </si>
-  <si>
-    <t>134672507</t>
-  </si>
-  <si>
-    <t>134740298</t>
-  </si>
-  <si>
-    <t>134740327</t>
-  </si>
-  <si>
-    <t>134740379</t>
-  </si>
-  <si>
-    <t>134740414</t>
-  </si>
-  <si>
-    <t>134740570</t>
-  </si>
-  <si>
-    <t>134741190</t>
-  </si>
-  <si>
-    <t>134741206</t>
-  </si>
-  <si>
-    <t>134741265</t>
-  </si>
-  <si>
-    <t>134741310</t>
-  </si>
-  <si>
-    <t>134741311</t>
-  </si>
-  <si>
-    <t>134741424</t>
-  </si>
-  <si>
-    <t>134741489</t>
-  </si>
-  <si>
-    <t>134741517</t>
-  </si>
-  <si>
-    <t>134741726</t>
-  </si>
-  <si>
-    <t>134741929</t>
-  </si>
-  <si>
-    <t>134741979</t>
-  </si>
-  <si>
-    <t>134742186</t>
-  </si>
-  <si>
-    <t>134742217</t>
-  </si>
-  <si>
-    <t>134742657</t>
-  </si>
-  <si>
-    <t>134742891</t>
-  </si>
-  <si>
-    <t>134742893</t>
-  </si>
-  <si>
-    <t>134742907</t>
-  </si>
-  <si>
-    <t>134742910</t>
-  </si>
-  <si>
-    <t>134742994</t>
-  </si>
-  <si>
-    <t>134742998</t>
-  </si>
-  <si>
-    <t>134743024</t>
-  </si>
-  <si>
-    <t>134743066</t>
-  </si>
-  <si>
-    <t>134743100</t>
-  </si>
-  <si>
-    <t>134743204</t>
-  </si>
-  <si>
-    <t>134743272</t>
-  </si>
-  <si>
-    <t>134743312</t>
-  </si>
-  <si>
-    <t>134743459</t>
-  </si>
-  <si>
-    <t>134743475</t>
-  </si>
-  <si>
-    <t>134743490</t>
-  </si>
-  <si>
-    <t>134743503</t>
-  </si>
-  <si>
-    <t>134743626</t>
-  </si>
-  <si>
-    <t>134743854</t>
-  </si>
-  <si>
-    <t>134743936</t>
-  </si>
-  <si>
-    <t>134744010</t>
-  </si>
-  <si>
-    <t>134744064</t>
-  </si>
-  <si>
-    <t>134744301</t>
-  </si>
-  <si>
-    <t>134744345</t>
-  </si>
-  <si>
-    <t>134744369</t>
-  </si>
-  <si>
-    <t>134744471</t>
-  </si>
-  <si>
-    <t>134744591</t>
-  </si>
-  <si>
-    <t>134744628</t>
-  </si>
-  <si>
-    <t>134744727</t>
-  </si>
-  <si>
-    <t>134744803</t>
-  </si>
-  <si>
-    <t>134744899</t>
-  </si>
-  <si>
-    <t>134745010</t>
-  </si>
-  <si>
-    <t>134745291</t>
-  </si>
-  <si>
-    <t>134745306</t>
-  </si>
-  <si>
-    <t>134745333</t>
-  </si>
-  <si>
-    <t>134745337</t>
-  </si>
-  <si>
-    <t>134745338</t>
-  </si>
-  <si>
-    <t>134745471</t>
-  </si>
-  <si>
-    <t>134745539</t>
-  </si>
-  <si>
-    <t>134745613</t>
-  </si>
-  <si>
-    <t>134745631</t>
-  </si>
-  <si>
-    <t>134745785</t>
-  </si>
-  <si>
-    <t>134745881</t>
-  </si>
-  <si>
-    <t>134745899</t>
-  </si>
-  <si>
-    <t>134745903</t>
-  </si>
-  <si>
-    <t>134745946</t>
-  </si>
-  <si>
-    <t>134746255</t>
-  </si>
-  <si>
-    <t>134746333</t>
-  </si>
-  <si>
-    <t>134746513</t>
-  </si>
-  <si>
-    <t>134746525</t>
-  </si>
-  <si>
-    <t>134746701</t>
-  </si>
-  <si>
-    <t>134746768</t>
-  </si>
-  <si>
-    <t>134746780</t>
-  </si>
-  <si>
-    <t>134747137</t>
-  </si>
-  <si>
-    <t>134747203</t>
-  </si>
-  <si>
-    <t>134747229</t>
-  </si>
-  <si>
-    <t>134747272</t>
-  </si>
-  <si>
-    <t>134747295</t>
-  </si>
-  <si>
-    <t>134747381</t>
-  </si>
-  <si>
-    <t>134747413</t>
-  </si>
-  <si>
-    <t>134747445</t>
-  </si>
-  <si>
-    <t>134747487</t>
-  </si>
-  <si>
-    <t>134747548</t>
-  </si>
-  <si>
-    <t>134747602</t>
-  </si>
-  <si>
-    <t>134747639</t>
-  </si>
-  <si>
-    <t>134747811</t>
-  </si>
-  <si>
-    <t>134748080</t>
-  </si>
-  <si>
-    <t>134748111</t>
-  </si>
-  <si>
-    <t>134748210</t>
-  </si>
-  <si>
-    <t>134748296</t>
-  </si>
-  <si>
-    <t>134748304</t>
-  </si>
-  <si>
-    <t>134748357</t>
-  </si>
-  <si>
-    <t>134748392</t>
-  </si>
-  <si>
-    <t>134748464</t>
-  </si>
-  <si>
-    <t>134748622</t>
-  </si>
-  <si>
-    <t>134748670</t>
-  </si>
-  <si>
-    <t>134748680</t>
-  </si>
-  <si>
-    <t>134748737</t>
-  </si>
-  <si>
-    <t>134748853</t>
-  </si>
-  <si>
-    <t>134748934</t>
-  </si>
-  <si>
-    <t>134749144</t>
-  </si>
-  <si>
-    <t>134749198</t>
-  </si>
-  <si>
-    <t>134749273</t>
-  </si>
-  <si>
-    <t>134749444</t>
-  </si>
-  <si>
-    <t>134749799</t>
-  </si>
-  <si>
-    <t>134749859</t>
-  </si>
-  <si>
-    <t>134750015</t>
-  </si>
-  <si>
-    <t>134750097</t>
-  </si>
-  <si>
-    <t>134750289</t>
-  </si>
-  <si>
-    <t>134750311</t>
-  </si>
-  <si>
-    <t>134750346</t>
-  </si>
-  <si>
-    <t>134750573</t>
-  </si>
-  <si>
-    <t>134750590</t>
-  </si>
-  <si>
-    <t>134750715</t>
-  </si>
-  <si>
-    <t>134750786</t>
-  </si>
-  <si>
-    <t>134750790</t>
-  </si>
-  <si>
-    <t>134750805</t>
-  </si>
-  <si>
-    <t>134750850</t>
-  </si>
-  <si>
-    <t>134750883</t>
-  </si>
-  <si>
-    <t>134750932</t>
-  </si>
-  <si>
-    <t>134750982</t>
-  </si>
-  <si>
-    <t>134751080</t>
-  </si>
-  <si>
-    <t>134751082</t>
-  </si>
-  <si>
-    <t>134751221</t>
-  </si>
-  <si>
-    <t>134751482</t>
-  </si>
-  <si>
-    <t>134751506</t>
-  </si>
-  <si>
-    <t>134751535</t>
-  </si>
-  <si>
-    <t>134751634</t>
-  </si>
-  <si>
-    <t>134751769</t>
-  </si>
-  <si>
-    <t>134751865</t>
-  </si>
-  <si>
-    <t>134752085</t>
-  </si>
-  <si>
-    <t>134752117</t>
-  </si>
-  <si>
-    <t>134752265</t>
-  </si>
-  <si>
-    <t>134752458</t>
-  </si>
-  <si>
-    <t>134752478</t>
-  </si>
-  <si>
-    <t>134752516</t>
-  </si>
-  <si>
-    <t>134752521</t>
-  </si>
-  <si>
-    <t>134752621</t>
-  </si>
-  <si>
-    <t>134752874</t>
-  </si>
-  <si>
-    <t>134752919</t>
-  </si>
-  <si>
-    <t>134752955</t>
-  </si>
-  <si>
-    <t>134753016</t>
-  </si>
-  <si>
-    <t>134753023</t>
-  </si>
-  <si>
-    <t>134753099</t>
-  </si>
-  <si>
-    <t>134753181</t>
-  </si>
-  <si>
-    <t>134753424</t>
-  </si>
-  <si>
-    <t>134753427</t>
-  </si>
-  <si>
-    <t>134753432</t>
-  </si>
-  <si>
-    <t>134753494</t>
-  </si>
-  <si>
-    <t>134753526</t>
-  </si>
-  <si>
-    <t>134753614</t>
-  </si>
-  <si>
-    <t>134753808</t>
-  </si>
-  <si>
-    <t>134753873</t>
-  </si>
-  <si>
-    <t>134753889</t>
-  </si>
-  <si>
-    <t>134753938</t>
-  </si>
-  <si>
-    <t>134753990</t>
-  </si>
-  <si>
-    <t>134754173</t>
-  </si>
-  <si>
-    <t>134754290</t>
-  </si>
-  <si>
-    <t>134754322</t>
-  </si>
-  <si>
-    <t>134754358</t>
-  </si>
-  <si>
-    <t>134754550</t>
-  </si>
-  <si>
-    <t>134754557</t>
-  </si>
-  <si>
-    <t>134754570</t>
-  </si>
-  <si>
-    <t>134754669</t>
-  </si>
-  <si>
-    <t>134754713</t>
-  </si>
-  <si>
-    <t>134754907</t>
-  </si>
-  <si>
-    <t>134754922</t>
-  </si>
-  <si>
-    <t>134755011</t>
-  </si>
-  <si>
-    <t>134755061</t>
-  </si>
-  <si>
-    <t>134755304</t>
-  </si>
-  <si>
-    <t>134755358</t>
-  </si>
-  <si>
-    <t>134755438</t>
-  </si>
-  <si>
-    <t>134755521</t>
-  </si>
-  <si>
-    <t>134755524</t>
-  </si>
-  <si>
-    <t>134755664</t>
-  </si>
-  <si>
-    <t>134755686</t>
-  </si>
-  <si>
-    <t>134755703</t>
-  </si>
-  <si>
-    <t>134755767</t>
-  </si>
-  <si>
-    <t>134755776</t>
-  </si>
-  <si>
-    <t>134755806</t>
-  </si>
-  <si>
-    <t>134755955</t>
-  </si>
-  <si>
-    <t>134755966</t>
-  </si>
-  <si>
-    <t>134755978</t>
-  </si>
-  <si>
-    <t>134755988</t>
-  </si>
-  <si>
-    <t>134756002</t>
-  </si>
-  <si>
-    <t>134756049</t>
-  </si>
-  <si>
-    <t>134756242</t>
-  </si>
-  <si>
-    <t>134756268</t>
-  </si>
-  <si>
-    <t>134756349</t>
-  </si>
-  <si>
-    <t>134756365</t>
-  </si>
-  <si>
-    <t>134756370</t>
-  </si>
-  <si>
-    <t>134756385</t>
-  </si>
-  <si>
-    <t>134756415</t>
-  </si>
-  <si>
-    <t>134756476</t>
-  </si>
-  <si>
-    <t>134756504</t>
-  </si>
-  <si>
-    <t>134756573</t>
-  </si>
-  <si>
-    <t>134756582</t>
-  </si>
-  <si>
-    <t>134756642</t>
-  </si>
-  <si>
-    <t>134756660</t>
-  </si>
-  <si>
-    <t>134756730</t>
-  </si>
-  <si>
-    <t>134756752</t>
-  </si>
-  <si>
-    <t>134756781</t>
-  </si>
-  <si>
-    <t>134756795</t>
-  </si>
-  <si>
-    <t>134756865</t>
-  </si>
-  <si>
-    <t>134756891</t>
-  </si>
-  <si>
-    <t>134756951</t>
-  </si>
-  <si>
-    <t>134756982</t>
-  </si>
-  <si>
-    <t>134757113</t>
-  </si>
-  <si>
-    <t>134757149</t>
-  </si>
-  <si>
-    <t>134757420</t>
-  </si>
-  <si>
-    <t>134757462</t>
-  </si>
-  <si>
-    <t>134757645</t>
-  </si>
-  <si>
-    <t>134757674</t>
-  </si>
-  <si>
-    <t>134757690</t>
-  </si>
-  <si>
-    <t>134757710</t>
-  </si>
-  <si>
-    <t>134757757</t>
-  </si>
-  <si>
-    <t>134757771</t>
-  </si>
-  <si>
-    <t>134757899</t>
-  </si>
-  <si>
-    <t>134757942</t>
-  </si>
-  <si>
-    <t>134757943</t>
-  </si>
-  <si>
-    <t>134758393</t>
-  </si>
-  <si>
-    <t>134758420</t>
-  </si>
-  <si>
-    <t>134758505</t>
-  </si>
-  <si>
-    <t>134758520</t>
-  </si>
-  <si>
-    <t>134758555</t>
-  </si>
-  <si>
-    <t>134758635</t>
-  </si>
-  <si>
-    <t>134758646</t>
-  </si>
-  <si>
-    <t>134758703</t>
-  </si>
-  <si>
-    <t>134758707</t>
-  </si>
-  <si>
-    <t>134758720</t>
-  </si>
-  <si>
-    <t>134758846</t>
-  </si>
-  <si>
-    <t>134758948</t>
-  </si>
-  <si>
-    <t>134758954</t>
-  </si>
-  <si>
-    <t>134758960</t>
-  </si>
-  <si>
-    <t>134759043</t>
-  </si>
-  <si>
-    <t>134759165</t>
-  </si>
-  <si>
-    <t>134759199</t>
-  </si>
-  <si>
-    <t>134759493</t>
-  </si>
-  <si>
-    <t>134759496</t>
-  </si>
-  <si>
-    <t>134759730</t>
-  </si>
-  <si>
-    <t>134759806</t>
-  </si>
-  <si>
-    <t>134759892</t>
-  </si>
-  <si>
-    <t>134760142</t>
-  </si>
-  <si>
-    <t>134760244</t>
-  </si>
-  <si>
-    <t>134760383</t>
-  </si>
-  <si>
-    <t>134760396</t>
-  </si>
-  <si>
-    <t>134760403</t>
-  </si>
-  <si>
-    <t>134760520</t>
-  </si>
-  <si>
-    <t>134760690</t>
-  </si>
-  <si>
-    <t>134760730</t>
-  </si>
-  <si>
-    <t>134760755</t>
+    <t>130139848</t>
+  </si>
+  <si>
+    <t>130208078</t>
+  </si>
+  <si>
+    <t>130244455</t>
+  </si>
+  <si>
+    <t>130302784</t>
+  </si>
+  <si>
+    <t>130304848</t>
+  </si>
+  <si>
+    <t>130353183</t>
+  </si>
+  <si>
+    <t>130421865</t>
+  </si>
+  <si>
+    <t>130584373</t>
+  </si>
+  <si>
+    <t>130659873</t>
+  </si>
+  <si>
+    <t>130835142</t>
+  </si>
+  <si>
+    <t>131134014</t>
+  </si>
+  <si>
+    <t>131178459</t>
+  </si>
+  <si>
+    <t>131372663</t>
+  </si>
+  <si>
+    <t>131450066</t>
+  </si>
+  <si>
+    <t>131529545</t>
+  </si>
+  <si>
+    <t>131577897</t>
+  </si>
+  <si>
+    <t>131634438</t>
+  </si>
+  <si>
+    <t>131746585</t>
+  </si>
+  <si>
+    <t>131822429</t>
+  </si>
+  <si>
+    <t>131906641</t>
+  </si>
+  <si>
+    <t>132029395</t>
+  </si>
+  <si>
+    <t>132390166</t>
+  </si>
+  <si>
+    <t>132580948</t>
+  </si>
+  <si>
+    <t>132709738</t>
+  </si>
+  <si>
+    <t>132782170</t>
+  </si>
+  <si>
+    <t>132784320</t>
+  </si>
+  <si>
+    <t>132896001</t>
+  </si>
+  <si>
+    <t>132925855</t>
+  </si>
+  <si>
+    <t>133020510</t>
+  </si>
+  <si>
+    <t>133203383</t>
+  </si>
+  <si>
+    <t>133292993</t>
+  </si>
+  <si>
+    <t>133665150</t>
+  </si>
+  <si>
+    <t>133702546</t>
+  </si>
+  <si>
+    <t>133850449</t>
+  </si>
+  <si>
+    <t>134556355</t>
+  </si>
+  <si>
+    <t>134588394</t>
+  </si>
+  <si>
+    <t>134620708</t>
+  </si>
+  <si>
+    <t>134760843</t>
+  </si>
+  <si>
+    <t>134760870</t>
+  </si>
+  <si>
+    <t>134760926</t>
+  </si>
+  <si>
+    <t>134761038</t>
+  </si>
+  <si>
+    <t>134761257</t>
+  </si>
+  <si>
+    <t>134761547</t>
+  </si>
+  <si>
+    <t>134761612</t>
+  </si>
+  <si>
+    <t>134761750</t>
+  </si>
+  <si>
+    <t>134761781</t>
+  </si>
+  <si>
+    <t>134761811</t>
+  </si>
+  <si>
+    <t>134761843</t>
+  </si>
+  <si>
+    <t>134762024</t>
+  </si>
+  <si>
+    <t>134762034</t>
+  </si>
+  <si>
+    <t>134762109</t>
+  </si>
+  <si>
+    <t>134762140</t>
+  </si>
+  <si>
+    <t>134762489</t>
+  </si>
+  <si>
+    <t>134762672</t>
+  </si>
+  <si>
+    <t>134763221</t>
+  </si>
+  <si>
+    <t>134763271</t>
+  </si>
+  <si>
+    <t>134763513</t>
+  </si>
+  <si>
+    <t>134763556</t>
+  </si>
+  <si>
+    <t>134763635</t>
+  </si>
+  <si>
+    <t>134763746</t>
+  </si>
+  <si>
+    <t>134763826</t>
+  </si>
+  <si>
+    <t>134763932</t>
+  </si>
+  <si>
+    <t>134764005</t>
+  </si>
+  <si>
+    <t>134764104</t>
+  </si>
+  <si>
+    <t>134764128</t>
+  </si>
+  <si>
+    <t>134764132</t>
+  </si>
+  <si>
+    <t>134764377</t>
+  </si>
+  <si>
+    <t>134764418</t>
+  </si>
+  <si>
+    <t>134764503</t>
+  </si>
+  <si>
+    <t>134764518</t>
+  </si>
+  <si>
+    <t>134764639</t>
+  </si>
+  <si>
+    <t>134764747</t>
+  </si>
+  <si>
+    <t>134764962</t>
+  </si>
+  <si>
+    <t>134765094</t>
+  </si>
+  <si>
+    <t>134765198</t>
+  </si>
+  <si>
+    <t>134765235</t>
+  </si>
+  <si>
+    <t>134765271</t>
+  </si>
+  <si>
+    <t>134765280</t>
+  </si>
+  <si>
+    <t>134765407</t>
+  </si>
+  <si>
+    <t>134765767</t>
+  </si>
+  <si>
+    <t>134765859</t>
+  </si>
+  <si>
+    <t>134766301</t>
+  </si>
+  <si>
+    <t>134766341</t>
+  </si>
+  <si>
+    <t>134766347</t>
+  </si>
+  <si>
+    <t>134766424</t>
+  </si>
+  <si>
+    <t>134766438</t>
+  </si>
+  <si>
+    <t>134766481</t>
+  </si>
+  <si>
+    <t>134766644</t>
+  </si>
+  <si>
+    <t>134766819</t>
+  </si>
+  <si>
+    <t>134767026</t>
+  </si>
+  <si>
+    <t>134767172</t>
+  </si>
+  <si>
+    <t>134767173</t>
+  </si>
+  <si>
+    <t>134767308</t>
+  </si>
+  <si>
+    <t>134767489</t>
+  </si>
+  <si>
+    <t>134767571</t>
+  </si>
+  <si>
+    <t>134767643</t>
+  </si>
+  <si>
+    <t>134767671</t>
+  </si>
+  <si>
+    <t>134767754</t>
+  </si>
+  <si>
+    <t>134767882</t>
+  </si>
+  <si>
+    <t>134767956</t>
+  </si>
+  <si>
+    <t>134768347</t>
+  </si>
+  <si>
+    <t>134768370</t>
+  </si>
+  <si>
+    <t>134768415</t>
+  </si>
+  <si>
+    <t>134768540</t>
+  </si>
+  <si>
+    <t>134768565</t>
+  </si>
+  <si>
+    <t>134768574</t>
+  </si>
+  <si>
+    <t>134768648</t>
+  </si>
+  <si>
+    <t>134768702</t>
+  </si>
+  <si>
+    <t>134768801</t>
+  </si>
+  <si>
+    <t>134769059</t>
+  </si>
+  <si>
+    <t>134769253</t>
+  </si>
+  <si>
+    <t>134769270</t>
+  </si>
+  <si>
+    <t>134769376</t>
+  </si>
+  <si>
+    <t>134769386</t>
+  </si>
+  <si>
+    <t>134769401</t>
+  </si>
+  <si>
+    <t>134769415</t>
+  </si>
+  <si>
+    <t>134769439</t>
+  </si>
+  <si>
+    <t>134769442</t>
+  </si>
+  <si>
+    <t>134769481</t>
+  </si>
+  <si>
+    <t>134769488</t>
+  </si>
+  <si>
+    <t>134769625</t>
+  </si>
+  <si>
+    <t>134769674</t>
+  </si>
+  <si>
+    <t>134769769</t>
+  </si>
+  <si>
+    <t>134769793</t>
+  </si>
+  <si>
+    <t>134770084</t>
+  </si>
+  <si>
+    <t>134770109</t>
+  </si>
+  <si>
+    <t>134770112</t>
+  </si>
+  <si>
+    <t>134770187</t>
+  </si>
+  <si>
+    <t>134770357</t>
+  </si>
+  <si>
+    <t>134770874</t>
+  </si>
+  <si>
+    <t>134770884</t>
+  </si>
+  <si>
+    <t>134771010</t>
+  </si>
+  <si>
+    <t>134771068</t>
+  </si>
+  <si>
+    <t>134771081</t>
+  </si>
+  <si>
+    <t>134771115</t>
+  </si>
+  <si>
+    <t>134771277</t>
+  </si>
+  <si>
+    <t>134771416</t>
+  </si>
+  <si>
+    <t>134771468</t>
+  </si>
+  <si>
+    <t>134771582</t>
+  </si>
+  <si>
+    <t>134772054</t>
+  </si>
+  <si>
+    <t>134772228</t>
+  </si>
+  <si>
+    <t>134772374</t>
+  </si>
+  <si>
+    <t>134772495</t>
+  </si>
+  <si>
+    <t>134772604</t>
+  </si>
+  <si>
+    <t>134772774</t>
+  </si>
+  <si>
+    <t>134772833</t>
+  </si>
+  <si>
+    <t>134772998</t>
+  </si>
+  <si>
+    <t>134773060</t>
+  </si>
+  <si>
+    <t>134773132</t>
+  </si>
+  <si>
+    <t>134773187</t>
+  </si>
+  <si>
+    <t>134773279</t>
+  </si>
+  <si>
+    <t>134773405</t>
+  </si>
+  <si>
+    <t>134773494</t>
+  </si>
+  <si>
+    <t>134773527</t>
+  </si>
+  <si>
+    <t>134773577</t>
+  </si>
+  <si>
+    <t>134773644</t>
+  </si>
+  <si>
+    <t>134773805</t>
+  </si>
+  <si>
+    <t>134773815</t>
+  </si>
+  <si>
+    <t>134773819</t>
+  </si>
+  <si>
+    <t>134773896</t>
+  </si>
+  <si>
+    <t>134773958</t>
+  </si>
+  <si>
+    <t>134774112</t>
+  </si>
+  <si>
+    <t>134774573</t>
+  </si>
+  <si>
+    <t>134774595</t>
+  </si>
+  <si>
+    <t>134774628</t>
+  </si>
+  <si>
+    <t>134774653</t>
+  </si>
+  <si>
+    <t>134774656</t>
+  </si>
+  <si>
+    <t>134774709</t>
+  </si>
+  <si>
+    <t>134774772</t>
+  </si>
+  <si>
+    <t>134775090</t>
+  </si>
+  <si>
+    <t>134775548</t>
+  </si>
+  <si>
+    <t>134775581</t>
+  </si>
+  <si>
+    <t>134775591</t>
+  </si>
+  <si>
+    <t>134776024</t>
+  </si>
+  <si>
+    <t>134776078</t>
+  </si>
+  <si>
+    <t>134776124</t>
+  </si>
+  <si>
+    <t>134776258</t>
+  </si>
+  <si>
+    <t>134776603</t>
+  </si>
+  <si>
+    <t>134776626</t>
+  </si>
+  <si>
+    <t>134776779</t>
+  </si>
+  <si>
+    <t>134776883</t>
+  </si>
+  <si>
+    <t>134776961</t>
+  </si>
+  <si>
+    <t>134776982</t>
+  </si>
+  <si>
+    <t>134776994</t>
+  </si>
+  <si>
+    <t>134777084</t>
+  </si>
+  <si>
+    <t>134777101</t>
+  </si>
+  <si>
+    <t>134777121</t>
+  </si>
+  <si>
+    <t>134777206</t>
+  </si>
+  <si>
+    <t>134777234</t>
+  </si>
+  <si>
+    <t>134777404</t>
+  </si>
+  <si>
+    <t>134777407</t>
+  </si>
+  <si>
+    <t>134777428</t>
+  </si>
+  <si>
+    <t>134777520</t>
+  </si>
+  <si>
+    <t>134777622</t>
+  </si>
+  <si>
+    <t>134777694</t>
+  </si>
+  <si>
+    <t>134777912</t>
+  </si>
+  <si>
+    <t>134777963</t>
+  </si>
+  <si>
+    <t>134778185</t>
+  </si>
+  <si>
+    <t>134778197</t>
+  </si>
+  <si>
+    <t>134778307</t>
+  </si>
+  <si>
+    <t>134778316</t>
+  </si>
+  <si>
+    <t>134778516</t>
+  </si>
+  <si>
+    <t>134778558</t>
+  </si>
+  <si>
+    <t>134778617</t>
+  </si>
+  <si>
+    <t>134778766</t>
+  </si>
+  <si>
+    <t>134778927</t>
+  </si>
+  <si>
+    <t>134778928</t>
+  </si>
+  <si>
+    <t>134778941</t>
+  </si>
+  <si>
+    <t>134778988</t>
+  </si>
+  <si>
+    <t>134779138</t>
+  </si>
+  <si>
+    <t>134779210</t>
+  </si>
+  <si>
+    <t>134779261</t>
+  </si>
+  <si>
+    <t>134779358</t>
+  </si>
+  <si>
+    <t>134779359</t>
+  </si>
+  <si>
+    <t>134779560</t>
+  </si>
+  <si>
+    <t>134779701</t>
+  </si>
+  <si>
+    <t>134779754</t>
+  </si>
+  <si>
+    <t>134779793</t>
+  </si>
+  <si>
+    <t>134779933</t>
+  </si>
+  <si>
+    <t>134780021</t>
+  </si>
+  <si>
+    <t>134780431</t>
+  </si>
+  <si>
+    <t>134780500</t>
+  </si>
+  <si>
+    <t>134780685</t>
+  </si>
+  <si>
+    <t>134780690</t>
+  </si>
+  <si>
+    <t>134780696</t>
+  </si>
+  <si>
+    <t>134780719</t>
+  </si>
+  <si>
+    <t>134780831</t>
+  </si>
+  <si>
+    <t>134780962</t>
+  </si>
+  <si>
+    <t>134781151</t>
+  </si>
+  <si>
+    <t>134781197</t>
+  </si>
+  <si>
+    <t>134781302</t>
+  </si>
+  <si>
+    <t>134781314</t>
+  </si>
+  <si>
+    <t>134781486</t>
+  </si>
+  <si>
+    <t>134781613</t>
+  </si>
+  <si>
+    <t>134781742</t>
+  </si>
+  <si>
+    <t>134781836</t>
+  </si>
+  <si>
+    <t>134781889</t>
+  </si>
+  <si>
+    <t>134781925</t>
+  </si>
+  <si>
+    <t>134781963</t>
+  </si>
+  <si>
+    <t>134782113</t>
+  </si>
+  <si>
+    <t>134782132</t>
+  </si>
+  <si>
+    <t>134782253</t>
+  </si>
+  <si>
+    <t>134782311</t>
+  </si>
+  <si>
+    <t>134782336</t>
+  </si>
+  <si>
+    <t>134782358</t>
+  </si>
+  <si>
+    <t>134782372</t>
+  </si>
+  <si>
+    <t>134782380</t>
+  </si>
+  <si>
+    <t>134782473</t>
+  </si>
+  <si>
+    <t>134782493</t>
+  </si>
+  <si>
+    <t>134782504</t>
+  </si>
+  <si>
+    <t>134782706</t>
+  </si>
+  <si>
+    <t>134782787</t>
+  </si>
+  <si>
+    <t>134782800</t>
+  </si>
+  <si>
+    <t>134782825</t>
+  </si>
+  <si>
+    <t>134782828</t>
+  </si>
+  <si>
+    <t>134782868</t>
+  </si>
+  <si>
+    <t>134782933</t>
+  </si>
+  <si>
+    <t>134782951</t>
+  </si>
+  <si>
+    <t>134782997</t>
+  </si>
+  <si>
+    <t>134783058</t>
+  </si>
+  <si>
+    <t>134783126</t>
+  </si>
+  <si>
+    <t>134783173</t>
+  </si>
+  <si>
+    <t>134783187</t>
+  </si>
+  <si>
+    <t>134783191</t>
+  </si>
+  <si>
+    <t>134783229</t>
+  </si>
+  <si>
+    <t>134783281</t>
+  </si>
+  <si>
+    <t>134783295</t>
+  </si>
+  <si>
+    <t>134783607</t>
+  </si>
+  <si>
+    <t>134783689</t>
+  </si>
+  <si>
+    <t>134783693</t>
+  </si>
+  <si>
+    <t>134783724</t>
+  </si>
+  <si>
+    <t>134783757</t>
+  </si>
+  <si>
+    <t>134783798</t>
+  </si>
+  <si>
+    <t>134783865</t>
+  </si>
+  <si>
+    <t>134783936</t>
+  </si>
+  <si>
+    <t>134783946</t>
+  </si>
+  <si>
+    <t>134783956</t>
+  </si>
+  <si>
+    <t>134783964</t>
+  </si>
+  <si>
+    <t>134784086</t>
+  </si>
+  <si>
+    <t>134784135</t>
+  </si>
+  <si>
+    <t>134784227</t>
+  </si>
+  <si>
+    <t>134784229</t>
+  </si>
+  <si>
+    <t>134784251</t>
+  </si>
+  <si>
+    <t>134784547</t>
+  </si>
+  <si>
+    <t>134784747</t>
+  </si>
+  <si>
+    <t>134785651</t>
+  </si>
+  <si>
+    <t>134785762</t>
+  </si>
+  <si>
+    <t>134785926</t>
+  </si>
+  <si>
+    <t>134786239</t>
+  </si>
+  <si>
+    <t>134786797</t>
+  </si>
+  <si>
+    <t>134787121</t>
+  </si>
+  <si>
+    <t>134787126</t>
+  </si>
+  <si>
+    <t>134787187</t>
+  </si>
+  <si>
+    <t>134787213</t>
+  </si>
+  <si>
+    <t>134787242</t>
+  </si>
+  <si>
+    <t>134787332</t>
+  </si>
+  <si>
+    <t>134787334</t>
+  </si>
+  <si>
+    <t>134787371</t>
+  </si>
+  <si>
+    <t>134787382</t>
+  </si>
+  <si>
+    <t>134787482</t>
+  </si>
+  <si>
+    <t>134787650</t>
+  </si>
+  <si>
+    <t>134787719</t>
+  </si>
+  <si>
+    <t>134787731</t>
+  </si>
+  <si>
+    <t>134787792</t>
+  </si>
+  <si>
+    <t>134787901</t>
+  </si>
+  <si>
+    <t>134787904</t>
+  </si>
+  <si>
+    <t>134787956</t>
+  </si>
+  <si>
+    <t>134787977</t>
+  </si>
+  <si>
+    <t>134788016</t>
+  </si>
+  <si>
+    <t>134788038</t>
+  </si>
+  <si>
+    <t>134788058</t>
+  </si>
+  <si>
+    <t>134788116</t>
+  </si>
+  <si>
+    <t>134788195</t>
+  </si>
+  <si>
+    <t>134788216</t>
+  </si>
+  <si>
+    <t>134788225</t>
+  </si>
+  <si>
+    <t>134788228</t>
+  </si>
+  <si>
+    <t>134788516</t>
+  </si>
+  <si>
+    <t>134788557</t>
+  </si>
+  <si>
+    <t>134788585</t>
+  </si>
+  <si>
+    <t>134788602</t>
+  </si>
+  <si>
+    <t>134788605</t>
+  </si>
+  <si>
+    <t>134788612</t>
+  </si>
+  <si>
+    <t>134788615</t>
+  </si>
+  <si>
+    <t>134788620</t>
+  </si>
+  <si>
+    <t>134788650</t>
+  </si>
+  <si>
+    <t>134788771</t>
+  </si>
+  <si>
+    <t>134788822</t>
+  </si>
+  <si>
+    <t>134788871</t>
+  </si>
+  <si>
+    <t>134788913</t>
+  </si>
+  <si>
+    <t>134788977</t>
+  </si>
+  <si>
+    <t>134789034</t>
+  </si>
+  <si>
+    <t>134789057</t>
+  </si>
+  <si>
+    <t>134789139</t>
+  </si>
+  <si>
+    <t>134789145</t>
+  </si>
+  <si>
+    <t>134789146</t>
+  </si>
+  <si>
+    <t>134789159</t>
+  </si>
+  <si>
+    <t>134789204</t>
+  </si>
+  <si>
+    <t>134789526</t>
+  </si>
+  <si>
+    <t>134789548</t>
+  </si>
+  <si>
+    <t>134789600</t>
+  </si>
+  <si>
+    <t>134789677</t>
+  </si>
+  <si>
+    <t>134789770</t>
+  </si>
+  <si>
+    <t>134789771</t>
+  </si>
+  <si>
+    <t>134789821</t>
+  </si>
+  <si>
+    <t>134789825</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C333"/>
+  <dimension ref="A1:C346"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -4485,210 +4659,539 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B289" s="6"/>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C289" s="5"/>
     </row>
-    <row r="290" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B290" s="6"/>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C290" s="5"/>
     </row>
-    <row r="291" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B291" s="6"/>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C291" s="5"/>
     </row>
-    <row r="292" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B292" s="6"/>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C292" s="5"/>
     </row>
-    <row r="293" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B293" s="6"/>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C293" s="5"/>
     </row>
-    <row r="294" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B294" s="6"/>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C294" s="5"/>
     </row>
-    <row r="295" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B295" s="6"/>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C295" s="5"/>
     </row>
-    <row r="296" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B296" s="6"/>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C296" s="5"/>
     </row>
-    <row r="297" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B297" s="6"/>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C297" s="5"/>
     </row>
-    <row r="298" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B298" s="6"/>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C298" s="5"/>
     </row>
-    <row r="299" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B299" s="6"/>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C299" s="5"/>
     </row>
-    <row r="300" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B300" s="6"/>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C300" s="5"/>
     </row>
-    <row r="301" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B301" s="6"/>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C301" s="5"/>
     </row>
-    <row r="302" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B302" s="6"/>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C302" s="5"/>
     </row>
-    <row r="303" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B303" s="6"/>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C303" s="5"/>
     </row>
-    <row r="304" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B304" s="6"/>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C304" s="5"/>
     </row>
-    <row r="305" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B305" s="6"/>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C305" s="5"/>
     </row>
-    <row r="306" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B306" s="6"/>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C306" s="5"/>
     </row>
-    <row r="307" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B307" s="6"/>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C307" s="5"/>
     </row>
-    <row r="308" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B308" s="6"/>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C308" s="5"/>
     </row>
-    <row r="309" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B309" s="6"/>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C309" s="5"/>
     </row>
-    <row r="310" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B310" s="6"/>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C310" s="5"/>
     </row>
-    <row r="311" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B311" s="6"/>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C311" s="5"/>
     </row>
-    <row r="312" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B312" s="6"/>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C312" s="5"/>
     </row>
-    <row r="313" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B313" s="6"/>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C313" s="5"/>
     </row>
-    <row r="314" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B314" s="6"/>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C314" s="5"/>
     </row>
-    <row r="315" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B315" s="6"/>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C315" s="5"/>
     </row>
-    <row r="316" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B316" s="6"/>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C316" s="5"/>
     </row>
-    <row r="317" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B317" s="6"/>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C317" s="5"/>
     </row>
-    <row r="318" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B318" s="6"/>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C318" s="5"/>
     </row>
-    <row r="319" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B319" s="6"/>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C319" s="5"/>
     </row>
-    <row r="320" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B320" s="6"/>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C320" s="5"/>
     </row>
-    <row r="321" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B321" s="6"/>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C321" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B322" s="6"/>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C322" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B323" s="6"/>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C323" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B324" s="6"/>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C324" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B325" s="6"/>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C325" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B326" s="6"/>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C326" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B327" s="6"/>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C327" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B328" s="6"/>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C328" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B329" s="6"/>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C329" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B330" s="6"/>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C330" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B331" s="6"/>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C331" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B332" s="6"/>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C332" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B333" s="6"/>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C333" s="5" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B340" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E920386-0383-4C5D-B0FA-2D7C1F3E48FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAD255D-A2C8-4938-BD50-6D2B8D74D41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="366">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,1039 +45,1087 @@
     <t>.</t>
   </si>
   <si>
-    <t>130139848</t>
-  </si>
-  <si>
-    <t>130208078</t>
-  </si>
-  <si>
-    <t>130244455</t>
-  </si>
-  <si>
-    <t>130302784</t>
-  </si>
-  <si>
-    <t>130304848</t>
-  </si>
-  <si>
-    <t>130353183</t>
-  </si>
-  <si>
-    <t>130421865</t>
-  </si>
-  <si>
-    <t>130584373</t>
-  </si>
-  <si>
-    <t>130659873</t>
-  </si>
-  <si>
-    <t>130835142</t>
-  </si>
-  <si>
-    <t>131134014</t>
-  </si>
-  <si>
-    <t>131178459</t>
-  </si>
-  <si>
-    <t>131372663</t>
-  </si>
-  <si>
-    <t>131450066</t>
-  </si>
-  <si>
-    <t>131529545</t>
-  </si>
-  <si>
-    <t>131577897</t>
-  </si>
-  <si>
-    <t>131634438</t>
-  </si>
-  <si>
-    <t>131746585</t>
-  </si>
-  <si>
-    <t>131822429</t>
-  </si>
-  <si>
-    <t>131906641</t>
-  </si>
-  <si>
-    <t>132029395</t>
-  </si>
-  <si>
-    <t>132390166</t>
-  </si>
-  <si>
-    <t>132580948</t>
-  </si>
-  <si>
-    <t>132709738</t>
-  </si>
-  <si>
-    <t>132782170</t>
-  </si>
-  <si>
-    <t>132784320</t>
-  </si>
-  <si>
-    <t>132896001</t>
-  </si>
-  <si>
-    <t>132925855</t>
-  </si>
-  <si>
-    <t>133020510</t>
-  </si>
-  <si>
-    <t>133203383</t>
-  </si>
-  <si>
-    <t>133292993</t>
-  </si>
-  <si>
-    <t>133665150</t>
-  </si>
-  <si>
-    <t>133702546</t>
-  </si>
-  <si>
-    <t>133850449</t>
-  </si>
-  <si>
-    <t>134556355</t>
-  </si>
-  <si>
-    <t>134588394</t>
-  </si>
-  <si>
-    <t>134620708</t>
-  </si>
-  <si>
-    <t>134760843</t>
-  </si>
-  <si>
-    <t>134760870</t>
-  </si>
-  <si>
-    <t>134760926</t>
-  </si>
-  <si>
-    <t>134761038</t>
-  </si>
-  <si>
-    <t>134761257</t>
-  </si>
-  <si>
-    <t>134761547</t>
-  </si>
-  <si>
-    <t>134761612</t>
-  </si>
-  <si>
-    <t>134761750</t>
-  </si>
-  <si>
-    <t>134761781</t>
-  </si>
-  <si>
-    <t>134761811</t>
-  </si>
-  <si>
-    <t>134761843</t>
-  </si>
-  <si>
-    <t>134762024</t>
-  </si>
-  <si>
-    <t>134762034</t>
-  </si>
-  <si>
-    <t>134762109</t>
-  </si>
-  <si>
-    <t>134762140</t>
-  </si>
-  <si>
-    <t>134762489</t>
-  </si>
-  <si>
-    <t>134762672</t>
-  </si>
-  <si>
-    <t>134763221</t>
-  </si>
-  <si>
-    <t>134763271</t>
-  </si>
-  <si>
-    <t>134763513</t>
-  </si>
-  <si>
-    <t>134763556</t>
-  </si>
-  <si>
-    <t>134763635</t>
-  </si>
-  <si>
-    <t>134763746</t>
-  </si>
-  <si>
-    <t>134763826</t>
-  </si>
-  <si>
-    <t>134763932</t>
-  </si>
-  <si>
-    <t>134764005</t>
-  </si>
-  <si>
-    <t>134764104</t>
-  </si>
-  <si>
-    <t>134764128</t>
-  </si>
-  <si>
-    <t>134764132</t>
-  </si>
-  <si>
-    <t>134764377</t>
-  </si>
-  <si>
-    <t>134764418</t>
-  </si>
-  <si>
-    <t>134764503</t>
-  </si>
-  <si>
-    <t>134764518</t>
-  </si>
-  <si>
-    <t>134764639</t>
-  </si>
-  <si>
-    <t>134764747</t>
-  </si>
-  <si>
-    <t>134764962</t>
-  </si>
-  <si>
-    <t>134765094</t>
-  </si>
-  <si>
-    <t>134765198</t>
-  </si>
-  <si>
-    <t>134765235</t>
-  </si>
-  <si>
-    <t>134765271</t>
-  </si>
-  <si>
-    <t>134765280</t>
-  </si>
-  <si>
-    <t>134765407</t>
-  </si>
-  <si>
-    <t>134765767</t>
-  </si>
-  <si>
-    <t>134765859</t>
-  </si>
-  <si>
-    <t>134766301</t>
-  </si>
-  <si>
-    <t>134766341</t>
-  </si>
-  <si>
-    <t>134766347</t>
-  </si>
-  <si>
-    <t>134766424</t>
-  </si>
-  <si>
-    <t>134766438</t>
-  </si>
-  <si>
-    <t>134766481</t>
-  </si>
-  <si>
-    <t>134766644</t>
-  </si>
-  <si>
-    <t>134766819</t>
-  </si>
-  <si>
-    <t>134767026</t>
-  </si>
-  <si>
-    <t>134767172</t>
-  </si>
-  <si>
-    <t>134767173</t>
-  </si>
-  <si>
-    <t>134767308</t>
-  </si>
-  <si>
-    <t>134767489</t>
-  </si>
-  <si>
-    <t>134767571</t>
-  </si>
-  <si>
-    <t>134767643</t>
-  </si>
-  <si>
-    <t>134767671</t>
-  </si>
-  <si>
-    <t>134767754</t>
-  </si>
-  <si>
-    <t>134767882</t>
-  </si>
-  <si>
-    <t>134767956</t>
-  </si>
-  <si>
-    <t>134768347</t>
-  </si>
-  <si>
-    <t>134768370</t>
-  </si>
-  <si>
-    <t>134768415</t>
-  </si>
-  <si>
-    <t>134768540</t>
-  </si>
-  <si>
-    <t>134768565</t>
-  </si>
-  <si>
-    <t>134768574</t>
-  </si>
-  <si>
-    <t>134768648</t>
-  </si>
-  <si>
-    <t>134768702</t>
-  </si>
-  <si>
-    <t>134768801</t>
-  </si>
-  <si>
-    <t>134769059</t>
-  </si>
-  <si>
-    <t>134769253</t>
-  </si>
-  <si>
-    <t>134769270</t>
-  </si>
-  <si>
-    <t>134769376</t>
-  </si>
-  <si>
-    <t>134769386</t>
-  </si>
-  <si>
-    <t>134769401</t>
-  </si>
-  <si>
-    <t>134769415</t>
-  </si>
-  <si>
-    <t>134769439</t>
-  </si>
-  <si>
-    <t>134769442</t>
-  </si>
-  <si>
-    <t>134769481</t>
-  </si>
-  <si>
-    <t>134769488</t>
-  </si>
-  <si>
-    <t>134769625</t>
-  </si>
-  <si>
-    <t>134769674</t>
-  </si>
-  <si>
-    <t>134769769</t>
-  </si>
-  <si>
-    <t>134769793</t>
-  </si>
-  <si>
-    <t>134770084</t>
-  </si>
-  <si>
-    <t>134770109</t>
-  </si>
-  <si>
-    <t>134770112</t>
-  </si>
-  <si>
-    <t>134770187</t>
-  </si>
-  <si>
-    <t>134770357</t>
-  </si>
-  <si>
-    <t>134770874</t>
-  </si>
-  <si>
-    <t>134770884</t>
-  </si>
-  <si>
-    <t>134771010</t>
-  </si>
-  <si>
-    <t>134771068</t>
-  </si>
-  <si>
-    <t>134771081</t>
-  </si>
-  <si>
-    <t>134771115</t>
-  </si>
-  <si>
-    <t>134771277</t>
-  </si>
-  <si>
-    <t>134771416</t>
-  </si>
-  <si>
-    <t>134771468</t>
-  </si>
-  <si>
-    <t>134771582</t>
-  </si>
-  <si>
-    <t>134772054</t>
-  </si>
-  <si>
-    <t>134772228</t>
-  </si>
-  <si>
-    <t>134772374</t>
-  </si>
-  <si>
-    <t>134772495</t>
-  </si>
-  <si>
-    <t>134772604</t>
-  </si>
-  <si>
-    <t>134772774</t>
-  </si>
-  <si>
-    <t>134772833</t>
-  </si>
-  <si>
-    <t>134772998</t>
-  </si>
-  <si>
-    <t>134773060</t>
-  </si>
-  <si>
-    <t>134773132</t>
-  </si>
-  <si>
-    <t>134773187</t>
-  </si>
-  <si>
-    <t>134773279</t>
-  </si>
-  <si>
-    <t>134773405</t>
-  </si>
-  <si>
-    <t>134773494</t>
-  </si>
-  <si>
-    <t>134773527</t>
-  </si>
-  <si>
-    <t>134773577</t>
-  </si>
-  <si>
-    <t>134773644</t>
-  </si>
-  <si>
-    <t>134773805</t>
-  </si>
-  <si>
-    <t>134773815</t>
-  </si>
-  <si>
-    <t>134773819</t>
-  </si>
-  <si>
-    <t>134773896</t>
-  </si>
-  <si>
-    <t>134773958</t>
-  </si>
-  <si>
-    <t>134774112</t>
-  </si>
-  <si>
-    <t>134774573</t>
-  </si>
-  <si>
-    <t>134774595</t>
-  </si>
-  <si>
-    <t>134774628</t>
-  </si>
-  <si>
-    <t>134774653</t>
-  </si>
-  <si>
-    <t>134774656</t>
-  </si>
-  <si>
-    <t>134774709</t>
-  </si>
-  <si>
-    <t>134774772</t>
-  </si>
-  <si>
-    <t>134775090</t>
-  </si>
-  <si>
-    <t>134775548</t>
-  </si>
-  <si>
-    <t>134775581</t>
-  </si>
-  <si>
-    <t>134775591</t>
-  </si>
-  <si>
-    <t>134776024</t>
-  </si>
-  <si>
-    <t>134776078</t>
-  </si>
-  <si>
-    <t>134776124</t>
-  </si>
-  <si>
-    <t>134776258</t>
-  </si>
-  <si>
-    <t>134776603</t>
-  </si>
-  <si>
-    <t>134776626</t>
-  </si>
-  <si>
-    <t>134776779</t>
-  </si>
-  <si>
-    <t>134776883</t>
-  </si>
-  <si>
-    <t>134776961</t>
-  </si>
-  <si>
-    <t>134776982</t>
-  </si>
-  <si>
-    <t>134776994</t>
-  </si>
-  <si>
-    <t>134777084</t>
-  </si>
-  <si>
-    <t>134777101</t>
-  </si>
-  <si>
-    <t>134777121</t>
-  </si>
-  <si>
-    <t>134777206</t>
-  </si>
-  <si>
-    <t>134777234</t>
-  </si>
-  <si>
-    <t>134777404</t>
-  </si>
-  <si>
-    <t>134777407</t>
-  </si>
-  <si>
-    <t>134777428</t>
-  </si>
-  <si>
-    <t>134777520</t>
-  </si>
-  <si>
-    <t>134777622</t>
-  </si>
-  <si>
-    <t>134777694</t>
-  </si>
-  <si>
-    <t>134777912</t>
-  </si>
-  <si>
-    <t>134777963</t>
-  </si>
-  <si>
-    <t>134778185</t>
-  </si>
-  <si>
-    <t>134778197</t>
-  </si>
-  <si>
-    <t>134778307</t>
-  </si>
-  <si>
-    <t>134778316</t>
-  </si>
-  <si>
-    <t>134778516</t>
-  </si>
-  <si>
-    <t>134778558</t>
-  </si>
-  <si>
-    <t>134778617</t>
-  </si>
-  <si>
-    <t>134778766</t>
-  </si>
-  <si>
-    <t>134778927</t>
-  </si>
-  <si>
-    <t>134778928</t>
-  </si>
-  <si>
-    <t>134778941</t>
-  </si>
-  <si>
-    <t>134778988</t>
-  </si>
-  <si>
-    <t>134779138</t>
-  </si>
-  <si>
-    <t>134779210</t>
-  </si>
-  <si>
-    <t>134779261</t>
-  </si>
-  <si>
-    <t>134779358</t>
-  </si>
-  <si>
-    <t>134779359</t>
-  </si>
-  <si>
-    <t>134779560</t>
-  </si>
-  <si>
-    <t>134779701</t>
-  </si>
-  <si>
-    <t>134779754</t>
-  </si>
-  <si>
-    <t>134779793</t>
-  </si>
-  <si>
-    <t>134779933</t>
-  </si>
-  <si>
-    <t>134780021</t>
-  </si>
-  <si>
-    <t>134780431</t>
-  </si>
-  <si>
-    <t>134780500</t>
-  </si>
-  <si>
-    <t>134780685</t>
-  </si>
-  <si>
-    <t>134780690</t>
-  </si>
-  <si>
-    <t>134780696</t>
-  </si>
-  <si>
-    <t>134780719</t>
-  </si>
-  <si>
-    <t>134780831</t>
-  </si>
-  <si>
-    <t>134780962</t>
-  </si>
-  <si>
-    <t>134781151</t>
-  </si>
-  <si>
-    <t>134781197</t>
-  </si>
-  <si>
-    <t>134781302</t>
-  </si>
-  <si>
-    <t>134781314</t>
-  </si>
-  <si>
-    <t>134781486</t>
-  </si>
-  <si>
-    <t>134781613</t>
-  </si>
-  <si>
-    <t>134781742</t>
-  </si>
-  <si>
-    <t>134781836</t>
-  </si>
-  <si>
-    <t>134781889</t>
-  </si>
-  <si>
-    <t>134781925</t>
-  </si>
-  <si>
-    <t>134781963</t>
-  </si>
-  <si>
-    <t>134782113</t>
-  </si>
-  <si>
-    <t>134782132</t>
-  </si>
-  <si>
-    <t>134782253</t>
-  </si>
-  <si>
-    <t>134782311</t>
-  </si>
-  <si>
-    <t>134782336</t>
-  </si>
-  <si>
-    <t>134782358</t>
-  </si>
-  <si>
-    <t>134782372</t>
-  </si>
-  <si>
-    <t>134782380</t>
-  </si>
-  <si>
-    <t>134782473</t>
-  </si>
-  <si>
-    <t>134782493</t>
-  </si>
-  <si>
-    <t>134782504</t>
-  </si>
-  <si>
-    <t>134782706</t>
-  </si>
-  <si>
-    <t>134782787</t>
-  </si>
-  <si>
-    <t>134782800</t>
-  </si>
-  <si>
-    <t>134782825</t>
-  </si>
-  <si>
-    <t>134782828</t>
-  </si>
-  <si>
-    <t>134782868</t>
-  </si>
-  <si>
-    <t>134782933</t>
-  </si>
-  <si>
-    <t>134782951</t>
-  </si>
-  <si>
-    <t>134782997</t>
-  </si>
-  <si>
-    <t>134783058</t>
-  </si>
-  <si>
-    <t>134783126</t>
-  </si>
-  <si>
-    <t>134783173</t>
-  </si>
-  <si>
-    <t>134783187</t>
-  </si>
-  <si>
-    <t>134783191</t>
-  </si>
-  <si>
-    <t>134783229</t>
-  </si>
-  <si>
-    <t>134783281</t>
-  </si>
-  <si>
-    <t>134783295</t>
-  </si>
-  <si>
-    <t>134783607</t>
-  </si>
-  <si>
-    <t>134783689</t>
-  </si>
-  <si>
-    <t>134783693</t>
-  </si>
-  <si>
-    <t>134783724</t>
-  </si>
-  <si>
-    <t>134783757</t>
-  </si>
-  <si>
-    <t>134783798</t>
-  </si>
-  <si>
-    <t>134783865</t>
-  </si>
-  <si>
-    <t>134783936</t>
-  </si>
-  <si>
-    <t>134783946</t>
-  </si>
-  <si>
-    <t>134783956</t>
-  </si>
-  <si>
-    <t>134783964</t>
-  </si>
-  <si>
-    <t>134784086</t>
-  </si>
-  <si>
-    <t>134784135</t>
-  </si>
-  <si>
-    <t>134784227</t>
-  </si>
-  <si>
-    <t>134784229</t>
-  </si>
-  <si>
-    <t>134784251</t>
-  </si>
-  <si>
-    <t>134784547</t>
-  </si>
-  <si>
-    <t>134784747</t>
-  </si>
-  <si>
-    <t>134785651</t>
-  </si>
-  <si>
-    <t>134785762</t>
-  </si>
-  <si>
-    <t>134785926</t>
-  </si>
-  <si>
-    <t>134786239</t>
-  </si>
-  <si>
-    <t>134786797</t>
-  </si>
-  <si>
-    <t>134787121</t>
-  </si>
-  <si>
-    <t>134787126</t>
-  </si>
-  <si>
-    <t>134787187</t>
-  </si>
-  <si>
-    <t>134787213</t>
-  </si>
-  <si>
-    <t>134787242</t>
-  </si>
-  <si>
-    <t>134787332</t>
-  </si>
-  <si>
-    <t>134787334</t>
-  </si>
-  <si>
-    <t>134787371</t>
-  </si>
-  <si>
-    <t>134787382</t>
-  </si>
-  <si>
-    <t>134787482</t>
-  </si>
-  <si>
-    <t>134787650</t>
-  </si>
-  <si>
-    <t>134787719</t>
-  </si>
-  <si>
-    <t>134787731</t>
-  </si>
-  <si>
-    <t>134787792</t>
-  </si>
-  <si>
-    <t>134787901</t>
-  </si>
-  <si>
-    <t>134787904</t>
-  </si>
-  <si>
-    <t>134787956</t>
-  </si>
-  <si>
-    <t>134787977</t>
-  </si>
-  <si>
-    <t>134788016</t>
-  </si>
-  <si>
-    <t>134788038</t>
-  </si>
-  <si>
-    <t>134788058</t>
-  </si>
-  <si>
-    <t>134788116</t>
-  </si>
-  <si>
-    <t>134788195</t>
-  </si>
-  <si>
-    <t>134788216</t>
-  </si>
-  <si>
-    <t>134788225</t>
-  </si>
-  <si>
-    <t>134788228</t>
-  </si>
-  <si>
-    <t>134788516</t>
-  </si>
-  <si>
-    <t>134788557</t>
-  </si>
-  <si>
-    <t>134788585</t>
-  </si>
-  <si>
-    <t>134788602</t>
-  </si>
-  <si>
-    <t>134788605</t>
-  </si>
-  <si>
-    <t>134788612</t>
-  </si>
-  <si>
-    <t>134788615</t>
-  </si>
-  <si>
-    <t>134788620</t>
-  </si>
-  <si>
-    <t>134788650</t>
-  </si>
-  <si>
-    <t>134788771</t>
-  </si>
-  <si>
-    <t>134788822</t>
-  </si>
-  <si>
-    <t>134788871</t>
-  </si>
-  <si>
-    <t>134788913</t>
-  </si>
-  <si>
-    <t>134788977</t>
-  </si>
-  <si>
-    <t>134789034</t>
-  </si>
-  <si>
-    <t>134789057</t>
-  </si>
-  <si>
-    <t>134789139</t>
-  </si>
-  <si>
-    <t>134789145</t>
-  </si>
-  <si>
-    <t>134789146</t>
-  </si>
-  <si>
-    <t>134789159</t>
-  </si>
-  <si>
-    <t>134789204</t>
-  </si>
-  <si>
-    <t>134789526</t>
-  </si>
-  <si>
-    <t>134789548</t>
-  </si>
-  <si>
-    <t>134789600</t>
-  </si>
-  <si>
-    <t>134789677</t>
-  </si>
-  <si>
-    <t>134789770</t>
-  </si>
-  <si>
-    <t>134789771</t>
-  </si>
-  <si>
-    <t>134789821</t>
-  </si>
-  <si>
-    <t>134789825</t>
+    <t>131284175</t>
+  </si>
+  <si>
+    <t>131408286</t>
+  </si>
+  <si>
+    <t>131753794</t>
+  </si>
+  <si>
+    <t>131956479</t>
+  </si>
+  <si>
+    <t>132021163</t>
+  </si>
+  <si>
+    <t>132434165</t>
+  </si>
+  <si>
+    <t>132501500</t>
+  </si>
+  <si>
+    <t>132658943</t>
+  </si>
+  <si>
+    <t>132715315</t>
+  </si>
+  <si>
+    <t>132735152</t>
+  </si>
+  <si>
+    <t>132953279</t>
+  </si>
+  <si>
+    <t>133514131</t>
+  </si>
+  <si>
+    <t>133748728</t>
+  </si>
+  <si>
+    <t>133847633</t>
+  </si>
+  <si>
+    <t>133861394</t>
+  </si>
+  <si>
+    <t>133976168</t>
+  </si>
+  <si>
+    <t>134037153</t>
+  </si>
+  <si>
+    <t>134113266</t>
+  </si>
+  <si>
+    <t>134180685</t>
+  </si>
+  <si>
+    <t>134277001</t>
+  </si>
+  <si>
+    <t>134277020</t>
+  </si>
+  <si>
+    <t>134277590</t>
+  </si>
+  <si>
+    <t>134621713</t>
+  </si>
+  <si>
+    <t>134656648</t>
+  </si>
+  <si>
+    <t>134727273</t>
+  </si>
+  <si>
+    <t>134771917</t>
+  </si>
+  <si>
+    <t>134783255</t>
+  </si>
+  <si>
+    <t>134796717</t>
+  </si>
+  <si>
+    <t>134796758</t>
+  </si>
+  <si>
+    <t>134805196</t>
+  </si>
+  <si>
+    <t>134812043</t>
+  </si>
+  <si>
+    <t>134865572</t>
+  </si>
+  <si>
+    <t>134869393</t>
+  </si>
+  <si>
+    <t>134877354</t>
+  </si>
+  <si>
+    <t>134877971</t>
+  </si>
+  <si>
+    <t>134880497</t>
+  </si>
+  <si>
+    <t>134900016</t>
+  </si>
+  <si>
+    <t>134901814</t>
+  </si>
+  <si>
+    <t>134901892</t>
+  </si>
+  <si>
+    <t>134901998</t>
+  </si>
+  <si>
+    <t>134902156</t>
+  </si>
+  <si>
+    <t>134902185</t>
+  </si>
+  <si>
+    <t>134902243</t>
+  </si>
+  <si>
+    <t>134902278</t>
+  </si>
+  <si>
+    <t>134902360</t>
+  </si>
+  <si>
+    <t>134902457</t>
+  </si>
+  <si>
+    <t>134902485</t>
+  </si>
+  <si>
+    <t>134902510</t>
+  </si>
+  <si>
+    <t>134902693</t>
+  </si>
+  <si>
+    <t>134902788</t>
+  </si>
+  <si>
+    <t>134902853</t>
+  </si>
+  <si>
+    <t>134902950</t>
+  </si>
+  <si>
+    <t>134902976</t>
+  </si>
+  <si>
+    <t>134903025</t>
+  </si>
+  <si>
+    <t>134903049</t>
+  </si>
+  <si>
+    <t>134903113</t>
+  </si>
+  <si>
+    <t>134903118</t>
+  </si>
+  <si>
+    <t>134903140</t>
+  </si>
+  <si>
+    <t>134903220</t>
+  </si>
+  <si>
+    <t>134903347</t>
+  </si>
+  <si>
+    <t>134903445</t>
+  </si>
+  <si>
+    <t>134903462</t>
+  </si>
+  <si>
+    <t>134903467</t>
+  </si>
+  <si>
+    <t>134903583</t>
+  </si>
+  <si>
+    <t>134903593</t>
+  </si>
+  <si>
+    <t>134903603</t>
+  </si>
+  <si>
+    <t>134903612</t>
+  </si>
+  <si>
+    <t>134903998</t>
+  </si>
+  <si>
+    <t>134904056</t>
+  </si>
+  <si>
+    <t>134904151</t>
+  </si>
+  <si>
+    <t>134904190</t>
+  </si>
+  <si>
+    <t>134904298</t>
+  </si>
+  <si>
+    <t>134904340</t>
+  </si>
+  <si>
+    <t>134904482</t>
+  </si>
+  <si>
+    <t>134904731</t>
+  </si>
+  <si>
+    <t>134904755</t>
+  </si>
+  <si>
+    <t>134904760</t>
+  </si>
+  <si>
+    <t>134904954</t>
+  </si>
+  <si>
+    <t>134905061</t>
+  </si>
+  <si>
+    <t>134905299</t>
+  </si>
+  <si>
+    <t>134905312</t>
+  </si>
+  <si>
+    <t>134905372</t>
+  </si>
+  <si>
+    <t>134905393</t>
+  </si>
+  <si>
+    <t>134905423</t>
+  </si>
+  <si>
+    <t>134905438</t>
+  </si>
+  <si>
+    <t>134905476</t>
+  </si>
+  <si>
+    <t>134905489</t>
+  </si>
+  <si>
+    <t>134905559</t>
+  </si>
+  <si>
+    <t>134905572</t>
+  </si>
+  <si>
+    <t>134905588</t>
+  </si>
+  <si>
+    <t>134905630</t>
+  </si>
+  <si>
+    <t>134905633</t>
+  </si>
+  <si>
+    <t>134905638</t>
+  </si>
+  <si>
+    <t>134905647</t>
+  </si>
+  <si>
+    <t>134905675</t>
+  </si>
+  <si>
+    <t>134905742</t>
+  </si>
+  <si>
+    <t>134905772</t>
+  </si>
+  <si>
+    <t>134905846</t>
+  </si>
+  <si>
+    <t>134906043</t>
+  </si>
+  <si>
+    <t>134906100</t>
+  </si>
+  <si>
+    <t>134906147</t>
+  </si>
+  <si>
+    <t>134906171</t>
+  </si>
+  <si>
+    <t>134906331</t>
+  </si>
+  <si>
+    <t>134906345</t>
+  </si>
+  <si>
+    <t>134906371</t>
+  </si>
+  <si>
+    <t>134906501</t>
+  </si>
+  <si>
+    <t>134906552</t>
+  </si>
+  <si>
+    <t>134906562</t>
+  </si>
+  <si>
+    <t>134906597</t>
+  </si>
+  <si>
+    <t>134906704</t>
+  </si>
+  <si>
+    <t>134906717</t>
+  </si>
+  <si>
+    <t>134906756</t>
+  </si>
+  <si>
+    <t>134906796</t>
+  </si>
+  <si>
+    <t>134906816</t>
+  </si>
+  <si>
+    <t>134906832</t>
+  </si>
+  <si>
+    <t>134906886</t>
+  </si>
+  <si>
+    <t>134906900</t>
+  </si>
+  <si>
+    <t>134906919</t>
+  </si>
+  <si>
+    <t>134906956</t>
+  </si>
+  <si>
+    <t>134907053</t>
+  </si>
+  <si>
+    <t>134907249</t>
+  </si>
+  <si>
+    <t>134907277</t>
+  </si>
+  <si>
+    <t>134907335</t>
+  </si>
+  <si>
+    <t>134907481</t>
+  </si>
+  <si>
+    <t>134907507</t>
+  </si>
+  <si>
+    <t>134907611</t>
+  </si>
+  <si>
+    <t>134907628</t>
+  </si>
+  <si>
+    <t>134907653</t>
+  </si>
+  <si>
+    <t>134907745</t>
+  </si>
+  <si>
+    <t>134907946</t>
+  </si>
+  <si>
+    <t>134907987</t>
+  </si>
+  <si>
+    <t>134908001</t>
+  </si>
+  <si>
+    <t>134908049</t>
+  </si>
+  <si>
+    <t>134908104</t>
+  </si>
+  <si>
+    <t>134908258</t>
+  </si>
+  <si>
+    <t>134908352</t>
+  </si>
+  <si>
+    <t>134908458</t>
+  </si>
+  <si>
+    <t>134908911</t>
+  </si>
+  <si>
+    <t>134908942</t>
+  </si>
+  <si>
+    <t>134909136</t>
+  </si>
+  <si>
+    <t>134909157</t>
+  </si>
+  <si>
+    <t>134909202</t>
+  </si>
+  <si>
+    <t>134909302</t>
+  </si>
+  <si>
+    <t>134909317</t>
+  </si>
+  <si>
+    <t>134909384</t>
+  </si>
+  <si>
+    <t>134909473</t>
+  </si>
+  <si>
+    <t>134909477</t>
+  </si>
+  <si>
+    <t>134909578</t>
+  </si>
+  <si>
+    <t>134909614</t>
+  </si>
+  <si>
+    <t>134909656</t>
+  </si>
+  <si>
+    <t>134909763</t>
+  </si>
+  <si>
+    <t>134909962</t>
+  </si>
+  <si>
+    <t>134910169</t>
+  </si>
+  <si>
+    <t>134910372</t>
+  </si>
+  <si>
+    <t>134910470</t>
+  </si>
+  <si>
+    <t>134910695</t>
+  </si>
+  <si>
+    <t>134910791</t>
+  </si>
+  <si>
+    <t>134910881</t>
+  </si>
+  <si>
+    <t>134910918</t>
+  </si>
+  <si>
+    <t>134910994</t>
+  </si>
+  <si>
+    <t>134911047</t>
+  </si>
+  <si>
+    <t>134911353</t>
+  </si>
+  <si>
+    <t>134911409</t>
+  </si>
+  <si>
+    <t>134911430</t>
+  </si>
+  <si>
+    <t>134911769</t>
+  </si>
+  <si>
+    <t>134911774</t>
+  </si>
+  <si>
+    <t>134911891</t>
+  </si>
+  <si>
+    <t>134912087</t>
+  </si>
+  <si>
+    <t>134912177</t>
+  </si>
+  <si>
+    <t>134912293</t>
+  </si>
+  <si>
+    <t>134912365</t>
+  </si>
+  <si>
+    <t>134912566</t>
+  </si>
+  <si>
+    <t>134912579</t>
+  </si>
+  <si>
+    <t>134912605</t>
+  </si>
+  <si>
+    <t>134912620</t>
+  </si>
+  <si>
+    <t>134912722</t>
+  </si>
+  <si>
+    <t>134912736</t>
+  </si>
+  <si>
+    <t>134912745</t>
+  </si>
+  <si>
+    <t>134912774</t>
+  </si>
+  <si>
+    <t>134912876</t>
+  </si>
+  <si>
+    <t>134912896</t>
+  </si>
+  <si>
+    <t>134913059</t>
+  </si>
+  <si>
+    <t>134913122</t>
+  </si>
+  <si>
+    <t>134913129</t>
+  </si>
+  <si>
+    <t>134913206</t>
+  </si>
+  <si>
+    <t>134913335</t>
+  </si>
+  <si>
+    <t>134913462</t>
+  </si>
+  <si>
+    <t>134913652</t>
+  </si>
+  <si>
+    <t>134913687</t>
+  </si>
+  <si>
+    <t>134913716</t>
+  </si>
+  <si>
+    <t>134913774</t>
+  </si>
+  <si>
+    <t>134913869</t>
+  </si>
+  <si>
+    <t>134913886</t>
+  </si>
+  <si>
+    <t>134913917</t>
+  </si>
+  <si>
+    <t>134913979</t>
+  </si>
+  <si>
+    <t>134913994</t>
+  </si>
+  <si>
+    <t>134914000</t>
+  </si>
+  <si>
+    <t>134914151</t>
+  </si>
+  <si>
+    <t>134914276</t>
+  </si>
+  <si>
+    <t>134914312</t>
+  </si>
+  <si>
+    <t>134914361</t>
+  </si>
+  <si>
+    <t>134914458</t>
+  </si>
+  <si>
+    <t>134915154</t>
+  </si>
+  <si>
+    <t>134915157</t>
+  </si>
+  <si>
+    <t>134915294</t>
+  </si>
+  <si>
+    <t>134915317</t>
+  </si>
+  <si>
+    <t>134915543</t>
+  </si>
+  <si>
+    <t>134915713</t>
+  </si>
+  <si>
+    <t>134915716</t>
+  </si>
+  <si>
+    <t>134916041</t>
+  </si>
+  <si>
+    <t>134916240</t>
+  </si>
+  <si>
+    <t>134916270</t>
+  </si>
+  <si>
+    <t>134916275</t>
+  </si>
+  <si>
+    <t>134916369</t>
+  </si>
+  <si>
+    <t>134916400</t>
+  </si>
+  <si>
+    <t>134916448</t>
+  </si>
+  <si>
+    <t>134916533</t>
+  </si>
+  <si>
+    <t>134916565</t>
+  </si>
+  <si>
+    <t>134916639</t>
+  </si>
+  <si>
+    <t>134916872</t>
+  </si>
+  <si>
+    <t>134916879</t>
+  </si>
+  <si>
+    <t>134916934</t>
+  </si>
+  <si>
+    <t>134917018</t>
+  </si>
+  <si>
+    <t>134917066</t>
+  </si>
+  <si>
+    <t>134917169</t>
+  </si>
+  <si>
+    <t>134917239</t>
+  </si>
+  <si>
+    <t>134917278</t>
+  </si>
+  <si>
+    <t>134917464</t>
+  </si>
+  <si>
+    <t>134917480</t>
+  </si>
+  <si>
+    <t>134917631</t>
+  </si>
+  <si>
+    <t>134918293</t>
+  </si>
+  <si>
+    <t>134918396</t>
+  </si>
+  <si>
+    <t>134918636</t>
+  </si>
+  <si>
+    <t>134918789</t>
+  </si>
+  <si>
+    <t>134918915</t>
+  </si>
+  <si>
+    <t>134918987</t>
+  </si>
+  <si>
+    <t>134919065</t>
+  </si>
+  <si>
+    <t>134919090</t>
+  </si>
+  <si>
+    <t>134919102</t>
+  </si>
+  <si>
+    <t>134919115</t>
+  </si>
+  <si>
+    <t>134919126</t>
+  </si>
+  <si>
+    <t>134919237</t>
+  </si>
+  <si>
+    <t>134919239</t>
+  </si>
+  <si>
+    <t>134919282</t>
+  </si>
+  <si>
+    <t>134919463</t>
+  </si>
+  <si>
+    <t>134919584</t>
+  </si>
+  <si>
+    <t>134919632</t>
+  </si>
+  <si>
+    <t>134919634</t>
+  </si>
+  <si>
+    <t>134919641</t>
+  </si>
+  <si>
+    <t>134919679</t>
+  </si>
+  <si>
+    <t>134919688</t>
+  </si>
+  <si>
+    <t>134919753</t>
+  </si>
+  <si>
+    <t>134919916</t>
+  </si>
+  <si>
+    <t>134920089</t>
+  </si>
+  <si>
+    <t>134920258</t>
+  </si>
+  <si>
+    <t>134920264</t>
+  </si>
+  <si>
+    <t>134920303</t>
+  </si>
+  <si>
+    <t>134920365</t>
+  </si>
+  <si>
+    <t>134920368</t>
+  </si>
+  <si>
+    <t>134920394</t>
+  </si>
+  <si>
+    <t>134920398</t>
+  </si>
+  <si>
+    <t>134920499</t>
+  </si>
+  <si>
+    <t>134920519</t>
+  </si>
+  <si>
+    <t>134920521</t>
+  </si>
+  <si>
+    <t>134920578</t>
+  </si>
+  <si>
+    <t>134920644</t>
+  </si>
+  <si>
+    <t>134920726</t>
+  </si>
+  <si>
+    <t>134920731</t>
+  </si>
+  <si>
+    <t>134920867</t>
+  </si>
+  <si>
+    <t>134921055</t>
+  </si>
+  <si>
+    <t>134921068</t>
+  </si>
+  <si>
+    <t>134921112</t>
+  </si>
+  <si>
+    <t>134921127</t>
+  </si>
+  <si>
+    <t>134921129</t>
+  </si>
+  <si>
+    <t>134921162</t>
+  </si>
+  <si>
+    <t>134921169</t>
+  </si>
+  <si>
+    <t>134921221</t>
+  </si>
+  <si>
+    <t>134921247</t>
+  </si>
+  <si>
+    <t>134921274</t>
+  </si>
+  <si>
+    <t>134921303</t>
+  </si>
+  <si>
+    <t>134921339</t>
+  </si>
+  <si>
+    <t>134921417</t>
+  </si>
+  <si>
+    <t>134921461</t>
+  </si>
+  <si>
+    <t>134921533</t>
+  </si>
+  <si>
+    <t>134921552</t>
+  </si>
+  <si>
+    <t>134921592</t>
+  </si>
+  <si>
+    <t>134921747</t>
+  </si>
+  <si>
+    <t>134921773</t>
+  </si>
+  <si>
+    <t>134921819</t>
+  </si>
+  <si>
+    <t>134921931</t>
+  </si>
+  <si>
+    <t>134921993</t>
+  </si>
+  <si>
+    <t>134922008</t>
+  </si>
+  <si>
+    <t>134922084</t>
+  </si>
+  <si>
+    <t>134922104</t>
+  </si>
+  <si>
+    <t>134922154</t>
+  </si>
+  <si>
+    <t>134922156</t>
+  </si>
+  <si>
+    <t>134922263</t>
+  </si>
+  <si>
+    <t>134922275</t>
+  </si>
+  <si>
+    <t>134922305</t>
+  </si>
+  <si>
+    <t>134922307</t>
+  </si>
+  <si>
+    <t>134922375</t>
+  </si>
+  <si>
+    <t>134922500</t>
+  </si>
+  <si>
+    <t>134922546</t>
+  </si>
+  <si>
+    <t>134922587</t>
+  </si>
+  <si>
+    <t>134922611</t>
+  </si>
+  <si>
+    <t>134922684</t>
+  </si>
+  <si>
+    <t>134922729</t>
+  </si>
+  <si>
+    <t>134922803</t>
+  </si>
+  <si>
+    <t>134922806</t>
+  </si>
+  <si>
+    <t>131041334</t>
+  </si>
+  <si>
+    <t>132213819</t>
+  </si>
+  <si>
+    <t>133808226</t>
+  </si>
+  <si>
+    <t>134903342</t>
+  </si>
+  <si>
+    <t>134905162</t>
+  </si>
+  <si>
+    <t>134905485</t>
+  </si>
+  <si>
+    <t>134905673</t>
+  </si>
+  <si>
+    <t>134905737</t>
+  </si>
+  <si>
+    <t>134906352</t>
+  </si>
+  <si>
+    <t>134906911</t>
+  </si>
+  <si>
+    <t>134908492</t>
+  </si>
+  <si>
+    <t>134910663</t>
+  </si>
+  <si>
+    <t>134910894</t>
+  </si>
+  <si>
+    <t>134911304</t>
+  </si>
+  <si>
+    <t>134911461</t>
+  </si>
+  <si>
+    <t>134911602</t>
+  </si>
+  <si>
+    <t>134911791</t>
+  </si>
+  <si>
+    <t>134913477</t>
+  </si>
+  <si>
+    <t>134913783</t>
+  </si>
+  <si>
+    <t>134914208</t>
+  </si>
+  <si>
+    <t>134914286</t>
+  </si>
+  <si>
+    <t>134916039</t>
+  </si>
+  <si>
+    <t>134919190</t>
+  </si>
+  <si>
+    <t>134919202</t>
+  </si>
+  <si>
+    <t>134920378</t>
+  </si>
+  <si>
+    <t>134920460</t>
+  </si>
+  <si>
+    <t>134920465</t>
+  </si>
+  <si>
+    <t>134920650</t>
+  </si>
+  <si>
+    <t>134920960</t>
+  </si>
+  <si>
+    <t>134921683</t>
+  </si>
+  <si>
+    <t>134921708</t>
+  </si>
+  <si>
+    <t>134921771</t>
+  </si>
+  <si>
+    <t>134922129</t>
+  </si>
+  <si>
+    <t>888211222</t>
+  </si>
+  <si>
+    <t>888211228</t>
+  </si>
+  <si>
+    <t>888211240</t>
+  </si>
+  <si>
+    <t>888211241</t>
+  </si>
+  <si>
+    <t>888211242</t>
+  </si>
+  <si>
+    <t>888211244</t>
+  </si>
+  <si>
+    <t>888211248</t>
+  </si>
+  <si>
+    <t>888211252</t>
+  </si>
+  <si>
+    <t>888211257</t>
+  </si>
+  <si>
+    <t>888211265</t>
+  </si>
+  <si>
+    <t>888211274</t>
+  </si>
+  <si>
+    <t>888211281</t>
+  </si>
+  <si>
+    <t>888211282</t>
+  </si>
+  <si>
+    <t>888211286</t>
+  </si>
+  <si>
+    <t>888211288</t>
+  </si>
+  <si>
+    <t>888211293</t>
+  </si>
+  <si>
+    <t>888211295</t>
+  </si>
+  <si>
+    <t>888211301</t>
+  </si>
+  <si>
+    <t>888211302</t>
   </si>
 </sst>
 </file>
@@ -1482,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C346"/>
+  <dimension ref="A1:C362"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -5194,6 +5242,134 @@
         <v>3</v>
       </c>
     </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B353" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAD255D-A2C8-4938-BD50-6D2B8D74D41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BB5D45-F5BE-4326-855F-3E3990B57875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="232">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,1087 +45,685 @@
     <t>.</t>
   </si>
   <si>
-    <t>131284175</t>
-  </si>
-  <si>
-    <t>131408286</t>
-  </si>
-  <si>
-    <t>131753794</t>
-  </si>
-  <si>
-    <t>131956479</t>
-  </si>
-  <si>
-    <t>132021163</t>
-  </si>
-  <si>
-    <t>132434165</t>
-  </si>
-  <si>
-    <t>132501500</t>
-  </si>
-  <si>
-    <t>132658943</t>
-  </si>
-  <si>
-    <t>132715315</t>
-  </si>
-  <si>
-    <t>132735152</t>
-  </si>
-  <si>
-    <t>132953279</t>
-  </si>
-  <si>
-    <t>133514131</t>
-  </si>
-  <si>
-    <t>133748728</t>
-  </si>
-  <si>
-    <t>133847633</t>
-  </si>
-  <si>
-    <t>133861394</t>
-  </si>
-  <si>
-    <t>133976168</t>
-  </si>
-  <si>
-    <t>134037153</t>
-  </si>
-  <si>
-    <t>134113266</t>
-  </si>
-  <si>
-    <t>134180685</t>
-  </si>
-  <si>
-    <t>134277001</t>
-  </si>
-  <si>
-    <t>134277020</t>
-  </si>
-  <si>
-    <t>134277590</t>
-  </si>
-  <si>
-    <t>134621713</t>
-  </si>
-  <si>
-    <t>134656648</t>
-  </si>
-  <si>
-    <t>134727273</t>
-  </si>
-  <si>
-    <t>134771917</t>
-  </si>
-  <si>
-    <t>134783255</t>
-  </si>
-  <si>
-    <t>134796717</t>
-  </si>
-  <si>
-    <t>134796758</t>
-  </si>
-  <si>
-    <t>134805196</t>
-  </si>
-  <si>
-    <t>134812043</t>
-  </si>
-  <si>
-    <t>134865572</t>
-  </si>
-  <si>
-    <t>134869393</t>
-  </si>
-  <si>
-    <t>134877354</t>
-  </si>
-  <si>
-    <t>134877971</t>
-  </si>
-  <si>
-    <t>134880497</t>
-  </si>
-  <si>
-    <t>134900016</t>
-  </si>
-  <si>
-    <t>134901814</t>
-  </si>
-  <si>
-    <t>134901892</t>
-  </si>
-  <si>
-    <t>134901998</t>
-  </si>
-  <si>
-    <t>134902156</t>
-  </si>
-  <si>
-    <t>134902185</t>
-  </si>
-  <si>
-    <t>134902243</t>
-  </si>
-  <si>
-    <t>134902278</t>
-  </si>
-  <si>
-    <t>134902360</t>
-  </si>
-  <si>
-    <t>134902457</t>
-  </si>
-  <si>
-    <t>134902485</t>
-  </si>
-  <si>
-    <t>134902510</t>
-  </si>
-  <si>
-    <t>134902693</t>
-  </si>
-  <si>
-    <t>134902788</t>
-  </si>
-  <si>
-    <t>134902853</t>
-  </si>
-  <si>
-    <t>134902950</t>
-  </si>
-  <si>
-    <t>134902976</t>
-  </si>
-  <si>
-    <t>134903025</t>
-  </si>
-  <si>
-    <t>134903049</t>
-  </si>
-  <si>
-    <t>134903113</t>
-  </si>
-  <si>
-    <t>134903118</t>
-  </si>
-  <si>
-    <t>134903140</t>
-  </si>
-  <si>
-    <t>134903220</t>
-  </si>
-  <si>
-    <t>134903347</t>
-  </si>
-  <si>
-    <t>134903445</t>
-  </si>
-  <si>
-    <t>134903462</t>
-  </si>
-  <si>
-    <t>134903467</t>
-  </si>
-  <si>
-    <t>134903583</t>
-  </si>
-  <si>
-    <t>134903593</t>
-  </si>
-  <si>
-    <t>134903603</t>
-  </si>
-  <si>
-    <t>134903612</t>
-  </si>
-  <si>
-    <t>134903998</t>
-  </si>
-  <si>
-    <t>134904056</t>
-  </si>
-  <si>
-    <t>134904151</t>
-  </si>
-  <si>
-    <t>134904190</t>
-  </si>
-  <si>
-    <t>134904298</t>
-  </si>
-  <si>
-    <t>134904340</t>
-  </si>
-  <si>
-    <t>134904482</t>
-  </si>
-  <si>
-    <t>134904731</t>
-  </si>
-  <si>
-    <t>134904755</t>
-  </si>
-  <si>
-    <t>134904760</t>
-  </si>
-  <si>
-    <t>134904954</t>
-  </si>
-  <si>
-    <t>134905061</t>
-  </si>
-  <si>
-    <t>134905299</t>
-  </si>
-  <si>
-    <t>134905312</t>
-  </si>
-  <si>
-    <t>134905372</t>
-  </si>
-  <si>
-    <t>134905393</t>
-  </si>
-  <si>
-    <t>134905423</t>
-  </si>
-  <si>
-    <t>134905438</t>
-  </si>
-  <si>
-    <t>134905476</t>
-  </si>
-  <si>
-    <t>134905489</t>
-  </si>
-  <si>
-    <t>134905559</t>
-  </si>
-  <si>
-    <t>134905572</t>
-  </si>
-  <si>
-    <t>134905588</t>
-  </si>
-  <si>
-    <t>134905630</t>
-  </si>
-  <si>
-    <t>134905633</t>
-  </si>
-  <si>
-    <t>134905638</t>
-  </si>
-  <si>
-    <t>134905647</t>
-  </si>
-  <si>
-    <t>134905675</t>
-  </si>
-  <si>
-    <t>134905742</t>
-  </si>
-  <si>
-    <t>134905772</t>
-  </si>
-  <si>
-    <t>134905846</t>
-  </si>
-  <si>
-    <t>134906043</t>
-  </si>
-  <si>
-    <t>134906100</t>
-  </si>
-  <si>
-    <t>134906147</t>
-  </si>
-  <si>
-    <t>134906171</t>
-  </si>
-  <si>
-    <t>134906331</t>
-  </si>
-  <si>
-    <t>134906345</t>
-  </si>
-  <si>
-    <t>134906371</t>
-  </si>
-  <si>
-    <t>134906501</t>
-  </si>
-  <si>
-    <t>134906552</t>
-  </si>
-  <si>
-    <t>134906562</t>
-  </si>
-  <si>
-    <t>134906597</t>
-  </si>
-  <si>
-    <t>134906704</t>
-  </si>
-  <si>
-    <t>134906717</t>
-  </si>
-  <si>
-    <t>134906756</t>
-  </si>
-  <si>
-    <t>134906796</t>
-  </si>
-  <si>
-    <t>134906816</t>
-  </si>
-  <si>
-    <t>134906832</t>
-  </si>
-  <si>
-    <t>134906886</t>
-  </si>
-  <si>
-    <t>134906900</t>
-  </si>
-  <si>
-    <t>134906919</t>
-  </si>
-  <si>
-    <t>134906956</t>
-  </si>
-  <si>
-    <t>134907053</t>
-  </si>
-  <si>
-    <t>134907249</t>
-  </si>
-  <si>
-    <t>134907277</t>
-  </si>
-  <si>
-    <t>134907335</t>
-  </si>
-  <si>
-    <t>134907481</t>
-  </si>
-  <si>
-    <t>134907507</t>
-  </si>
-  <si>
-    <t>134907611</t>
-  </si>
-  <si>
-    <t>134907628</t>
-  </si>
-  <si>
-    <t>134907653</t>
-  </si>
-  <si>
-    <t>134907745</t>
-  </si>
-  <si>
-    <t>134907946</t>
-  </si>
-  <si>
-    <t>134907987</t>
-  </si>
-  <si>
-    <t>134908001</t>
-  </si>
-  <si>
-    <t>134908049</t>
-  </si>
-  <si>
-    <t>134908104</t>
-  </si>
-  <si>
-    <t>134908258</t>
-  </si>
-  <si>
-    <t>134908352</t>
-  </si>
-  <si>
-    <t>134908458</t>
-  </si>
-  <si>
-    <t>134908911</t>
-  </si>
-  <si>
-    <t>134908942</t>
-  </si>
-  <si>
-    <t>134909136</t>
-  </si>
-  <si>
-    <t>134909157</t>
-  </si>
-  <si>
-    <t>134909202</t>
-  </si>
-  <si>
-    <t>134909302</t>
-  </si>
-  <si>
-    <t>134909317</t>
-  </si>
-  <si>
-    <t>134909384</t>
-  </si>
-  <si>
-    <t>134909473</t>
-  </si>
-  <si>
-    <t>134909477</t>
-  </si>
-  <si>
-    <t>134909578</t>
-  </si>
-  <si>
-    <t>134909614</t>
-  </si>
-  <si>
-    <t>134909656</t>
-  </si>
-  <si>
-    <t>134909763</t>
-  </si>
-  <si>
-    <t>134909962</t>
-  </si>
-  <si>
-    <t>134910169</t>
-  </si>
-  <si>
-    <t>134910372</t>
-  </si>
-  <si>
-    <t>134910470</t>
-  </si>
-  <si>
-    <t>134910695</t>
-  </si>
-  <si>
-    <t>134910791</t>
-  </si>
-  <si>
-    <t>134910881</t>
-  </si>
-  <si>
-    <t>134910918</t>
-  </si>
-  <si>
-    <t>134910994</t>
-  </si>
-  <si>
-    <t>134911047</t>
-  </si>
-  <si>
-    <t>134911353</t>
-  </si>
-  <si>
-    <t>134911409</t>
-  </si>
-  <si>
-    <t>134911430</t>
-  </si>
-  <si>
-    <t>134911769</t>
-  </si>
-  <si>
-    <t>134911774</t>
-  </si>
-  <si>
-    <t>134911891</t>
-  </si>
-  <si>
-    <t>134912087</t>
-  </si>
-  <si>
-    <t>134912177</t>
-  </si>
-  <si>
-    <t>134912293</t>
-  </si>
-  <si>
-    <t>134912365</t>
-  </si>
-  <si>
-    <t>134912566</t>
-  </si>
-  <si>
-    <t>134912579</t>
-  </si>
-  <si>
-    <t>134912605</t>
-  </si>
-  <si>
-    <t>134912620</t>
-  </si>
-  <si>
-    <t>134912722</t>
-  </si>
-  <si>
-    <t>134912736</t>
-  </si>
-  <si>
-    <t>134912745</t>
-  </si>
-  <si>
-    <t>134912774</t>
-  </si>
-  <si>
-    <t>134912876</t>
-  </si>
-  <si>
-    <t>134912896</t>
-  </si>
-  <si>
-    <t>134913059</t>
-  </si>
-  <si>
-    <t>134913122</t>
-  </si>
-  <si>
-    <t>134913129</t>
-  </si>
-  <si>
-    <t>134913206</t>
-  </si>
-  <si>
-    <t>134913335</t>
-  </si>
-  <si>
-    <t>134913462</t>
-  </si>
-  <si>
-    <t>134913652</t>
-  </si>
-  <si>
-    <t>134913687</t>
-  </si>
-  <si>
-    <t>134913716</t>
-  </si>
-  <si>
-    <t>134913774</t>
-  </si>
-  <si>
-    <t>134913869</t>
-  </si>
-  <si>
-    <t>134913886</t>
-  </si>
-  <si>
-    <t>134913917</t>
-  </si>
-  <si>
-    <t>134913979</t>
-  </si>
-  <si>
-    <t>134913994</t>
-  </si>
-  <si>
-    <t>134914000</t>
-  </si>
-  <si>
-    <t>134914151</t>
-  </si>
-  <si>
-    <t>134914276</t>
-  </si>
-  <si>
-    <t>134914312</t>
-  </si>
-  <si>
-    <t>134914361</t>
-  </si>
-  <si>
-    <t>134914458</t>
-  </si>
-  <si>
-    <t>134915154</t>
-  </si>
-  <si>
-    <t>134915157</t>
-  </si>
-  <si>
-    <t>134915294</t>
-  </si>
-  <si>
-    <t>134915317</t>
-  </si>
-  <si>
-    <t>134915543</t>
-  </si>
-  <si>
-    <t>134915713</t>
-  </si>
-  <si>
-    <t>134915716</t>
-  </si>
-  <si>
-    <t>134916041</t>
-  </si>
-  <si>
-    <t>134916240</t>
-  </si>
-  <si>
-    <t>134916270</t>
-  </si>
-  <si>
-    <t>134916275</t>
-  </si>
-  <si>
-    <t>134916369</t>
-  </si>
-  <si>
-    <t>134916400</t>
-  </si>
-  <si>
-    <t>134916448</t>
-  </si>
-  <si>
-    <t>134916533</t>
-  </si>
-  <si>
-    <t>134916565</t>
-  </si>
-  <si>
-    <t>134916639</t>
-  </si>
-  <si>
-    <t>134916872</t>
-  </si>
-  <si>
-    <t>134916879</t>
-  </si>
-  <si>
-    <t>134916934</t>
-  </si>
-  <si>
-    <t>134917018</t>
-  </si>
-  <si>
-    <t>134917066</t>
-  </si>
-  <si>
-    <t>134917169</t>
-  </si>
-  <si>
-    <t>134917239</t>
-  </si>
-  <si>
-    <t>134917278</t>
-  </si>
-  <si>
-    <t>134917464</t>
-  </si>
-  <si>
-    <t>134917480</t>
-  </si>
-  <si>
-    <t>134917631</t>
-  </si>
-  <si>
-    <t>134918293</t>
-  </si>
-  <si>
-    <t>134918396</t>
-  </si>
-  <si>
-    <t>134918636</t>
-  </si>
-  <si>
-    <t>134918789</t>
-  </si>
-  <si>
-    <t>134918915</t>
-  </si>
-  <si>
-    <t>134918987</t>
-  </si>
-  <si>
-    <t>134919065</t>
-  </si>
-  <si>
-    <t>134919090</t>
-  </si>
-  <si>
-    <t>134919102</t>
-  </si>
-  <si>
-    <t>134919115</t>
-  </si>
-  <si>
-    <t>134919126</t>
-  </si>
-  <si>
-    <t>134919237</t>
-  </si>
-  <si>
-    <t>134919239</t>
-  </si>
-  <si>
-    <t>134919282</t>
-  </si>
-  <si>
-    <t>134919463</t>
-  </si>
-  <si>
-    <t>134919584</t>
-  </si>
-  <si>
-    <t>134919632</t>
-  </si>
-  <si>
-    <t>134919634</t>
-  </si>
-  <si>
-    <t>134919641</t>
-  </si>
-  <si>
-    <t>134919679</t>
-  </si>
-  <si>
-    <t>134919688</t>
-  </si>
-  <si>
-    <t>134919753</t>
-  </si>
-  <si>
-    <t>134919916</t>
-  </si>
-  <si>
-    <t>134920089</t>
-  </si>
-  <si>
-    <t>134920258</t>
-  </si>
-  <si>
-    <t>134920264</t>
-  </si>
-  <si>
-    <t>134920303</t>
-  </si>
-  <si>
-    <t>134920365</t>
-  </si>
-  <si>
-    <t>134920368</t>
-  </si>
-  <si>
-    <t>134920394</t>
-  </si>
-  <si>
-    <t>134920398</t>
-  </si>
-  <si>
-    <t>134920499</t>
-  </si>
-  <si>
-    <t>134920519</t>
-  </si>
-  <si>
-    <t>134920521</t>
-  </si>
-  <si>
-    <t>134920578</t>
-  </si>
-  <si>
-    <t>134920644</t>
-  </si>
-  <si>
-    <t>134920726</t>
-  </si>
-  <si>
-    <t>134920731</t>
-  </si>
-  <si>
-    <t>134920867</t>
-  </si>
-  <si>
-    <t>134921055</t>
-  </si>
-  <si>
-    <t>134921068</t>
-  </si>
-  <si>
-    <t>134921112</t>
-  </si>
-  <si>
-    <t>134921127</t>
-  </si>
-  <si>
-    <t>134921129</t>
-  </si>
-  <si>
-    <t>134921162</t>
-  </si>
-  <si>
-    <t>134921169</t>
-  </si>
-  <si>
-    <t>134921221</t>
-  </si>
-  <si>
-    <t>134921247</t>
-  </si>
-  <si>
-    <t>134921274</t>
-  </si>
-  <si>
-    <t>134921303</t>
-  </si>
-  <si>
-    <t>134921339</t>
-  </si>
-  <si>
-    <t>134921417</t>
-  </si>
-  <si>
-    <t>134921461</t>
-  </si>
-  <si>
-    <t>134921533</t>
-  </si>
-  <si>
-    <t>134921552</t>
-  </si>
-  <si>
-    <t>134921592</t>
-  </si>
-  <si>
-    <t>134921747</t>
-  </si>
-  <si>
-    <t>134921773</t>
-  </si>
-  <si>
-    <t>134921819</t>
-  </si>
-  <si>
-    <t>134921931</t>
-  </si>
-  <si>
-    <t>134921993</t>
-  </si>
-  <si>
-    <t>134922008</t>
-  </si>
-  <si>
-    <t>134922084</t>
-  </si>
-  <si>
-    <t>134922104</t>
-  </si>
-  <si>
-    <t>134922154</t>
-  </si>
-  <si>
-    <t>134922156</t>
-  </si>
-  <si>
-    <t>134922263</t>
-  </si>
-  <si>
-    <t>134922275</t>
-  </si>
-  <si>
-    <t>134922305</t>
-  </si>
-  <si>
-    <t>134922307</t>
-  </si>
-  <si>
-    <t>134922375</t>
-  </si>
-  <si>
-    <t>134922500</t>
-  </si>
-  <si>
-    <t>134922546</t>
-  </si>
-  <si>
-    <t>134922587</t>
-  </si>
-  <si>
-    <t>134922611</t>
-  </si>
-  <si>
-    <t>134922684</t>
-  </si>
-  <si>
-    <t>134922729</t>
-  </si>
-  <si>
-    <t>134922803</t>
-  </si>
-  <si>
-    <t>134922806</t>
-  </si>
-  <si>
-    <t>131041334</t>
-  </si>
-  <si>
-    <t>132213819</t>
-  </si>
-  <si>
-    <t>133808226</t>
-  </si>
-  <si>
-    <t>134903342</t>
-  </si>
-  <si>
-    <t>134905162</t>
-  </si>
-  <si>
-    <t>134905485</t>
-  </si>
-  <si>
-    <t>134905673</t>
-  </si>
-  <si>
-    <t>134905737</t>
-  </si>
-  <si>
-    <t>134906352</t>
-  </si>
-  <si>
-    <t>134906911</t>
-  </si>
-  <si>
-    <t>134908492</t>
-  </si>
-  <si>
-    <t>134910663</t>
-  </si>
-  <si>
-    <t>134910894</t>
-  </si>
-  <si>
-    <t>134911304</t>
-  </si>
-  <si>
-    <t>134911461</t>
-  </si>
-  <si>
-    <t>134911602</t>
-  </si>
-  <si>
-    <t>134911791</t>
-  </si>
-  <si>
-    <t>134913477</t>
-  </si>
-  <si>
-    <t>134913783</t>
-  </si>
-  <si>
-    <t>134914208</t>
-  </si>
-  <si>
-    <t>134914286</t>
-  </si>
-  <si>
-    <t>134916039</t>
-  </si>
-  <si>
-    <t>134919190</t>
-  </si>
-  <si>
-    <t>134919202</t>
-  </si>
-  <si>
-    <t>134920378</t>
-  </si>
-  <si>
-    <t>134920460</t>
-  </si>
-  <si>
-    <t>134920465</t>
-  </si>
-  <si>
-    <t>134920650</t>
-  </si>
-  <si>
-    <t>134920960</t>
-  </si>
-  <si>
-    <t>134921683</t>
-  </si>
-  <si>
-    <t>134921708</t>
-  </si>
-  <si>
-    <t>134921771</t>
-  </si>
-  <si>
-    <t>134922129</t>
-  </si>
-  <si>
-    <t>888211222</t>
-  </si>
-  <si>
-    <t>888211228</t>
-  </si>
-  <si>
-    <t>888211240</t>
-  </si>
-  <si>
-    <t>888211241</t>
-  </si>
-  <si>
-    <t>888211242</t>
-  </si>
-  <si>
-    <t>888211244</t>
-  </si>
-  <si>
-    <t>888211248</t>
-  </si>
-  <si>
-    <t>888211252</t>
-  </si>
-  <si>
-    <t>888211257</t>
-  </si>
-  <si>
-    <t>888211265</t>
-  </si>
-  <si>
-    <t>888211274</t>
-  </si>
-  <si>
-    <t>888211281</t>
-  </si>
-  <si>
-    <t>888211282</t>
-  </si>
-  <si>
-    <t>888211286</t>
-  </si>
-  <si>
-    <t>888211288</t>
-  </si>
-  <si>
-    <t>888211293</t>
-  </si>
-  <si>
-    <t>888211295</t>
-  </si>
-  <si>
-    <t>888211301</t>
-  </si>
-  <si>
-    <t>888211302</t>
+    <t>129984928</t>
+  </si>
+  <si>
+    <t>130078389</t>
+  </si>
+  <si>
+    <t>130183665</t>
+  </si>
+  <si>
+    <t>130213605</t>
+  </si>
+  <si>
+    <t>130214350</t>
+  </si>
+  <si>
+    <t>130332509</t>
+  </si>
+  <si>
+    <t>130435545</t>
+  </si>
+  <si>
+    <t>130639447</t>
+  </si>
+  <si>
+    <t>131154405</t>
+  </si>
+  <si>
+    <t>131271166</t>
+  </si>
+  <si>
+    <t>131742625</t>
+  </si>
+  <si>
+    <t>132050213</t>
+  </si>
+  <si>
+    <t>132401957</t>
+  </si>
+  <si>
+    <t>132947517</t>
+  </si>
+  <si>
+    <t>133657185</t>
+  </si>
+  <si>
+    <t>133879863</t>
+  </si>
+  <si>
+    <t>134007436</t>
+  </si>
+  <si>
+    <t>134064980</t>
+  </si>
+  <si>
+    <t>134425955</t>
+  </si>
+  <si>
+    <t>134630851</t>
+  </si>
+  <si>
+    <t>134721243</t>
+  </si>
+  <si>
+    <t>134789921</t>
+  </si>
+  <si>
+    <t>134789936</t>
+  </si>
+  <si>
+    <t>134790024</t>
+  </si>
+  <si>
+    <t>134790169</t>
+  </si>
+  <si>
+    <t>134790764</t>
+  </si>
+  <si>
+    <t>134791002</t>
+  </si>
+  <si>
+    <t>134791029</t>
+  </si>
+  <si>
+    <t>134791057</t>
+  </si>
+  <si>
+    <t>134791094</t>
+  </si>
+  <si>
+    <t>134791511</t>
+  </si>
+  <si>
+    <t>134791512</t>
+  </si>
+  <si>
+    <t>134791581</t>
+  </si>
+  <si>
+    <t>134791629</t>
+  </si>
+  <si>
+    <t>134791736</t>
+  </si>
+  <si>
+    <t>134791874</t>
+  </si>
+  <si>
+    <t>134792105</t>
+  </si>
+  <si>
+    <t>134792208</t>
+  </si>
+  <si>
+    <t>134792539</t>
+  </si>
+  <si>
+    <t>134792562</t>
+  </si>
+  <si>
+    <t>134792569</t>
+  </si>
+  <si>
+    <t>134792729</t>
+  </si>
+  <si>
+    <t>134792758</t>
+  </si>
+  <si>
+    <t>134792759</t>
+  </si>
+  <si>
+    <t>134792802</t>
+  </si>
+  <si>
+    <t>134792809</t>
+  </si>
+  <si>
+    <t>134793176</t>
+  </si>
+  <si>
+    <t>134793285</t>
+  </si>
+  <si>
+    <t>134793721</t>
+  </si>
+  <si>
+    <t>134793724</t>
+  </si>
+  <si>
+    <t>134793735</t>
+  </si>
+  <si>
+    <t>134793823</t>
+  </si>
+  <si>
+    <t>134793859</t>
+  </si>
+  <si>
+    <t>134793907</t>
+  </si>
+  <si>
+    <t>134793958</t>
+  </si>
+  <si>
+    <t>134794359</t>
+  </si>
+  <si>
+    <t>134794393</t>
+  </si>
+  <si>
+    <t>134794532</t>
+  </si>
+  <si>
+    <t>134794641</t>
+  </si>
+  <si>
+    <t>134794808</t>
+  </si>
+  <si>
+    <t>134794962</t>
+  </si>
+  <si>
+    <t>134794980</t>
+  </si>
+  <si>
+    <t>134795082</t>
+  </si>
+  <si>
+    <t>134795105</t>
+  </si>
+  <si>
+    <t>134795159</t>
+  </si>
+  <si>
+    <t>134795169</t>
+  </si>
+  <si>
+    <t>134795309</t>
+  </si>
+  <si>
+    <t>134795315</t>
+  </si>
+  <si>
+    <t>134795538</t>
+  </si>
+  <si>
+    <t>134795622</t>
+  </si>
+  <si>
+    <t>134795630</t>
+  </si>
+  <si>
+    <t>134795650</t>
+  </si>
+  <si>
+    <t>134795685</t>
+  </si>
+  <si>
+    <t>134795689</t>
+  </si>
+  <si>
+    <t>134795892</t>
+  </si>
+  <si>
+    <t>134795918</t>
+  </si>
+  <si>
+    <t>134796282</t>
+  </si>
+  <si>
+    <t>134796301</t>
+  </si>
+  <si>
+    <t>134796411</t>
+  </si>
+  <si>
+    <t>134796435</t>
+  </si>
+  <si>
+    <t>134796470</t>
+  </si>
+  <si>
+    <t>134796502</t>
+  </si>
+  <si>
+    <t>134796547</t>
+  </si>
+  <si>
+    <t>134796567</t>
+  </si>
+  <si>
+    <t>134796722</t>
+  </si>
+  <si>
+    <t>134796748</t>
+  </si>
+  <si>
+    <t>134796789</t>
+  </si>
+  <si>
+    <t>134796805</t>
+  </si>
+  <si>
+    <t>134796844</t>
+  </si>
+  <si>
+    <t>134796877</t>
+  </si>
+  <si>
+    <t>134796947</t>
+  </si>
+  <si>
+    <t>134797027</t>
+  </si>
+  <si>
+    <t>134797087</t>
+  </si>
+  <si>
+    <t>134797219</t>
+  </si>
+  <si>
+    <t>134797327</t>
+  </si>
+  <si>
+    <t>134797375</t>
+  </si>
+  <si>
+    <t>134797968</t>
+  </si>
+  <si>
+    <t>134798049</t>
+  </si>
+  <si>
+    <t>134798453</t>
+  </si>
+  <si>
+    <t>134798555</t>
+  </si>
+  <si>
+    <t>134798681</t>
+  </si>
+  <si>
+    <t>134798705</t>
+  </si>
+  <si>
+    <t>134798789</t>
+  </si>
+  <si>
+    <t>134798820</t>
+  </si>
+  <si>
+    <t>134798989</t>
+  </si>
+  <si>
+    <t>134799019</t>
+  </si>
+  <si>
+    <t>134799109</t>
+  </si>
+  <si>
+    <t>134799200</t>
+  </si>
+  <si>
+    <t>134799585</t>
+  </si>
+  <si>
+    <t>134799875</t>
+  </si>
+  <si>
+    <t>134800221</t>
+  </si>
+  <si>
+    <t>134800234</t>
+  </si>
+  <si>
+    <t>134800262</t>
+  </si>
+  <si>
+    <t>134800331</t>
+  </si>
+  <si>
+    <t>134800443</t>
+  </si>
+  <si>
+    <t>134800461</t>
+  </si>
+  <si>
+    <t>134800551</t>
+  </si>
+  <si>
+    <t>134800611</t>
+  </si>
+  <si>
+    <t>134800663</t>
+  </si>
+  <si>
+    <t>134800714</t>
+  </si>
+  <si>
+    <t>134801013</t>
+  </si>
+  <si>
+    <t>134801047</t>
+  </si>
+  <si>
+    <t>134801227</t>
+  </si>
+  <si>
+    <t>134801264</t>
+  </si>
+  <si>
+    <t>134801730</t>
+  </si>
+  <si>
+    <t>134801756</t>
+  </si>
+  <si>
+    <t>134801769</t>
+  </si>
+  <si>
+    <t>134801863</t>
+  </si>
+  <si>
+    <t>134801914</t>
+  </si>
+  <si>
+    <t>134801941</t>
+  </si>
+  <si>
+    <t>134802135</t>
+  </si>
+  <si>
+    <t>134802251</t>
+  </si>
+  <si>
+    <t>134802262</t>
+  </si>
+  <si>
+    <t>134802315</t>
+  </si>
+  <si>
+    <t>134802468</t>
+  </si>
+  <si>
+    <t>134802549</t>
+  </si>
+  <si>
+    <t>134802553</t>
+  </si>
+  <si>
+    <t>134802595</t>
+  </si>
+  <si>
+    <t>134802628</t>
+  </si>
+  <si>
+    <t>134802663</t>
+  </si>
+  <si>
+    <t>134802724</t>
+  </si>
+  <si>
+    <t>134802839</t>
+  </si>
+  <si>
+    <t>134802850</t>
+  </si>
+  <si>
+    <t>134802874</t>
+  </si>
+  <si>
+    <t>134802999</t>
+  </si>
+  <si>
+    <t>134803097</t>
+  </si>
+  <si>
+    <t>134803127</t>
+  </si>
+  <si>
+    <t>134803226</t>
+  </si>
+  <si>
+    <t>134803312</t>
+  </si>
+  <si>
+    <t>134803387</t>
+  </si>
+  <si>
+    <t>134803447</t>
+  </si>
+  <si>
+    <t>134803542</t>
+  </si>
+  <si>
+    <t>134803609</t>
+  </si>
+  <si>
+    <t>134803714</t>
+  </si>
+  <si>
+    <t>134803930</t>
+  </si>
+  <si>
+    <t>134804139</t>
+  </si>
+  <si>
+    <t>134804148</t>
+  </si>
+  <si>
+    <t>134804220</t>
+  </si>
+  <si>
+    <t>134804347</t>
+  </si>
+  <si>
+    <t>134804408</t>
+  </si>
+  <si>
+    <t>134804532</t>
+  </si>
+  <si>
+    <t>134804548</t>
+  </si>
+  <si>
+    <t>134804615</t>
+  </si>
+  <si>
+    <t>134804721</t>
+  </si>
+  <si>
+    <t>134804791</t>
+  </si>
+  <si>
+    <t>134805081</t>
+  </si>
+  <si>
+    <t>134805171</t>
+  </si>
+  <si>
+    <t>134805270</t>
+  </si>
+  <si>
+    <t>134805383</t>
+  </si>
+  <si>
+    <t>134805403</t>
+  </si>
+  <si>
+    <t>134805533</t>
+  </si>
+  <si>
+    <t>134805570</t>
+  </si>
+  <si>
+    <t>134805587</t>
+  </si>
+  <si>
+    <t>134805663</t>
+  </si>
+  <si>
+    <t>134805806</t>
+  </si>
+  <si>
+    <t>134805834</t>
+  </si>
+  <si>
+    <t>134805878</t>
+  </si>
+  <si>
+    <t>134805941</t>
+  </si>
+  <si>
+    <t>134805952</t>
+  </si>
+  <si>
+    <t>134805986</t>
+  </si>
+  <si>
+    <t>134806005</t>
+  </si>
+  <si>
+    <t>134806089</t>
+  </si>
+  <si>
+    <t>134806116</t>
+  </si>
+  <si>
+    <t>134806125</t>
+  </si>
+  <si>
+    <t>134806200</t>
+  </si>
+  <si>
+    <t>134806212</t>
+  </si>
+  <si>
+    <t>134806233</t>
+  </si>
+  <si>
+    <t>134806314</t>
+  </si>
+  <si>
+    <t>134806356</t>
+  </si>
+  <si>
+    <t>134806416</t>
+  </si>
+  <si>
+    <t>134806417</t>
+  </si>
+  <si>
+    <t>134806424</t>
+  </si>
+  <si>
+    <t>134806434</t>
+  </si>
+  <si>
+    <t>134806446</t>
+  </si>
+  <si>
+    <t>134806520</t>
+  </si>
+  <si>
+    <t>134806540</t>
+  </si>
+  <si>
+    <t>134806560</t>
+  </si>
+  <si>
+    <t>134806648</t>
+  </si>
+  <si>
+    <t>134806735</t>
+  </si>
+  <si>
+    <t>134806747</t>
+  </si>
+  <si>
+    <t>134806786</t>
+  </si>
+  <si>
+    <t>134806792</t>
+  </si>
+  <si>
+    <t>134806802</t>
+  </si>
+  <si>
+    <t>134806897</t>
+  </si>
+  <si>
+    <t>134806920</t>
+  </si>
+  <si>
+    <t>134806963</t>
+  </si>
+  <si>
+    <t>134807006</t>
+  </si>
+  <si>
+    <t>134807040</t>
+  </si>
+  <si>
+    <t>134807042</t>
+  </si>
+  <si>
+    <t>134807125</t>
+  </si>
+  <si>
+    <t>134807184</t>
+  </si>
+  <si>
+    <t>134807269</t>
+  </si>
+  <si>
+    <t>134807407</t>
+  </si>
+  <si>
+    <t>134807680</t>
+  </si>
+  <si>
+    <t>134807723</t>
+  </si>
+  <si>
+    <t>134807775</t>
+  </si>
+  <si>
+    <t>134807780</t>
+  </si>
+  <si>
+    <t>134807897</t>
+  </si>
+  <si>
+    <t>134809327</t>
+  </si>
+  <si>
+    <t>134809333</t>
+  </si>
+  <si>
+    <t>134809770</t>
+  </si>
+  <si>
+    <t>134809794</t>
+  </si>
+  <si>
+    <t>134809877</t>
+  </si>
+  <si>
+    <t>134809896</t>
+  </si>
+  <si>
+    <t>134809942</t>
+  </si>
+  <si>
+    <t>134809995</t>
+  </si>
+  <si>
+    <t>134810135</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C362"/>
+  <dimension ref="A1:C228"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -4047,1329 +3645,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B237" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B239" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B242" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B243" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B245" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B246" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B247" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B248" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C250" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B251" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C256" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B257" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B258" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B261" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B262" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C262" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B263" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C264" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C266" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B267" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B269" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B270" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C270" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B271" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B272" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C272" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B273" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C273" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B274" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C274" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B275" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B276" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B277" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C277" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B278" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C278" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B279" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C279" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B280" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C280" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B281" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C281" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="B282" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C282" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C283" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C284" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B285" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B286" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C286" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B287" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B288" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C288" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C289" s="5"/>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C290" s="5"/>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C291" s="5"/>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B292" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C292" s="5"/>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C293" s="5"/>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C294" s="5"/>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B295" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C295" s="5"/>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B296" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C296" s="5"/>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C297" s="5"/>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B298" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C298" s="5"/>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B299" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C299" s="5"/>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B300" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C300" s="5"/>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A301" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B301" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C301" s="5"/>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B302" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C302" s="5"/>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A303" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B303" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C303" s="5"/>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A304" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B304" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C304" s="5"/>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A305" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B305" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C305" s="5"/>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A306" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B306" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C306" s="5"/>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A307" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B307" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C307" s="5"/>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A308" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B308" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C308" s="5"/>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A309" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B309" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C309" s="5"/>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A310" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B310" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C310" s="5"/>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A311" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B311" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C311" s="5"/>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A312" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B312" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C312" s="5"/>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A313" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B313" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C313" s="5"/>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A314" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B314" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C314" s="5"/>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A315" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B315" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C315" s="5"/>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A316" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B316" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C316" s="5"/>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A317" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B317" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C317" s="5"/>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A318" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B318" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C318" s="5"/>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A319" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B319" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C319" s="5"/>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A320" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B320" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C320" s="5"/>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A321" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B321" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C321" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A322" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B322" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C322" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A323" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B323" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C323" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A324" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B324" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C324" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A325" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B325" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C325" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A326" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B326" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C326" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A327" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B327" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C327" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A328" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B328" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C328" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A329" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B329" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A330" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B330" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C330" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A331" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B331" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C331" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A332" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B332" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C332" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B333" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C333" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B334" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A335" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B335" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A336" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B336" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B337" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B338" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B339" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="B340" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B341" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B342" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B343" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B344" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B345" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B346" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B347" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A348" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B348" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A349" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B349" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B350" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A351" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B351" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A352" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B352" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A353" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B353" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A354" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B354" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A355" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B355" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A356" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B356" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A357" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="B357" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A358" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B358" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A359" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B359" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A360" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B360" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A361" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B361" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A362" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B362" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4998C37C-9A8C-4C37-88AF-F17A54815A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06183F5-FEF6-41EF-9877-A2E17812AED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="188">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,637 +45,553 @@
     <t>.</t>
   </si>
   <si>
-    <t>130605647</t>
-  </si>
-  <si>
-    <t>130667659</t>
-  </si>
-  <si>
-    <t>130872171</t>
-  </si>
-  <si>
-    <t>131006461</t>
-  </si>
-  <si>
-    <t>131205242</t>
-  </si>
-  <si>
-    <t>132125974</t>
-  </si>
-  <si>
-    <t>132162965</t>
-  </si>
-  <si>
-    <t>132381832</t>
-  </si>
-  <si>
-    <t>132808027</t>
-  </si>
-  <si>
-    <t>133057689</t>
-  </si>
-  <si>
-    <t>133247770</t>
-  </si>
-  <si>
-    <t>133894326</t>
-  </si>
-  <si>
-    <t>133918353</t>
-  </si>
-  <si>
-    <t>134006050</t>
-  </si>
-  <si>
-    <t>134231743</t>
-  </si>
-  <si>
-    <t>134421276</t>
-  </si>
-  <si>
-    <t>134758809</t>
-  </si>
-  <si>
-    <t>134916321</t>
-  </si>
-  <si>
-    <t>134916354</t>
-  </si>
-  <si>
-    <t>134916522</t>
-  </si>
-  <si>
-    <t>134916559</t>
-  </si>
-  <si>
-    <t>134916662</t>
-  </si>
-  <si>
-    <t>134916675</t>
-  </si>
-  <si>
-    <t>134916788</t>
-  </si>
-  <si>
-    <t>134916937</t>
-  </si>
-  <si>
-    <t>134917157</t>
-  </si>
-  <si>
-    <t>134917232</t>
-  </si>
-  <si>
-    <t>134917784</t>
-  </si>
-  <si>
-    <t>134917811</t>
-  </si>
-  <si>
-    <t>134918026</t>
-  </si>
-  <si>
-    <t>134918096</t>
-  </si>
-  <si>
-    <t>134918184</t>
-  </si>
-  <si>
-    <t>134918241</t>
-  </si>
-  <si>
-    <t>134918464</t>
-  </si>
-  <si>
-    <t>134918482</t>
-  </si>
-  <si>
-    <t>134918495</t>
-  </si>
-  <si>
-    <t>134918522</t>
-  </si>
-  <si>
-    <t>134918740</t>
-  </si>
-  <si>
-    <t>134918832</t>
-  </si>
-  <si>
-    <t>134918939</t>
-  </si>
-  <si>
-    <t>134919254</t>
-  </si>
-  <si>
-    <t>134919324</t>
-  </si>
-  <si>
-    <t>134919453</t>
-  </si>
-  <si>
-    <t>134919532</t>
-  </si>
-  <si>
-    <t>134919705</t>
-  </si>
-  <si>
-    <t>134919824</t>
-  </si>
-  <si>
-    <t>134919889</t>
-  </si>
-  <si>
-    <t>134920031</t>
-  </si>
-  <si>
-    <t>134920101</t>
-  </si>
-  <si>
-    <t>134920140</t>
-  </si>
-  <si>
-    <t>134920220</t>
-  </si>
-  <si>
-    <t>134920448</t>
-  </si>
-  <si>
-    <t>134920515</t>
-  </si>
-  <si>
-    <t>134920579</t>
-  </si>
-  <si>
-    <t>134920627</t>
-  </si>
-  <si>
-    <t>134920962</t>
-  </si>
-  <si>
-    <t>134921033</t>
-  </si>
-  <si>
-    <t>134921062</t>
-  </si>
-  <si>
-    <t>134921101</t>
-  </si>
-  <si>
-    <t>134921149</t>
-  </si>
-  <si>
-    <t>134921174</t>
-  </si>
-  <si>
-    <t>134921281</t>
-  </si>
-  <si>
-    <t>134921403</t>
-  </si>
-  <si>
-    <t>134921472</t>
-  </si>
-  <si>
-    <t>134921541</t>
-  </si>
-  <si>
-    <t>134921545</t>
-  </si>
-  <si>
-    <t>134921548</t>
-  </si>
-  <si>
-    <t>134921601</t>
-  </si>
-  <si>
-    <t>134921763</t>
-  </si>
-  <si>
-    <t>134921815</t>
-  </si>
-  <si>
-    <t>134921882</t>
-  </si>
-  <si>
-    <t>134922033</t>
-  </si>
-  <si>
-    <t>134922108</t>
-  </si>
-  <si>
-    <t>134922257</t>
-  </si>
-  <si>
-    <t>134922519</t>
-  </si>
-  <si>
-    <t>134922761</t>
-  </si>
-  <si>
-    <t>134922772</t>
-  </si>
-  <si>
-    <t>134922971</t>
-  </si>
-  <si>
-    <t>134923009</t>
-  </si>
-  <si>
-    <t>134923048</t>
-  </si>
-  <si>
-    <t>134923310</t>
-  </si>
-  <si>
-    <t>134923609</t>
-  </si>
-  <si>
-    <t>134923753</t>
-  </si>
-  <si>
-    <t>134923854</t>
-  </si>
-  <si>
-    <t>134923879</t>
-  </si>
-  <si>
-    <t>134923906</t>
-  </si>
-  <si>
-    <t>134923963</t>
-  </si>
-  <si>
-    <t>134923973</t>
-  </si>
-  <si>
-    <t>134923980</t>
-  </si>
-  <si>
-    <t>134924055</t>
-  </si>
-  <si>
-    <t>134924183</t>
-  </si>
-  <si>
-    <t>134924207</t>
-  </si>
-  <si>
-    <t>134924247</t>
-  </si>
-  <si>
-    <t>134924276</t>
-  </si>
-  <si>
-    <t>134924298</t>
-  </si>
-  <si>
-    <t>134924360</t>
-  </si>
-  <si>
-    <t>134924430</t>
-  </si>
-  <si>
-    <t>134924645</t>
-  </si>
-  <si>
-    <t>134924847</t>
-  </si>
-  <si>
-    <t>134925263</t>
-  </si>
-  <si>
-    <t>134925375</t>
-  </si>
-  <si>
-    <t>134925588</t>
-  </si>
-  <si>
-    <t>134925718</t>
-  </si>
-  <si>
-    <t>134925739</t>
-  </si>
-  <si>
-    <t>134925825</t>
-  </si>
-  <si>
-    <t>134926028</t>
-  </si>
-  <si>
-    <t>134926092</t>
-  </si>
-  <si>
-    <t>134926433</t>
-  </si>
-  <si>
-    <t>134926532</t>
-  </si>
-  <si>
-    <t>134926589</t>
-  </si>
-  <si>
-    <t>134926661</t>
-  </si>
-  <si>
-    <t>134926675</t>
-  </si>
-  <si>
-    <t>134926993</t>
-  </si>
-  <si>
-    <t>134927435</t>
-  </si>
-  <si>
-    <t>134927538</t>
-  </si>
-  <si>
-    <t>134927555</t>
-  </si>
-  <si>
-    <t>134927709</t>
-  </si>
-  <si>
-    <t>134927788</t>
-  </si>
-  <si>
-    <t>134927932</t>
-  </si>
-  <si>
-    <t>134927976</t>
-  </si>
-  <si>
-    <t>134928117</t>
-  </si>
-  <si>
-    <t>134928254</t>
-  </si>
-  <si>
-    <t>134928422</t>
-  </si>
-  <si>
-    <t>134928562</t>
-  </si>
-  <si>
-    <t>134928682</t>
-  </si>
-  <si>
-    <t>134928683</t>
-  </si>
-  <si>
-    <t>134928778</t>
-  </si>
-  <si>
-    <t>134928828</t>
-  </si>
-  <si>
-    <t>134928881</t>
-  </si>
-  <si>
-    <t>134928890</t>
-  </si>
-  <si>
-    <t>134929059</t>
-  </si>
-  <si>
-    <t>134929185</t>
-  </si>
-  <si>
-    <t>134929317</t>
-  </si>
-  <si>
-    <t>134929467</t>
-  </si>
-  <si>
-    <t>134929553</t>
-  </si>
-  <si>
-    <t>134929663</t>
-  </si>
-  <si>
-    <t>134929881</t>
-  </si>
-  <si>
-    <t>134929884</t>
-  </si>
-  <si>
-    <t>134929913</t>
-  </si>
-  <si>
-    <t>134930138</t>
-  </si>
-  <si>
-    <t>134930164</t>
-  </si>
-  <si>
-    <t>134930252</t>
-  </si>
-  <si>
-    <t>134930289</t>
-  </si>
-  <si>
-    <t>134930352</t>
-  </si>
-  <si>
-    <t>134930401</t>
-  </si>
-  <si>
-    <t>134930565</t>
-  </si>
-  <si>
-    <t>134930566</t>
-  </si>
-  <si>
-    <t>134930605</t>
-  </si>
-  <si>
-    <t>134930664</t>
-  </si>
-  <si>
-    <t>134930830</t>
-  </si>
-  <si>
-    <t>134931067</t>
-  </si>
-  <si>
-    <t>134931084</t>
-  </si>
-  <si>
-    <t>134931352</t>
-  </si>
-  <si>
-    <t>134931374</t>
-  </si>
-  <si>
-    <t>134931481</t>
-  </si>
-  <si>
-    <t>134931516</t>
-  </si>
-  <si>
-    <t>134931545</t>
-  </si>
-  <si>
-    <t>134931566</t>
-  </si>
-  <si>
-    <t>134931618</t>
-  </si>
-  <si>
-    <t>134931692</t>
-  </si>
-  <si>
-    <t>134931693</t>
-  </si>
-  <si>
-    <t>134931717</t>
-  </si>
-  <si>
-    <t>134931852</t>
-  </si>
-  <si>
-    <t>134932114</t>
-  </si>
-  <si>
-    <t>134932121</t>
-  </si>
-  <si>
-    <t>134932175</t>
-  </si>
-  <si>
-    <t>134932323</t>
-  </si>
-  <si>
-    <t>134932419</t>
-  </si>
-  <si>
-    <t>134932426</t>
-  </si>
-  <si>
-    <t>134932603</t>
-  </si>
-  <si>
-    <t>134932688</t>
-  </si>
-  <si>
-    <t>134932851</t>
-  </si>
-  <si>
-    <t>134932943</t>
-  </si>
-  <si>
-    <t>134932982</t>
-  </si>
-  <si>
-    <t>134933174</t>
-  </si>
-  <si>
-    <t>134933224</t>
-  </si>
-  <si>
-    <t>134933434</t>
-  </si>
-  <si>
-    <t>134933521</t>
-  </si>
-  <si>
-    <t>134933562</t>
-  </si>
-  <si>
-    <t>134933614</t>
-  </si>
-  <si>
-    <t>134933707</t>
-  </si>
-  <si>
-    <t>134933778</t>
-  </si>
-  <si>
-    <t>134933883</t>
-  </si>
-  <si>
-    <t>134934017</t>
-  </si>
-  <si>
-    <t>134934035</t>
-  </si>
-  <si>
-    <t>134934045</t>
-  </si>
-  <si>
-    <t>134934047</t>
-  </si>
-  <si>
-    <t>134934074</t>
-  </si>
-  <si>
-    <t>134934199</t>
-  </si>
-  <si>
-    <t>134934316</t>
-  </si>
-  <si>
-    <t>134934327</t>
-  </si>
-  <si>
-    <t>134934457</t>
-  </si>
-  <si>
-    <t>134934627</t>
-  </si>
-  <si>
-    <t>134934718</t>
-  </si>
-  <si>
-    <t>134934900</t>
-  </si>
-  <si>
-    <t>134934983</t>
-  </si>
-  <si>
-    <t>134935095</t>
-  </si>
-  <si>
-    <t>134935117</t>
-  </si>
-  <si>
-    <t>134935313</t>
-  </si>
-  <si>
-    <t>134935440</t>
-  </si>
-  <si>
-    <t>134935501</t>
-  </si>
-  <si>
-    <t>134936077</t>
-  </si>
-  <si>
-    <t>134936282</t>
-  </si>
-  <si>
-    <t>134936329</t>
-  </si>
-  <si>
-    <t>134936519</t>
-  </si>
-  <si>
-    <t>134936619</t>
-  </si>
-  <si>
-    <t>134936688</t>
-  </si>
-  <si>
-    <t>134937244</t>
-  </si>
-  <si>
-    <t>134937261</t>
-  </si>
-  <si>
-    <t>134937348</t>
-  </si>
-  <si>
-    <t>134937390</t>
+    <t>130458580</t>
+  </si>
+  <si>
+    <t>130606062</t>
+  </si>
+  <si>
+    <t>130639447</t>
+  </si>
+  <si>
+    <t>130751818</t>
+  </si>
+  <si>
+    <t>130907521</t>
+  </si>
+  <si>
+    <t>131084153</t>
+  </si>
+  <si>
+    <t>131182054</t>
+  </si>
+  <si>
+    <t>132039837</t>
+  </si>
+  <si>
+    <t>132133169</t>
+  </si>
+  <si>
+    <t>132224032</t>
+  </si>
+  <si>
+    <t>132366928</t>
+  </si>
+  <si>
+    <t>132855608</t>
+  </si>
+  <si>
+    <t>133032061</t>
+  </si>
+  <si>
+    <t>133114731</t>
+  </si>
+  <si>
+    <t>133311618</t>
+  </si>
+  <si>
+    <t>133609393</t>
+  </si>
+  <si>
+    <t>133879863</t>
+  </si>
+  <si>
+    <t>134009253</t>
+  </si>
+  <si>
+    <t>134131374</t>
+  </si>
+  <si>
+    <t>134779406</t>
+  </si>
+  <si>
+    <t>134937511</t>
+  </si>
+  <si>
+    <t>134937649</t>
+  </si>
+  <si>
+    <t>134937730</t>
+  </si>
+  <si>
+    <t>134938262</t>
+  </si>
+  <si>
+    <t>134938266</t>
+  </si>
+  <si>
+    <t>134938310</t>
+  </si>
+  <si>
+    <t>134938343</t>
+  </si>
+  <si>
+    <t>134938361</t>
+  </si>
+  <si>
+    <t>134938656</t>
+  </si>
+  <si>
+    <t>134938761</t>
+  </si>
+  <si>
+    <t>134938790</t>
+  </si>
+  <si>
+    <t>134938972</t>
+  </si>
+  <si>
+    <t>134939185</t>
+  </si>
+  <si>
+    <t>134939244</t>
+  </si>
+  <si>
+    <t>134939434</t>
+  </si>
+  <si>
+    <t>134939465</t>
+  </si>
+  <si>
+    <t>134939522</t>
+  </si>
+  <si>
+    <t>134939568</t>
+  </si>
+  <si>
+    <t>134939635</t>
+  </si>
+  <si>
+    <t>134940015</t>
+  </si>
+  <si>
+    <t>134940290</t>
+  </si>
+  <si>
+    <t>134940443</t>
+  </si>
+  <si>
+    <t>134940726</t>
+  </si>
+  <si>
+    <t>134940742</t>
+  </si>
+  <si>
+    <t>134940898</t>
+  </si>
+  <si>
+    <t>134941206</t>
+  </si>
+  <si>
+    <t>134941242</t>
+  </si>
+  <si>
+    <t>134941395</t>
+  </si>
+  <si>
+    <t>134941585</t>
+  </si>
+  <si>
+    <t>134941628</t>
+  </si>
+  <si>
+    <t>134941753</t>
+  </si>
+  <si>
+    <t>134942055</t>
+  </si>
+  <si>
+    <t>134942068</t>
+  </si>
+  <si>
+    <t>134942070</t>
+  </si>
+  <si>
+    <t>134942143</t>
+  </si>
+  <si>
+    <t>134942283</t>
+  </si>
+  <si>
+    <t>134942683</t>
+  </si>
+  <si>
+    <t>134942751</t>
+  </si>
+  <si>
+    <t>134942775</t>
+  </si>
+  <si>
+    <t>134942842</t>
+  </si>
+  <si>
+    <t>134942951</t>
+  </si>
+  <si>
+    <t>134943303</t>
+  </si>
+  <si>
+    <t>134943309</t>
+  </si>
+  <si>
+    <t>134943426</t>
+  </si>
+  <si>
+    <t>134943613</t>
+  </si>
+  <si>
+    <t>134943641</t>
+  </si>
+  <si>
+    <t>134943855</t>
+  </si>
+  <si>
+    <t>134943960</t>
+  </si>
+  <si>
+    <t>134944226</t>
+  </si>
+  <si>
+    <t>134944364</t>
+  </si>
+  <si>
+    <t>134944369</t>
+  </si>
+  <si>
+    <t>134944454</t>
+  </si>
+  <si>
+    <t>134944462</t>
+  </si>
+  <si>
+    <t>134944836</t>
+  </si>
+  <si>
+    <t>134944847</t>
+  </si>
+  <si>
+    <t>134944880</t>
+  </si>
+  <si>
+    <t>134944905</t>
+  </si>
+  <si>
+    <t>134945003</t>
+  </si>
+  <si>
+    <t>134945033</t>
+  </si>
+  <si>
+    <t>134945339</t>
+  </si>
+  <si>
+    <t>134945358</t>
+  </si>
+  <si>
+    <t>134945395</t>
+  </si>
+  <si>
+    <t>134945397</t>
+  </si>
+  <si>
+    <t>134945443</t>
+  </si>
+  <si>
+    <t>134945577</t>
+  </si>
+  <si>
+    <t>134945584</t>
+  </si>
+  <si>
+    <t>134945751</t>
+  </si>
+  <si>
+    <t>134945886</t>
+  </si>
+  <si>
+    <t>134945923</t>
+  </si>
+  <si>
+    <t>134945982</t>
+  </si>
+  <si>
+    <t>134946308</t>
+  </si>
+  <si>
+    <t>134946448</t>
+  </si>
+  <si>
+    <t>134946470</t>
+  </si>
+  <si>
+    <t>134946725</t>
+  </si>
+  <si>
+    <t>134946960</t>
+  </si>
+  <si>
+    <t>134947094</t>
+  </si>
+  <si>
+    <t>134947266</t>
+  </si>
+  <si>
+    <t>134947281</t>
+  </si>
+  <si>
+    <t>134947614</t>
+  </si>
+  <si>
+    <t>134947691</t>
+  </si>
+  <si>
+    <t>134947799</t>
+  </si>
+  <si>
+    <t>134947919</t>
+  </si>
+  <si>
+    <t>134948045</t>
+  </si>
+  <si>
+    <t>134948081</t>
+  </si>
+  <si>
+    <t>134948229</t>
+  </si>
+  <si>
+    <t>134948236</t>
+  </si>
+  <si>
+    <t>134948628</t>
+  </si>
+  <si>
+    <t>134948682</t>
+  </si>
+  <si>
+    <t>134948739</t>
+  </si>
+  <si>
+    <t>134948836</t>
+  </si>
+  <si>
+    <t>134948875</t>
+  </si>
+  <si>
+    <t>134948944</t>
+  </si>
+  <si>
+    <t>134949097</t>
+  </si>
+  <si>
+    <t>134949238</t>
+  </si>
+  <si>
+    <t>134949258</t>
+  </si>
+  <si>
+    <t>134949625</t>
+  </si>
+  <si>
+    <t>134949656</t>
+  </si>
+  <si>
+    <t>134949878</t>
+  </si>
+  <si>
+    <t>134949924</t>
+  </si>
+  <si>
+    <t>134950132</t>
+  </si>
+  <si>
+    <t>134950249</t>
+  </si>
+  <si>
+    <t>134950270</t>
+  </si>
+  <si>
+    <t>134950369</t>
+  </si>
+  <si>
+    <t>134950384</t>
+  </si>
+  <si>
+    <t>134950459</t>
+  </si>
+  <si>
+    <t>134950467</t>
+  </si>
+  <si>
+    <t>134950527</t>
+  </si>
+  <si>
+    <t>134950542</t>
+  </si>
+  <si>
+    <t>134950818</t>
+  </si>
+  <si>
+    <t>134950987</t>
+  </si>
+  <si>
+    <t>134951353</t>
+  </si>
+  <si>
+    <t>134951911</t>
+  </si>
+  <si>
+    <t>134952023</t>
+  </si>
+  <si>
+    <t>134952077</t>
+  </si>
+  <si>
+    <t>134952275</t>
+  </si>
+  <si>
+    <t>134952291</t>
+  </si>
+  <si>
+    <t>134952292</t>
+  </si>
+  <si>
+    <t>134952350</t>
+  </si>
+  <si>
+    <t>134952418</t>
+  </si>
+  <si>
+    <t>134952419</t>
+  </si>
+  <si>
+    <t>134952441</t>
+  </si>
+  <si>
+    <t>134952449</t>
+  </si>
+  <si>
+    <t>134952503</t>
+  </si>
+  <si>
+    <t>134952563</t>
+  </si>
+  <si>
+    <t>134952625</t>
+  </si>
+  <si>
+    <t>134952745</t>
+  </si>
+  <si>
+    <t>134952750</t>
+  </si>
+  <si>
+    <t>134952988</t>
+  </si>
+  <si>
+    <t>134953032</t>
+  </si>
+  <si>
+    <t>134953282</t>
+  </si>
+  <si>
+    <t>134953321</t>
+  </si>
+  <si>
+    <t>134953369</t>
+  </si>
+  <si>
+    <t>134953465</t>
+  </si>
+  <si>
+    <t>134953597</t>
+  </si>
+  <si>
+    <t>134953705</t>
+  </si>
+  <si>
+    <t>134953974</t>
+  </si>
+  <si>
+    <t>134954130</t>
+  </si>
+  <si>
+    <t>134954268</t>
+  </si>
+  <si>
+    <t>134954329</t>
+  </si>
+  <si>
+    <t>134954415</t>
+  </si>
+  <si>
+    <t>134954446</t>
+  </si>
+  <si>
+    <t>134954571</t>
+  </si>
+  <si>
+    <t>134954624</t>
+  </si>
+  <si>
+    <t>134954960</t>
+  </si>
+  <si>
+    <t>134955100</t>
+  </si>
+  <si>
+    <t>134955167</t>
+  </si>
+  <si>
+    <t>134955193</t>
+  </si>
+  <si>
+    <t>134955274</t>
+  </si>
+  <si>
+    <t>134955422</t>
+  </si>
+  <si>
+    <t>134955470</t>
+  </si>
+  <si>
+    <t>134955496</t>
+  </si>
+  <si>
+    <t>134955698</t>
+  </si>
+  <si>
+    <t>134955703</t>
+  </si>
+  <si>
+    <t>134955749</t>
+  </si>
+  <si>
+    <t>134955816</t>
+  </si>
+  <si>
+    <t>134955951</t>
+  </si>
+  <si>
+    <t>134956671</t>
+  </si>
+  <si>
+    <t>134956716</t>
+  </si>
+  <si>
+    <t>134957090</t>
+  </si>
+  <si>
+    <t>134957228</t>
+  </si>
+  <si>
+    <t>134957241</t>
+  </si>
+  <si>
+    <t>134957281</t>
+  </si>
+  <si>
+    <t>134957303</t>
   </si>
 </sst>
 </file>
@@ -3114,312 +3030,137 @@
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A185" s="4"/>
+      <c r="B185" s="6"/>
+      <c r="C185" s="5"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A186" s="4"/>
+      <c r="B186" s="6"/>
+      <c r="C186" s="5"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A187" s="4"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="5"/>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A188" s="4"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="5"/>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A189" s="4"/>
+      <c r="B189" s="6"/>
+      <c r="C189" s="5"/>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A190" s="4"/>
+      <c r="B190" s="6"/>
+      <c r="C190" s="5"/>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A191" s="4"/>
+      <c r="B191" s="6"/>
+      <c r="C191" s="5"/>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A192" s="4"/>
+      <c r="B192" s="6"/>
+      <c r="C192" s="5"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A193" s="4"/>
+      <c r="B193" s="6"/>
+      <c r="C193" s="5"/>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A194" s="4"/>
+      <c r="B194" s="6"/>
+      <c r="C194" s="5"/>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A195" s="4"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="5"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A196" s="4"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="5"/>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A197" s="4"/>
+      <c r="B197" s="6"/>
+      <c r="C197" s="5"/>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A198" s="4"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="5"/>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A199" s="4"/>
+      <c r="B199" s="6"/>
+      <c r="C199" s="5"/>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B200" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A200" s="4"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="5"/>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A201" s="4"/>
+      <c r="B201" s="6"/>
+      <c r="C201" s="5"/>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A202" s="4"/>
+      <c r="B202" s="6"/>
+      <c r="C202" s="5"/>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A203" s="4"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="5"/>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A204" s="4"/>
+      <c r="B204" s="6"/>
+      <c r="C204" s="5"/>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A205" s="4"/>
+      <c r="B205" s="6"/>
+      <c r="C205" s="5"/>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B206" s="6"/>
+      <c r="C206" s="5"/>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B207" s="6"/>
+      <c r="C207" s="5"/>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="B208" s="6"/>
+      <c r="C208" s="5"/>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B209" s="6"/>
+      <c r="C209" s="5"/>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B210" s="6"/>
+      <c r="C210" s="5"/>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B211" s="6"/>
+      <c r="C211" s="5"/>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B212" s="6"/>
+      <c r="C212" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06183F5-FEF6-41EF-9877-A2E17812AED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26885892-149D-4DB2-B48D-C7E4376D62F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="109">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,553 +45,316 @@
     <t>.</t>
   </si>
   <si>
-    <t>130458580</t>
-  </si>
-  <si>
-    <t>130606062</t>
-  </si>
-  <si>
-    <t>130639447</t>
-  </si>
-  <si>
-    <t>130751818</t>
-  </si>
-  <si>
-    <t>130907521</t>
-  </si>
-  <si>
-    <t>131084153</t>
-  </si>
-  <si>
-    <t>131182054</t>
-  </si>
-  <si>
-    <t>132039837</t>
-  </si>
-  <si>
-    <t>132133169</t>
-  </si>
-  <si>
-    <t>132224032</t>
-  </si>
-  <si>
-    <t>132366928</t>
-  </si>
-  <si>
-    <t>132855608</t>
-  </si>
-  <si>
-    <t>133032061</t>
-  </si>
-  <si>
-    <t>133114731</t>
-  </si>
-  <si>
-    <t>133311618</t>
-  </si>
-  <si>
-    <t>133609393</t>
-  </si>
-  <si>
-    <t>133879863</t>
-  </si>
-  <si>
-    <t>134009253</t>
-  </si>
-  <si>
-    <t>134131374</t>
-  </si>
-  <si>
-    <t>134779406</t>
-  </si>
-  <si>
-    <t>134937511</t>
-  </si>
-  <si>
-    <t>134937649</t>
-  </si>
-  <si>
-    <t>134937730</t>
-  </si>
-  <si>
-    <t>134938262</t>
-  </si>
-  <si>
-    <t>134938266</t>
-  </si>
-  <si>
-    <t>134938310</t>
-  </si>
-  <si>
-    <t>134938343</t>
-  </si>
-  <si>
-    <t>134938361</t>
-  </si>
-  <si>
-    <t>134938656</t>
-  </si>
-  <si>
-    <t>134938761</t>
-  </si>
-  <si>
-    <t>134938790</t>
-  </si>
-  <si>
-    <t>134938972</t>
-  </si>
-  <si>
-    <t>134939185</t>
-  </si>
-  <si>
-    <t>134939244</t>
-  </si>
-  <si>
-    <t>134939434</t>
-  </si>
-  <si>
-    <t>134939465</t>
-  </si>
-  <si>
-    <t>134939522</t>
-  </si>
-  <si>
-    <t>134939568</t>
-  </si>
-  <si>
-    <t>134939635</t>
-  </si>
-  <si>
-    <t>134940015</t>
-  </si>
-  <si>
-    <t>134940290</t>
-  </si>
-  <si>
-    <t>134940443</t>
-  </si>
-  <si>
-    <t>134940726</t>
-  </si>
-  <si>
-    <t>134940742</t>
-  </si>
-  <si>
-    <t>134940898</t>
-  </si>
-  <si>
-    <t>134941206</t>
-  </si>
-  <si>
-    <t>134941242</t>
-  </si>
-  <si>
-    <t>134941395</t>
-  </si>
-  <si>
-    <t>134941585</t>
-  </si>
-  <si>
-    <t>134941628</t>
-  </si>
-  <si>
-    <t>134941753</t>
-  </si>
-  <si>
-    <t>134942055</t>
-  </si>
-  <si>
-    <t>134942068</t>
-  </si>
-  <si>
-    <t>134942070</t>
-  </si>
-  <si>
-    <t>134942143</t>
-  </si>
-  <si>
-    <t>134942283</t>
-  </si>
-  <si>
-    <t>134942683</t>
-  </si>
-  <si>
-    <t>134942751</t>
-  </si>
-  <si>
-    <t>134942775</t>
-  </si>
-  <si>
-    <t>134942842</t>
-  </si>
-  <si>
-    <t>134942951</t>
-  </si>
-  <si>
-    <t>134943303</t>
-  </si>
-  <si>
-    <t>134943309</t>
-  </si>
-  <si>
-    <t>134943426</t>
-  </si>
-  <si>
-    <t>134943613</t>
-  </si>
-  <si>
-    <t>134943641</t>
-  </si>
-  <si>
-    <t>134943855</t>
-  </si>
-  <si>
-    <t>134943960</t>
-  </si>
-  <si>
-    <t>134944226</t>
-  </si>
-  <si>
-    <t>134944364</t>
-  </si>
-  <si>
-    <t>134944369</t>
-  </si>
-  <si>
-    <t>134944454</t>
-  </si>
-  <si>
-    <t>134944462</t>
-  </si>
-  <si>
-    <t>134944836</t>
-  </si>
-  <si>
-    <t>134944847</t>
-  </si>
-  <si>
-    <t>134944880</t>
-  </si>
-  <si>
-    <t>134944905</t>
-  </si>
-  <si>
-    <t>134945003</t>
-  </si>
-  <si>
-    <t>134945033</t>
-  </si>
-  <si>
-    <t>134945339</t>
-  </si>
-  <si>
-    <t>134945358</t>
-  </si>
-  <si>
-    <t>134945395</t>
-  </si>
-  <si>
-    <t>134945397</t>
-  </si>
-  <si>
-    <t>134945443</t>
-  </si>
-  <si>
-    <t>134945577</t>
-  </si>
-  <si>
-    <t>134945584</t>
-  </si>
-  <si>
-    <t>134945751</t>
-  </si>
-  <si>
-    <t>134945886</t>
-  </si>
-  <si>
-    <t>134945923</t>
-  </si>
-  <si>
-    <t>134945982</t>
-  </si>
-  <si>
-    <t>134946308</t>
-  </si>
-  <si>
-    <t>134946448</t>
-  </si>
-  <si>
-    <t>134946470</t>
-  </si>
-  <si>
-    <t>134946725</t>
-  </si>
-  <si>
-    <t>134946960</t>
-  </si>
-  <si>
-    <t>134947094</t>
-  </si>
-  <si>
-    <t>134947266</t>
-  </si>
-  <si>
-    <t>134947281</t>
-  </si>
-  <si>
-    <t>134947614</t>
-  </si>
-  <si>
-    <t>134947691</t>
-  </si>
-  <si>
-    <t>134947799</t>
-  </si>
-  <si>
-    <t>134947919</t>
-  </si>
-  <si>
-    <t>134948045</t>
-  </si>
-  <si>
-    <t>134948081</t>
-  </si>
-  <si>
-    <t>134948229</t>
-  </si>
-  <si>
-    <t>134948236</t>
-  </si>
-  <si>
-    <t>134948628</t>
-  </si>
-  <si>
-    <t>134948682</t>
-  </si>
-  <si>
-    <t>134948739</t>
-  </si>
-  <si>
-    <t>134948836</t>
-  </si>
-  <si>
-    <t>134948875</t>
-  </si>
-  <si>
-    <t>134948944</t>
-  </si>
-  <si>
-    <t>134949097</t>
-  </si>
-  <si>
-    <t>134949238</t>
-  </si>
-  <si>
-    <t>134949258</t>
-  </si>
-  <si>
-    <t>134949625</t>
-  </si>
-  <si>
-    <t>134949656</t>
-  </si>
-  <si>
-    <t>134949878</t>
-  </si>
-  <si>
-    <t>134949924</t>
-  </si>
-  <si>
-    <t>134950132</t>
-  </si>
-  <si>
-    <t>134950249</t>
-  </si>
-  <si>
-    <t>134950270</t>
-  </si>
-  <si>
-    <t>134950369</t>
-  </si>
-  <si>
-    <t>134950384</t>
-  </si>
-  <si>
-    <t>134950459</t>
-  </si>
-  <si>
-    <t>134950467</t>
-  </si>
-  <si>
-    <t>134950527</t>
-  </si>
-  <si>
-    <t>134950542</t>
-  </si>
-  <si>
-    <t>134950818</t>
-  </si>
-  <si>
-    <t>134950987</t>
-  </si>
-  <si>
-    <t>134951353</t>
-  </si>
-  <si>
-    <t>134951911</t>
-  </si>
-  <si>
-    <t>134952023</t>
-  </si>
-  <si>
-    <t>134952077</t>
-  </si>
-  <si>
-    <t>134952275</t>
-  </si>
-  <si>
-    <t>134952291</t>
-  </si>
-  <si>
-    <t>134952292</t>
-  </si>
-  <si>
-    <t>134952350</t>
-  </si>
-  <si>
-    <t>134952418</t>
-  </si>
-  <si>
-    <t>134952419</t>
-  </si>
-  <si>
-    <t>134952441</t>
-  </si>
-  <si>
-    <t>134952449</t>
-  </si>
-  <si>
-    <t>134952503</t>
-  </si>
-  <si>
-    <t>134952563</t>
-  </si>
-  <si>
-    <t>134952625</t>
-  </si>
-  <si>
-    <t>134952745</t>
-  </si>
-  <si>
-    <t>134952750</t>
-  </si>
-  <si>
-    <t>134952988</t>
-  </si>
-  <si>
-    <t>134953032</t>
-  </si>
-  <si>
-    <t>134953282</t>
-  </si>
-  <si>
-    <t>134953321</t>
-  </si>
-  <si>
-    <t>134953369</t>
-  </si>
-  <si>
-    <t>134953465</t>
-  </si>
-  <si>
-    <t>134953597</t>
-  </si>
-  <si>
-    <t>134953705</t>
-  </si>
-  <si>
-    <t>134953974</t>
-  </si>
-  <si>
-    <t>134954130</t>
-  </si>
-  <si>
-    <t>134954268</t>
-  </si>
-  <si>
-    <t>134954329</t>
-  </si>
-  <si>
-    <t>134954415</t>
-  </si>
-  <si>
-    <t>134954446</t>
-  </si>
-  <si>
-    <t>134954571</t>
-  </si>
-  <si>
-    <t>134954624</t>
-  </si>
-  <si>
-    <t>134954960</t>
-  </si>
-  <si>
-    <t>134955100</t>
-  </si>
-  <si>
-    <t>134955167</t>
-  </si>
-  <si>
-    <t>134955193</t>
-  </si>
-  <si>
-    <t>134955274</t>
-  </si>
-  <si>
-    <t>134955422</t>
-  </si>
-  <si>
-    <t>134955470</t>
-  </si>
-  <si>
-    <t>134955496</t>
-  </si>
-  <si>
-    <t>134955698</t>
-  </si>
-  <si>
-    <t>134955703</t>
-  </si>
-  <si>
-    <t>134955749</t>
-  </si>
-  <si>
-    <t>134955816</t>
-  </si>
-  <si>
-    <t>134955951</t>
-  </si>
-  <si>
-    <t>134956671</t>
-  </si>
-  <si>
-    <t>134956716</t>
-  </si>
-  <si>
-    <t>134957090</t>
-  </si>
-  <si>
-    <t>134957228</t>
-  </si>
-  <si>
-    <t>134957241</t>
-  </si>
-  <si>
-    <t>134957281</t>
-  </si>
-  <si>
-    <t>134957303</t>
+    <t>130005612</t>
+  </si>
+  <si>
+    <t>130883149</t>
+  </si>
+  <si>
+    <t>132244928</t>
+  </si>
+  <si>
+    <t>133041604</t>
+  </si>
+  <si>
+    <t>133753806</t>
+  </si>
+  <si>
+    <t>133787879</t>
+  </si>
+  <si>
+    <t>134648235</t>
+  </si>
+  <si>
+    <t>134672998</t>
+  </si>
+  <si>
+    <t>134890224</t>
+  </si>
+  <si>
+    <t>134957464</t>
+  </si>
+  <si>
+    <t>134957595</t>
+  </si>
+  <si>
+    <t>134958351</t>
+  </si>
+  <si>
+    <t>134958842</t>
+  </si>
+  <si>
+    <t>134958954</t>
+  </si>
+  <si>
+    <t>134959037</t>
+  </si>
+  <si>
+    <t>134959509</t>
+  </si>
+  <si>
+    <t>134959678</t>
+  </si>
+  <si>
+    <t>134959766</t>
+  </si>
+  <si>
+    <t>134960095</t>
+  </si>
+  <si>
+    <t>134960107</t>
+  </si>
+  <si>
+    <t>134960181</t>
+  </si>
+  <si>
+    <t>134960206</t>
+  </si>
+  <si>
+    <t>134960742</t>
+  </si>
+  <si>
+    <t>134961173</t>
+  </si>
+  <si>
+    <t>134961918</t>
+  </si>
+  <si>
+    <t>134962377</t>
+  </si>
+  <si>
+    <t>134962517</t>
+  </si>
+  <si>
+    <t>134962694</t>
+  </si>
+  <si>
+    <t>134963068</t>
+  </si>
+  <si>
+    <t>134963431</t>
+  </si>
+  <si>
+    <t>134963564</t>
+  </si>
+  <si>
+    <t>134963808</t>
+  </si>
+  <si>
+    <t>134963864</t>
+  </si>
+  <si>
+    <t>134963936</t>
+  </si>
+  <si>
+    <t>134964191</t>
+  </si>
+  <si>
+    <t>134964619</t>
+  </si>
+  <si>
+    <t>134964653</t>
+  </si>
+  <si>
+    <t>134964966</t>
+  </si>
+  <si>
+    <t>134965067</t>
+  </si>
+  <si>
+    <t>134965203</t>
+  </si>
+  <si>
+    <t>134965318</t>
+  </si>
+  <si>
+    <t>134965652</t>
+  </si>
+  <si>
+    <t>134965656</t>
+  </si>
+  <si>
+    <t>134965838</t>
+  </si>
+  <si>
+    <t>134966103</t>
+  </si>
+  <si>
+    <t>134966181</t>
+  </si>
+  <si>
+    <t>134966278</t>
+  </si>
+  <si>
+    <t>134966456</t>
+  </si>
+  <si>
+    <t>134967181</t>
+  </si>
+  <si>
+    <t>134967473</t>
+  </si>
+  <si>
+    <t>134967553</t>
+  </si>
+  <si>
+    <t>134967665</t>
+  </si>
+  <si>
+    <t>134967740</t>
+  </si>
+  <si>
+    <t>134967758</t>
+  </si>
+  <si>
+    <t>134968134</t>
+  </si>
+  <si>
+    <t>134968173</t>
+  </si>
+  <si>
+    <t>134968189</t>
+  </si>
+  <si>
+    <t>134968477</t>
+  </si>
+  <si>
+    <t>134968489</t>
+  </si>
+  <si>
+    <t>134968722</t>
+  </si>
+  <si>
+    <t>134968740</t>
+  </si>
+  <si>
+    <t>134968828</t>
+  </si>
+  <si>
+    <t>134968908</t>
+  </si>
+  <si>
+    <t>134968968</t>
+  </si>
+  <si>
+    <t>134969536</t>
+  </si>
+  <si>
+    <t>134969573</t>
+  </si>
+  <si>
+    <t>134969590</t>
+  </si>
+  <si>
+    <t>134970156</t>
+  </si>
+  <si>
+    <t>134970332</t>
+  </si>
+  <si>
+    <t>134970647</t>
+  </si>
+  <si>
+    <t>134970654</t>
+  </si>
+  <si>
+    <t>134971099</t>
+  </si>
+  <si>
+    <t>134972078</t>
+  </si>
+  <si>
+    <t>134972256</t>
+  </si>
+  <si>
+    <t>134972460</t>
+  </si>
+  <si>
+    <t>134972731</t>
+  </si>
+  <si>
+    <t>134972856</t>
+  </si>
+  <si>
+    <t>134973064</t>
+  </si>
+  <si>
+    <t>134973342</t>
+  </si>
+  <si>
+    <t>134973486</t>
+  </si>
+  <si>
+    <t>134973661</t>
+  </si>
+  <si>
+    <t>134974393</t>
+  </si>
+  <si>
+    <t>134974873</t>
+  </si>
+  <si>
+    <t>134975182</t>
+  </si>
+  <si>
+    <t>134975527</t>
+  </si>
+  <si>
+    <t>134975583</t>
+  </si>
+  <si>
+    <t>134975719</t>
+  </si>
+  <si>
+    <t>134975790</t>
+  </si>
+  <si>
+    <t>134975796</t>
+  </si>
+  <si>
+    <t>134976274</t>
+  </si>
+  <si>
+    <t>134976422</t>
+  </si>
+  <si>
+    <t>134976488</t>
+  </si>
+  <si>
+    <t>134976519</t>
+  </si>
+  <si>
+    <t>134976622</t>
+  </si>
+  <si>
+    <t>134976669</t>
+  </si>
+  <si>
+    <t>134976829</t>
+  </si>
+  <si>
+    <t>134976912</t>
+  </si>
+  <si>
+    <t>134977194</t>
+  </si>
+  <si>
+    <t>134977529</t>
+  </si>
+  <si>
+    <t>134977850</t>
+  </si>
+  <si>
+    <t>134978139</t>
+  </si>
+  <si>
+    <t>134978317</t>
+  </si>
+  <si>
+    <t>134978689</t>
+  </si>
+  <si>
+    <t>134978854</t>
   </si>
 </sst>
 </file>
@@ -2161,873 +1924,399 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A106" s="4"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A107" s="4"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A108" s="4"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A109" s="4"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A110" s="4"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A111" s="4"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A112" s="4"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="5"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A113" s="4"/>
+      <c r="B113" s="6"/>
+      <c r="C113" s="5"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A114" s="4"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="5"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A115" s="4"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A116" s="4"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A117" s="4"/>
+      <c r="B117" s="6"/>
+      <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A118" s="4"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A119" s="4"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="5"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A120" s="4"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="5"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A121" s="4"/>
+      <c r="B121" s="6"/>
+      <c r="C121" s="5"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A122" s="4"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="5"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A123" s="4"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A124" s="4"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A125" s="4"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A126" s="4"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A127" s="4"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A128" s="4"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A129" s="4"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A130" s="4"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="5"/>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A131" s="4"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A132" s="4"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A133" s="4"/>
+      <c r="B133" s="6"/>
+      <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A134" s="4"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="5"/>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A135" s="4"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="5"/>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A136" s="4"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="5"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A137" s="4"/>
+      <c r="B137" s="6"/>
+      <c r="C137" s="5"/>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A138" s="4"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A139" s="4"/>
+      <c r="B139" s="6"/>
+      <c r="C139" s="5"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A140" s="4"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A141" s="4"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A142" s="4"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="5"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A143" s="4"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="5"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A144" s="4"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="5"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A145" s="4"/>
+      <c r="B145" s="6"/>
+      <c r="C145" s="5"/>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A146" s="4"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="5"/>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A147" s="4"/>
+      <c r="B147" s="6"/>
+      <c r="C147" s="5"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A148" s="4"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A149" s="4"/>
+      <c r="B149" s="6"/>
+      <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A150" s="4"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="5"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A151" s="4"/>
+      <c r="B151" s="6"/>
+      <c r="C151" s="5"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A152" s="4"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="5"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A153" s="4"/>
+      <c r="B153" s="6"/>
+      <c r="C153" s="5"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A154" s="4"/>
+      <c r="B154" s="6"/>
+      <c r="C154" s="5"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A155" s="4"/>
+      <c r="B155" s="6"/>
+      <c r="C155" s="5"/>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A156" s="4"/>
+      <c r="B156" s="6"/>
+      <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A157" s="4"/>
+      <c r="B157" s="6"/>
+      <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A158" s="4"/>
+      <c r="B158" s="6"/>
+      <c r="C158" s="5"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A159" s="4"/>
+      <c r="B159" s="6"/>
+      <c r="C159" s="5"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A160" s="4"/>
+      <c r="B160" s="6"/>
+      <c r="C160" s="5"/>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A161" s="4"/>
+      <c r="B161" s="6"/>
+      <c r="C161" s="5"/>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A162" s="4"/>
+      <c r="B162" s="6"/>
+      <c r="C162" s="5"/>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A163" s="4"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="5"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A164" s="4"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A165" s="4"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="5"/>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A166" s="4"/>
+      <c r="B166" s="6"/>
+      <c r="C166" s="5"/>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A167" s="4"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="5"/>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A168" s="4"/>
+      <c r="B168" s="6"/>
+      <c r="C168" s="5"/>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A169" s="4"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="5"/>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A170" s="4"/>
+      <c r="B170" s="6"/>
+      <c r="C170" s="5"/>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A171" s="4"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="5"/>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A172" s="4"/>
+      <c r="B172" s="6"/>
+      <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A173" s="4"/>
+      <c r="B173" s="6"/>
+      <c r="C173" s="5"/>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A174" s="4"/>
+      <c r="B174" s="6"/>
+      <c r="C174" s="5"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A175" s="4"/>
+      <c r="B175" s="6"/>
+      <c r="C175" s="5"/>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A176" s="4"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="5"/>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A177" s="4"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="5"/>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A178" s="4"/>
+      <c r="B178" s="6"/>
+      <c r="C178" s="5"/>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A179" s="4"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="5"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A180" s="4"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="5"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A181" s="4"/>
+      <c r="B181" s="6"/>
+      <c r="C181" s="5"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A182" s="4"/>
+      <c r="B182" s="6"/>
+      <c r="C182" s="5"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A183" s="4"/>
+      <c r="B183" s="6"/>
+      <c r="C183" s="5"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A184" s="4"/>
+      <c r="B184" s="6"/>
+      <c r="C184" s="5"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26885892-149D-4DB2-B48D-C7E4376D62F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078603C4-0FAF-4991-95D7-0E1DC8C468A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="167">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,316 +45,490 @@
     <t>.</t>
   </si>
   <si>
-    <t>130005612</t>
-  </si>
-  <si>
-    <t>130883149</t>
-  </si>
-  <si>
-    <t>132244928</t>
-  </si>
-  <si>
-    <t>133041604</t>
-  </si>
-  <si>
-    <t>133753806</t>
-  </si>
-  <si>
-    <t>133787879</t>
-  </si>
-  <si>
-    <t>134648235</t>
-  </si>
-  <si>
-    <t>134672998</t>
-  </si>
-  <si>
-    <t>134890224</t>
-  </si>
-  <si>
-    <t>134957464</t>
-  </si>
-  <si>
-    <t>134957595</t>
-  </si>
-  <si>
-    <t>134958351</t>
-  </si>
-  <si>
-    <t>134958842</t>
-  </si>
-  <si>
-    <t>134958954</t>
-  </si>
-  <si>
-    <t>134959037</t>
-  </si>
-  <si>
-    <t>134959509</t>
-  </si>
-  <si>
-    <t>134959678</t>
-  </si>
-  <si>
-    <t>134959766</t>
-  </si>
-  <si>
-    <t>134960095</t>
-  </si>
-  <si>
-    <t>134960107</t>
-  </si>
-  <si>
-    <t>134960181</t>
-  </si>
-  <si>
-    <t>134960206</t>
-  </si>
-  <si>
-    <t>134960742</t>
-  </si>
-  <si>
-    <t>134961173</t>
-  </si>
-  <si>
-    <t>134961918</t>
-  </si>
-  <si>
-    <t>134962377</t>
-  </si>
-  <si>
-    <t>134962517</t>
-  </si>
-  <si>
-    <t>134962694</t>
-  </si>
-  <si>
-    <t>134963068</t>
-  </si>
-  <si>
-    <t>134963431</t>
-  </si>
-  <si>
-    <t>134963564</t>
-  </si>
-  <si>
-    <t>134963808</t>
-  </si>
-  <si>
-    <t>134963864</t>
-  </si>
-  <si>
-    <t>134963936</t>
-  </si>
-  <si>
-    <t>134964191</t>
-  </si>
-  <si>
-    <t>134964619</t>
-  </si>
-  <si>
-    <t>134964653</t>
-  </si>
-  <si>
-    <t>134964966</t>
-  </si>
-  <si>
-    <t>134965067</t>
-  </si>
-  <si>
-    <t>134965203</t>
-  </si>
-  <si>
-    <t>134965318</t>
-  </si>
-  <si>
-    <t>134965652</t>
-  </si>
-  <si>
-    <t>134965656</t>
-  </si>
-  <si>
-    <t>134965838</t>
-  </si>
-  <si>
-    <t>134966103</t>
-  </si>
-  <si>
-    <t>134966181</t>
-  </si>
-  <si>
-    <t>134966278</t>
-  </si>
-  <si>
-    <t>134966456</t>
-  </si>
-  <si>
-    <t>134967181</t>
-  </si>
-  <si>
-    <t>134967473</t>
-  </si>
-  <si>
-    <t>134967553</t>
-  </si>
-  <si>
-    <t>134967665</t>
-  </si>
-  <si>
-    <t>134967740</t>
-  </si>
-  <si>
-    <t>134967758</t>
-  </si>
-  <si>
-    <t>134968134</t>
-  </si>
-  <si>
-    <t>134968173</t>
-  </si>
-  <si>
-    <t>134968189</t>
-  </si>
-  <si>
-    <t>134968477</t>
-  </si>
-  <si>
-    <t>134968489</t>
-  </si>
-  <si>
-    <t>134968722</t>
-  </si>
-  <si>
-    <t>134968740</t>
-  </si>
-  <si>
-    <t>134968828</t>
-  </si>
-  <si>
-    <t>134968908</t>
-  </si>
-  <si>
-    <t>134968968</t>
-  </si>
-  <si>
-    <t>134969536</t>
-  </si>
-  <si>
-    <t>134969573</t>
-  </si>
-  <si>
-    <t>134969590</t>
-  </si>
-  <si>
-    <t>134970156</t>
-  </si>
-  <si>
-    <t>134970332</t>
-  </si>
-  <si>
-    <t>134970647</t>
-  </si>
-  <si>
-    <t>134970654</t>
-  </si>
-  <si>
-    <t>134971099</t>
-  </si>
-  <si>
-    <t>134972078</t>
-  </si>
-  <si>
-    <t>134972256</t>
-  </si>
-  <si>
-    <t>134972460</t>
-  </si>
-  <si>
-    <t>134972731</t>
-  </si>
-  <si>
-    <t>134972856</t>
-  </si>
-  <si>
-    <t>134973064</t>
-  </si>
-  <si>
-    <t>134973342</t>
-  </si>
-  <si>
-    <t>134973486</t>
-  </si>
-  <si>
-    <t>134973661</t>
-  </si>
-  <si>
-    <t>134974393</t>
-  </si>
-  <si>
-    <t>134974873</t>
-  </si>
-  <si>
-    <t>134975182</t>
-  </si>
-  <si>
-    <t>134975527</t>
-  </si>
-  <si>
-    <t>134975583</t>
-  </si>
-  <si>
-    <t>134975719</t>
-  </si>
-  <si>
-    <t>134975790</t>
-  </si>
-  <si>
-    <t>134975796</t>
-  </si>
-  <si>
-    <t>134976274</t>
-  </si>
-  <si>
-    <t>134976422</t>
-  </si>
-  <si>
-    <t>134976488</t>
-  </si>
-  <si>
-    <t>134976519</t>
-  </si>
-  <si>
-    <t>134976622</t>
-  </si>
-  <si>
-    <t>134976669</t>
-  </si>
-  <si>
-    <t>134976829</t>
-  </si>
-  <si>
-    <t>134976912</t>
-  </si>
-  <si>
-    <t>134977194</t>
-  </si>
-  <si>
-    <t>134977529</t>
-  </si>
-  <si>
-    <t>134977850</t>
-  </si>
-  <si>
-    <t>134978139</t>
-  </si>
-  <si>
-    <t>134978317</t>
-  </si>
-  <si>
-    <t>134978689</t>
-  </si>
-  <si>
-    <t>134978854</t>
+    <t>130164482</t>
+  </si>
+  <si>
+    <t>130486982</t>
+  </si>
+  <si>
+    <t>130536068</t>
+  </si>
+  <si>
+    <t>130596590</t>
+  </si>
+  <si>
+    <t>131733639</t>
+  </si>
+  <si>
+    <t>131889970</t>
+  </si>
+  <si>
+    <t>131954898</t>
+  </si>
+  <si>
+    <t>132148049</t>
+  </si>
+  <si>
+    <t>132408501</t>
+  </si>
+  <si>
+    <t>132782170</t>
+  </si>
+  <si>
+    <t>132978229</t>
+  </si>
+  <si>
+    <t>133041472</t>
+  </si>
+  <si>
+    <t>133521558</t>
+  </si>
+  <si>
+    <t>133549787</t>
+  </si>
+  <si>
+    <t>133632105</t>
+  </si>
+  <si>
+    <t>133727711</t>
+  </si>
+  <si>
+    <t>133840795</t>
+  </si>
+  <si>
+    <t>134364483</t>
+  </si>
+  <si>
+    <t>134837279</t>
+  </si>
+  <si>
+    <t>134979468</t>
+  </si>
+  <si>
+    <t>134979857</t>
+  </si>
+  <si>
+    <t>134979891</t>
+  </si>
+  <si>
+    <t>134979995</t>
+  </si>
+  <si>
+    <t>134980215</t>
+  </si>
+  <si>
+    <t>134980376</t>
+  </si>
+  <si>
+    <t>134980800</t>
+  </si>
+  <si>
+    <t>134980809</t>
+  </si>
+  <si>
+    <t>134981819</t>
+  </si>
+  <si>
+    <t>134981937</t>
+  </si>
+  <si>
+    <t>134982059</t>
+  </si>
+  <si>
+    <t>134982241</t>
+  </si>
+  <si>
+    <t>134982249</t>
+  </si>
+  <si>
+    <t>134983519</t>
+  </si>
+  <si>
+    <t>134983669</t>
+  </si>
+  <si>
+    <t>134983887</t>
+  </si>
+  <si>
+    <t>134983963</t>
+  </si>
+  <si>
+    <t>134984579</t>
+  </si>
+  <si>
+    <t>134984582</t>
+  </si>
+  <si>
+    <t>134984751</t>
+  </si>
+  <si>
+    <t>134984825</t>
+  </si>
+  <si>
+    <t>134985202</t>
+  </si>
+  <si>
+    <t>134985258</t>
+  </si>
+  <si>
+    <t>134986277</t>
+  </si>
+  <si>
+    <t>134986413</t>
+  </si>
+  <si>
+    <t>134986857</t>
+  </si>
+  <si>
+    <t>134986893</t>
+  </si>
+  <si>
+    <t>134987288</t>
+  </si>
+  <si>
+    <t>134987327</t>
+  </si>
+  <si>
+    <t>134987637</t>
+  </si>
+  <si>
+    <t>134987912</t>
+  </si>
+  <si>
+    <t>134988141</t>
+  </si>
+  <si>
+    <t>134988152</t>
+  </si>
+  <si>
+    <t>134988300</t>
+  </si>
+  <si>
+    <t>134988518</t>
+  </si>
+  <si>
+    <t>134988741</t>
+  </si>
+  <si>
+    <t>134988848</t>
+  </si>
+  <si>
+    <t>134988928</t>
+  </si>
+  <si>
+    <t>134989200</t>
+  </si>
+  <si>
+    <t>134989653</t>
+  </si>
+  <si>
+    <t>134989842</t>
+  </si>
+  <si>
+    <t>134990069</t>
+  </si>
+  <si>
+    <t>134990563</t>
+  </si>
+  <si>
+    <t>134990625</t>
+  </si>
+  <si>
+    <t>134990659</t>
+  </si>
+  <si>
+    <t>134991107</t>
+  </si>
+  <si>
+    <t>134991366</t>
+  </si>
+  <si>
+    <t>134991474</t>
+  </si>
+  <si>
+    <t>134991560</t>
+  </si>
+  <si>
+    <t>134991743</t>
+  </si>
+  <si>
+    <t>134991905</t>
+  </si>
+  <si>
+    <t>134991958</t>
+  </si>
+  <si>
+    <t>134992171</t>
+  </si>
+  <si>
+    <t>134992206</t>
+  </si>
+  <si>
+    <t>134992384</t>
+  </si>
+  <si>
+    <t>134992453</t>
+  </si>
+  <si>
+    <t>134992807</t>
+  </si>
+  <si>
+    <t>134992813</t>
+  </si>
+  <si>
+    <t>134992908</t>
+  </si>
+  <si>
+    <t>134993122</t>
+  </si>
+  <si>
+    <t>134993474</t>
+  </si>
+  <si>
+    <t>134993892</t>
+  </si>
+  <si>
+    <t>134994013</t>
+  </si>
+  <si>
+    <t>134994103</t>
+  </si>
+  <si>
+    <t>134994271</t>
+  </si>
+  <si>
+    <t>134994662</t>
+  </si>
+  <si>
+    <t>134994808</t>
+  </si>
+  <si>
+    <t>134994832</t>
+  </si>
+  <si>
+    <t>134995134</t>
+  </si>
+  <si>
+    <t>134995372</t>
+  </si>
+  <si>
+    <t>134995515</t>
+  </si>
+  <si>
+    <t>134995573</t>
+  </si>
+  <si>
+    <t>134995666</t>
+  </si>
+  <si>
+    <t>134995697</t>
+  </si>
+  <si>
+    <t>134995698</t>
+  </si>
+  <si>
+    <t>134996056</t>
+  </si>
+  <si>
+    <t>134996070</t>
+  </si>
+  <si>
+    <t>134996240</t>
+  </si>
+  <si>
+    <t>134996458</t>
+  </si>
+  <si>
+    <t>134996519</t>
+  </si>
+  <si>
+    <t>134996617</t>
+  </si>
+  <si>
+    <t>134996651</t>
+  </si>
+  <si>
+    <t>134996771</t>
+  </si>
+  <si>
+    <t>134997088</t>
+  </si>
+  <si>
+    <t>134997167</t>
+  </si>
+  <si>
+    <t>134997240</t>
+  </si>
+  <si>
+    <t>134997276</t>
+  </si>
+  <si>
+    <t>134997622</t>
+  </si>
+  <si>
+    <t>134997809</t>
+  </si>
+  <si>
+    <t>134998036</t>
+  </si>
+  <si>
+    <t>134998109</t>
+  </si>
+  <si>
+    <t>134998150</t>
+  </si>
+  <si>
+    <t>134998211</t>
+  </si>
+  <si>
+    <t>134998390</t>
+  </si>
+  <si>
+    <t>134998477</t>
+  </si>
+  <si>
+    <t>134998500</t>
+  </si>
+  <si>
+    <t>134998653</t>
+  </si>
+  <si>
+    <t>134998677</t>
+  </si>
+  <si>
+    <t>134998753</t>
+  </si>
+  <si>
+    <t>134998935</t>
+  </si>
+  <si>
+    <t>134999069</t>
+  </si>
+  <si>
+    <t>134999537</t>
+  </si>
+  <si>
+    <t>134999685</t>
+  </si>
+  <si>
+    <t>134999951</t>
+  </si>
+  <si>
+    <t>134999992</t>
+  </si>
+  <si>
+    <t>135000119</t>
+  </si>
+  <si>
+    <t>135000205</t>
+  </si>
+  <si>
+    <t>135000243</t>
+  </si>
+  <si>
+    <t>135000389</t>
+  </si>
+  <si>
+    <t>135000540</t>
+  </si>
+  <si>
+    <t>135000748</t>
+  </si>
+  <si>
+    <t>135000942</t>
+  </si>
+  <si>
+    <t>135001105</t>
+  </si>
+  <si>
+    <t>135001421</t>
+  </si>
+  <si>
+    <t>135001696</t>
+  </si>
+  <si>
+    <t>135001869</t>
+  </si>
+  <si>
+    <t>135001897</t>
+  </si>
+  <si>
+    <t>135002033</t>
+  </si>
+  <si>
+    <t>135002041</t>
+  </si>
+  <si>
+    <t>135002058</t>
+  </si>
+  <si>
+    <t>135002096</t>
+  </si>
+  <si>
+    <t>135002098</t>
+  </si>
+  <si>
+    <t>135002109</t>
+  </si>
+  <si>
+    <t>135002173</t>
+  </si>
+  <si>
+    <t>135002203</t>
+  </si>
+  <si>
+    <t>135002248</t>
+  </si>
+  <si>
+    <t>135002488</t>
+  </si>
+  <si>
+    <t>135002627</t>
+  </si>
+  <si>
+    <t>135002653</t>
+  </si>
+  <si>
+    <t>135002686</t>
+  </si>
+  <si>
+    <t>135002695</t>
+  </si>
+  <si>
+    <t>135002720</t>
+  </si>
+  <si>
+    <t>135002722</t>
+  </si>
+  <si>
+    <t>135002789</t>
+  </si>
+  <si>
+    <t>135002913</t>
+  </si>
+  <si>
+    <t>135003161</t>
+  </si>
+  <si>
+    <t>135003206</t>
+  </si>
+  <si>
+    <t>135003269</t>
+  </si>
+  <si>
+    <t>135003593</t>
+  </si>
+  <si>
+    <t>135003853</t>
+  </si>
+  <si>
+    <t>135003924</t>
+  </si>
+  <si>
+    <t>135004356</t>
+  </si>
+  <si>
+    <t>135004817</t>
   </si>
 </sst>
 </file>
@@ -1924,503 +2098,819 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4"/>
-      <c r="B106" s="6"/>
+      <c r="A106" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
-      <c r="B107" s="6"/>
+      <c r="A107" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4"/>
-      <c r="B108" s="6"/>
+      <c r="A108" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
-      <c r="B109" s="6"/>
+      <c r="A109" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4"/>
-      <c r="B110" s="6"/>
+      <c r="A110" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
-      <c r="B111" s="6"/>
+      <c r="A111" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
-      <c r="B112" s="6"/>
+      <c r="A112" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C112" s="5"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
-      <c r="B113" s="6"/>
+      <c r="A113" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C113" s="5"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
-      <c r="B114" s="6"/>
+      <c r="A114" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C114" s="5"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="4"/>
-      <c r="B115" s="6"/>
+      <c r="A115" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="4"/>
-      <c r="B116" s="6"/>
+      <c r="A116" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
-      <c r="B117" s="6"/>
+      <c r="A117" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="4"/>
-      <c r="B118" s="6"/>
+      <c r="A118" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
-      <c r="B119" s="6"/>
+      <c r="A119" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C119" s="5"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="4"/>
-      <c r="B120" s="6"/>
+      <c r="A120" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C120" s="5"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="4"/>
-      <c r="B121" s="6"/>
+      <c r="A121" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C121" s="5"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-      <c r="B122" s="6"/>
+      <c r="A122" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C122" s="5"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="4"/>
-      <c r="B123" s="6"/>
+      <c r="A123" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="4"/>
-      <c r="B124" s="6"/>
+      <c r="A124" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="4"/>
-      <c r="B125" s="6"/>
+      <c r="A125" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="4"/>
-      <c r="B126" s="6"/>
+      <c r="A126" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="4"/>
-      <c r="B127" s="6"/>
+      <c r="A127" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="4"/>
-      <c r="B128" s="6"/>
+      <c r="A128" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="4"/>
-      <c r="B129" s="6"/>
+      <c r="A129" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="4"/>
-      <c r="B130" s="6"/>
+      <c r="A130" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C130" s="5"/>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="4"/>
-      <c r="B131" s="6"/>
+      <c r="A131" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="4"/>
-      <c r="B132" s="6"/>
+      <c r="A132" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="4"/>
-      <c r="B133" s="6"/>
+      <c r="A133" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="4"/>
-      <c r="B134" s="6"/>
+      <c r="A134" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C134" s="5"/>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="4"/>
-      <c r="B135" s="6"/>
+      <c r="A135" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C135" s="5"/>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="4"/>
-      <c r="B136" s="6"/>
+      <c r="A136" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C136" s="5"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="4"/>
-      <c r="B137" s="6"/>
+      <c r="A137" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C137" s="5"/>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="4"/>
-      <c r="B138" s="6"/>
+      <c r="A138" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="4"/>
-      <c r="B139" s="6"/>
+      <c r="A139" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C139" s="5"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="4"/>
-      <c r="B140" s="6"/>
+      <c r="A140" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="4"/>
-      <c r="B141" s="6"/>
+      <c r="A141" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="4"/>
-      <c r="B142" s="6"/>
+      <c r="A142" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C142" s="5"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="4"/>
-      <c r="B143" s="6"/>
+      <c r="A143" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C143" s="5"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="4"/>
-      <c r="B144" s="6"/>
+      <c r="A144" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C144" s="5"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="4"/>
-      <c r="B145" s="6"/>
+      <c r="A145" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C145" s="5"/>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="4"/>
-      <c r="B146" s="6"/>
+      <c r="A146" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C146" s="5"/>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="4"/>
-      <c r="B147" s="6"/>
+      <c r="A147" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C147" s="5"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="4"/>
-      <c r="B148" s="6"/>
+      <c r="A148" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="4"/>
-      <c r="B149" s="6"/>
+      <c r="A149" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="4"/>
-      <c r="B150" s="6"/>
+      <c r="A150" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C150" s="5"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="4"/>
-      <c r="B151" s="6"/>
+      <c r="A151" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C151" s="5"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="4"/>
-      <c r="B152" s="6"/>
+      <c r="A152" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C152" s="5"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="4"/>
-      <c r="B153" s="6"/>
+      <c r="A153" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C153" s="5"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="4"/>
-      <c r="B154" s="6"/>
+      <c r="A154" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C154" s="5"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="4"/>
-      <c r="B155" s="6"/>
+      <c r="A155" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C155" s="5"/>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="4"/>
-      <c r="B156" s="6"/>
+      <c r="A156" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="4"/>
-      <c r="B157" s="6"/>
+      <c r="A157" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="4"/>
-      <c r="B158" s="6"/>
+      <c r="A158" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C158" s="5"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="4"/>
-      <c r="B159" s="6"/>
+      <c r="A159" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C159" s="5"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="4"/>
-      <c r="B160" s="6"/>
+      <c r="A160" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C160" s="5"/>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="4"/>
-      <c r="B161" s="6"/>
+      <c r="A161" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C161" s="5"/>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="4"/>
-      <c r="B162" s="6"/>
+      <c r="A162" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C162" s="5"/>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="4"/>
-      <c r="B163" s="6"/>
+      <c r="A163" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C163" s="5"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4"/>
-      <c r="B164" s="6"/>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4"/>
-      <c r="B165" s="6"/>
+      <c r="B165" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C165" s="5"/>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
-      <c r="B166" s="6"/>
+      <c r="B166" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C166" s="5"/>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4"/>
-      <c r="B167" s="6"/>
+      <c r="B167" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C167" s="5"/>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4"/>
-      <c r="B168" s="6"/>
+      <c r="B168" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C168" s="5"/>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="4"/>
-      <c r="B169" s="6"/>
+      <c r="B169" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C169" s="5"/>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4"/>
-      <c r="B170" s="6"/>
+      <c r="B170" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C170" s="5"/>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4"/>
-      <c r="B171" s="6"/>
+      <c r="B171" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C171" s="5"/>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4"/>
-      <c r="B172" s="6"/>
+      <c r="B172" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="4"/>
-      <c r="B173" s="6"/>
+      <c r="B173" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C173" s="5"/>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
-      <c r="B174" s="6"/>
+      <c r="B174" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C174" s="5"/>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4"/>
-      <c r="B175" s="6"/>
+      <c r="B175" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C175" s="5"/>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4"/>
-      <c r="B176" s="6"/>
+      <c r="B176" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C176" s="5"/>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4"/>
-      <c r="B177" s="6"/>
+      <c r="B177" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C177" s="5"/>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4"/>
-      <c r="B178" s="6"/>
+      <c r="B178" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C178" s="5"/>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4"/>
-      <c r="B179" s="6"/>
+      <c r="B179" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C179" s="5"/>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
-      <c r="B180" s="6"/>
+      <c r="B180" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C180" s="5"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4"/>
-      <c r="B181" s="6"/>
+      <c r="B181" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C181" s="5"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4"/>
-      <c r="B182" s="6"/>
+      <c r="B182" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C182" s="5"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4"/>
-      <c r="B183" s="6"/>
+      <c r="B183" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C183" s="5"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4"/>
-      <c r="B184" s="6"/>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C184" s="5"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4"/>
-      <c r="B185" s="6"/>
+      <c r="B185" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C185" s="5"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4"/>
-      <c r="B186" s="6"/>
+      <c r="B186" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C186" s="5"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4"/>
-      <c r="B187" s="6"/>
+      <c r="B187" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C187" s="5"/>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4"/>
-      <c r="B188" s="6"/>
+      <c r="B188" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C188" s="5"/>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4"/>
-      <c r="B189" s="6"/>
+      <c r="B189" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C189" s="5"/>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4"/>
-      <c r="B190" s="6"/>
+      <c r="B190" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C190" s="5"/>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="4"/>
-      <c r="B191" s="6"/>
+      <c r="B191" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C191" s="5"/>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4"/>
-      <c r="B192" s="6"/>
+      <c r="B192" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C192" s="5"/>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="4"/>
-      <c r="B193" s="6"/>
+      <c r="B193" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C193" s="5"/>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
-      <c r="B194" s="6"/>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C194" s="5"/>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="4"/>
-      <c r="B195" s="6"/>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C195" s="5"/>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4"/>
-      <c r="B196" s="6"/>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C196" s="5"/>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="4"/>
-      <c r="B197" s="6"/>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C197" s="5"/>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4"/>
-      <c r="B198" s="6"/>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C198" s="5"/>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="4"/>
-      <c r="B199" s="6"/>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C199" s="5"/>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4"/>
-      <c r="B200" s="6"/>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C200" s="5"/>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
-      <c r="B201" s="6"/>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C201" s="5"/>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4"/>
-      <c r="B202" s="6"/>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C202" s="5"/>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="4"/>
-      <c r="B203" s="6"/>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C203" s="5"/>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
-      <c r="B204" s="6"/>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C204" s="5"/>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="4"/>
-      <c r="B205" s="6"/>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C205" s="5"/>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078603C4-0FAF-4991-95D7-0E1DC8C468A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFDD600-0E92-4305-B5B7-F90E757F31D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="83">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,490 +45,238 @@
     <t>.</t>
   </si>
   <si>
-    <t>130164482</t>
-  </si>
-  <si>
-    <t>130486982</t>
-  </si>
-  <si>
-    <t>130536068</t>
-  </si>
-  <si>
-    <t>130596590</t>
-  </si>
-  <si>
-    <t>131733639</t>
-  </si>
-  <si>
-    <t>131889970</t>
-  </si>
-  <si>
-    <t>131954898</t>
-  </si>
-  <si>
-    <t>132148049</t>
-  </si>
-  <si>
-    <t>132408501</t>
-  </si>
-  <si>
-    <t>132782170</t>
-  </si>
-  <si>
-    <t>132978229</t>
-  </si>
-  <si>
-    <t>133041472</t>
-  </si>
-  <si>
-    <t>133521558</t>
-  </si>
-  <si>
-    <t>133549787</t>
-  </si>
-  <si>
-    <t>133632105</t>
-  </si>
-  <si>
-    <t>133727711</t>
-  </si>
-  <si>
-    <t>133840795</t>
-  </si>
-  <si>
-    <t>134364483</t>
-  </si>
-  <si>
-    <t>134837279</t>
-  </si>
-  <si>
-    <t>134979468</t>
-  </si>
-  <si>
-    <t>134979857</t>
-  </si>
-  <si>
-    <t>134979891</t>
-  </si>
-  <si>
-    <t>134979995</t>
-  </si>
-  <si>
-    <t>134980215</t>
-  </si>
-  <si>
-    <t>134980376</t>
-  </si>
-  <si>
-    <t>134980800</t>
-  </si>
-  <si>
-    <t>134980809</t>
-  </si>
-  <si>
-    <t>134981819</t>
-  </si>
-  <si>
-    <t>134981937</t>
-  </si>
-  <si>
-    <t>134982059</t>
-  </si>
-  <si>
-    <t>134982241</t>
-  </si>
-  <si>
-    <t>134982249</t>
-  </si>
-  <si>
-    <t>134983519</t>
-  </si>
-  <si>
-    <t>134983669</t>
-  </si>
-  <si>
-    <t>134983887</t>
-  </si>
-  <si>
-    <t>134983963</t>
-  </si>
-  <si>
-    <t>134984579</t>
-  </si>
-  <si>
-    <t>134984582</t>
-  </si>
-  <si>
-    <t>134984751</t>
-  </si>
-  <si>
-    <t>134984825</t>
-  </si>
-  <si>
-    <t>134985202</t>
-  </si>
-  <si>
-    <t>134985258</t>
-  </si>
-  <si>
-    <t>134986277</t>
-  </si>
-  <si>
-    <t>134986413</t>
-  </si>
-  <si>
-    <t>134986857</t>
-  </si>
-  <si>
-    <t>134986893</t>
-  </si>
-  <si>
-    <t>134987288</t>
-  </si>
-  <si>
-    <t>134987327</t>
-  </si>
-  <si>
-    <t>134987637</t>
-  </si>
-  <si>
-    <t>134987912</t>
-  </si>
-  <si>
-    <t>134988141</t>
-  </si>
-  <si>
-    <t>134988152</t>
-  </si>
-  <si>
-    <t>134988300</t>
-  </si>
-  <si>
-    <t>134988518</t>
-  </si>
-  <si>
-    <t>134988741</t>
-  </si>
-  <si>
-    <t>134988848</t>
-  </si>
-  <si>
-    <t>134988928</t>
-  </si>
-  <si>
-    <t>134989200</t>
-  </si>
-  <si>
-    <t>134989653</t>
-  </si>
-  <si>
-    <t>134989842</t>
-  </si>
-  <si>
-    <t>134990069</t>
-  </si>
-  <si>
-    <t>134990563</t>
-  </si>
-  <si>
-    <t>134990625</t>
-  </si>
-  <si>
-    <t>134990659</t>
-  </si>
-  <si>
-    <t>134991107</t>
-  </si>
-  <si>
-    <t>134991366</t>
-  </si>
-  <si>
-    <t>134991474</t>
-  </si>
-  <si>
-    <t>134991560</t>
-  </si>
-  <si>
-    <t>134991743</t>
-  </si>
-  <si>
-    <t>134991905</t>
-  </si>
-  <si>
-    <t>134991958</t>
-  </si>
-  <si>
-    <t>134992171</t>
-  </si>
-  <si>
-    <t>134992206</t>
-  </si>
-  <si>
-    <t>134992384</t>
-  </si>
-  <si>
-    <t>134992453</t>
-  </si>
-  <si>
-    <t>134992807</t>
-  </si>
-  <si>
-    <t>134992813</t>
-  </si>
-  <si>
-    <t>134992908</t>
-  </si>
-  <si>
-    <t>134993122</t>
-  </si>
-  <si>
-    <t>134993474</t>
-  </si>
-  <si>
-    <t>134993892</t>
-  </si>
-  <si>
-    <t>134994013</t>
-  </si>
-  <si>
-    <t>134994103</t>
-  </si>
-  <si>
-    <t>134994271</t>
-  </si>
-  <si>
-    <t>134994662</t>
-  </si>
-  <si>
-    <t>134994808</t>
-  </si>
-  <si>
-    <t>134994832</t>
-  </si>
-  <si>
-    <t>134995134</t>
-  </si>
-  <si>
-    <t>134995372</t>
-  </si>
-  <si>
-    <t>134995515</t>
-  </si>
-  <si>
-    <t>134995573</t>
-  </si>
-  <si>
-    <t>134995666</t>
-  </si>
-  <si>
-    <t>134995697</t>
-  </si>
-  <si>
-    <t>134995698</t>
-  </si>
-  <si>
-    <t>134996056</t>
-  </si>
-  <si>
-    <t>134996070</t>
-  </si>
-  <si>
-    <t>134996240</t>
-  </si>
-  <si>
-    <t>134996458</t>
-  </si>
-  <si>
-    <t>134996519</t>
-  </si>
-  <si>
-    <t>134996617</t>
-  </si>
-  <si>
-    <t>134996651</t>
-  </si>
-  <si>
-    <t>134996771</t>
-  </si>
-  <si>
-    <t>134997088</t>
-  </si>
-  <si>
-    <t>134997167</t>
-  </si>
-  <si>
-    <t>134997240</t>
-  </si>
-  <si>
-    <t>134997276</t>
-  </si>
-  <si>
-    <t>134997622</t>
-  </si>
-  <si>
-    <t>134997809</t>
-  </si>
-  <si>
-    <t>134998036</t>
-  </si>
-  <si>
-    <t>134998109</t>
-  </si>
-  <si>
-    <t>134998150</t>
-  </si>
-  <si>
-    <t>134998211</t>
-  </si>
-  <si>
-    <t>134998390</t>
-  </si>
-  <si>
-    <t>134998477</t>
-  </si>
-  <si>
-    <t>134998500</t>
-  </si>
-  <si>
-    <t>134998653</t>
-  </si>
-  <si>
-    <t>134998677</t>
-  </si>
-  <si>
-    <t>134998753</t>
-  </si>
-  <si>
-    <t>134998935</t>
-  </si>
-  <si>
-    <t>134999069</t>
-  </si>
-  <si>
-    <t>134999537</t>
-  </si>
-  <si>
-    <t>134999685</t>
-  </si>
-  <si>
-    <t>134999951</t>
-  </si>
-  <si>
-    <t>134999992</t>
-  </si>
-  <si>
-    <t>135000119</t>
-  </si>
-  <si>
-    <t>135000205</t>
-  </si>
-  <si>
-    <t>135000243</t>
-  </si>
-  <si>
-    <t>135000389</t>
-  </si>
-  <si>
-    <t>135000540</t>
-  </si>
-  <si>
-    <t>135000748</t>
-  </si>
-  <si>
-    <t>135000942</t>
-  </si>
-  <si>
-    <t>135001105</t>
-  </si>
-  <si>
-    <t>135001421</t>
-  </si>
-  <si>
-    <t>135001696</t>
-  </si>
-  <si>
-    <t>135001869</t>
-  </si>
-  <si>
-    <t>135001897</t>
-  </si>
-  <si>
-    <t>135002033</t>
-  </si>
-  <si>
-    <t>135002041</t>
-  </si>
-  <si>
-    <t>135002058</t>
-  </si>
-  <si>
-    <t>135002096</t>
-  </si>
-  <si>
-    <t>135002098</t>
-  </si>
-  <si>
-    <t>135002109</t>
-  </si>
-  <si>
-    <t>135002173</t>
-  </si>
-  <si>
-    <t>135002203</t>
-  </si>
-  <si>
-    <t>135002248</t>
-  </si>
-  <si>
-    <t>135002488</t>
-  </si>
-  <si>
-    <t>135002627</t>
-  </si>
-  <si>
-    <t>135002653</t>
-  </si>
-  <si>
-    <t>135002686</t>
-  </si>
-  <si>
-    <t>135002695</t>
-  </si>
-  <si>
-    <t>135002720</t>
-  </si>
-  <si>
-    <t>135002722</t>
-  </si>
-  <si>
-    <t>135002789</t>
-  </si>
-  <si>
-    <t>135002913</t>
-  </si>
-  <si>
-    <t>135003161</t>
-  </si>
-  <si>
-    <t>135003206</t>
-  </si>
-  <si>
-    <t>135003269</t>
-  </si>
-  <si>
-    <t>135003593</t>
-  </si>
-  <si>
-    <t>135003853</t>
-  </si>
-  <si>
-    <t>135003924</t>
-  </si>
-  <si>
-    <t>135004356</t>
-  </si>
-  <si>
-    <t>135004817</t>
+    <t>130284326</t>
+  </si>
+  <si>
+    <t>130686410</t>
+  </si>
+  <si>
+    <t>132972276</t>
+  </si>
+  <si>
+    <t>133060040</t>
+  </si>
+  <si>
+    <t>133202170</t>
+  </si>
+  <si>
+    <t>133262160</t>
+  </si>
+  <si>
+    <t>134323170</t>
+  </si>
+  <si>
+    <t>134340281</t>
+  </si>
+  <si>
+    <t>135005173</t>
+  </si>
+  <si>
+    <t>135005541</t>
+  </si>
+  <si>
+    <t>135005645</t>
+  </si>
+  <si>
+    <t>135006231</t>
+  </si>
+  <si>
+    <t>135006318</t>
+  </si>
+  <si>
+    <t>135007221</t>
+  </si>
+  <si>
+    <t>135007262</t>
+  </si>
+  <si>
+    <t>135007424</t>
+  </si>
+  <si>
+    <t>135007482</t>
+  </si>
+  <si>
+    <t>135007994</t>
+  </si>
+  <si>
+    <t>135008374</t>
+  </si>
+  <si>
+    <t>135008434</t>
+  </si>
+  <si>
+    <t>135008817</t>
+  </si>
+  <si>
+    <t>135008871</t>
+  </si>
+  <si>
+    <t>135009056</t>
+  </si>
+  <si>
+    <t>135009122</t>
+  </si>
+  <si>
+    <t>135009609</t>
+  </si>
+  <si>
+    <t>135009736</t>
+  </si>
+  <si>
+    <t>135010066</t>
+  </si>
+  <si>
+    <t>135010133</t>
+  </si>
+  <si>
+    <t>135010313</t>
+  </si>
+  <si>
+    <t>135010624</t>
+  </si>
+  <si>
+    <t>135010731</t>
+  </si>
+  <si>
+    <t>135010829</t>
+  </si>
+  <si>
+    <t>135010857</t>
+  </si>
+  <si>
+    <t>135011074</t>
+  </si>
+  <si>
+    <t>135011190</t>
+  </si>
+  <si>
+    <t>135011224</t>
+  </si>
+  <si>
+    <t>135011662</t>
+  </si>
+  <si>
+    <t>135011847</t>
+  </si>
+  <si>
+    <t>135011866</t>
+  </si>
+  <si>
+    <t>135012281</t>
+  </si>
+  <si>
+    <t>135012411</t>
+  </si>
+  <si>
+    <t>135012703</t>
+  </si>
+  <si>
+    <t>135013805</t>
+  </si>
+  <si>
+    <t>135014593</t>
+  </si>
+  <si>
+    <t>135014698</t>
+  </si>
+  <si>
+    <t>135015407</t>
+  </si>
+  <si>
+    <t>135015844</t>
+  </si>
+  <si>
+    <t>135016015</t>
+  </si>
+  <si>
+    <t>135016289</t>
+  </si>
+  <si>
+    <t>135016572</t>
+  </si>
+  <si>
+    <t>135016753</t>
+  </si>
+  <si>
+    <t>135016851</t>
+  </si>
+  <si>
+    <t>135016853</t>
+  </si>
+  <si>
+    <t>135016864</t>
+  </si>
+  <si>
+    <t>135017014</t>
+  </si>
+  <si>
+    <t>135017307</t>
+  </si>
+  <si>
+    <t>135017329</t>
+  </si>
+  <si>
+    <t>135017413</t>
+  </si>
+  <si>
+    <t>135017546</t>
+  </si>
+  <si>
+    <t>135017647</t>
+  </si>
+  <si>
+    <t>135017899</t>
+  </si>
+  <si>
+    <t>135018203</t>
+  </si>
+  <si>
+    <t>135018236</t>
+  </si>
+  <si>
+    <t>135018238</t>
+  </si>
+  <si>
+    <t>135018406</t>
+  </si>
+  <si>
+    <t>135018639</t>
+  </si>
+  <si>
+    <t>135018670</t>
+  </si>
+  <si>
+    <t>135018750</t>
+  </si>
+  <si>
+    <t>135018905</t>
+  </si>
+  <si>
+    <t>135018963</t>
+  </si>
+  <si>
+    <t>135018985</t>
+  </si>
+  <si>
+    <t>135019035</t>
+  </si>
+  <si>
+    <t>135019161</t>
+  </si>
+  <si>
+    <t>135019356</t>
+  </si>
+  <si>
+    <t>135019379</t>
+  </si>
+  <si>
+    <t>135019494</t>
+  </si>
+  <si>
+    <t>135019725</t>
+  </si>
+  <si>
+    <t>135021416</t>
   </si>
 </sst>
 </file>
@@ -1812,811 +1560,423 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A80" s="4"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="5"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A81" s="4"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="5"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A82" s="4"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="5"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A83" s="4"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A84" s="4"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="5"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A85" s="4"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="5"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A86" s="4"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="5"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A87" s="4"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="5"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A88" s="4"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="5"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A89" s="4"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="5"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A90" s="4"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="5"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A91" s="4"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A92" s="4"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A93" s="4"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="5"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A94" s="4"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="5"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A95" s="4"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="5"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A96" s="4"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="5"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A97" s="4"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="5"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A98" s="4"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="5"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A99" s="4"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A100" s="4"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A101" s="4"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="5"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A102" s="4"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="5"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A103" s="4"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="5"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A104" s="4"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="5"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A105" s="4"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="5"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A106" s="4"/>
+      <c r="B106" s="6"/>
       <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A107" s="4"/>
+      <c r="B107" s="6"/>
       <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A108" s="4"/>
+      <c r="B108" s="6"/>
       <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A109" s="4"/>
+      <c r="B109" s="6"/>
       <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A110" s="4"/>
+      <c r="B110" s="6"/>
       <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A111" s="4"/>
+      <c r="B111" s="6"/>
       <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A112" s="4"/>
+      <c r="B112" s="6"/>
       <c r="C112" s="5"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A113" s="4"/>
+      <c r="B113" s="6"/>
       <c r="C113" s="5"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A114" s="4"/>
+      <c r="B114" s="6"/>
       <c r="C114" s="5"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A115" s="4"/>
+      <c r="B115" s="6"/>
       <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A116" s="4"/>
+      <c r="B116" s="6"/>
       <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A117" s="4"/>
+      <c r="B117" s="6"/>
       <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A118" s="4"/>
+      <c r="B118" s="6"/>
       <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A119" s="4"/>
+      <c r="B119" s="6"/>
       <c r="C119" s="5"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A120" s="4"/>
+      <c r="B120" s="6"/>
       <c r="C120" s="5"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A121" s="4"/>
+      <c r="B121" s="6"/>
       <c r="C121" s="5"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A122" s="4"/>
+      <c r="B122" s="6"/>
       <c r="C122" s="5"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A123" s="4"/>
+      <c r="B123" s="6"/>
       <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A124" s="4"/>
+      <c r="B124" s="6"/>
       <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A125" s="4"/>
+      <c r="B125" s="6"/>
       <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A126" s="4"/>
+      <c r="B126" s="6"/>
       <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A127" s="4"/>
+      <c r="B127" s="6"/>
       <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A128" s="4"/>
+      <c r="B128" s="6"/>
       <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A129" s="4"/>
+      <c r="B129" s="6"/>
       <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A130" s="4"/>
+      <c r="B130" s="6"/>
       <c r="C130" s="5"/>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A131" s="4"/>
+      <c r="B131" s="6"/>
       <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A132" s="4"/>
+      <c r="B132" s="6"/>
       <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A133" s="4"/>
+      <c r="B133" s="6"/>
       <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A134" s="4"/>
+      <c r="B134" s="6"/>
       <c r="C134" s="5"/>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A135" s="4"/>
+      <c r="B135" s="6"/>
       <c r="C135" s="5"/>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A136" s="4"/>
+      <c r="B136" s="6"/>
       <c r="C136" s="5"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A137" s="4"/>
+      <c r="B137" s="6"/>
       <c r="C137" s="5"/>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A138" s="4"/>
+      <c r="B138" s="6"/>
       <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A139" s="4"/>
+      <c r="B139" s="6"/>
       <c r="C139" s="5"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A140" s="4"/>
+      <c r="B140" s="6"/>
       <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A141" s="4"/>
+      <c r="B141" s="6"/>
       <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A142" s="4"/>
+      <c r="B142" s="6"/>
       <c r="C142" s="5"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A143" s="4"/>
+      <c r="B143" s="6"/>
       <c r="C143" s="5"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A144" s="4"/>
+      <c r="B144" s="6"/>
       <c r="C144" s="5"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A145" s="4"/>
+      <c r="B145" s="6"/>
       <c r="C145" s="5"/>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A146" s="4"/>
+      <c r="B146" s="6"/>
       <c r="C146" s="5"/>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A147" s="4"/>
+      <c r="B147" s="6"/>
       <c r="C147" s="5"/>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A148" s="4"/>
+      <c r="B148" s="6"/>
       <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A149" s="4"/>
+      <c r="B149" s="6"/>
       <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A150" s="4"/>
+      <c r="B150" s="6"/>
       <c r="C150" s="5"/>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A151" s="4"/>
+      <c r="B151" s="6"/>
       <c r="C151" s="5"/>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A152" s="4"/>
+      <c r="B152" s="6"/>
       <c r="C152" s="5"/>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A153" s="4"/>
+      <c r="B153" s="6"/>
       <c r="C153" s="5"/>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A154" s="4"/>
+      <c r="B154" s="6"/>
       <c r="C154" s="5"/>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A155" s="4"/>
+      <c r="B155" s="6"/>
       <c r="C155" s="5"/>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A156" s="4"/>
+      <c r="B156" s="6"/>
       <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A157" s="4"/>
+      <c r="B157" s="6"/>
       <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A158" s="4"/>
+      <c r="B158" s="6"/>
       <c r="C158" s="5"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A159" s="4"/>
+      <c r="B159" s="6"/>
       <c r="C159" s="5"/>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A160" s="4"/>
+      <c r="B160" s="6"/>
       <c r="C160" s="5"/>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A161" s="4"/>
+      <c r="B161" s="6"/>
       <c r="C161" s="5"/>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A162" s="4"/>
+      <c r="B162" s="6"/>
       <c r="C162" s="5"/>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A163" s="4"/>
+      <c r="B163" s="6"/>
       <c r="C163" s="5"/>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061DE324-412D-4ED8-AE86-B1000516732B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF458CB-4C27-42D0-BC9B-B75DF3665322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$205</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="5">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -43,294 +43,6 @@
   </si>
   <si>
     <t>.</t>
-  </si>
-  <si>
-    <t>130211129</t>
-  </si>
-  <si>
-    <t>131348321</t>
-  </si>
-  <si>
-    <t>133180321</t>
-  </si>
-  <si>
-    <t>133191720</t>
-  </si>
-  <si>
-    <t>134546985</t>
-  </si>
-  <si>
-    <t>135022315</t>
-  </si>
-  <si>
-    <t>135022601</t>
-  </si>
-  <si>
-    <t>135022658</t>
-  </si>
-  <si>
-    <t>135023724</t>
-  </si>
-  <si>
-    <t>135023984</t>
-  </si>
-  <si>
-    <t>135024376</t>
-  </si>
-  <si>
-    <t>135025037</t>
-  </si>
-  <si>
-    <t>135025461</t>
-  </si>
-  <si>
-    <t>135025576</t>
-  </si>
-  <si>
-    <t>135025692</t>
-  </si>
-  <si>
-    <t>135026023</t>
-  </si>
-  <si>
-    <t>135026153</t>
-  </si>
-  <si>
-    <t>135026180</t>
-  </si>
-  <si>
-    <t>135026677</t>
-  </si>
-  <si>
-    <t>135026899</t>
-  </si>
-  <si>
-    <t>135026915</t>
-  </si>
-  <si>
-    <t>135027109</t>
-  </si>
-  <si>
-    <t>135027322</t>
-  </si>
-  <si>
-    <t>135027358</t>
-  </si>
-  <si>
-    <t>135027802</t>
-  </si>
-  <si>
-    <t>135027924</t>
-  </si>
-  <si>
-    <t>135028220</t>
-  </si>
-  <si>
-    <t>135028334</t>
-  </si>
-  <si>
-    <t>135028377</t>
-  </si>
-  <si>
-    <t>135028379</t>
-  </si>
-  <si>
-    <t>135028797</t>
-  </si>
-  <si>
-    <t>135028866</t>
-  </si>
-  <si>
-    <t>135028993</t>
-  </si>
-  <si>
-    <t>135029320</t>
-  </si>
-  <si>
-    <t>135029445</t>
-  </si>
-  <si>
-    <t>135029534</t>
-  </si>
-  <si>
-    <t>135029679</t>
-  </si>
-  <si>
-    <t>135029682</t>
-  </si>
-  <si>
-    <t>135030079</t>
-  </si>
-  <si>
-    <t>135030358</t>
-  </si>
-  <si>
-    <t>135030404</t>
-  </si>
-  <si>
-    <t>135030558</t>
-  </si>
-  <si>
-    <t>135030641</t>
-  </si>
-  <si>
-    <t>135030715</t>
-  </si>
-  <si>
-    <t>135031617</t>
-  </si>
-  <si>
-    <t>135031797</t>
-  </si>
-  <si>
-    <t>135032151</t>
-  </si>
-  <si>
-    <t>135032162</t>
-  </si>
-  <si>
-    <t>135032446</t>
-  </si>
-  <si>
-    <t>135032469</t>
-  </si>
-  <si>
-    <t>135032818</t>
-  </si>
-  <si>
-    <t>135033227</t>
-  </si>
-  <si>
-    <t>135033277</t>
-  </si>
-  <si>
-    <t>135033469</t>
-  </si>
-  <si>
-    <t>135033496</t>
-  </si>
-  <si>
-    <t>135033610</t>
-  </si>
-  <si>
-    <t>135033721</t>
-  </si>
-  <si>
-    <t>135034015</t>
-  </si>
-  <si>
-    <t>135034230</t>
-  </si>
-  <si>
-    <t>135035158</t>
-  </si>
-  <si>
-    <t>135035164</t>
-  </si>
-  <si>
-    <t>135035305</t>
-  </si>
-  <si>
-    <t>135035753</t>
-  </si>
-  <si>
-    <t>135035878</t>
-  </si>
-  <si>
-    <t>135036007</t>
-  </si>
-  <si>
-    <t>135036374</t>
-  </si>
-  <si>
-    <t>135036427</t>
-  </si>
-  <si>
-    <t>135036833</t>
-  </si>
-  <si>
-    <t>135036993</t>
-  </si>
-  <si>
-    <t>135037003</t>
-  </si>
-  <si>
-    <t>135037040</t>
-  </si>
-  <si>
-    <t>135037356</t>
-  </si>
-  <si>
-    <t>135037466</t>
-  </si>
-  <si>
-    <t>135037771</t>
-  </si>
-  <si>
-    <t>135038018</t>
-  </si>
-  <si>
-    <t>135038318</t>
-  </si>
-  <si>
-    <t>135038536</t>
-  </si>
-  <si>
-    <t>135038772</t>
-  </si>
-  <si>
-    <t>135038787</t>
-  </si>
-  <si>
-    <t>135039090</t>
-  </si>
-  <si>
-    <t>135039115</t>
-  </si>
-  <si>
-    <t>135039196</t>
-  </si>
-  <si>
-    <t>135039432</t>
-  </si>
-  <si>
-    <t>135039789</t>
-  </si>
-  <si>
-    <t>135039958</t>
-  </si>
-  <si>
-    <t>135040017</t>
-  </si>
-  <si>
-    <t>135040272</t>
-  </si>
-  <si>
-    <t>135040286</t>
-  </si>
-  <si>
-    <t>135040379</t>
-  </si>
-  <si>
-    <t>135040424</t>
-  </si>
-  <si>
-    <t>135040614</t>
-  </si>
-  <si>
-    <t>135040940</t>
-  </si>
-  <si>
-    <t>135040953</t>
-  </si>
-  <si>
-    <t>135041159</t>
-  </si>
-  <si>
-    <t>135041417</t>
-  </si>
-  <si>
-    <t>135041841</t>
   </si>
 </sst>
 </file>
@@ -735,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C333"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -756,9 +468,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
@@ -767,9 +477,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
@@ -778,9 +486,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A4" s="4"/>
       <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
@@ -789,9 +495,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
@@ -800,9 +504,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="4"/>
       <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
@@ -811,9 +513,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A7" s="4"/>
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
@@ -822,9 +522,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="A8" s="4"/>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
@@ -833,9 +531,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="6" t="s">
         <v>3</v>
       </c>
@@ -844,9 +540,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
@@ -855,9 +549,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A11" s="4"/>
       <c r="B11" s="6" t="s">
         <v>3</v>
       </c>
@@ -866,9 +558,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A12" s="4"/>
       <c r="B12" s="6" t="s">
         <v>3</v>
       </c>
@@ -877,9 +567,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
+      <c r="A13" s="4"/>
       <c r="B13" s="6" t="s">
         <v>3</v>
       </c>
@@ -888,9 +576,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="A14" s="4"/>
       <c r="B14" s="6" t="s">
         <v>3</v>
       </c>
@@ -899,9 +585,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A15" s="4"/>
       <c r="B15" s="6" t="s">
         <v>3</v>
       </c>
@@ -910,9 +594,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="A16" s="4"/>
       <c r="B16" s="6" t="s">
         <v>3</v>
       </c>
@@ -921,9 +603,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A17" s="4"/>
       <c r="B17" s="6" t="s">
         <v>3</v>
       </c>
@@ -932,9 +612,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="A18" s="4"/>
       <c r="B18" s="6" t="s">
         <v>3</v>
       </c>
@@ -943,9 +621,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="A19" s="4"/>
       <c r="B19" s="6" t="s">
         <v>3</v>
       </c>
@@ -954,9 +630,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="A20" s="4"/>
       <c r="B20" s="6" t="s">
         <v>3</v>
       </c>
@@ -965,9 +639,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="A21" s="4"/>
       <c r="B21" s="6" t="s">
         <v>3</v>
       </c>
@@ -976,9 +648,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="A22" s="4"/>
       <c r="B22" s="6" t="s">
         <v>3</v>
       </c>
@@ -987,9 +657,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A23" s="4"/>
       <c r="B23" s="6" t="s">
         <v>3</v>
       </c>
@@ -998,9 +666,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A24" s="4"/>
       <c r="B24" s="6" t="s">
         <v>3</v>
       </c>
@@ -1009,9 +675,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="A25" s="4"/>
       <c r="B25" s="6" t="s">
         <v>3</v>
       </c>
@@ -1020,9 +684,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="A26" s="4"/>
       <c r="B26" s="6" t="s">
         <v>3</v>
       </c>
@@ -1031,9 +693,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A27" s="4"/>
       <c r="B27" s="6" t="s">
         <v>3</v>
       </c>
@@ -1042,9 +702,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="A28" s="4"/>
       <c r="B28" s="6" t="s">
         <v>3</v>
       </c>
@@ -1053,9 +711,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="A29" s="4"/>
       <c r="B29" s="6" t="s">
         <v>3</v>
       </c>
@@ -1064,9 +720,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="A30" s="4"/>
       <c r="B30" s="6" t="s">
         <v>3</v>
       </c>
@@ -1075,9 +729,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>34</v>
-      </c>
+      <c r="A31" s="4"/>
       <c r="B31" s="6" t="s">
         <v>3</v>
       </c>
@@ -1086,9 +738,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="A32" s="4"/>
       <c r="B32" s="6" t="s">
         <v>3</v>
       </c>
@@ -1097,9 +747,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="A33" s="4"/>
       <c r="B33" s="6" t="s">
         <v>3</v>
       </c>
@@ -1108,9 +756,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="A34" s="4"/>
       <c r="B34" s="6" t="s">
         <v>3</v>
       </c>
@@ -1119,9 +765,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="A35" s="4"/>
       <c r="B35" s="6" t="s">
         <v>3</v>
       </c>
@@ -1130,9 +774,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="A36" s="4"/>
       <c r="B36" s="6" t="s">
         <v>3</v>
       </c>
@@ -1141,9 +783,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="A37" s="4"/>
       <c r="B37" s="6" t="s">
         <v>3</v>
       </c>
@@ -1152,9 +792,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="A38" s="4"/>
       <c r="B38" s="6" t="s">
         <v>3</v>
       </c>
@@ -1163,9 +801,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="A39" s="4"/>
       <c r="B39" s="6" t="s">
         <v>3</v>
       </c>
@@ -1174,9 +810,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="A40" s="4"/>
       <c r="B40" s="6" t="s">
         <v>3</v>
       </c>
@@ -1185,9 +819,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="A41" s="4"/>
       <c r="B41" s="6" t="s">
         <v>3</v>
       </c>
@@ -1196,9 +828,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="A42" s="4"/>
       <c r="B42" s="6" t="s">
         <v>3</v>
       </c>
@@ -1207,9 +837,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="A43" s="4"/>
       <c r="B43" s="6" t="s">
         <v>3</v>
       </c>
@@ -1218,9 +846,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="A44" s="4"/>
       <c r="B44" s="6" t="s">
         <v>3</v>
       </c>
@@ -1229,9 +855,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="A45" s="4"/>
       <c r="B45" s="6" t="s">
         <v>3</v>
       </c>
@@ -1240,9 +864,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="A46" s="4"/>
       <c r="B46" s="6" t="s">
         <v>3</v>
       </c>
@@ -1251,9 +873,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="A47" s="4"/>
       <c r="B47" s="6" t="s">
         <v>3</v>
       </c>
@@ -1262,9 +882,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="A48" s="4"/>
       <c r="B48" s="6" t="s">
         <v>3</v>
       </c>
@@ -1273,9 +891,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>52</v>
-      </c>
+      <c r="A49" s="4"/>
       <c r="B49" s="6" t="s">
         <v>3</v>
       </c>
@@ -1284,9 +900,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A50" s="4"/>
       <c r="B50" s="6" t="s">
         <v>3</v>
       </c>
@@ -1295,9 +909,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A51" s="4"/>
       <c r="B51" s="6" t="s">
         <v>3</v>
       </c>
@@ -1306,9 +918,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A52" s="4"/>
       <c r="B52" s="6" t="s">
         <v>3</v>
       </c>
@@ -1317,9 +927,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="A53" s="4"/>
       <c r="B53" s="6" t="s">
         <v>3</v>
       </c>
@@ -1328,9 +936,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="A54" s="4"/>
       <c r="B54" s="6" t="s">
         <v>3</v>
       </c>
@@ -1339,9 +945,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="A55" s="4"/>
       <c r="B55" s="6" t="s">
         <v>3</v>
       </c>
@@ -1350,9 +954,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="A56" s="4"/>
       <c r="B56" s="6" t="s">
         <v>3</v>
       </c>
@@ -1361,9 +963,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A57" s="4"/>
       <c r="B57" s="6" t="s">
         <v>3</v>
       </c>
@@ -1372,9 +972,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="A58" s="4"/>
       <c r="B58" s="6" t="s">
         <v>3</v>
       </c>
@@ -1383,9 +981,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="A59" s="4"/>
       <c r="B59" s="6" t="s">
         <v>3</v>
       </c>
@@ -1394,9 +990,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="A60" s="4"/>
       <c r="B60" s="6" t="s">
         <v>3</v>
       </c>
@@ -1405,9 +999,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="A61" s="4"/>
       <c r="B61" s="6" t="s">
         <v>3</v>
       </c>
@@ -1416,9 +1008,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A62" s="4"/>
       <c r="B62" s="6" t="s">
         <v>3</v>
       </c>
@@ -1427,9 +1017,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="A63" s="4"/>
       <c r="B63" s="6" t="s">
         <v>3</v>
       </c>
@@ -1438,9 +1026,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>67</v>
-      </c>
+      <c r="A64" s="4"/>
       <c r="B64" s="6" t="s">
         <v>3</v>
       </c>
@@ -1449,9 +1035,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="A65" s="4"/>
       <c r="B65" s="6" t="s">
         <v>3</v>
       </c>
@@ -1460,9 +1044,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A66" s="4"/>
       <c r="B66" s="6" t="s">
         <v>3</v>
       </c>
@@ -1471,9 +1053,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A67" s="4"/>
       <c r="B67" s="6" t="s">
         <v>3</v>
       </c>
@@ -1482,9 +1062,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="A68" s="4"/>
       <c r="B68" s="6" t="s">
         <v>3</v>
       </c>
@@ -1493,9 +1071,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="A69" s="4"/>
       <c r="B69" s="6" t="s">
         <v>3</v>
       </c>
@@ -1504,9 +1080,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A70" s="4"/>
       <c r="B70" s="6" t="s">
         <v>3</v>
       </c>
@@ -1515,9 +1089,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>74</v>
-      </c>
+      <c r="A71" s="4"/>
       <c r="B71" s="6" t="s">
         <v>3</v>
       </c>
@@ -1526,9 +1098,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>75</v>
-      </c>
+      <c r="A72" s="4"/>
       <c r="B72" s="6" t="s">
         <v>3</v>
       </c>
@@ -1537,9 +1107,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>76</v>
-      </c>
+      <c r="A73" s="4"/>
       <c r="B73" s="6" t="s">
         <v>3</v>
       </c>
@@ -1548,9 +1116,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>77</v>
-      </c>
+      <c r="A74" s="4"/>
       <c r="B74" s="6" t="s">
         <v>3</v>
       </c>
@@ -1559,9 +1125,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>78</v>
-      </c>
+      <c r="A75" s="4"/>
       <c r="B75" s="6" t="s">
         <v>3</v>
       </c>
@@ -1570,9 +1134,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>79</v>
-      </c>
+      <c r="A76" s="4"/>
       <c r="B76" s="6" t="s">
         <v>3</v>
       </c>
@@ -1581,9 +1143,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>80</v>
-      </c>
+      <c r="A77" s="4"/>
       <c r="B77" s="6" t="s">
         <v>3</v>
       </c>
@@ -1592,9 +1152,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>81</v>
-      </c>
+      <c r="A78" s="4"/>
       <c r="B78" s="6" t="s">
         <v>3</v>
       </c>
@@ -1603,9 +1161,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>82</v>
-      </c>
+      <c r="A79" s="4"/>
       <c r="B79" s="6" t="s">
         <v>3</v>
       </c>
@@ -1614,9 +1170,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>83</v>
-      </c>
+      <c r="A80" s="4"/>
       <c r="B80" s="6" t="s">
         <v>3</v>
       </c>
@@ -1625,9 +1179,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>84</v>
-      </c>
+      <c r="A81" s="4"/>
       <c r="B81" s="6" t="s">
         <v>3</v>
       </c>
@@ -1636,9 +1188,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>85</v>
-      </c>
+      <c r="A82" s="4"/>
       <c r="B82" s="6" t="s">
         <v>3</v>
       </c>
@@ -1647,9 +1197,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="A83" s="4"/>
       <c r="B83" s="6" t="s">
         <v>3</v>
       </c>
@@ -1658,9 +1206,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>87</v>
-      </c>
+      <c r="A84" s="4"/>
       <c r="B84" s="6" t="s">
         <v>3</v>
       </c>
@@ -1669,9 +1215,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>88</v>
-      </c>
+      <c r="A85" s="4"/>
       <c r="B85" s="6" t="s">
         <v>3</v>
       </c>
@@ -1680,9 +1224,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>89</v>
-      </c>
+      <c r="A86" s="4"/>
       <c r="B86" s="6" t="s">
         <v>3</v>
       </c>
@@ -1691,9 +1233,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>90</v>
-      </c>
+      <c r="A87" s="4"/>
       <c r="B87" s="6" t="s">
         <v>3</v>
       </c>
@@ -1702,9 +1242,7 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="A88" s="4"/>
       <c r="B88" s="6" t="s">
         <v>3</v>
       </c>
@@ -1713,9 +1251,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="A89" s="4"/>
       <c r="B89" s="6" t="s">
         <v>3</v>
       </c>
@@ -1724,9 +1260,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>93</v>
-      </c>
+      <c r="A90" s="4"/>
       <c r="B90" s="6" t="s">
         <v>3</v>
       </c>
@@ -1735,9 +1269,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>94</v>
-      </c>
+      <c r="A91" s="4"/>
       <c r="B91" s="6" t="s">
         <v>3</v>
       </c>
@@ -1746,9 +1278,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>95</v>
-      </c>
+      <c r="A92" s="4"/>
       <c r="B92" s="6" t="s">
         <v>3</v>
       </c>
@@ -1757,9 +1287,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>96</v>
-      </c>
+      <c r="A93" s="4"/>
       <c r="B93" s="6" t="s">
         <v>3</v>
       </c>
@@ -1768,9 +1296,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>97</v>
-      </c>
+      <c r="A94" s="4"/>
       <c r="B94" s="6" t="s">
         <v>3</v>
       </c>
@@ -1779,9 +1305,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="A95" s="4"/>
       <c r="B95" s="6" t="s">
         <v>3</v>
       </c>
@@ -1790,9 +1314,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>99</v>
-      </c>
+      <c r="A96" s="4"/>
       <c r="B96" s="6" t="s">
         <v>3</v>
       </c>
@@ -1801,9 +1323,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>100</v>
-      </c>
+      <c r="A97" s="4"/>
       <c r="B97" s="6" t="s">
         <v>3</v>
       </c>
@@ -1811,8 +1331,2004 @@
         <v>4</v>
       </c>
     </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4"/>
+      <c r="B98" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4"/>
+      <c r="B99" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4"/>
+      <c r="B100" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4"/>
+      <c r="B101" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4"/>
+      <c r="B102" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4"/>
+      <c r="B103" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4"/>
+      <c r="B104" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4"/>
+      <c r="B105" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4"/>
+      <c r="B106" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4"/>
+      <c r="B107" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4"/>
+      <c r="B108" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4"/>
+      <c r="B109" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4"/>
+      <c r="B110" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4"/>
+      <c r="B111" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4"/>
+      <c r="B112" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4"/>
+      <c r="B113" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4"/>
+      <c r="B114" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4"/>
+      <c r="B115" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4"/>
+      <c r="B116" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4"/>
+      <c r="B117" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4"/>
+      <c r="B118" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4"/>
+      <c r="B119" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4"/>
+      <c r="B120" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4"/>
+      <c r="B121" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4"/>
+      <c r="B122" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4"/>
+      <c r="B123" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4"/>
+      <c r="B124" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4"/>
+      <c r="B125" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4"/>
+      <c r="B126" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4"/>
+      <c r="B127" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4"/>
+      <c r="B128" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4"/>
+      <c r="B129" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4"/>
+      <c r="B130" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4"/>
+      <c r="B131" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4"/>
+      <c r="B132" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4"/>
+      <c r="B133" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4"/>
+      <c r="B134" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4"/>
+      <c r="B135" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4"/>
+      <c r="B136" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4"/>
+      <c r="B137" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4"/>
+      <c r="B138" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4"/>
+      <c r="B139" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4"/>
+      <c r="B140" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4"/>
+      <c r="B141" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4"/>
+      <c r="B142" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4"/>
+      <c r="B143" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4"/>
+      <c r="B144" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4"/>
+      <c r="B145" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4"/>
+      <c r="B146" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4"/>
+      <c r="B147" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4"/>
+      <c r="B148" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4"/>
+      <c r="B149" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4"/>
+      <c r="B150" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4"/>
+      <c r="B151" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4"/>
+      <c r="B152" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4"/>
+      <c r="B153" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4"/>
+      <c r="B154" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4"/>
+      <c r="B155" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4"/>
+      <c r="B156" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4"/>
+      <c r="B157" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4"/>
+      <c r="B158" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4"/>
+      <c r="B159" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4"/>
+      <c r="B160" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4"/>
+      <c r="B161" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4"/>
+      <c r="B162" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4"/>
+      <c r="B163" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4"/>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4"/>
+      <c r="B165" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4"/>
+      <c r="B166" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4"/>
+      <c r="B167" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4"/>
+      <c r="B168" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4"/>
+      <c r="B169" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4"/>
+      <c r="B170" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4"/>
+      <c r="B171" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4"/>
+      <c r="B172" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4"/>
+      <c r="B173" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4"/>
+      <c r="B174" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4"/>
+      <c r="B175" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4"/>
+      <c r="B176" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4"/>
+      <c r="B177" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4"/>
+      <c r="B178" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4"/>
+      <c r="B179" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4"/>
+      <c r="B180" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4"/>
+      <c r="B181" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4"/>
+      <c r="B182" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4"/>
+      <c r="B183" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4"/>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4"/>
+      <c r="B185" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4"/>
+      <c r="B186" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4"/>
+      <c r="B187" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4"/>
+      <c r="B188" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4"/>
+      <c r="B189" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4"/>
+      <c r="B190" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4"/>
+      <c r="B191" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4"/>
+      <c r="B192" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4"/>
+      <c r="B193" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4"/>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4"/>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4"/>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4"/>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4"/>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4"/>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4"/>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4"/>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4"/>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4"/>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4"/>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4"/>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B328" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B329" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B330" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B331" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B332" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B333" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C97" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF458CB-4C27-42D0-BC9B-B75DF3665322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D580B540-2198-4A0A-BAF8-58545F08AE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="186">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -43,6 +43,549 @@
   </si>
   <si>
     <t>.</t>
+  </si>
+  <si>
+    <t>130496860</t>
+  </si>
+  <si>
+    <t>130502267</t>
+  </si>
+  <si>
+    <t>131049366</t>
+  </si>
+  <si>
+    <t>131353766</t>
+  </si>
+  <si>
+    <t>131958642</t>
+  </si>
+  <si>
+    <t>132327890</t>
+  </si>
+  <si>
+    <t>132758005</t>
+  </si>
+  <si>
+    <t>132780949</t>
+  </si>
+  <si>
+    <t>132936692</t>
+  </si>
+  <si>
+    <t>132988074</t>
+  </si>
+  <si>
+    <t>133016532</t>
+  </si>
+  <si>
+    <t>133399888</t>
+  </si>
+  <si>
+    <t>133479005</t>
+  </si>
+  <si>
+    <t>133488513</t>
+  </si>
+  <si>
+    <t>133572916</t>
+  </si>
+  <si>
+    <t>133939544</t>
+  </si>
+  <si>
+    <t>134345714</t>
+  </si>
+  <si>
+    <t>134418400</t>
+  </si>
+  <si>
+    <t>134886251</t>
+  </si>
+  <si>
+    <t>135062399</t>
+  </si>
+  <si>
+    <t>135062425</t>
+  </si>
+  <si>
+    <t>135062454</t>
+  </si>
+  <si>
+    <t>135062463</t>
+  </si>
+  <si>
+    <t>135062495</t>
+  </si>
+  <si>
+    <t>135062609</t>
+  </si>
+  <si>
+    <t>135062632</t>
+  </si>
+  <si>
+    <t>135062712</t>
+  </si>
+  <si>
+    <t>135062766</t>
+  </si>
+  <si>
+    <t>135062811</t>
+  </si>
+  <si>
+    <t>135062851</t>
+  </si>
+  <si>
+    <t>135063267</t>
+  </si>
+  <si>
+    <t>135063509</t>
+  </si>
+  <si>
+    <t>135063612</t>
+  </si>
+  <si>
+    <t>135063974</t>
+  </si>
+  <si>
+    <t>135064123</t>
+  </si>
+  <si>
+    <t>135064219</t>
+  </si>
+  <si>
+    <t>135064395</t>
+  </si>
+  <si>
+    <t>135064878</t>
+  </si>
+  <si>
+    <t>135064890</t>
+  </si>
+  <si>
+    <t>135064936</t>
+  </si>
+  <si>
+    <t>135065034</t>
+  </si>
+  <si>
+    <t>135065176</t>
+  </si>
+  <si>
+    <t>135065231</t>
+  </si>
+  <si>
+    <t>135065376</t>
+  </si>
+  <si>
+    <t>135065537</t>
+  </si>
+  <si>
+    <t>135065657</t>
+  </si>
+  <si>
+    <t>135065679</t>
+  </si>
+  <si>
+    <t>135065765</t>
+  </si>
+  <si>
+    <t>135065829</t>
+  </si>
+  <si>
+    <t>135065964</t>
+  </si>
+  <si>
+    <t>135066509</t>
+  </si>
+  <si>
+    <t>135066734</t>
+  </si>
+  <si>
+    <t>135066877</t>
+  </si>
+  <si>
+    <t>135067216</t>
+  </si>
+  <si>
+    <t>135067693</t>
+  </si>
+  <si>
+    <t>135067783</t>
+  </si>
+  <si>
+    <t>135067964</t>
+  </si>
+  <si>
+    <t>135068030</t>
+  </si>
+  <si>
+    <t>135068148</t>
+  </si>
+  <si>
+    <t>135068316</t>
+  </si>
+  <si>
+    <t>135068476</t>
+  </si>
+  <si>
+    <t>135068649</t>
+  </si>
+  <si>
+    <t>135068711</t>
+  </si>
+  <si>
+    <t>135068713</t>
+  </si>
+  <si>
+    <t>135069193</t>
+  </si>
+  <si>
+    <t>135069223</t>
+  </si>
+  <si>
+    <t>135069960</t>
+  </si>
+  <si>
+    <t>135069970</t>
+  </si>
+  <si>
+    <t>135070018</t>
+  </si>
+  <si>
+    <t>135070030</t>
+  </si>
+  <si>
+    <t>135070042</t>
+  </si>
+  <si>
+    <t>135070167</t>
+  </si>
+  <si>
+    <t>135070231</t>
+  </si>
+  <si>
+    <t>135070247</t>
+  </si>
+  <si>
+    <t>135070255</t>
+  </si>
+  <si>
+    <t>135070455</t>
+  </si>
+  <si>
+    <t>135070544</t>
+  </si>
+  <si>
+    <t>135070690</t>
+  </si>
+  <si>
+    <t>135070780</t>
+  </si>
+  <si>
+    <t>135070865</t>
+  </si>
+  <si>
+    <t>135070892</t>
+  </si>
+  <si>
+    <t>135070927</t>
+  </si>
+  <si>
+    <t>135071025</t>
+  </si>
+  <si>
+    <t>135071144</t>
+  </si>
+  <si>
+    <t>135071149</t>
+  </si>
+  <si>
+    <t>135071174</t>
+  </si>
+  <si>
+    <t>135071378</t>
+  </si>
+  <si>
+    <t>135071534</t>
+  </si>
+  <si>
+    <t>135071556</t>
+  </si>
+  <si>
+    <t>135071785</t>
+  </si>
+  <si>
+    <t>135072077</t>
+  </si>
+  <si>
+    <t>135072682</t>
+  </si>
+  <si>
+    <t>135072802</t>
+  </si>
+  <si>
+    <t>135073146</t>
+  </si>
+  <si>
+    <t>135073231</t>
+  </si>
+  <si>
+    <t>135073273</t>
+  </si>
+  <si>
+    <t>135073326</t>
+  </si>
+  <si>
+    <t>135073511</t>
+  </si>
+  <si>
+    <t>135073582</t>
+  </si>
+  <si>
+    <t>135073613</t>
+  </si>
+  <si>
+    <t>135073934</t>
+  </si>
+  <si>
+    <t>135074011</t>
+  </si>
+  <si>
+    <t>135074186</t>
+  </si>
+  <si>
+    <t>135074316</t>
+  </si>
+  <si>
+    <t>135074435</t>
+  </si>
+  <si>
+    <t>135074441</t>
+  </si>
+  <si>
+    <t>135074488</t>
+  </si>
+  <si>
+    <t>135074617</t>
+  </si>
+  <si>
+    <t>135075239</t>
+  </si>
+  <si>
+    <t>135075358</t>
+  </si>
+  <si>
+    <t>135075408</t>
+  </si>
+  <si>
+    <t>135075513</t>
+  </si>
+  <si>
+    <t>135075633</t>
+  </si>
+  <si>
+    <t>135075677</t>
+  </si>
+  <si>
+    <t>135075799</t>
+  </si>
+  <si>
+    <t>135075828</t>
+  </si>
+  <si>
+    <t>135075891</t>
+  </si>
+  <si>
+    <t>135075895</t>
+  </si>
+  <si>
+    <t>135075931</t>
+  </si>
+  <si>
+    <t>135076181</t>
+  </si>
+  <si>
+    <t>135076206</t>
+  </si>
+  <si>
+    <t>135076377</t>
+  </si>
+  <si>
+    <t>135076500</t>
+  </si>
+  <si>
+    <t>135076607</t>
+  </si>
+  <si>
+    <t>135076694</t>
+  </si>
+  <si>
+    <t>135076764</t>
+  </si>
+  <si>
+    <t>135076966</t>
+  </si>
+  <si>
+    <t>135077006</t>
+  </si>
+  <si>
+    <t>135077032</t>
+  </si>
+  <si>
+    <t>135077066</t>
+  </si>
+  <si>
+    <t>135077093</t>
+  </si>
+  <si>
+    <t>135077158</t>
+  </si>
+  <si>
+    <t>135077193</t>
+  </si>
+  <si>
+    <t>135077479</t>
+  </si>
+  <si>
+    <t>135077595</t>
+  </si>
+  <si>
+    <t>135077597</t>
+  </si>
+  <si>
+    <t>135077688</t>
+  </si>
+  <si>
+    <t>135077784</t>
+  </si>
+  <si>
+    <t>135077992</t>
+  </si>
+  <si>
+    <t>135078087</t>
+  </si>
+  <si>
+    <t>135078130</t>
+  </si>
+  <si>
+    <t>135078173</t>
+  </si>
+  <si>
+    <t>135078244</t>
+  </si>
+  <si>
+    <t>135078363</t>
+  </si>
+  <si>
+    <t>135078379</t>
+  </si>
+  <si>
+    <t>135078421</t>
+  </si>
+  <si>
+    <t>135078503</t>
+  </si>
+  <si>
+    <t>135078611</t>
+  </si>
+  <si>
+    <t>135078708</t>
+  </si>
+  <si>
+    <t>135078729</t>
+  </si>
+  <si>
+    <t>135078742</t>
+  </si>
+  <si>
+    <t>135078821</t>
+  </si>
+  <si>
+    <t>135079181</t>
+  </si>
+  <si>
+    <t>135079275</t>
+  </si>
+  <si>
+    <t>135079339</t>
+  </si>
+  <si>
+    <t>135079410</t>
+  </si>
+  <si>
+    <t>135079411</t>
+  </si>
+  <si>
+    <t>135079455</t>
+  </si>
+  <si>
+    <t>135079513</t>
+  </si>
+  <si>
+    <t>135079682</t>
+  </si>
+  <si>
+    <t>135079751</t>
+  </si>
+  <si>
+    <t>135079829</t>
+  </si>
+  <si>
+    <t>135079857</t>
+  </si>
+  <si>
+    <t>135079872</t>
+  </si>
+  <si>
+    <t>135079909</t>
+  </si>
+  <si>
+    <t>135080012</t>
+  </si>
+  <si>
+    <t>135080065</t>
+  </si>
+  <si>
+    <t>135080183</t>
+  </si>
+  <si>
+    <t>135080370</t>
+  </si>
+  <si>
+    <t>135080394</t>
+  </si>
+  <si>
+    <t>135080454</t>
+  </si>
+  <si>
+    <t>135080458</t>
+  </si>
+  <si>
+    <t>135080538</t>
+  </si>
+  <si>
+    <t>135080547</t>
+  </si>
+  <si>
+    <t>135080632</t>
+  </si>
+  <si>
+    <t>135080820</t>
+  </si>
+  <si>
+    <t>135080839</t>
+  </si>
+  <si>
+    <t>135080885</t>
+  </si>
+  <si>
+    <t>135080987</t>
+  </si>
+  <si>
+    <t>135081306</t>
+  </si>
+  <si>
+    <t>135081926</t>
   </si>
 </sst>
 </file>
@@ -447,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C333"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -468,7 +1011,9 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
@@ -477,7 +1022,9 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
@@ -486,7 +1033,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
@@ -495,7 +1044,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
@@ -504,7 +1055,9 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
@@ -513,7 +1066,9 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
@@ -522,7 +1077,9 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
@@ -531,7 +1088,9 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="B9" s="6" t="s">
         <v>3</v>
       </c>
@@ -540,7 +1099,9 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
@@ -549,7 +1110,9 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="B11" s="6" t="s">
         <v>3</v>
       </c>
@@ -558,7 +1121,9 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
+      <c r="A12" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="B12" s="6" t="s">
         <v>3</v>
       </c>
@@ -567,7 +1132,9 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="B13" s="6" t="s">
         <v>3</v>
       </c>
@@ -576,7 +1143,9 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="B14" s="6" t="s">
         <v>3</v>
       </c>
@@ -585,7 +1154,9 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B15" s="6" t="s">
         <v>3</v>
       </c>
@@ -594,7 +1165,9 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+      <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="B16" s="6" t="s">
         <v>3</v>
       </c>
@@ -603,7 +1176,9 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
+      <c r="A17" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="B17" s="6" t="s">
         <v>3</v>
       </c>
@@ -612,7 +1187,9 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="B18" s="6" t="s">
         <v>3</v>
       </c>
@@ -621,7 +1198,9 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
+      <c r="A19" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="B19" s="6" t="s">
         <v>3</v>
       </c>
@@ -630,7 +1209,9 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
+      <c r="A20" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="B20" s="6" t="s">
         <v>3</v>
       </c>
@@ -639,7 +1220,9 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
+      <c r="A21" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B21" s="6" t="s">
         <v>3</v>
       </c>
@@ -648,7 +1231,9 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="B22" s="6" t="s">
         <v>3</v>
       </c>
@@ -657,7 +1242,9 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
+      <c r="A23" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="B23" s="6" t="s">
         <v>3</v>
       </c>
@@ -666,7 +1253,9 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
+      <c r="A24" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="B24" s="6" t="s">
         <v>3</v>
       </c>
@@ -675,7 +1264,9 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
+      <c r="A25" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="B25" s="6" t="s">
         <v>3</v>
       </c>
@@ -684,7 +1275,9 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
+      <c r="A26" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="B26" s="6" t="s">
         <v>3</v>
       </c>
@@ -693,7 +1286,9 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
+      <c r="A27" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="B27" s="6" t="s">
         <v>3</v>
       </c>
@@ -702,7 +1297,9 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
+      <c r="A28" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="B28" s="6" t="s">
         <v>3</v>
       </c>
@@ -711,7 +1308,9 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
+      <c r="A29" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="B29" s="6" t="s">
         <v>3</v>
       </c>
@@ -720,7 +1319,9 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
+      <c r="A30" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="B30" s="6" t="s">
         <v>3</v>
       </c>
@@ -729,7 +1330,9 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
+      <c r="A31" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="B31" s="6" t="s">
         <v>3</v>
       </c>
@@ -738,7 +1341,9 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
+      <c r="A32" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="B32" s="6" t="s">
         <v>3</v>
       </c>
@@ -747,7 +1352,9 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
+      <c r="A33" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="B33" s="6" t="s">
         <v>3</v>
       </c>
@@ -756,7 +1363,9 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
+      <c r="A34" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="B34" s="6" t="s">
         <v>3</v>
       </c>
@@ -765,7 +1374,9 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
+      <c r="A35" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="B35" s="6" t="s">
         <v>3</v>
       </c>
@@ -774,7 +1385,9 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
+      <c r="A36" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B36" s="6" t="s">
         <v>3</v>
       </c>
@@ -783,7 +1396,9 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
+      <c r="A37" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="B37" s="6" t="s">
         <v>3</v>
       </c>
@@ -792,7 +1407,9 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
+      <c r="A38" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="B38" s="6" t="s">
         <v>3</v>
       </c>
@@ -801,7 +1418,9 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
+      <c r="A39" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B39" s="6" t="s">
         <v>3</v>
       </c>
@@ -810,7 +1429,9 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
+      <c r="A40" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="B40" s="6" t="s">
         <v>3</v>
       </c>
@@ -819,7 +1440,9 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
+      <c r="A41" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="B41" s="6" t="s">
         <v>3</v>
       </c>
@@ -828,7 +1451,9 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
+      <c r="A42" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="B42" s="6" t="s">
         <v>3</v>
       </c>
@@ -837,7 +1462,9 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
+      <c r="A43" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="B43" s="6" t="s">
         <v>3</v>
       </c>
@@ -846,7 +1473,9 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+      <c r="A44" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="B44" s="6" t="s">
         <v>3</v>
       </c>
@@ -855,7 +1484,9 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
+      <c r="A45" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="B45" s="6" t="s">
         <v>3</v>
       </c>
@@ -864,7 +1495,9 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
+      <c r="A46" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="B46" s="6" t="s">
         <v>3</v>
       </c>
@@ -873,7 +1506,9 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="B47" s="6" t="s">
         <v>3</v>
       </c>
@@ -882,7 +1517,9 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
+      <c r="A48" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="B48" s="6" t="s">
         <v>3</v>
       </c>
@@ -891,7 +1528,9 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
+      <c r="A49" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="B49" s="6" t="s">
         <v>3</v>
       </c>
@@ -900,7 +1539,9 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
+      <c r="A50" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="B50" s="6" t="s">
         <v>3</v>
       </c>
@@ -909,7 +1550,9 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
+      <c r="A51" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="B51" s="6" t="s">
         <v>3</v>
       </c>
@@ -918,7 +1561,9 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
+      <c r="A52" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="B52" s="6" t="s">
         <v>3</v>
       </c>
@@ -927,7 +1572,9 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
+      <c r="A53" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="B53" s="6" t="s">
         <v>3</v>
       </c>
@@ -936,7 +1583,9 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
+      <c r="A54" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="B54" s="6" t="s">
         <v>3</v>
       </c>
@@ -945,7 +1594,9 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
+      <c r="A55" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="B55" s="6" t="s">
         <v>3</v>
       </c>
@@ -954,7 +1605,9 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
+      <c r="A56" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="B56" s="6" t="s">
         <v>3</v>
       </c>
@@ -963,7 +1616,9 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
+      <c r="A57" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="B57" s="6" t="s">
         <v>3</v>
       </c>
@@ -972,7 +1627,9 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
+      <c r="A58" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="B58" s="6" t="s">
         <v>3</v>
       </c>
@@ -981,7 +1638,9 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
+      <c r="A59" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="B59" s="6" t="s">
         <v>3</v>
       </c>
@@ -990,7 +1649,9 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
+      <c r="A60" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="B60" s="6" t="s">
         <v>3</v>
       </c>
@@ -999,7 +1660,9 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
+      <c r="A61" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="B61" s="6" t="s">
         <v>3</v>
       </c>
@@ -1008,7 +1671,9 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
+      <c r="A62" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="B62" s="6" t="s">
         <v>3</v>
       </c>
@@ -1017,7 +1682,9 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
+      <c r="A63" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="B63" s="6" t="s">
         <v>3</v>
       </c>
@@ -1026,7 +1693,9 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
+      <c r="A64" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="B64" s="6" t="s">
         <v>3</v>
       </c>
@@ -1035,7 +1704,9 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
+      <c r="A65" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="B65" s="6" t="s">
         <v>3</v>
       </c>
@@ -1044,7 +1715,9 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
+      <c r="A66" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="B66" s="6" t="s">
         <v>3</v>
       </c>
@@ -1053,7 +1726,9 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
+      <c r="A67" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="B67" s="6" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1737,9 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
+      <c r="A68" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="B68" s="6" t="s">
         <v>3</v>
       </c>
@@ -1071,7 +1748,9 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="4"/>
+      <c r="A69" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="B69" s="6" t="s">
         <v>3</v>
       </c>
@@ -1080,7 +1759,9 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
+      <c r="A70" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="B70" s="6" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1770,9 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="4"/>
+      <c r="A71" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="B71" s="6" t="s">
         <v>3</v>
       </c>
@@ -1098,7 +1781,9 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
+      <c r="A72" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="B72" s="6" t="s">
         <v>3</v>
       </c>
@@ -1107,7 +1792,9 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="4"/>
+      <c r="A73" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="B73" s="6" t="s">
         <v>3</v>
       </c>
@@ -1116,7 +1803,9 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
+      <c r="A74" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="B74" s="6" t="s">
         <v>3</v>
       </c>
@@ -1125,7 +1814,9 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
+      <c r="A75" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="B75" s="6" t="s">
         <v>3</v>
       </c>
@@ -1134,7 +1825,9 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
+      <c r="A76" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="B76" s="6" t="s">
         <v>3</v>
       </c>
@@ -1143,7 +1836,9 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
+      <c r="A77" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="B77" s="6" t="s">
         <v>3</v>
       </c>
@@ -1152,7 +1847,9 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
+      <c r="A78" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="B78" s="6" t="s">
         <v>3</v>
       </c>
@@ -1161,7 +1858,9 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="4"/>
+      <c r="A79" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="B79" s="6" t="s">
         <v>3</v>
       </c>
@@ -1170,7 +1869,9 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
+      <c r="A80" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="B80" s="6" t="s">
         <v>3</v>
       </c>
@@ -1179,7 +1880,9 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4"/>
+      <c r="A81" s="4" t="s">
+        <v>84</v>
+      </c>
       <c r="B81" s="6" t="s">
         <v>3</v>
       </c>
@@ -1188,7 +1891,9 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
+      <c r="A82" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="B82" s="6" t="s">
         <v>3</v>
       </c>
@@ -1197,7 +1902,9 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4"/>
+      <c r="A83" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="B83" s="6" t="s">
         <v>3</v>
       </c>
@@ -1206,7 +1913,9 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
+      <c r="A84" s="4" t="s">
+        <v>87</v>
+      </c>
       <c r="B84" s="6" t="s">
         <v>3</v>
       </c>
@@ -1215,7 +1924,9 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4"/>
+      <c r="A85" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="B85" s="6" t="s">
         <v>3</v>
       </c>
@@ -1224,7 +1935,9 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
+      <c r="A86" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="B86" s="6" t="s">
         <v>3</v>
       </c>
@@ -1233,7 +1946,9 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4"/>
+      <c r="A87" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="B87" s="6" t="s">
         <v>3</v>
       </c>
@@ -1242,7 +1957,9 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
+      <c r="A88" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="B88" s="6" t="s">
         <v>3</v>
       </c>
@@ -1251,7 +1968,9 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4"/>
+      <c r="A89" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="B89" s="6" t="s">
         <v>3</v>
       </c>
@@ -1260,7 +1979,9 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
+      <c r="A90" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="B90" s="6" t="s">
         <v>3</v>
       </c>
@@ -1269,7 +1990,9 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4"/>
+      <c r="A91" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="B91" s="6" t="s">
         <v>3</v>
       </c>
@@ -1278,7 +2001,9 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
+      <c r="A92" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="B92" s="6" t="s">
         <v>3</v>
       </c>
@@ -1287,7 +2012,9 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4"/>
+      <c r="A93" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="B93" s="6" t="s">
         <v>3</v>
       </c>
@@ -1296,7 +2023,9 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
+      <c r="A94" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="B94" s="6" t="s">
         <v>3</v>
       </c>
@@ -1305,7 +2034,9 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4"/>
+      <c r="A95" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="B95" s="6" t="s">
         <v>3</v>
       </c>
@@ -1314,7 +2045,9 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
+      <c r="A96" s="4" t="s">
+        <v>99</v>
+      </c>
       <c r="B96" s="6" t="s">
         <v>3</v>
       </c>
@@ -1323,7 +2056,9 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
+      <c r="A97" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="B97" s="6" t="s">
         <v>3</v>
       </c>
@@ -1332,7 +2067,9 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
+      <c r="A98" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="B98" s="6" t="s">
         <v>3</v>
       </c>
@@ -1341,7 +2078,9 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="4"/>
+      <c r="A99" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="B99" s="6" t="s">
         <v>3</v>
       </c>
@@ -1350,7 +2089,9 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="4"/>
+      <c r="A100" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="B100" s="6" t="s">
         <v>3</v>
       </c>
@@ -1359,7 +2100,9 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="4"/>
+      <c r="A101" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="B101" s="6" t="s">
         <v>3</v>
       </c>
@@ -1368,7 +2111,9 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="4"/>
+      <c r="A102" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="B102" s="6" t="s">
         <v>3</v>
       </c>
@@ -1377,7 +2122,9 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="4"/>
+      <c r="A103" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="B103" s="6" t="s">
         <v>3</v>
       </c>
@@ -1386,7 +2133,9 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="4"/>
+      <c r="A104" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="B104" s="6" t="s">
         <v>3</v>
       </c>
@@ -1395,7 +2144,9 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="4"/>
+      <c r="A105" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="B105" s="6" t="s">
         <v>3</v>
       </c>
@@ -1404,7 +2155,9 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4"/>
+      <c r="A106" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="B106" s="6" t="s">
         <v>3</v>
       </c>
@@ -1413,7 +2166,9 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
+      <c r="A107" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="B107" s="6" t="s">
         <v>3</v>
       </c>
@@ -1422,7 +2177,9 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4"/>
+      <c r="A108" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="B108" s="6" t="s">
         <v>3</v>
       </c>
@@ -1431,7 +2188,9 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
+      <c r="A109" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="B109" s="6" t="s">
         <v>3</v>
       </c>
@@ -1440,7 +2199,9 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4"/>
+      <c r="A110" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="B110" s="6" t="s">
         <v>3</v>
       </c>
@@ -1449,7 +2210,9 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
+      <c r="A111" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="B111" s="6" t="s">
         <v>3</v>
       </c>
@@ -1458,7 +2221,9 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
+      <c r="A112" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="B112" s="6" t="s">
         <v>3</v>
       </c>
@@ -1467,7 +2232,9 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
+      <c r="A113" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="B113" s="6" t="s">
         <v>3</v>
       </c>
@@ -1476,7 +2243,9 @@
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
+      <c r="A114" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="B114" s="6" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +2254,9 @@
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="4"/>
+      <c r="A115" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="B115" s="6" t="s">
         <v>3</v>
       </c>
@@ -1494,7 +2265,9 @@
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="4"/>
+      <c r="A116" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="B116" s="6" t="s">
         <v>3</v>
       </c>
@@ -1503,7 +2276,9 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
+      <c r="A117" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="B117" s="6" t="s">
         <v>3</v>
       </c>
@@ -1512,7 +2287,9 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="4"/>
+      <c r="A118" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="B118" s="6" t="s">
         <v>3</v>
       </c>
@@ -1521,7 +2298,9 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
+      <c r="A119" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="B119" s="6" t="s">
         <v>3</v>
       </c>
@@ -1530,7 +2309,9 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="4"/>
+      <c r="A120" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="B120" s="6" t="s">
         <v>3</v>
       </c>
@@ -1539,7 +2320,9 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="4"/>
+      <c r="A121" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="B121" s="6" t="s">
         <v>3</v>
       </c>
@@ -1548,7 +2331,9 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
+      <c r="A122" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="B122" s="6" t="s">
         <v>3</v>
       </c>
@@ -1557,7 +2342,9 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="4"/>
+      <c r="A123" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="B123" s="6" t="s">
         <v>3</v>
       </c>
@@ -1566,7 +2353,9 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="4"/>
+      <c r="A124" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="B124" s="6" t="s">
         <v>3</v>
       </c>
@@ -1575,7 +2364,9 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="4"/>
+      <c r="A125" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="B125" s="6" t="s">
         <v>3</v>
       </c>
@@ -1584,7 +2375,9 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="4"/>
+      <c r="A126" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="B126" s="6" t="s">
         <v>3</v>
       </c>
@@ -1593,7 +2386,9 @@
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="4"/>
+      <c r="A127" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="B127" s="6" t="s">
         <v>3</v>
       </c>
@@ -1602,7 +2397,9 @@
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="4"/>
+      <c r="A128" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="B128" s="6" t="s">
         <v>3</v>
       </c>
@@ -1611,7 +2408,9 @@
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="4"/>
+      <c r="A129" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="B129" s="6" t="s">
         <v>3</v>
       </c>
@@ -1620,7 +2419,9 @@
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="4"/>
+      <c r="A130" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="B130" s="6" t="s">
         <v>3</v>
       </c>
@@ -1629,7 +2430,9 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="4"/>
+      <c r="A131" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="B131" s="6" t="s">
         <v>3</v>
       </c>
@@ -1638,7 +2441,9 @@
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="4"/>
+      <c r="A132" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="B132" s="6" t="s">
         <v>3</v>
       </c>
@@ -1647,7 +2452,9 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="4"/>
+      <c r="A133" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="B133" s="6" t="s">
         <v>3</v>
       </c>
@@ -1656,7 +2463,9 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="4"/>
+      <c r="A134" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="B134" s="6" t="s">
         <v>3</v>
       </c>
@@ -1665,7 +2474,9 @@
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="4"/>
+      <c r="A135" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="B135" s="6" t="s">
         <v>3</v>
       </c>
@@ -1674,7 +2485,9 @@
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="4"/>
+      <c r="A136" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="B136" s="6" t="s">
         <v>3</v>
       </c>
@@ -1683,7 +2496,9 @@
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="4"/>
+      <c r="A137" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="B137" s="6" t="s">
         <v>3</v>
       </c>
@@ -1692,7 +2507,9 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="4"/>
+      <c r="A138" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="B138" s="6" t="s">
         <v>3</v>
       </c>
@@ -1701,7 +2518,9 @@
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="4"/>
+      <c r="A139" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="B139" s="6" t="s">
         <v>3</v>
       </c>
@@ -1710,7 +2529,9 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="4"/>
+      <c r="A140" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="B140" s="6" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +2540,9 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="4"/>
+      <c r="A141" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="B141" s="6" t="s">
         <v>3</v>
       </c>
@@ -1728,7 +2551,9 @@
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="4"/>
+      <c r="A142" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="B142" s="6" t="s">
         <v>3</v>
       </c>
@@ -1737,7 +2562,9 @@
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="4"/>
+      <c r="A143" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="B143" s="6" t="s">
         <v>3</v>
       </c>
@@ -1746,7 +2573,9 @@
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="4"/>
+      <c r="A144" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="B144" s="6" t="s">
         <v>3</v>
       </c>
@@ -1755,7 +2584,9 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="4"/>
+      <c r="A145" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="B145" s="6" t="s">
         <v>3</v>
       </c>
@@ -1764,7 +2595,9 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="4"/>
+      <c r="A146" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="B146" s="6" t="s">
         <v>3</v>
       </c>
@@ -1773,7 +2606,9 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="4"/>
+      <c r="A147" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="B147" s="6" t="s">
         <v>3</v>
       </c>
@@ -1782,7 +2617,9 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="4"/>
+      <c r="A148" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="B148" s="6" t="s">
         <v>3</v>
       </c>
@@ -1791,7 +2628,9 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="4"/>
+      <c r="A149" s="4" t="s">
+        <v>152</v>
+      </c>
       <c r="B149" s="6" t="s">
         <v>3</v>
       </c>
@@ -1800,7 +2639,9 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="4"/>
+      <c r="A150" s="4" t="s">
+        <v>153</v>
+      </c>
       <c r="B150" s="6" t="s">
         <v>3</v>
       </c>
@@ -1809,7 +2650,9 @@
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="4"/>
+      <c r="A151" s="4" t="s">
+        <v>154</v>
+      </c>
       <c r="B151" s="6" t="s">
         <v>3</v>
       </c>
@@ -1818,7 +2661,9 @@
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="4"/>
+      <c r="A152" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="B152" s="6" t="s">
         <v>3</v>
       </c>
@@ -1827,7 +2672,9 @@
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="4"/>
+      <c r="A153" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="B153" s="6" t="s">
         <v>3</v>
       </c>
@@ -1836,7 +2683,9 @@
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="4"/>
+      <c r="A154" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="B154" s="6" t="s">
         <v>3</v>
       </c>
@@ -1845,7 +2694,9 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="4"/>
+      <c r="A155" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="B155" s="6" t="s">
         <v>3</v>
       </c>
@@ -1854,7 +2705,9 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="4"/>
+      <c r="A156" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="B156" s="6" t="s">
         <v>3</v>
       </c>
@@ -1863,7 +2716,9 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="4"/>
+      <c r="A157" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="B157" s="6" t="s">
         <v>3</v>
       </c>
@@ -1872,7 +2727,9 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="4"/>
+      <c r="A158" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="B158" s="6" t="s">
         <v>3</v>
       </c>
@@ -1881,7 +2738,9 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="4"/>
+      <c r="A159" s="4" t="s">
+        <v>162</v>
+      </c>
       <c r="B159" s="6" t="s">
         <v>3</v>
       </c>
@@ -1890,7 +2749,9 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="4"/>
+      <c r="A160" s="4" t="s">
+        <v>163</v>
+      </c>
       <c r="B160" s="6" t="s">
         <v>3</v>
       </c>
@@ -1899,7 +2760,9 @@
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="4"/>
+      <c r="A161" s="4" t="s">
+        <v>164</v>
+      </c>
       <c r="B161" s="6" t="s">
         <v>3</v>
       </c>
@@ -1908,7 +2771,9 @@
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="4"/>
+      <c r="A162" s="4" t="s">
+        <v>165</v>
+      </c>
       <c r="B162" s="6" t="s">
         <v>3</v>
       </c>
@@ -1917,7 +2782,9 @@
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="4"/>
+      <c r="A163" s="4" t="s">
+        <v>166</v>
+      </c>
       <c r="B163" s="6" t="s">
         <v>3</v>
       </c>
@@ -1926,7 +2793,9 @@
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="4"/>
+      <c r="A164" s="4" t="s">
+        <v>167</v>
+      </c>
       <c r="B164" s="6" t="s">
         <v>3</v>
       </c>
@@ -1935,7 +2804,9 @@
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="4"/>
+      <c r="A165" s="4" t="s">
+        <v>168</v>
+      </c>
       <c r="B165" s="6" t="s">
         <v>3</v>
       </c>
@@ -1944,7 +2815,9 @@
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="4"/>
+      <c r="A166" s="4" t="s">
+        <v>169</v>
+      </c>
       <c r="B166" s="6" t="s">
         <v>3</v>
       </c>
@@ -1953,7 +2826,9 @@
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="4"/>
+      <c r="A167" s="4" t="s">
+        <v>170</v>
+      </c>
       <c r="B167" s="6" t="s">
         <v>3</v>
       </c>
@@ -1962,7 +2837,9 @@
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="4"/>
+      <c r="A168" s="4" t="s">
+        <v>171</v>
+      </c>
       <c r="B168" s="6" t="s">
         <v>3</v>
       </c>
@@ -1971,7 +2848,9 @@
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="4"/>
+      <c r="A169" s="4" t="s">
+        <v>172</v>
+      </c>
       <c r="B169" s="6" t="s">
         <v>3</v>
       </c>
@@ -1980,7 +2859,9 @@
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="4"/>
+      <c r="A170" s="4" t="s">
+        <v>173</v>
+      </c>
       <c r="B170" s="6" t="s">
         <v>3</v>
       </c>
@@ -1989,7 +2870,9 @@
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="4"/>
+      <c r="A171" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="B171" s="6" t="s">
         <v>3</v>
       </c>
@@ -1998,7 +2881,9 @@
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="4"/>
+      <c r="A172" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="B172" s="6" t="s">
         <v>3</v>
       </c>
@@ -2007,7 +2892,9 @@
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="4"/>
+      <c r="A173" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="B173" s="6" t="s">
         <v>3</v>
       </c>
@@ -2016,7 +2903,9 @@
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="4"/>
+      <c r="A174" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="B174" s="6" t="s">
         <v>3</v>
       </c>
@@ -2025,7 +2914,9 @@
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="4"/>
+      <c r="A175" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="B175" s="6" t="s">
         <v>3</v>
       </c>
@@ -2034,7 +2925,9 @@
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="4"/>
+      <c r="A176" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="B176" s="6" t="s">
         <v>3</v>
       </c>
@@ -2043,7 +2936,9 @@
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="4"/>
+      <c r="A177" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="B177" s="6" t="s">
         <v>3</v>
       </c>
@@ -2052,7 +2947,9 @@
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="4"/>
+      <c r="A178" s="4" t="s">
+        <v>181</v>
+      </c>
       <c r="B178" s="6" t="s">
         <v>3</v>
       </c>
@@ -2061,7 +2958,9 @@
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="4"/>
+      <c r="A179" s="4" t="s">
+        <v>182</v>
+      </c>
       <c r="B179" s="6" t="s">
         <v>3</v>
       </c>
@@ -2070,7 +2969,9 @@
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="4"/>
+      <c r="A180" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="B180" s="6" t="s">
         <v>3</v>
       </c>
@@ -2079,7 +2980,9 @@
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="4"/>
+      <c r="A181" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="B181" s="6" t="s">
         <v>3</v>
       </c>
@@ -2088,7 +2991,9 @@
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="4"/>
+      <c r="A182" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="B182" s="6" t="s">
         <v>3</v>
       </c>
@@ -2096,1239 +3001,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="4"/>
-      <c r="B183" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="4"/>
-      <c r="B184" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="4"/>
-      <c r="B185" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="4"/>
-      <c r="B186" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="4"/>
-      <c r="B187" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="4"/>
-      <c r="B188" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="4"/>
-      <c r="B189" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="4"/>
-      <c r="B190" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="4"/>
-      <c r="B191" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="4"/>
-      <c r="B192" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="4"/>
-      <c r="B193" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="4"/>
-      <c r="B194" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="4"/>
-      <c r="B195" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C195" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="4"/>
-      <c r="B196" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C196" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="4"/>
-      <c r="B197" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="4"/>
-      <c r="B198" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="4"/>
-      <c r="B199" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="4"/>
-      <c r="B200" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="4"/>
-      <c r="B201" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="4"/>
-      <c r="B202" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="4"/>
-      <c r="B203" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C203" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="4"/>
-      <c r="B204" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="4"/>
-      <c r="B205" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B206" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C206" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B207" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B208" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B209" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C209" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B210" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C210" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B211" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B212" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B213" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B214" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C214" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B215" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B216" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C216" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B217" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B218" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B219" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B220" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B221" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B222" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B223" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B224" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="225" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B225" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B226" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="227" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B227" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="228" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B228" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="229" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B229" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B230" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C230" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="231" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B231" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="232" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B232" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="233" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B233" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="234" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B234" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="235" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B235" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="236" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B236" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="237" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B237" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="238" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B238" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="239" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B239" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="240" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B240" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="241" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B241" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="242" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B242" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="243" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B243" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="244" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B244" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="245" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B245" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="246" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B246" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="247" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B247" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="248" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B248" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="249" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B249" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="250" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B250" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C250" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="251" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B251" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="252" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B252" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C252" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="253" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B253" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="254" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B254" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C254" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="255" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B255" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="256" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B256" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C256" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="257" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B257" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="258" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B258" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C258" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="259" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B259" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="260" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B260" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C260" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="261" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B261" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="262" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B262" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C262" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="263" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B263" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="264" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B264" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C264" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="265" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B265" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="266" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B266" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C266" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="267" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B267" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="268" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B268" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="269" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B269" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="270" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B270" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C270" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="271" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B271" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="272" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B272" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C272" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="273" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B273" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C273" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="274" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B274" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C274" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="275" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B275" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="276" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B276" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="277" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B277" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C277" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="278" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B278" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C278" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="279" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B279" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C279" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="280" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B280" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C280" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="281" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B281" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C281" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="282" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B282" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C282" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="283" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B283" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C283" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="284" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B284" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C284" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="285" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B285" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="286" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B286" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C286" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="287" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B287" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="288" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B288" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C288" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="289" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B289" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C289" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="290" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B290" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C290" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="291" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B291" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="292" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B292" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C292" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="293" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B293" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C293" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="294" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B294" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C294" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="295" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B295" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C295" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="296" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B296" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C296" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="297" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B297" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C297" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="298" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B298" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C298" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="299" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B299" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C299" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="300" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B300" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C300" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="301" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B301" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C301" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="302" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B302" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C302" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="303" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B303" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C303" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="304" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B304" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C304" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="305" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B305" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C305" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="306" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B306" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C306" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="307" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B307" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="308" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B308" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="309" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B309" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C309" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="310" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B310" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C310" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="311" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B311" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C311" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="312" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B312" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C312" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="313" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B313" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C313" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="314" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B314" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C314" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="315" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B315" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C315" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="316" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B316" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C316" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="317" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B317" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C317" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="318" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B318" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C318" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="319" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B319" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C319" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="320" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B320" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C320" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="321" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B321" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C321" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="322" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B322" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C322" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="323" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B323" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C323" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="324" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B324" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C324" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="325" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B325" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C325" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="326" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B326" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C326" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="327" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B327" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C327" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="328" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B328" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C328" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="329" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B329" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="330" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B330" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C330" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="331" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B331" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C331" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="332" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B332" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C332" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="333" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B333" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C333" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C182" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D580B540-2198-4A0A-BAF8-58545F08AE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05BB070-09F8-4D41-9003-4A85905EEDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05BB070-09F8-4D41-9003-4A85905EEDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF0614D-7BFF-41FA-97CD-07706F68F7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$177</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="181">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,547 +45,532 @@
     <t>.</t>
   </si>
   <si>
-    <t>130496860</t>
-  </si>
-  <si>
-    <t>130502267</t>
-  </si>
-  <si>
-    <t>131049366</t>
-  </si>
-  <si>
-    <t>131353766</t>
-  </si>
-  <si>
-    <t>131958642</t>
-  </si>
-  <si>
-    <t>132327890</t>
-  </si>
-  <si>
-    <t>132758005</t>
-  </si>
-  <si>
-    <t>132780949</t>
-  </si>
-  <si>
-    <t>132936692</t>
-  </si>
-  <si>
-    <t>132988074</t>
-  </si>
-  <si>
-    <t>133016532</t>
-  </si>
-  <si>
-    <t>133399888</t>
-  </si>
-  <si>
-    <t>133479005</t>
-  </si>
-  <si>
-    <t>133488513</t>
-  </si>
-  <si>
-    <t>133572916</t>
-  </si>
-  <si>
-    <t>133939544</t>
-  </si>
-  <si>
-    <t>134345714</t>
-  </si>
-  <si>
-    <t>134418400</t>
-  </si>
-  <si>
-    <t>134886251</t>
-  </si>
-  <si>
-    <t>135062399</t>
-  </si>
-  <si>
-    <t>135062425</t>
-  </si>
-  <si>
-    <t>135062454</t>
-  </si>
-  <si>
-    <t>135062463</t>
-  </si>
-  <si>
-    <t>135062495</t>
-  </si>
-  <si>
-    <t>135062609</t>
-  </si>
-  <si>
-    <t>135062632</t>
-  </si>
-  <si>
-    <t>135062712</t>
-  </si>
-  <si>
-    <t>135062766</t>
-  </si>
-  <si>
-    <t>135062811</t>
-  </si>
-  <si>
-    <t>135062851</t>
-  </si>
-  <si>
-    <t>135063267</t>
-  </si>
-  <si>
-    <t>135063509</t>
-  </si>
-  <si>
-    <t>135063612</t>
-  </si>
-  <si>
-    <t>135063974</t>
-  </si>
-  <si>
-    <t>135064123</t>
-  </si>
-  <si>
-    <t>135064219</t>
-  </si>
-  <si>
-    <t>135064395</t>
-  </si>
-  <si>
-    <t>135064878</t>
-  </si>
-  <si>
-    <t>135064890</t>
-  </si>
-  <si>
-    <t>135064936</t>
-  </si>
-  <si>
-    <t>135065034</t>
-  </si>
-  <si>
-    <t>135065176</t>
-  </si>
-  <si>
-    <t>135065231</t>
-  </si>
-  <si>
-    <t>135065376</t>
-  </si>
-  <si>
-    <t>135065537</t>
-  </si>
-  <si>
-    <t>135065657</t>
-  </si>
-  <si>
-    <t>135065679</t>
-  </si>
-  <si>
-    <t>135065765</t>
-  </si>
-  <si>
-    <t>135065829</t>
-  </si>
-  <si>
-    <t>135065964</t>
-  </si>
-  <si>
-    <t>135066509</t>
-  </si>
-  <si>
-    <t>135066734</t>
-  </si>
-  <si>
-    <t>135066877</t>
-  </si>
-  <si>
-    <t>135067216</t>
-  </si>
-  <si>
-    <t>135067693</t>
-  </si>
-  <si>
-    <t>135067783</t>
-  </si>
-  <si>
-    <t>135067964</t>
-  </si>
-  <si>
-    <t>135068030</t>
-  </si>
-  <si>
-    <t>135068148</t>
-  </si>
-  <si>
-    <t>135068316</t>
-  </si>
-  <si>
-    <t>135068476</t>
-  </si>
-  <si>
-    <t>135068649</t>
-  </si>
-  <si>
-    <t>135068711</t>
-  </si>
-  <si>
-    <t>135068713</t>
-  </si>
-  <si>
-    <t>135069193</t>
-  </si>
-  <si>
-    <t>135069223</t>
-  </si>
-  <si>
-    <t>135069960</t>
-  </si>
-  <si>
-    <t>135069970</t>
-  </si>
-  <si>
-    <t>135070018</t>
-  </si>
-  <si>
-    <t>135070030</t>
-  </si>
-  <si>
-    <t>135070042</t>
-  </si>
-  <si>
-    <t>135070167</t>
-  </si>
-  <si>
-    <t>135070231</t>
-  </si>
-  <si>
-    <t>135070247</t>
-  </si>
-  <si>
-    <t>135070255</t>
-  </si>
-  <si>
-    <t>135070455</t>
-  </si>
-  <si>
-    <t>135070544</t>
-  </si>
-  <si>
-    <t>135070690</t>
-  </si>
-  <si>
-    <t>135070780</t>
-  </si>
-  <si>
-    <t>135070865</t>
-  </si>
-  <si>
-    <t>135070892</t>
-  </si>
-  <si>
-    <t>135070927</t>
-  </si>
-  <si>
-    <t>135071025</t>
-  </si>
-  <si>
-    <t>135071144</t>
-  </si>
-  <si>
-    <t>135071149</t>
-  </si>
-  <si>
-    <t>135071174</t>
-  </si>
-  <si>
-    <t>135071378</t>
-  </si>
-  <si>
-    <t>135071534</t>
-  </si>
-  <si>
-    <t>135071556</t>
-  </si>
-  <si>
-    <t>135071785</t>
-  </si>
-  <si>
-    <t>135072077</t>
-  </si>
-  <si>
-    <t>135072682</t>
-  </si>
-  <si>
-    <t>135072802</t>
-  </si>
-  <si>
-    <t>135073146</t>
-  </si>
-  <si>
-    <t>135073231</t>
-  </si>
-  <si>
-    <t>135073273</t>
-  </si>
-  <si>
-    <t>135073326</t>
-  </si>
-  <si>
-    <t>135073511</t>
-  </si>
-  <si>
-    <t>135073582</t>
-  </si>
-  <si>
-    <t>135073613</t>
-  </si>
-  <si>
-    <t>135073934</t>
-  </si>
-  <si>
-    <t>135074011</t>
-  </si>
-  <si>
-    <t>135074186</t>
-  </si>
-  <si>
-    <t>135074316</t>
-  </si>
-  <si>
-    <t>135074435</t>
-  </si>
-  <si>
-    <t>135074441</t>
-  </si>
-  <si>
-    <t>135074488</t>
-  </si>
-  <si>
-    <t>135074617</t>
-  </si>
-  <si>
-    <t>135075239</t>
-  </si>
-  <si>
-    <t>135075358</t>
-  </si>
-  <si>
-    <t>135075408</t>
-  </si>
-  <si>
-    <t>135075513</t>
-  </si>
-  <si>
-    <t>135075633</t>
-  </si>
-  <si>
-    <t>135075677</t>
-  </si>
-  <si>
-    <t>135075799</t>
-  </si>
-  <si>
-    <t>135075828</t>
-  </si>
-  <si>
-    <t>135075891</t>
-  </si>
-  <si>
-    <t>135075895</t>
-  </si>
-  <si>
-    <t>135075931</t>
-  </si>
-  <si>
-    <t>135076181</t>
-  </si>
-  <si>
-    <t>135076206</t>
-  </si>
-  <si>
-    <t>135076377</t>
-  </si>
-  <si>
-    <t>135076500</t>
-  </si>
-  <si>
-    <t>135076607</t>
-  </si>
-  <si>
-    <t>135076694</t>
-  </si>
-  <si>
-    <t>135076764</t>
-  </si>
-  <si>
-    <t>135076966</t>
-  </si>
-  <si>
-    <t>135077006</t>
-  </si>
-  <si>
-    <t>135077032</t>
-  </si>
-  <si>
-    <t>135077066</t>
-  </si>
-  <si>
-    <t>135077093</t>
-  </si>
-  <si>
-    <t>135077158</t>
-  </si>
-  <si>
-    <t>135077193</t>
-  </si>
-  <si>
-    <t>135077479</t>
-  </si>
-  <si>
-    <t>135077595</t>
-  </si>
-  <si>
-    <t>135077597</t>
-  </si>
-  <si>
-    <t>135077688</t>
-  </si>
-  <si>
-    <t>135077784</t>
-  </si>
-  <si>
-    <t>135077992</t>
-  </si>
-  <si>
-    <t>135078087</t>
-  </si>
-  <si>
-    <t>135078130</t>
-  </si>
-  <si>
-    <t>135078173</t>
-  </si>
-  <si>
-    <t>135078244</t>
-  </si>
-  <si>
-    <t>135078363</t>
-  </si>
-  <si>
-    <t>135078379</t>
-  </si>
-  <si>
-    <t>135078421</t>
-  </si>
-  <si>
-    <t>135078503</t>
-  </si>
-  <si>
-    <t>135078611</t>
-  </si>
-  <si>
-    <t>135078708</t>
-  </si>
-  <si>
-    <t>135078729</t>
-  </si>
-  <si>
-    <t>135078742</t>
-  </si>
-  <si>
-    <t>135078821</t>
-  </si>
-  <si>
-    <t>135079181</t>
-  </si>
-  <si>
-    <t>135079275</t>
-  </si>
-  <si>
-    <t>135079339</t>
-  </si>
-  <si>
-    <t>135079410</t>
-  </si>
-  <si>
-    <t>135079411</t>
-  </si>
-  <si>
-    <t>135079455</t>
-  </si>
-  <si>
-    <t>135079513</t>
-  </si>
-  <si>
-    <t>135079682</t>
-  </si>
-  <si>
-    <t>135079751</t>
-  </si>
-  <si>
-    <t>135079829</t>
-  </si>
-  <si>
-    <t>135079857</t>
-  </si>
-  <si>
-    <t>135079872</t>
-  </si>
-  <si>
-    <t>135079909</t>
-  </si>
-  <si>
-    <t>135080012</t>
-  </si>
-  <si>
-    <t>135080065</t>
-  </si>
-  <si>
-    <t>135080183</t>
-  </si>
-  <si>
-    <t>135080370</t>
-  </si>
-  <si>
-    <t>135080394</t>
-  </si>
-  <si>
-    <t>135080454</t>
-  </si>
-  <si>
-    <t>135080458</t>
-  </si>
-  <si>
-    <t>135080538</t>
-  </si>
-  <si>
-    <t>135080547</t>
-  </si>
-  <si>
-    <t>135080632</t>
-  </si>
-  <si>
-    <t>135080820</t>
-  </si>
-  <si>
-    <t>135080839</t>
-  </si>
-  <si>
-    <t>135080885</t>
-  </si>
-  <si>
-    <t>135080987</t>
-  </si>
-  <si>
-    <t>135081306</t>
-  </si>
-  <si>
-    <t>135081926</t>
+    <t>130092422</t>
+  </si>
+  <si>
+    <t>130649662</t>
+  </si>
+  <si>
+    <t>130828978</t>
+  </si>
+  <si>
+    <t>131264617</t>
+  </si>
+  <si>
+    <t>131271125</t>
+  </si>
+  <si>
+    <t>131429518</t>
+  </si>
+  <si>
+    <t>131881855</t>
+  </si>
+  <si>
+    <t>131898699</t>
+  </si>
+  <si>
+    <t>131923198</t>
+  </si>
+  <si>
+    <t>132515526</t>
+  </si>
+  <si>
+    <t>132543261</t>
+  </si>
+  <si>
+    <t>132777280</t>
+  </si>
+  <si>
+    <t>132799146</t>
+  </si>
+  <si>
+    <t>132833363</t>
+  </si>
+  <si>
+    <t>133000829</t>
+  </si>
+  <si>
+    <t>133122754</t>
+  </si>
+  <si>
+    <t>133311618</t>
+  </si>
+  <si>
+    <t>133979440</t>
+  </si>
+  <si>
+    <t>134454632</t>
+  </si>
+  <si>
+    <t>134805870</t>
+  </si>
+  <si>
+    <t>135107585</t>
+  </si>
+  <si>
+    <t>135107798</t>
+  </si>
+  <si>
+    <t>135107899</t>
+  </si>
+  <si>
+    <t>135107944</t>
+  </si>
+  <si>
+    <t>135108002</t>
+  </si>
+  <si>
+    <t>135108367</t>
+  </si>
+  <si>
+    <t>135108509</t>
+  </si>
+  <si>
+    <t>135108519</t>
+  </si>
+  <si>
+    <t>135108682</t>
+  </si>
+  <si>
+    <t>135108909</t>
+  </si>
+  <si>
+    <t>135108942</t>
+  </si>
+  <si>
+    <t>135109087</t>
+  </si>
+  <si>
+    <t>135109275</t>
+  </si>
+  <si>
+    <t>135109970</t>
+  </si>
+  <si>
+    <t>135110129</t>
+  </si>
+  <si>
+    <t>135110222</t>
+  </si>
+  <si>
+    <t>135110434</t>
+  </si>
+  <si>
+    <t>135110547</t>
+  </si>
+  <si>
+    <t>135110929</t>
+  </si>
+  <si>
+    <t>135110979</t>
+  </si>
+  <si>
+    <t>135111061</t>
+  </si>
+  <si>
+    <t>135111267</t>
+  </si>
+  <si>
+    <t>135111542</t>
+  </si>
+  <si>
+    <t>135111547</t>
+  </si>
+  <si>
+    <t>135111704</t>
+  </si>
+  <si>
+    <t>135111738</t>
+  </si>
+  <si>
+    <t>135111759</t>
+  </si>
+  <si>
+    <t>135112004</t>
+  </si>
+  <si>
+    <t>135112106</t>
+  </si>
+  <si>
+    <t>135112276</t>
+  </si>
+  <si>
+    <t>135112447</t>
+  </si>
+  <si>
+    <t>135112571</t>
+  </si>
+  <si>
+    <t>135112764</t>
+  </si>
+  <si>
+    <t>135112863</t>
+  </si>
+  <si>
+    <t>135112866</t>
+  </si>
+  <si>
+    <t>135112910</t>
+  </si>
+  <si>
+    <t>135112972</t>
+  </si>
+  <si>
+    <t>135113255</t>
+  </si>
+  <si>
+    <t>135113402</t>
+  </si>
+  <si>
+    <t>135113414</t>
+  </si>
+  <si>
+    <t>135113420</t>
+  </si>
+  <si>
+    <t>135113678</t>
+  </si>
+  <si>
+    <t>135113748</t>
+  </si>
+  <si>
+    <t>135113854</t>
+  </si>
+  <si>
+    <t>135113855</t>
+  </si>
+  <si>
+    <t>135113870</t>
+  </si>
+  <si>
+    <t>135113890</t>
+  </si>
+  <si>
+    <t>135113932</t>
+  </si>
+  <si>
+    <t>135114065</t>
+  </si>
+  <si>
+    <t>135114243</t>
+  </si>
+  <si>
+    <t>135114251</t>
+  </si>
+  <si>
+    <t>135114260</t>
+  </si>
+  <si>
+    <t>135114351</t>
+  </si>
+  <si>
+    <t>135114486</t>
+  </si>
+  <si>
+    <t>135114488</t>
+  </si>
+  <si>
+    <t>135114616</t>
+  </si>
+  <si>
+    <t>135114641</t>
+  </si>
+  <si>
+    <t>135114969</t>
+  </si>
+  <si>
+    <t>135115214</t>
+  </si>
+  <si>
+    <t>135115386</t>
+  </si>
+  <si>
+    <t>135115416</t>
+  </si>
+  <si>
+    <t>135115553</t>
+  </si>
+  <si>
+    <t>135115747</t>
+  </si>
+  <si>
+    <t>135116173</t>
+  </si>
+  <si>
+    <t>135116677</t>
+  </si>
+  <si>
+    <t>135116720</t>
+  </si>
+  <si>
+    <t>135116830</t>
+  </si>
+  <si>
+    <t>135117158</t>
+  </si>
+  <si>
+    <t>135117275</t>
+  </si>
+  <si>
+    <t>135117297</t>
+  </si>
+  <si>
+    <t>135117442</t>
+  </si>
+  <si>
+    <t>135117495</t>
+  </si>
+  <si>
+    <t>135117564</t>
+  </si>
+  <si>
+    <t>135117638</t>
+  </si>
+  <si>
+    <t>135117755</t>
+  </si>
+  <si>
+    <t>135117894</t>
+  </si>
+  <si>
+    <t>135117934</t>
+  </si>
+  <si>
+    <t>135117937</t>
+  </si>
+  <si>
+    <t>135117964</t>
+  </si>
+  <si>
+    <t>135118015</t>
+  </si>
+  <si>
+    <t>135118072</t>
+  </si>
+  <si>
+    <t>135118173</t>
+  </si>
+  <si>
+    <t>135118216</t>
+  </si>
+  <si>
+    <t>135118595</t>
+  </si>
+  <si>
+    <t>135118678</t>
+  </si>
+  <si>
+    <t>135118875</t>
+  </si>
+  <si>
+    <t>135118932</t>
+  </si>
+  <si>
+    <t>135118940</t>
+  </si>
+  <si>
+    <t>135118989</t>
+  </si>
+  <si>
+    <t>135119105</t>
+  </si>
+  <si>
+    <t>135119169</t>
+  </si>
+  <si>
+    <t>135119464</t>
+  </si>
+  <si>
+    <t>135119609</t>
+  </si>
+  <si>
+    <t>135119649</t>
+  </si>
+  <si>
+    <t>135119853</t>
+  </si>
+  <si>
+    <t>135120101</t>
+  </si>
+  <si>
+    <t>135120758</t>
+  </si>
+  <si>
+    <t>135120804</t>
+  </si>
+  <si>
+    <t>135120837</t>
+  </si>
+  <si>
+    <t>135120839</t>
+  </si>
+  <si>
+    <t>135121002</t>
+  </si>
+  <si>
+    <t>135121067</t>
+  </si>
+  <si>
+    <t>135121082</t>
+  </si>
+  <si>
+    <t>135121201</t>
+  </si>
+  <si>
+    <t>135121438</t>
+  </si>
+  <si>
+    <t>135121469</t>
+  </si>
+  <si>
+    <t>135121597</t>
+  </si>
+  <si>
+    <t>135121608</t>
+  </si>
+  <si>
+    <t>135121641</t>
+  </si>
+  <si>
+    <t>135121674</t>
+  </si>
+  <si>
+    <t>135121845</t>
+  </si>
+  <si>
+    <t>135121933</t>
+  </si>
+  <si>
+    <t>135121940</t>
+  </si>
+  <si>
+    <t>135121966</t>
+  </si>
+  <si>
+    <t>135122036</t>
+  </si>
+  <si>
+    <t>135122163</t>
+  </si>
+  <si>
+    <t>135122357</t>
+  </si>
+  <si>
+    <t>135122382</t>
+  </si>
+  <si>
+    <t>135122669</t>
+  </si>
+  <si>
+    <t>135122863</t>
+  </si>
+  <si>
+    <t>135122892</t>
+  </si>
+  <si>
+    <t>135122897</t>
+  </si>
+  <si>
+    <t>135122979</t>
+  </si>
+  <si>
+    <t>135123025</t>
+  </si>
+  <si>
+    <t>135123048</t>
+  </si>
+  <si>
+    <t>135123083</t>
+  </si>
+  <si>
+    <t>135123133</t>
+  </si>
+  <si>
+    <t>135123208</t>
+  </si>
+  <si>
+    <t>135123403</t>
+  </si>
+  <si>
+    <t>135123442</t>
+  </si>
+  <si>
+    <t>135123549</t>
+  </si>
+  <si>
+    <t>135123572</t>
+  </si>
+  <si>
+    <t>135123608</t>
+  </si>
+  <si>
+    <t>135123676</t>
+  </si>
+  <si>
+    <t>135123737</t>
+  </si>
+  <si>
+    <t>135123767</t>
+  </si>
+  <si>
+    <t>135123968</t>
+  </si>
+  <si>
+    <t>135124018</t>
+  </si>
+  <si>
+    <t>135124112</t>
+  </si>
+  <si>
+    <t>135124148</t>
+  </si>
+  <si>
+    <t>135124268</t>
+  </si>
+  <si>
+    <t>135124341</t>
+  </si>
+  <si>
+    <t>135124534</t>
+  </si>
+  <si>
+    <t>135124742</t>
+  </si>
+  <si>
+    <t>135124892</t>
+  </si>
+  <si>
+    <t>135124923</t>
+  </si>
+  <si>
+    <t>135125477</t>
+  </si>
+  <si>
+    <t>135125509</t>
+  </si>
+  <si>
+    <t>135125663</t>
+  </si>
+  <si>
+    <t>135125933</t>
+  </si>
+  <si>
+    <t>135125965</t>
+  </si>
+  <si>
+    <t>135125998</t>
+  </si>
+  <si>
+    <t>135126048</t>
+  </si>
+  <si>
+    <t>135126101</t>
+  </si>
+  <si>
+    <t>135126106</t>
+  </si>
+  <si>
+    <t>135126228</t>
   </si>
 </sst>
 </file>
@@ -990,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C182"/>
+  <dimension ref="A1:C177"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2946,63 +2931,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C182" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C177" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF0614D-7BFF-41FA-97CD-07706F68F7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0C41FB-7350-4F9C-BE76-421C1F700216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="188">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,532 +45,553 @@
     <t>.</t>
   </si>
   <si>
-    <t>130092422</t>
-  </si>
-  <si>
-    <t>130649662</t>
-  </si>
-  <si>
-    <t>130828978</t>
-  </si>
-  <si>
-    <t>131264617</t>
-  </si>
-  <si>
-    <t>131271125</t>
-  </si>
-  <si>
-    <t>131429518</t>
-  </si>
-  <si>
-    <t>131881855</t>
-  </si>
-  <si>
-    <t>131898699</t>
-  </si>
-  <si>
-    <t>131923198</t>
-  </si>
-  <si>
-    <t>132515526</t>
-  </si>
-  <si>
-    <t>132543261</t>
-  </si>
-  <si>
-    <t>132777280</t>
-  </si>
-  <si>
-    <t>132799146</t>
-  </si>
-  <si>
-    <t>132833363</t>
-  </si>
-  <si>
-    <t>133000829</t>
-  </si>
-  <si>
-    <t>133122754</t>
-  </si>
-  <si>
-    <t>133311618</t>
-  </si>
-  <si>
-    <t>133979440</t>
-  </si>
-  <si>
-    <t>134454632</t>
-  </si>
-  <si>
-    <t>134805870</t>
-  </si>
-  <si>
-    <t>135107585</t>
-  </si>
-  <si>
-    <t>135107798</t>
-  </si>
-  <si>
-    <t>135107899</t>
-  </si>
-  <si>
-    <t>135107944</t>
-  </si>
-  <si>
-    <t>135108002</t>
-  </si>
-  <si>
-    <t>135108367</t>
-  </si>
-  <si>
-    <t>135108509</t>
-  </si>
-  <si>
-    <t>135108519</t>
-  </si>
-  <si>
-    <t>135108682</t>
-  </si>
-  <si>
-    <t>135108909</t>
-  </si>
-  <si>
-    <t>135108942</t>
-  </si>
-  <si>
-    <t>135109087</t>
-  </si>
-  <si>
-    <t>135109275</t>
-  </si>
-  <si>
-    <t>135109970</t>
-  </si>
-  <si>
-    <t>135110129</t>
-  </si>
-  <si>
-    <t>135110222</t>
-  </si>
-  <si>
-    <t>135110434</t>
-  </si>
-  <si>
-    <t>135110547</t>
-  </si>
-  <si>
-    <t>135110929</t>
-  </si>
-  <si>
-    <t>135110979</t>
-  </si>
-  <si>
-    <t>135111061</t>
-  </si>
-  <si>
-    <t>135111267</t>
-  </si>
-  <si>
-    <t>135111542</t>
-  </si>
-  <si>
-    <t>135111547</t>
-  </si>
-  <si>
-    <t>135111704</t>
-  </si>
-  <si>
-    <t>135111738</t>
-  </si>
-  <si>
-    <t>135111759</t>
-  </si>
-  <si>
-    <t>135112004</t>
-  </si>
-  <si>
-    <t>135112106</t>
-  </si>
-  <si>
-    <t>135112276</t>
-  </si>
-  <si>
-    <t>135112447</t>
-  </si>
-  <si>
-    <t>135112571</t>
-  </si>
-  <si>
-    <t>135112764</t>
-  </si>
-  <si>
-    <t>135112863</t>
-  </si>
-  <si>
-    <t>135112866</t>
-  </si>
-  <si>
-    <t>135112910</t>
-  </si>
-  <si>
-    <t>135112972</t>
-  </si>
-  <si>
-    <t>135113255</t>
-  </si>
-  <si>
-    <t>135113402</t>
-  </si>
-  <si>
-    <t>135113414</t>
-  </si>
-  <si>
-    <t>135113420</t>
-  </si>
-  <si>
-    <t>135113678</t>
-  </si>
-  <si>
-    <t>135113748</t>
-  </si>
-  <si>
-    <t>135113854</t>
-  </si>
-  <si>
-    <t>135113855</t>
-  </si>
-  <si>
-    <t>135113870</t>
-  </si>
-  <si>
-    <t>135113890</t>
-  </si>
-  <si>
-    <t>135113932</t>
-  </si>
-  <si>
-    <t>135114065</t>
-  </si>
-  <si>
-    <t>135114243</t>
-  </si>
-  <si>
-    <t>135114251</t>
-  </si>
-  <si>
-    <t>135114260</t>
-  </si>
-  <si>
-    <t>135114351</t>
-  </si>
-  <si>
-    <t>135114486</t>
-  </si>
-  <si>
-    <t>135114488</t>
-  </si>
-  <si>
-    <t>135114616</t>
-  </si>
-  <si>
-    <t>135114641</t>
-  </si>
-  <si>
-    <t>135114969</t>
-  </si>
-  <si>
-    <t>135115214</t>
-  </si>
-  <si>
-    <t>135115386</t>
-  </si>
-  <si>
-    <t>135115416</t>
-  </si>
-  <si>
-    <t>135115553</t>
-  </si>
-  <si>
-    <t>135115747</t>
-  </si>
-  <si>
-    <t>135116173</t>
-  </si>
-  <si>
-    <t>135116677</t>
-  </si>
-  <si>
-    <t>135116720</t>
-  </si>
-  <si>
-    <t>135116830</t>
-  </si>
-  <si>
-    <t>135117158</t>
-  </si>
-  <si>
-    <t>135117275</t>
-  </si>
-  <si>
-    <t>135117297</t>
-  </si>
-  <si>
-    <t>135117442</t>
-  </si>
-  <si>
-    <t>135117495</t>
-  </si>
-  <si>
-    <t>135117564</t>
-  </si>
-  <si>
-    <t>135117638</t>
-  </si>
-  <si>
-    <t>135117755</t>
-  </si>
-  <si>
-    <t>135117894</t>
-  </si>
-  <si>
-    <t>135117934</t>
-  </si>
-  <si>
-    <t>135117937</t>
-  </si>
-  <si>
-    <t>135117964</t>
-  </si>
-  <si>
-    <t>135118015</t>
-  </si>
-  <si>
-    <t>135118072</t>
-  </si>
-  <si>
-    <t>135118173</t>
-  </si>
-  <si>
-    <t>135118216</t>
-  </si>
-  <si>
-    <t>135118595</t>
-  </si>
-  <si>
-    <t>135118678</t>
-  </si>
-  <si>
-    <t>135118875</t>
-  </si>
-  <si>
-    <t>135118932</t>
-  </si>
-  <si>
-    <t>135118940</t>
-  </si>
-  <si>
-    <t>135118989</t>
-  </si>
-  <si>
-    <t>135119105</t>
-  </si>
-  <si>
-    <t>135119169</t>
-  </si>
-  <si>
-    <t>135119464</t>
-  </si>
-  <si>
-    <t>135119609</t>
-  </si>
-  <si>
-    <t>135119649</t>
-  </si>
-  <si>
-    <t>135119853</t>
-  </si>
-  <si>
-    <t>135120101</t>
-  </si>
-  <si>
-    <t>135120758</t>
-  </si>
-  <si>
-    <t>135120804</t>
-  </si>
-  <si>
-    <t>135120837</t>
-  </si>
-  <si>
-    <t>135120839</t>
-  </si>
-  <si>
-    <t>135121002</t>
-  </si>
-  <si>
-    <t>135121067</t>
-  </si>
-  <si>
-    <t>135121082</t>
-  </si>
-  <si>
-    <t>135121201</t>
-  </si>
-  <si>
-    <t>135121438</t>
-  </si>
-  <si>
-    <t>135121469</t>
-  </si>
-  <si>
-    <t>135121597</t>
-  </si>
-  <si>
-    <t>135121608</t>
-  </si>
-  <si>
-    <t>135121641</t>
-  </si>
-  <si>
-    <t>135121674</t>
-  </si>
-  <si>
-    <t>135121845</t>
-  </si>
-  <si>
-    <t>135121933</t>
-  </si>
-  <si>
-    <t>135121940</t>
-  </si>
-  <si>
-    <t>135121966</t>
-  </si>
-  <si>
-    <t>135122036</t>
-  </si>
-  <si>
-    <t>135122163</t>
-  </si>
-  <si>
-    <t>135122357</t>
-  </si>
-  <si>
-    <t>135122382</t>
-  </si>
-  <si>
-    <t>135122669</t>
-  </si>
-  <si>
-    <t>135122863</t>
-  </si>
-  <si>
-    <t>135122892</t>
-  </si>
-  <si>
-    <t>135122897</t>
-  </si>
-  <si>
-    <t>135122979</t>
-  </si>
-  <si>
-    <t>135123025</t>
-  </si>
-  <si>
-    <t>135123048</t>
-  </si>
-  <si>
-    <t>135123083</t>
-  </si>
-  <si>
-    <t>135123133</t>
-  </si>
-  <si>
-    <t>135123208</t>
-  </si>
-  <si>
-    <t>135123403</t>
-  </si>
-  <si>
-    <t>135123442</t>
-  </si>
-  <si>
-    <t>135123549</t>
-  </si>
-  <si>
-    <t>135123572</t>
-  </si>
-  <si>
-    <t>135123608</t>
-  </si>
-  <si>
-    <t>135123676</t>
-  </si>
-  <si>
-    <t>135123737</t>
-  </si>
-  <si>
-    <t>135123767</t>
-  </si>
-  <si>
-    <t>135123968</t>
-  </si>
-  <si>
-    <t>135124018</t>
-  </si>
-  <si>
-    <t>135124112</t>
-  </si>
-  <si>
-    <t>135124148</t>
-  </si>
-  <si>
-    <t>135124268</t>
-  </si>
-  <si>
-    <t>135124341</t>
-  </si>
-  <si>
-    <t>135124534</t>
-  </si>
-  <si>
-    <t>135124742</t>
-  </si>
-  <si>
-    <t>135124892</t>
-  </si>
-  <si>
-    <t>135124923</t>
-  </si>
-  <si>
-    <t>135125477</t>
-  </si>
-  <si>
-    <t>135125509</t>
-  </si>
-  <si>
-    <t>135125663</t>
-  </si>
-  <si>
-    <t>135125933</t>
-  </si>
-  <si>
-    <t>135125965</t>
-  </si>
-  <si>
-    <t>135125998</t>
-  </si>
-  <si>
-    <t>135126048</t>
-  </si>
-  <si>
-    <t>135126101</t>
-  </si>
-  <si>
-    <t>135126106</t>
-  </si>
-  <si>
-    <t>135126228</t>
+    <t>130293149</t>
+  </si>
+  <si>
+    <t>130391165</t>
+  </si>
+  <si>
+    <t>130484028</t>
+  </si>
+  <si>
+    <t>130798550</t>
+  </si>
+  <si>
+    <t>130972422</t>
+  </si>
+  <si>
+    <t>131102859</t>
+  </si>
+  <si>
+    <t>131510131</t>
+  </si>
+  <si>
+    <t>132131302</t>
+  </si>
+  <si>
+    <t>132189672</t>
+  </si>
+  <si>
+    <t>132289061</t>
+  </si>
+  <si>
+    <t>132702092</t>
+  </si>
+  <si>
+    <t>132991392</t>
+  </si>
+  <si>
+    <t>133060437</t>
+  </si>
+  <si>
+    <t>133987435</t>
+  </si>
+  <si>
+    <t>134562336</t>
+  </si>
+  <si>
+    <t>134595149</t>
+  </si>
+  <si>
+    <t>135126288</t>
+  </si>
+  <si>
+    <t>135126339</t>
+  </si>
+  <si>
+    <t>135126971</t>
+  </si>
+  <si>
+    <t>135127081</t>
+  </si>
+  <si>
+    <t>135127257</t>
+  </si>
+  <si>
+    <t>135127470</t>
+  </si>
+  <si>
+    <t>135127916</t>
+  </si>
+  <si>
+    <t>135128001</t>
+  </si>
+  <si>
+    <t>135128447</t>
+  </si>
+  <si>
+    <t>135128478</t>
+  </si>
+  <si>
+    <t>135128652</t>
+  </si>
+  <si>
+    <t>135128663</t>
+  </si>
+  <si>
+    <t>135129012</t>
+  </si>
+  <si>
+    <t>135129342</t>
+  </si>
+  <si>
+    <t>135129502</t>
+  </si>
+  <si>
+    <t>135129639</t>
+  </si>
+  <si>
+    <t>135129674</t>
+  </si>
+  <si>
+    <t>135129838</t>
+  </si>
+  <si>
+    <t>135129903</t>
+  </si>
+  <si>
+    <t>135129910</t>
+  </si>
+  <si>
+    <t>135129934</t>
+  </si>
+  <si>
+    <t>135130128</t>
+  </si>
+  <si>
+    <t>135130318</t>
+  </si>
+  <si>
+    <t>135130517</t>
+  </si>
+  <si>
+    <t>135131175</t>
+  </si>
+  <si>
+    <t>135131204</t>
+  </si>
+  <si>
+    <t>135131256</t>
+  </si>
+  <si>
+    <t>135131538</t>
+  </si>
+  <si>
+    <t>135131552</t>
+  </si>
+  <si>
+    <t>135131570</t>
+  </si>
+  <si>
+    <t>135131743</t>
+  </si>
+  <si>
+    <t>135131766</t>
+  </si>
+  <si>
+    <t>135131790</t>
+  </si>
+  <si>
+    <t>135131839</t>
+  </si>
+  <si>
+    <t>135131897</t>
+  </si>
+  <si>
+    <t>135132200</t>
+  </si>
+  <si>
+    <t>135132220</t>
+  </si>
+  <si>
+    <t>135132294</t>
+  </si>
+  <si>
+    <t>135132321</t>
+  </si>
+  <si>
+    <t>135132480</t>
+  </si>
+  <si>
+    <t>135132507</t>
+  </si>
+  <si>
+    <t>135132613</t>
+  </si>
+  <si>
+    <t>135132661</t>
+  </si>
+  <si>
+    <t>135132869</t>
+  </si>
+  <si>
+    <t>135132937</t>
+  </si>
+  <si>
+    <t>135132944</t>
+  </si>
+  <si>
+    <t>135133252</t>
+  </si>
+  <si>
+    <t>135133332</t>
+  </si>
+  <si>
+    <t>135133722</t>
+  </si>
+  <si>
+    <t>135133820</t>
+  </si>
+  <si>
+    <t>135133869</t>
+  </si>
+  <si>
+    <t>135133874</t>
+  </si>
+  <si>
+    <t>135133878</t>
+  </si>
+  <si>
+    <t>135133947</t>
+  </si>
+  <si>
+    <t>135133986</t>
+  </si>
+  <si>
+    <t>135134019</t>
+  </si>
+  <si>
+    <t>135134236</t>
+  </si>
+  <si>
+    <t>135134249</t>
+  </si>
+  <si>
+    <t>135134466</t>
+  </si>
+  <si>
+    <t>135134503</t>
+  </si>
+  <si>
+    <t>135134514</t>
+  </si>
+  <si>
+    <t>135134870</t>
+  </si>
+  <si>
+    <t>135135054</t>
+  </si>
+  <si>
+    <t>135135418</t>
+  </si>
+  <si>
+    <t>135135508</t>
+  </si>
+  <si>
+    <t>135135682</t>
+  </si>
+  <si>
+    <t>135135779</t>
+  </si>
+  <si>
+    <t>135135896</t>
+  </si>
+  <si>
+    <t>135135976</t>
+  </si>
+  <si>
+    <t>135136044</t>
+  </si>
+  <si>
+    <t>135136342</t>
+  </si>
+  <si>
+    <t>135136647</t>
+  </si>
+  <si>
+    <t>135136668</t>
+  </si>
+  <si>
+    <t>135136737</t>
+  </si>
+  <si>
+    <t>135136757</t>
+  </si>
+  <si>
+    <t>135136759</t>
+  </si>
+  <si>
+    <t>135136881</t>
+  </si>
+  <si>
+    <t>135136956</t>
+  </si>
+  <si>
+    <t>135136993</t>
+  </si>
+  <si>
+    <t>135137112</t>
+  </si>
+  <si>
+    <t>135137142</t>
+  </si>
+  <si>
+    <t>135137182</t>
+  </si>
+  <si>
+    <t>135137183</t>
+  </si>
+  <si>
+    <t>135137265</t>
+  </si>
+  <si>
+    <t>135137337</t>
+  </si>
+  <si>
+    <t>135137564</t>
+  </si>
+  <si>
+    <t>135137606</t>
+  </si>
+  <si>
+    <t>135137611</t>
+  </si>
+  <si>
+    <t>135138008</t>
+  </si>
+  <si>
+    <t>135138015</t>
+  </si>
+  <si>
+    <t>135138059</t>
+  </si>
+  <si>
+    <t>135138084</t>
+  </si>
+  <si>
+    <t>135138142</t>
+  </si>
+  <si>
+    <t>135138201</t>
+  </si>
+  <si>
+    <t>135138477</t>
+  </si>
+  <si>
+    <t>135138697</t>
+  </si>
+  <si>
+    <t>135138751</t>
+  </si>
+  <si>
+    <t>135138801</t>
+  </si>
+  <si>
+    <t>135138809</t>
+  </si>
+  <si>
+    <t>135138811</t>
+  </si>
+  <si>
+    <t>135138988</t>
+  </si>
+  <si>
+    <t>135139179</t>
+  </si>
+  <si>
+    <t>135139265</t>
+  </si>
+  <si>
+    <t>135139614</t>
+  </si>
+  <si>
+    <t>135139622</t>
+  </si>
+  <si>
+    <t>135139861</t>
+  </si>
+  <si>
+    <t>135139953</t>
+  </si>
+  <si>
+    <t>135140141</t>
+  </si>
+  <si>
+    <t>135140181</t>
+  </si>
+  <si>
+    <t>135140376</t>
+  </si>
+  <si>
+    <t>135140566</t>
+  </si>
+  <si>
+    <t>135140711</t>
+  </si>
+  <si>
+    <t>135140875</t>
+  </si>
+  <si>
+    <t>135140924</t>
+  </si>
+  <si>
+    <t>135140967</t>
+  </si>
+  <si>
+    <t>135141148</t>
+  </si>
+  <si>
+    <t>135141278</t>
+  </si>
+  <si>
+    <t>135141304</t>
+  </si>
+  <si>
+    <t>135141590</t>
+  </si>
+  <si>
+    <t>135141681</t>
+  </si>
+  <si>
+    <t>135141813</t>
+  </si>
+  <si>
+    <t>135141911</t>
+  </si>
+  <si>
+    <t>135142007</t>
+  </si>
+  <si>
+    <t>135142037</t>
+  </si>
+  <si>
+    <t>135142226</t>
+  </si>
+  <si>
+    <t>135142275</t>
+  </si>
+  <si>
+    <t>135142378</t>
+  </si>
+  <si>
+    <t>135142729</t>
+  </si>
+  <si>
+    <t>135142886</t>
+  </si>
+  <si>
+    <t>135142892</t>
+  </si>
+  <si>
+    <t>135142955</t>
+  </si>
+  <si>
+    <t>135143047</t>
+  </si>
+  <si>
+    <t>135143152</t>
+  </si>
+  <si>
+    <t>135143239</t>
+  </si>
+  <si>
+    <t>135143349</t>
+  </si>
+  <si>
+    <t>135143378</t>
+  </si>
+  <si>
+    <t>135143415</t>
+  </si>
+  <si>
+    <t>135143557</t>
+  </si>
+  <si>
+    <t>135143600</t>
+  </si>
+  <si>
+    <t>135143615</t>
+  </si>
+  <si>
+    <t>135143624</t>
+  </si>
+  <si>
+    <t>135143923</t>
+  </si>
+  <si>
+    <t>135144041</t>
+  </si>
+  <si>
+    <t>135144071</t>
+  </si>
+  <si>
+    <t>135144077</t>
+  </si>
+  <si>
+    <t>135144107</t>
+  </si>
+  <si>
+    <t>135144132</t>
+  </si>
+  <si>
+    <t>135144174</t>
+  </si>
+  <si>
+    <t>135144252</t>
+  </si>
+  <si>
+    <t>135144450</t>
+  </si>
+  <si>
+    <t>135144530</t>
+  </si>
+  <si>
+    <t>135144544</t>
+  </si>
+  <si>
+    <t>135144554</t>
+  </si>
+  <si>
+    <t>135144678</t>
+  </si>
+  <si>
+    <t>135144707</t>
+  </si>
+  <si>
+    <t>135144736</t>
+  </si>
+  <si>
+    <t>135144753</t>
+  </si>
+  <si>
+    <t>135144858</t>
+  </si>
+  <si>
+    <t>135144874</t>
+  </si>
+  <si>
+    <t>135145743</t>
+  </si>
+  <si>
+    <t>135145791</t>
+  </si>
+  <si>
+    <t>135146024</t>
+  </si>
+  <si>
+    <t>135146073</t>
+  </si>
+  <si>
+    <t>135146124</t>
+  </si>
+  <si>
+    <t>135146207</t>
+  </si>
+  <si>
+    <t>135146317</t>
+  </si>
+  <si>
+    <t>135146372</t>
   </si>
 </sst>
 </file>
@@ -975,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:C184"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2931,6 +2952,62 @@
         <v>4</v>
       </c>
     </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C177" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0C41FB-7350-4F9C-BE76-421C1F700216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A37959-006C-43D0-A1D6-45306C7402A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="187">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,553 +45,550 @@
     <t>.</t>
   </si>
   <si>
-    <t>130293149</t>
-  </si>
-  <si>
-    <t>130391165</t>
-  </si>
-  <si>
-    <t>130484028</t>
-  </si>
-  <si>
-    <t>130798550</t>
-  </si>
-  <si>
-    <t>130972422</t>
-  </si>
-  <si>
-    <t>131102859</t>
-  </si>
-  <si>
-    <t>131510131</t>
-  </si>
-  <si>
-    <t>132131302</t>
-  </si>
-  <si>
-    <t>132189672</t>
-  </si>
-  <si>
-    <t>132289061</t>
-  </si>
-  <si>
-    <t>132702092</t>
-  </si>
-  <si>
-    <t>132991392</t>
-  </si>
-  <si>
-    <t>133060437</t>
-  </si>
-  <si>
-    <t>133987435</t>
-  </si>
-  <si>
-    <t>134562336</t>
-  </si>
-  <si>
-    <t>134595149</t>
-  </si>
-  <si>
-    <t>135126288</t>
-  </si>
-  <si>
-    <t>135126339</t>
-  </si>
-  <si>
-    <t>135126971</t>
-  </si>
-  <si>
-    <t>135127081</t>
-  </si>
-  <si>
-    <t>135127257</t>
-  </si>
-  <si>
-    <t>135127470</t>
-  </si>
-  <si>
-    <t>135127916</t>
-  </si>
-  <si>
-    <t>135128001</t>
-  </si>
-  <si>
-    <t>135128447</t>
-  </si>
-  <si>
-    <t>135128478</t>
-  </si>
-  <si>
-    <t>135128652</t>
-  </si>
-  <si>
-    <t>135128663</t>
-  </si>
-  <si>
-    <t>135129012</t>
-  </si>
-  <si>
-    <t>135129342</t>
-  </si>
-  <si>
-    <t>135129502</t>
-  </si>
-  <si>
-    <t>135129639</t>
-  </si>
-  <si>
-    <t>135129674</t>
-  </si>
-  <si>
-    <t>135129838</t>
-  </si>
-  <si>
-    <t>135129903</t>
-  </si>
-  <si>
-    <t>135129910</t>
-  </si>
-  <si>
-    <t>135129934</t>
-  </si>
-  <si>
-    <t>135130128</t>
-  </si>
-  <si>
-    <t>135130318</t>
-  </si>
-  <si>
-    <t>135130517</t>
-  </si>
-  <si>
-    <t>135131175</t>
-  </si>
-  <si>
-    <t>135131204</t>
-  </si>
-  <si>
-    <t>135131256</t>
-  </si>
-  <si>
-    <t>135131538</t>
-  </si>
-  <si>
-    <t>135131552</t>
-  </si>
-  <si>
-    <t>135131570</t>
-  </si>
-  <si>
-    <t>135131743</t>
-  </si>
-  <si>
-    <t>135131766</t>
-  </si>
-  <si>
-    <t>135131790</t>
-  </si>
-  <si>
-    <t>135131839</t>
-  </si>
-  <si>
-    <t>135131897</t>
-  </si>
-  <si>
-    <t>135132200</t>
-  </si>
-  <si>
-    <t>135132220</t>
-  </si>
-  <si>
-    <t>135132294</t>
-  </si>
-  <si>
-    <t>135132321</t>
-  </si>
-  <si>
-    <t>135132480</t>
-  </si>
-  <si>
-    <t>135132507</t>
-  </si>
-  <si>
-    <t>135132613</t>
-  </si>
-  <si>
-    <t>135132661</t>
-  </si>
-  <si>
-    <t>135132869</t>
-  </si>
-  <si>
-    <t>135132937</t>
-  </si>
-  <si>
-    <t>135132944</t>
-  </si>
-  <si>
-    <t>135133252</t>
-  </si>
-  <si>
-    <t>135133332</t>
-  </si>
-  <si>
-    <t>135133722</t>
-  </si>
-  <si>
-    <t>135133820</t>
-  </si>
-  <si>
-    <t>135133869</t>
-  </si>
-  <si>
-    <t>135133874</t>
-  </si>
-  <si>
-    <t>135133878</t>
-  </si>
-  <si>
-    <t>135133947</t>
-  </si>
-  <si>
-    <t>135133986</t>
-  </si>
-  <si>
-    <t>135134019</t>
-  </si>
-  <si>
-    <t>135134236</t>
-  </si>
-  <si>
-    <t>135134249</t>
-  </si>
-  <si>
-    <t>135134466</t>
-  </si>
-  <si>
-    <t>135134503</t>
-  </si>
-  <si>
-    <t>135134514</t>
-  </si>
-  <si>
-    <t>135134870</t>
-  </si>
-  <si>
-    <t>135135054</t>
-  </si>
-  <si>
-    <t>135135418</t>
-  </si>
-  <si>
-    <t>135135508</t>
-  </si>
-  <si>
-    <t>135135682</t>
-  </si>
-  <si>
-    <t>135135779</t>
-  </si>
-  <si>
-    <t>135135896</t>
-  </si>
-  <si>
-    <t>135135976</t>
-  </si>
-  <si>
-    <t>135136044</t>
-  </si>
-  <si>
-    <t>135136342</t>
-  </si>
-  <si>
-    <t>135136647</t>
-  </si>
-  <si>
-    <t>135136668</t>
-  </si>
-  <si>
-    <t>135136737</t>
-  </si>
-  <si>
-    <t>135136757</t>
-  </si>
-  <si>
-    <t>135136759</t>
-  </si>
-  <si>
-    <t>135136881</t>
-  </si>
-  <si>
-    <t>135136956</t>
-  </si>
-  <si>
-    <t>135136993</t>
-  </si>
-  <si>
-    <t>135137112</t>
-  </si>
-  <si>
-    <t>135137142</t>
-  </si>
-  <si>
-    <t>135137182</t>
-  </si>
-  <si>
-    <t>135137183</t>
-  </si>
-  <si>
-    <t>135137265</t>
-  </si>
-  <si>
-    <t>135137337</t>
-  </si>
-  <si>
-    <t>135137564</t>
-  </si>
-  <si>
-    <t>135137606</t>
-  </si>
-  <si>
-    <t>135137611</t>
-  </si>
-  <si>
-    <t>135138008</t>
-  </si>
-  <si>
-    <t>135138015</t>
-  </si>
-  <si>
-    <t>135138059</t>
-  </si>
-  <si>
-    <t>135138084</t>
-  </si>
-  <si>
-    <t>135138142</t>
-  </si>
-  <si>
-    <t>135138201</t>
-  </si>
-  <si>
-    <t>135138477</t>
-  </si>
-  <si>
-    <t>135138697</t>
-  </si>
-  <si>
-    <t>135138751</t>
-  </si>
-  <si>
-    <t>135138801</t>
-  </si>
-  <si>
-    <t>135138809</t>
-  </si>
-  <si>
-    <t>135138811</t>
-  </si>
-  <si>
-    <t>135138988</t>
-  </si>
-  <si>
-    <t>135139179</t>
-  </si>
-  <si>
-    <t>135139265</t>
-  </si>
-  <si>
-    <t>135139614</t>
-  </si>
-  <si>
-    <t>135139622</t>
-  </si>
-  <si>
-    <t>135139861</t>
-  </si>
-  <si>
-    <t>135139953</t>
-  </si>
-  <si>
-    <t>135140141</t>
-  </si>
-  <si>
-    <t>135140181</t>
-  </si>
-  <si>
-    <t>135140376</t>
-  </si>
-  <si>
-    <t>135140566</t>
-  </si>
-  <si>
-    <t>135140711</t>
-  </si>
-  <si>
-    <t>135140875</t>
-  </si>
-  <si>
-    <t>135140924</t>
-  </si>
-  <si>
-    <t>135140967</t>
-  </si>
-  <si>
-    <t>135141148</t>
-  </si>
-  <si>
-    <t>135141278</t>
-  </si>
-  <si>
-    <t>135141304</t>
-  </si>
-  <si>
-    <t>135141590</t>
-  </si>
-  <si>
-    <t>135141681</t>
-  </si>
-  <si>
-    <t>135141813</t>
-  </si>
-  <si>
-    <t>135141911</t>
-  </si>
-  <si>
-    <t>135142007</t>
-  </si>
-  <si>
-    <t>135142037</t>
-  </si>
-  <si>
-    <t>135142226</t>
-  </si>
-  <si>
-    <t>135142275</t>
-  </si>
-  <si>
-    <t>135142378</t>
-  </si>
-  <si>
-    <t>135142729</t>
-  </si>
-  <si>
-    <t>135142886</t>
-  </si>
-  <si>
-    <t>135142892</t>
-  </si>
-  <si>
-    <t>135142955</t>
-  </si>
-  <si>
-    <t>135143047</t>
-  </si>
-  <si>
-    <t>135143152</t>
-  </si>
-  <si>
-    <t>135143239</t>
-  </si>
-  <si>
-    <t>135143349</t>
-  </si>
-  <si>
-    <t>135143378</t>
-  </si>
-  <si>
-    <t>135143415</t>
-  </si>
-  <si>
-    <t>135143557</t>
-  </si>
-  <si>
-    <t>135143600</t>
-  </si>
-  <si>
-    <t>135143615</t>
-  </si>
-  <si>
-    <t>135143624</t>
-  </si>
-  <si>
-    <t>135143923</t>
-  </si>
-  <si>
-    <t>135144041</t>
-  </si>
-  <si>
-    <t>135144071</t>
-  </si>
-  <si>
-    <t>135144077</t>
-  </si>
-  <si>
-    <t>135144107</t>
-  </si>
-  <si>
-    <t>135144132</t>
-  </si>
-  <si>
-    <t>135144174</t>
-  </si>
-  <si>
-    <t>135144252</t>
-  </si>
-  <si>
-    <t>135144450</t>
-  </si>
-  <si>
-    <t>135144530</t>
-  </si>
-  <si>
-    <t>135144544</t>
-  </si>
-  <si>
-    <t>135144554</t>
-  </si>
-  <si>
-    <t>135144678</t>
-  </si>
-  <si>
-    <t>135144707</t>
-  </si>
-  <si>
-    <t>135144736</t>
-  </si>
-  <si>
-    <t>135144753</t>
-  </si>
-  <si>
-    <t>135144858</t>
-  </si>
-  <si>
-    <t>135144874</t>
-  </si>
-  <si>
-    <t>135145743</t>
-  </si>
-  <si>
-    <t>135145791</t>
-  </si>
-  <si>
-    <t>135146024</t>
-  </si>
-  <si>
-    <t>135146073</t>
-  </si>
-  <si>
-    <t>135146124</t>
-  </si>
-  <si>
-    <t>135146207</t>
-  </si>
-  <si>
-    <t>135146317</t>
-  </si>
-  <si>
-    <t>135146372</t>
+    <t>130142230</t>
+  </si>
+  <si>
+    <t>130653218</t>
+  </si>
+  <si>
+    <t>130962446</t>
+  </si>
+  <si>
+    <t>131017154</t>
+  </si>
+  <si>
+    <t>131095474</t>
+  </si>
+  <si>
+    <t>131568024</t>
+  </si>
+  <si>
+    <t>131715043</t>
+  </si>
+  <si>
+    <t>132134784</t>
+  </si>
+  <si>
+    <t>132913359</t>
+  </si>
+  <si>
+    <t>133121251</t>
+  </si>
+  <si>
+    <t>133888640</t>
+  </si>
+  <si>
+    <t>134071585</t>
+  </si>
+  <si>
+    <t>134298199</t>
+  </si>
+  <si>
+    <t>135146413</t>
+  </si>
+  <si>
+    <t>135146948</t>
+  </si>
+  <si>
+    <t>135147239</t>
+  </si>
+  <si>
+    <t>135147289</t>
+  </si>
+  <si>
+    <t>135147313</t>
+  </si>
+  <si>
+    <t>135147334</t>
+  </si>
+  <si>
+    <t>135147504</t>
+  </si>
+  <si>
+    <t>135147912</t>
+  </si>
+  <si>
+    <t>135148235</t>
+  </si>
+  <si>
+    <t>135148358</t>
+  </si>
+  <si>
+    <t>135148413</t>
+  </si>
+  <si>
+    <t>135148431</t>
+  </si>
+  <si>
+    <t>135148480</t>
+  </si>
+  <si>
+    <t>135148592</t>
+  </si>
+  <si>
+    <t>135148964</t>
+  </si>
+  <si>
+    <t>135148982</t>
+  </si>
+  <si>
+    <t>135149269</t>
+  </si>
+  <si>
+    <t>135149350</t>
+  </si>
+  <si>
+    <t>135149455</t>
+  </si>
+  <si>
+    <t>135149626</t>
+  </si>
+  <si>
+    <t>135149696</t>
+  </si>
+  <si>
+    <t>135149799</t>
+  </si>
+  <si>
+    <t>135149863</t>
+  </si>
+  <si>
+    <t>135150017</t>
+  </si>
+  <si>
+    <t>135150167</t>
+  </si>
+  <si>
+    <t>135150214</t>
+  </si>
+  <si>
+    <t>135150255</t>
+  </si>
+  <si>
+    <t>135150311</t>
+  </si>
+  <si>
+    <t>135150760</t>
+  </si>
+  <si>
+    <t>135150844</t>
+  </si>
+  <si>
+    <t>135151041</t>
+  </si>
+  <si>
+    <t>135151127</t>
+  </si>
+  <si>
+    <t>135151155</t>
+  </si>
+  <si>
+    <t>135151207</t>
+  </si>
+  <si>
+    <t>135151440</t>
+  </si>
+  <si>
+    <t>135151668</t>
+  </si>
+  <si>
+    <t>135151804</t>
+  </si>
+  <si>
+    <t>135152124</t>
+  </si>
+  <si>
+    <t>135152146</t>
+  </si>
+  <si>
+    <t>135152298</t>
+  </si>
+  <si>
+    <t>135152339</t>
+  </si>
+  <si>
+    <t>135152378</t>
+  </si>
+  <si>
+    <t>135152474</t>
+  </si>
+  <si>
+    <t>135152525</t>
+  </si>
+  <si>
+    <t>135152716</t>
+  </si>
+  <si>
+    <t>135152745</t>
+  </si>
+  <si>
+    <t>135152805</t>
+  </si>
+  <si>
+    <t>135152860</t>
+  </si>
+  <si>
+    <t>135152940</t>
+  </si>
+  <si>
+    <t>135152984</t>
+  </si>
+  <si>
+    <t>135153003</t>
+  </si>
+  <si>
+    <t>135153066</t>
+  </si>
+  <si>
+    <t>135153271</t>
+  </si>
+  <si>
+    <t>135153415</t>
+  </si>
+  <si>
+    <t>135153496</t>
+  </si>
+  <si>
+    <t>135153663</t>
+  </si>
+  <si>
+    <t>135153707</t>
+  </si>
+  <si>
+    <t>135153754</t>
+  </si>
+  <si>
+    <t>135153835</t>
+  </si>
+  <si>
+    <t>135153932</t>
+  </si>
+  <si>
+    <t>135153940</t>
+  </si>
+  <si>
+    <t>135153953</t>
+  </si>
+  <si>
+    <t>135153979</t>
+  </si>
+  <si>
+    <t>135154032</t>
+  </si>
+  <si>
+    <t>135154045</t>
+  </si>
+  <si>
+    <t>135154143</t>
+  </si>
+  <si>
+    <t>135154163</t>
+  </si>
+  <si>
+    <t>135154172</t>
+  </si>
+  <si>
+    <t>135154224</t>
+  </si>
+  <si>
+    <t>135154256</t>
+  </si>
+  <si>
+    <t>135154455</t>
+  </si>
+  <si>
+    <t>135154592</t>
+  </si>
+  <si>
+    <t>135154652</t>
+  </si>
+  <si>
+    <t>135154813</t>
+  </si>
+  <si>
+    <t>135154953</t>
+  </si>
+  <si>
+    <t>135155294</t>
+  </si>
+  <si>
+    <t>135155403</t>
+  </si>
+  <si>
+    <t>135155510</t>
+  </si>
+  <si>
+    <t>135155538</t>
+  </si>
+  <si>
+    <t>135155620</t>
+  </si>
+  <si>
+    <t>135155622</t>
+  </si>
+  <si>
+    <t>135155787</t>
+  </si>
+  <si>
+    <t>135156213</t>
+  </si>
+  <si>
+    <t>135156220</t>
+  </si>
+  <si>
+    <t>135156353</t>
+  </si>
+  <si>
+    <t>135156381</t>
+  </si>
+  <si>
+    <t>135156685</t>
+  </si>
+  <si>
+    <t>135156746</t>
+  </si>
+  <si>
+    <t>135156827</t>
+  </si>
+  <si>
+    <t>135157015</t>
+  </si>
+  <si>
+    <t>135157175</t>
+  </si>
+  <si>
+    <t>135157373</t>
+  </si>
+  <si>
+    <t>135157390</t>
+  </si>
+  <si>
+    <t>135157573</t>
+  </si>
+  <si>
+    <t>135157735</t>
+  </si>
+  <si>
+    <t>135157932</t>
+  </si>
+  <si>
+    <t>135158020</t>
+  </si>
+  <si>
+    <t>135158058</t>
+  </si>
+  <si>
+    <t>135158262</t>
+  </si>
+  <si>
+    <t>135158368</t>
+  </si>
+  <si>
+    <t>135158541</t>
+  </si>
+  <si>
+    <t>135158607</t>
+  </si>
+  <si>
+    <t>135158705</t>
+  </si>
+  <si>
+    <t>135158767</t>
+  </si>
+  <si>
+    <t>135158989</t>
+  </si>
+  <si>
+    <t>135159031</t>
+  </si>
+  <si>
+    <t>135159106</t>
+  </si>
+  <si>
+    <t>135159146</t>
+  </si>
+  <si>
+    <t>135159289</t>
+  </si>
+  <si>
+    <t>135159311</t>
+  </si>
+  <si>
+    <t>135159401</t>
+  </si>
+  <si>
+    <t>135159402</t>
+  </si>
+  <si>
+    <t>135159559</t>
+  </si>
+  <si>
+    <t>135159628</t>
+  </si>
+  <si>
+    <t>135159773</t>
+  </si>
+  <si>
+    <t>135160047</t>
+  </si>
+  <si>
+    <t>135160135</t>
+  </si>
+  <si>
+    <t>135160312</t>
+  </si>
+  <si>
+    <t>135160626</t>
+  </si>
+  <si>
+    <t>135160793</t>
+  </si>
+  <si>
+    <t>135160796</t>
+  </si>
+  <si>
+    <t>135160945</t>
+  </si>
+  <si>
+    <t>135160982</t>
+  </si>
+  <si>
+    <t>135161246</t>
+  </si>
+  <si>
+    <t>135161482</t>
+  </si>
+  <si>
+    <t>135161508</t>
+  </si>
+  <si>
+    <t>135161855</t>
+  </si>
+  <si>
+    <t>135162024</t>
+  </si>
+  <si>
+    <t>135162103</t>
+  </si>
+  <si>
+    <t>135162124</t>
+  </si>
+  <si>
+    <t>135162301</t>
+  </si>
+  <si>
+    <t>135162388</t>
+  </si>
+  <si>
+    <t>135162453</t>
+  </si>
+  <si>
+    <t>135162496</t>
+  </si>
+  <si>
+    <t>135162595</t>
+  </si>
+  <si>
+    <t>135162633</t>
+  </si>
+  <si>
+    <t>135162997</t>
+  </si>
+  <si>
+    <t>135163012</t>
+  </si>
+  <si>
+    <t>135163013</t>
+  </si>
+  <si>
+    <t>135163056</t>
+  </si>
+  <si>
+    <t>135163085</t>
+  </si>
+  <si>
+    <t>135163105</t>
+  </si>
+  <si>
+    <t>135163106</t>
+  </si>
+  <si>
+    <t>135163195</t>
+  </si>
+  <si>
+    <t>135163210</t>
+  </si>
+  <si>
+    <t>135163213</t>
+  </si>
+  <si>
+    <t>135163218</t>
+  </si>
+  <si>
+    <t>135163254</t>
+  </si>
+  <si>
+    <t>135163354</t>
+  </si>
+  <si>
+    <t>135163486</t>
+  </si>
+  <si>
+    <t>135163552</t>
+  </si>
+  <si>
+    <t>135163644</t>
+  </si>
+  <si>
+    <t>135163670</t>
+  </si>
+  <si>
+    <t>135163715</t>
+  </si>
+  <si>
+    <t>135163746</t>
+  </si>
+  <si>
+    <t>135164077</t>
+  </si>
+  <si>
+    <t>135164098</t>
+  </si>
+  <si>
+    <t>135164110</t>
+  </si>
+  <si>
+    <t>135164300</t>
+  </si>
+  <si>
+    <t>135164358</t>
+  </si>
+  <si>
+    <t>135164485</t>
+  </si>
+  <si>
+    <t>135164486</t>
+  </si>
+  <si>
+    <t>135164538</t>
+  </si>
+  <si>
+    <t>135164558</t>
+  </si>
+  <si>
+    <t>135164609</t>
+  </si>
+  <si>
+    <t>135164640</t>
+  </si>
+  <si>
+    <t>135164739</t>
+  </si>
+  <si>
+    <t>135164979</t>
+  </si>
+  <si>
+    <t>135165013</t>
   </si>
 </sst>
 </file>
@@ -3001,12 +2998,7 @@
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>3</v>
-      </c>
+      <c r="B184" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C177" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A37959-006C-43D0-A1D6-45306C7402A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B215398A-DB4E-45CE-9A65-06CC981B1E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="252">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,550 +45,745 @@
     <t>.</t>
   </si>
   <si>
-    <t>130142230</t>
-  </si>
-  <si>
-    <t>130653218</t>
-  </si>
-  <si>
-    <t>130962446</t>
-  </si>
-  <si>
-    <t>131017154</t>
-  </si>
-  <si>
-    <t>131095474</t>
-  </si>
-  <si>
-    <t>131568024</t>
-  </si>
-  <si>
-    <t>131715043</t>
-  </si>
-  <si>
-    <t>132134784</t>
-  </si>
-  <si>
-    <t>132913359</t>
-  </si>
-  <si>
-    <t>133121251</t>
-  </si>
-  <si>
-    <t>133888640</t>
-  </si>
-  <si>
-    <t>134071585</t>
-  </si>
-  <si>
-    <t>134298199</t>
-  </si>
-  <si>
-    <t>135146413</t>
-  </si>
-  <si>
-    <t>135146948</t>
-  </si>
-  <si>
-    <t>135147239</t>
-  </si>
-  <si>
-    <t>135147289</t>
-  </si>
-  <si>
-    <t>135147313</t>
-  </si>
-  <si>
-    <t>135147334</t>
-  </si>
-  <si>
-    <t>135147504</t>
-  </si>
-  <si>
-    <t>135147912</t>
-  </si>
-  <si>
-    <t>135148235</t>
-  </si>
-  <si>
-    <t>135148358</t>
-  </si>
-  <si>
-    <t>135148413</t>
-  </si>
-  <si>
-    <t>135148431</t>
-  </si>
-  <si>
-    <t>135148480</t>
-  </si>
-  <si>
-    <t>135148592</t>
-  </si>
-  <si>
-    <t>135148964</t>
-  </si>
-  <si>
-    <t>135148982</t>
-  </si>
-  <si>
-    <t>135149269</t>
-  </si>
-  <si>
-    <t>135149350</t>
-  </si>
-  <si>
-    <t>135149455</t>
-  </si>
-  <si>
-    <t>135149626</t>
-  </si>
-  <si>
-    <t>135149696</t>
-  </si>
-  <si>
-    <t>135149799</t>
-  </si>
-  <si>
-    <t>135149863</t>
-  </si>
-  <si>
-    <t>135150017</t>
-  </si>
-  <si>
-    <t>135150167</t>
-  </si>
-  <si>
-    <t>135150214</t>
-  </si>
-  <si>
-    <t>135150255</t>
-  </si>
-  <si>
-    <t>135150311</t>
-  </si>
-  <si>
-    <t>135150760</t>
-  </si>
-  <si>
-    <t>135150844</t>
-  </si>
-  <si>
-    <t>135151041</t>
-  </si>
-  <si>
-    <t>135151127</t>
-  </si>
-  <si>
-    <t>135151155</t>
-  </si>
-  <si>
-    <t>135151207</t>
-  </si>
-  <si>
-    <t>135151440</t>
-  </si>
-  <si>
-    <t>135151668</t>
-  </si>
-  <si>
-    <t>135151804</t>
-  </si>
-  <si>
-    <t>135152124</t>
-  </si>
-  <si>
-    <t>135152146</t>
-  </si>
-  <si>
-    <t>135152298</t>
-  </si>
-  <si>
-    <t>135152339</t>
-  </si>
-  <si>
-    <t>135152378</t>
-  </si>
-  <si>
-    <t>135152474</t>
-  </si>
-  <si>
-    <t>135152525</t>
-  </si>
-  <si>
-    <t>135152716</t>
-  </si>
-  <si>
-    <t>135152745</t>
-  </si>
-  <si>
-    <t>135152805</t>
-  </si>
-  <si>
-    <t>135152860</t>
-  </si>
-  <si>
-    <t>135152940</t>
-  </si>
-  <si>
-    <t>135152984</t>
-  </si>
-  <si>
-    <t>135153003</t>
-  </si>
-  <si>
-    <t>135153066</t>
-  </si>
-  <si>
-    <t>135153271</t>
-  </si>
-  <si>
-    <t>135153415</t>
-  </si>
-  <si>
-    <t>135153496</t>
-  </si>
-  <si>
-    <t>135153663</t>
-  </si>
-  <si>
-    <t>135153707</t>
-  </si>
-  <si>
-    <t>135153754</t>
-  </si>
-  <si>
-    <t>135153835</t>
-  </si>
-  <si>
-    <t>135153932</t>
-  </si>
-  <si>
-    <t>135153940</t>
-  </si>
-  <si>
-    <t>135153953</t>
-  </si>
-  <si>
-    <t>135153979</t>
-  </si>
-  <si>
-    <t>135154032</t>
-  </si>
-  <si>
-    <t>135154045</t>
-  </si>
-  <si>
-    <t>135154143</t>
-  </si>
-  <si>
-    <t>135154163</t>
-  </si>
-  <si>
-    <t>135154172</t>
-  </si>
-  <si>
-    <t>135154224</t>
-  </si>
-  <si>
-    <t>135154256</t>
-  </si>
-  <si>
-    <t>135154455</t>
-  </si>
-  <si>
-    <t>135154592</t>
-  </si>
-  <si>
-    <t>135154652</t>
-  </si>
-  <si>
-    <t>135154813</t>
-  </si>
-  <si>
-    <t>135154953</t>
-  </si>
-  <si>
-    <t>135155294</t>
-  </si>
-  <si>
-    <t>135155403</t>
-  </si>
-  <si>
-    <t>135155510</t>
-  </si>
-  <si>
-    <t>135155538</t>
-  </si>
-  <si>
-    <t>135155620</t>
-  </si>
-  <si>
-    <t>135155622</t>
-  </si>
-  <si>
-    <t>135155787</t>
-  </si>
-  <si>
-    <t>135156213</t>
-  </si>
-  <si>
-    <t>135156220</t>
-  </si>
-  <si>
-    <t>135156353</t>
-  </si>
-  <si>
-    <t>135156381</t>
-  </si>
-  <si>
-    <t>135156685</t>
-  </si>
-  <si>
-    <t>135156746</t>
-  </si>
-  <si>
-    <t>135156827</t>
-  </si>
-  <si>
-    <t>135157015</t>
-  </si>
-  <si>
-    <t>135157175</t>
-  </si>
-  <si>
-    <t>135157373</t>
-  </si>
-  <si>
-    <t>135157390</t>
-  </si>
-  <si>
-    <t>135157573</t>
-  </si>
-  <si>
-    <t>135157735</t>
-  </si>
-  <si>
-    <t>135157932</t>
-  </si>
-  <si>
-    <t>135158020</t>
-  </si>
-  <si>
-    <t>135158058</t>
-  </si>
-  <si>
-    <t>135158262</t>
-  </si>
-  <si>
-    <t>135158368</t>
-  </si>
-  <si>
-    <t>135158541</t>
-  </si>
-  <si>
-    <t>135158607</t>
-  </si>
-  <si>
-    <t>135158705</t>
-  </si>
-  <si>
-    <t>135158767</t>
-  </si>
-  <si>
-    <t>135158989</t>
-  </si>
-  <si>
-    <t>135159031</t>
-  </si>
-  <si>
-    <t>135159106</t>
-  </si>
-  <si>
-    <t>135159146</t>
-  </si>
-  <si>
-    <t>135159289</t>
-  </si>
-  <si>
-    <t>135159311</t>
-  </si>
-  <si>
-    <t>135159401</t>
-  </si>
-  <si>
-    <t>135159402</t>
-  </si>
-  <si>
-    <t>135159559</t>
-  </si>
-  <si>
-    <t>135159628</t>
-  </si>
-  <si>
-    <t>135159773</t>
-  </si>
-  <si>
-    <t>135160047</t>
-  </si>
-  <si>
-    <t>135160135</t>
-  </si>
-  <si>
-    <t>135160312</t>
-  </si>
-  <si>
-    <t>135160626</t>
-  </si>
-  <si>
-    <t>135160793</t>
-  </si>
-  <si>
-    <t>135160796</t>
-  </si>
-  <si>
-    <t>135160945</t>
-  </si>
-  <si>
-    <t>135160982</t>
-  </si>
-  <si>
-    <t>135161246</t>
-  </si>
-  <si>
-    <t>135161482</t>
-  </si>
-  <si>
-    <t>135161508</t>
-  </si>
-  <si>
-    <t>135161855</t>
-  </si>
-  <si>
-    <t>135162024</t>
-  </si>
-  <si>
-    <t>135162103</t>
-  </si>
-  <si>
-    <t>135162124</t>
-  </si>
-  <si>
-    <t>135162301</t>
-  </si>
-  <si>
-    <t>135162388</t>
-  </si>
-  <si>
-    <t>135162453</t>
-  </si>
-  <si>
-    <t>135162496</t>
-  </si>
-  <si>
-    <t>135162595</t>
-  </si>
-  <si>
-    <t>135162633</t>
-  </si>
-  <si>
-    <t>135162997</t>
-  </si>
-  <si>
-    <t>135163012</t>
-  </si>
-  <si>
-    <t>135163013</t>
-  </si>
-  <si>
-    <t>135163056</t>
-  </si>
-  <si>
-    <t>135163085</t>
-  </si>
-  <si>
-    <t>135163105</t>
-  </si>
-  <si>
-    <t>135163106</t>
-  </si>
-  <si>
-    <t>135163195</t>
-  </si>
-  <si>
-    <t>135163210</t>
-  </si>
-  <si>
-    <t>135163213</t>
-  </si>
-  <si>
-    <t>135163218</t>
-  </si>
-  <si>
-    <t>135163254</t>
-  </si>
-  <si>
-    <t>135163354</t>
-  </si>
-  <si>
-    <t>135163486</t>
-  </si>
-  <si>
-    <t>135163552</t>
-  </si>
-  <si>
-    <t>135163644</t>
-  </si>
-  <si>
-    <t>135163670</t>
-  </si>
-  <si>
-    <t>135163715</t>
-  </si>
-  <si>
-    <t>135163746</t>
-  </si>
-  <si>
-    <t>135164077</t>
-  </si>
-  <si>
-    <t>135164098</t>
-  </si>
-  <si>
-    <t>135164110</t>
-  </si>
-  <si>
-    <t>135164300</t>
-  </si>
-  <si>
-    <t>135164358</t>
-  </si>
-  <si>
-    <t>135164485</t>
-  </si>
-  <si>
-    <t>135164486</t>
-  </si>
-  <si>
-    <t>135164538</t>
-  </si>
-  <si>
-    <t>135164558</t>
-  </si>
-  <si>
-    <t>135164609</t>
-  </si>
-  <si>
-    <t>135164640</t>
-  </si>
-  <si>
-    <t>135164739</t>
-  </si>
-  <si>
-    <t>135164979</t>
-  </si>
-  <si>
-    <t>135165013</t>
+    <t>130472141</t>
+  </si>
+  <si>
+    <t>130527748</t>
+  </si>
+  <si>
+    <t>130618757</t>
+  </si>
+  <si>
+    <t>130818056</t>
+  </si>
+  <si>
+    <t>130926400</t>
+  </si>
+  <si>
+    <t>130939820</t>
+  </si>
+  <si>
+    <t>130970728</t>
+  </si>
+  <si>
+    <t>131102267</t>
+  </si>
+  <si>
+    <t>131229931</t>
+  </si>
+  <si>
+    <t>131402401</t>
+  </si>
+  <si>
+    <t>131689881</t>
+  </si>
+  <si>
+    <t>131837828</t>
+  </si>
+  <si>
+    <t>131926933</t>
+  </si>
+  <si>
+    <t>132079022</t>
+  </si>
+  <si>
+    <t>132975810</t>
+  </si>
+  <si>
+    <t>133344058</t>
+  </si>
+  <si>
+    <t>133519772</t>
+  </si>
+  <si>
+    <t>133627405</t>
+  </si>
+  <si>
+    <t>134073339</t>
+  </si>
+  <si>
+    <t>134219901</t>
+  </si>
+  <si>
+    <t>134369360</t>
+  </si>
+  <si>
+    <t>134486510</t>
+  </si>
+  <si>
+    <t>134992538</t>
+  </si>
+  <si>
+    <t>135165491</t>
+  </si>
+  <si>
+    <t>135165506</t>
+  </si>
+  <si>
+    <t>135165737</t>
+  </si>
+  <si>
+    <t>135165760</t>
+  </si>
+  <si>
+    <t>135165797</t>
+  </si>
+  <si>
+    <t>135165940</t>
+  </si>
+  <si>
+    <t>135165944</t>
+  </si>
+  <si>
+    <t>135165976</t>
+  </si>
+  <si>
+    <t>135166137</t>
+  </si>
+  <si>
+    <t>135166220</t>
+  </si>
+  <si>
+    <t>135166355</t>
+  </si>
+  <si>
+    <t>135166564</t>
+  </si>
+  <si>
+    <t>135166723</t>
+  </si>
+  <si>
+    <t>135166788</t>
+  </si>
+  <si>
+    <t>135166852</t>
+  </si>
+  <si>
+    <t>135166922</t>
+  </si>
+  <si>
+    <t>135166931</t>
+  </si>
+  <si>
+    <t>135166996</t>
+  </si>
+  <si>
+    <t>135167253</t>
+  </si>
+  <si>
+    <t>135167257</t>
+  </si>
+  <si>
+    <t>135167542</t>
+  </si>
+  <si>
+    <t>135167680</t>
+  </si>
+  <si>
+    <t>135167681</t>
+  </si>
+  <si>
+    <t>135167726</t>
+  </si>
+  <si>
+    <t>135167800</t>
+  </si>
+  <si>
+    <t>135167825</t>
+  </si>
+  <si>
+    <t>135167875</t>
+  </si>
+  <si>
+    <t>135168227</t>
+  </si>
+  <si>
+    <t>135168665</t>
+  </si>
+  <si>
+    <t>135168703</t>
+  </si>
+  <si>
+    <t>135168728</t>
+  </si>
+  <si>
+    <t>135168983</t>
+  </si>
+  <si>
+    <t>135169059</t>
+  </si>
+  <si>
+    <t>135169121</t>
+  </si>
+  <si>
+    <t>135169278</t>
+  </si>
+  <si>
+    <t>135169298</t>
+  </si>
+  <si>
+    <t>135169300</t>
+  </si>
+  <si>
+    <t>135169307</t>
+  </si>
+  <si>
+    <t>135169361</t>
+  </si>
+  <si>
+    <t>135169366</t>
+  </si>
+  <si>
+    <t>135169571</t>
+  </si>
+  <si>
+    <t>135169668</t>
+  </si>
+  <si>
+    <t>135169685</t>
+  </si>
+  <si>
+    <t>135169768</t>
+  </si>
+  <si>
+    <t>135169814</t>
+  </si>
+  <si>
+    <t>135170131</t>
+  </si>
+  <si>
+    <t>135170165</t>
+  </si>
+  <si>
+    <t>135170262</t>
+  </si>
+  <si>
+    <t>135170299</t>
+  </si>
+  <si>
+    <t>135170434</t>
+  </si>
+  <si>
+    <t>135170599</t>
+  </si>
+  <si>
+    <t>135170610</t>
+  </si>
+  <si>
+    <t>135170729</t>
+  </si>
+  <si>
+    <t>135170772</t>
+  </si>
+  <si>
+    <t>135170918</t>
+  </si>
+  <si>
+    <t>135170942</t>
+  </si>
+  <si>
+    <t>135170955</t>
+  </si>
+  <si>
+    <t>135171095</t>
+  </si>
+  <si>
+    <t>135171360</t>
+  </si>
+  <si>
+    <t>135171367</t>
+  </si>
+  <si>
+    <t>135171475</t>
+  </si>
+  <si>
+    <t>135171770</t>
+  </si>
+  <si>
+    <t>135171835</t>
+  </si>
+  <si>
+    <t>135171923</t>
+  </si>
+  <si>
+    <t>135171967</t>
+  </si>
+  <si>
+    <t>135171969</t>
+  </si>
+  <si>
+    <t>135171984</t>
+  </si>
+  <si>
+    <t>135172128</t>
+  </si>
+  <si>
+    <t>135172272</t>
+  </si>
+  <si>
+    <t>135172289</t>
+  </si>
+  <si>
+    <t>135172366</t>
+  </si>
+  <si>
+    <t>135172468</t>
+  </si>
+  <si>
+    <t>135172500</t>
+  </si>
+  <si>
+    <t>135172614</t>
+  </si>
+  <si>
+    <t>135172678</t>
+  </si>
+  <si>
+    <t>135172727</t>
+  </si>
+  <si>
+    <t>135172782</t>
+  </si>
+  <si>
+    <t>135172922</t>
+  </si>
+  <si>
+    <t>135172969</t>
+  </si>
+  <si>
+    <t>135173210</t>
+  </si>
+  <si>
+    <t>135173231</t>
+  </si>
+  <si>
+    <t>135173309</t>
+  </si>
+  <si>
+    <t>135173356</t>
+  </si>
+  <si>
+    <t>135173360</t>
+  </si>
+  <si>
+    <t>135173470</t>
+  </si>
+  <si>
+    <t>135173613</t>
+  </si>
+  <si>
+    <t>135173719</t>
+  </si>
+  <si>
+    <t>135173794</t>
+  </si>
+  <si>
+    <t>135173830</t>
+  </si>
+  <si>
+    <t>135173857</t>
+  </si>
+  <si>
+    <t>135173888</t>
+  </si>
+  <si>
+    <t>135174010</t>
+  </si>
+  <si>
+    <t>135174178</t>
+  </si>
+  <si>
+    <t>135174185</t>
+  </si>
+  <si>
+    <t>135174235</t>
+  </si>
+  <si>
+    <t>135174297</t>
+  </si>
+  <si>
+    <t>135174345</t>
+  </si>
+  <si>
+    <t>135174461</t>
+  </si>
+  <si>
+    <t>135174608</t>
+  </si>
+  <si>
+    <t>135174633</t>
+  </si>
+  <si>
+    <t>135174764</t>
+  </si>
+  <si>
+    <t>135174862</t>
+  </si>
+  <si>
+    <t>135174893</t>
+  </si>
+  <si>
+    <t>135175239</t>
+  </si>
+  <si>
+    <t>135175470</t>
+  </si>
+  <si>
+    <t>135175692</t>
+  </si>
+  <si>
+    <t>135175714</t>
+  </si>
+  <si>
+    <t>135175879</t>
+  </si>
+  <si>
+    <t>135175975</t>
+  </si>
+  <si>
+    <t>135176012</t>
+  </si>
+  <si>
+    <t>135176096</t>
+  </si>
+  <si>
+    <t>135176202</t>
+  </si>
+  <si>
+    <t>135176207</t>
+  </si>
+  <si>
+    <t>135176251</t>
+  </si>
+  <si>
+    <t>135176294</t>
+  </si>
+  <si>
+    <t>135176325</t>
+  </si>
+  <si>
+    <t>135176348</t>
+  </si>
+  <si>
+    <t>135176431</t>
+  </si>
+  <si>
+    <t>135176658</t>
+  </si>
+  <si>
+    <t>135176813</t>
+  </si>
+  <si>
+    <t>135176827</t>
+  </si>
+  <si>
+    <t>135176894</t>
+  </si>
+  <si>
+    <t>135176963</t>
+  </si>
+  <si>
+    <t>135176986</t>
+  </si>
+  <si>
+    <t>135177147</t>
+  </si>
+  <si>
+    <t>135177157</t>
+  </si>
+  <si>
+    <t>135177181</t>
+  </si>
+  <si>
+    <t>135177192</t>
+  </si>
+  <si>
+    <t>135177302</t>
+  </si>
+  <si>
+    <t>135177402</t>
+  </si>
+  <si>
+    <t>135177508</t>
+  </si>
+  <si>
+    <t>135177532</t>
+  </si>
+  <si>
+    <t>135177558</t>
+  </si>
+  <si>
+    <t>135177561</t>
+  </si>
+  <si>
+    <t>135177712</t>
+  </si>
+  <si>
+    <t>135177783</t>
+  </si>
+  <si>
+    <t>135177879</t>
+  </si>
+  <si>
+    <t>135177907</t>
+  </si>
+  <si>
+    <t>135178101</t>
+  </si>
+  <si>
+    <t>135178206</t>
+  </si>
+  <si>
+    <t>135178358</t>
+  </si>
+  <si>
+    <t>135178449</t>
+  </si>
+  <si>
+    <t>135178456</t>
+  </si>
+  <si>
+    <t>135178463</t>
+  </si>
+  <si>
+    <t>135178583</t>
+  </si>
+  <si>
+    <t>135178697</t>
+  </si>
+  <si>
+    <t>135178796</t>
+  </si>
+  <si>
+    <t>135179088</t>
+  </si>
+  <si>
+    <t>135179127</t>
+  </si>
+  <si>
+    <t>135179237</t>
+  </si>
+  <si>
+    <t>135179301</t>
+  </si>
+  <si>
+    <t>135179392</t>
+  </si>
+  <si>
+    <t>135179437</t>
+  </si>
+  <si>
+    <t>135179487</t>
+  </si>
+  <si>
+    <t>135179696</t>
+  </si>
+  <si>
+    <t>135179953</t>
+  </si>
+  <si>
+    <t>135179968</t>
+  </si>
+  <si>
+    <t>135179982</t>
+  </si>
+  <si>
+    <t>135180021</t>
+  </si>
+  <si>
+    <t>135180053</t>
+  </si>
+  <si>
+    <t>135180081</t>
+  </si>
+  <si>
+    <t>135180084</t>
+  </si>
+  <si>
+    <t>135180095</t>
+  </si>
+  <si>
+    <t>135180183</t>
+  </si>
+  <si>
+    <t>135180207</t>
+  </si>
+  <si>
+    <t>135180258</t>
+  </si>
+  <si>
+    <t>135180274</t>
+  </si>
+  <si>
+    <t>135180291</t>
+  </si>
+  <si>
+    <t>135180298</t>
+  </si>
+  <si>
+    <t>135180377</t>
+  </si>
+  <si>
+    <t>135180464</t>
+  </si>
+  <si>
+    <t>135180554</t>
+  </si>
+  <si>
+    <t>135180731</t>
+  </si>
+  <si>
+    <t>135180853</t>
+  </si>
+  <si>
+    <t>135180962</t>
+  </si>
+  <si>
+    <t>135180965</t>
+  </si>
+  <si>
+    <t>135181015</t>
+  </si>
+  <si>
+    <t>135181115</t>
+  </si>
+  <si>
+    <t>135181119</t>
+  </si>
+  <si>
+    <t>135181220</t>
+  </si>
+  <si>
+    <t>135181389</t>
+  </si>
+  <si>
+    <t>135181407</t>
+  </si>
+  <si>
+    <t>135181453</t>
+  </si>
+  <si>
+    <t>135181489</t>
+  </si>
+  <si>
+    <t>135181550</t>
+  </si>
+  <si>
+    <t>135181578</t>
+  </si>
+  <si>
+    <t>135181757</t>
+  </si>
+  <si>
+    <t>135181818</t>
+  </si>
+  <si>
+    <t>135181829</t>
+  </si>
+  <si>
+    <t>135181844</t>
+  </si>
+  <si>
+    <t>135181862</t>
+  </si>
+  <si>
+    <t>135181984</t>
+  </si>
+  <si>
+    <t>135181989</t>
+  </si>
+  <si>
+    <t>135182013</t>
+  </si>
+  <si>
+    <t>135182044</t>
+  </si>
+  <si>
+    <t>135182133</t>
+  </si>
+  <si>
+    <t>135182233</t>
+  </si>
+  <si>
+    <t>135182306</t>
+  </si>
+  <si>
+    <t>135182323</t>
+  </si>
+  <si>
+    <t>135182735</t>
+  </si>
+  <si>
+    <t>135182748</t>
+  </si>
+  <si>
+    <t>135182760</t>
+  </si>
+  <si>
+    <t>135182767</t>
+  </si>
+  <si>
+    <t>135182777</t>
+  </si>
+  <si>
+    <t>135182812</t>
+  </si>
+  <si>
+    <t>135182910</t>
+  </si>
+  <si>
+    <t>135182949</t>
+  </si>
+  <si>
+    <t>135183078</t>
+  </si>
+  <si>
+    <t>135183097</t>
+  </si>
+  <si>
+    <t>135183167</t>
+  </si>
+  <si>
+    <t>135183269</t>
+  </si>
+  <si>
+    <t>135183352</t>
+  </si>
+  <si>
+    <t>135183373</t>
+  </si>
+  <si>
+    <t>135183535</t>
+  </si>
+  <si>
+    <t>135183599</t>
+  </si>
+  <si>
+    <t>135183617</t>
+  </si>
+  <si>
+    <t>135184184</t>
+  </si>
+  <si>
+    <t>135184469</t>
+  </si>
+  <si>
+    <t>135184487</t>
+  </si>
+  <si>
+    <t>135184687</t>
+  </si>
+  <si>
+    <t>135184731</t>
+  </si>
+  <si>
+    <t>135184847</t>
+  </si>
+  <si>
+    <t>135184899</t>
+  </si>
+  <si>
+    <t>135184955</t>
   </si>
 </sst>
 </file>
@@ -993,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C184"/>
+  <dimension ref="A1:C248"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2998,7 +3193,524 @@
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B184" s="6"/>
+      <c r="A184" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C177" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B215398A-DB4E-45CE-9A65-06CC981B1E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F09B3D8-B288-4E79-AFCB-6F3DD8E99C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="304">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,745 +45,901 @@
     <t>.</t>
   </si>
   <si>
-    <t>130472141</t>
-  </si>
-  <si>
-    <t>130527748</t>
-  </si>
-  <si>
-    <t>130618757</t>
-  </si>
-  <si>
-    <t>130818056</t>
-  </si>
-  <si>
-    <t>130926400</t>
-  </si>
-  <si>
-    <t>130939820</t>
-  </si>
-  <si>
-    <t>130970728</t>
-  </si>
-  <si>
-    <t>131102267</t>
-  </si>
-  <si>
-    <t>131229931</t>
-  </si>
-  <si>
-    <t>131402401</t>
-  </si>
-  <si>
-    <t>131689881</t>
-  </si>
-  <si>
-    <t>131837828</t>
-  </si>
-  <si>
-    <t>131926933</t>
-  </si>
-  <si>
-    <t>132079022</t>
-  </si>
-  <si>
-    <t>132975810</t>
-  </si>
-  <si>
-    <t>133344058</t>
-  </si>
-  <si>
-    <t>133519772</t>
-  </si>
-  <si>
-    <t>133627405</t>
-  </si>
-  <si>
-    <t>134073339</t>
-  </si>
-  <si>
-    <t>134219901</t>
-  </si>
-  <si>
-    <t>134369360</t>
-  </si>
-  <si>
-    <t>134486510</t>
-  </si>
-  <si>
-    <t>134992538</t>
-  </si>
-  <si>
-    <t>135165491</t>
-  </si>
-  <si>
-    <t>135165506</t>
-  </si>
-  <si>
-    <t>135165737</t>
-  </si>
-  <si>
-    <t>135165760</t>
-  </si>
-  <si>
-    <t>135165797</t>
-  </si>
-  <si>
-    <t>135165940</t>
-  </si>
-  <si>
-    <t>135165944</t>
-  </si>
-  <si>
-    <t>135165976</t>
-  </si>
-  <si>
-    <t>135166137</t>
-  </si>
-  <si>
-    <t>135166220</t>
-  </si>
-  <si>
-    <t>135166355</t>
-  </si>
-  <si>
-    <t>135166564</t>
-  </si>
-  <si>
-    <t>135166723</t>
-  </si>
-  <si>
-    <t>135166788</t>
-  </si>
-  <si>
-    <t>135166852</t>
-  </si>
-  <si>
-    <t>135166922</t>
-  </si>
-  <si>
-    <t>135166931</t>
-  </si>
-  <si>
-    <t>135166996</t>
-  </si>
-  <si>
-    <t>135167253</t>
-  </si>
-  <si>
-    <t>135167257</t>
-  </si>
-  <si>
-    <t>135167542</t>
-  </si>
-  <si>
-    <t>135167680</t>
-  </si>
-  <si>
-    <t>135167681</t>
-  </si>
-  <si>
-    <t>135167726</t>
-  </si>
-  <si>
-    <t>135167800</t>
-  </si>
-  <si>
-    <t>135167825</t>
-  </si>
-  <si>
-    <t>135167875</t>
-  </si>
-  <si>
-    <t>135168227</t>
-  </si>
-  <si>
-    <t>135168665</t>
-  </si>
-  <si>
-    <t>135168703</t>
-  </si>
-  <si>
-    <t>135168728</t>
-  </si>
-  <si>
-    <t>135168983</t>
-  </si>
-  <si>
-    <t>135169059</t>
-  </si>
-  <si>
-    <t>135169121</t>
-  </si>
-  <si>
-    <t>135169278</t>
-  </si>
-  <si>
-    <t>135169298</t>
-  </si>
-  <si>
-    <t>135169300</t>
-  </si>
-  <si>
-    <t>135169307</t>
-  </si>
-  <si>
-    <t>135169361</t>
-  </si>
-  <si>
-    <t>135169366</t>
-  </si>
-  <si>
-    <t>135169571</t>
-  </si>
-  <si>
-    <t>135169668</t>
-  </si>
-  <si>
-    <t>135169685</t>
-  </si>
-  <si>
-    <t>135169768</t>
-  </si>
-  <si>
-    <t>135169814</t>
-  </si>
-  <si>
-    <t>135170131</t>
-  </si>
-  <si>
-    <t>135170165</t>
-  </si>
-  <si>
-    <t>135170262</t>
-  </si>
-  <si>
-    <t>135170299</t>
-  </si>
-  <si>
-    <t>135170434</t>
-  </si>
-  <si>
-    <t>135170599</t>
-  </si>
-  <si>
-    <t>135170610</t>
-  </si>
-  <si>
-    <t>135170729</t>
-  </si>
-  <si>
-    <t>135170772</t>
-  </si>
-  <si>
-    <t>135170918</t>
-  </si>
-  <si>
-    <t>135170942</t>
-  </si>
-  <si>
-    <t>135170955</t>
-  </si>
-  <si>
-    <t>135171095</t>
-  </si>
-  <si>
-    <t>135171360</t>
-  </si>
-  <si>
-    <t>135171367</t>
-  </si>
-  <si>
-    <t>135171475</t>
-  </si>
-  <si>
-    <t>135171770</t>
-  </si>
-  <si>
-    <t>135171835</t>
-  </si>
-  <si>
-    <t>135171923</t>
-  </si>
-  <si>
-    <t>135171967</t>
-  </si>
-  <si>
-    <t>135171969</t>
-  </si>
-  <si>
-    <t>135171984</t>
-  </si>
-  <si>
-    <t>135172128</t>
-  </si>
-  <si>
-    <t>135172272</t>
-  </si>
-  <si>
-    <t>135172289</t>
-  </si>
-  <si>
-    <t>135172366</t>
-  </si>
-  <si>
-    <t>135172468</t>
-  </si>
-  <si>
-    <t>135172500</t>
-  </si>
-  <si>
-    <t>135172614</t>
-  </si>
-  <si>
-    <t>135172678</t>
-  </si>
-  <si>
-    <t>135172727</t>
-  </si>
-  <si>
-    <t>135172782</t>
-  </si>
-  <si>
-    <t>135172922</t>
-  </si>
-  <si>
-    <t>135172969</t>
-  </si>
-  <si>
-    <t>135173210</t>
-  </si>
-  <si>
-    <t>135173231</t>
-  </si>
-  <si>
-    <t>135173309</t>
-  </si>
-  <si>
-    <t>135173356</t>
-  </si>
-  <si>
-    <t>135173360</t>
-  </si>
-  <si>
-    <t>135173470</t>
-  </si>
-  <si>
-    <t>135173613</t>
-  </si>
-  <si>
-    <t>135173719</t>
-  </si>
-  <si>
-    <t>135173794</t>
-  </si>
-  <si>
-    <t>135173830</t>
-  </si>
-  <si>
-    <t>135173857</t>
-  </si>
-  <si>
-    <t>135173888</t>
-  </si>
-  <si>
-    <t>135174010</t>
-  </si>
-  <si>
-    <t>135174178</t>
-  </si>
-  <si>
-    <t>135174185</t>
-  </si>
-  <si>
-    <t>135174235</t>
-  </si>
-  <si>
-    <t>135174297</t>
-  </si>
-  <si>
-    <t>135174345</t>
-  </si>
-  <si>
-    <t>135174461</t>
-  </si>
-  <si>
-    <t>135174608</t>
-  </si>
-  <si>
-    <t>135174633</t>
-  </si>
-  <si>
-    <t>135174764</t>
-  </si>
-  <si>
-    <t>135174862</t>
-  </si>
-  <si>
-    <t>135174893</t>
-  </si>
-  <si>
-    <t>135175239</t>
-  </si>
-  <si>
-    <t>135175470</t>
-  </si>
-  <si>
-    <t>135175692</t>
-  </si>
-  <si>
-    <t>135175714</t>
-  </si>
-  <si>
-    <t>135175879</t>
-  </si>
-  <si>
-    <t>135175975</t>
-  </si>
-  <si>
-    <t>135176012</t>
-  </si>
-  <si>
-    <t>135176096</t>
-  </si>
-  <si>
-    <t>135176202</t>
-  </si>
-  <si>
-    <t>135176207</t>
-  </si>
-  <si>
-    <t>135176251</t>
-  </si>
-  <si>
-    <t>135176294</t>
-  </si>
-  <si>
-    <t>135176325</t>
-  </si>
-  <si>
-    <t>135176348</t>
-  </si>
-  <si>
-    <t>135176431</t>
-  </si>
-  <si>
-    <t>135176658</t>
-  </si>
-  <si>
-    <t>135176813</t>
-  </si>
-  <si>
-    <t>135176827</t>
-  </si>
-  <si>
-    <t>135176894</t>
-  </si>
-  <si>
-    <t>135176963</t>
-  </si>
-  <si>
-    <t>135176986</t>
-  </si>
-  <si>
-    <t>135177147</t>
-  </si>
-  <si>
-    <t>135177157</t>
-  </si>
-  <si>
-    <t>135177181</t>
-  </si>
-  <si>
-    <t>135177192</t>
-  </si>
-  <si>
-    <t>135177302</t>
-  </si>
-  <si>
-    <t>135177402</t>
-  </si>
-  <si>
-    <t>135177508</t>
-  </si>
-  <si>
-    <t>135177532</t>
-  </si>
-  <si>
-    <t>135177558</t>
-  </si>
-  <si>
-    <t>135177561</t>
-  </si>
-  <si>
-    <t>135177712</t>
-  </si>
-  <si>
-    <t>135177783</t>
-  </si>
-  <si>
-    <t>135177879</t>
-  </si>
-  <si>
-    <t>135177907</t>
-  </si>
-  <si>
-    <t>135178101</t>
-  </si>
-  <si>
-    <t>135178206</t>
-  </si>
-  <si>
-    <t>135178358</t>
-  </si>
-  <si>
-    <t>135178449</t>
-  </si>
-  <si>
-    <t>135178456</t>
-  </si>
-  <si>
-    <t>135178463</t>
-  </si>
-  <si>
-    <t>135178583</t>
-  </si>
-  <si>
-    <t>135178697</t>
-  </si>
-  <si>
-    <t>135178796</t>
-  </si>
-  <si>
-    <t>135179088</t>
-  </si>
-  <si>
-    <t>135179127</t>
-  </si>
-  <si>
-    <t>135179237</t>
-  </si>
-  <si>
-    <t>135179301</t>
-  </si>
-  <si>
-    <t>135179392</t>
-  </si>
-  <si>
-    <t>135179437</t>
-  </si>
-  <si>
-    <t>135179487</t>
-  </si>
-  <si>
-    <t>135179696</t>
-  </si>
-  <si>
-    <t>135179953</t>
-  </si>
-  <si>
-    <t>135179968</t>
-  </si>
-  <si>
-    <t>135179982</t>
-  </si>
-  <si>
-    <t>135180021</t>
-  </si>
-  <si>
-    <t>135180053</t>
-  </si>
-  <si>
-    <t>135180081</t>
-  </si>
-  <si>
-    <t>135180084</t>
-  </si>
-  <si>
-    <t>135180095</t>
-  </si>
-  <si>
-    <t>135180183</t>
-  </si>
-  <si>
-    <t>135180207</t>
-  </si>
-  <si>
-    <t>135180258</t>
-  </si>
-  <si>
-    <t>135180274</t>
-  </si>
-  <si>
-    <t>135180291</t>
-  </si>
-  <si>
-    <t>135180298</t>
-  </si>
-  <si>
-    <t>135180377</t>
-  </si>
-  <si>
-    <t>135180464</t>
-  </si>
-  <si>
-    <t>135180554</t>
-  </si>
-  <si>
-    <t>135180731</t>
-  </si>
-  <si>
-    <t>135180853</t>
-  </si>
-  <si>
-    <t>135180962</t>
-  </si>
-  <si>
-    <t>135180965</t>
-  </si>
-  <si>
-    <t>135181015</t>
-  </si>
-  <si>
-    <t>135181115</t>
-  </si>
-  <si>
-    <t>135181119</t>
-  </si>
-  <si>
-    <t>135181220</t>
-  </si>
-  <si>
-    <t>135181389</t>
-  </si>
-  <si>
-    <t>135181407</t>
-  </si>
-  <si>
-    <t>135181453</t>
-  </si>
-  <si>
-    <t>135181489</t>
-  </si>
-  <si>
-    <t>135181550</t>
-  </si>
-  <si>
-    <t>135181578</t>
-  </si>
-  <si>
-    <t>135181757</t>
-  </si>
-  <si>
-    <t>135181818</t>
-  </si>
-  <si>
-    <t>135181829</t>
-  </si>
-  <si>
-    <t>135181844</t>
-  </si>
-  <si>
-    <t>135181862</t>
-  </si>
-  <si>
-    <t>135181984</t>
-  </si>
-  <si>
-    <t>135181989</t>
-  </si>
-  <si>
-    <t>135182013</t>
-  </si>
-  <si>
-    <t>135182044</t>
-  </si>
-  <si>
-    <t>135182133</t>
-  </si>
-  <si>
-    <t>135182233</t>
-  </si>
-  <si>
-    <t>135182306</t>
-  </si>
-  <si>
-    <t>135182323</t>
-  </si>
-  <si>
-    <t>135182735</t>
-  </si>
-  <si>
-    <t>135182748</t>
-  </si>
-  <si>
-    <t>135182760</t>
-  </si>
-  <si>
-    <t>135182767</t>
-  </si>
-  <si>
-    <t>135182777</t>
-  </si>
-  <si>
-    <t>135182812</t>
-  </si>
-  <si>
-    <t>135182910</t>
-  </si>
-  <si>
-    <t>135182949</t>
-  </si>
-  <si>
-    <t>135183078</t>
-  </si>
-  <si>
-    <t>135183097</t>
-  </si>
-  <si>
-    <t>135183167</t>
-  </si>
-  <si>
-    <t>135183269</t>
-  </si>
-  <si>
-    <t>135183352</t>
-  </si>
-  <si>
-    <t>135183373</t>
-  </si>
-  <si>
-    <t>135183535</t>
-  </si>
-  <si>
-    <t>135183599</t>
-  </si>
-  <si>
-    <t>135183617</t>
-  </si>
-  <si>
-    <t>135184184</t>
-  </si>
-  <si>
-    <t>135184469</t>
-  </si>
-  <si>
-    <t>135184487</t>
-  </si>
-  <si>
-    <t>135184687</t>
-  </si>
-  <si>
-    <t>135184731</t>
-  </si>
-  <si>
-    <t>135184847</t>
-  </si>
-  <si>
-    <t>135184899</t>
-  </si>
-  <si>
-    <t>135184955</t>
+    <t>130146182</t>
+  </si>
+  <si>
+    <t>130601458</t>
+  </si>
+  <si>
+    <t>130872171</t>
+  </si>
+  <si>
+    <t>131059074</t>
+  </si>
+  <si>
+    <t>131059245</t>
+  </si>
+  <si>
+    <t>131160754</t>
+  </si>
+  <si>
+    <t>131262287</t>
+  </si>
+  <si>
+    <t>131354843</t>
+  </si>
+  <si>
+    <t>131814119</t>
+  </si>
+  <si>
+    <t>132292713</t>
+  </si>
+  <si>
+    <t>132306133</t>
+  </si>
+  <si>
+    <t>132429852</t>
+  </si>
+  <si>
+    <t>132430877</t>
+  </si>
+  <si>
+    <t>132587252</t>
+  </si>
+  <si>
+    <t>132969568</t>
+  </si>
+  <si>
+    <t>132999122</t>
+  </si>
+  <si>
+    <t>133075161</t>
+  </si>
+  <si>
+    <t>133116802</t>
+  </si>
+  <si>
+    <t>133367953</t>
+  </si>
+  <si>
+    <t>133506857</t>
+  </si>
+  <si>
+    <t>133519399</t>
+  </si>
+  <si>
+    <t>133618641</t>
+  </si>
+  <si>
+    <t>133634032</t>
+  </si>
+  <si>
+    <t>133785363</t>
+  </si>
+  <si>
+    <t>133924096</t>
+  </si>
+  <si>
+    <t>134830405</t>
+  </si>
+  <si>
+    <t>134892806</t>
+  </si>
+  <si>
+    <t>134974822</t>
+  </si>
+  <si>
+    <t>135056915</t>
+  </si>
+  <si>
+    <t>135185032</t>
+  </si>
+  <si>
+    <t>135185033</t>
+  </si>
+  <si>
+    <t>135185259</t>
+  </si>
+  <si>
+    <t>135185295</t>
+  </si>
+  <si>
+    <t>135185328</t>
+  </si>
+  <si>
+    <t>135185540</t>
+  </si>
+  <si>
+    <t>135185646</t>
+  </si>
+  <si>
+    <t>135185711</t>
+  </si>
+  <si>
+    <t>135185803</t>
+  </si>
+  <si>
+    <t>135185959</t>
+  </si>
+  <si>
+    <t>135186013</t>
+  </si>
+  <si>
+    <t>135186165</t>
+  </si>
+  <si>
+    <t>135186342</t>
+  </si>
+  <si>
+    <t>135186473</t>
+  </si>
+  <si>
+    <t>135186499</t>
+  </si>
+  <si>
+    <t>135186679</t>
+  </si>
+  <si>
+    <t>135186700</t>
+  </si>
+  <si>
+    <t>135186910</t>
+  </si>
+  <si>
+    <t>135186960</t>
+  </si>
+  <si>
+    <t>135186980</t>
+  </si>
+  <si>
+    <t>135186984</t>
+  </si>
+  <si>
+    <t>135187006</t>
+  </si>
+  <si>
+    <t>135187161</t>
+  </si>
+  <si>
+    <t>135187384</t>
+  </si>
+  <si>
+    <t>135187560</t>
+  </si>
+  <si>
+    <t>135187651</t>
+  </si>
+  <si>
+    <t>135187709</t>
+  </si>
+  <si>
+    <t>135187899</t>
+  </si>
+  <si>
+    <t>135187919</t>
+  </si>
+  <si>
+    <t>135188014</t>
+  </si>
+  <si>
+    <t>135188096</t>
+  </si>
+  <si>
+    <t>135188395</t>
+  </si>
+  <si>
+    <t>135188470</t>
+  </si>
+  <si>
+    <t>135188484</t>
+  </si>
+  <si>
+    <t>135188530</t>
+  </si>
+  <si>
+    <t>135188744</t>
+  </si>
+  <si>
+    <t>135188745</t>
+  </si>
+  <si>
+    <t>135188845</t>
+  </si>
+  <si>
+    <t>135189003</t>
+  </si>
+  <si>
+    <t>135189061</t>
+  </si>
+  <si>
+    <t>135189125</t>
+  </si>
+  <si>
+    <t>135189201</t>
+  </si>
+  <si>
+    <t>135189305</t>
+  </si>
+  <si>
+    <t>135189312</t>
+  </si>
+  <si>
+    <t>135189397</t>
+  </si>
+  <si>
+    <t>135189415</t>
+  </si>
+  <si>
+    <t>135189425</t>
+  </si>
+  <si>
+    <t>135189543</t>
+  </si>
+  <si>
+    <t>135189574</t>
+  </si>
+  <si>
+    <t>135189634</t>
+  </si>
+  <si>
+    <t>135189666</t>
+  </si>
+  <si>
+    <t>135189723</t>
+  </si>
+  <si>
+    <t>135189791</t>
+  </si>
+  <si>
+    <t>135189860</t>
+  </si>
+  <si>
+    <t>135189943</t>
+  </si>
+  <si>
+    <t>135189980</t>
+  </si>
+  <si>
+    <t>135190229</t>
+  </si>
+  <si>
+    <t>135190233</t>
+  </si>
+  <si>
+    <t>135190315</t>
+  </si>
+  <si>
+    <t>135190587</t>
+  </si>
+  <si>
+    <t>135190609</t>
+  </si>
+  <si>
+    <t>135190673</t>
+  </si>
+  <si>
+    <t>135190814</t>
+  </si>
+  <si>
+    <t>135191018</t>
+  </si>
+  <si>
+    <t>135191056</t>
+  </si>
+  <si>
+    <t>135191209</t>
+  </si>
+  <si>
+    <t>135191224</t>
+  </si>
+  <si>
+    <t>135191310</t>
+  </si>
+  <si>
+    <t>135191415</t>
+  </si>
+  <si>
+    <t>135191545</t>
+  </si>
+  <si>
+    <t>135191753</t>
+  </si>
+  <si>
+    <t>135191763</t>
+  </si>
+  <si>
+    <t>135191873</t>
+  </si>
+  <si>
+    <t>135191878</t>
+  </si>
+  <si>
+    <t>135191930</t>
+  </si>
+  <si>
+    <t>135192125</t>
+  </si>
+  <si>
+    <t>135192161</t>
+  </si>
+  <si>
+    <t>135192284</t>
+  </si>
+  <si>
+    <t>135192343</t>
+  </si>
+  <si>
+    <t>135192353</t>
+  </si>
+  <si>
+    <t>135192397</t>
+  </si>
+  <si>
+    <t>135192414</t>
+  </si>
+  <si>
+    <t>135192552</t>
+  </si>
+  <si>
+    <t>135192618</t>
+  </si>
+  <si>
+    <t>135192671</t>
+  </si>
+  <si>
+    <t>135192703</t>
+  </si>
+  <si>
+    <t>135192752</t>
+  </si>
+  <si>
+    <t>135192787</t>
+  </si>
+  <si>
+    <t>135193019</t>
+  </si>
+  <si>
+    <t>135193022</t>
+  </si>
+  <si>
+    <t>135193195</t>
+  </si>
+  <si>
+    <t>135193261</t>
+  </si>
+  <si>
+    <t>135193430</t>
+  </si>
+  <si>
+    <t>135193564</t>
+  </si>
+  <si>
+    <t>135193662</t>
+  </si>
+  <si>
+    <t>135193839</t>
+  </si>
+  <si>
+    <t>135193876</t>
+  </si>
+  <si>
+    <t>135193921</t>
+  </si>
+  <si>
+    <t>135194168</t>
+  </si>
+  <si>
+    <t>135194258</t>
+  </si>
+  <si>
+    <t>135194531</t>
+  </si>
+  <si>
+    <t>135194541</t>
+  </si>
+  <si>
+    <t>135194634</t>
+  </si>
+  <si>
+    <t>135194649</t>
+  </si>
+  <si>
+    <t>135194674</t>
+  </si>
+  <si>
+    <t>135194756</t>
+  </si>
+  <si>
+    <t>135194768</t>
+  </si>
+  <si>
+    <t>135194771</t>
+  </si>
+  <si>
+    <t>135194781</t>
+  </si>
+  <si>
+    <t>135194866</t>
+  </si>
+  <si>
+    <t>135194869</t>
+  </si>
+  <si>
+    <t>135195086</t>
+  </si>
+  <si>
+    <t>135195199</t>
+  </si>
+  <si>
+    <t>135195267</t>
+  </si>
+  <si>
+    <t>135195416</t>
+  </si>
+  <si>
+    <t>135195597</t>
+  </si>
+  <si>
+    <t>135195855</t>
+  </si>
+  <si>
+    <t>135196029</t>
+  </si>
+  <si>
+    <t>135196307</t>
+  </si>
+  <si>
+    <t>135196441</t>
+  </si>
+  <si>
+    <t>135196556</t>
+  </si>
+  <si>
+    <t>135196569</t>
+  </si>
+  <si>
+    <t>135196607</t>
+  </si>
+  <si>
+    <t>135196668</t>
+  </si>
+  <si>
+    <t>135196768</t>
+  </si>
+  <si>
+    <t>135196788</t>
+  </si>
+  <si>
+    <t>135196909</t>
+  </si>
+  <si>
+    <t>135196992</t>
+  </si>
+  <si>
+    <t>135197056</t>
+  </si>
+  <si>
+    <t>135197064</t>
+  </si>
+  <si>
+    <t>135197088</t>
+  </si>
+  <si>
+    <t>135197096</t>
+  </si>
+  <si>
+    <t>135197120</t>
+  </si>
+  <si>
+    <t>135197174</t>
+  </si>
+  <si>
+    <t>135197177</t>
+  </si>
+  <si>
+    <t>135197326</t>
+  </si>
+  <si>
+    <t>135197531</t>
+  </si>
+  <si>
+    <t>135197605</t>
+  </si>
+  <si>
+    <t>135197608</t>
+  </si>
+  <si>
+    <t>135197612</t>
+  </si>
+  <si>
+    <t>135197636</t>
+  </si>
+  <si>
+    <t>135197701</t>
+  </si>
+  <si>
+    <t>135197711</t>
+  </si>
+  <si>
+    <t>135197806</t>
+  </si>
+  <si>
+    <t>135198061</t>
+  </si>
+  <si>
+    <t>135198117</t>
+  </si>
+  <si>
+    <t>135198237</t>
+  </si>
+  <si>
+    <t>135198311</t>
+  </si>
+  <si>
+    <t>135198313</t>
+  </si>
+  <si>
+    <t>135198362</t>
+  </si>
+  <si>
+    <t>135198371</t>
+  </si>
+  <si>
+    <t>135198413</t>
+  </si>
+  <si>
+    <t>135198439</t>
+  </si>
+  <si>
+    <t>135198476</t>
+  </si>
+  <si>
+    <t>135198501</t>
+  </si>
+  <si>
+    <t>135198606</t>
+  </si>
+  <si>
+    <t>135198631</t>
+  </si>
+  <si>
+    <t>135198637</t>
+  </si>
+  <si>
+    <t>135198652</t>
+  </si>
+  <si>
+    <t>135198727</t>
+  </si>
+  <si>
+    <t>135198744</t>
+  </si>
+  <si>
+    <t>135198787</t>
+  </si>
+  <si>
+    <t>135198892</t>
+  </si>
+  <si>
+    <t>135198941</t>
+  </si>
+  <si>
+    <t>135199136</t>
+  </si>
+  <si>
+    <t>135199427</t>
+  </si>
+  <si>
+    <t>135199448</t>
+  </si>
+  <si>
+    <t>135199516</t>
+  </si>
+  <si>
+    <t>135199550</t>
+  </si>
+  <si>
+    <t>135199592</t>
+  </si>
+  <si>
+    <t>135199650</t>
+  </si>
+  <si>
+    <t>135199711</t>
+  </si>
+  <si>
+    <t>135199761</t>
+  </si>
+  <si>
+    <t>135199767</t>
+  </si>
+  <si>
+    <t>135199781</t>
+  </si>
+  <si>
+    <t>135199816</t>
+  </si>
+  <si>
+    <t>135199874</t>
+  </si>
+  <si>
+    <t>135199949</t>
+  </si>
+  <si>
+    <t>135199964</t>
+  </si>
+  <si>
+    <t>135200116</t>
+  </si>
+  <si>
+    <t>135200193</t>
+  </si>
+  <si>
+    <t>135200205</t>
+  </si>
+  <si>
+    <t>135200217</t>
+  </si>
+  <si>
+    <t>135200229</t>
+  </si>
+  <si>
+    <t>135200268</t>
+  </si>
+  <si>
+    <t>135200300</t>
+  </si>
+  <si>
+    <t>135200380</t>
+  </si>
+  <si>
+    <t>135200455</t>
+  </si>
+  <si>
+    <t>135200480</t>
+  </si>
+  <si>
+    <t>135200503</t>
+  </si>
+  <si>
+    <t>135200543</t>
+  </si>
+  <si>
+    <t>135200553</t>
+  </si>
+  <si>
+    <t>135200592</t>
+  </si>
+  <si>
+    <t>135200626</t>
+  </si>
+  <si>
+    <t>135200777</t>
+  </si>
+  <si>
+    <t>135200794</t>
+  </si>
+  <si>
+    <t>135200817</t>
+  </si>
+  <si>
+    <t>135200820</t>
+  </si>
+  <si>
+    <t>135200878</t>
+  </si>
+  <si>
+    <t>135200896</t>
+  </si>
+  <si>
+    <t>135200917</t>
+  </si>
+  <si>
+    <t>135200934</t>
+  </si>
+  <si>
+    <t>135200985</t>
+  </si>
+  <si>
+    <t>135201021</t>
+  </si>
+  <si>
+    <t>135201037</t>
+  </si>
+  <si>
+    <t>135201073</t>
+  </si>
+  <si>
+    <t>135201074</t>
+  </si>
+  <si>
+    <t>135201260</t>
+  </si>
+  <si>
+    <t>135201277</t>
+  </si>
+  <si>
+    <t>135201305</t>
+  </si>
+  <si>
+    <t>135201322</t>
+  </si>
+  <si>
+    <t>135201345</t>
+  </si>
+  <si>
+    <t>135201390</t>
+  </si>
+  <si>
+    <t>135201399</t>
+  </si>
+  <si>
+    <t>135201429</t>
+  </si>
+  <si>
+    <t>135201502</t>
+  </si>
+  <si>
+    <t>135201543</t>
+  </si>
+  <si>
+    <t>135201597</t>
+  </si>
+  <si>
+    <t>135201673</t>
+  </si>
+  <si>
+    <t>135201678</t>
+  </si>
+  <si>
+    <t>135201706</t>
+  </si>
+  <si>
+    <t>135201741</t>
+  </si>
+  <si>
+    <t>135201880</t>
+  </si>
+  <si>
+    <t>135201903</t>
+  </si>
+  <si>
+    <t>135201911</t>
+  </si>
+  <si>
+    <t>135201945</t>
+  </si>
+  <si>
+    <t>135202006</t>
+  </si>
+  <si>
+    <t>135202033</t>
+  </si>
+  <si>
+    <t>135202058</t>
+  </si>
+  <si>
+    <t>135202080</t>
+  </si>
+  <si>
+    <t>135202123</t>
+  </si>
+  <si>
+    <t>135202126</t>
+  </si>
+  <si>
+    <t>135202190</t>
+  </si>
+  <si>
+    <t>135202253</t>
+  </si>
+  <si>
+    <t>135202267</t>
+  </si>
+  <si>
+    <t>135202271</t>
+  </si>
+  <si>
+    <t>135202275</t>
+  </si>
+  <si>
+    <t>135202300</t>
+  </si>
+  <si>
+    <t>135202338</t>
+  </si>
+  <si>
+    <t>135202357</t>
+  </si>
+  <si>
+    <t>135202410</t>
+  </si>
+  <si>
+    <t>135202418</t>
+  </si>
+  <si>
+    <t>135202428</t>
+  </si>
+  <si>
+    <t>135202531</t>
+  </si>
+  <si>
+    <t>135202546</t>
+  </si>
+  <si>
+    <t>135202614</t>
+  </si>
+  <si>
+    <t>135202625</t>
+  </si>
+  <si>
+    <t>135202775</t>
+  </si>
+  <si>
+    <t>135202825</t>
+  </si>
+  <si>
+    <t>135202849</t>
+  </si>
+  <si>
+    <t>135202870</t>
+  </si>
+  <si>
+    <t>135202900</t>
+  </si>
+  <si>
+    <t>135202968</t>
+  </si>
+  <si>
+    <t>135203097</t>
+  </si>
+  <si>
+    <t>135203132</t>
+  </si>
+  <si>
+    <t>135203144</t>
+  </si>
+  <si>
+    <t>135203193</t>
+  </si>
+  <si>
+    <t>135203198</t>
+  </si>
+  <si>
+    <t>135203655</t>
+  </si>
+  <si>
+    <t>135203750</t>
+  </si>
+  <si>
+    <t>135203786</t>
+  </si>
+  <si>
+    <t>135203855</t>
+  </si>
+  <si>
+    <t>135203974</t>
+  </si>
+  <si>
+    <t>135204115</t>
+  </si>
+  <si>
+    <t>135204187</t>
+  </si>
+  <si>
+    <t>135204234</t>
+  </si>
+  <si>
+    <t>135204253</t>
+  </si>
+  <si>
+    <t>135204254</t>
+  </si>
+  <si>
+    <t>135204285</t>
+  </si>
+  <si>
+    <t>135204462</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C248"/>
+  <dimension ref="A1:C300"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3712,6 +3868,422 @@
         <v>3</v>
       </c>
     </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C177" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AB4973-82E3-408F-A826-5B6888F63C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F99265-8A12-4401-A202-A97EFE990DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="127">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,22 +45,370 @@
     <t>.</t>
   </si>
   <si>
-    <t>135206313</t>
-  </si>
-  <si>
-    <t>135206315</t>
-  </si>
-  <si>
-    <t>135206428</t>
-  </si>
-  <si>
-    <t>135206814</t>
-  </si>
-  <si>
-    <t>135206863</t>
-  </si>
-  <si>
-    <t>135206871</t>
+    <t>131388385</t>
+  </si>
+  <si>
+    <t>131506326</t>
+  </si>
+  <si>
+    <t>131578343</t>
+  </si>
+  <si>
+    <t>131624750</t>
+  </si>
+  <si>
+    <t>132178349</t>
+  </si>
+  <si>
+    <t>132341330</t>
+  </si>
+  <si>
+    <t>132362738</t>
+  </si>
+  <si>
+    <t>132444484</t>
+  </si>
+  <si>
+    <t>133660903</t>
+  </si>
+  <si>
+    <t>134251609</t>
+  </si>
+  <si>
+    <t>135207160</t>
+  </si>
+  <si>
+    <t>135207256</t>
+  </si>
+  <si>
+    <t>135207629</t>
+  </si>
+  <si>
+    <t>135207951</t>
+  </si>
+  <si>
+    <t>135208277</t>
+  </si>
+  <si>
+    <t>135208380</t>
+  </si>
+  <si>
+    <t>135208539</t>
+  </si>
+  <si>
+    <t>135208705</t>
+  </si>
+  <si>
+    <t>135208710</t>
+  </si>
+  <si>
+    <t>135209012</t>
+  </si>
+  <si>
+    <t>135209290</t>
+  </si>
+  <si>
+    <t>135209768</t>
+  </si>
+  <si>
+    <t>135209789</t>
+  </si>
+  <si>
+    <t>135209941</t>
+  </si>
+  <si>
+    <t>135209988</t>
+  </si>
+  <si>
+    <t>135210020</t>
+  </si>
+  <si>
+    <t>135210283</t>
+  </si>
+  <si>
+    <t>135210345</t>
+  </si>
+  <si>
+    <t>135210444</t>
+  </si>
+  <si>
+    <t>135211010</t>
+  </si>
+  <si>
+    <t>135211102</t>
+  </si>
+  <si>
+    <t>135211542</t>
+  </si>
+  <si>
+    <t>135211600</t>
+  </si>
+  <si>
+    <t>135211849</t>
+  </si>
+  <si>
+    <t>135212079</t>
+  </si>
+  <si>
+    <t>135212084</t>
+  </si>
+  <si>
+    <t>135212250</t>
+  </si>
+  <si>
+    <t>135212284</t>
+  </si>
+  <si>
+    <t>135212302</t>
+  </si>
+  <si>
+    <t>135212304</t>
+  </si>
+  <si>
+    <t>135212567</t>
+  </si>
+  <si>
+    <t>135212590</t>
+  </si>
+  <si>
+    <t>135212644</t>
+  </si>
+  <si>
+    <t>135212655</t>
+  </si>
+  <si>
+    <t>135212771</t>
+  </si>
+  <si>
+    <t>135212822</t>
+  </si>
+  <si>
+    <t>135212962</t>
+  </si>
+  <si>
+    <t>135213076</t>
+  </si>
+  <si>
+    <t>135213375</t>
+  </si>
+  <si>
+    <t>135213522</t>
+  </si>
+  <si>
+    <t>135213561</t>
+  </si>
+  <si>
+    <t>135213602</t>
+  </si>
+  <si>
+    <t>135213849</t>
+  </si>
+  <si>
+    <t>135214265</t>
+  </si>
+  <si>
+    <t>135214309</t>
+  </si>
+  <si>
+    <t>135214381</t>
+  </si>
+  <si>
+    <t>135214515</t>
+  </si>
+  <si>
+    <t>135214693</t>
+  </si>
+  <si>
+    <t>135214696</t>
+  </si>
+  <si>
+    <t>135214735</t>
+  </si>
+  <si>
+    <t>135215088</t>
+  </si>
+  <si>
+    <t>135215091</t>
+  </si>
+  <si>
+    <t>135215762</t>
+  </si>
+  <si>
+    <t>135215851</t>
+  </si>
+  <si>
+    <t>135215920</t>
+  </si>
+  <si>
+    <t>135216004</t>
+  </si>
+  <si>
+    <t>135216190</t>
+  </si>
+  <si>
+    <t>135216398</t>
+  </si>
+  <si>
+    <t>135216399</t>
+  </si>
+  <si>
+    <t>135216527</t>
+  </si>
+  <si>
+    <t>135216719</t>
+  </si>
+  <si>
+    <t>135216935</t>
+  </si>
+  <si>
+    <t>135216953</t>
+  </si>
+  <si>
+    <t>135217260</t>
+  </si>
+  <si>
+    <t>135217307</t>
+  </si>
+  <si>
+    <t>135217624</t>
+  </si>
+  <si>
+    <t>135217782</t>
+  </si>
+  <si>
+    <t>135217818</t>
+  </si>
+  <si>
+    <t>135217909</t>
+  </si>
+  <si>
+    <t>135217953</t>
+  </si>
+  <si>
+    <t>135218023</t>
+  </si>
+  <si>
+    <t>135218376</t>
+  </si>
+  <si>
+    <t>135218654</t>
+  </si>
+  <si>
+    <t>135218710</t>
+  </si>
+  <si>
+    <t>135218761</t>
+  </si>
+  <si>
+    <t>135218850</t>
+  </si>
+  <si>
+    <t>135219054</t>
+  </si>
+  <si>
+    <t>135219064</t>
+  </si>
+  <si>
+    <t>135219089</t>
+  </si>
+  <si>
+    <t>135219223</t>
+  </si>
+  <si>
+    <t>135219311</t>
+  </si>
+  <si>
+    <t>135219384</t>
+  </si>
+  <si>
+    <t>135219422</t>
+  </si>
+  <si>
+    <t>135219446</t>
+  </si>
+  <si>
+    <t>135220531</t>
+  </si>
+  <si>
+    <t>135220589</t>
+  </si>
+  <si>
+    <t>135220834</t>
+  </si>
+  <si>
+    <t>135220866</t>
+  </si>
+  <si>
+    <t>135220999</t>
+  </si>
+  <si>
+    <t>135221053</t>
+  </si>
+  <si>
+    <t>135221510</t>
+  </si>
+  <si>
+    <t>135221690</t>
+  </si>
+  <si>
+    <t>135221715</t>
+  </si>
+  <si>
+    <t>135221739</t>
+  </si>
+  <si>
+    <t>135221871</t>
+  </si>
+  <si>
+    <t>135222203</t>
+  </si>
+  <si>
+    <t>135222294</t>
+  </si>
+  <si>
+    <t>135222320</t>
+  </si>
+  <si>
+    <t>135222384</t>
+  </si>
+  <si>
+    <t>135222570</t>
+  </si>
+  <si>
+    <t>135222960</t>
+  </si>
+  <si>
+    <t>135223146</t>
+  </si>
+  <si>
+    <t>135223390</t>
+  </si>
+  <si>
+    <t>135223462</t>
+  </si>
+  <si>
+    <t>135223475</t>
+  </si>
+  <si>
+    <t>135223621</t>
+  </si>
+  <si>
+    <t>135223651</t>
+  </si>
+  <si>
+    <t>135223777</t>
+  </si>
+  <si>
+    <t>135223860</t>
+  </si>
+  <si>
+    <t>135224194</t>
+  </si>
+  <si>
+    <t>135225727</t>
+  </si>
+  <si>
+    <t>135226550</t>
   </si>
 </sst>
 </file>
@@ -552,583 +900,1047 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C8" s="5"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C18" s="5"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C19" s="5"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="6"/>
+      <c r="A20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C20" s="5"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C21" s="5"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C22" s="5"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="6"/>
+      <c r="A23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C23" s="5"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="6"/>
+      <c r="A24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C24" s="5"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="6"/>
+      <c r="A25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C25" s="5"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="6"/>
+      <c r="A26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C26" s="5"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="6"/>
+      <c r="A27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="6"/>
+      <c r="A28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C28" s="5"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="6"/>
+      <c r="A29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C29" s="5"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="6"/>
+      <c r="A30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C30" s="5"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="6"/>
+      <c r="A31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C31" s="5"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="6"/>
+      <c r="A32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C32" s="5"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="6"/>
+      <c r="A33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C33" s="5"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="6"/>
+      <c r="A34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C34" s="5"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="6"/>
+      <c r="A35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C35" s="5"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="6"/>
+      <c r="A36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C36" s="5"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="6"/>
+      <c r="A37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C37" s="5"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="6"/>
+      <c r="A38" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C38" s="5"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="6"/>
+      <c r="A39" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C39" s="5"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="6"/>
+      <c r="A40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C40" s="5"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="4"/>
-      <c r="B41" s="6"/>
+      <c r="A41" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C41" s="5"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-      <c r="B42" s="6"/>
+      <c r="A42" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C42" s="5"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C43" s="5"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="6"/>
+      <c r="A44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C44" s="5"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="B45" s="6"/>
+      <c r="A45" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C45" s="5"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="6"/>
+      <c r="A46" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C46" s="5"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="6"/>
+      <c r="A47" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C47" s="5"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="6"/>
+      <c r="A48" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C48" s="5"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="B49" s="6"/>
+      <c r="A49" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C49" s="5"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="B50" s="6"/>
+      <c r="A50" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="6"/>
+      <c r="A51" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C51" s="5"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="6"/>
+      <c r="A52" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C52" s="5"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-      <c r="B53" s="6"/>
+      <c r="A53" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C53" s="5"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-      <c r="B54" s="6"/>
+      <c r="A54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C54" s="5"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
-      <c r="B55" s="6"/>
+      <c r="A55" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="6"/>
+      <c r="A56" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C56" s="5"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
-      <c r="B57" s="6"/>
+      <c r="A57" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C57" s="5"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-      <c r="B58" s="6"/>
+      <c r="A58" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
-      <c r="B59" s="6"/>
+      <c r="A59" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-      <c r="B60" s="6"/>
+      <c r="A60" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C60" s="5"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
-      <c r="B61" s="6"/>
+      <c r="A61" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C61" s="5"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
-      <c r="B62" s="6"/>
+      <c r="A62" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C62" s="5"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
-      <c r="B63" s="6"/>
+      <c r="A63" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C63" s="5"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-      <c r="B64" s="6"/>
+      <c r="A64" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C64" s="5"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
-      <c r="B65" s="6"/>
+      <c r="A65" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C65" s="5"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-      <c r="B66" s="6"/>
+      <c r="A66" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C66" s="5"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-      <c r="B67" s="6"/>
+      <c r="A67" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
-      <c r="B68" s="6"/>
+      <c r="A68" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="4"/>
-      <c r="B69" s="6"/>
+      <c r="A69" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C69" s="5"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
-      <c r="B70" s="6"/>
+      <c r="A70" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C70" s="5"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="4"/>
-      <c r="B71" s="6"/>
+      <c r="A71" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C71" s="5"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="4"/>
-      <c r="B72" s="6"/>
+      <c r="A72" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C72" s="5"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="4"/>
-      <c r="B73" s="6"/>
+      <c r="A73" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C73" s="5"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-      <c r="B74" s="6"/>
+      <c r="A74" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C74" s="5"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="6"/>
+      <c r="A75" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C75" s="5"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-      <c r="B76" s="6"/>
+      <c r="A76" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C76" s="5"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="6"/>
+      <c r="A77" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C77" s="5"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-      <c r="B78" s="6"/>
+      <c r="A78" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C78" s="5"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="4"/>
-      <c r="B79" s="6"/>
+      <c r="A79" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C79" s="5"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-      <c r="B80" s="6"/>
+      <c r="A80" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C80" s="5"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4"/>
-      <c r="B81" s="6"/>
+      <c r="A81" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C81" s="5"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-      <c r="B82" s="6"/>
+      <c r="A82" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C82" s="5"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4"/>
-      <c r="B83" s="6"/>
+      <c r="A83" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-      <c r="B84" s="6"/>
+      <c r="A84" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C84" s="5"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4"/>
-      <c r="B85" s="6"/>
+      <c r="A85" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C85" s="5"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-      <c r="B86" s="6"/>
+      <c r="A86" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C86" s="5"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4"/>
-      <c r="B87" s="6"/>
+      <c r="A87" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C87" s="5"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-      <c r="B88" s="6"/>
+      <c r="A88" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C88" s="5"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4"/>
-      <c r="B89" s="6"/>
+      <c r="A89" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C89" s="5"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-      <c r="B90" s="6"/>
+      <c r="A90" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C90" s="5"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4"/>
-      <c r="B91" s="6"/>
+      <c r="A91" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-      <c r="B92" s="6"/>
+      <c r="A92" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4"/>
-      <c r="B93" s="6"/>
+      <c r="A93" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C93" s="5"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-      <c r="B94" s="6"/>
+      <c r="A94" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C94" s="5"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4"/>
-      <c r="B95" s="6"/>
+      <c r="A95" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C95" s="5"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
-      <c r="B96" s="6"/>
+      <c r="A96" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C96" s="5"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
-      <c r="B97" s="6"/>
+      <c r="A97" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C97" s="5"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-      <c r="B98" s="6"/>
+      <c r="A98" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C98" s="5"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="4"/>
-      <c r="B99" s="6"/>
+      <c r="A99" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="4"/>
-      <c r="B100" s="6"/>
+      <c r="A100" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="4"/>
-      <c r="B101" s="6"/>
+      <c r="A101" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C101" s="5"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="4"/>
-      <c r="B102" s="6"/>
+      <c r="A102" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C102" s="5"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="4"/>
-      <c r="B103" s="6"/>
+      <c r="A103" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C103" s="5"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="4"/>
-      <c r="B104" s="6"/>
+      <c r="A104" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C104" s="5"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="4"/>
-      <c r="B105" s="6"/>
+      <c r="A105" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C105" s="5"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4"/>
-      <c r="B106" s="6"/>
+      <c r="A106" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4"/>
-      <c r="B107" s="6"/>
+      <c r="A107" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4"/>
-      <c r="B108" s="6"/>
+      <c r="A108" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4"/>
-      <c r="B109" s="6"/>
+      <c r="A109" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4"/>
-      <c r="B110" s="6"/>
+      <c r="A110" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4"/>
-      <c r="B111" s="6"/>
+      <c r="A111" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
-      <c r="B112" s="6"/>
+      <c r="A112" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C112" s="5"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4"/>
-      <c r="B113" s="6"/>
+      <c r="A113" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C113" s="5"/>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
-      <c r="B114" s="6"/>
+      <c r="A114" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C114" s="5"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="4"/>
-      <c r="B115" s="6"/>
+      <c r="A115" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="4"/>
-      <c r="B116" s="6"/>
+      <c r="A116" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
-      <c r="B117" s="6"/>
+      <c r="A117" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="4"/>
-      <c r="B118" s="6"/>
+      <c r="A118" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
-      <c r="B119" s="6"/>
+      <c r="A119" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C119" s="5"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="4"/>
-      <c r="B120" s="6"/>
+      <c r="A120" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C120" s="5"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="4"/>
-      <c r="B121" s="6"/>
+      <c r="A121" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C121" s="5"/>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-      <c r="B122" s="6"/>
+      <c r="A122" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C122" s="5"/>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="4"/>
-      <c r="B123" s="6"/>
+      <c r="A123" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C123" s="5"/>
     </row>
   </sheetData>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F99265-8A12-4401-A202-A97EFE990DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699F3627-B0D7-4416-A3C3-A67D9FED524F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="129">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,370 +45,376 @@
     <t>.</t>
   </si>
   <si>
-    <t>131388385</t>
-  </si>
-  <si>
-    <t>131506326</t>
-  </si>
-  <si>
-    <t>131578343</t>
-  </si>
-  <si>
-    <t>131624750</t>
-  </si>
-  <si>
-    <t>132178349</t>
-  </si>
-  <si>
-    <t>132341330</t>
-  </si>
-  <si>
-    <t>132362738</t>
-  </si>
-  <si>
-    <t>132444484</t>
-  </si>
-  <si>
-    <t>133660903</t>
-  </si>
-  <si>
-    <t>134251609</t>
-  </si>
-  <si>
-    <t>135207160</t>
-  </si>
-  <si>
-    <t>135207256</t>
-  </si>
-  <si>
-    <t>135207629</t>
-  </si>
-  <si>
-    <t>135207951</t>
-  </si>
-  <si>
-    <t>135208277</t>
-  </si>
-  <si>
-    <t>135208380</t>
-  </si>
-  <si>
-    <t>135208539</t>
-  </si>
-  <si>
-    <t>135208705</t>
-  </si>
-  <si>
-    <t>135208710</t>
-  </si>
-  <si>
-    <t>135209012</t>
-  </si>
-  <si>
-    <t>135209290</t>
-  </si>
-  <si>
-    <t>135209768</t>
-  </si>
-  <si>
-    <t>135209789</t>
-  </si>
-  <si>
-    <t>135209941</t>
-  </si>
-  <si>
-    <t>135209988</t>
-  </si>
-  <si>
-    <t>135210020</t>
-  </si>
-  <si>
-    <t>135210283</t>
-  </si>
-  <si>
-    <t>135210345</t>
-  </si>
-  <si>
-    <t>135210444</t>
-  </si>
-  <si>
-    <t>135211010</t>
-  </si>
-  <si>
-    <t>135211102</t>
-  </si>
-  <si>
-    <t>135211542</t>
-  </si>
-  <si>
-    <t>135211600</t>
-  </si>
-  <si>
-    <t>135211849</t>
-  </si>
-  <si>
-    <t>135212079</t>
-  </si>
-  <si>
-    <t>135212084</t>
-  </si>
-  <si>
-    <t>135212250</t>
-  </si>
-  <si>
-    <t>135212284</t>
-  </si>
-  <si>
-    <t>135212302</t>
-  </si>
-  <si>
-    <t>135212304</t>
-  </si>
-  <si>
-    <t>135212567</t>
-  </si>
-  <si>
-    <t>135212590</t>
-  </si>
-  <si>
-    <t>135212644</t>
-  </si>
-  <si>
-    <t>135212655</t>
-  </si>
-  <si>
-    <t>135212771</t>
-  </si>
-  <si>
-    <t>135212822</t>
-  </si>
-  <si>
-    <t>135212962</t>
-  </si>
-  <si>
-    <t>135213076</t>
-  </si>
-  <si>
-    <t>135213375</t>
-  </si>
-  <si>
-    <t>135213522</t>
-  </si>
-  <si>
-    <t>135213561</t>
-  </si>
-  <si>
-    <t>135213602</t>
-  </si>
-  <si>
-    <t>135213849</t>
-  </si>
-  <si>
-    <t>135214265</t>
-  </si>
-  <si>
-    <t>135214309</t>
-  </si>
-  <si>
-    <t>135214381</t>
-  </si>
-  <si>
-    <t>135214515</t>
-  </si>
-  <si>
-    <t>135214693</t>
-  </si>
-  <si>
-    <t>135214696</t>
-  </si>
-  <si>
-    <t>135214735</t>
-  </si>
-  <si>
-    <t>135215088</t>
-  </si>
-  <si>
-    <t>135215091</t>
-  </si>
-  <si>
-    <t>135215762</t>
-  </si>
-  <si>
-    <t>135215851</t>
-  </si>
-  <si>
-    <t>135215920</t>
-  </si>
-  <si>
-    <t>135216004</t>
-  </si>
-  <si>
-    <t>135216190</t>
-  </si>
-  <si>
-    <t>135216398</t>
-  </si>
-  <si>
-    <t>135216399</t>
-  </si>
-  <si>
-    <t>135216527</t>
-  </si>
-  <si>
-    <t>135216719</t>
-  </si>
-  <si>
-    <t>135216935</t>
-  </si>
-  <si>
-    <t>135216953</t>
-  </si>
-  <si>
-    <t>135217260</t>
-  </si>
-  <si>
-    <t>135217307</t>
-  </si>
-  <si>
-    <t>135217624</t>
-  </si>
-  <si>
-    <t>135217782</t>
-  </si>
-  <si>
-    <t>135217818</t>
-  </si>
-  <si>
-    <t>135217909</t>
-  </si>
-  <si>
-    <t>135217953</t>
-  </si>
-  <si>
-    <t>135218023</t>
-  </si>
-  <si>
-    <t>135218376</t>
-  </si>
-  <si>
-    <t>135218654</t>
-  </si>
-  <si>
-    <t>135218710</t>
-  </si>
-  <si>
-    <t>135218761</t>
-  </si>
-  <si>
-    <t>135218850</t>
-  </si>
-  <si>
-    <t>135219054</t>
-  </si>
-  <si>
-    <t>135219064</t>
-  </si>
-  <si>
-    <t>135219089</t>
-  </si>
-  <si>
-    <t>135219223</t>
-  </si>
-  <si>
-    <t>135219311</t>
-  </si>
-  <si>
-    <t>135219384</t>
-  </si>
-  <si>
-    <t>135219422</t>
-  </si>
-  <si>
-    <t>135219446</t>
-  </si>
-  <si>
-    <t>135220531</t>
-  </si>
-  <si>
-    <t>135220589</t>
-  </si>
-  <si>
-    <t>135220834</t>
-  </si>
-  <si>
-    <t>135220866</t>
-  </si>
-  <si>
-    <t>135220999</t>
-  </si>
-  <si>
-    <t>135221053</t>
-  </si>
-  <si>
-    <t>135221510</t>
-  </si>
-  <si>
-    <t>135221690</t>
-  </si>
-  <si>
-    <t>135221715</t>
-  </si>
-  <si>
-    <t>135221739</t>
-  </si>
-  <si>
-    <t>135221871</t>
-  </si>
-  <si>
-    <t>135222203</t>
-  </si>
-  <si>
-    <t>135222294</t>
-  </si>
-  <si>
-    <t>135222320</t>
-  </si>
-  <si>
-    <t>135222384</t>
-  </si>
-  <si>
-    <t>135222570</t>
-  </si>
-  <si>
-    <t>135222960</t>
-  </si>
-  <si>
-    <t>135223146</t>
-  </si>
-  <si>
-    <t>135223390</t>
-  </si>
-  <si>
-    <t>135223462</t>
-  </si>
-  <si>
-    <t>135223475</t>
-  </si>
-  <si>
-    <t>135223621</t>
-  </si>
-  <si>
-    <t>135223651</t>
-  </si>
-  <si>
-    <t>135223777</t>
-  </si>
-  <si>
-    <t>135223860</t>
-  </si>
-  <si>
-    <t>135224194</t>
-  </si>
-  <si>
-    <t>135225727</t>
-  </si>
-  <si>
-    <t>135226550</t>
+    <t>130534492</t>
+  </si>
+  <si>
+    <t>130736586</t>
+  </si>
+  <si>
+    <t>130863628</t>
+  </si>
+  <si>
+    <t>130887860</t>
+  </si>
+  <si>
+    <t>130927862</t>
+  </si>
+  <si>
+    <t>131188294</t>
+  </si>
+  <si>
+    <t>131397503</t>
+  </si>
+  <si>
+    <t>131686906</t>
+  </si>
+  <si>
+    <t>131843228</t>
+  </si>
+  <si>
+    <t>132180553</t>
+  </si>
+  <si>
+    <t>132782584</t>
+  </si>
+  <si>
+    <t>132798675</t>
+  </si>
+  <si>
+    <t>134053339</t>
+  </si>
+  <si>
+    <t>135226841</t>
+  </si>
+  <si>
+    <t>135227103</t>
+  </si>
+  <si>
+    <t>135227656</t>
+  </si>
+  <si>
+    <t>135227855</t>
+  </si>
+  <si>
+    <t>135228209</t>
+  </si>
+  <si>
+    <t>135229166</t>
+  </si>
+  <si>
+    <t>135229265</t>
+  </si>
+  <si>
+    <t>135229730</t>
+  </si>
+  <si>
+    <t>135229790</t>
+  </si>
+  <si>
+    <t>135230203</t>
+  </si>
+  <si>
+    <t>135230254</t>
+  </si>
+  <si>
+    <t>135230366</t>
+  </si>
+  <si>
+    <t>135230543</t>
+  </si>
+  <si>
+    <t>135230582</t>
+  </si>
+  <si>
+    <t>135230640</t>
+  </si>
+  <si>
+    <t>135230689</t>
+  </si>
+  <si>
+    <t>135230792</t>
+  </si>
+  <si>
+    <t>135230900</t>
+  </si>
+  <si>
+    <t>135231253</t>
+  </si>
+  <si>
+    <t>135231632</t>
+  </si>
+  <si>
+    <t>135231782</t>
+  </si>
+  <si>
+    <t>135231829</t>
+  </si>
+  <si>
+    <t>135232024</t>
+  </si>
+  <si>
+    <t>135232464</t>
+  </si>
+  <si>
+    <t>135232512</t>
+  </si>
+  <si>
+    <t>135232625</t>
+  </si>
+  <si>
+    <t>135232708</t>
+  </si>
+  <si>
+    <t>135232927</t>
+  </si>
+  <si>
+    <t>135232968</t>
+  </si>
+  <si>
+    <t>135233052</t>
+  </si>
+  <si>
+    <t>135233274</t>
+  </si>
+  <si>
+    <t>135233389</t>
+  </si>
+  <si>
+    <t>135233427</t>
+  </si>
+  <si>
+    <t>135233463</t>
+  </si>
+  <si>
+    <t>135233645</t>
+  </si>
+  <si>
+    <t>135234083</t>
+  </si>
+  <si>
+    <t>135234370</t>
+  </si>
+  <si>
+    <t>135234386</t>
+  </si>
+  <si>
+    <t>135234396</t>
+  </si>
+  <si>
+    <t>135234428</t>
+  </si>
+  <si>
+    <t>135234434</t>
+  </si>
+  <si>
+    <t>135234636</t>
+  </si>
+  <si>
+    <t>135234746</t>
+  </si>
+  <si>
+    <t>135234887</t>
+  </si>
+  <si>
+    <t>135235024</t>
+  </si>
+  <si>
+    <t>135235053</t>
+  </si>
+  <si>
+    <t>135235976</t>
+  </si>
+  <si>
+    <t>135236107</t>
+  </si>
+  <si>
+    <t>135236215</t>
+  </si>
+  <si>
+    <t>135236225</t>
+  </si>
+  <si>
+    <t>135236306</t>
+  </si>
+  <si>
+    <t>135236606</t>
+  </si>
+  <si>
+    <t>135236754</t>
+  </si>
+  <si>
+    <t>135236926</t>
+  </si>
+  <si>
+    <t>135237007</t>
+  </si>
+  <si>
+    <t>135237102</t>
+  </si>
+  <si>
+    <t>135237258</t>
+  </si>
+  <si>
+    <t>135237480</t>
+  </si>
+  <si>
+    <t>135237661</t>
+  </si>
+  <si>
+    <t>135237725</t>
+  </si>
+  <si>
+    <t>135237956</t>
+  </si>
+  <si>
+    <t>135238048</t>
+  </si>
+  <si>
+    <t>135238253</t>
+  </si>
+  <si>
+    <t>135238827</t>
+  </si>
+  <si>
+    <t>135239073</t>
+  </si>
+  <si>
+    <t>135239108</t>
+  </si>
+  <si>
+    <t>135239332</t>
+  </si>
+  <si>
+    <t>135239356</t>
+  </si>
+  <si>
+    <t>135239811</t>
+  </si>
+  <si>
+    <t>135239919</t>
+  </si>
+  <si>
+    <t>135240065</t>
+  </si>
+  <si>
+    <t>135240497</t>
+  </si>
+  <si>
+    <t>135240565</t>
+  </si>
+  <si>
+    <t>135240616</t>
+  </si>
+  <si>
+    <t>135240625</t>
+  </si>
+  <si>
+    <t>135240947</t>
+  </si>
+  <si>
+    <t>135240999</t>
+  </si>
+  <si>
+    <t>135241387</t>
+  </si>
+  <si>
+    <t>135241502</t>
+  </si>
+  <si>
+    <t>135241600</t>
+  </si>
+  <si>
+    <t>135242165</t>
+  </si>
+  <si>
+    <t>135242492</t>
+  </si>
+  <si>
+    <t>135242509</t>
+  </si>
+  <si>
+    <t>135242583</t>
+  </si>
+  <si>
+    <t>135242678</t>
+  </si>
+  <si>
+    <t>135242702</t>
+  </si>
+  <si>
+    <t>135242742</t>
+  </si>
+  <si>
+    <t>135242937</t>
+  </si>
+  <si>
+    <t>135242958</t>
+  </si>
+  <si>
+    <t>135243035</t>
+  </si>
+  <si>
+    <t>135243384</t>
+  </si>
+  <si>
+    <t>135243448</t>
+  </si>
+  <si>
+    <t>135243659</t>
+  </si>
+  <si>
+    <t>135244118</t>
+  </si>
+  <si>
+    <t>135244122</t>
+  </si>
+  <si>
+    <t>135244271</t>
+  </si>
+  <si>
+    <t>135244428</t>
+  </si>
+  <si>
+    <t>135244600</t>
+  </si>
+  <si>
+    <t>135244724</t>
+  </si>
+  <si>
+    <t>135244746</t>
+  </si>
+  <si>
+    <t>135245031</t>
+  </si>
+  <si>
+    <t>135245172</t>
+  </si>
+  <si>
+    <t>135245182</t>
+  </si>
+  <si>
+    <t>135246134</t>
+  </si>
+  <si>
+    <t>135246201</t>
+  </si>
+  <si>
+    <t>135246470</t>
+  </si>
+  <si>
+    <t>135246595</t>
+  </si>
+  <si>
+    <t>135246650</t>
+  </si>
+  <si>
+    <t>135246716</t>
+  </si>
+  <si>
+    <t>135246866</t>
+  </si>
+  <si>
+    <t>135247010</t>
   </si>
 </sst>
 </file>
@@ -813,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -906,7 +912,9 @@
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -915,7 +923,9 @@
       <c r="B9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -924,7 +934,9 @@
       <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -933,7 +945,9 @@
       <c r="B11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -942,7 +956,9 @@
       <c r="B12" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -951,7 +967,9 @@
       <c r="B13" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -960,7 +978,9 @@
       <c r="B14" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -969,7 +989,9 @@
       <c r="B15" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -978,7 +1000,9 @@
       <c r="B16" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -987,7 +1011,9 @@
       <c r="B17" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -996,7 +1022,9 @@
       <c r="B18" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1005,7 +1033,9 @@
       <c r="B19" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1014,7 +1044,9 @@
       <c r="B20" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
@@ -1023,7 +1055,9 @@
       <c r="B21" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -1032,7 +1066,9 @@
       <c r="B22" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1041,7 +1077,9 @@
       <c r="B23" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1050,7 +1088,9 @@
       <c r="B24" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1059,7 +1099,9 @@
       <c r="B25" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="5"/>
+      <c r="C25" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1068,7 +1110,9 @@
       <c r="B26" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1077,7 +1121,9 @@
       <c r="B27" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -1086,7 +1132,9 @@
       <c r="B28" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="5"/>
+      <c r="C28" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1095,7 +1143,9 @@
       <c r="B29" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="5"/>
+      <c r="C29" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1104,7 +1154,9 @@
       <c r="B30" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="5"/>
+      <c r="C30" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1113,7 +1165,9 @@
       <c r="B31" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="5"/>
+      <c r="C31" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1122,7 +1176,9 @@
       <c r="B32" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
@@ -1131,7 +1187,9 @@
       <c r="B33" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="5"/>
+      <c r="C33" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -1140,7 +1198,9 @@
       <c r="B34" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="5"/>
+      <c r="C34" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
@@ -1149,7 +1209,9 @@
       <c r="B35" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="5"/>
+      <c r="C35" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -1158,7 +1220,9 @@
       <c r="B36" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="5"/>
+      <c r="C36" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -1167,7 +1231,9 @@
       <c r="B37" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="5"/>
+      <c r="C37" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -1176,7 +1242,9 @@
       <c r="B38" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="5"/>
+      <c r="C38" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -1185,7 +1253,9 @@
       <c r="B39" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="5"/>
+      <c r="C39" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -1194,7 +1264,9 @@
       <c r="B40" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="5"/>
+      <c r="C40" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
@@ -1203,7 +1275,9 @@
       <c r="B41" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="5"/>
+      <c r="C41" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -1212,7 +1286,9 @@
       <c r="B42" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="5"/>
+      <c r="C42" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
@@ -1221,7 +1297,9 @@
       <c r="B43" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C43" s="5"/>
+      <c r="C43" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
@@ -1230,7 +1308,9 @@
       <c r="B44" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C44" s="5"/>
+      <c r="C44" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
@@ -1239,7 +1319,9 @@
       <c r="B45" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="5"/>
+      <c r="C45" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
@@ -1248,7 +1330,9 @@
       <c r="B46" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="5"/>
+      <c r="C46" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
@@ -1257,7 +1341,9 @@
       <c r="B47" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="5"/>
+      <c r="C47" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
@@ -1266,7 +1352,9 @@
       <c r="B48" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C48" s="5"/>
+      <c r="C48" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -1275,7 +1363,9 @@
       <c r="B49" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C49" s="5"/>
+      <c r="C49" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
@@ -1284,7 +1374,9 @@
       <c r="B50" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C50" s="5"/>
+      <c r="C50" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
@@ -1293,7 +1385,9 @@
       <c r="B51" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="5"/>
+      <c r="C51" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
@@ -1302,7 +1396,9 @@
       <c r="B52" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="5"/>
+      <c r="C52" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
@@ -1311,7 +1407,9 @@
       <c r="B53" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="5"/>
+      <c r="C53" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -1320,7 +1418,9 @@
       <c r="B54" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C54" s="5"/>
+      <c r="C54" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
@@ -1329,7 +1429,9 @@
       <c r="B55" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C55" s="5"/>
+      <c r="C55" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
@@ -1338,7 +1440,9 @@
       <c r="B56" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="5"/>
+      <c r="C56" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
@@ -1347,7 +1451,9 @@
       <c r="B57" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C57" s="5"/>
+      <c r="C57" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -1356,7 +1462,9 @@
       <c r="B58" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="5"/>
+      <c r="C58" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
@@ -1365,7 +1473,9 @@
       <c r="B59" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C59" s="5"/>
+      <c r="C59" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
@@ -1374,7 +1484,9 @@
       <c r="B60" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C60" s="5"/>
+      <c r="C60" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
@@ -1383,7 +1495,9 @@
       <c r="B61" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C61" s="5"/>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -1392,7 +1506,9 @@
       <c r="B62" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="5"/>
+      <c r="C62" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
@@ -1401,7 +1517,9 @@
       <c r="B63" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C63" s="5"/>
+      <c r="C63" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -1410,7 +1528,9 @@
       <c r="B64" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="5"/>
+      <c r="C64" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
@@ -1419,7 +1539,9 @@
       <c r="B65" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="5"/>
+      <c r="C65" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
@@ -1428,7 +1550,9 @@
       <c r="B66" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C66" s="5"/>
+      <c r="C66" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
@@ -1437,7 +1561,9 @@
       <c r="B67" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C67" s="5"/>
+      <c r="C67" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
@@ -1446,7 +1572,9 @@
       <c r="B68" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C68" s="5"/>
+      <c r="C68" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
@@ -1455,7 +1583,9 @@
       <c r="B69" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="5"/>
+      <c r="C69" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
@@ -1464,7 +1594,9 @@
       <c r="B70" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C70" s="5"/>
+      <c r="C70" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
@@ -1473,7 +1605,9 @@
       <c r="B71" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="5"/>
+      <c r="C71" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
@@ -1482,7 +1616,9 @@
       <c r="B72" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C72" s="5"/>
+      <c r="C72" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
@@ -1491,7 +1627,9 @@
       <c r="B73" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C73" s="5"/>
+      <c r="C73" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
@@ -1500,7 +1638,9 @@
       <c r="B74" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C74" s="5"/>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
@@ -1509,7 +1649,9 @@
       <c r="B75" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="5"/>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
@@ -1518,7 +1660,9 @@
       <c r="B76" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="5"/>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
@@ -1527,7 +1671,9 @@
       <c r="B77" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C77" s="5"/>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
@@ -1536,7 +1682,9 @@
       <c r="B78" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C78" s="5"/>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
@@ -1545,7 +1693,9 @@
       <c r="B79" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C79" s="5"/>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
@@ -1554,7 +1704,9 @@
       <c r="B80" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="5"/>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
@@ -1563,7 +1715,9 @@
       <c r="B81" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="5"/>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
@@ -1572,7 +1726,9 @@
       <c r="B82" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C82" s="5"/>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
@@ -1581,7 +1737,9 @@
       <c r="B83" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C83" s="5"/>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
@@ -1590,7 +1748,9 @@
       <c r="B84" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="5"/>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
@@ -1599,7 +1759,9 @@
       <c r="B85" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C85" s="5"/>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
@@ -1608,7 +1770,9 @@
       <c r="B86" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C86" s="5"/>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
@@ -1617,7 +1781,9 @@
       <c r="B87" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C87" s="5"/>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
@@ -1626,7 +1792,9 @@
       <c r="B88" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C88" s="5"/>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
@@ -1635,7 +1803,9 @@
       <c r="B89" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C89" s="5"/>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
@@ -1644,7 +1814,9 @@
       <c r="B90" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C90" s="5"/>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
@@ -1653,7 +1825,9 @@
       <c r="B91" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="5"/>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
@@ -1662,7 +1836,9 @@
       <c r="B92" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C92" s="5"/>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
@@ -1671,7 +1847,9 @@
       <c r="B93" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C93" s="5"/>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
@@ -1680,7 +1858,9 @@
       <c r="B94" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C94" s="5"/>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
@@ -1689,7 +1869,9 @@
       <c r="B95" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C95" s="5"/>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
@@ -1698,7 +1880,9 @@
       <c r="B96" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C96" s="5"/>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
@@ -1707,7 +1891,9 @@
       <c r="B97" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C97" s="5"/>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
@@ -1716,7 +1902,9 @@
       <c r="B98" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C98" s="5"/>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
@@ -1725,7 +1913,9 @@
       <c r="B99" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C99" s="5"/>
+      <c r="C99" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
@@ -1734,7 +1924,9 @@
       <c r="B100" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C100" s="5"/>
+      <c r="C100" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
@@ -1743,7 +1935,9 @@
       <c r="B101" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="5"/>
+      <c r="C101" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
@@ -1752,7 +1946,9 @@
       <c r="B102" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C102" s="5"/>
+      <c r="C102" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
@@ -1761,7 +1957,9 @@
       <c r="B103" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C103" s="5"/>
+      <c r="C103" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
@@ -1770,7 +1968,9 @@
       <c r="B104" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C104" s="5"/>
+      <c r="C104" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
@@ -1779,7 +1979,9 @@
       <c r="B105" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C105" s="5"/>
+      <c r="C105" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
@@ -1788,7 +1990,9 @@
       <c r="B106" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C106" s="5"/>
+      <c r="C106" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
@@ -1797,7 +2001,9 @@
       <c r="B107" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C107" s="5"/>
+      <c r="C107" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
@@ -1806,7 +2012,9 @@
       <c r="B108" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C108" s="5"/>
+      <c r="C108" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
@@ -1815,7 +2023,9 @@
       <c r="B109" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C109" s="5"/>
+      <c r="C109" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
@@ -1824,7 +2034,9 @@
       <c r="B110" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C110" s="5"/>
+      <c r="C110" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
@@ -1833,7 +2045,9 @@
       <c r="B111" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C111" s="5"/>
+      <c r="C111" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -1842,7 +2056,9 @@
       <c r="B112" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C112" s="5"/>
+      <c r="C112" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
@@ -1851,7 +2067,9 @@
       <c r="B113" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C113" s="5"/>
+      <c r="C113" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
@@ -1860,7 +2078,9 @@
       <c r="B114" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C114" s="5"/>
+      <c r="C114" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
@@ -1869,7 +2089,9 @@
       <c r="B115" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C115" s="5"/>
+      <c r="C115" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
@@ -1878,7 +2100,9 @@
       <c r="B116" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C116" s="5"/>
+      <c r="C116" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
@@ -1887,7 +2111,9 @@
       <c r="B117" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C117" s="5"/>
+      <c r="C117" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
@@ -1896,7 +2122,9 @@
       <c r="B118" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C118" s="5"/>
+      <c r="C118" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
@@ -1905,7 +2133,9 @@
       <c r="B119" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C119" s="5"/>
+      <c r="C119" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
@@ -1914,7 +2144,9 @@
       <c r="B120" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C120" s="5"/>
+      <c r="C120" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
@@ -1923,7 +2155,9 @@
       <c r="B121" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C121" s="5"/>
+      <c r="C121" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
@@ -1932,7 +2166,9 @@
       <c r="B122" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C122" s="5"/>
+      <c r="C122" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
@@ -1941,10 +2177,34 @@
       <c r="B123" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C123" s="5"/>
+      <c r="C123" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C123" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C125" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699F3627-B0D7-4416-A3C3-A67D9FED524F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C542EC-F30E-4215-B0E0-F6E25BF6D826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="25815" yWindow="1800" windowWidth="21600" windowHeight="11385" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="661">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,376 +45,1972 @@
     <t>.</t>
   </si>
   <si>
-    <t>130534492</t>
-  </si>
-  <si>
-    <t>130736586</t>
-  </si>
-  <si>
-    <t>130863628</t>
-  </si>
-  <si>
-    <t>130887860</t>
-  </si>
-  <si>
-    <t>130927862</t>
-  </si>
-  <si>
-    <t>131188294</t>
-  </si>
-  <si>
-    <t>131397503</t>
-  </si>
-  <si>
-    <t>131686906</t>
-  </si>
-  <si>
-    <t>131843228</t>
-  </si>
-  <si>
-    <t>132180553</t>
-  </si>
-  <si>
-    <t>132782584</t>
-  </si>
-  <si>
-    <t>132798675</t>
-  </si>
-  <si>
-    <t>134053339</t>
-  </si>
-  <si>
-    <t>135226841</t>
-  </si>
-  <si>
-    <t>135227103</t>
-  </si>
-  <si>
-    <t>135227656</t>
-  </si>
-  <si>
-    <t>135227855</t>
-  </si>
-  <si>
-    <t>135228209</t>
-  </si>
-  <si>
-    <t>135229166</t>
-  </si>
-  <si>
-    <t>135229265</t>
-  </si>
-  <si>
-    <t>135229730</t>
-  </si>
-  <si>
-    <t>135229790</t>
-  </si>
-  <si>
-    <t>135230203</t>
-  </si>
-  <si>
-    <t>135230254</t>
-  </si>
-  <si>
-    <t>135230366</t>
-  </si>
-  <si>
-    <t>135230543</t>
-  </si>
-  <si>
-    <t>135230582</t>
-  </si>
-  <si>
-    <t>135230640</t>
-  </si>
-  <si>
-    <t>135230689</t>
-  </si>
-  <si>
-    <t>135230792</t>
-  </si>
-  <si>
-    <t>135230900</t>
-  </si>
-  <si>
-    <t>135231253</t>
-  </si>
-  <si>
-    <t>135231632</t>
-  </si>
-  <si>
-    <t>135231782</t>
-  </si>
-  <si>
-    <t>135231829</t>
-  </si>
-  <si>
-    <t>135232024</t>
-  </si>
-  <si>
-    <t>135232464</t>
-  </si>
-  <si>
-    <t>135232512</t>
-  </si>
-  <si>
-    <t>135232625</t>
-  </si>
-  <si>
-    <t>135232708</t>
-  </si>
-  <si>
-    <t>135232927</t>
-  </si>
-  <si>
-    <t>135232968</t>
-  </si>
-  <si>
-    <t>135233052</t>
-  </si>
-  <si>
-    <t>135233274</t>
-  </si>
-  <si>
-    <t>135233389</t>
-  </si>
-  <si>
-    <t>135233427</t>
-  </si>
-  <si>
-    <t>135233463</t>
-  </si>
-  <si>
-    <t>135233645</t>
-  </si>
-  <si>
-    <t>135234083</t>
-  </si>
-  <si>
-    <t>135234370</t>
-  </si>
-  <si>
-    <t>135234386</t>
-  </si>
-  <si>
-    <t>135234396</t>
-  </si>
-  <si>
-    <t>135234428</t>
-  </si>
-  <si>
-    <t>135234434</t>
-  </si>
-  <si>
-    <t>135234636</t>
-  </si>
-  <si>
-    <t>135234746</t>
-  </si>
-  <si>
-    <t>135234887</t>
-  </si>
-  <si>
-    <t>135235024</t>
-  </si>
-  <si>
-    <t>135235053</t>
-  </si>
-  <si>
-    <t>135235976</t>
-  </si>
-  <si>
-    <t>135236107</t>
-  </si>
-  <si>
-    <t>135236215</t>
-  </si>
-  <si>
-    <t>135236225</t>
-  </si>
-  <si>
-    <t>135236306</t>
-  </si>
-  <si>
-    <t>135236606</t>
-  </si>
-  <si>
-    <t>135236754</t>
-  </si>
-  <si>
-    <t>135236926</t>
-  </si>
-  <si>
-    <t>135237007</t>
-  </si>
-  <si>
-    <t>135237102</t>
-  </si>
-  <si>
-    <t>135237258</t>
-  </si>
-  <si>
-    <t>135237480</t>
-  </si>
-  <si>
-    <t>135237661</t>
-  </si>
-  <si>
-    <t>135237725</t>
-  </si>
-  <si>
-    <t>135237956</t>
-  </si>
-  <si>
-    <t>135238048</t>
-  </si>
-  <si>
-    <t>135238253</t>
-  </si>
-  <si>
-    <t>135238827</t>
-  </si>
-  <si>
-    <t>135239073</t>
-  </si>
-  <si>
-    <t>135239108</t>
-  </si>
-  <si>
-    <t>135239332</t>
-  </si>
-  <si>
-    <t>135239356</t>
-  </si>
-  <si>
-    <t>135239811</t>
-  </si>
-  <si>
-    <t>135239919</t>
-  </si>
-  <si>
-    <t>135240065</t>
-  </si>
-  <si>
-    <t>135240497</t>
-  </si>
-  <si>
-    <t>135240565</t>
-  </si>
-  <si>
-    <t>135240616</t>
-  </si>
-  <si>
-    <t>135240625</t>
-  </si>
-  <si>
-    <t>135240947</t>
-  </si>
-  <si>
-    <t>135240999</t>
-  </si>
-  <si>
-    <t>135241387</t>
-  </si>
-  <si>
-    <t>135241502</t>
-  </si>
-  <si>
-    <t>135241600</t>
-  </si>
-  <si>
-    <t>135242165</t>
-  </si>
-  <si>
-    <t>135242492</t>
-  </si>
-  <si>
-    <t>135242509</t>
-  </si>
-  <si>
-    <t>135242583</t>
-  </si>
-  <si>
-    <t>135242678</t>
-  </si>
-  <si>
-    <t>135242702</t>
-  </si>
-  <si>
-    <t>135242742</t>
-  </si>
-  <si>
-    <t>135242937</t>
-  </si>
-  <si>
-    <t>135242958</t>
-  </si>
-  <si>
-    <t>135243035</t>
-  </si>
-  <si>
-    <t>135243384</t>
-  </si>
-  <si>
-    <t>135243448</t>
-  </si>
-  <si>
-    <t>135243659</t>
-  </si>
-  <si>
-    <t>135244118</t>
-  </si>
-  <si>
-    <t>135244122</t>
-  </si>
-  <si>
-    <t>135244271</t>
-  </si>
-  <si>
-    <t>135244428</t>
-  </si>
-  <si>
-    <t>135244600</t>
-  </si>
-  <si>
-    <t>135244724</t>
-  </si>
-  <si>
-    <t>135244746</t>
-  </si>
-  <si>
-    <t>135245031</t>
-  </si>
-  <si>
-    <t>135245172</t>
-  </si>
-  <si>
-    <t>135245182</t>
-  </si>
-  <si>
-    <t>135246134</t>
-  </si>
-  <si>
-    <t>135246201</t>
-  </si>
-  <si>
-    <t>135246470</t>
-  </si>
-  <si>
-    <t>135246595</t>
-  </si>
-  <si>
-    <t>135246650</t>
-  </si>
-  <si>
-    <t>135246716</t>
-  </si>
-  <si>
-    <t>135246866</t>
-  </si>
-  <si>
-    <t>135247010</t>
+    <t>130114198</t>
+  </si>
+  <si>
+    <t>130616857</t>
+  </si>
+  <si>
+    <t>130654291</t>
+  </si>
+  <si>
+    <t>130674349</t>
+  </si>
+  <si>
+    <t>130705235</t>
+  </si>
+  <si>
+    <t>130729196</t>
+  </si>
+  <si>
+    <t>130730113</t>
+  </si>
+  <si>
+    <t>130824127</t>
+  </si>
+  <si>
+    <t>130929311</t>
+  </si>
+  <si>
+    <t>131059459</t>
+  </si>
+  <si>
+    <t>131210989</t>
+  </si>
+  <si>
+    <t>131235417</t>
+  </si>
+  <si>
+    <t>131270899</t>
+  </si>
+  <si>
+    <t>131286181</t>
+  </si>
+  <si>
+    <t>131568024</t>
+  </si>
+  <si>
+    <t>131607542</t>
+  </si>
+  <si>
+    <t>131652891</t>
+  </si>
+  <si>
+    <t>131683859</t>
+  </si>
+  <si>
+    <t>131747488</t>
+  </si>
+  <si>
+    <t>131862473</t>
+  </si>
+  <si>
+    <t>131922532</t>
+  </si>
+  <si>
+    <t>132022115</t>
+  </si>
+  <si>
+    <t>132077332</t>
+  </si>
+  <si>
+    <t>132182716</t>
+  </si>
+  <si>
+    <t>132261025</t>
+  </si>
+  <si>
+    <t>132318937</t>
+  </si>
+  <si>
+    <t>132381713</t>
+  </si>
+  <si>
+    <t>132518844</t>
+  </si>
+  <si>
+    <t>132521449</t>
+  </si>
+  <si>
+    <t>132619181</t>
+  </si>
+  <si>
+    <t>132704922</t>
+  </si>
+  <si>
+    <t>132733171</t>
+  </si>
+  <si>
+    <t>132744528</t>
+  </si>
+  <si>
+    <t>132788195</t>
+  </si>
+  <si>
+    <t>132839373</t>
+  </si>
+  <si>
+    <t>132899218</t>
+  </si>
+  <si>
+    <t>132946147</t>
+  </si>
+  <si>
+    <t>132950468</t>
+  </si>
+  <si>
+    <t>132970336</t>
+  </si>
+  <si>
+    <t>133040728</t>
+  </si>
+  <si>
+    <t>133107261</t>
+  </si>
+  <si>
+    <t>133136882</t>
+  </si>
+  <si>
+    <t>133146025</t>
+  </si>
+  <si>
+    <t>133164809</t>
+  </si>
+  <si>
+    <t>133215309</t>
+  </si>
+  <si>
+    <t>133269657</t>
+  </si>
+  <si>
+    <t>133285337</t>
+  </si>
+  <si>
+    <t>133467883</t>
+  </si>
+  <si>
+    <t>133513208</t>
+  </si>
+  <si>
+    <t>133600942</t>
+  </si>
+  <si>
+    <t>133609393</t>
+  </si>
+  <si>
+    <t>133619072</t>
+  </si>
+  <si>
+    <t>133666271</t>
+  </si>
+  <si>
+    <t>133736330</t>
+  </si>
+  <si>
+    <t>133797579</t>
+  </si>
+  <si>
+    <t>133820711</t>
+  </si>
+  <si>
+    <t>133840795</t>
+  </si>
+  <si>
+    <t>133959617</t>
+  </si>
+  <si>
+    <t>134006653</t>
+  </si>
+  <si>
+    <t>134010107</t>
+  </si>
+  <si>
+    <t>134042298</t>
+  </si>
+  <si>
+    <t>134051853</t>
+  </si>
+  <si>
+    <t>134184343</t>
+  </si>
+  <si>
+    <t>134460026</t>
+  </si>
+  <si>
+    <t>134629903</t>
+  </si>
+  <si>
+    <t>134730430</t>
+  </si>
+  <si>
+    <t>134991191</t>
+  </si>
+  <si>
+    <t>134998990</t>
+  </si>
+  <si>
+    <t>135042050</t>
+  </si>
+  <si>
+    <t>135069810</t>
+  </si>
+  <si>
+    <t>135091996</t>
+  </si>
+  <si>
+    <t>135121264</t>
+  </si>
+  <si>
+    <t>135247094</t>
+  </si>
+  <si>
+    <t>135247205</t>
+  </si>
+  <si>
+    <t>135247300</t>
+  </si>
+  <si>
+    <t>135247647</t>
+  </si>
+  <si>
+    <t>135248020</t>
+  </si>
+  <si>
+    <t>135248192</t>
+  </si>
+  <si>
+    <t>135248374</t>
+  </si>
+  <si>
+    <t>135248503</t>
+  </si>
+  <si>
+    <t>135248554</t>
+  </si>
+  <si>
+    <t>135248561</t>
+  </si>
+  <si>
+    <t>135248613</t>
+  </si>
+  <si>
+    <t>135248739</t>
+  </si>
+  <si>
+    <t>135248849</t>
+  </si>
+  <si>
+    <t>135248974</t>
+  </si>
+  <si>
+    <t>135249142</t>
+  </si>
+  <si>
+    <t>135249241</t>
+  </si>
+  <si>
+    <t>135249312</t>
+  </si>
+  <si>
+    <t>135249524</t>
+  </si>
+  <si>
+    <t>135249867</t>
+  </si>
+  <si>
+    <t>135249926</t>
+  </si>
+  <si>
+    <t>135250319</t>
+  </si>
+  <si>
+    <t>135250325</t>
+  </si>
+  <si>
+    <t>135250558</t>
+  </si>
+  <si>
+    <t>135250604</t>
+  </si>
+  <si>
+    <t>135250698</t>
+  </si>
+  <si>
+    <t>135250771</t>
+  </si>
+  <si>
+    <t>135250896</t>
+  </si>
+  <si>
+    <t>135251259</t>
+  </si>
+  <si>
+    <t>135251408</t>
+  </si>
+  <si>
+    <t>135251476</t>
+  </si>
+  <si>
+    <t>135252123</t>
+  </si>
+  <si>
+    <t>135252208</t>
+  </si>
+  <si>
+    <t>135252514</t>
+  </si>
+  <si>
+    <t>135252585</t>
+  </si>
+  <si>
+    <t>135253060</t>
+  </si>
+  <si>
+    <t>135253071</t>
+  </si>
+  <si>
+    <t>135253384</t>
+  </si>
+  <si>
+    <t>135253598</t>
+  </si>
+  <si>
+    <t>135253796</t>
+  </si>
+  <si>
+    <t>135254245</t>
+  </si>
+  <si>
+    <t>135254575</t>
+  </si>
+  <si>
+    <t>135255092</t>
+  </si>
+  <si>
+    <t>135255332</t>
+  </si>
+  <si>
+    <t>135255339</t>
+  </si>
+  <si>
+    <t>135255460</t>
+  </si>
+  <si>
+    <t>135255654</t>
+  </si>
+  <si>
+    <t>135256387</t>
+  </si>
+  <si>
+    <t>135256405</t>
+  </si>
+  <si>
+    <t>135256714</t>
+  </si>
+  <si>
+    <t>135256865</t>
+  </si>
+  <si>
+    <t>135256972</t>
+  </si>
+  <si>
+    <t>135257274</t>
+  </si>
+  <si>
+    <t>135258239</t>
+  </si>
+  <si>
+    <t>135258264</t>
+  </si>
+  <si>
+    <t>135258294</t>
+  </si>
+  <si>
+    <t>135258597</t>
+  </si>
+  <si>
+    <t>135258614</t>
+  </si>
+  <si>
+    <t>135258755</t>
+  </si>
+  <si>
+    <t>135258949</t>
+  </si>
+  <si>
+    <t>135259176</t>
+  </si>
+  <si>
+    <t>135259369</t>
+  </si>
+  <si>
+    <t>135259544</t>
+  </si>
+  <si>
+    <t>135259587</t>
+  </si>
+  <si>
+    <t>135259656</t>
+  </si>
+  <si>
+    <t>135260207</t>
+  </si>
+  <si>
+    <t>135260698</t>
+  </si>
+  <si>
+    <t>135260994</t>
+  </si>
+  <si>
+    <t>135261149</t>
+  </si>
+  <si>
+    <t>135261236</t>
+  </si>
+  <si>
+    <t>135261674</t>
+  </si>
+  <si>
+    <t>135261834</t>
+  </si>
+  <si>
+    <t>135261862</t>
+  </si>
+  <si>
+    <t>135262091</t>
+  </si>
+  <si>
+    <t>135262124</t>
+  </si>
+  <si>
+    <t>135262204</t>
+  </si>
+  <si>
+    <t>135262207</t>
+  </si>
+  <si>
+    <t>135262326</t>
+  </si>
+  <si>
+    <t>135262534</t>
+  </si>
+  <si>
+    <t>135262631</t>
+  </si>
+  <si>
+    <t>135262928</t>
+  </si>
+  <si>
+    <t>135263022</t>
+  </si>
+  <si>
+    <t>135263032</t>
+  </si>
+  <si>
+    <t>135263184</t>
+  </si>
+  <si>
+    <t>135263214</t>
+  </si>
+  <si>
+    <t>135263342</t>
+  </si>
+  <si>
+    <t>135263345</t>
+  </si>
+  <si>
+    <t>135263437</t>
+  </si>
+  <si>
+    <t>135263686</t>
+  </si>
+  <si>
+    <t>135263703</t>
+  </si>
+  <si>
+    <t>135263798</t>
+  </si>
+  <si>
+    <t>135264059</t>
+  </si>
+  <si>
+    <t>135264073</t>
+  </si>
+  <si>
+    <t>135264225</t>
+  </si>
+  <si>
+    <t>135264289</t>
+  </si>
+  <si>
+    <t>135264301</t>
+  </si>
+  <si>
+    <t>135264523</t>
+  </si>
+  <si>
+    <t>135264605</t>
+  </si>
+  <si>
+    <t>135264694</t>
+  </si>
+  <si>
+    <t>135264896</t>
+  </si>
+  <si>
+    <t>135264907</t>
+  </si>
+  <si>
+    <t>135265087</t>
+  </si>
+  <si>
+    <t>135265297</t>
+  </si>
+  <si>
+    <t>135265401</t>
+  </si>
+  <si>
+    <t>135265402</t>
+  </si>
+  <si>
+    <t>135265549</t>
+  </si>
+  <si>
+    <t>135265560</t>
+  </si>
+  <si>
+    <t>135265565</t>
+  </si>
+  <si>
+    <t>135265847</t>
+  </si>
+  <si>
+    <t>135265960</t>
+  </si>
+  <si>
+    <t>135266230</t>
+  </si>
+  <si>
+    <t>135267681</t>
+  </si>
+  <si>
+    <t>135267764</t>
+  </si>
+  <si>
+    <t>135267846</t>
+  </si>
+  <si>
+    <t>135267877</t>
+  </si>
+  <si>
+    <t>135268192</t>
+  </si>
+  <si>
+    <t>135268346</t>
+  </si>
+  <si>
+    <t>135268476</t>
+  </si>
+  <si>
+    <t>135268532</t>
+  </si>
+  <si>
+    <t>135268554</t>
+  </si>
+  <si>
+    <t>135269061</t>
+  </si>
+  <si>
+    <t>135269176</t>
+  </si>
+  <si>
+    <t>135269205</t>
+  </si>
+  <si>
+    <t>135269213</t>
+  </si>
+  <si>
+    <t>135269229</t>
+  </si>
+  <si>
+    <t>135269314</t>
+  </si>
+  <si>
+    <t>135269357</t>
+  </si>
+  <si>
+    <t>135269373</t>
+  </si>
+  <si>
+    <t>135269828</t>
+  </si>
+  <si>
+    <t>135269910</t>
+  </si>
+  <si>
+    <t>135270100</t>
+  </si>
+  <si>
+    <t>135270238</t>
+  </si>
+  <si>
+    <t>135270315</t>
+  </si>
+  <si>
+    <t>135270336</t>
+  </si>
+  <si>
+    <t>135270363</t>
+  </si>
+  <si>
+    <t>135270449</t>
+  </si>
+  <si>
+    <t>135270618</t>
+  </si>
+  <si>
+    <t>135270694</t>
+  </si>
+  <si>
+    <t>135270727</t>
+  </si>
+  <si>
+    <t>135270889</t>
+  </si>
+  <si>
+    <t>135271082</t>
+  </si>
+  <si>
+    <t>135271102</t>
+  </si>
+  <si>
+    <t>135271429</t>
+  </si>
+  <si>
+    <t>135271755</t>
+  </si>
+  <si>
+    <t>135271768</t>
+  </si>
+  <si>
+    <t>135271972</t>
+  </si>
+  <si>
+    <t>135272056</t>
+  </si>
+  <si>
+    <t>135272238</t>
+  </si>
+  <si>
+    <t>135272303</t>
+  </si>
+  <si>
+    <t>135272432</t>
+  </si>
+  <si>
+    <t>135272445</t>
+  </si>
+  <si>
+    <t>135272884</t>
+  </si>
+  <si>
+    <t>135272895</t>
+  </si>
+  <si>
+    <t>135272930</t>
+  </si>
+  <si>
+    <t>135273181</t>
+  </si>
+  <si>
+    <t>135273221</t>
+  </si>
+  <si>
+    <t>135273459</t>
+  </si>
+  <si>
+    <t>135273503</t>
+  </si>
+  <si>
+    <t>135273563</t>
+  </si>
+  <si>
+    <t>135273610</t>
+  </si>
+  <si>
+    <t>135273844</t>
+  </si>
+  <si>
+    <t>135273927</t>
+  </si>
+  <si>
+    <t>135273973</t>
+  </si>
+  <si>
+    <t>135274009</t>
+  </si>
+  <si>
+    <t>135274090</t>
+  </si>
+  <si>
+    <t>135274115</t>
+  </si>
+  <si>
+    <t>135274280</t>
+  </si>
+  <si>
+    <t>135274867</t>
+  </si>
+  <si>
+    <t>135274979</t>
+  </si>
+  <si>
+    <t>135275007</t>
+  </si>
+  <si>
+    <t>135275040</t>
+  </si>
+  <si>
+    <t>135275613</t>
+  </si>
+  <si>
+    <t>135275624</t>
+  </si>
+  <si>
+    <t>135275846</t>
+  </si>
+  <si>
+    <t>135275858</t>
+  </si>
+  <si>
+    <t>135275942</t>
+  </si>
+  <si>
+    <t>135276021</t>
+  </si>
+  <si>
+    <t>135276025</t>
+  </si>
+  <si>
+    <t>135276156</t>
+  </si>
+  <si>
+    <t>135276251</t>
+  </si>
+  <si>
+    <t>135276263</t>
+  </si>
+  <si>
+    <t>135276369</t>
+  </si>
+  <si>
+    <t>135276377</t>
+  </si>
+  <si>
+    <t>135276658</t>
+  </si>
+  <si>
+    <t>135276989</t>
+  </si>
+  <si>
+    <t>135277163</t>
+  </si>
+  <si>
+    <t>135277262</t>
+  </si>
+  <si>
+    <t>135277419</t>
+  </si>
+  <si>
+    <t>135277970</t>
+  </si>
+  <si>
+    <t>135278044</t>
+  </si>
+  <si>
+    <t>135278065</t>
+  </si>
+  <si>
+    <t>135278229</t>
+  </si>
+  <si>
+    <t>135278642</t>
+  </si>
+  <si>
+    <t>135278872</t>
+  </si>
+  <si>
+    <t>135278883</t>
+  </si>
+  <si>
+    <t>135278965</t>
+  </si>
+  <si>
+    <t>135279133</t>
+  </si>
+  <si>
+    <t>135279301</t>
+  </si>
+  <si>
+    <t>135279381</t>
+  </si>
+  <si>
+    <t>135279406</t>
+  </si>
+  <si>
+    <t>135279473</t>
+  </si>
+  <si>
+    <t>135279476</t>
+  </si>
+  <si>
+    <t>135279526</t>
+  </si>
+  <si>
+    <t>135279606</t>
+  </si>
+  <si>
+    <t>135279620</t>
+  </si>
+  <si>
+    <t>135279638</t>
+  </si>
+  <si>
+    <t>135279684</t>
+  </si>
+  <si>
+    <t>135279809</t>
+  </si>
+  <si>
+    <t>135279877</t>
+  </si>
+  <si>
+    <t>135279912</t>
+  </si>
+  <si>
+    <t>135279913</t>
+  </si>
+  <si>
+    <t>135279927</t>
+  </si>
+  <si>
+    <t>135279960</t>
+  </si>
+  <si>
+    <t>135280418</t>
+  </si>
+  <si>
+    <t>135280534</t>
+  </si>
+  <si>
+    <t>135280709</t>
+  </si>
+  <si>
+    <t>135280763</t>
+  </si>
+  <si>
+    <t>135280912</t>
+  </si>
+  <si>
+    <t>135281237</t>
+  </si>
+  <si>
+    <t>135281324</t>
+  </si>
+  <si>
+    <t>135281373</t>
+  </si>
+  <si>
+    <t>135281397</t>
+  </si>
+  <si>
+    <t>135281678</t>
+  </si>
+  <si>
+    <t>135281877</t>
+  </si>
+  <si>
+    <t>135281890</t>
+  </si>
+  <si>
+    <t>135281948</t>
+  </si>
+  <si>
+    <t>135282036</t>
+  </si>
+  <si>
+    <t>135282492</t>
+  </si>
+  <si>
+    <t>135282544</t>
+  </si>
+  <si>
+    <t>135282561</t>
+  </si>
+  <si>
+    <t>135282610</t>
+  </si>
+  <si>
+    <t>135282844</t>
+  </si>
+  <si>
+    <t>135282870</t>
+  </si>
+  <si>
+    <t>135282911</t>
+  </si>
+  <si>
+    <t>135283050</t>
+  </si>
+  <si>
+    <t>135283221</t>
+  </si>
+  <si>
+    <t>135283325</t>
+  </si>
+  <si>
+    <t>135283342</t>
+  </si>
+  <si>
+    <t>135283661</t>
+  </si>
+  <si>
+    <t>135283686</t>
+  </si>
+  <si>
+    <t>135283764</t>
+  </si>
+  <si>
+    <t>135283823</t>
+  </si>
+  <si>
+    <t>135284000</t>
+  </si>
+  <si>
+    <t>135284017</t>
+  </si>
+  <si>
+    <t>135284090</t>
+  </si>
+  <si>
+    <t>135284384</t>
+  </si>
+  <si>
+    <t>135284562</t>
+  </si>
+  <si>
+    <t>135284741</t>
+  </si>
+  <si>
+    <t>135284756</t>
+  </si>
+  <si>
+    <t>135284785</t>
+  </si>
+  <si>
+    <t>135284818</t>
+  </si>
+  <si>
+    <t>135284860</t>
+  </si>
+  <si>
+    <t>135284898</t>
+  </si>
+  <si>
+    <t>135284995</t>
+  </si>
+  <si>
+    <t>135285004</t>
+  </si>
+  <si>
+    <t>135285016</t>
+  </si>
+  <si>
+    <t>135285137</t>
+  </si>
+  <si>
+    <t>135285138</t>
+  </si>
+  <si>
+    <t>135285183</t>
+  </si>
+  <si>
+    <t>135285220</t>
+  </si>
+  <si>
+    <t>135285223</t>
+  </si>
+  <si>
+    <t>135285241</t>
+  </si>
+  <si>
+    <t>135285288</t>
+  </si>
+  <si>
+    <t>135285357</t>
+  </si>
+  <si>
+    <t>135285394</t>
+  </si>
+  <si>
+    <t>135285620</t>
+  </si>
+  <si>
+    <t>135285667</t>
+  </si>
+  <si>
+    <t>135285694</t>
+  </si>
+  <si>
+    <t>135285703</t>
+  </si>
+  <si>
+    <t>135285736</t>
+  </si>
+  <si>
+    <t>135285759</t>
+  </si>
+  <si>
+    <t>135285779</t>
+  </si>
+  <si>
+    <t>135285800</t>
+  </si>
+  <si>
+    <t>135286139</t>
+  </si>
+  <si>
+    <t>135286275</t>
+  </si>
+  <si>
+    <t>135286341</t>
+  </si>
+  <si>
+    <t>135286397</t>
+  </si>
+  <si>
+    <t>135286413</t>
+  </si>
+  <si>
+    <t>135286502</t>
+  </si>
+  <si>
+    <t>135286583</t>
+  </si>
+  <si>
+    <t>135287102</t>
+  </si>
+  <si>
+    <t>135287103</t>
+  </si>
+  <si>
+    <t>135287238</t>
+  </si>
+  <si>
+    <t>135287405</t>
+  </si>
+  <si>
+    <t>135287477</t>
+  </si>
+  <si>
+    <t>135287760</t>
+  </si>
+  <si>
+    <t>135288240</t>
+  </si>
+  <si>
+    <t>135288368</t>
+  </si>
+  <si>
+    <t>135288515</t>
+  </si>
+  <si>
+    <t>135288564</t>
+  </si>
+  <si>
+    <t>135288902</t>
+  </si>
+  <si>
+    <t>135288975</t>
+  </si>
+  <si>
+    <t>135289295</t>
+  </si>
+  <si>
+    <t>135289303</t>
+  </si>
+  <si>
+    <t>135289363</t>
+  </si>
+  <si>
+    <t>135289387</t>
+  </si>
+  <si>
+    <t>135289833</t>
+  </si>
+  <si>
+    <t>135289851</t>
+  </si>
+  <si>
+    <t>135289896</t>
+  </si>
+  <si>
+    <t>135289956</t>
+  </si>
+  <si>
+    <t>135290130</t>
+  </si>
+  <si>
+    <t>135290167</t>
+  </si>
+  <si>
+    <t>135290285</t>
+  </si>
+  <si>
+    <t>135290401</t>
+  </si>
+  <si>
+    <t>135290466</t>
+  </si>
+  <si>
+    <t>135290592</t>
+  </si>
+  <si>
+    <t>135290818</t>
+  </si>
+  <si>
+    <t>135290928</t>
+  </si>
+  <si>
+    <t>135290937</t>
+  </si>
+  <si>
+    <t>135290944</t>
+  </si>
+  <si>
+    <t>135290965</t>
+  </si>
+  <si>
+    <t>135290975</t>
+  </si>
+  <si>
+    <t>135291208</t>
+  </si>
+  <si>
+    <t>135291260</t>
+  </si>
+  <si>
+    <t>135291287</t>
+  </si>
+  <si>
+    <t>135291391</t>
+  </si>
+  <si>
+    <t>135291454</t>
+  </si>
+  <si>
+    <t>135291479</t>
+  </si>
+  <si>
+    <t>135291882</t>
+  </si>
+  <si>
+    <t>135291966</t>
+  </si>
+  <si>
+    <t>135291975</t>
+  </si>
+  <si>
+    <t>135292037</t>
+  </si>
+  <si>
+    <t>135292248</t>
+  </si>
+  <si>
+    <t>135292299</t>
+  </si>
+  <si>
+    <t>135292322</t>
+  </si>
+  <si>
+    <t>135292343</t>
+  </si>
+  <si>
+    <t>135292357</t>
+  </si>
+  <si>
+    <t>135292373</t>
+  </si>
+  <si>
+    <t>135292454</t>
+  </si>
+  <si>
+    <t>135292715</t>
+  </si>
+  <si>
+    <t>135292766</t>
+  </si>
+  <si>
+    <t>135292805</t>
+  </si>
+  <si>
+    <t>135293047</t>
+  </si>
+  <si>
+    <t>135293121</t>
+  </si>
+  <si>
+    <t>135293192</t>
+  </si>
+  <si>
+    <t>135293550</t>
+  </si>
+  <si>
+    <t>135293629</t>
+  </si>
+  <si>
+    <t>135293702</t>
+  </si>
+  <si>
+    <t>135293796</t>
+  </si>
+  <si>
+    <t>135293990</t>
+  </si>
+  <si>
+    <t>135294061</t>
+  </si>
+  <si>
+    <t>135294097</t>
+  </si>
+  <si>
+    <t>135294513</t>
+  </si>
+  <si>
+    <t>135294531</t>
+  </si>
+  <si>
+    <t>135294759</t>
+  </si>
+  <si>
+    <t>135294877</t>
+  </si>
+  <si>
+    <t>135294951</t>
+  </si>
+  <si>
+    <t>135294996</t>
+  </si>
+  <si>
+    <t>135295005</t>
+  </si>
+  <si>
+    <t>135295034</t>
+  </si>
+  <si>
+    <t>135295161</t>
+  </si>
+  <si>
+    <t>135295382</t>
+  </si>
+  <si>
+    <t>135295457</t>
+  </si>
+  <si>
+    <t>135295522</t>
+  </si>
+  <si>
+    <t>135295567</t>
+  </si>
+  <si>
+    <t>135295629</t>
+  </si>
+  <si>
+    <t>135295640</t>
+  </si>
+  <si>
+    <t>135295678</t>
+  </si>
+  <si>
+    <t>135295732</t>
+  </si>
+  <si>
+    <t>135295883</t>
+  </si>
+  <si>
+    <t>135295885</t>
+  </si>
+  <si>
+    <t>135295941</t>
+  </si>
+  <si>
+    <t>135296042</t>
+  </si>
+  <si>
+    <t>135296074</t>
+  </si>
+  <si>
+    <t>135296144</t>
+  </si>
+  <si>
+    <t>135296244</t>
+  </si>
+  <si>
+    <t>135296314</t>
+  </si>
+  <si>
+    <t>135296562</t>
+  </si>
+  <si>
+    <t>135296671</t>
+  </si>
+  <si>
+    <t>135296685</t>
+  </si>
+  <si>
+    <t>135296915</t>
+  </si>
+  <si>
+    <t>135296975</t>
+  </si>
+  <si>
+    <t>135297228</t>
+  </si>
+  <si>
+    <t>135297311</t>
+  </si>
+  <si>
+    <t>135297364</t>
+  </si>
+  <si>
+    <t>135297391</t>
+  </si>
+  <si>
+    <t>135297719</t>
+  </si>
+  <si>
+    <t>135297910</t>
+  </si>
+  <si>
+    <t>135298091</t>
+  </si>
+  <si>
+    <t>135298097</t>
+  </si>
+  <si>
+    <t>135298139</t>
+  </si>
+  <si>
+    <t>135298212</t>
+  </si>
+  <si>
+    <t>135298220</t>
+  </si>
+  <si>
+    <t>135298236</t>
+  </si>
+  <si>
+    <t>135298347</t>
+  </si>
+  <si>
+    <t>135298354</t>
+  </si>
+  <si>
+    <t>135298366</t>
+  </si>
+  <si>
+    <t>135298396</t>
+  </si>
+  <si>
+    <t>135298481</t>
+  </si>
+  <si>
+    <t>135298510</t>
+  </si>
+  <si>
+    <t>135298598</t>
+  </si>
+  <si>
+    <t>135298608</t>
+  </si>
+  <si>
+    <t>135298767</t>
+  </si>
+  <si>
+    <t>135298803</t>
+  </si>
+  <si>
+    <t>135298805</t>
+  </si>
+  <si>
+    <t>135298875</t>
+  </si>
+  <si>
+    <t>135298975</t>
+  </si>
+  <si>
+    <t>135299007</t>
+  </si>
+  <si>
+    <t>135299139</t>
+  </si>
+  <si>
+    <t>135299215</t>
+  </si>
+  <si>
+    <t>135299218</t>
+  </si>
+  <si>
+    <t>135299381</t>
+  </si>
+  <si>
+    <t>135299523</t>
+  </si>
+  <si>
+    <t>135299581</t>
+  </si>
+  <si>
+    <t>135299685</t>
+  </si>
+  <si>
+    <t>135299689</t>
+  </si>
+  <si>
+    <t>135299947</t>
+  </si>
+  <si>
+    <t>135299977</t>
+  </si>
+  <si>
+    <t>135300426</t>
+  </si>
+  <si>
+    <t>135300429</t>
+  </si>
+  <si>
+    <t>135300701</t>
+  </si>
+  <si>
+    <t>135300828</t>
+  </si>
+  <si>
+    <t>135300861</t>
+  </si>
+  <si>
+    <t>135301052</t>
+  </si>
+  <si>
+    <t>135301150</t>
+  </si>
+  <si>
+    <t>135301223</t>
+  </si>
+  <si>
+    <t>135301363</t>
+  </si>
+  <si>
+    <t>135301365</t>
+  </si>
+  <si>
+    <t>135301398</t>
+  </si>
+  <si>
+    <t>135301403</t>
+  </si>
+  <si>
+    <t>135301468</t>
+  </si>
+  <si>
+    <t>135301820</t>
+  </si>
+  <si>
+    <t>135301945</t>
+  </si>
+  <si>
+    <t>135302107</t>
+  </si>
+  <si>
+    <t>135302122</t>
+  </si>
+  <si>
+    <t>135302257</t>
+  </si>
+  <si>
+    <t>135302277</t>
+  </si>
+  <si>
+    <t>135302337</t>
+  </si>
+  <si>
+    <t>135302346</t>
+  </si>
+  <si>
+    <t>135302360</t>
+  </si>
+  <si>
+    <t>135302501</t>
+  </si>
+  <si>
+    <t>135302610</t>
+  </si>
+  <si>
+    <t>135302631</t>
+  </si>
+  <si>
+    <t>135302691</t>
+  </si>
+  <si>
+    <t>135302757</t>
+  </si>
+  <si>
+    <t>135302761</t>
+  </si>
+  <si>
+    <t>135302866</t>
+  </si>
+  <si>
+    <t>135302879</t>
+  </si>
+  <si>
+    <t>135303025</t>
+  </si>
+  <si>
+    <t>135303147</t>
+  </si>
+  <si>
+    <t>135303285</t>
+  </si>
+  <si>
+    <t>135303531</t>
+  </si>
+  <si>
+    <t>135303542</t>
+  </si>
+  <si>
+    <t>135303572</t>
+  </si>
+  <si>
+    <t>135303615</t>
+  </si>
+  <si>
+    <t>135303882</t>
+  </si>
+  <si>
+    <t>135303979</t>
+  </si>
+  <si>
+    <t>135304173</t>
+  </si>
+  <si>
+    <t>135304206</t>
+  </si>
+  <si>
+    <t>135304353</t>
+  </si>
+  <si>
+    <t>135304355</t>
+  </si>
+  <si>
+    <t>135304391</t>
+  </si>
+  <si>
+    <t>135304423</t>
+  </si>
+  <si>
+    <t>135304430</t>
+  </si>
+  <si>
+    <t>135304517</t>
+  </si>
+  <si>
+    <t>135304628</t>
+  </si>
+  <si>
+    <t>135304656</t>
+  </si>
+  <si>
+    <t>135304658</t>
+  </si>
+  <si>
+    <t>135304691</t>
+  </si>
+  <si>
+    <t>135304716</t>
+  </si>
+  <si>
+    <t>135304736</t>
+  </si>
+  <si>
+    <t>135304831</t>
+  </si>
+  <si>
+    <t>135304883</t>
+  </si>
+  <si>
+    <t>135304906</t>
+  </si>
+  <si>
+    <t>135305010</t>
+  </si>
+  <si>
+    <t>135305078</t>
+  </si>
+  <si>
+    <t>135305226</t>
+  </si>
+  <si>
+    <t>135305241</t>
+  </si>
+  <si>
+    <t>135305422</t>
+  </si>
+  <si>
+    <t>135305535</t>
+  </si>
+  <si>
+    <t>135305594</t>
+  </si>
+  <si>
+    <t>135305709</t>
+  </si>
+  <si>
+    <t>135305723</t>
+  </si>
+  <si>
+    <t>135305849</t>
+  </si>
+  <si>
+    <t>135305889</t>
+  </si>
+  <si>
+    <t>135305968</t>
+  </si>
+  <si>
+    <t>135305969</t>
+  </si>
+  <si>
+    <t>135305974</t>
+  </si>
+  <si>
+    <t>135306086</t>
+  </si>
+  <si>
+    <t>135306102</t>
+  </si>
+  <si>
+    <t>135306135</t>
+  </si>
+  <si>
+    <t>135306192</t>
+  </si>
+  <si>
+    <t>135306362</t>
+  </si>
+  <si>
+    <t>135306417</t>
+  </si>
+  <si>
+    <t>135306463</t>
+  </si>
+  <si>
+    <t>135306564</t>
+  </si>
+  <si>
+    <t>135306594</t>
+  </si>
+  <si>
+    <t>135306614</t>
+  </si>
+  <si>
+    <t>135306715</t>
+  </si>
+  <si>
+    <t>135306819</t>
+  </si>
+  <si>
+    <t>135306838</t>
+  </si>
+  <si>
+    <t>135306860</t>
+  </si>
+  <si>
+    <t>135306908</t>
+  </si>
+  <si>
+    <t>135306991</t>
+  </si>
+  <si>
+    <t>135306993</t>
+  </si>
+  <si>
+    <t>135307029</t>
+  </si>
+  <si>
+    <t>135307084</t>
+  </si>
+  <si>
+    <t>135307206</t>
+  </si>
+  <si>
+    <t>135307219</t>
+  </si>
+  <si>
+    <t>135307220</t>
+  </si>
+  <si>
+    <t>135307277</t>
+  </si>
+  <si>
+    <t>135307286</t>
+  </si>
+  <si>
+    <t>135307291</t>
+  </si>
+  <si>
+    <t>135307376</t>
+  </si>
+  <si>
+    <t>135307477</t>
+  </si>
+  <si>
+    <t>135307482</t>
+  </si>
+  <si>
+    <t>135307521</t>
+  </si>
+  <si>
+    <t>135307603</t>
+  </si>
+  <si>
+    <t>135307625</t>
+  </si>
+  <si>
+    <t>135307689</t>
+  </si>
+  <si>
+    <t>135307704</t>
+  </si>
+  <si>
+    <t>135307738</t>
+  </si>
+  <si>
+    <t>135307759</t>
+  </si>
+  <si>
+    <t>135307840</t>
+  </si>
+  <si>
+    <t>135307986</t>
+  </si>
+  <si>
+    <t>135308033</t>
+  </si>
+  <si>
+    <t>135308093</t>
+  </si>
+  <si>
+    <t>135308096</t>
+  </si>
+  <si>
+    <t>135308119</t>
+  </si>
+  <si>
+    <t>135308193</t>
+  </si>
+  <si>
+    <t>135308252</t>
+  </si>
+  <si>
+    <t>135308315</t>
+  </si>
+  <si>
+    <t>135308364</t>
+  </si>
+  <si>
+    <t>135308393</t>
+  </si>
+  <si>
+    <t>135308413</t>
+  </si>
+  <si>
+    <t>135308420</t>
+  </si>
+  <si>
+    <t>135308451</t>
+  </si>
+  <si>
+    <t>135308575</t>
+  </si>
+  <si>
+    <t>135308578</t>
+  </si>
+  <si>
+    <t>135308726</t>
+  </si>
+  <si>
+    <t>135308802</t>
+  </si>
+  <si>
+    <t>135308810</t>
+  </si>
+  <si>
+    <t>135308828</t>
+  </si>
+  <si>
+    <t>135308917</t>
+  </si>
+  <si>
+    <t>135308946</t>
+  </si>
+  <si>
+    <t>135308960</t>
+  </si>
+  <si>
+    <t>135309276</t>
+  </si>
+  <si>
+    <t>135309383</t>
+  </si>
+  <si>
+    <t>135309418</t>
+  </si>
+  <si>
+    <t>135309461</t>
+  </si>
+  <si>
+    <t>135309556</t>
+  </si>
+  <si>
+    <t>135309570</t>
+  </si>
+  <si>
+    <t>135309622</t>
+  </si>
+  <si>
+    <t>135309650</t>
+  </si>
+  <si>
+    <t>135309684</t>
+  </si>
+  <si>
+    <t>135309740</t>
+  </si>
+  <si>
+    <t>135309741</t>
+  </si>
+  <si>
+    <t>135309779</t>
+  </si>
+  <si>
+    <t>135309795</t>
+  </si>
+  <si>
+    <t>135309808</t>
+  </si>
+  <si>
+    <t>135310146</t>
+  </si>
+  <si>
+    <t>135310147</t>
+  </si>
+  <si>
+    <t>135310242</t>
+  </si>
+  <si>
+    <t>135310343</t>
+  </si>
+  <si>
+    <t>135310400</t>
+  </si>
+  <si>
+    <t>135310410</t>
+  </si>
+  <si>
+    <t>135310441</t>
+  </si>
+  <si>
+    <t>135310539</t>
+  </si>
+  <si>
+    <t>135310611</t>
+  </si>
+  <si>
+    <t>135310724</t>
+  </si>
+  <si>
+    <t>135310755</t>
+  </si>
+  <si>
+    <t>135310785</t>
+  </si>
+  <si>
+    <t>135310807</t>
+  </si>
+  <si>
+    <t>135310920</t>
+  </si>
+  <si>
+    <t>135310921</t>
+  </si>
+  <si>
+    <t>135311007</t>
+  </si>
+  <si>
+    <t>135311038</t>
+  </si>
+  <si>
+    <t>135311040</t>
+  </si>
+  <si>
+    <t>135311136</t>
+  </si>
+  <si>
+    <t>135311177</t>
+  </si>
+  <si>
+    <t>135311280</t>
+  </si>
+  <si>
+    <t>135311317</t>
+  </si>
+  <si>
+    <t>135311477</t>
+  </si>
+  <si>
+    <t>135311482</t>
+  </si>
+  <si>
+    <t>135311547</t>
+  </si>
+  <si>
+    <t>135312645</t>
+  </si>
+  <si>
+    <t>135312674</t>
+  </si>
+  <si>
+    <t>135312681</t>
+  </si>
+  <si>
+    <t>135312698</t>
+  </si>
+  <si>
+    <t>135312713</t>
+  </si>
+  <si>
+    <t>135312727</t>
+  </si>
+  <si>
+    <t>135312786</t>
+  </si>
+  <si>
+    <t>135312890</t>
+  </si>
+  <si>
+    <t>135312930</t>
+  </si>
+  <si>
+    <t>135312931</t>
   </si>
 </sst>
 </file>
@@ -819,7 +2415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C657"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2203,6 +3799,4262 @@
         <v>4</v>
       </c>
     </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B340" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B353" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B364" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B367" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B369" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B370" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B372" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B373" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B375" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B384" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B386" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B387" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B389" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B391" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B395" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B396" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B397" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B398" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B399" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B400" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B401" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B402" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B403" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B404" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B405" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B406" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B407" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B408" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B409" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B410" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B411" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B412" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B413" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B414" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B415" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B416" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B417" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B418" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B419" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B420" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B421" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B422" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B423" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B424" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B425" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B426" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B427" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B428" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B429" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B430" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B431" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B433" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B434" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B435" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B436" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B437" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B438" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B439" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B440" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B441" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B442" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B443" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B444" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B445" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B446" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B447" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B448" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A449" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B449" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A450" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B450" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A451" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B451" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A452" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B452" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A453" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B453" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A454" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B454" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B455" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A456" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B456" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A457" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B457" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A458" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B458" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A459" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B459" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A460" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B460" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A461" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B461" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A462" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B462" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A463" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B463" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A464" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B464" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A465" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B465" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A466" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B466" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A467" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B467" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A468" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B468" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A469" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B469" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A470" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B470" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A471" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B471" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A472" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B472" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A473" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B473" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A474" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B474" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A475" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B475" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A476" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B476" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A477" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B477" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A478" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B478" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A479" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B479" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A480" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B480" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A481" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B481" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A482" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B482" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A483" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B483" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A484" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B484" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A485" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B485" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A486" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B486" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A487" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B487" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A488" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B488" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A489" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B489" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A490" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B490" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A491" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B491" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A492" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B492" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A493" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B493" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A494" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B494" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A495" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B495" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A496" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B496" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A497" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B497" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A498" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B498" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A499" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B499" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A500" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B500" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A501" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B501" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A502" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B502" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A503" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B503" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A504" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B504" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A505" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B505" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A506" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B506" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A507" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B507" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A508" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B508" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A509" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B509" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A510" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B510" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A511" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B511" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A512" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B512" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A513" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B513" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A514" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B514" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A515" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B515" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A516" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B516" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A517" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B517" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A518" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B518" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A519" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B519" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A520" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B520" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A521" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B521" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A522" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B522" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A523" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B523" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A524" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B524" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A525" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B525" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A526" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B526" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A527" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B527" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A528" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B528" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A529" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B529" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A530" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B530" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A531" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B531" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A532" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B532" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A533" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B533" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A534" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B534" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A535" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B535" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A536" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B536" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A537" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B537" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A538" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B538" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A539" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B539" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A540" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B540" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A541" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B541" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A542" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B542" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A543" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B543" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A544" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B544" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A545" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B545" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A546" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B546" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A547" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B547" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A548" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B548" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A549" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B549" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A550" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B550" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A551" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B551" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A552" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B552" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A553" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B553" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A554" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B554" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A555" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B555" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A556" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B556" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A557" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B557" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A558" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B558" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A559" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B559" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A560" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B560" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A561" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B561" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A562" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B562" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A563" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B563" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A564" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B564" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A565" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B565" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A566" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B566" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A567" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B567" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A568" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B568" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A569" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B569" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A570" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B570" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A571" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B571" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A572" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B572" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A573" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B573" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A574" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B574" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A575" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B575" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A576" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B576" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A577" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B577" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A578" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B578" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A579" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B579" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A580" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B580" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A581" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B581" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A582" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B582" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A583" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B583" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A584" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B584" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A585" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B585" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A586" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B586" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A587" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B587" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A588" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B588" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A589" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B589" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A590" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B590" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A591" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B591" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A592" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B592" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A593" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B593" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A594" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B594" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A595" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B595" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A596" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B596" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A597" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B597" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A598" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B598" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A599" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B599" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A600" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B600" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A601" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B601" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A602" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B602" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A603" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B603" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A604" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B604" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A605" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B605" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A606" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B606" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A607" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B607" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A608" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B608" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A609" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B609" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A610" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="B610" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A611" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B611" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A612" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B612" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A613" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B613" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A614" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B614" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A615" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B615" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A616" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B616" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A617" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B617" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A618" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B618" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A619" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B619" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A620" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B620" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A621" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B621" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A622" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B622" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A623" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B623" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A624" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B624" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A625" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B625" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A626" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B626" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A627" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B627" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A628" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B628" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A629" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B629" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A630" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B630" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A631" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B631" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A632" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B632" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A633" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B633" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A634" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B634" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A635" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B635" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A636" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B636" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A637" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B637" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A638" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B638" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A639" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B639" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A640" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B640" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A641" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B641" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A642" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B642" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A643" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B643" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A644" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B644" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A645" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B645" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A646" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B646" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A647" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B647" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A648" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B648" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A649" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B649" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A650" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B650" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A651" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B651" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A652" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B652" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A653" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B653" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A654" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B654" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A655" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B655" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A656" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B656" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A657" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B657" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C125" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{311741D5-0D8E-48D2-9702-1D619426A37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2822410-20BC-47A4-ABF3-6ECEBAED5005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="517">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,55 +45,1540 @@
     <t>.</t>
   </si>
   <si>
-    <t>130851079</t>
-  </si>
-  <si>
-    <t>135312986</t>
-  </si>
-  <si>
-    <t>135312999</t>
-  </si>
-  <si>
-    <t>135313027</t>
-  </si>
-  <si>
-    <t>135313061</t>
-  </si>
-  <si>
-    <t>135313180</t>
-  </si>
-  <si>
-    <t>135313279</t>
-  </si>
-  <si>
-    <t>135313354</t>
-  </si>
-  <si>
-    <t>135313414</t>
-  </si>
-  <si>
-    <t>135313630</t>
-  </si>
-  <si>
-    <t>135313687</t>
-  </si>
-  <si>
-    <t>135313788</t>
-  </si>
-  <si>
-    <t>135314269</t>
-  </si>
-  <si>
-    <t>135314526</t>
-  </si>
-  <si>
-    <t>135314532</t>
-  </si>
-  <si>
-    <t>135314551</t>
-  </si>
-  <si>
-    <t>135314564</t>
+    <t>130391165</t>
+  </si>
+  <si>
+    <t>130410342</t>
+  </si>
+  <si>
+    <t>130428941</t>
+  </si>
+  <si>
+    <t>130440223</t>
+  </si>
+  <si>
+    <t>130625724</t>
+  </si>
+  <si>
+    <t>130779095</t>
+  </si>
+  <si>
+    <t>130790983</t>
+  </si>
+  <si>
+    <t>131006390</t>
+  </si>
+  <si>
+    <t>131098359</t>
+  </si>
+  <si>
+    <t>131160754</t>
+  </si>
+  <si>
+    <t>131229931</t>
+  </si>
+  <si>
+    <t>131278259</t>
+  </si>
+  <si>
+    <t>131293711</t>
+  </si>
+  <si>
+    <t>131322144</t>
+  </si>
+  <si>
+    <t>131498878</t>
+  </si>
+  <si>
+    <t>131515053</t>
+  </si>
+  <si>
+    <t>131612297</t>
+  </si>
+  <si>
+    <t>131663478</t>
+  </si>
+  <si>
+    <t>131819759</t>
+  </si>
+  <si>
+    <t>131824150</t>
+  </si>
+  <si>
+    <t>131829804</t>
+  </si>
+  <si>
+    <t>131843361</t>
+  </si>
+  <si>
+    <t>131873320</t>
+  </si>
+  <si>
+    <t>131937348</t>
+  </si>
+  <si>
+    <t>132004439</t>
+  </si>
+  <si>
+    <t>132100130</t>
+  </si>
+  <si>
+    <t>132102591</t>
+  </si>
+  <si>
+    <t>132158263</t>
+  </si>
+  <si>
+    <t>132466481</t>
+  </si>
+  <si>
+    <t>132585427</t>
+  </si>
+  <si>
+    <t>132602912</t>
+  </si>
+  <si>
+    <t>132645687</t>
+  </si>
+  <si>
+    <t>132661391</t>
+  </si>
+  <si>
+    <t>132777564</t>
+  </si>
+  <si>
+    <t>132798980</t>
+  </si>
+  <si>
+    <t>132800700</t>
+  </si>
+  <si>
+    <t>132801333</t>
+  </si>
+  <si>
+    <t>132851671</t>
+  </si>
+  <si>
+    <t>133145925</t>
+  </si>
+  <si>
+    <t>133194958</t>
+  </si>
+  <si>
+    <t>133214701</t>
+  </si>
+  <si>
+    <t>133330004</t>
+  </si>
+  <si>
+    <t>133331591</t>
+  </si>
+  <si>
+    <t>133344058</t>
+  </si>
+  <si>
+    <t>133390292</t>
+  </si>
+  <si>
+    <t>133458630</t>
+  </si>
+  <si>
+    <t>133632105</t>
+  </si>
+  <si>
+    <t>133762461</t>
+  </si>
+  <si>
+    <t>133763695</t>
+  </si>
+  <si>
+    <t>133809902</t>
+  </si>
+  <si>
+    <t>133818535</t>
+  </si>
+  <si>
+    <t>133880679</t>
+  </si>
+  <si>
+    <t>133948749</t>
+  </si>
+  <si>
+    <t>134097417</t>
+  </si>
+  <si>
+    <t>134259124</t>
+  </si>
+  <si>
+    <t>134383144</t>
+  </si>
+  <si>
+    <t>134427059</t>
+  </si>
+  <si>
+    <t>134696272</t>
+  </si>
+  <si>
+    <t>134754952</t>
+  </si>
+  <si>
+    <t>134859517</t>
+  </si>
+  <si>
+    <t>134890224</t>
+  </si>
+  <si>
+    <t>134971789</t>
+  </si>
+  <si>
+    <t>134974822</t>
+  </si>
+  <si>
+    <t>135019201</t>
+  </si>
+  <si>
+    <t>135106354</t>
+  </si>
+  <si>
+    <t>135314708</t>
+  </si>
+  <si>
+    <t>135314779</t>
+  </si>
+  <si>
+    <t>135314853</t>
+  </si>
+  <si>
+    <t>135314869</t>
+  </si>
+  <si>
+    <t>135315040</t>
+  </si>
+  <si>
+    <t>135315291</t>
+  </si>
+  <si>
+    <t>135315352</t>
+  </si>
+  <si>
+    <t>135315414</t>
+  </si>
+  <si>
+    <t>135315429</t>
+  </si>
+  <si>
+    <t>135315433</t>
+  </si>
+  <si>
+    <t>135315675</t>
+  </si>
+  <si>
+    <t>135316493</t>
+  </si>
+  <si>
+    <t>135316622</t>
+  </si>
+  <si>
+    <t>135316675</t>
+  </si>
+  <si>
+    <t>135316834</t>
+  </si>
+  <si>
+    <t>135317047</t>
+  </si>
+  <si>
+    <t>135317184</t>
+  </si>
+  <si>
+    <t>135317274</t>
+  </si>
+  <si>
+    <t>135317381</t>
+  </si>
+  <si>
+    <t>135317478</t>
+  </si>
+  <si>
+    <t>135317497</t>
+  </si>
+  <si>
+    <t>135317846</t>
+  </si>
+  <si>
+    <t>135317862</t>
+  </si>
+  <si>
+    <t>135318092</t>
+  </si>
+  <si>
+    <t>135318270</t>
+  </si>
+  <si>
+    <t>135318439</t>
+  </si>
+  <si>
+    <t>135318550</t>
+  </si>
+  <si>
+    <t>135318604</t>
+  </si>
+  <si>
+    <t>135318989</t>
+  </si>
+  <si>
+    <t>135319060</t>
+  </si>
+  <si>
+    <t>135319085</t>
+  </si>
+  <si>
+    <t>135319216</t>
+  </si>
+  <si>
+    <t>135319343</t>
+  </si>
+  <si>
+    <t>135319373</t>
+  </si>
+  <si>
+    <t>135319682</t>
+  </si>
+  <si>
+    <t>135319766</t>
+  </si>
+  <si>
+    <t>135319890</t>
+  </si>
+  <si>
+    <t>135319975</t>
+  </si>
+  <si>
+    <t>135320025</t>
+  </si>
+  <si>
+    <t>135320173</t>
+  </si>
+  <si>
+    <t>135320194</t>
+  </si>
+  <si>
+    <t>135320195</t>
+  </si>
+  <si>
+    <t>135320212</t>
+  </si>
+  <si>
+    <t>135320362</t>
+  </si>
+  <si>
+    <t>135320575</t>
+  </si>
+  <si>
+    <t>135320601</t>
+  </si>
+  <si>
+    <t>135320625</t>
+  </si>
+  <si>
+    <t>135320660</t>
+  </si>
+  <si>
+    <t>135320666</t>
+  </si>
+  <si>
+    <t>135320869</t>
+  </si>
+  <si>
+    <t>135320997</t>
+  </si>
+  <si>
+    <t>135321057</t>
+  </si>
+  <si>
+    <t>135321281</t>
+  </si>
+  <si>
+    <t>135321485</t>
+  </si>
+  <si>
+    <t>135321662</t>
+  </si>
+  <si>
+    <t>135321685</t>
+  </si>
+  <si>
+    <t>135321732</t>
+  </si>
+  <si>
+    <t>135321975</t>
+  </si>
+  <si>
+    <t>135321977</t>
+  </si>
+  <si>
+    <t>135321995</t>
+  </si>
+  <si>
+    <t>135322061</t>
+  </si>
+  <si>
+    <t>135322098</t>
+  </si>
+  <si>
+    <t>135322252</t>
+  </si>
+  <si>
+    <t>135322301</t>
+  </si>
+  <si>
+    <t>135322376</t>
+  </si>
+  <si>
+    <t>135322535</t>
+  </si>
+  <si>
+    <t>135322640</t>
+  </si>
+  <si>
+    <t>135322699</t>
+  </si>
+  <si>
+    <t>135322715</t>
+  </si>
+  <si>
+    <t>135322802</t>
+  </si>
+  <si>
+    <t>135322847</t>
+  </si>
+  <si>
+    <t>135322866</t>
+  </si>
+  <si>
+    <t>135323196</t>
+  </si>
+  <si>
+    <t>135323203</t>
+  </si>
+  <si>
+    <t>135323275</t>
+  </si>
+  <si>
+    <t>135323304</t>
+  </si>
+  <si>
+    <t>135323564</t>
+  </si>
+  <si>
+    <t>135323619</t>
+  </si>
+  <si>
+    <t>135323696</t>
+  </si>
+  <si>
+    <t>135324258</t>
+  </si>
+  <si>
+    <t>135324312</t>
+  </si>
+  <si>
+    <t>135324367</t>
+  </si>
+  <si>
+    <t>135324694</t>
+  </si>
+  <si>
+    <t>135325031</t>
+  </si>
+  <si>
+    <t>135325067</t>
+  </si>
+  <si>
+    <t>135325262</t>
+  </si>
+  <si>
+    <t>135325290</t>
+  </si>
+  <si>
+    <t>135325339</t>
+  </si>
+  <si>
+    <t>135325412</t>
+  </si>
+  <si>
+    <t>135325423</t>
+  </si>
+  <si>
+    <t>135325452</t>
+  </si>
+  <si>
+    <t>135325557</t>
+  </si>
+  <si>
+    <t>135325655</t>
+  </si>
+  <si>
+    <t>135325828</t>
+  </si>
+  <si>
+    <t>135325976</t>
+  </si>
+  <si>
+    <t>135326015</t>
+  </si>
+  <si>
+    <t>135326050</t>
+  </si>
+  <si>
+    <t>135326162</t>
+  </si>
+  <si>
+    <t>135326210</t>
+  </si>
+  <si>
+    <t>135326697</t>
+  </si>
+  <si>
+    <t>135326739</t>
+  </si>
+  <si>
+    <t>135327388</t>
+  </si>
+  <si>
+    <t>135327724</t>
+  </si>
+  <si>
+    <t>135327777</t>
+  </si>
+  <si>
+    <t>135328124</t>
+  </si>
+  <si>
+    <t>135328196</t>
+  </si>
+  <si>
+    <t>135328296</t>
+  </si>
+  <si>
+    <t>135328326</t>
+  </si>
+  <si>
+    <t>135328399</t>
+  </si>
+  <si>
+    <t>135328468</t>
+  </si>
+  <si>
+    <t>135328634</t>
+  </si>
+  <si>
+    <t>135328676</t>
+  </si>
+  <si>
+    <t>135328831</t>
+  </si>
+  <si>
+    <t>135329359</t>
+  </si>
+  <si>
+    <t>135329433</t>
+  </si>
+  <si>
+    <t>135329598</t>
+  </si>
+  <si>
+    <t>135329897</t>
+  </si>
+  <si>
+    <t>135329915</t>
+  </si>
+  <si>
+    <t>135330057</t>
+  </si>
+  <si>
+    <t>135330231</t>
+  </si>
+  <si>
+    <t>135330376</t>
+  </si>
+  <si>
+    <t>135330455</t>
+  </si>
+  <si>
+    <t>135330537</t>
+  </si>
+  <si>
+    <t>135330580</t>
+  </si>
+  <si>
+    <t>135330582</t>
+  </si>
+  <si>
+    <t>135330592</t>
+  </si>
+  <si>
+    <t>135330698</t>
+  </si>
+  <si>
+    <t>135330772</t>
+  </si>
+  <si>
+    <t>135330849</t>
+  </si>
+  <si>
+    <t>135330994</t>
+  </si>
+  <si>
+    <t>135331020</t>
+  </si>
+  <si>
+    <t>135331241</t>
+  </si>
+  <si>
+    <t>135331356</t>
+  </si>
+  <si>
+    <t>135331440</t>
+  </si>
+  <si>
+    <t>135331461</t>
+  </si>
+  <si>
+    <t>135331507</t>
+  </si>
+  <si>
+    <t>135331566</t>
+  </si>
+  <si>
+    <t>135331606</t>
+  </si>
+  <si>
+    <t>135332080</t>
+  </si>
+  <si>
+    <t>135332103</t>
+  </si>
+  <si>
+    <t>135332148</t>
+  </si>
+  <si>
+    <t>135332169</t>
+  </si>
+  <si>
+    <t>135332240</t>
+  </si>
+  <si>
+    <t>135332340</t>
+  </si>
+  <si>
+    <t>135332572</t>
+  </si>
+  <si>
+    <t>135332627</t>
+  </si>
+  <si>
+    <t>135332646</t>
+  </si>
+  <si>
+    <t>135332656</t>
+  </si>
+  <si>
+    <t>135332673</t>
+  </si>
+  <si>
+    <t>135332796</t>
+  </si>
+  <si>
+    <t>135332850</t>
+  </si>
+  <si>
+    <t>135332932</t>
+  </si>
+  <si>
+    <t>135332964</t>
+  </si>
+  <si>
+    <t>135333094</t>
+  </si>
+  <si>
+    <t>135333193</t>
+  </si>
+  <si>
+    <t>135333199</t>
+  </si>
+  <si>
+    <t>135333238</t>
+  </si>
+  <si>
+    <t>135333290</t>
+  </si>
+  <si>
+    <t>135333495</t>
+  </si>
+  <si>
+    <t>135334217</t>
+  </si>
+  <si>
+    <t>135334669</t>
+  </si>
+  <si>
+    <t>135335112</t>
+  </si>
+  <si>
+    <t>135335148</t>
+  </si>
+  <si>
+    <t>135335206</t>
+  </si>
+  <si>
+    <t>135335259</t>
+  </si>
+  <si>
+    <t>135335261</t>
+  </si>
+  <si>
+    <t>135335413</t>
+  </si>
+  <si>
+    <t>135355316</t>
+  </si>
+  <si>
+    <t>135355478</t>
+  </si>
+  <si>
+    <t>135355700</t>
+  </si>
+  <si>
+    <t>135355715</t>
+  </si>
+  <si>
+    <t>135355834</t>
+  </si>
+  <si>
+    <t>135355883</t>
+  </si>
+  <si>
+    <t>135355919</t>
+  </si>
+  <si>
+    <t>135356022</t>
+  </si>
+  <si>
+    <t>135356061</t>
+  </si>
+  <si>
+    <t>135356191</t>
+  </si>
+  <si>
+    <t>135356332</t>
+  </si>
+  <si>
+    <t>135356447</t>
+  </si>
+  <si>
+    <t>135356474</t>
+  </si>
+  <si>
+    <t>135356529</t>
+  </si>
+  <si>
+    <t>135356598</t>
+  </si>
+  <si>
+    <t>135356620</t>
+  </si>
+  <si>
+    <t>135356655</t>
+  </si>
+  <si>
+    <t>135356673</t>
+  </si>
+  <si>
+    <t>135356691</t>
+  </si>
+  <si>
+    <t>135356731</t>
+  </si>
+  <si>
+    <t>135356816</t>
+  </si>
+  <si>
+    <t>135356835</t>
+  </si>
+  <si>
+    <t>135356876</t>
+  </si>
+  <si>
+    <t>135357016</t>
+  </si>
+  <si>
+    <t>135357071</t>
+  </si>
+  <si>
+    <t>135357148</t>
+  </si>
+  <si>
+    <t>135357251</t>
+  </si>
+  <si>
+    <t>135357278</t>
+  </si>
+  <si>
+    <t>135357287</t>
+  </si>
+  <si>
+    <t>135357317</t>
+  </si>
+  <si>
+    <t>135357332</t>
+  </si>
+  <si>
+    <t>135357482</t>
+  </si>
+  <si>
+    <t>135357512</t>
+  </si>
+  <si>
+    <t>135357639</t>
+  </si>
+  <si>
+    <t>135357781</t>
+  </si>
+  <si>
+    <t>135357785</t>
+  </si>
+  <si>
+    <t>135357966</t>
+  </si>
+  <si>
+    <t>135358026</t>
+  </si>
+  <si>
+    <t>135358037</t>
+  </si>
+  <si>
+    <t>135358069</t>
+  </si>
+  <si>
+    <t>135358142</t>
+  </si>
+  <si>
+    <t>135358330</t>
+  </si>
+  <si>
+    <t>135358356</t>
+  </si>
+  <si>
+    <t>135358386</t>
+  </si>
+  <si>
+    <t>135358398</t>
+  </si>
+  <si>
+    <t>135358582</t>
+  </si>
+  <si>
+    <t>135358720</t>
+  </si>
+  <si>
+    <t>135358809</t>
+  </si>
+  <si>
+    <t>135358867</t>
+  </si>
+  <si>
+    <t>135358992</t>
+  </si>
+  <si>
+    <t>135359029</t>
+  </si>
+  <si>
+    <t>135359116</t>
+  </si>
+  <si>
+    <t>135359332</t>
+  </si>
+  <si>
+    <t>135359379</t>
+  </si>
+  <si>
+    <t>135359525</t>
+  </si>
+  <si>
+    <t>135359571</t>
+  </si>
+  <si>
+    <t>135359603</t>
+  </si>
+  <si>
+    <t>135359722</t>
+  </si>
+  <si>
+    <t>135359740</t>
+  </si>
+  <si>
+    <t>135359775</t>
+  </si>
+  <si>
+    <t>135360087</t>
+  </si>
+  <si>
+    <t>135360161</t>
+  </si>
+  <si>
+    <t>135360220</t>
+  </si>
+  <si>
+    <t>135360374</t>
+  </si>
+  <si>
+    <t>135360433</t>
+  </si>
+  <si>
+    <t>135360716</t>
+  </si>
+  <si>
+    <t>135360889</t>
+  </si>
+  <si>
+    <t>135360906</t>
+  </si>
+  <si>
+    <t>135361505</t>
+  </si>
+  <si>
+    <t>135361522</t>
+  </si>
+  <si>
+    <t>135361700</t>
+  </si>
+  <si>
+    <t>135361892</t>
+  </si>
+  <si>
+    <t>135361975</t>
+  </si>
+  <si>
+    <t>135362095</t>
+  </si>
+  <si>
+    <t>135362155</t>
+  </si>
+  <si>
+    <t>135362156</t>
+  </si>
+  <si>
+    <t>135362184</t>
+  </si>
+  <si>
+    <t>135362275</t>
+  </si>
+  <si>
+    <t>135362395</t>
+  </si>
+  <si>
+    <t>135362406</t>
+  </si>
+  <si>
+    <t>135362463</t>
+  </si>
+  <si>
+    <t>135362476</t>
+  </si>
+  <si>
+    <t>135362523</t>
+  </si>
+  <si>
+    <t>135362660</t>
+  </si>
+  <si>
+    <t>135362685</t>
+  </si>
+  <si>
+    <t>135362706</t>
+  </si>
+  <si>
+    <t>135362712</t>
+  </si>
+  <si>
+    <t>135362737</t>
+  </si>
+  <si>
+    <t>135362768</t>
+  </si>
+  <si>
+    <t>135362916</t>
+  </si>
+  <si>
+    <t>135362993</t>
+  </si>
+  <si>
+    <t>135363062</t>
+  </si>
+  <si>
+    <t>135363097</t>
+  </si>
+  <si>
+    <t>135363133</t>
+  </si>
+  <si>
+    <t>135363195</t>
+  </si>
+  <si>
+    <t>135363350</t>
+  </si>
+  <si>
+    <t>135363387</t>
+  </si>
+  <si>
+    <t>135363422</t>
+  </si>
+  <si>
+    <t>135363430</t>
+  </si>
+  <si>
+    <t>135363475</t>
+  </si>
+  <si>
+    <t>135363509</t>
+  </si>
+  <si>
+    <t>135363614</t>
+  </si>
+  <si>
+    <t>135363691</t>
+  </si>
+  <si>
+    <t>135363821</t>
+  </si>
+  <si>
+    <t>135363968</t>
+  </si>
+  <si>
+    <t>135364007</t>
+  </si>
+  <si>
+    <t>135364124</t>
+  </si>
+  <si>
+    <t>135364230</t>
+  </si>
+  <si>
+    <t>135364238</t>
+  </si>
+  <si>
+    <t>135364242</t>
+  </si>
+  <si>
+    <t>135364294</t>
+  </si>
+  <si>
+    <t>135364297</t>
+  </si>
+  <si>
+    <t>135364485</t>
+  </si>
+  <si>
+    <t>135364548</t>
+  </si>
+  <si>
+    <t>135364555</t>
+  </si>
+  <si>
+    <t>135364556</t>
+  </si>
+  <si>
+    <t>135364590</t>
+  </si>
+  <si>
+    <t>135364644</t>
+  </si>
+  <si>
+    <t>135364699</t>
+  </si>
+  <si>
+    <t>135364751</t>
+  </si>
+  <si>
+    <t>135364821</t>
+  </si>
+  <si>
+    <t>135364840</t>
+  </si>
+  <si>
+    <t>135364846</t>
+  </si>
+  <si>
+    <t>135364901</t>
+  </si>
+  <si>
+    <t>135365027</t>
+  </si>
+  <si>
+    <t>135365031</t>
+  </si>
+  <si>
+    <t>135365063</t>
+  </si>
+  <si>
+    <t>135365129</t>
+  </si>
+  <si>
+    <t>135365287</t>
+  </si>
+  <si>
+    <t>135365508</t>
+  </si>
+  <si>
+    <t>135365588</t>
+  </si>
+  <si>
+    <t>135365647</t>
+  </si>
+  <si>
+    <t>135365721</t>
+  </si>
+  <si>
+    <t>135365783</t>
+  </si>
+  <si>
+    <t>135365868</t>
+  </si>
+  <si>
+    <t>135365901</t>
+  </si>
+  <si>
+    <t>135365970</t>
+  </si>
+  <si>
+    <t>135366010</t>
+  </si>
+  <si>
+    <t>135366120</t>
+  </si>
+  <si>
+    <t>135366173</t>
+  </si>
+  <si>
+    <t>135366269</t>
+  </si>
+  <si>
+    <t>135366282</t>
+  </si>
+  <si>
+    <t>135366582</t>
+  </si>
+  <si>
+    <t>135366786</t>
+  </si>
+  <si>
+    <t>135366818</t>
+  </si>
+  <si>
+    <t>135366850</t>
+  </si>
+  <si>
+    <t>135366881</t>
+  </si>
+  <si>
+    <t>135366897</t>
+  </si>
+  <si>
+    <t>135366979</t>
+  </si>
+  <si>
+    <t>135367134</t>
+  </si>
+  <si>
+    <t>135367212</t>
+  </si>
+  <si>
+    <t>135367235</t>
+  </si>
+  <si>
+    <t>135367340</t>
+  </si>
+  <si>
+    <t>135367553</t>
+  </si>
+  <si>
+    <t>135367588</t>
+  </si>
+  <si>
+    <t>135367636</t>
+  </si>
+  <si>
+    <t>135367638</t>
+  </si>
+  <si>
+    <t>135367652</t>
+  </si>
+  <si>
+    <t>135367691</t>
+  </si>
+  <si>
+    <t>135367822</t>
+  </si>
+  <si>
+    <t>135367845</t>
+  </si>
+  <si>
+    <t>135367872</t>
+  </si>
+  <si>
+    <t>135368285</t>
+  </si>
+  <si>
+    <t>135368384</t>
+  </si>
+  <si>
+    <t>135368410</t>
+  </si>
+  <si>
+    <t>135368443</t>
+  </si>
+  <si>
+    <t>135368478</t>
+  </si>
+  <si>
+    <t>135368522</t>
+  </si>
+  <si>
+    <t>135368544</t>
+  </si>
+  <si>
+    <t>135368577</t>
+  </si>
+  <si>
+    <t>135368606</t>
+  </si>
+  <si>
+    <t>135368619</t>
+  </si>
+  <si>
+    <t>135368677</t>
+  </si>
+  <si>
+    <t>135368971</t>
+  </si>
+  <si>
+    <t>135368973</t>
+  </si>
+  <si>
+    <t>135369021</t>
+  </si>
+  <si>
+    <t>135369093</t>
+  </si>
+  <si>
+    <t>135369102</t>
+  </si>
+  <si>
+    <t>135369117</t>
+  </si>
+  <si>
+    <t>135369126</t>
+  </si>
+  <si>
+    <t>135369221</t>
+  </si>
+  <si>
+    <t>135369334</t>
+  </si>
+  <si>
+    <t>135369393</t>
+  </si>
+  <si>
+    <t>135369464</t>
+  </si>
+  <si>
+    <t>135369504</t>
+  </si>
+  <si>
+    <t>135369683</t>
+  </si>
+  <si>
+    <t>135369727</t>
+  </si>
+  <si>
+    <t>135369754</t>
+  </si>
+  <si>
+    <t>135369776</t>
+  </si>
+  <si>
+    <t>135369783</t>
+  </si>
+  <si>
+    <t>135369841</t>
+  </si>
+  <si>
+    <t>135370093</t>
+  </si>
+  <si>
+    <t>135370108</t>
+  </si>
+  <si>
+    <t>135370186</t>
+  </si>
+  <si>
+    <t>135370235</t>
+  </si>
+  <si>
+    <t>135370261</t>
+  </si>
+  <si>
+    <t>135370330</t>
+  </si>
+  <si>
+    <t>135370346</t>
+  </si>
+  <si>
+    <t>135370364</t>
+  </si>
+  <si>
+    <t>135370370</t>
+  </si>
+  <si>
+    <t>135370531</t>
+  </si>
+  <si>
+    <t>135370534</t>
+  </si>
+  <si>
+    <t>135370788</t>
+  </si>
+  <si>
+    <t>135370854</t>
+  </si>
+  <si>
+    <t>135370890</t>
+  </si>
+  <si>
+    <t>135370898</t>
+  </si>
+  <si>
+    <t>135370932</t>
+  </si>
+  <si>
+    <t>135370944</t>
+  </si>
+  <si>
+    <t>135371037</t>
+  </si>
+  <si>
+    <t>135371067</t>
+  </si>
+  <si>
+    <t>135371115</t>
+  </si>
+  <si>
+    <t>135371130</t>
+  </si>
+  <si>
+    <t>135371325</t>
+  </si>
+  <si>
+    <t>135371344</t>
+  </si>
+  <si>
+    <t>135371353</t>
+  </si>
+  <si>
+    <t>135371407</t>
+  </si>
+  <si>
+    <t>135371427</t>
+  </si>
+  <si>
+    <t>135371443</t>
+  </si>
+  <si>
+    <t>135371498</t>
+  </si>
+  <si>
+    <t>135371512</t>
+  </si>
+  <si>
+    <t>135371600</t>
+  </si>
+  <si>
+    <t>135371689</t>
+  </si>
+  <si>
+    <t>135371702</t>
+  </si>
+  <si>
+    <t>135371757</t>
+  </si>
+  <si>
+    <t>135371767</t>
+  </si>
+  <si>
+    <t>135371819</t>
+  </si>
+  <si>
+    <t>135371899</t>
+  </si>
+  <si>
+    <t>135371918</t>
+  </si>
+  <si>
+    <t>135371949</t>
+  </si>
+  <si>
+    <t>135372028</t>
+  </si>
+  <si>
+    <t>135372033</t>
+  </si>
+  <si>
+    <t>135372077</t>
+  </si>
+  <si>
+    <t>135372104</t>
+  </si>
+  <si>
+    <t>135372126</t>
+  </si>
+  <si>
+    <t>135372175</t>
+  </si>
+  <si>
+    <t>135372354</t>
+  </si>
+  <si>
+    <t>135372382</t>
+  </si>
+  <si>
+    <t>135372414</t>
+  </si>
+  <si>
+    <t>135372482</t>
+  </si>
+  <si>
+    <t>135372519</t>
+  </si>
+  <si>
+    <t>135372610</t>
+  </si>
+  <si>
+    <t>135372662</t>
+  </si>
+  <si>
+    <t>135372762</t>
+  </si>
+  <si>
+    <t>135372882</t>
+  </si>
+  <si>
+    <t>135373320</t>
+  </si>
+  <si>
+    <t>135373330</t>
+  </si>
+  <si>
+    <t>135373954</t>
+  </si>
+  <si>
+    <t>135374001</t>
+  </si>
+  <si>
+    <t>135374006</t>
+  </si>
+  <si>
+    <t>135374065</t>
+  </si>
+  <si>
+    <t>135374141</t>
+  </si>
+  <si>
+    <t>135374177</t>
+  </si>
+  <si>
+    <t>135374182</t>
+  </si>
+  <si>
+    <t>135374213</t>
+  </si>
+  <si>
+    <t>135374227</t>
+  </si>
+  <si>
+    <t>135374243</t>
+  </si>
+  <si>
+    <t>135374263</t>
+  </si>
+  <si>
+    <t>135374353</t>
+  </si>
+  <si>
+    <t>135363028</t>
+  </si>
+  <si>
+    <t>135358439</t>
+  </si>
+  <si>
+    <t>135285736</t>
+  </si>
+  <si>
+    <t>135320339</t>
+  </si>
+  <si>
+    <t>135278872</t>
+  </si>
+  <si>
+    <t>135277881</t>
+  </si>
+  <si>
+    <t>135281237</t>
+  </si>
+  <si>
+    <t>135299007</t>
+  </si>
+  <si>
+    <t>135322302</t>
+  </si>
+  <si>
+    <t>130631228</t>
+  </si>
+  <si>
+    <t>134611900</t>
+  </si>
+  <si>
+    <t>135285981</t>
+  </si>
+  <si>
+    <t>135269910</t>
+  </si>
+  <si>
+    <t>135282921</t>
+  </si>
+  <si>
+    <t>135314198</t>
+  </si>
+  <si>
+    <t>135234427</t>
+  </si>
+  <si>
+    <t>135299416</t>
+  </si>
+  <si>
+    <t>135260222</t>
+  </si>
+  <si>
+    <t>135266824</t>
+  </si>
+  <si>
+    <t>134140104</t>
+  </si>
+  <si>
+    <t>135251034</t>
+  </si>
+  <si>
+    <t>135227591</t>
   </si>
 </sst>
 </file>
@@ -498,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C513"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -705,6 +2190,3966 @@
         <v>4</v>
       </c>
     </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A330" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A331" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A333" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B340" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B353" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B364" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B367" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B369" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B370" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B372" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B373" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B375" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B384" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B386" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B387" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B389" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B391" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B395" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B396" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B397" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B398" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B399" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B400" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B401" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B402" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B403" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B404" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B405" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B406" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B407" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B408" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B409" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B410" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B411" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B412" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B413" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B414" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B415" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B416" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A417" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B417" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A418" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B418" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A419" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B419" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A420" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B420" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A421" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B421" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A422" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B422" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A423" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B423" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A424" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B424" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A425" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B425" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A426" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B426" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A427" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B427" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A428" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B428" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A429" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B429" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A430" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B430" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A431" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B431" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A432" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B433" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B434" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B435" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B436" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B437" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B438" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B439" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B440" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B441" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B442" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B443" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B444" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B445" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B446" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B447" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B448" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A449" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B449" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A450" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B450" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A451" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B451" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A452" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B452" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A453" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B453" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A454" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B454" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B455" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A456" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B456" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A457" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B457" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A458" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B458" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A459" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B459" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A460" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B460" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A461" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B461" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A462" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B462" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A463" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B463" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A464" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B464" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A465" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B465" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A466" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B466" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A467" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B467" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A468" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B468" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A469" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B469" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A470" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B470" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A471" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B471" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A472" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B472" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A473" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B473" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A474" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B474" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A475" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B475" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A476" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B476" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A477" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B477" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A478" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B478" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A479" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B479" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A480" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B480" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A481" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B481" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A482" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B482" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A483" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B483" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A484" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B484" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A485" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B485" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A486" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B486" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A487" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B487" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A488" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B488" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A489" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B489" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A490" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B490" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A491" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B491" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A492" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B492" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A493" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B493" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A494" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B494" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A495" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B495" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A496" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B496" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A497" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B497" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A498" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B498" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A499" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B499" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A500" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B500" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A501" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B501" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A502" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B502" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A503" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B503" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A504" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B504" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A505" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B505" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A506" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B506" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A507" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B507" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A508" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B508" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A509" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B509" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A510" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B510" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A511" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B511" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A512" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B512" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A513" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B513" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C18" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6AC8F3-192E-41F3-8936-92A8F7BBE25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6D9BF4-8B44-4C7A-98B6-CBF92E87966C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="326">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,742 +45,967 @@
     <t>.</t>
   </si>
   <si>
-    <t>130568980</t>
-  </si>
-  <si>
-    <t>130879570</t>
-  </si>
-  <si>
-    <t>131043007</t>
-  </si>
-  <si>
-    <t>131353146</t>
-  </si>
-  <si>
-    <t>131440934</t>
-  </si>
-  <si>
-    <t>131597612</t>
-  </si>
-  <si>
-    <t>131771917</t>
-  </si>
-  <si>
-    <t>131810526</t>
-  </si>
-  <si>
-    <t>131827880</t>
-  </si>
-  <si>
-    <t>131966018</t>
-  </si>
-  <si>
-    <t>132037256</t>
-  </si>
-  <si>
-    <t>132044097</t>
-  </si>
-  <si>
-    <t>132062464</t>
-  </si>
-  <si>
-    <t>132515526</t>
-  </si>
-  <si>
-    <t>132635933</t>
-  </si>
-  <si>
-    <t>133141227</t>
-  </si>
-  <si>
-    <t>133391139</t>
-  </si>
-  <si>
-    <t>133710191</t>
-  </si>
-  <si>
-    <t>133919978</t>
-  </si>
-  <si>
-    <t>134108411</t>
-  </si>
-  <si>
-    <t>134238807</t>
-  </si>
-  <si>
-    <t>134298199</t>
-  </si>
-  <si>
-    <t>134620804</t>
-  </si>
-  <si>
-    <t>134649807</t>
-  </si>
-  <si>
-    <t>134744092</t>
-  </si>
-  <si>
-    <t>134757905</t>
-  </si>
-  <si>
-    <t>134874962</t>
-  </si>
-  <si>
-    <t>134998732</t>
-  </si>
-  <si>
-    <t>135374555</t>
-  </si>
-  <si>
-    <t>135374564</t>
-  </si>
-  <si>
-    <t>135374694</t>
-  </si>
-  <si>
-    <t>135374731</t>
-  </si>
-  <si>
-    <t>135374824</t>
-  </si>
-  <si>
-    <t>135375216</t>
-  </si>
-  <si>
-    <t>135375318</t>
-  </si>
-  <si>
-    <t>135375415</t>
-  </si>
-  <si>
-    <t>135375463</t>
-  </si>
-  <si>
-    <t>135375492</t>
-  </si>
-  <si>
-    <t>135375529</t>
-  </si>
-  <si>
-    <t>135375662</t>
-  </si>
-  <si>
-    <t>135375874</t>
-  </si>
-  <si>
-    <t>135376104</t>
-  </si>
-  <si>
-    <t>135376141</t>
-  </si>
-  <si>
-    <t>135376149</t>
-  </si>
-  <si>
-    <t>135376291</t>
-  </si>
-  <si>
-    <t>135376428</t>
-  </si>
-  <si>
-    <t>135376503</t>
-  </si>
-  <si>
-    <t>135376513</t>
-  </si>
-  <si>
-    <t>135376589</t>
-  </si>
-  <si>
-    <t>135376608</t>
-  </si>
-  <si>
-    <t>135376802</t>
-  </si>
-  <si>
-    <t>135376811</t>
-  </si>
-  <si>
-    <t>135377144</t>
-  </si>
-  <si>
-    <t>135377225</t>
-  </si>
-  <si>
-    <t>135377233</t>
-  </si>
-  <si>
-    <t>135377277</t>
-  </si>
-  <si>
-    <t>135377335</t>
-  </si>
-  <si>
-    <t>135377380</t>
-  </si>
-  <si>
-    <t>135377454</t>
-  </si>
-  <si>
-    <t>135377495</t>
-  </si>
-  <si>
-    <t>135377531</t>
-  </si>
-  <si>
-    <t>135377581</t>
-  </si>
-  <si>
-    <t>135377768</t>
-  </si>
-  <si>
-    <t>135377965</t>
-  </si>
-  <si>
-    <t>135377986</t>
-  </si>
-  <si>
-    <t>135378219</t>
-  </si>
-  <si>
-    <t>135378268</t>
-  </si>
-  <si>
-    <t>135378625</t>
-  </si>
-  <si>
-    <t>135378691</t>
-  </si>
-  <si>
-    <t>135378696</t>
-  </si>
-  <si>
-    <t>135378762</t>
-  </si>
-  <si>
-    <t>135379032</t>
-  </si>
-  <si>
-    <t>135379056</t>
-  </si>
-  <si>
-    <t>135379654</t>
-  </si>
-  <si>
-    <t>135379683</t>
-  </si>
-  <si>
-    <t>135379741</t>
-  </si>
-  <si>
-    <t>135379845</t>
-  </si>
-  <si>
-    <t>135379860</t>
-  </si>
-  <si>
-    <t>135379982</t>
-  </si>
-  <si>
-    <t>135380001</t>
-  </si>
-  <si>
-    <t>135380036</t>
-  </si>
-  <si>
-    <t>135380173</t>
-  </si>
-  <si>
-    <t>135380250</t>
-  </si>
-  <si>
-    <t>135380452</t>
-  </si>
-  <si>
-    <t>135380629</t>
-  </si>
-  <si>
-    <t>135380667</t>
-  </si>
-  <si>
-    <t>135380670</t>
-  </si>
-  <si>
-    <t>135380711</t>
-  </si>
-  <si>
-    <t>135380760</t>
-  </si>
-  <si>
-    <t>135380811</t>
-  </si>
-  <si>
-    <t>135380882</t>
-  </si>
-  <si>
-    <t>135380949</t>
-  </si>
-  <si>
-    <t>135380975</t>
-  </si>
-  <si>
-    <t>135380985</t>
-  </si>
-  <si>
-    <t>135381081</t>
-  </si>
-  <si>
-    <t>135381095</t>
-  </si>
-  <si>
-    <t>135381133</t>
-  </si>
-  <si>
-    <t>135381168</t>
-  </si>
-  <si>
-    <t>135381190</t>
-  </si>
-  <si>
-    <t>135381278</t>
-  </si>
-  <si>
-    <t>135381341</t>
-  </si>
-  <si>
-    <t>135381393</t>
-  </si>
-  <si>
-    <t>135381479</t>
-  </si>
-  <si>
-    <t>135381504</t>
-  </si>
-  <si>
-    <t>135381724</t>
-  </si>
-  <si>
-    <t>135381733</t>
-  </si>
-  <si>
-    <t>135381734</t>
-  </si>
-  <si>
-    <t>135381842</t>
-  </si>
-  <si>
-    <t>135381901</t>
-  </si>
-  <si>
-    <t>135382212</t>
-  </si>
-  <si>
-    <t>135382306</t>
-  </si>
-  <si>
-    <t>135382310</t>
-  </si>
-  <si>
-    <t>135382346</t>
-  </si>
-  <si>
-    <t>135382496</t>
-  </si>
-  <si>
-    <t>135382646</t>
-  </si>
-  <si>
-    <t>135382932</t>
-  </si>
-  <si>
-    <t>135383281</t>
-  </si>
-  <si>
-    <t>135383295</t>
-  </si>
-  <si>
-    <t>135383311</t>
-  </si>
-  <si>
-    <t>135383436</t>
-  </si>
-  <si>
-    <t>135383444</t>
-  </si>
-  <si>
-    <t>135383607</t>
-  </si>
-  <si>
-    <t>135383876</t>
-  </si>
-  <si>
-    <t>135384260</t>
-  </si>
-  <si>
-    <t>135384359</t>
-  </si>
-  <si>
-    <t>135384443</t>
-  </si>
-  <si>
-    <t>135384665</t>
-  </si>
-  <si>
-    <t>135384685</t>
-  </si>
-  <si>
-    <t>135384697</t>
-  </si>
-  <si>
-    <t>135384854</t>
-  </si>
-  <si>
-    <t>135384960</t>
-  </si>
-  <si>
-    <t>135384983</t>
-  </si>
-  <si>
-    <t>135385006</t>
-  </si>
-  <si>
-    <t>135385092</t>
-  </si>
-  <si>
-    <t>135385098</t>
-  </si>
-  <si>
-    <t>135385153</t>
-  </si>
-  <si>
-    <t>135385154</t>
-  </si>
-  <si>
-    <t>135385265</t>
-  </si>
-  <si>
-    <t>135385323</t>
-  </si>
-  <si>
-    <t>135385425</t>
-  </si>
-  <si>
-    <t>135385602</t>
-  </si>
-  <si>
-    <t>135385731</t>
-  </si>
-  <si>
-    <t>135385770</t>
-  </si>
-  <si>
-    <t>135385787</t>
-  </si>
-  <si>
-    <t>135385863</t>
-  </si>
-  <si>
-    <t>135385883</t>
-  </si>
-  <si>
-    <t>135386002</t>
-  </si>
-  <si>
-    <t>135386020</t>
-  </si>
-  <si>
-    <t>135386045</t>
-  </si>
-  <si>
-    <t>135386406</t>
-  </si>
-  <si>
-    <t>135386611</t>
-  </si>
-  <si>
-    <t>135386691</t>
-  </si>
-  <si>
-    <t>135386719</t>
-  </si>
-  <si>
-    <t>135386873</t>
-  </si>
-  <si>
-    <t>135386934</t>
-  </si>
-  <si>
-    <t>135386965</t>
-  </si>
-  <si>
-    <t>135386998</t>
-  </si>
-  <si>
-    <t>135387019</t>
-  </si>
-  <si>
-    <t>135387044</t>
-  </si>
-  <si>
-    <t>135387083</t>
-  </si>
-  <si>
-    <t>135387084</t>
-  </si>
-  <si>
-    <t>135387161</t>
-  </si>
-  <si>
-    <t>135387204</t>
-  </si>
-  <si>
-    <t>135387242</t>
-  </si>
-  <si>
-    <t>135387300</t>
-  </si>
-  <si>
-    <t>135387335</t>
-  </si>
-  <si>
-    <t>135387437</t>
-  </si>
-  <si>
-    <t>135387453</t>
-  </si>
-  <si>
-    <t>135387528</t>
-  </si>
-  <si>
-    <t>135387590</t>
-  </si>
-  <si>
-    <t>135387606</t>
-  </si>
-  <si>
-    <t>135387796</t>
-  </si>
-  <si>
-    <t>135387814</t>
-  </si>
-  <si>
-    <t>135387952</t>
-  </si>
-  <si>
-    <t>135388023</t>
-  </si>
-  <si>
-    <t>135388034</t>
-  </si>
-  <si>
-    <t>135388054</t>
-  </si>
-  <si>
-    <t>135388110</t>
-  </si>
-  <si>
-    <t>135388118</t>
-  </si>
-  <si>
-    <t>135388129</t>
-  </si>
-  <si>
-    <t>135388152</t>
-  </si>
-  <si>
-    <t>135388178</t>
-  </si>
-  <si>
-    <t>135388406</t>
-  </si>
-  <si>
-    <t>135388426</t>
-  </si>
-  <si>
-    <t>135388457</t>
-  </si>
-  <si>
-    <t>135388488</t>
-  </si>
-  <si>
-    <t>135388708</t>
-  </si>
-  <si>
-    <t>135388850</t>
-  </si>
-  <si>
-    <t>135388901</t>
-  </si>
-  <si>
-    <t>135388911</t>
-  </si>
-  <si>
-    <t>135388965</t>
-  </si>
-  <si>
-    <t>135389009</t>
-  </si>
-  <si>
-    <t>135389034</t>
-  </si>
-  <si>
-    <t>135389148</t>
-  </si>
-  <si>
-    <t>135389151</t>
-  </si>
-  <si>
-    <t>135389341</t>
-  </si>
-  <si>
-    <t>135389548</t>
-  </si>
-  <si>
-    <t>135389639</t>
-  </si>
-  <si>
-    <t>135389655</t>
-  </si>
-  <si>
-    <t>135389714</t>
-  </si>
-  <si>
-    <t>135389723</t>
-  </si>
-  <si>
-    <t>135389789</t>
-  </si>
-  <si>
-    <t>135389939</t>
-  </si>
-  <si>
-    <t>135390013</t>
-  </si>
-  <si>
-    <t>135390054</t>
-  </si>
-  <si>
-    <t>135390106</t>
-  </si>
-  <si>
-    <t>135390123</t>
-  </si>
-  <si>
-    <t>135390232</t>
-  </si>
-  <si>
-    <t>135390249</t>
-  </si>
-  <si>
-    <t>135390362</t>
-  </si>
-  <si>
-    <t>135390429</t>
-  </si>
-  <si>
-    <t>135390459</t>
-  </si>
-  <si>
-    <t>135390500</t>
-  </si>
-  <si>
-    <t>135390505</t>
-  </si>
-  <si>
-    <t>135390806</t>
-  </si>
-  <si>
-    <t>135391025</t>
-  </si>
-  <si>
-    <t>135391032</t>
-  </si>
-  <si>
-    <t>135391092</t>
-  </si>
-  <si>
-    <t>135391256</t>
-  </si>
-  <si>
-    <t>135391288</t>
-  </si>
-  <si>
-    <t>135391347</t>
-  </si>
-  <si>
-    <t>135391392</t>
-  </si>
-  <si>
-    <t>135391409</t>
-  </si>
-  <si>
-    <t>135391413</t>
-  </si>
-  <si>
-    <t>135391472</t>
-  </si>
-  <si>
-    <t>135391493</t>
-  </si>
-  <si>
-    <t>135391589</t>
-  </si>
-  <si>
-    <t>135391670</t>
-  </si>
-  <si>
-    <t>135391711</t>
-  </si>
-  <si>
-    <t>135391821</t>
-  </si>
-  <si>
-    <t>135392120</t>
-  </si>
-  <si>
-    <t>135392219</t>
-  </si>
-  <si>
-    <t>135392284</t>
-  </si>
-  <si>
-    <t>135392327</t>
-  </si>
-  <si>
-    <t>135392417</t>
-  </si>
-  <si>
-    <t>135392431</t>
-  </si>
-  <si>
-    <t>135392456</t>
-  </si>
-  <si>
-    <t>135392483</t>
-  </si>
-  <si>
-    <t>135392548</t>
-  </si>
-  <si>
-    <t>135392573</t>
-  </si>
-  <si>
-    <t>135392746</t>
-  </si>
-  <si>
-    <t>135392919</t>
-  </si>
-  <si>
-    <t>135393124</t>
-  </si>
-  <si>
-    <t>135393794</t>
-  </si>
-  <si>
-    <t>135393958</t>
-  </si>
-  <si>
-    <t>135394047</t>
+    <t>130522716</t>
+  </si>
+  <si>
+    <t>130646840</t>
+  </si>
+  <si>
+    <t>130811664</t>
+  </si>
+  <si>
+    <t>130943722</t>
+  </si>
+  <si>
+    <t>130986168</t>
+  </si>
+  <si>
+    <t>131129936</t>
+  </si>
+  <si>
+    <t>131153542</t>
+  </si>
+  <si>
+    <t>131385165</t>
+  </si>
+  <si>
+    <t>131412686</t>
+  </si>
+  <si>
+    <t>131468628</t>
+  </si>
+  <si>
+    <t>131469537</t>
+  </si>
+  <si>
+    <t>131621370</t>
+  </si>
+  <si>
+    <t>131856407</t>
+  </si>
+  <si>
+    <t>132060786</t>
+  </si>
+  <si>
+    <t>132169745</t>
+  </si>
+  <si>
+    <t>132180792</t>
+  </si>
+  <si>
+    <t>132182299</t>
+  </si>
+  <si>
+    <t>132188611</t>
+  </si>
+  <si>
+    <t>132226797</t>
+  </si>
+  <si>
+    <t>132493826</t>
+  </si>
+  <si>
+    <t>132543204</t>
+  </si>
+  <si>
+    <t>132844370</t>
+  </si>
+  <si>
+    <t>132965013</t>
+  </si>
+  <si>
+    <t>132973221</t>
+  </si>
+  <si>
+    <t>132983711</t>
+  </si>
+  <si>
+    <t>133016532</t>
+  </si>
+  <si>
+    <t>133185171</t>
+  </si>
+  <si>
+    <t>133504017</t>
+  </si>
+  <si>
+    <t>133555083</t>
+  </si>
+  <si>
+    <t>133644261</t>
+  </si>
+  <si>
+    <t>133757122</t>
+  </si>
+  <si>
+    <t>133990376</t>
+  </si>
+  <si>
+    <t>134038845</t>
+  </si>
+  <si>
+    <t>134222961</t>
+  </si>
+  <si>
+    <t>134252035</t>
+  </si>
+  <si>
+    <t>134655767</t>
+  </si>
+  <si>
+    <t>134714701</t>
+  </si>
+  <si>
+    <t>134728810</t>
+  </si>
+  <si>
+    <t>135032202</t>
+  </si>
+  <si>
+    <t>135195250</t>
+  </si>
+  <si>
+    <t>135394101</t>
+  </si>
+  <si>
+    <t>135394171</t>
+  </si>
+  <si>
+    <t>135394175</t>
+  </si>
+  <si>
+    <t>135394292</t>
+  </si>
+  <si>
+    <t>135394369</t>
+  </si>
+  <si>
+    <t>135394527</t>
+  </si>
+  <si>
+    <t>135394547</t>
+  </si>
+  <si>
+    <t>135394646</t>
+  </si>
+  <si>
+    <t>135394703</t>
+  </si>
+  <si>
+    <t>135394706</t>
+  </si>
+  <si>
+    <t>135394738</t>
+  </si>
+  <si>
+    <t>135394950</t>
+  </si>
+  <si>
+    <t>135395004</t>
+  </si>
+  <si>
+    <t>135395052</t>
+  </si>
+  <si>
+    <t>135395420</t>
+  </si>
+  <si>
+    <t>135395459</t>
+  </si>
+  <si>
+    <t>135395548</t>
+  </si>
+  <si>
+    <t>135395552</t>
+  </si>
+  <si>
+    <t>135395649</t>
+  </si>
+  <si>
+    <t>135395715</t>
+  </si>
+  <si>
+    <t>135395810</t>
+  </si>
+  <si>
+    <t>135395894</t>
+  </si>
+  <si>
+    <t>135395940</t>
+  </si>
+  <si>
+    <t>135395964</t>
+  </si>
+  <si>
+    <t>135396062</t>
+  </si>
+  <si>
+    <t>135396064</t>
+  </si>
+  <si>
+    <t>135396204</t>
+  </si>
+  <si>
+    <t>135396344</t>
+  </si>
+  <si>
+    <t>135396490</t>
+  </si>
+  <si>
+    <t>135396535</t>
+  </si>
+  <si>
+    <t>135396556</t>
+  </si>
+  <si>
+    <t>135396788</t>
+  </si>
+  <si>
+    <t>135396887</t>
+  </si>
+  <si>
+    <t>135396895</t>
+  </si>
+  <si>
+    <t>135396898</t>
+  </si>
+  <si>
+    <t>135397039</t>
+  </si>
+  <si>
+    <t>135397070</t>
+  </si>
+  <si>
+    <t>135397181</t>
+  </si>
+  <si>
+    <t>135397279</t>
+  </si>
+  <si>
+    <t>135397542</t>
+  </si>
+  <si>
+    <t>135397654</t>
+  </si>
+  <si>
+    <t>135397864</t>
+  </si>
+  <si>
+    <t>135398111</t>
+  </si>
+  <si>
+    <t>135398159</t>
+  </si>
+  <si>
+    <t>135398313</t>
+  </si>
+  <si>
+    <t>135398328</t>
+  </si>
+  <si>
+    <t>135398429</t>
+  </si>
+  <si>
+    <t>135398595</t>
+  </si>
+  <si>
+    <t>135398687</t>
+  </si>
+  <si>
+    <t>135399026</t>
+  </si>
+  <si>
+    <t>135399053</t>
+  </si>
+  <si>
+    <t>135399217</t>
+  </si>
+  <si>
+    <t>135399356</t>
+  </si>
+  <si>
+    <t>135399414</t>
+  </si>
+  <si>
+    <t>135399456</t>
+  </si>
+  <si>
+    <t>135399481</t>
+  </si>
+  <si>
+    <t>135399520</t>
+  </si>
+  <si>
+    <t>135399583</t>
+  </si>
+  <si>
+    <t>135399670</t>
+  </si>
+  <si>
+    <t>135399748</t>
+  </si>
+  <si>
+    <t>135399898</t>
+  </si>
+  <si>
+    <t>135399919</t>
+  </si>
+  <si>
+    <t>135399941</t>
+  </si>
+  <si>
+    <t>135400020</t>
+  </si>
+  <si>
+    <t>135400046</t>
+  </si>
+  <si>
+    <t>135400083</t>
+  </si>
+  <si>
+    <t>135400154</t>
+  </si>
+  <si>
+    <t>135400176</t>
+  </si>
+  <si>
+    <t>135400195</t>
+  </si>
+  <si>
+    <t>135400218</t>
+  </si>
+  <si>
+    <t>135400539</t>
+  </si>
+  <si>
+    <t>135400593</t>
+  </si>
+  <si>
+    <t>135400594</t>
+  </si>
+  <si>
+    <t>135400693</t>
+  </si>
+  <si>
+    <t>135400785</t>
+  </si>
+  <si>
+    <t>135400911</t>
+  </si>
+  <si>
+    <t>135400913</t>
+  </si>
+  <si>
+    <t>135400948</t>
+  </si>
+  <si>
+    <t>135400979</t>
+  </si>
+  <si>
+    <t>135400989</t>
+  </si>
+  <si>
+    <t>135401100</t>
+  </si>
+  <si>
+    <t>135401551</t>
+  </si>
+  <si>
+    <t>135401640</t>
+  </si>
+  <si>
+    <t>135401642</t>
+  </si>
+  <si>
+    <t>135401707</t>
+  </si>
+  <si>
+    <t>135401772</t>
+  </si>
+  <si>
+    <t>135401858</t>
+  </si>
+  <si>
+    <t>135401955</t>
+  </si>
+  <si>
+    <t>135401990</t>
+  </si>
+  <si>
+    <t>135402027</t>
+  </si>
+  <si>
+    <t>135402030</t>
+  </si>
+  <si>
+    <t>135402062</t>
+  </si>
+  <si>
+    <t>135402098</t>
+  </si>
+  <si>
+    <t>135402221</t>
+  </si>
+  <si>
+    <t>135402241</t>
+  </si>
+  <si>
+    <t>135402285</t>
+  </si>
+  <si>
+    <t>135402383</t>
+  </si>
+  <si>
+    <t>135402390</t>
+  </si>
+  <si>
+    <t>135402424</t>
+  </si>
+  <si>
+    <t>135402443</t>
+  </si>
+  <si>
+    <t>135402518</t>
+  </si>
+  <si>
+    <t>135402524</t>
+  </si>
+  <si>
+    <t>135402579</t>
+  </si>
+  <si>
+    <t>135402580</t>
+  </si>
+  <si>
+    <t>135402598</t>
+  </si>
+  <si>
+    <t>135402626</t>
+  </si>
+  <si>
+    <t>135402693</t>
+  </si>
+  <si>
+    <t>135402869</t>
+  </si>
+  <si>
+    <t>135403261</t>
+  </si>
+  <si>
+    <t>135403482</t>
+  </si>
+  <si>
+    <t>135403625</t>
+  </si>
+  <si>
+    <t>135403628</t>
+  </si>
+  <si>
+    <t>135403815</t>
+  </si>
+  <si>
+    <t>135403967</t>
+  </si>
+  <si>
+    <t>135404028</t>
+  </si>
+  <si>
+    <t>135404398</t>
+  </si>
+  <si>
+    <t>135404568</t>
+  </si>
+  <si>
+    <t>135404795</t>
+  </si>
+  <si>
+    <t>135404982</t>
+  </si>
+  <si>
+    <t>135405032</t>
+  </si>
+  <si>
+    <t>135405155</t>
+  </si>
+  <si>
+    <t>135405157</t>
+  </si>
+  <si>
+    <t>135405191</t>
+  </si>
+  <si>
+    <t>135405264</t>
+  </si>
+  <si>
+    <t>135405326</t>
+  </si>
+  <si>
+    <t>135405331</t>
+  </si>
+  <si>
+    <t>135405364</t>
+  </si>
+  <si>
+    <t>135405431</t>
+  </si>
+  <si>
+    <t>135405474</t>
+  </si>
+  <si>
+    <t>135405522</t>
+  </si>
+  <si>
+    <t>135405722</t>
+  </si>
+  <si>
+    <t>135405761</t>
+  </si>
+  <si>
+    <t>135405919</t>
+  </si>
+  <si>
+    <t>135405951</t>
+  </si>
+  <si>
+    <t>135405976</t>
+  </si>
+  <si>
+    <t>135406064</t>
+  </si>
+  <si>
+    <t>135406107</t>
+  </si>
+  <si>
+    <t>135406124</t>
+  </si>
+  <si>
+    <t>135406160</t>
+  </si>
+  <si>
+    <t>135406244</t>
+  </si>
+  <si>
+    <t>135406288</t>
+  </si>
+  <si>
+    <t>135406362</t>
+  </si>
+  <si>
+    <t>135406371</t>
+  </si>
+  <si>
+    <t>135406500</t>
+  </si>
+  <si>
+    <t>135406527</t>
+  </si>
+  <si>
+    <t>135406547</t>
+  </si>
+  <si>
+    <t>135406608</t>
+  </si>
+  <si>
+    <t>135406917</t>
+  </si>
+  <si>
+    <t>135407001</t>
+  </si>
+  <si>
+    <t>135407084</t>
+  </si>
+  <si>
+    <t>135407135</t>
+  </si>
+  <si>
+    <t>135407234</t>
+  </si>
+  <si>
+    <t>135407330</t>
+  </si>
+  <si>
+    <t>135407334</t>
+  </si>
+  <si>
+    <t>135407542</t>
+  </si>
+  <si>
+    <t>135407560</t>
+  </si>
+  <si>
+    <t>135407622</t>
+  </si>
+  <si>
+    <t>135407729</t>
+  </si>
+  <si>
+    <t>135407772</t>
+  </si>
+  <si>
+    <t>135407792</t>
+  </si>
+  <si>
+    <t>135407816</t>
+  </si>
+  <si>
+    <t>135407825</t>
+  </si>
+  <si>
+    <t>135407979</t>
+  </si>
+  <si>
+    <t>135408056</t>
+  </si>
+  <si>
+    <t>135408087</t>
+  </si>
+  <si>
+    <t>135408142</t>
+  </si>
+  <si>
+    <t>135408156</t>
+  </si>
+  <si>
+    <t>135408294</t>
+  </si>
+  <si>
+    <t>135408561</t>
+  </si>
+  <si>
+    <t>135408597</t>
+  </si>
+  <si>
+    <t>135408644</t>
+  </si>
+  <si>
+    <t>135408687</t>
+  </si>
+  <si>
+    <t>135408710</t>
+  </si>
+  <si>
+    <t>135408747</t>
+  </si>
+  <si>
+    <t>135408776</t>
+  </si>
+  <si>
+    <t>135408845</t>
+  </si>
+  <si>
+    <t>135408871</t>
+  </si>
+  <si>
+    <t>135408921</t>
+  </si>
+  <si>
+    <t>135409035</t>
+  </si>
+  <si>
+    <t>135409077</t>
+  </si>
+  <si>
+    <t>135409107</t>
+  </si>
+  <si>
+    <t>135409253</t>
+  </si>
+  <si>
+    <t>135409465</t>
+  </si>
+  <si>
+    <t>135409501</t>
+  </si>
+  <si>
+    <t>135409533</t>
+  </si>
+  <si>
+    <t>135409540</t>
+  </si>
+  <si>
+    <t>135409576</t>
+  </si>
+  <si>
+    <t>135409615</t>
+  </si>
+  <si>
+    <t>135409664</t>
+  </si>
+  <si>
+    <t>135409677</t>
+  </si>
+  <si>
+    <t>135409773</t>
+  </si>
+  <si>
+    <t>135409795</t>
+  </si>
+  <si>
+    <t>135409799</t>
+  </si>
+  <si>
+    <t>135409871</t>
+  </si>
+  <si>
+    <t>135409902</t>
+  </si>
+  <si>
+    <t>135409967</t>
+  </si>
+  <si>
+    <t>135410012</t>
+  </si>
+  <si>
+    <t>135410137</t>
+  </si>
+  <si>
+    <t>135410142</t>
+  </si>
+  <si>
+    <t>135410182</t>
+  </si>
+  <si>
+    <t>135410191</t>
+  </si>
+  <si>
+    <t>135410217</t>
+  </si>
+  <si>
+    <t>135410240</t>
+  </si>
+  <si>
+    <t>135410250</t>
+  </si>
+  <si>
+    <t>135410293</t>
+  </si>
+  <si>
+    <t>135410607</t>
+  </si>
+  <si>
+    <t>135410608</t>
+  </si>
+  <si>
+    <t>135410612</t>
+  </si>
+  <si>
+    <t>135410697</t>
+  </si>
+  <si>
+    <t>135410719</t>
+  </si>
+  <si>
+    <t>135410752</t>
+  </si>
+  <si>
+    <t>135410795</t>
+  </si>
+  <si>
+    <t>135410971</t>
+  </si>
+  <si>
+    <t>135410993</t>
+  </si>
+  <si>
+    <t>135411033</t>
+  </si>
+  <si>
+    <t>135411170</t>
+  </si>
+  <si>
+    <t>135411176</t>
+  </si>
+  <si>
+    <t>135411195</t>
+  </si>
+  <si>
+    <t>135411243</t>
+  </si>
+  <si>
+    <t>135411318</t>
+  </si>
+  <si>
+    <t>135411369</t>
+  </si>
+  <si>
+    <t>135411385</t>
+  </si>
+  <si>
+    <t>135411439</t>
+  </si>
+  <si>
+    <t>135411479</t>
+  </si>
+  <si>
+    <t>135411505</t>
+  </si>
+  <si>
+    <t>135411519</t>
+  </si>
+  <si>
+    <t>135411561</t>
+  </si>
+  <si>
+    <t>135411598</t>
+  </si>
+  <si>
+    <t>135411608</t>
+  </si>
+  <si>
+    <t>135411610</t>
+  </si>
+  <si>
+    <t>135411650</t>
+  </si>
+  <si>
+    <t>135411699</t>
+  </si>
+  <si>
+    <t>135411731</t>
+  </si>
+  <si>
+    <t>135411812</t>
+  </si>
+  <si>
+    <t>135411861</t>
+  </si>
+  <si>
+    <t>135411885</t>
+  </si>
+  <si>
+    <t>135411926</t>
+  </si>
+  <si>
+    <t>135411934</t>
+  </si>
+  <si>
+    <t>135411950</t>
+  </si>
+  <si>
+    <t>135411979</t>
+  </si>
+  <si>
+    <t>135412025</t>
+  </si>
+  <si>
+    <t>135412039</t>
+  </si>
+  <si>
+    <t>135412052</t>
+  </si>
+  <si>
+    <t>135412071</t>
+  </si>
+  <si>
+    <t>135412102</t>
+  </si>
+  <si>
+    <t>135412104</t>
+  </si>
+  <si>
+    <t>135412109</t>
+  </si>
+  <si>
+    <t>135412175</t>
+  </si>
+  <si>
+    <t>135412271</t>
+  </si>
+  <si>
+    <t>135412304</t>
+  </si>
+  <si>
+    <t>135412397</t>
+  </si>
+  <si>
+    <t>135412482</t>
+  </si>
+  <si>
+    <t>135412504</t>
+  </si>
+  <si>
+    <t>135412827</t>
+  </si>
+  <si>
+    <t>135412911</t>
+  </si>
+  <si>
+    <t>135412935</t>
+  </si>
+  <si>
+    <t>135412951</t>
+  </si>
+  <si>
+    <t>135413036</t>
+  </si>
+  <si>
+    <t>135413046</t>
+  </si>
+  <si>
+    <t>135413095</t>
+  </si>
+  <si>
+    <t>135413214</t>
+  </si>
+  <si>
+    <t>135413237</t>
+  </si>
+  <si>
+    <t>135413257</t>
+  </si>
+  <si>
+    <t>135413351</t>
+  </si>
+  <si>
+    <t>135413450</t>
+  </si>
+  <si>
+    <t>135413529</t>
+  </si>
+  <si>
+    <t>135413776</t>
+  </si>
+  <si>
+    <t>135413894</t>
+  </si>
+  <si>
+    <t>135414111</t>
+  </si>
+  <si>
+    <t>135414126</t>
+  </si>
+  <si>
+    <t>135414142</t>
+  </si>
+  <si>
+    <t>135414344</t>
+  </si>
+  <si>
+    <t>135414556</t>
+  </si>
+  <si>
+    <t>135414593</t>
+  </si>
+  <si>
+    <t>135414603</t>
+  </si>
+  <si>
+    <t>135414626</t>
+  </si>
+  <si>
+    <t>135414635</t>
+  </si>
+  <si>
+    <t>135414681</t>
+  </si>
+  <si>
+    <t>135414739</t>
+  </si>
+  <si>
+    <t>135414791</t>
+  </si>
+  <si>
+    <t>135414813</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C247"/>
+  <dimension ref="A1:C322"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -3911,6 +4136,606 @@
         <v>4</v>
       </c>
     </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A298" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3F6943-E75E-479D-8C0B-C8B4DC0BFD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBB7C9E-7DA9-4646-9AF0-20F3F0905A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,55 +45,28 @@
     <t>.</t>
   </si>
   <si>
-    <t>131321151</t>
-  </si>
-  <si>
-    <t>135414873</t>
-  </si>
-  <si>
-    <t>135414886</t>
-  </si>
-  <si>
-    <t>135414956</t>
-  </si>
-  <si>
-    <t>135414988</t>
-  </si>
-  <si>
-    <t>135415029</t>
-  </si>
-  <si>
-    <t>135415082</t>
-  </si>
-  <si>
-    <t>135415213</t>
-  </si>
-  <si>
-    <t>135415231</t>
-  </si>
-  <si>
-    <t>135415334</t>
-  </si>
-  <si>
-    <t>135415416</t>
-  </si>
-  <si>
-    <t>135415468</t>
-  </si>
-  <si>
-    <t>135415488</t>
-  </si>
-  <si>
-    <t>135415502</t>
-  </si>
-  <si>
-    <t>135415789</t>
-  </si>
-  <si>
-    <t>135415802</t>
-  </si>
-  <si>
-    <t>135415812</t>
+    <t>132387714</t>
+  </si>
+  <si>
+    <t>135416016</t>
+  </si>
+  <si>
+    <t>135416072</t>
+  </si>
+  <si>
+    <t>135416127</t>
+  </si>
+  <si>
+    <t>135416606</t>
+  </si>
+  <si>
+    <t>135416666</t>
+  </si>
+  <si>
+    <t>135416670</t>
+  </si>
+  <si>
+    <t>135416749</t>
   </si>
 </sst>
 </file>
@@ -607,103 +580,49 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A18" s="4"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C18" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBB7C9E-7DA9-4646-9AF0-20F3F0905A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF4E2C8-138C-415D-BFA5-B458EBC36753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="163">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,28 +45,478 @@
     <t>.</t>
   </si>
   <si>
-    <t>132387714</t>
-  </si>
-  <si>
-    <t>135416016</t>
-  </si>
-  <si>
-    <t>135416072</t>
-  </si>
-  <si>
-    <t>135416127</t>
-  </si>
-  <si>
-    <t>135416606</t>
-  </si>
-  <si>
-    <t>135416666</t>
-  </si>
-  <si>
-    <t>135416670</t>
-  </si>
-  <si>
-    <t>135416749</t>
+    <t>130705235</t>
+  </si>
+  <si>
+    <t>131328620</t>
+  </si>
+  <si>
+    <t>131388385</t>
+  </si>
+  <si>
+    <t>131492404</t>
+  </si>
+  <si>
+    <t>131517709</t>
+  </si>
+  <si>
+    <t>131894277</t>
+  </si>
+  <si>
+    <t>131999697</t>
+  </si>
+  <si>
+    <t>132211516</t>
+  </si>
+  <si>
+    <t>132273748</t>
+  </si>
+  <si>
+    <t>132334740</t>
+  </si>
+  <si>
+    <t>132368234</t>
+  </si>
+  <si>
+    <t>132897903</t>
+  </si>
+  <si>
+    <t>133293546</t>
+  </si>
+  <si>
+    <t>133589119</t>
+  </si>
+  <si>
+    <t>133638139</t>
+  </si>
+  <si>
+    <t>133730610</t>
+  </si>
+  <si>
+    <t>133749915</t>
+  </si>
+  <si>
+    <t>133819125</t>
+  </si>
+  <si>
+    <t>134225538</t>
+  </si>
+  <si>
+    <t>134242899</t>
+  </si>
+  <si>
+    <t>135000451</t>
+  </si>
+  <si>
+    <t>135350635</t>
+  </si>
+  <si>
+    <t>135417093</t>
+  </si>
+  <si>
+    <t>135417178</t>
+  </si>
+  <si>
+    <t>135417257</t>
+  </si>
+  <si>
+    <t>135417506</t>
+  </si>
+  <si>
+    <t>135417618</t>
+  </si>
+  <si>
+    <t>135417771</t>
+  </si>
+  <si>
+    <t>135417856</t>
+  </si>
+  <si>
+    <t>135417926</t>
+  </si>
+  <si>
+    <t>135418259</t>
+  </si>
+  <si>
+    <t>135418509</t>
+  </si>
+  <si>
+    <t>135418749</t>
+  </si>
+  <si>
+    <t>135419308</t>
+  </si>
+  <si>
+    <t>135419375</t>
+  </si>
+  <si>
+    <t>135419502</t>
+  </si>
+  <si>
+    <t>135419605</t>
+  </si>
+  <si>
+    <t>135419607</t>
+  </si>
+  <si>
+    <t>135419634</t>
+  </si>
+  <si>
+    <t>135420095</t>
+  </si>
+  <si>
+    <t>135420340</t>
+  </si>
+  <si>
+    <t>135420456</t>
+  </si>
+  <si>
+    <t>135420655</t>
+  </si>
+  <si>
+    <t>135420693</t>
+  </si>
+  <si>
+    <t>135420799</t>
+  </si>
+  <si>
+    <t>135420857</t>
+  </si>
+  <si>
+    <t>135420946</t>
+  </si>
+  <si>
+    <t>135421341</t>
+  </si>
+  <si>
+    <t>135421467</t>
+  </si>
+  <si>
+    <t>135421535</t>
+  </si>
+  <si>
+    <t>135421567</t>
+  </si>
+  <si>
+    <t>135421784</t>
+  </si>
+  <si>
+    <t>135421899</t>
+  </si>
+  <si>
+    <t>135422128</t>
+  </si>
+  <si>
+    <t>135422133</t>
+  </si>
+  <si>
+    <t>135422265</t>
+  </si>
+  <si>
+    <t>135422316</t>
+  </si>
+  <si>
+    <t>135422329</t>
+  </si>
+  <si>
+    <t>135422404</t>
+  </si>
+  <si>
+    <t>135422616</t>
+  </si>
+  <si>
+    <t>135422657</t>
+  </si>
+  <si>
+    <t>135422777</t>
+  </si>
+  <si>
+    <t>135422809</t>
+  </si>
+  <si>
+    <t>135423031</t>
+  </si>
+  <si>
+    <t>135423196</t>
+  </si>
+  <si>
+    <t>135423272</t>
+  </si>
+  <si>
+    <t>135423517</t>
+  </si>
+  <si>
+    <t>135423554</t>
+  </si>
+  <si>
+    <t>135423560</t>
+  </si>
+  <si>
+    <t>135423697</t>
+  </si>
+  <si>
+    <t>135423755</t>
+  </si>
+  <si>
+    <t>135423885</t>
+  </si>
+  <si>
+    <t>135423988</t>
+  </si>
+  <si>
+    <t>135424666</t>
+  </si>
+  <si>
+    <t>135424717</t>
+  </si>
+  <si>
+    <t>135425055</t>
+  </si>
+  <si>
+    <t>135425129</t>
+  </si>
+  <si>
+    <t>135425260</t>
+  </si>
+  <si>
+    <t>135425459</t>
+  </si>
+  <si>
+    <t>135425488</t>
+  </si>
+  <si>
+    <t>135425601</t>
+  </si>
+  <si>
+    <t>135425722</t>
+  </si>
+  <si>
+    <t>135425854</t>
+  </si>
+  <si>
+    <t>135426098</t>
+  </si>
+  <si>
+    <t>135426171</t>
+  </si>
+  <si>
+    <t>135426181</t>
+  </si>
+  <si>
+    <t>135426489</t>
+  </si>
+  <si>
+    <t>135426691</t>
+  </si>
+  <si>
+    <t>135426917</t>
+  </si>
+  <si>
+    <t>135426951</t>
+  </si>
+  <si>
+    <t>135427086</t>
+  </si>
+  <si>
+    <t>135427440</t>
+  </si>
+  <si>
+    <t>135427738</t>
+  </si>
+  <si>
+    <t>135427839</t>
+  </si>
+  <si>
+    <t>135428200</t>
+  </si>
+  <si>
+    <t>135428475</t>
+  </si>
+  <si>
+    <t>135428559</t>
+  </si>
+  <si>
+    <t>135428578</t>
+  </si>
+  <si>
+    <t>135428720</t>
+  </si>
+  <si>
+    <t>135428758</t>
+  </si>
+  <si>
+    <t>135429183</t>
+  </si>
+  <si>
+    <t>135429347</t>
+  </si>
+  <si>
+    <t>135429674</t>
+  </si>
+  <si>
+    <t>135430166</t>
+  </si>
+  <si>
+    <t>135430285</t>
+  </si>
+  <si>
+    <t>135430391</t>
+  </si>
+  <si>
+    <t>135430533</t>
+  </si>
+  <si>
+    <t>135430556</t>
+  </si>
+  <si>
+    <t>135430736</t>
+  </si>
+  <si>
+    <t>135430919</t>
+  </si>
+  <si>
+    <t>135430978</t>
+  </si>
+  <si>
+    <t>135431026</t>
+  </si>
+  <si>
+    <t>135431165</t>
+  </si>
+  <si>
+    <t>135431170</t>
+  </si>
+  <si>
+    <t>135431178</t>
+  </si>
+  <si>
+    <t>135431196</t>
+  </si>
+  <si>
+    <t>135431343</t>
+  </si>
+  <si>
+    <t>135431347</t>
+  </si>
+  <si>
+    <t>135431465</t>
+  </si>
+  <si>
+    <t>135431502</t>
+  </si>
+  <si>
+    <t>135431553</t>
+  </si>
+  <si>
+    <t>135431610</t>
+  </si>
+  <si>
+    <t>135431671</t>
+  </si>
+  <si>
+    <t>135431777</t>
+  </si>
+  <si>
+    <t>135432017</t>
+  </si>
+  <si>
+    <t>135432047</t>
+  </si>
+  <si>
+    <t>135432176</t>
+  </si>
+  <si>
+    <t>135432254</t>
+  </si>
+  <si>
+    <t>135432284</t>
+  </si>
+  <si>
+    <t>135432313</t>
+  </si>
+  <si>
+    <t>135432542</t>
+  </si>
+  <si>
+    <t>135432580</t>
+  </si>
+  <si>
+    <t>135432841</t>
+  </si>
+  <si>
+    <t>135433033</t>
+  </si>
+  <si>
+    <t>135433230</t>
+  </si>
+  <si>
+    <t>135433280</t>
+  </si>
+  <si>
+    <t>135433419</t>
+  </si>
+  <si>
+    <t>135433515</t>
+  </si>
+  <si>
+    <t>135433530</t>
+  </si>
+  <si>
+    <t>135433543</t>
+  </si>
+  <si>
+    <t>135433573</t>
+  </si>
+  <si>
+    <t>135433777</t>
+  </si>
+  <si>
+    <t>135433878</t>
+  </si>
+  <si>
+    <t>135433960</t>
+  </si>
+  <si>
+    <t>135434074</t>
+  </si>
+  <si>
+    <t>135434150</t>
+  </si>
+  <si>
+    <t>135434190</t>
+  </si>
+  <si>
+    <t>135434706</t>
+  </si>
+  <si>
+    <t>135434736</t>
+  </si>
+  <si>
+    <t>135434815</t>
+  </si>
+  <si>
+    <t>135434817</t>
+  </si>
+  <si>
+    <t>135435555</t>
+  </si>
+  <si>
+    <t>135435669</t>
+  </si>
+  <si>
+    <t>135435673</t>
+  </si>
+  <si>
+    <t>135435822</t>
+  </si>
+  <si>
+    <t>135435989</t>
+  </si>
+  <si>
+    <t>135436001</t>
+  </si>
+  <si>
+    <t>135436006</t>
   </si>
 </sst>
 </file>
@@ -471,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -580,49 +1030,1213 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C18" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF4E2C8-138C-415D-BFA5-B458EBC36753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340929D7-D0B3-486F-95AF-D0F30B6790BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="170">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,478 +45,499 @@
     <t>.</t>
   </si>
   <si>
-    <t>130705235</t>
-  </si>
-  <si>
-    <t>131328620</t>
-  </si>
-  <si>
-    <t>131388385</t>
-  </si>
-  <si>
-    <t>131492404</t>
-  </si>
-  <si>
-    <t>131517709</t>
-  </si>
-  <si>
-    <t>131894277</t>
-  </si>
-  <si>
-    <t>131999697</t>
-  </si>
-  <si>
-    <t>132211516</t>
-  </si>
-  <si>
-    <t>132273748</t>
-  </si>
-  <si>
-    <t>132334740</t>
-  </si>
-  <si>
-    <t>132368234</t>
-  </si>
-  <si>
-    <t>132897903</t>
-  </si>
-  <si>
-    <t>133293546</t>
-  </si>
-  <si>
-    <t>133589119</t>
-  </si>
-  <si>
-    <t>133638139</t>
-  </si>
-  <si>
-    <t>133730610</t>
-  </si>
-  <si>
-    <t>133749915</t>
-  </si>
-  <si>
-    <t>133819125</t>
-  </si>
-  <si>
-    <t>134225538</t>
-  </si>
-  <si>
-    <t>134242899</t>
-  </si>
-  <si>
-    <t>135000451</t>
-  </si>
-  <si>
-    <t>135350635</t>
-  </si>
-  <si>
-    <t>135417093</t>
-  </si>
-  <si>
-    <t>135417178</t>
-  </si>
-  <si>
-    <t>135417257</t>
-  </si>
-  <si>
-    <t>135417506</t>
-  </si>
-  <si>
-    <t>135417618</t>
-  </si>
-  <si>
-    <t>135417771</t>
-  </si>
-  <si>
-    <t>135417856</t>
-  </si>
-  <si>
-    <t>135417926</t>
-  </si>
-  <si>
-    <t>135418259</t>
-  </si>
-  <si>
-    <t>135418509</t>
-  </si>
-  <si>
-    <t>135418749</t>
-  </si>
-  <si>
-    <t>135419308</t>
-  </si>
-  <si>
-    <t>135419375</t>
-  </si>
-  <si>
-    <t>135419502</t>
-  </si>
-  <si>
-    <t>135419605</t>
-  </si>
-  <si>
-    <t>135419607</t>
-  </si>
-  <si>
-    <t>135419634</t>
-  </si>
-  <si>
-    <t>135420095</t>
-  </si>
-  <si>
-    <t>135420340</t>
-  </si>
-  <si>
-    <t>135420456</t>
-  </si>
-  <si>
-    <t>135420655</t>
-  </si>
-  <si>
-    <t>135420693</t>
-  </si>
-  <si>
-    <t>135420799</t>
-  </si>
-  <si>
-    <t>135420857</t>
-  </si>
-  <si>
-    <t>135420946</t>
-  </si>
-  <si>
-    <t>135421341</t>
-  </si>
-  <si>
-    <t>135421467</t>
-  </si>
-  <si>
-    <t>135421535</t>
-  </si>
-  <si>
-    <t>135421567</t>
-  </si>
-  <si>
-    <t>135421784</t>
-  </si>
-  <si>
-    <t>135421899</t>
-  </si>
-  <si>
-    <t>135422128</t>
-  </si>
-  <si>
-    <t>135422133</t>
-  </si>
-  <si>
-    <t>135422265</t>
-  </si>
-  <si>
-    <t>135422316</t>
-  </si>
-  <si>
-    <t>135422329</t>
-  </si>
-  <si>
-    <t>135422404</t>
-  </si>
-  <si>
-    <t>135422616</t>
-  </si>
-  <si>
-    <t>135422657</t>
-  </si>
-  <si>
-    <t>135422777</t>
-  </si>
-  <si>
-    <t>135422809</t>
-  </si>
-  <si>
-    <t>135423031</t>
-  </si>
-  <si>
-    <t>135423196</t>
-  </si>
-  <si>
-    <t>135423272</t>
-  </si>
-  <si>
-    <t>135423517</t>
-  </si>
-  <si>
-    <t>135423554</t>
-  </si>
-  <si>
-    <t>135423560</t>
-  </si>
-  <si>
-    <t>135423697</t>
-  </si>
-  <si>
-    <t>135423755</t>
-  </si>
-  <si>
-    <t>135423885</t>
-  </si>
-  <si>
-    <t>135423988</t>
-  </si>
-  <si>
-    <t>135424666</t>
-  </si>
-  <si>
-    <t>135424717</t>
-  </si>
-  <si>
-    <t>135425055</t>
-  </si>
-  <si>
-    <t>135425129</t>
-  </si>
-  <si>
-    <t>135425260</t>
-  </si>
-  <si>
-    <t>135425459</t>
-  </si>
-  <si>
-    <t>135425488</t>
-  </si>
-  <si>
-    <t>135425601</t>
-  </si>
-  <si>
-    <t>135425722</t>
-  </si>
-  <si>
-    <t>135425854</t>
-  </si>
-  <si>
-    <t>135426098</t>
-  </si>
-  <si>
-    <t>135426171</t>
-  </si>
-  <si>
-    <t>135426181</t>
-  </si>
-  <si>
-    <t>135426489</t>
-  </si>
-  <si>
-    <t>135426691</t>
-  </si>
-  <si>
-    <t>135426917</t>
-  </si>
-  <si>
-    <t>135426951</t>
-  </si>
-  <si>
-    <t>135427086</t>
-  </si>
-  <si>
-    <t>135427440</t>
-  </si>
-  <si>
-    <t>135427738</t>
-  </si>
-  <si>
-    <t>135427839</t>
-  </si>
-  <si>
-    <t>135428200</t>
-  </si>
-  <si>
-    <t>135428475</t>
-  </si>
-  <si>
-    <t>135428559</t>
-  </si>
-  <si>
-    <t>135428578</t>
-  </si>
-  <si>
-    <t>135428720</t>
-  </si>
-  <si>
-    <t>135428758</t>
-  </si>
-  <si>
-    <t>135429183</t>
-  </si>
-  <si>
-    <t>135429347</t>
-  </si>
-  <si>
-    <t>135429674</t>
-  </si>
-  <si>
-    <t>135430166</t>
-  </si>
-  <si>
-    <t>135430285</t>
-  </si>
-  <si>
-    <t>135430391</t>
-  </si>
-  <si>
-    <t>135430533</t>
-  </si>
-  <si>
-    <t>135430556</t>
-  </si>
-  <si>
-    <t>135430736</t>
-  </si>
-  <si>
-    <t>135430919</t>
-  </si>
-  <si>
-    <t>135430978</t>
-  </si>
-  <si>
-    <t>135431026</t>
-  </si>
-  <si>
-    <t>135431165</t>
-  </si>
-  <si>
-    <t>135431170</t>
-  </si>
-  <si>
-    <t>135431178</t>
-  </si>
-  <si>
-    <t>135431196</t>
-  </si>
-  <si>
-    <t>135431343</t>
-  </si>
-  <si>
-    <t>135431347</t>
-  </si>
-  <si>
-    <t>135431465</t>
-  </si>
-  <si>
-    <t>135431502</t>
-  </si>
-  <si>
-    <t>135431553</t>
-  </si>
-  <si>
-    <t>135431610</t>
-  </si>
-  <si>
-    <t>135431671</t>
-  </si>
-  <si>
-    <t>135431777</t>
-  </si>
-  <si>
-    <t>135432017</t>
-  </si>
-  <si>
-    <t>135432047</t>
-  </si>
-  <si>
-    <t>135432176</t>
-  </si>
-  <si>
-    <t>135432254</t>
-  </si>
-  <si>
-    <t>135432284</t>
-  </si>
-  <si>
-    <t>135432313</t>
-  </si>
-  <si>
-    <t>135432542</t>
-  </si>
-  <si>
-    <t>135432580</t>
-  </si>
-  <si>
-    <t>135432841</t>
-  </si>
-  <si>
-    <t>135433033</t>
-  </si>
-  <si>
-    <t>135433230</t>
-  </si>
-  <si>
-    <t>135433280</t>
-  </si>
-  <si>
-    <t>135433419</t>
-  </si>
-  <si>
-    <t>135433515</t>
-  </si>
-  <si>
-    <t>135433530</t>
-  </si>
-  <si>
-    <t>135433543</t>
-  </si>
-  <si>
-    <t>135433573</t>
-  </si>
-  <si>
-    <t>135433777</t>
-  </si>
-  <si>
-    <t>135433878</t>
-  </si>
-  <si>
-    <t>135433960</t>
-  </si>
-  <si>
-    <t>135434074</t>
-  </si>
-  <si>
-    <t>135434150</t>
-  </si>
-  <si>
-    <t>135434190</t>
-  </si>
-  <si>
-    <t>135434706</t>
-  </si>
-  <si>
-    <t>135434736</t>
-  </si>
-  <si>
-    <t>135434815</t>
-  </si>
-  <si>
-    <t>135434817</t>
-  </si>
-  <si>
-    <t>135435555</t>
-  </si>
-  <si>
-    <t>135435669</t>
-  </si>
-  <si>
-    <t>135435673</t>
-  </si>
-  <si>
-    <t>135435822</t>
-  </si>
-  <si>
-    <t>135435989</t>
-  </si>
-  <si>
-    <t>135436001</t>
-  </si>
-  <si>
-    <t>135436006</t>
+    <t>130607350</t>
+  </si>
+  <si>
+    <t>130698011</t>
+  </si>
+  <si>
+    <t>130876070</t>
+  </si>
+  <si>
+    <t>131686906</t>
+  </si>
+  <si>
+    <t>131854427</t>
+  </si>
+  <si>
+    <t>132042491</t>
+  </si>
+  <si>
+    <t>132679621</t>
+  </si>
+  <si>
+    <t>132774034</t>
+  </si>
+  <si>
+    <t>132907672</t>
+  </si>
+  <si>
+    <t>133256434</t>
+  </si>
+  <si>
+    <t>133741509</t>
+  </si>
+  <si>
+    <t>134258355</t>
+  </si>
+  <si>
+    <t>134331159</t>
+  </si>
+  <si>
+    <t>134660611</t>
+  </si>
+  <si>
+    <t>134869150</t>
+  </si>
+  <si>
+    <t>135358060</t>
+  </si>
+  <si>
+    <t>135436159</t>
+  </si>
+  <si>
+    <t>135436189</t>
+  </si>
+  <si>
+    <t>135436766</t>
+  </si>
+  <si>
+    <t>135436822</t>
+  </si>
+  <si>
+    <t>135436925</t>
+  </si>
+  <si>
+    <t>135437329</t>
+  </si>
+  <si>
+    <t>135437787</t>
+  </si>
+  <si>
+    <t>135437791</t>
+  </si>
+  <si>
+    <t>135437858</t>
+  </si>
+  <si>
+    <t>135438024</t>
+  </si>
+  <si>
+    <t>135438112</t>
+  </si>
+  <si>
+    <t>135438225</t>
+  </si>
+  <si>
+    <t>135438322</t>
+  </si>
+  <si>
+    <t>135438337</t>
+  </si>
+  <si>
+    <t>135438551</t>
+  </si>
+  <si>
+    <t>135438565</t>
+  </si>
+  <si>
+    <t>135438974</t>
+  </si>
+  <si>
+    <t>135439146</t>
+  </si>
+  <si>
+    <t>135439224</t>
+  </si>
+  <si>
+    <t>135439729</t>
+  </si>
+  <si>
+    <t>135440293</t>
+  </si>
+  <si>
+    <t>135440490</t>
+  </si>
+  <si>
+    <t>135440590</t>
+  </si>
+  <si>
+    <t>135440737</t>
+  </si>
+  <si>
+    <t>135440774</t>
+  </si>
+  <si>
+    <t>135440839</t>
+  </si>
+  <si>
+    <t>135440871</t>
+  </si>
+  <si>
+    <t>135440975</t>
+  </si>
+  <si>
+    <t>135441005</t>
+  </si>
+  <si>
+    <t>135441171</t>
+  </si>
+  <si>
+    <t>135441264</t>
+  </si>
+  <si>
+    <t>135441413</t>
+  </si>
+  <si>
+    <t>135441427</t>
+  </si>
+  <si>
+    <t>135441540</t>
+  </si>
+  <si>
+    <t>135441798</t>
+  </si>
+  <si>
+    <t>135442211</t>
+  </si>
+  <si>
+    <t>135442392</t>
+  </si>
+  <si>
+    <t>135442855</t>
+  </si>
+  <si>
+    <t>135442974</t>
+  </si>
+  <si>
+    <t>135443054</t>
+  </si>
+  <si>
+    <t>135443061</t>
+  </si>
+  <si>
+    <t>135443098</t>
+  </si>
+  <si>
+    <t>135443127</t>
+  </si>
+  <si>
+    <t>135443133</t>
+  </si>
+  <si>
+    <t>135443192</t>
+  </si>
+  <si>
+    <t>135443262</t>
+  </si>
+  <si>
+    <t>135443270</t>
+  </si>
+  <si>
+    <t>135443498</t>
+  </si>
+  <si>
+    <t>135443515</t>
+  </si>
+  <si>
+    <t>135443728</t>
+  </si>
+  <si>
+    <t>135443982</t>
+  </si>
+  <si>
+    <t>135444064</t>
+  </si>
+  <si>
+    <t>135444073</t>
+  </si>
+  <si>
+    <t>135444215</t>
+  </si>
+  <si>
+    <t>135444264</t>
+  </si>
+  <si>
+    <t>135444291</t>
+  </si>
+  <si>
+    <t>135444351</t>
+  </si>
+  <si>
+    <t>135444525</t>
+  </si>
+  <si>
+    <t>135444561</t>
+  </si>
+  <si>
+    <t>135444722</t>
+  </si>
+  <si>
+    <t>135445282</t>
+  </si>
+  <si>
+    <t>135445423</t>
+  </si>
+  <si>
+    <t>135445469</t>
+  </si>
+  <si>
+    <t>135445901</t>
+  </si>
+  <si>
+    <t>135446123</t>
+  </si>
+  <si>
+    <t>135446213</t>
+  </si>
+  <si>
+    <t>135446284</t>
+  </si>
+  <si>
+    <t>135447141</t>
+  </si>
+  <si>
+    <t>135447191</t>
+  </si>
+  <si>
+    <t>135447507</t>
+  </si>
+  <si>
+    <t>135447565</t>
+  </si>
+  <si>
+    <t>135447663</t>
+  </si>
+  <si>
+    <t>135447755</t>
+  </si>
+  <si>
+    <t>135448114</t>
+  </si>
+  <si>
+    <t>135448172</t>
+  </si>
+  <si>
+    <t>135448313</t>
+  </si>
+  <si>
+    <t>135448383</t>
+  </si>
+  <si>
+    <t>135448408</t>
+  </si>
+  <si>
+    <t>135448483</t>
+  </si>
+  <si>
+    <t>135448566</t>
+  </si>
+  <si>
+    <t>135448736</t>
+  </si>
+  <si>
+    <t>135448998</t>
+  </si>
+  <si>
+    <t>135449179</t>
+  </si>
+  <si>
+    <t>135449231</t>
+  </si>
+  <si>
+    <t>135449351</t>
+  </si>
+  <si>
+    <t>135449394</t>
+  </si>
+  <si>
+    <t>135449476</t>
+  </si>
+  <si>
+    <t>135449551</t>
+  </si>
+  <si>
+    <t>135449599</t>
+  </si>
+  <si>
+    <t>135449601</t>
+  </si>
+  <si>
+    <t>135449830</t>
+  </si>
+  <si>
+    <t>135449932</t>
+  </si>
+  <si>
+    <t>135449948</t>
+  </si>
+  <si>
+    <t>135449977</t>
+  </si>
+  <si>
+    <t>135450097</t>
+  </si>
+  <si>
+    <t>135450174</t>
+  </si>
+  <si>
+    <t>135450449</t>
+  </si>
+  <si>
+    <t>135451156</t>
+  </si>
+  <si>
+    <t>135451869</t>
+  </si>
+  <si>
+    <t>135451902</t>
+  </si>
+  <si>
+    <t>135451937</t>
+  </si>
+  <si>
+    <t>135452037</t>
+  </si>
+  <si>
+    <t>135452070</t>
+  </si>
+  <si>
+    <t>135452092</t>
+  </si>
+  <si>
+    <t>135452247</t>
+  </si>
+  <si>
+    <t>135452326</t>
+  </si>
+  <si>
+    <t>135452646</t>
+  </si>
+  <si>
+    <t>135452748</t>
+  </si>
+  <si>
+    <t>135452804</t>
+  </si>
+  <si>
+    <t>135452984</t>
+  </si>
+  <si>
+    <t>135453191</t>
+  </si>
+  <si>
+    <t>135453317</t>
+  </si>
+  <si>
+    <t>135453396</t>
+  </si>
+  <si>
+    <t>135453413</t>
+  </si>
+  <si>
+    <t>135453478</t>
+  </si>
+  <si>
+    <t>135453526</t>
+  </si>
+  <si>
+    <t>135453624</t>
+  </si>
+  <si>
+    <t>135453627</t>
+  </si>
+  <si>
+    <t>135453629</t>
+  </si>
+  <si>
+    <t>135453662</t>
+  </si>
+  <si>
+    <t>135453775</t>
+  </si>
+  <si>
+    <t>135453804</t>
+  </si>
+  <si>
+    <t>135453879</t>
+  </si>
+  <si>
+    <t>135453935</t>
+  </si>
+  <si>
+    <t>135453976</t>
+  </si>
+  <si>
+    <t>135454078</t>
+  </si>
+  <si>
+    <t>135454176</t>
+  </si>
+  <si>
+    <t>135454177</t>
+  </si>
+  <si>
+    <t>135454279</t>
+  </si>
+  <si>
+    <t>135454333</t>
+  </si>
+  <si>
+    <t>135454415</t>
+  </si>
+  <si>
+    <t>135454509</t>
+  </si>
+  <si>
+    <t>135454611</t>
+  </si>
+  <si>
+    <t>135454615</t>
+  </si>
+  <si>
+    <t>135454628</t>
+  </si>
+  <si>
+    <t>135454644</t>
+  </si>
+  <si>
+    <t>135454763</t>
+  </si>
+  <si>
+    <t>135454858</t>
+  </si>
+  <si>
+    <t>135455301</t>
+  </si>
+  <si>
+    <t>135455372</t>
+  </si>
+  <si>
+    <t>135455455</t>
+  </si>
+  <si>
+    <t>135456157</t>
+  </si>
+  <si>
+    <t>135456386</t>
+  </si>
+  <si>
+    <t>135456692</t>
+  </si>
+  <si>
+    <t>135456724</t>
+  </si>
+  <si>
+    <t>135456806</t>
+  </si>
+  <si>
+    <t>135456907</t>
+  </si>
+  <si>
+    <t>135457027</t>
+  </si>
+  <si>
+    <t>135457117</t>
   </si>
 </sst>
 </file>
@@ -921,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2238,6 +2259,62 @@
         <v>3</v>
       </c>
     </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C18" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE921C6-2C77-4D28-A86A-DF092678A2AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8106AA2-3310-4618-A367-91804132F9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="159">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,439 +45,466 @@
     <t>.</t>
   </si>
   <si>
-    <t>131102099</t>
-  </si>
-  <si>
-    <t>131793897</t>
-  </si>
-  <si>
-    <t>131856851</t>
-  </si>
-  <si>
-    <t>132687891</t>
-  </si>
-  <si>
-    <t>133334611</t>
-  </si>
-  <si>
-    <t>133384191</t>
-  </si>
-  <si>
-    <t>133809902</t>
-  </si>
-  <si>
-    <t>134329480</t>
-  </si>
-  <si>
-    <t>134892806</t>
-  </si>
-  <si>
-    <t>135033673</t>
-  </si>
-  <si>
-    <t>135506624</t>
-  </si>
-  <si>
-    <t>135507207</t>
-  </si>
-  <si>
-    <t>135507494</t>
-  </si>
-  <si>
-    <t>135507983</t>
-  </si>
-  <si>
-    <t>135508007</t>
-  </si>
-  <si>
-    <t>135508040</t>
-  </si>
-  <si>
-    <t>135508150</t>
-  </si>
-  <si>
-    <t>135508526</t>
-  </si>
-  <si>
-    <t>135508650</t>
-  </si>
-  <si>
-    <t>135508690</t>
-  </si>
-  <si>
-    <t>135508706</t>
-  </si>
-  <si>
-    <t>135508957</t>
-  </si>
-  <si>
-    <t>135509087</t>
-  </si>
-  <si>
-    <t>135509208</t>
-  </si>
-  <si>
-    <t>135509650</t>
-  </si>
-  <si>
-    <t>135509673</t>
-  </si>
-  <si>
-    <t>135509699</t>
-  </si>
-  <si>
-    <t>135509862</t>
-  </si>
-  <si>
-    <t>135510380</t>
-  </si>
-  <si>
-    <t>135510591</t>
-  </si>
-  <si>
-    <t>135510881</t>
-  </si>
-  <si>
-    <t>135511014</t>
-  </si>
-  <si>
-    <t>135511021</t>
-  </si>
-  <si>
-    <t>135511129</t>
-  </si>
-  <si>
-    <t>135511148</t>
-  </si>
-  <si>
-    <t>135511193</t>
-  </si>
-  <si>
-    <t>135511235</t>
-  </si>
-  <si>
-    <t>135511638</t>
-  </si>
-  <si>
-    <t>135511788</t>
-  </si>
-  <si>
-    <t>135511933</t>
-  </si>
-  <si>
-    <t>135512065</t>
-  </si>
-  <si>
-    <t>135512187</t>
-  </si>
-  <si>
-    <t>135512262</t>
-  </si>
-  <si>
-    <t>135512381</t>
-  </si>
-  <si>
-    <t>135512426</t>
-  </si>
-  <si>
-    <t>135512462</t>
-  </si>
-  <si>
-    <t>135512548</t>
-  </si>
-  <si>
-    <t>135512582</t>
-  </si>
-  <si>
-    <t>135512631</t>
-  </si>
-  <si>
-    <t>135513015</t>
-  </si>
-  <si>
-    <t>135513275</t>
-  </si>
-  <si>
-    <t>135513401</t>
-  </si>
-  <si>
-    <t>135513721</t>
-  </si>
-  <si>
-    <t>135513952</t>
-  </si>
-  <si>
-    <t>135514104</t>
-  </si>
-  <si>
-    <t>135514166</t>
-  </si>
-  <si>
-    <t>135514179</t>
-  </si>
-  <si>
-    <t>135514208</t>
-  </si>
-  <si>
-    <t>135514368</t>
-  </si>
-  <si>
-    <t>135514432</t>
-  </si>
-  <si>
-    <t>135515047</t>
-  </si>
-  <si>
-    <t>135515371</t>
-  </si>
-  <si>
-    <t>135515451</t>
-  </si>
-  <si>
-    <t>135515765</t>
-  </si>
-  <si>
-    <t>135516762</t>
-  </si>
-  <si>
-    <t>135517032</t>
-  </si>
-  <si>
-    <t>135517113</t>
-  </si>
-  <si>
-    <t>135517168</t>
-  </si>
-  <si>
-    <t>135517301</t>
-  </si>
-  <si>
-    <t>135517402</t>
-  </si>
-  <si>
-    <t>135517549</t>
-  </si>
-  <si>
-    <t>135517796</t>
-  </si>
-  <si>
-    <t>135518413</t>
-  </si>
-  <si>
-    <t>135518625</t>
-  </si>
-  <si>
-    <t>135518918</t>
-  </si>
-  <si>
-    <t>135518927</t>
-  </si>
-  <si>
-    <t>135518973</t>
-  </si>
-  <si>
-    <t>135519031</t>
-  </si>
-  <si>
-    <t>135519036</t>
-  </si>
-  <si>
-    <t>135519177</t>
-  </si>
-  <si>
-    <t>135519598</t>
-  </si>
-  <si>
-    <t>135519626</t>
-  </si>
-  <si>
-    <t>135519873</t>
-  </si>
-  <si>
-    <t>135519957</t>
-  </si>
-  <si>
-    <t>135519960</t>
-  </si>
-  <si>
-    <t>135520147</t>
-  </si>
-  <si>
-    <t>135520403</t>
-  </si>
-  <si>
-    <t>135520409</t>
-  </si>
-  <si>
-    <t>135520535</t>
-  </si>
-  <si>
-    <t>135520683</t>
-  </si>
-  <si>
-    <t>135520703</t>
-  </si>
-  <si>
-    <t>135520985</t>
-  </si>
-  <si>
-    <t>135521033</t>
-  </si>
-  <si>
-    <t>135521091</t>
-  </si>
-  <si>
-    <t>135521457</t>
-  </si>
-  <si>
-    <t>135521501</t>
-  </si>
-  <si>
-    <t>135521511</t>
-  </si>
-  <si>
-    <t>135521527</t>
-  </si>
-  <si>
-    <t>135521872</t>
-  </si>
-  <si>
-    <t>135521966</t>
-  </si>
-  <si>
-    <t>135522141</t>
-  </si>
-  <si>
-    <t>135522224</t>
-  </si>
-  <si>
-    <t>135522298</t>
-  </si>
-  <si>
-    <t>135522368</t>
-  </si>
-  <si>
-    <t>135522409</t>
-  </si>
-  <si>
-    <t>135522551</t>
-  </si>
-  <si>
-    <t>135522709</t>
-  </si>
-  <si>
-    <t>135523012</t>
-  </si>
-  <si>
-    <t>135523017</t>
-  </si>
-  <si>
-    <t>135523174</t>
-  </si>
-  <si>
-    <t>135523236</t>
-  </si>
-  <si>
-    <t>135523245</t>
-  </si>
-  <si>
-    <t>135523324</t>
-  </si>
-  <si>
-    <t>135523684</t>
-  </si>
-  <si>
-    <t>135523704</t>
-  </si>
-  <si>
-    <t>135523741</t>
-  </si>
-  <si>
-    <t>135523774</t>
-  </si>
-  <si>
-    <t>135523780</t>
-  </si>
-  <si>
-    <t>135523950</t>
-  </si>
-  <si>
-    <t>135524160</t>
-  </si>
-  <si>
-    <t>135524202</t>
-  </si>
-  <si>
-    <t>135524288</t>
-  </si>
-  <si>
-    <t>135524756</t>
-  </si>
-  <si>
-    <t>135524843</t>
-  </si>
-  <si>
-    <t>135525028</t>
-  </si>
-  <si>
-    <t>135525101</t>
-  </si>
-  <si>
-    <t>135525159</t>
-  </si>
-  <si>
-    <t>135525161</t>
-  </si>
-  <si>
-    <t>135525215</t>
-  </si>
-  <si>
-    <t>135525365</t>
-  </si>
-  <si>
-    <t>135525451</t>
-  </si>
-  <si>
-    <t>135525588</t>
-  </si>
-  <si>
-    <t>135525680</t>
-  </si>
-  <si>
-    <t>135525882</t>
-  </si>
-  <si>
-    <t>135526011</t>
-  </si>
-  <si>
-    <t>135526724</t>
-  </si>
-  <si>
-    <t>135527308</t>
-  </si>
-  <si>
-    <t>135527400</t>
-  </si>
-  <si>
-    <t>135527444</t>
-  </si>
-  <si>
-    <t>135527562</t>
-  </si>
-  <si>
-    <t>135527563</t>
-  </si>
-  <si>
-    <t>135527651</t>
-  </si>
-  <si>
-    <t>135527697</t>
-  </si>
-  <si>
-    <t>135527753</t>
-  </si>
-  <si>
-    <t>135527777</t>
+    <t>130411451</t>
+  </si>
+  <si>
+    <t>130660565</t>
+  </si>
+  <si>
+    <t>130790983</t>
+  </si>
+  <si>
+    <t>130799874</t>
+  </si>
+  <si>
+    <t>131421609</t>
+  </si>
+  <si>
+    <t>131631275</t>
+  </si>
+  <si>
+    <t>131916709</t>
+  </si>
+  <si>
+    <t>131945415</t>
+  </si>
+  <si>
+    <t>132716806</t>
+  </si>
+  <si>
+    <t>133799869</t>
+  </si>
+  <si>
+    <t>134692584</t>
+  </si>
+  <si>
+    <t>135032202</t>
+  </si>
+  <si>
+    <t>135528552</t>
+  </si>
+  <si>
+    <t>135528608</t>
+  </si>
+  <si>
+    <t>135528644</t>
+  </si>
+  <si>
+    <t>135528861</t>
+  </si>
+  <si>
+    <t>135528998</t>
+  </si>
+  <si>
+    <t>135529479</t>
+  </si>
+  <si>
+    <t>135529871</t>
+  </si>
+  <si>
+    <t>135530099</t>
+  </si>
+  <si>
+    <t>135530182</t>
+  </si>
+  <si>
+    <t>135530258</t>
+  </si>
+  <si>
+    <t>135530396</t>
+  </si>
+  <si>
+    <t>135530581</t>
+  </si>
+  <si>
+    <t>135530799</t>
+  </si>
+  <si>
+    <t>135530876</t>
+  </si>
+  <si>
+    <t>135531035</t>
+  </si>
+  <si>
+    <t>135531262</t>
+  </si>
+  <si>
+    <t>135531402</t>
+  </si>
+  <si>
+    <t>135532149</t>
+  </si>
+  <si>
+    <t>135532411</t>
+  </si>
+  <si>
+    <t>135532438</t>
+  </si>
+  <si>
+    <t>135532588</t>
+  </si>
+  <si>
+    <t>135532787</t>
+  </si>
+  <si>
+    <t>135533001</t>
+  </si>
+  <si>
+    <t>135533050</t>
+  </si>
+  <si>
+    <t>135533133</t>
+  </si>
+  <si>
+    <t>135533142</t>
+  </si>
+  <si>
+    <t>135533249</t>
+  </si>
+  <si>
+    <t>135533311</t>
+  </si>
+  <si>
+    <t>135533680</t>
+  </si>
+  <si>
+    <t>135534313</t>
+  </si>
+  <si>
+    <t>135534403</t>
+  </si>
+  <si>
+    <t>135534438</t>
+  </si>
+  <si>
+    <t>135534460</t>
+  </si>
+  <si>
+    <t>135534532</t>
+  </si>
+  <si>
+    <t>135534712</t>
+  </si>
+  <si>
+    <t>135535116</t>
+  </si>
+  <si>
+    <t>135535217</t>
+  </si>
+  <si>
+    <t>135535236</t>
+  </si>
+  <si>
+    <t>135535259</t>
+  </si>
+  <si>
+    <t>135535598</t>
+  </si>
+  <si>
+    <t>135535656</t>
+  </si>
+  <si>
+    <t>135535725</t>
+  </si>
+  <si>
+    <t>135535906</t>
+  </si>
+  <si>
+    <t>135536219</t>
+  </si>
+  <si>
+    <t>135536356</t>
+  </si>
+  <si>
+    <t>135536479</t>
+  </si>
+  <si>
+    <t>135536496</t>
+  </si>
+  <si>
+    <t>135536526</t>
+  </si>
+  <si>
+    <t>135536549</t>
+  </si>
+  <si>
+    <t>135536571</t>
+  </si>
+  <si>
+    <t>135537184</t>
+  </si>
+  <si>
+    <t>135537211</t>
+  </si>
+  <si>
+    <t>135537508</t>
+  </si>
+  <si>
+    <t>135537575</t>
+  </si>
+  <si>
+    <t>135537657</t>
+  </si>
+  <si>
+    <t>135537896</t>
+  </si>
+  <si>
+    <t>135538097</t>
+  </si>
+  <si>
+    <t>135538263</t>
+  </si>
+  <si>
+    <t>135540081</t>
+  </si>
+  <si>
+    <t>135540086</t>
+  </si>
+  <si>
+    <t>135540208</t>
+  </si>
+  <si>
+    <t>135540406</t>
+  </si>
+  <si>
+    <t>135540877</t>
+  </si>
+  <si>
+    <t>135540925</t>
+  </si>
+  <si>
+    <t>135541132</t>
+  </si>
+  <si>
+    <t>135541164</t>
+  </si>
+  <si>
+    <t>135541169</t>
+  </si>
+  <si>
+    <t>135541292</t>
+  </si>
+  <si>
+    <t>135541453</t>
+  </si>
+  <si>
+    <t>135541511</t>
+  </si>
+  <si>
+    <t>135541535</t>
+  </si>
+  <si>
+    <t>135541656</t>
+  </si>
+  <si>
+    <t>135541916</t>
+  </si>
+  <si>
+    <t>135542012</t>
+  </si>
+  <si>
+    <t>135542100</t>
+  </si>
+  <si>
+    <t>135542557</t>
+  </si>
+  <si>
+    <t>135542789</t>
+  </si>
+  <si>
+    <t>135542852</t>
+  </si>
+  <si>
+    <t>135542874</t>
+  </si>
+  <si>
+    <t>135542911</t>
+  </si>
+  <si>
+    <t>135543048</t>
+  </si>
+  <si>
+    <t>135543570</t>
+  </si>
+  <si>
+    <t>135543647</t>
+  </si>
+  <si>
+    <t>135543886</t>
+  </si>
+  <si>
+    <t>135544009</t>
+  </si>
+  <si>
+    <t>135544066</t>
+  </si>
+  <si>
+    <t>135544159</t>
+  </si>
+  <si>
+    <t>135544432</t>
+  </si>
+  <si>
+    <t>135544584</t>
+  </si>
+  <si>
+    <t>135544612</t>
+  </si>
+  <si>
+    <t>135544628</t>
+  </si>
+  <si>
+    <t>135544931</t>
+  </si>
+  <si>
+    <t>135545186</t>
+  </si>
+  <si>
+    <t>135545256</t>
+  </si>
+  <si>
+    <t>135545532</t>
+  </si>
+  <si>
+    <t>135545659</t>
+  </si>
+  <si>
+    <t>135545670</t>
+  </si>
+  <si>
+    <t>135545836</t>
+  </si>
+  <si>
+    <t>135545963</t>
+  </si>
+  <si>
+    <t>135545974</t>
+  </si>
+  <si>
+    <t>135546013</t>
+  </si>
+  <si>
+    <t>135546055</t>
+  </si>
+  <si>
+    <t>135546103</t>
+  </si>
+  <si>
+    <t>135546207</t>
+  </si>
+  <si>
+    <t>135546302</t>
+  </si>
+  <si>
+    <t>135546351</t>
+  </si>
+  <si>
+    <t>135546387</t>
+  </si>
+  <si>
+    <t>135546409</t>
+  </si>
+  <si>
+    <t>135546476</t>
+  </si>
+  <si>
+    <t>135546672</t>
+  </si>
+  <si>
+    <t>135546856</t>
+  </si>
+  <si>
+    <t>135546941</t>
+  </si>
+  <si>
+    <t>135547315</t>
+  </si>
+  <si>
+    <t>135547480</t>
+  </si>
+  <si>
+    <t>135547529</t>
+  </si>
+  <si>
+    <t>135547618</t>
+  </si>
+  <si>
+    <t>135547738</t>
+  </si>
+  <si>
+    <t>135547850</t>
+  </si>
+  <si>
+    <t>135547879</t>
+  </si>
+  <si>
+    <t>135547919</t>
+  </si>
+  <si>
+    <t>135547953</t>
+  </si>
+  <si>
+    <t>135548033</t>
+  </si>
+  <si>
+    <t>135548051</t>
+  </si>
+  <si>
+    <t>135548060</t>
+  </si>
+  <si>
+    <t>135548063</t>
+  </si>
+  <si>
+    <t>135548147</t>
+  </si>
+  <si>
+    <t>135548240</t>
+  </si>
+  <si>
+    <t>135548299</t>
+  </si>
+  <si>
+    <t>135548694</t>
+  </si>
+  <si>
+    <t>135548719</t>
+  </si>
+  <si>
+    <t>135548787</t>
+  </si>
+  <si>
+    <t>135548975</t>
+  </si>
+  <si>
+    <t>135549652</t>
+  </si>
+  <si>
+    <t>135549880</t>
+  </si>
+  <si>
+    <t>135550079</t>
+  </si>
+  <si>
+    <t>135550094</t>
+  </si>
+  <si>
+    <t>135550095</t>
+  </si>
+  <si>
+    <t>135550136</t>
+  </si>
+  <si>
+    <t>135550390</t>
+  </si>
+  <si>
+    <t>135550457</t>
+  </si>
+  <si>
+    <t>135550460</t>
+  </si>
+  <si>
+    <t>135550536</t>
   </si>
 </sst>
 </file>
@@ -882,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2497,6 +2524,78 @@
         <v>4</v>
       </c>
     </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C146" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5AB171-40E9-4D2A-AB97-730A20784E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502EEDEB-E14B-40A0-8C81-D30D45D2CBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="843">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,1903 +45,2518 @@
     <t>.</t>
   </si>
   <si>
-    <t>130741053</t>
-  </si>
-  <si>
-    <t>130873466</t>
-  </si>
-  <si>
-    <t>131006390</t>
-  </si>
-  <si>
     <t>131013144</t>
   </si>
   <si>
-    <t>131147005</t>
-  </si>
-  <si>
     <t>131249640</t>
   </si>
   <si>
-    <t>131278259</t>
-  </si>
-  <si>
-    <t>131315625</t>
-  </si>
-  <si>
-    <t>131471929</t>
-  </si>
-  <si>
-    <t>131480728</t>
-  </si>
-  <si>
-    <t>131573904</t>
-  </si>
-  <si>
-    <t>131670437</t>
-  </si>
-  <si>
-    <t>131683859</t>
-  </si>
-  <si>
-    <t>131852114</t>
-  </si>
-  <si>
-    <t>131980325</t>
-  </si>
-  <si>
-    <t>131987902</t>
-  </si>
-  <si>
-    <t>132510262</t>
-  </si>
-  <si>
-    <t>132602912</t>
-  </si>
-  <si>
-    <t>132846147</t>
-  </si>
-  <si>
-    <t>132877918</t>
-  </si>
-  <si>
-    <t>132981302</t>
-  </si>
-  <si>
     <t>133061172</t>
   </si>
   <si>
-    <t>133206590</t>
-  </si>
-  <si>
-    <t>133249266</t>
-  </si>
-  <si>
-    <t>133274395</t>
-  </si>
-  <si>
-    <t>133289669</t>
-  </si>
-  <si>
-    <t>133339295</t>
-  </si>
-  <si>
-    <t>133492881</t>
-  </si>
-  <si>
-    <t>133531556</t>
-  </si>
-  <si>
-    <t>133632163</t>
-  </si>
-  <si>
-    <t>133639412</t>
-  </si>
-  <si>
-    <t>133983147</t>
-  </si>
-  <si>
-    <t>134049197</t>
-  </si>
-  <si>
-    <t>134104954</t>
-  </si>
-  <si>
-    <t>134138112</t>
-  </si>
-  <si>
-    <t>134242899</t>
-  </si>
-  <si>
-    <t>134527755</t>
-  </si>
-  <si>
-    <t>134555668</t>
-  </si>
-  <si>
-    <t>134562336</t>
-  </si>
-  <si>
-    <t>135035924</t>
-  </si>
-  <si>
-    <t>135046237</t>
-  </si>
-  <si>
-    <t>135079687</t>
-  </si>
-  <si>
-    <t>135116527</t>
-  </si>
-  <si>
-    <t>135550583</t>
-  </si>
-  <si>
-    <t>135550740</t>
-  </si>
-  <si>
-    <t>135550882</t>
-  </si>
-  <si>
-    <t>135551120</t>
-  </si>
-  <si>
-    <t>135551140</t>
-  </si>
-  <si>
-    <t>135551236</t>
-  </si>
-  <si>
-    <t>135551256</t>
-  </si>
-  <si>
-    <t>135551380</t>
-  </si>
-  <si>
-    <t>135551382</t>
-  </si>
-  <si>
-    <t>135551597</t>
-  </si>
-  <si>
-    <t>135551840</t>
-  </si>
-  <si>
-    <t>135552728</t>
-  </si>
-  <si>
-    <t>135552732</t>
-  </si>
-  <si>
-    <t>135552797</t>
-  </si>
-  <si>
-    <t>135553216</t>
-  </si>
-  <si>
-    <t>135553524</t>
-  </si>
-  <si>
-    <t>135553910</t>
-  </si>
-  <si>
-    <t>135553918</t>
-  </si>
-  <si>
-    <t>135554301</t>
-  </si>
-  <si>
-    <t>135554417</t>
-  </si>
-  <si>
-    <t>135554637</t>
-  </si>
-  <si>
-    <t>135554745</t>
-  </si>
-  <si>
-    <t>135554746</t>
-  </si>
-  <si>
-    <t>135555021</t>
-  </si>
-  <si>
-    <t>135555024</t>
-  </si>
-  <si>
-    <t>135555047</t>
-  </si>
-  <si>
-    <t>135555191</t>
-  </si>
-  <si>
-    <t>135555373</t>
-  </si>
-  <si>
-    <t>135555492</t>
-  </si>
-  <si>
-    <t>135555622</t>
-  </si>
-  <si>
-    <t>135555702</t>
-  </si>
-  <si>
-    <t>135555882</t>
-  </si>
-  <si>
-    <t>135556067</t>
-  </si>
-  <si>
-    <t>135556076</t>
-  </si>
-  <si>
-    <t>135556210</t>
-  </si>
-  <si>
-    <t>135556381</t>
-  </si>
-  <si>
-    <t>135556669</t>
-  </si>
-  <si>
-    <t>135556824</t>
-  </si>
-  <si>
-    <t>135556990</t>
-  </si>
-  <si>
-    <t>135557483</t>
-  </si>
-  <si>
-    <t>135557516</t>
-  </si>
-  <si>
-    <t>135557537</t>
-  </si>
-  <si>
-    <t>135557555</t>
-  </si>
-  <si>
-    <t>135557975</t>
-  </si>
-  <si>
-    <t>135558090</t>
-  </si>
-  <si>
-    <t>135558264</t>
-  </si>
-  <si>
-    <t>135558379</t>
-  </si>
-  <si>
-    <t>135558901</t>
-  </si>
-  <si>
-    <t>135558908</t>
-  </si>
-  <si>
-    <t>135558939</t>
-  </si>
-  <si>
-    <t>135558993</t>
-  </si>
-  <si>
-    <t>135559249</t>
-  </si>
-  <si>
-    <t>135559323</t>
-  </si>
-  <si>
-    <t>135559426</t>
-  </si>
-  <si>
-    <t>135559536</t>
-  </si>
-  <si>
-    <t>135559786</t>
-  </si>
-  <si>
-    <t>135559864</t>
-  </si>
-  <si>
-    <t>135559902</t>
-  </si>
-  <si>
-    <t>135559993</t>
-  </si>
-  <si>
-    <t>135560599</t>
-  </si>
-  <si>
-    <t>135560608</t>
-  </si>
-  <si>
-    <t>135560748</t>
-  </si>
-  <si>
-    <t>135560824</t>
-  </si>
-  <si>
-    <t>135560854</t>
-  </si>
-  <si>
-    <t>135560991</t>
-  </si>
-  <si>
-    <t>135561209</t>
-  </si>
-  <si>
-    <t>135561475</t>
-  </si>
-  <si>
-    <t>135561568</t>
-  </si>
-  <si>
-    <t>135561761</t>
-  </si>
-  <si>
-    <t>135562057</t>
-  </si>
-  <si>
-    <t>135562265</t>
-  </si>
-  <si>
-    <t>135562378</t>
-  </si>
-  <si>
-    <t>135562779</t>
-  </si>
-  <si>
-    <t>135562880</t>
-  </si>
-  <si>
-    <t>135563347</t>
-  </si>
-  <si>
-    <t>135563669</t>
-  </si>
-  <si>
-    <t>135563887</t>
-  </si>
-  <si>
-    <t>135564058</t>
-  </si>
-  <si>
-    <t>135564155</t>
-  </si>
-  <si>
-    <t>135564345</t>
-  </si>
-  <si>
-    <t>135565016</t>
-  </si>
-  <si>
-    <t>135565117</t>
-  </si>
-  <si>
-    <t>135565264</t>
-  </si>
-  <si>
-    <t>135565435</t>
-  </si>
-  <si>
-    <t>135565831</t>
-  </si>
-  <si>
-    <t>135565886</t>
-  </si>
-  <si>
-    <t>135566394</t>
-  </si>
-  <si>
-    <t>135566497</t>
-  </si>
-  <si>
-    <t>135566608</t>
-  </si>
-  <si>
-    <t>135566831</t>
-  </si>
-  <si>
-    <t>135566945</t>
-  </si>
-  <si>
-    <t>135566955</t>
-  </si>
-  <si>
-    <t>135567072</t>
-  </si>
-  <si>
-    <t>135567327</t>
-  </si>
-  <si>
-    <t>135567566</t>
-  </si>
-  <si>
-    <t>135567668</t>
-  </si>
-  <si>
-    <t>135567690</t>
-  </si>
-  <si>
-    <t>135567693</t>
-  </si>
-  <si>
-    <t>135567806</t>
-  </si>
-  <si>
-    <t>135568109</t>
-  </si>
-  <si>
-    <t>135568216</t>
-  </si>
-  <si>
-    <t>135568282</t>
-  </si>
-  <si>
-    <t>135568289</t>
-  </si>
-  <si>
-    <t>135568334</t>
-  </si>
-  <si>
-    <t>135568395</t>
-  </si>
-  <si>
-    <t>135568522</t>
-  </si>
-  <si>
-    <t>135568537</t>
-  </si>
-  <si>
-    <t>135568599</t>
-  </si>
-  <si>
-    <t>135568721</t>
-  </si>
-  <si>
-    <t>135569161</t>
-  </si>
-  <si>
-    <t>135569172</t>
-  </si>
-  <si>
-    <t>135569243</t>
-  </si>
-  <si>
-    <t>135569244</t>
-  </si>
-  <si>
-    <t>135569458</t>
-  </si>
-  <si>
-    <t>135569673</t>
-  </si>
-  <si>
-    <t>135570389</t>
-  </si>
-  <si>
-    <t>135570418</t>
-  </si>
-  <si>
-    <t>135570565</t>
-  </si>
-  <si>
-    <t>135571564</t>
-  </si>
-  <si>
-    <t>135571624</t>
-  </si>
-  <si>
-    <t>135571855</t>
-  </si>
-  <si>
-    <t>135571908</t>
-  </si>
-  <si>
-    <t>135571995</t>
-  </si>
-  <si>
-    <t>135572190</t>
-  </si>
-  <si>
-    <t>135572205</t>
-  </si>
-  <si>
-    <t>135572288</t>
-  </si>
-  <si>
-    <t>135572773</t>
-  </si>
-  <si>
-    <t>135572786</t>
-  </si>
-  <si>
-    <t>135572983</t>
-  </si>
-  <si>
-    <t>135573125</t>
-  </si>
-  <si>
-    <t>135573621</t>
-  </si>
-  <si>
-    <t>135573644</t>
-  </si>
-  <si>
-    <t>135573843</t>
-  </si>
-  <si>
-    <t>135573951</t>
-  </si>
-  <si>
-    <t>135573997</t>
-  </si>
-  <si>
-    <t>135574107</t>
-  </si>
-  <si>
-    <t>135574206</t>
-  </si>
-  <si>
-    <t>135574217</t>
-  </si>
-  <si>
-    <t>135574309</t>
-  </si>
-  <si>
-    <t>135574750</t>
-  </si>
-  <si>
-    <t>135575052</t>
-  </si>
-  <si>
-    <t>135575335</t>
-  </si>
-  <si>
-    <t>135575383</t>
-  </si>
-  <si>
-    <t>135575548</t>
-  </si>
-  <si>
-    <t>135575635</t>
-  </si>
-  <si>
-    <t>135575841</t>
-  </si>
-  <si>
-    <t>135576139</t>
-  </si>
-  <si>
-    <t>135576381</t>
-  </si>
-  <si>
-    <t>135576394</t>
-  </si>
-  <si>
-    <t>135576441</t>
-  </si>
-  <si>
-    <t>135576598</t>
-  </si>
-  <si>
-    <t>135576912</t>
-  </si>
-  <si>
-    <t>135577029</t>
-  </si>
-  <si>
-    <t>135577118</t>
-  </si>
-  <si>
-    <t>135577563</t>
-  </si>
-  <si>
-    <t>135577594</t>
-  </si>
-  <si>
-    <t>135577698</t>
-  </si>
-  <si>
-    <t>135577714</t>
-  </si>
-  <si>
-    <t>135577781</t>
-  </si>
-  <si>
-    <t>135578161</t>
-  </si>
-  <si>
-    <t>135578457</t>
-  </si>
-  <si>
-    <t>135578614</t>
-  </si>
-  <si>
-    <t>135578673</t>
-  </si>
-  <si>
-    <t>135578681</t>
-  </si>
-  <si>
-    <t>135578783</t>
-  </si>
-  <si>
-    <t>135579182</t>
-  </si>
-  <si>
-    <t>135579540</t>
-  </si>
-  <si>
-    <t>135579568</t>
-  </si>
-  <si>
-    <t>135579770</t>
-  </si>
-  <si>
-    <t>135579868</t>
-  </si>
-  <si>
-    <t>135579903</t>
-  </si>
-  <si>
-    <t>135579929</t>
-  </si>
-  <si>
-    <t>135580149</t>
-  </si>
-  <si>
-    <t>135580187</t>
-  </si>
-  <si>
-    <t>135580225</t>
-  </si>
-  <si>
-    <t>135580452</t>
-  </si>
-  <si>
-    <t>135580490</t>
-  </si>
-  <si>
-    <t>135580523</t>
-  </si>
-  <si>
-    <t>135580572</t>
-  </si>
-  <si>
-    <t>135580585</t>
-  </si>
-  <si>
-    <t>135580745</t>
-  </si>
-  <si>
-    <t>135580835</t>
-  </si>
-  <si>
-    <t>135580872</t>
-  </si>
-  <si>
-    <t>135580925</t>
-  </si>
-  <si>
-    <t>135581038</t>
-  </si>
-  <si>
-    <t>135581255</t>
-  </si>
-  <si>
-    <t>135581456</t>
-  </si>
-  <si>
-    <t>135581477</t>
-  </si>
-  <si>
-    <t>135581510</t>
-  </si>
-  <si>
-    <t>135581683</t>
-  </si>
-  <si>
-    <t>135581819</t>
-  </si>
-  <si>
-    <t>135582125</t>
-  </si>
-  <si>
-    <t>135582244</t>
-  </si>
-  <si>
-    <t>135582252</t>
-  </si>
-  <si>
-    <t>135582287</t>
-  </si>
-  <si>
-    <t>135582301</t>
-  </si>
-  <si>
-    <t>135582383</t>
-  </si>
-  <si>
-    <t>135582402</t>
-  </si>
-  <si>
-    <t>135582592</t>
-  </si>
-  <si>
-    <t>135582943</t>
-  </si>
-  <si>
-    <t>135583055</t>
-  </si>
-  <si>
-    <t>135583088</t>
-  </si>
-  <si>
-    <t>135583295</t>
-  </si>
-  <si>
-    <t>135583485</t>
-  </si>
-  <si>
-    <t>135583587</t>
-  </si>
-  <si>
-    <t>135583746</t>
-  </si>
-  <si>
-    <t>135583857</t>
-  </si>
-  <si>
-    <t>135583880</t>
-  </si>
-  <si>
-    <t>135584167</t>
-  </si>
-  <si>
-    <t>135584263</t>
-  </si>
-  <si>
-    <t>135584316</t>
-  </si>
-  <si>
-    <t>135584630</t>
-  </si>
-  <si>
-    <t>135585155</t>
-  </si>
-  <si>
-    <t>135585387</t>
-  </si>
-  <si>
-    <t>135585620</t>
-  </si>
-  <si>
-    <t>135585662</t>
-  </si>
-  <si>
-    <t>135585844</t>
-  </si>
-  <si>
-    <t>135585936</t>
-  </si>
-  <si>
-    <t>135585994</t>
-  </si>
-  <si>
-    <t>135586091</t>
-  </si>
-  <si>
-    <t>135586262</t>
-  </si>
-  <si>
-    <t>135586704</t>
-  </si>
-  <si>
-    <t>135586874</t>
-  </si>
-  <si>
-    <t>135586910</t>
-  </si>
-  <si>
-    <t>135586915</t>
-  </si>
-  <si>
-    <t>135587133</t>
-  </si>
-  <si>
-    <t>135587277</t>
-  </si>
-  <si>
-    <t>135587300</t>
-  </si>
-  <si>
-    <t>135587576</t>
-  </si>
-  <si>
-    <t>135587601</t>
-  </si>
-  <si>
-    <t>135587608</t>
-  </si>
-  <si>
-    <t>135587650</t>
-  </si>
-  <si>
-    <t>135587740</t>
-  </si>
-  <si>
-    <t>135587855</t>
-  </si>
-  <si>
-    <t>135587889</t>
-  </si>
-  <si>
-    <t>135587931</t>
-  </si>
-  <si>
-    <t>135587983</t>
-  </si>
-  <si>
-    <t>135587989</t>
-  </si>
-  <si>
-    <t>135587990</t>
-  </si>
-  <si>
-    <t>135588081</t>
-  </si>
-  <si>
-    <t>135588088</t>
-  </si>
-  <si>
-    <t>135588254</t>
-  </si>
-  <si>
-    <t>135588257</t>
-  </si>
-  <si>
-    <t>135588577</t>
-  </si>
-  <si>
-    <t>135588866</t>
-  </si>
-  <si>
-    <t>135588931</t>
-  </si>
-  <si>
-    <t>135589012</t>
-  </si>
-  <si>
-    <t>135589090</t>
-  </si>
-  <si>
-    <t>135589202</t>
-  </si>
-  <si>
-    <t>135589224</t>
-  </si>
-  <si>
-    <t>135589420</t>
-  </si>
-  <si>
-    <t>135589628</t>
-  </si>
-  <si>
-    <t>135589657</t>
-  </si>
-  <si>
-    <t>135589931</t>
-  </si>
-  <si>
-    <t>135590066</t>
-  </si>
-  <si>
-    <t>135590095</t>
-  </si>
-  <si>
-    <t>135590241</t>
-  </si>
-  <si>
-    <t>135590349</t>
-  </si>
-  <si>
-    <t>135590360</t>
-  </si>
-  <si>
-    <t>135590503</t>
-  </si>
-  <si>
-    <t>135590590</t>
-  </si>
-  <si>
-    <t>135590675</t>
-  </si>
-  <si>
-    <t>135590753</t>
-  </si>
-  <si>
-    <t>135590873</t>
-  </si>
-  <si>
-    <t>135590976</t>
-  </si>
-  <si>
-    <t>135591150</t>
-  </si>
-  <si>
-    <t>135591154</t>
-  </si>
-  <si>
-    <t>135591247</t>
-  </si>
-  <si>
-    <t>135591397</t>
-  </si>
-  <si>
-    <t>135591444</t>
-  </si>
-  <si>
-    <t>135591450</t>
-  </si>
-  <si>
-    <t>135591467</t>
-  </si>
-  <si>
-    <t>135591513</t>
-  </si>
-  <si>
-    <t>135591550</t>
-  </si>
-  <si>
-    <t>135591631</t>
-  </si>
-  <si>
-    <t>135591644</t>
-  </si>
-  <si>
-    <t>135592003</t>
-  </si>
-  <si>
-    <t>135593368</t>
-  </si>
-  <si>
-    <t>135593617</t>
-  </si>
-  <si>
-    <t>135593649</t>
-  </si>
-  <si>
-    <t>135593975</t>
-  </si>
-  <si>
-    <t>135594008</t>
-  </si>
-  <si>
-    <t>135594022</t>
-  </si>
-  <si>
-    <t>135594023</t>
-  </si>
-  <si>
-    <t>135594032</t>
-  </si>
-  <si>
-    <t>135594893</t>
-  </si>
-  <si>
-    <t>135595061</t>
-  </si>
-  <si>
-    <t>135595281</t>
-  </si>
-  <si>
-    <t>135595349</t>
-  </si>
-  <si>
-    <t>135595506</t>
-  </si>
-  <si>
-    <t>135595715</t>
-  </si>
-  <si>
-    <t>135595813</t>
-  </si>
-  <si>
-    <t>135595966</t>
-  </si>
-  <si>
-    <t>135596034</t>
-  </si>
-  <si>
-    <t>135596356</t>
-  </si>
-  <si>
-    <t>135596420</t>
-  </si>
-  <si>
-    <t>135596601</t>
-  </si>
-  <si>
-    <t>135597063</t>
-  </si>
-  <si>
-    <t>135597098</t>
-  </si>
-  <si>
-    <t>135597296</t>
-  </si>
-  <si>
-    <t>135597382</t>
-  </si>
-  <si>
-    <t>135597391</t>
-  </si>
-  <si>
-    <t>135597397</t>
-  </si>
-  <si>
-    <t>135597436</t>
-  </si>
-  <si>
-    <t>135597475</t>
-  </si>
-  <si>
-    <t>135597491</t>
-  </si>
-  <si>
-    <t>135597694</t>
-  </si>
-  <si>
-    <t>135597909</t>
-  </si>
-  <si>
-    <t>135598064</t>
-  </si>
-  <si>
-    <t>135598177</t>
-  </si>
-  <si>
-    <t>135598587</t>
-  </si>
-  <si>
-    <t>135598668</t>
-  </si>
-  <si>
-    <t>135598770</t>
-  </si>
-  <si>
-    <t>135599365</t>
-  </si>
-  <si>
-    <t>135599618</t>
-  </si>
-  <si>
-    <t>135599788</t>
-  </si>
-  <si>
-    <t>135599826</t>
-  </si>
-  <si>
-    <t>135599903</t>
-  </si>
-  <si>
-    <t>135599978</t>
-  </si>
-  <si>
-    <t>135599979</t>
-  </si>
-  <si>
-    <t>135600015</t>
-  </si>
-  <si>
-    <t>135600240</t>
-  </si>
-  <si>
-    <t>135600280</t>
-  </si>
-  <si>
-    <t>135600281</t>
-  </si>
-  <si>
-    <t>135600382</t>
-  </si>
-  <si>
-    <t>135600434</t>
-  </si>
-  <si>
-    <t>135600446</t>
-  </si>
-  <si>
-    <t>135600747</t>
-  </si>
-  <si>
-    <t>135600799</t>
-  </si>
-  <si>
-    <t>135601120</t>
-  </si>
-  <si>
-    <t>135601241</t>
-  </si>
-  <si>
-    <t>135601317</t>
-  </si>
-  <si>
-    <t>135601330</t>
-  </si>
-  <si>
-    <t>135601362</t>
-  </si>
-  <si>
-    <t>135601372</t>
-  </si>
-  <si>
-    <t>135601446</t>
-  </si>
-  <si>
-    <t>135601532</t>
-  </si>
-  <si>
-    <t>135601676</t>
-  </si>
-  <si>
-    <t>135601764</t>
-  </si>
-  <si>
-    <t>135601783</t>
-  </si>
-  <si>
-    <t>135601805</t>
-  </si>
-  <si>
-    <t>135601983</t>
-  </si>
-  <si>
-    <t>135602171</t>
-  </si>
-  <si>
-    <t>135602334</t>
-  </si>
-  <si>
-    <t>135602412</t>
-  </si>
-  <si>
-    <t>135602754</t>
-  </si>
-  <si>
-    <t>135603422</t>
-  </si>
-  <si>
-    <t>135603473</t>
-  </si>
-  <si>
-    <t>135603615</t>
-  </si>
-  <si>
-    <t>135603641</t>
-  </si>
-  <si>
-    <t>135603670</t>
-  </si>
-  <si>
-    <t>135603898</t>
-  </si>
-  <si>
-    <t>135604079</t>
-  </si>
-  <si>
-    <t>135604113</t>
-  </si>
-  <si>
-    <t>135604182</t>
-  </si>
-  <si>
-    <t>135604330</t>
-  </si>
-  <si>
-    <t>135604430</t>
-  </si>
-  <si>
-    <t>135604524</t>
-  </si>
-  <si>
-    <t>135604530</t>
-  </si>
-  <si>
-    <t>135604742</t>
-  </si>
-  <si>
-    <t>135604749</t>
-  </si>
-  <si>
-    <t>135604947</t>
-  </si>
-  <si>
-    <t>135605004</t>
-  </si>
-  <si>
-    <t>135605227</t>
-  </si>
-  <si>
-    <t>135605246</t>
-  </si>
-  <si>
-    <t>135605256</t>
-  </si>
-  <si>
-    <t>135605533</t>
-  </si>
-  <si>
-    <t>135605567</t>
-  </si>
-  <si>
-    <t>135605858</t>
-  </si>
-  <si>
-    <t>135605891</t>
-  </si>
-  <si>
-    <t>135605893</t>
-  </si>
-  <si>
-    <t>135606336</t>
-  </si>
-  <si>
-    <t>135606465</t>
-  </si>
-  <si>
-    <t>135606632</t>
-  </si>
-  <si>
-    <t>135606920</t>
-  </si>
-  <si>
-    <t>135606921</t>
-  </si>
-  <si>
-    <t>135607208</t>
-  </si>
-  <si>
-    <t>135607285</t>
-  </si>
-  <si>
-    <t>135607369</t>
-  </si>
-  <si>
-    <t>135607449</t>
-  </si>
-  <si>
-    <t>135607532</t>
-  </si>
-  <si>
-    <t>135607838</t>
-  </si>
-  <si>
-    <t>135607840</t>
-  </si>
-  <si>
-    <t>135608043</t>
-  </si>
-  <si>
-    <t>135608054</t>
-  </si>
-  <si>
-    <t>135608494</t>
-  </si>
-  <si>
-    <t>135608509</t>
-  </si>
-  <si>
-    <t>135608589</t>
-  </si>
-  <si>
-    <t>135608729</t>
-  </si>
-  <si>
-    <t>135608794</t>
-  </si>
-  <si>
-    <t>135608805</t>
-  </si>
-  <si>
-    <t>135608845</t>
-  </si>
-  <si>
-    <t>135608849</t>
-  </si>
-  <si>
-    <t>135608991</t>
-  </si>
-  <si>
-    <t>135609206</t>
-  </si>
-  <si>
-    <t>135609323</t>
-  </si>
-  <si>
-    <t>135609694</t>
-  </si>
-  <si>
-    <t>135609718</t>
-  </si>
-  <si>
-    <t>135610181</t>
-  </si>
-  <si>
-    <t>135610229</t>
-  </si>
-  <si>
-    <t>135610263</t>
-  </si>
-  <si>
-    <t>135610308</t>
-  </si>
-  <si>
-    <t>135610325</t>
-  </si>
-  <si>
-    <t>135610378</t>
-  </si>
-  <si>
-    <t>135610381</t>
-  </si>
-  <si>
-    <t>135610465</t>
-  </si>
-  <si>
-    <t>135610626</t>
-  </si>
-  <si>
-    <t>135610793</t>
-  </si>
-  <si>
-    <t>135610908</t>
-  </si>
-  <si>
-    <t>135610949</t>
-  </si>
-  <si>
-    <t>135610976</t>
-  </si>
-  <si>
-    <t>135611023</t>
-  </si>
-  <si>
-    <t>135611035</t>
-  </si>
-  <si>
-    <t>135611168</t>
-  </si>
-  <si>
-    <t>135611184</t>
-  </si>
-  <si>
-    <t>135611243</t>
-  </si>
-  <si>
-    <t>135611727</t>
-  </si>
-  <si>
-    <t>135611738</t>
-  </si>
-  <si>
-    <t>135611776</t>
-  </si>
-  <si>
-    <t>135611902</t>
-  </si>
-  <si>
-    <t>135612292</t>
-  </si>
-  <si>
-    <t>135612339</t>
-  </si>
-  <si>
-    <t>135612340</t>
-  </si>
-  <si>
-    <t>135612348</t>
-  </si>
-  <si>
-    <t>135612589</t>
-  </si>
-  <si>
-    <t>135612637</t>
-  </si>
-  <si>
-    <t>135612710</t>
-  </si>
-  <si>
-    <t>135612874</t>
-  </si>
-  <si>
-    <t>135612961</t>
-  </si>
-  <si>
-    <t>135613024</t>
-  </si>
-  <si>
-    <t>135613092</t>
-  </si>
-  <si>
-    <t>135613225</t>
-  </si>
-  <si>
-    <t>135613445</t>
-  </si>
-  <si>
-    <t>135613470</t>
-  </si>
-  <si>
-    <t>135613511</t>
-  </si>
-  <si>
-    <t>135613645</t>
-  </si>
-  <si>
-    <t>135613821</t>
-  </si>
-  <si>
-    <t>135613871</t>
-  </si>
-  <si>
-    <t>135613923</t>
-  </si>
-  <si>
-    <t>135614064</t>
-  </si>
-  <si>
-    <t>135614148</t>
-  </si>
-  <si>
-    <t>135614165</t>
-  </si>
-  <si>
-    <t>135614176</t>
-  </si>
-  <si>
-    <t>135614178</t>
-  </si>
-  <si>
-    <t>135614185</t>
-  </si>
-  <si>
-    <t>135614250</t>
-  </si>
-  <si>
-    <t>135614306</t>
-  </si>
-  <si>
-    <t>135614311</t>
-  </si>
-  <si>
-    <t>135614378</t>
-  </si>
-  <si>
-    <t>135614435</t>
-  </si>
-  <si>
-    <t>135614440</t>
-  </si>
-  <si>
-    <t>135614459</t>
-  </si>
-  <si>
-    <t>135614581</t>
-  </si>
-  <si>
-    <t>135614681</t>
-  </si>
-  <si>
-    <t>135614703</t>
-  </si>
-  <si>
-    <t>135614807</t>
-  </si>
-  <si>
-    <t>135614862</t>
-  </si>
-  <si>
-    <t>135614884</t>
-  </si>
-  <si>
-    <t>135614924</t>
-  </si>
-  <si>
-    <t>135614964</t>
-  </si>
-  <si>
-    <t>135615109</t>
-  </si>
-  <si>
-    <t>135615163</t>
-  </si>
-  <si>
-    <t>135615198</t>
-  </si>
-  <si>
-    <t>135615368</t>
-  </si>
-  <si>
-    <t>135615402</t>
-  </si>
-  <si>
-    <t>135615408</t>
-  </si>
-  <si>
-    <t>135615530</t>
-  </si>
-  <si>
-    <t>135615549</t>
-  </si>
-  <si>
-    <t>135615571</t>
-  </si>
-  <si>
-    <t>135615642</t>
-  </si>
-  <si>
-    <t>135615657</t>
-  </si>
-  <si>
-    <t>135615670</t>
-  </si>
-  <si>
-    <t>135615706</t>
-  </si>
-  <si>
-    <t>135615783</t>
-  </si>
-  <si>
-    <t>135615796</t>
-  </si>
-  <si>
-    <t>135615896</t>
-  </si>
-  <si>
-    <t>135615926</t>
-  </si>
-  <si>
-    <t>135616126</t>
-  </si>
-  <si>
-    <t>135616234</t>
-  </si>
-  <si>
-    <t>135616336</t>
-  </si>
-  <si>
-    <t>135616356</t>
-  </si>
-  <si>
-    <t>135616479</t>
-  </si>
-  <si>
-    <t>135616536</t>
-  </si>
-  <si>
-    <t>135616738</t>
-  </si>
-  <si>
-    <t>135616771</t>
-  </si>
-  <si>
-    <t>135616785</t>
-  </si>
-  <si>
-    <t>135616828</t>
-  </si>
-  <si>
-    <t>135616950</t>
-  </si>
-  <si>
-    <t>135616972</t>
-  </si>
-  <si>
-    <t>135616980</t>
-  </si>
-  <si>
-    <t>135617019</t>
-  </si>
-  <si>
-    <t>135617074</t>
-  </si>
-  <si>
-    <t>135617092</t>
-  </si>
-  <si>
-    <t>135617093</t>
-  </si>
-  <si>
-    <t>135617169</t>
-  </si>
-  <si>
-    <t>135617229</t>
-  </si>
-  <si>
-    <t>135617340</t>
-  </si>
-  <si>
-    <t>135617377</t>
-  </si>
-  <si>
-    <t>135617411</t>
-  </si>
-  <si>
-    <t>135617470</t>
-  </si>
-  <si>
-    <t>135617536</t>
-  </si>
-  <si>
-    <t>135617619</t>
-  </si>
-  <si>
-    <t>135617697</t>
-  </si>
-  <si>
-    <t>135617740</t>
-  </si>
-  <si>
-    <t>135617768</t>
-  </si>
-  <si>
-    <t>135617816</t>
-  </si>
-  <si>
-    <t>135617895</t>
-  </si>
-  <si>
-    <t>135618085</t>
-  </si>
-  <si>
-    <t>135618099</t>
-  </si>
-  <si>
-    <t>135618129</t>
-  </si>
-  <si>
-    <t>135618155</t>
-  </si>
-  <si>
-    <t>135618161</t>
-  </si>
-  <si>
-    <t>135618216</t>
-  </si>
-  <si>
-    <t>135618226</t>
-  </si>
-  <si>
-    <t>135618233</t>
-  </si>
-  <si>
-    <t>135618274</t>
-  </si>
-  <si>
-    <t>135618278</t>
-  </si>
-  <si>
-    <t>135618308</t>
-  </si>
-  <si>
-    <t>135618636</t>
-  </si>
-  <si>
-    <t>135618667</t>
-  </si>
-  <si>
-    <t>135618732</t>
-  </si>
-  <si>
-    <t>135618785</t>
-  </si>
-  <si>
-    <t>135618925</t>
-  </si>
-  <si>
-    <t>135619299</t>
-  </si>
-  <si>
-    <t>135619387</t>
-  </si>
-  <si>
-    <t>135619405</t>
-  </si>
-  <si>
-    <t>135619703</t>
-  </si>
-  <si>
-    <t>135619815</t>
-  </si>
-  <si>
-    <t>135619897</t>
-  </si>
-  <si>
-    <t>135619926</t>
-  </si>
-  <si>
-    <t>135619972</t>
-  </si>
-  <si>
-    <t>135620078</t>
-  </si>
-  <si>
-    <t>135620079</t>
-  </si>
-  <si>
-    <t>135620205</t>
-  </si>
-  <si>
-    <t>135620296</t>
-  </si>
-  <si>
-    <t>135620303</t>
-  </si>
-  <si>
-    <t>135620363</t>
-  </si>
-  <si>
-    <t>135620381</t>
-  </si>
-  <si>
-    <t>135620386</t>
-  </si>
-  <si>
-    <t>135620401</t>
-  </si>
-  <si>
-    <t>135620414</t>
-  </si>
-  <si>
-    <t>135620553</t>
-  </si>
-  <si>
-    <t>135620796</t>
-  </si>
-  <si>
-    <t>135621016</t>
-  </si>
-  <si>
-    <t>135621120</t>
-  </si>
-  <si>
-    <t>135621316</t>
-  </si>
-  <si>
-    <t>135621319</t>
-  </si>
-  <si>
-    <t>135621328</t>
-  </si>
-  <si>
-    <t>135621382</t>
-  </si>
-  <si>
-    <t>135621385</t>
-  </si>
-  <si>
-    <t>135621448</t>
-  </si>
-  <si>
-    <t>135621456</t>
-  </si>
-  <si>
-    <t>135621497</t>
-  </si>
-  <si>
-    <t>135621501</t>
-  </si>
-  <si>
-    <t>135621617</t>
-  </si>
-  <si>
-    <t>135621681</t>
-  </si>
-  <si>
-    <t>135621706</t>
-  </si>
-  <si>
-    <t>135621721</t>
-  </si>
-  <si>
-    <t>135621749</t>
-  </si>
-  <si>
-    <t>135621801</t>
-  </si>
-  <si>
-    <t>135621818</t>
-  </si>
-  <si>
-    <t>135621829</t>
-  </si>
-  <si>
-    <t>135622008</t>
-  </si>
-  <si>
-    <t>135622017</t>
-  </si>
-  <si>
-    <t>135622022</t>
-  </si>
-  <si>
-    <t>135622041</t>
-  </si>
-  <si>
-    <t>135622075</t>
-  </si>
-  <si>
-    <t>135622117</t>
-  </si>
-  <si>
-    <t>135622131</t>
-  </si>
-  <si>
-    <t>135622198</t>
-  </si>
-  <si>
-    <t>135622303</t>
-  </si>
-  <si>
-    <t>135622334</t>
-  </si>
-  <si>
-    <t>135622448</t>
-  </si>
-  <si>
-    <t>135622605</t>
-  </si>
-  <si>
-    <t>135622690</t>
-  </si>
-  <si>
-    <t>135622691</t>
-  </si>
-  <si>
-    <t>135622796</t>
-  </si>
-  <si>
-    <t>135622942</t>
-  </si>
-  <si>
-    <t>135622992</t>
-  </si>
-  <si>
-    <t>135623024</t>
-  </si>
-  <si>
-    <t>135623113</t>
-  </si>
-  <si>
-    <t>135623171</t>
-  </si>
-  <si>
-    <t>135623181</t>
-  </si>
-  <si>
-    <t>135623218</t>
-  </si>
-  <si>
-    <t>135623264</t>
-  </si>
-  <si>
-    <t>135623310</t>
-  </si>
-  <si>
-    <t>135623623</t>
-  </si>
-  <si>
-    <t>135623735</t>
-  </si>
-  <si>
-    <t>135623740</t>
-  </si>
-  <si>
-    <t>135623799</t>
+    <t>130830027</t>
+  </si>
+  <si>
+    <t>130871360</t>
+  </si>
+  <si>
+    <t>130946628</t>
+  </si>
+  <si>
+    <t>131073184</t>
+  </si>
+  <si>
+    <t>131086855</t>
+  </si>
+  <si>
+    <t>131202300</t>
+  </si>
+  <si>
+    <t>131688430</t>
+  </si>
+  <si>
+    <t>131793069</t>
+  </si>
+  <si>
+    <t>131925517</t>
+  </si>
+  <si>
+    <t>131945415</t>
+  </si>
+  <si>
+    <t>131967702</t>
+  </si>
+  <si>
+    <t>132072014</t>
+  </si>
+  <si>
+    <t>132118948</t>
+  </si>
+  <si>
+    <t>132156853</t>
+  </si>
+  <si>
+    <t>132184722</t>
+  </si>
+  <si>
+    <t>132204812</t>
+  </si>
+  <si>
+    <t>132217500</t>
+  </si>
+  <si>
+    <t>132217664</t>
+  </si>
+  <si>
+    <t>132350890</t>
+  </si>
+  <si>
+    <t>132356168</t>
+  </si>
+  <si>
+    <t>132417927</t>
+  </si>
+  <si>
+    <t>132459353</t>
+  </si>
+  <si>
+    <t>132492918</t>
+  </si>
+  <si>
+    <t>132557643</t>
+  </si>
+  <si>
+    <t>132596481</t>
+  </si>
+  <si>
+    <t>132599212</t>
+  </si>
+  <si>
+    <t>132664862</t>
+  </si>
+  <si>
+    <t>132678915</t>
+  </si>
+  <si>
+    <t>132723922</t>
+  </si>
+  <si>
+    <t>132725256</t>
+  </si>
+  <si>
+    <t>132793420</t>
+  </si>
+  <si>
+    <t>132809508</t>
+  </si>
+  <si>
+    <t>132883881</t>
+  </si>
+  <si>
+    <t>133014420</t>
+  </si>
+  <si>
+    <t>133078191</t>
+  </si>
+  <si>
+    <t>133212660</t>
+  </si>
+  <si>
+    <t>133297809</t>
+  </si>
+  <si>
+    <t>133346770</t>
+  </si>
+  <si>
+    <t>133367438</t>
+  </si>
+  <si>
+    <t>133432512</t>
+  </si>
+  <si>
+    <t>133515997</t>
+  </si>
+  <si>
+    <t>133617777</t>
+  </si>
+  <si>
+    <t>133622699</t>
+  </si>
+  <si>
+    <t>133654385</t>
+  </si>
+  <si>
+    <t>133669659</t>
+  </si>
+  <si>
+    <t>133673225</t>
+  </si>
+  <si>
+    <t>133755917</t>
+  </si>
+  <si>
+    <t>133799869</t>
+  </si>
+  <si>
+    <t>134144228</t>
+  </si>
+  <si>
+    <t>134154929</t>
+  </si>
+  <si>
+    <t>134247515</t>
+  </si>
+  <si>
+    <t>134294164</t>
+  </si>
+  <si>
+    <t>134356945</t>
+  </si>
+  <si>
+    <t>134414783</t>
+  </si>
+  <si>
+    <t>134437327</t>
+  </si>
+  <si>
+    <t>134482747</t>
+  </si>
+  <si>
+    <t>134509759</t>
+  </si>
+  <si>
+    <t>134539611</t>
+  </si>
+  <si>
+    <t>134585101</t>
+  </si>
+  <si>
+    <t>134609447</t>
+  </si>
+  <si>
+    <t>134618910</t>
+  </si>
+  <si>
+    <t>134636928</t>
+  </si>
+  <si>
+    <t>134637963</t>
+  </si>
+  <si>
+    <t>134775899</t>
+  </si>
+  <si>
+    <t>134907796</t>
+  </si>
+  <si>
+    <t>134924756</t>
+  </si>
+  <si>
+    <t>134998144</t>
+  </si>
+  <si>
+    <t>135189168</t>
+  </si>
+  <si>
+    <t>135197689</t>
+  </si>
+  <si>
+    <t>135285239</t>
+  </si>
+  <si>
+    <t>135287356</t>
+  </si>
+  <si>
+    <t>135404787</t>
+  </si>
+  <si>
+    <t>135460230</t>
+  </si>
+  <si>
+    <t>135477209</t>
+  </si>
+  <si>
+    <t>135486440</t>
+  </si>
+  <si>
+    <t>135526221</t>
+  </si>
+  <si>
+    <t>135782624</t>
+  </si>
+  <si>
+    <t>135782984</t>
+  </si>
+  <si>
+    <t>135783310</t>
+  </si>
+  <si>
+    <t>135783360</t>
+  </si>
+  <si>
+    <t>135783614</t>
+  </si>
+  <si>
+    <t>135783833</t>
+  </si>
+  <si>
+    <t>135784066</t>
+  </si>
+  <si>
+    <t>135784492</t>
+  </si>
+  <si>
+    <t>135784668</t>
+  </si>
+  <si>
+    <t>135784914</t>
+  </si>
+  <si>
+    <t>135784963</t>
+  </si>
+  <si>
+    <t>135785027</t>
+  </si>
+  <si>
+    <t>135785099</t>
+  </si>
+  <si>
+    <t>135785187</t>
+  </si>
+  <si>
+    <t>135785341</t>
+  </si>
+  <si>
+    <t>135785493</t>
+  </si>
+  <si>
+    <t>135785789</t>
+  </si>
+  <si>
+    <t>135785856</t>
+  </si>
+  <si>
+    <t>135786002</t>
+  </si>
+  <si>
+    <t>135786234</t>
+  </si>
+  <si>
+    <t>135786554</t>
+  </si>
+  <si>
+    <t>135786662</t>
+  </si>
+  <si>
+    <t>135786988</t>
+  </si>
+  <si>
+    <t>135786992</t>
+  </si>
+  <si>
+    <t>135787076</t>
+  </si>
+  <si>
+    <t>135787188</t>
+  </si>
+  <si>
+    <t>135787215</t>
+  </si>
+  <si>
+    <t>135787311</t>
+  </si>
+  <si>
+    <t>135787457</t>
+  </si>
+  <si>
+    <t>135787622</t>
+  </si>
+  <si>
+    <t>135787631</t>
+  </si>
+  <si>
+    <t>135787684</t>
+  </si>
+  <si>
+    <t>135787715</t>
+  </si>
+  <si>
+    <t>135787756</t>
+  </si>
+  <si>
+    <t>135788160</t>
+  </si>
+  <si>
+    <t>135788187</t>
+  </si>
+  <si>
+    <t>135788545</t>
+  </si>
+  <si>
+    <t>135788559</t>
+  </si>
+  <si>
+    <t>135788625</t>
+  </si>
+  <si>
+    <t>135788837</t>
+  </si>
+  <si>
+    <t>135788869</t>
+  </si>
+  <si>
+    <t>135789037</t>
+  </si>
+  <si>
+    <t>135789107</t>
+  </si>
+  <si>
+    <t>135789183</t>
+  </si>
+  <si>
+    <t>135789236</t>
+  </si>
+  <si>
+    <t>135789324</t>
+  </si>
+  <si>
+    <t>135789510</t>
+  </si>
+  <si>
+    <t>135789515</t>
+  </si>
+  <si>
+    <t>135789575</t>
+  </si>
+  <si>
+    <t>135789718</t>
+  </si>
+  <si>
+    <t>135789768</t>
+  </si>
+  <si>
+    <t>135789931</t>
+  </si>
+  <si>
+    <t>135790000</t>
+  </si>
+  <si>
+    <t>135790032</t>
+  </si>
+  <si>
+    <t>135790226</t>
+  </si>
+  <si>
+    <t>135790616</t>
+  </si>
+  <si>
+    <t>135790924</t>
+  </si>
+  <si>
+    <t>135790948</t>
+  </si>
+  <si>
+    <t>135790995</t>
+  </si>
+  <si>
+    <t>135790996</t>
+  </si>
+  <si>
+    <t>135791001</t>
+  </si>
+  <si>
+    <t>135791350</t>
+  </si>
+  <si>
+    <t>135791638</t>
+  </si>
+  <si>
+    <t>135791757</t>
+  </si>
+  <si>
+    <t>135792102</t>
+  </si>
+  <si>
+    <t>135792383</t>
+  </si>
+  <si>
+    <t>135792420</t>
+  </si>
+  <si>
+    <t>135792461</t>
+  </si>
+  <si>
+    <t>135792497</t>
+  </si>
+  <si>
+    <t>135792660</t>
+  </si>
+  <si>
+    <t>135792794</t>
+  </si>
+  <si>
+    <t>135792917</t>
+  </si>
+  <si>
+    <t>135792921</t>
+  </si>
+  <si>
+    <t>135793068</t>
+  </si>
+  <si>
+    <t>135793083</t>
+  </si>
+  <si>
+    <t>135793139</t>
+  </si>
+  <si>
+    <t>135794002</t>
+  </si>
+  <si>
+    <t>135794015</t>
+  </si>
+  <si>
+    <t>135794149</t>
+  </si>
+  <si>
+    <t>135794402</t>
+  </si>
+  <si>
+    <t>135794680</t>
+  </si>
+  <si>
+    <t>135794753</t>
+  </si>
+  <si>
+    <t>135794763</t>
+  </si>
+  <si>
+    <t>135794935</t>
+  </si>
+  <si>
+    <t>135795081</t>
+  </si>
+  <si>
+    <t>135795162</t>
+  </si>
+  <si>
+    <t>135795211</t>
+  </si>
+  <si>
+    <t>135795252</t>
+  </si>
+  <si>
+    <t>135795318</t>
+  </si>
+  <si>
+    <t>135795621</t>
+  </si>
+  <si>
+    <t>135795633</t>
+  </si>
+  <si>
+    <t>135795703</t>
+  </si>
+  <si>
+    <t>135795712</t>
+  </si>
+  <si>
+    <t>135795802</t>
+  </si>
+  <si>
+    <t>135796136</t>
+  </si>
+  <si>
+    <t>135796491</t>
+  </si>
+  <si>
+    <t>135796625</t>
+  </si>
+  <si>
+    <t>135796664</t>
+  </si>
+  <si>
+    <t>135796735</t>
+  </si>
+  <si>
+    <t>135796879</t>
+  </si>
+  <si>
+    <t>135796978</t>
+  </si>
+  <si>
+    <t>135797060</t>
+  </si>
+  <si>
+    <t>135797224</t>
+  </si>
+  <si>
+    <t>135797431</t>
+  </si>
+  <si>
+    <t>135797720</t>
+  </si>
+  <si>
+    <t>135797823</t>
+  </si>
+  <si>
+    <t>135797857</t>
+  </si>
+  <si>
+    <t>135797924</t>
+  </si>
+  <si>
+    <t>135797972</t>
+  </si>
+  <si>
+    <t>135798115</t>
+  </si>
+  <si>
+    <t>135798280</t>
+  </si>
+  <si>
+    <t>135798360</t>
+  </si>
+  <si>
+    <t>135798684</t>
+  </si>
+  <si>
+    <t>135798798</t>
+  </si>
+  <si>
+    <t>135798817</t>
+  </si>
+  <si>
+    <t>135798822</t>
+  </si>
+  <si>
+    <t>135798926</t>
+  </si>
+  <si>
+    <t>135798976</t>
+  </si>
+  <si>
+    <t>135799126</t>
+  </si>
+  <si>
+    <t>135799139</t>
+  </si>
+  <si>
+    <t>135799889</t>
+  </si>
+  <si>
+    <t>135800051</t>
+  </si>
+  <si>
+    <t>135800223</t>
+  </si>
+  <si>
+    <t>135800268</t>
+  </si>
+  <si>
+    <t>135800277</t>
+  </si>
+  <si>
+    <t>135800358</t>
+  </si>
+  <si>
+    <t>135800468</t>
+  </si>
+  <si>
+    <t>135800568</t>
+  </si>
+  <si>
+    <t>135800598</t>
+  </si>
+  <si>
+    <t>135800711</t>
+  </si>
+  <si>
+    <t>135800735</t>
+  </si>
+  <si>
+    <t>135800747</t>
+  </si>
+  <si>
+    <t>135801128</t>
+  </si>
+  <si>
+    <t>135801230</t>
+  </si>
+  <si>
+    <t>135801278</t>
+  </si>
+  <si>
+    <t>135801390</t>
+  </si>
+  <si>
+    <t>135801442</t>
+  </si>
+  <si>
+    <t>135801653</t>
+  </si>
+  <si>
+    <t>135801689</t>
+  </si>
+  <si>
+    <t>135801726</t>
+  </si>
+  <si>
+    <t>135801731</t>
+  </si>
+  <si>
+    <t>135801756</t>
+  </si>
+  <si>
+    <t>135801761</t>
+  </si>
+  <si>
+    <t>135801822</t>
+  </si>
+  <si>
+    <t>135802073</t>
+  </si>
+  <si>
+    <t>135802152</t>
+  </si>
+  <si>
+    <t>135802229</t>
+  </si>
+  <si>
+    <t>135802331</t>
+  </si>
+  <si>
+    <t>135802438</t>
+  </si>
+  <si>
+    <t>135802541</t>
+  </si>
+  <si>
+    <t>135802647</t>
+  </si>
+  <si>
+    <t>135802697</t>
+  </si>
+  <si>
+    <t>135802701</t>
+  </si>
+  <si>
+    <t>135802813</t>
+  </si>
+  <si>
+    <t>135802875</t>
+  </si>
+  <si>
+    <t>135803202</t>
+  </si>
+  <si>
+    <t>135803396</t>
+  </si>
+  <si>
+    <t>135803430</t>
+  </si>
+  <si>
+    <t>135803478</t>
+  </si>
+  <si>
+    <t>135803755</t>
+  </si>
+  <si>
+    <t>135803839</t>
+  </si>
+  <si>
+    <t>135803870</t>
+  </si>
+  <si>
+    <t>135804085</t>
+  </si>
+  <si>
+    <t>135804152</t>
+  </si>
+  <si>
+    <t>135804177</t>
+  </si>
+  <si>
+    <t>135804418</t>
+  </si>
+  <si>
+    <t>135805086</t>
+  </si>
+  <si>
+    <t>135805127</t>
+  </si>
+  <si>
+    <t>135805160</t>
+  </si>
+  <si>
+    <t>135805189</t>
+  </si>
+  <si>
+    <t>135805214</t>
+  </si>
+  <si>
+    <t>135805287</t>
+  </si>
+  <si>
+    <t>135805670</t>
+  </si>
+  <si>
+    <t>135805722</t>
+  </si>
+  <si>
+    <t>135806011</t>
+  </si>
+  <si>
+    <t>135806073</t>
+  </si>
+  <si>
+    <t>135806364</t>
+  </si>
+  <si>
+    <t>135806458</t>
+  </si>
+  <si>
+    <t>135806463</t>
+  </si>
+  <si>
+    <t>135806494</t>
+  </si>
+  <si>
+    <t>135806540</t>
+  </si>
+  <si>
+    <t>135806730</t>
+  </si>
+  <si>
+    <t>135806823</t>
+  </si>
+  <si>
+    <t>135806871</t>
+  </si>
+  <si>
+    <t>135806940</t>
+  </si>
+  <si>
+    <t>135807108</t>
+  </si>
+  <si>
+    <t>135807281</t>
+  </si>
+  <si>
+    <t>135807335</t>
+  </si>
+  <si>
+    <t>135807416</t>
+  </si>
+  <si>
+    <t>135807718</t>
+  </si>
+  <si>
+    <t>135807734</t>
+  </si>
+  <si>
+    <t>135807784</t>
+  </si>
+  <si>
+    <t>135807935</t>
+  </si>
+  <si>
+    <t>135807951</t>
+  </si>
+  <si>
+    <t>135808010</t>
+  </si>
+  <si>
+    <t>135808011</t>
+  </si>
+  <si>
+    <t>135808027</t>
+  </si>
+  <si>
+    <t>135808244</t>
+  </si>
+  <si>
+    <t>135808252</t>
+  </si>
+  <si>
+    <t>135808376</t>
+  </si>
+  <si>
+    <t>135808458</t>
+  </si>
+  <si>
+    <t>135808812</t>
+  </si>
+  <si>
+    <t>135808997</t>
+  </si>
+  <si>
+    <t>135809050</t>
+  </si>
+  <si>
+    <t>135809115</t>
+  </si>
+  <si>
+    <t>135809173</t>
+  </si>
+  <si>
+    <t>135809230</t>
+  </si>
+  <si>
+    <t>135809266</t>
+  </si>
+  <si>
+    <t>135809481</t>
+  </si>
+  <si>
+    <t>135809535</t>
+  </si>
+  <si>
+    <t>135809550</t>
+  </si>
+  <si>
+    <t>135809887</t>
+  </si>
+  <si>
+    <t>135810012</t>
+  </si>
+  <si>
+    <t>135810480</t>
+  </si>
+  <si>
+    <t>135810685</t>
+  </si>
+  <si>
+    <t>135810908</t>
+  </si>
+  <si>
+    <t>135810916</t>
+  </si>
+  <si>
+    <t>135810971</t>
+  </si>
+  <si>
+    <t>135811117</t>
+  </si>
+  <si>
+    <t>135811315</t>
+  </si>
+  <si>
+    <t>135811411</t>
+  </si>
+  <si>
+    <t>135811419</t>
+  </si>
+  <si>
+    <t>135811495</t>
+  </si>
+  <si>
+    <t>135811516</t>
+  </si>
+  <si>
+    <t>135811627</t>
+  </si>
+  <si>
+    <t>135811709</t>
+  </si>
+  <si>
+    <t>135811760</t>
+  </si>
+  <si>
+    <t>135811881</t>
+  </si>
+  <si>
+    <t>135811891</t>
+  </si>
+  <si>
+    <t>135811984</t>
+  </si>
+  <si>
+    <t>135811987</t>
+  </si>
+  <si>
+    <t>135812131</t>
+  </si>
+  <si>
+    <t>135812284</t>
+  </si>
+  <si>
+    <t>135812293</t>
+  </si>
+  <si>
+    <t>135812315</t>
+  </si>
+  <si>
+    <t>135812466</t>
+  </si>
+  <si>
+    <t>135812637</t>
+  </si>
+  <si>
+    <t>135812753</t>
+  </si>
+  <si>
+    <t>135812967</t>
+  </si>
+  <si>
+    <t>135813044</t>
+  </si>
+  <si>
+    <t>135813155</t>
+  </si>
+  <si>
+    <t>135813200</t>
+  </si>
+  <si>
+    <t>135813843</t>
+  </si>
+  <si>
+    <t>135814079</t>
+  </si>
+  <si>
+    <t>135814171</t>
+  </si>
+  <si>
+    <t>135814266</t>
+  </si>
+  <si>
+    <t>135814338</t>
+  </si>
+  <si>
+    <t>135814543</t>
+  </si>
+  <si>
+    <t>135814570</t>
+  </si>
+  <si>
+    <t>135814609</t>
+  </si>
+  <si>
+    <t>135814879</t>
+  </si>
+  <si>
+    <t>135814904</t>
+  </si>
+  <si>
+    <t>135814953</t>
+  </si>
+  <si>
+    <t>135815199</t>
+  </si>
+  <si>
+    <t>135815209</t>
+  </si>
+  <si>
+    <t>135815418</t>
+  </si>
+  <si>
+    <t>135815518</t>
+  </si>
+  <si>
+    <t>135815643</t>
+  </si>
+  <si>
+    <t>135815667</t>
+  </si>
+  <si>
+    <t>135815672</t>
+  </si>
+  <si>
+    <t>135815689</t>
+  </si>
+  <si>
+    <t>135815984</t>
+  </si>
+  <si>
+    <t>135816251</t>
+  </si>
+  <si>
+    <t>135816255</t>
+  </si>
+  <si>
+    <t>135816308</t>
+  </si>
+  <si>
+    <t>135816438</t>
+  </si>
+  <si>
+    <t>135816530</t>
+  </si>
+  <si>
+    <t>135816548</t>
+  </si>
+  <si>
+    <t>135816609</t>
+  </si>
+  <si>
+    <t>135816613</t>
+  </si>
+  <si>
+    <t>135816665</t>
+  </si>
+  <si>
+    <t>135817115</t>
+  </si>
+  <si>
+    <t>135817138</t>
+  </si>
+  <si>
+    <t>135817179</t>
+  </si>
+  <si>
+    <t>135817240</t>
+  </si>
+  <si>
+    <t>135817318</t>
+  </si>
+  <si>
+    <t>135817371</t>
+  </si>
+  <si>
+    <t>135817452</t>
+  </si>
+  <si>
+    <t>135817621</t>
+  </si>
+  <si>
+    <t>135817675</t>
+  </si>
+  <si>
+    <t>135817939</t>
+  </si>
+  <si>
+    <t>135817976</t>
+  </si>
+  <si>
+    <t>135817978</t>
+  </si>
+  <si>
+    <t>135818050</t>
+  </si>
+  <si>
+    <t>135818070</t>
+  </si>
+  <si>
+    <t>135818569</t>
+  </si>
+  <si>
+    <t>135818640</t>
+  </si>
+  <si>
+    <t>135818699</t>
+  </si>
+  <si>
+    <t>135818843</t>
+  </si>
+  <si>
+    <t>135818851</t>
+  </si>
+  <si>
+    <t>135818943</t>
+  </si>
+  <si>
+    <t>135818945</t>
+  </si>
+  <si>
+    <t>135818952</t>
+  </si>
+  <si>
+    <t>135818953</t>
+  </si>
+  <si>
+    <t>135818983</t>
+  </si>
+  <si>
+    <t>135818995</t>
+  </si>
+  <si>
+    <t>135819106</t>
+  </si>
+  <si>
+    <t>135819154</t>
+  </si>
+  <si>
+    <t>135819185</t>
+  </si>
+  <si>
+    <t>135819203</t>
+  </si>
+  <si>
+    <t>135819240</t>
+  </si>
+  <si>
+    <t>135819327</t>
+  </si>
+  <si>
+    <t>135819627</t>
+  </si>
+  <si>
+    <t>135819651</t>
+  </si>
+  <si>
+    <t>135819751</t>
+  </si>
+  <si>
+    <t>135819959</t>
+  </si>
+  <si>
+    <t>135820028</t>
+  </si>
+  <si>
+    <t>135820095</t>
+  </si>
+  <si>
+    <t>135820157</t>
+  </si>
+  <si>
+    <t>135820216</t>
+  </si>
+  <si>
+    <t>135820283</t>
+  </si>
+  <si>
+    <t>135820314</t>
+  </si>
+  <si>
+    <t>135820319</t>
+  </si>
+  <si>
+    <t>135820410</t>
+  </si>
+  <si>
+    <t>135820585</t>
+  </si>
+  <si>
+    <t>135820637</t>
+  </si>
+  <si>
+    <t>135820684</t>
+  </si>
+  <si>
+    <t>135820738</t>
+  </si>
+  <si>
+    <t>135820787</t>
+  </si>
+  <si>
+    <t>135820874</t>
+  </si>
+  <si>
+    <t>135820917</t>
+  </si>
+  <si>
+    <t>135821015</t>
+  </si>
+  <si>
+    <t>135821081</t>
+  </si>
+  <si>
+    <t>135821148</t>
+  </si>
+  <si>
+    <t>135821216</t>
+  </si>
+  <si>
+    <t>135821361</t>
+  </si>
+  <si>
+    <t>135821428</t>
+  </si>
+  <si>
+    <t>135821481</t>
+  </si>
+  <si>
+    <t>135821485</t>
+  </si>
+  <si>
+    <t>135821489</t>
+  </si>
+  <si>
+    <t>135821541</t>
+  </si>
+  <si>
+    <t>135821562</t>
+  </si>
+  <si>
+    <t>135821656</t>
+  </si>
+  <si>
+    <t>135821810</t>
+  </si>
+  <si>
+    <t>135821936</t>
+  </si>
+  <si>
+    <t>135821952</t>
+  </si>
+  <si>
+    <t>135821979</t>
+  </si>
+  <si>
+    <t>135822109</t>
+  </si>
+  <si>
+    <t>135822128</t>
+  </si>
+  <si>
+    <t>135822142</t>
+  </si>
+  <si>
+    <t>135822162</t>
+  </si>
+  <si>
+    <t>135822293</t>
+  </si>
+  <si>
+    <t>135822352</t>
+  </si>
+  <si>
+    <t>135822464</t>
+  </si>
+  <si>
+    <t>135822572</t>
+  </si>
+  <si>
+    <t>135822660</t>
+  </si>
+  <si>
+    <t>135822825</t>
+  </si>
+  <si>
+    <t>135822837</t>
+  </si>
+  <si>
+    <t>135822900</t>
+  </si>
+  <si>
+    <t>135822954</t>
+  </si>
+  <si>
+    <t>135823314</t>
+  </si>
+  <si>
+    <t>135823368</t>
+  </si>
+  <si>
+    <t>135823371</t>
+  </si>
+  <si>
+    <t>135823420</t>
+  </si>
+  <si>
+    <t>135823453</t>
+  </si>
+  <si>
+    <t>135823479</t>
+  </si>
+  <si>
+    <t>135823498</t>
+  </si>
+  <si>
+    <t>135823506</t>
+  </si>
+  <si>
+    <t>135823600</t>
+  </si>
+  <si>
+    <t>135823689</t>
+  </si>
+  <si>
+    <t>135823760</t>
+  </si>
+  <si>
+    <t>135823843</t>
+  </si>
+  <si>
+    <t>135823871</t>
+  </si>
+  <si>
+    <t>135823920</t>
+  </si>
+  <si>
+    <t>135823942</t>
+  </si>
+  <si>
+    <t>135823968</t>
+  </si>
+  <si>
+    <t>135824078</t>
+  </si>
+  <si>
+    <t>135824219</t>
+  </si>
+  <si>
+    <t>135824237</t>
+  </si>
+  <si>
+    <t>135824283</t>
+  </si>
+  <si>
+    <t>135824613</t>
+  </si>
+  <si>
+    <t>135824712</t>
+  </si>
+  <si>
+    <t>135824822</t>
+  </si>
+  <si>
+    <t>135824911</t>
+  </si>
+  <si>
+    <t>135824943</t>
+  </si>
+  <si>
+    <t>135824981</t>
+  </si>
+  <si>
+    <t>135825229</t>
+  </si>
+  <si>
+    <t>135825263</t>
+  </si>
+  <si>
+    <t>135825299</t>
+  </si>
+  <si>
+    <t>135825376</t>
+  </si>
+  <si>
+    <t>135825479</t>
+  </si>
+  <si>
+    <t>135825494</t>
+  </si>
+  <si>
+    <t>135825641</t>
+  </si>
+  <si>
+    <t>135825651</t>
+  </si>
+  <si>
+    <t>135825721</t>
+  </si>
+  <si>
+    <t>135825872</t>
+  </si>
+  <si>
+    <t>135825904</t>
+  </si>
+  <si>
+    <t>135825990</t>
+  </si>
+  <si>
+    <t>135826156</t>
+  </si>
+  <si>
+    <t>135826400</t>
+  </si>
+  <si>
+    <t>135826844</t>
+  </si>
+  <si>
+    <t>135826967</t>
+  </si>
+  <si>
+    <t>135827115</t>
+  </si>
+  <si>
+    <t>135827190</t>
+  </si>
+  <si>
+    <t>135827293</t>
+  </si>
+  <si>
+    <t>135827311</t>
+  </si>
+  <si>
+    <t>135827335</t>
+  </si>
+  <si>
+    <t>135827339</t>
+  </si>
+  <si>
+    <t>135827376</t>
+  </si>
+  <si>
+    <t>135827483</t>
+  </si>
+  <si>
+    <t>135827594</t>
+  </si>
+  <si>
+    <t>135827645</t>
+  </si>
+  <si>
+    <t>135827714</t>
+  </si>
+  <si>
+    <t>135827840</t>
+  </si>
+  <si>
+    <t>135827920</t>
+  </si>
+  <si>
+    <t>135827921</t>
+  </si>
+  <si>
+    <t>135827976</t>
+  </si>
+  <si>
+    <t>135828028</t>
+  </si>
+  <si>
+    <t>135828032</t>
+  </si>
+  <si>
+    <t>135828052</t>
+  </si>
+  <si>
+    <t>135828054</t>
+  </si>
+  <si>
+    <t>135828076</t>
+  </si>
+  <si>
+    <t>135828131</t>
+  </si>
+  <si>
+    <t>135828170</t>
+  </si>
+  <si>
+    <t>135828234</t>
+  </si>
+  <si>
+    <t>135828239</t>
+  </si>
+  <si>
+    <t>135828269</t>
+  </si>
+  <si>
+    <t>135828472</t>
+  </si>
+  <si>
+    <t>135828497</t>
+  </si>
+  <si>
+    <t>135828612</t>
+  </si>
+  <si>
+    <t>135828662</t>
+  </si>
+  <si>
+    <t>135828675</t>
+  </si>
+  <si>
+    <t>135828717</t>
+  </si>
+  <si>
+    <t>135828718</t>
+  </si>
+  <si>
+    <t>135828831</t>
+  </si>
+  <si>
+    <t>135828853</t>
+  </si>
+  <si>
+    <t>135828858</t>
+  </si>
+  <si>
+    <t>135828878</t>
+  </si>
+  <si>
+    <t>135829029</t>
+  </si>
+  <si>
+    <t>135829044</t>
+  </si>
+  <si>
+    <t>135829075</t>
+  </si>
+  <si>
+    <t>135829170</t>
+  </si>
+  <si>
+    <t>135829269</t>
+  </si>
+  <si>
+    <t>135829295</t>
+  </si>
+  <si>
+    <t>135829385</t>
+  </si>
+  <si>
+    <t>135829406</t>
+  </si>
+  <si>
+    <t>135829469</t>
+  </si>
+  <si>
+    <t>135829813</t>
+  </si>
+  <si>
+    <t>135829821</t>
+  </si>
+  <si>
+    <t>135829907</t>
+  </si>
+  <si>
+    <t>135830070</t>
+  </si>
+  <si>
+    <t>135830071</t>
+  </si>
+  <si>
+    <t>135830164</t>
+  </si>
+  <si>
+    <t>135830188</t>
+  </si>
+  <si>
+    <t>135830360</t>
+  </si>
+  <si>
+    <t>135830423</t>
+  </si>
+  <si>
+    <t>135830440</t>
+  </si>
+  <si>
+    <t>135830556</t>
+  </si>
+  <si>
+    <t>135830654</t>
+  </si>
+  <si>
+    <t>135830801</t>
+  </si>
+  <si>
+    <t>135830878</t>
+  </si>
+  <si>
+    <t>135830883</t>
+  </si>
+  <si>
+    <t>135830955</t>
+  </si>
+  <si>
+    <t>135831004</t>
+  </si>
+  <si>
+    <t>135831014</t>
+  </si>
+  <si>
+    <t>135831209</t>
+  </si>
+  <si>
+    <t>135831292</t>
+  </si>
+  <si>
+    <t>135831295</t>
+  </si>
+  <si>
+    <t>135831403</t>
+  </si>
+  <si>
+    <t>135831419</t>
+  </si>
+  <si>
+    <t>135831420</t>
+  </si>
+  <si>
+    <t>135831459</t>
+  </si>
+  <si>
+    <t>135831574</t>
+  </si>
+  <si>
+    <t>135831603</t>
+  </si>
+  <si>
+    <t>135831939</t>
+  </si>
+  <si>
+    <t>135831958</t>
+  </si>
+  <si>
+    <t>135831979</t>
+  </si>
+  <si>
+    <t>135832076</t>
+  </si>
+  <si>
+    <t>135832149</t>
+  </si>
+  <si>
+    <t>135832158</t>
+  </si>
+  <si>
+    <t>135832208</t>
+  </si>
+  <si>
+    <t>135832296</t>
+  </si>
+  <si>
+    <t>135832381</t>
+  </si>
+  <si>
+    <t>135832424</t>
+  </si>
+  <si>
+    <t>135832425</t>
+  </si>
+  <si>
+    <t>135832538</t>
+  </si>
+  <si>
+    <t>135832547</t>
+  </si>
+  <si>
+    <t>135832689</t>
+  </si>
+  <si>
+    <t>135832716</t>
+  </si>
+  <si>
+    <t>135832787</t>
+  </si>
+  <si>
+    <t>135832796</t>
+  </si>
+  <si>
+    <t>135833012</t>
+  </si>
+  <si>
+    <t>135833300</t>
+  </si>
+  <si>
+    <t>135833321</t>
+  </si>
+  <si>
+    <t>135833328</t>
+  </si>
+  <si>
+    <t>135833450</t>
+  </si>
+  <si>
+    <t>135833506</t>
+  </si>
+  <si>
+    <t>135833533</t>
+  </si>
+  <si>
+    <t>135833675</t>
+  </si>
+  <si>
+    <t>135833685</t>
+  </si>
+  <si>
+    <t>135833782</t>
+  </si>
+  <si>
+    <t>135833811</t>
+  </si>
+  <si>
+    <t>135833852</t>
+  </si>
+  <si>
+    <t>135833855</t>
+  </si>
+  <si>
+    <t>135833880</t>
+  </si>
+  <si>
+    <t>135833920</t>
+  </si>
+  <si>
+    <t>135834055</t>
+  </si>
+  <si>
+    <t>135834089</t>
+  </si>
+  <si>
+    <t>135834603</t>
+  </si>
+  <si>
+    <t>135834661</t>
+  </si>
+  <si>
+    <t>135834818</t>
+  </si>
+  <si>
+    <t>135834930</t>
+  </si>
+  <si>
+    <t>135834978</t>
+  </si>
+  <si>
+    <t>135835042</t>
+  </si>
+  <si>
+    <t>135835112</t>
+  </si>
+  <si>
+    <t>135835202</t>
+  </si>
+  <si>
+    <t>135835238</t>
+  </si>
+  <si>
+    <t>135835278</t>
+  </si>
+  <si>
+    <t>135835282</t>
+  </si>
+  <si>
+    <t>135835356</t>
+  </si>
+  <si>
+    <t>135835392</t>
+  </si>
+  <si>
+    <t>135835438</t>
+  </si>
+  <si>
+    <t>135835624</t>
+  </si>
+  <si>
+    <t>135835747</t>
+  </si>
+  <si>
+    <t>135835759</t>
+  </si>
+  <si>
+    <t>135835787</t>
+  </si>
+  <si>
+    <t>135835845</t>
+  </si>
+  <si>
+    <t>135836160</t>
+  </si>
+  <si>
+    <t>135836190</t>
+  </si>
+  <si>
+    <t>135836211</t>
+  </si>
+  <si>
+    <t>135836305</t>
+  </si>
+  <si>
+    <t>135836307</t>
+  </si>
+  <si>
+    <t>135836397</t>
+  </si>
+  <si>
+    <t>135836439</t>
+  </si>
+  <si>
+    <t>135836553</t>
+  </si>
+  <si>
+    <t>135836605</t>
+  </si>
+  <si>
+    <t>135836606</t>
+  </si>
+  <si>
+    <t>135836620</t>
+  </si>
+  <si>
+    <t>135836683</t>
+  </si>
+  <si>
+    <t>135836691</t>
+  </si>
+  <si>
+    <t>135836782</t>
+  </si>
+  <si>
+    <t>135836837</t>
+  </si>
+  <si>
+    <t>135836845</t>
+  </si>
+  <si>
+    <t>135836988</t>
+  </si>
+  <si>
+    <t>135837068</t>
+  </si>
+  <si>
+    <t>135837322</t>
+  </si>
+  <si>
+    <t>135837452</t>
+  </si>
+  <si>
+    <t>135837560</t>
+  </si>
+  <si>
+    <t>135837564</t>
+  </si>
+  <si>
+    <t>135837715</t>
+  </si>
+  <si>
+    <t>135837745</t>
+  </si>
+  <si>
+    <t>135837762</t>
+  </si>
+  <si>
+    <t>135837814</t>
+  </si>
+  <si>
+    <t>135837817</t>
+  </si>
+  <si>
+    <t>135837860</t>
+  </si>
+  <si>
+    <t>135837893</t>
+  </si>
+  <si>
+    <t>135837949</t>
+  </si>
+  <si>
+    <t>135838004</t>
+  </si>
+  <si>
+    <t>135838054</t>
+  </si>
+  <si>
+    <t>135838073</t>
+  </si>
+  <si>
+    <t>135838192</t>
+  </si>
+  <si>
+    <t>135838333</t>
+  </si>
+  <si>
+    <t>135838337</t>
+  </si>
+  <si>
+    <t>135838359</t>
+  </si>
+  <si>
+    <t>135838367</t>
+  </si>
+  <si>
+    <t>135838412</t>
+  </si>
+  <si>
+    <t>135838481</t>
+  </si>
+  <si>
+    <t>135838514</t>
+  </si>
+  <si>
+    <t>135838603</t>
+  </si>
+  <si>
+    <t>135838621</t>
+  </si>
+  <si>
+    <t>135838638</t>
+  </si>
+  <si>
+    <t>135838650</t>
+  </si>
+  <si>
+    <t>135838716</t>
+  </si>
+  <si>
+    <t>135838767</t>
+  </si>
+  <si>
+    <t>135838836</t>
+  </si>
+  <si>
+    <t>135838857</t>
+  </si>
+  <si>
+    <t>135838992</t>
+  </si>
+  <si>
+    <t>135839133</t>
+  </si>
+  <si>
+    <t>135839259</t>
+  </si>
+  <si>
+    <t>135839426</t>
+  </si>
+  <si>
+    <t>135839448</t>
+  </si>
+  <si>
+    <t>135839657</t>
+  </si>
+  <si>
+    <t>135839746</t>
+  </si>
+  <si>
+    <t>135839807</t>
+  </si>
+  <si>
+    <t>135839839</t>
+  </si>
+  <si>
+    <t>135839887</t>
+  </si>
+  <si>
+    <t>135839899</t>
+  </si>
+  <si>
+    <t>135839911</t>
+  </si>
+  <si>
+    <t>135839933</t>
+  </si>
+  <si>
+    <t>135839954</t>
+  </si>
+  <si>
+    <t>135840144</t>
+  </si>
+  <si>
+    <t>135840245</t>
+  </si>
+  <si>
+    <t>135840382</t>
+  </si>
+  <si>
+    <t>135840391</t>
+  </si>
+  <si>
+    <t>135840421</t>
+  </si>
+  <si>
+    <t>135840526</t>
+  </si>
+  <si>
+    <t>135840576</t>
+  </si>
+  <si>
+    <t>135840689</t>
+  </si>
+  <si>
+    <t>135840795</t>
+  </si>
+  <si>
+    <t>135840855</t>
+  </si>
+  <si>
+    <t>135840890</t>
+  </si>
+  <si>
+    <t>135840893</t>
+  </si>
+  <si>
+    <t>135840930</t>
+  </si>
+  <si>
+    <t>135841042</t>
+  </si>
+  <si>
+    <t>135841138</t>
+  </si>
+  <si>
+    <t>135841150</t>
+  </si>
+  <si>
+    <t>135841180</t>
+  </si>
+  <si>
+    <t>135841201</t>
+  </si>
+  <si>
+    <t>135841241</t>
+  </si>
+  <si>
+    <t>135841250</t>
+  </si>
+  <si>
+    <t>135841319</t>
+  </si>
+  <si>
+    <t>135841469</t>
+  </si>
+  <si>
+    <t>135841482</t>
+  </si>
+  <si>
+    <t>135841507</t>
+  </si>
+  <si>
+    <t>135841523</t>
+  </si>
+  <si>
+    <t>135841546</t>
+  </si>
+  <si>
+    <t>135841572</t>
+  </si>
+  <si>
+    <t>135841650</t>
+  </si>
+  <si>
+    <t>135841654</t>
+  </si>
+  <si>
+    <t>135841658</t>
+  </si>
+  <si>
+    <t>135841724</t>
+  </si>
+  <si>
+    <t>135841784</t>
+  </si>
+  <si>
+    <t>135841931</t>
+  </si>
+  <si>
+    <t>135841932</t>
+  </si>
+  <si>
+    <t>135841942</t>
+  </si>
+  <si>
+    <t>135842007</t>
+  </si>
+  <si>
+    <t>135842008</t>
+  </si>
+  <si>
+    <t>135842040</t>
+  </si>
+  <si>
+    <t>135842179</t>
+  </si>
+  <si>
+    <t>135842181</t>
+  </si>
+  <si>
+    <t>135842317</t>
+  </si>
+  <si>
+    <t>135842323</t>
+  </si>
+  <si>
+    <t>135842346</t>
+  </si>
+  <si>
+    <t>135842385</t>
+  </si>
+  <si>
+    <t>135842403</t>
+  </si>
+  <si>
+    <t>135842411</t>
+  </si>
+  <si>
+    <t>135842592</t>
+  </si>
+  <si>
+    <t>135842597</t>
+  </si>
+  <si>
+    <t>135842699</t>
+  </si>
+  <si>
+    <t>135842712</t>
+  </si>
+  <si>
+    <t>135842717</t>
+  </si>
+  <si>
+    <t>135842751</t>
+  </si>
+  <si>
+    <t>135842778</t>
+  </si>
+  <si>
+    <t>135842886</t>
+  </si>
+  <si>
+    <t>135842945</t>
+  </si>
+  <si>
+    <t>135843249</t>
+  </si>
+  <si>
+    <t>135843251</t>
+  </si>
+  <si>
+    <t>135843259</t>
+  </si>
+  <si>
+    <t>135843389</t>
+  </si>
+  <si>
+    <t>135843453</t>
+  </si>
+  <si>
+    <t>135843464</t>
+  </si>
+  <si>
+    <t>135843465</t>
+  </si>
+  <si>
+    <t>135843502</t>
+  </si>
+  <si>
+    <t>135843505</t>
+  </si>
+  <si>
+    <t>135843604</t>
+  </si>
+  <si>
+    <t>135843675</t>
+  </si>
+  <si>
+    <t>135843679</t>
+  </si>
+  <si>
+    <t>135843710</t>
+  </si>
+  <si>
+    <t>135843749</t>
+  </si>
+  <si>
+    <t>135843758</t>
+  </si>
+  <si>
+    <t>135843775</t>
+  </si>
+  <si>
+    <t>135843891</t>
+  </si>
+  <si>
+    <t>135843895</t>
+  </si>
+  <si>
+    <t>135843951</t>
+  </si>
+  <si>
+    <t>135844039</t>
+  </si>
+  <si>
+    <t>135844075</t>
+  </si>
+  <si>
+    <t>135844098</t>
+  </si>
+  <si>
+    <t>135844139</t>
+  </si>
+  <si>
+    <t>135844154</t>
+  </si>
+  <si>
+    <t>135844180</t>
+  </si>
+  <si>
+    <t>135844223</t>
+  </si>
+  <si>
+    <t>135844233</t>
+  </si>
+  <si>
+    <t>135844242</t>
+  </si>
+  <si>
+    <t>135844248</t>
+  </si>
+  <si>
+    <t>135844266</t>
+  </si>
+  <si>
+    <t>135844292</t>
+  </si>
+  <si>
+    <t>135844326</t>
+  </si>
+  <si>
+    <t>135844328</t>
+  </si>
+  <si>
+    <t>135844329</t>
+  </si>
+  <si>
+    <t>135844347</t>
+  </si>
+  <si>
+    <t>135844409</t>
+  </si>
+  <si>
+    <t>135844482</t>
+  </si>
+  <si>
+    <t>135844489</t>
+  </si>
+  <si>
+    <t>135844588</t>
+  </si>
+  <si>
+    <t>135844593</t>
+  </si>
+  <si>
+    <t>135844610</t>
+  </si>
+  <si>
+    <t>135844669</t>
+  </si>
+  <si>
+    <t>135844704</t>
+  </si>
+  <si>
+    <t>135844733</t>
+  </si>
+  <si>
+    <t>135844743</t>
+  </si>
+  <si>
+    <t>135844784</t>
+  </si>
+  <si>
+    <t>135844834</t>
+  </si>
+  <si>
+    <t>135844861</t>
+  </si>
+  <si>
+    <t>135844890</t>
+  </si>
+  <si>
+    <t>135844898</t>
+  </si>
+  <si>
+    <t>135844925</t>
+  </si>
+  <si>
+    <t>135844980</t>
+  </si>
+  <si>
+    <t>135845001</t>
+  </si>
+  <si>
+    <t>135845030</t>
+  </si>
+  <si>
+    <t>135845035</t>
+  </si>
+  <si>
+    <t>135845050</t>
+  </si>
+  <si>
+    <t>135845083</t>
+  </si>
+  <si>
+    <t>135845084</t>
+  </si>
+  <si>
+    <t>135845159</t>
+  </si>
+  <si>
+    <t>135845212</t>
+  </si>
+  <si>
+    <t>135845213</t>
+  </si>
+  <si>
+    <t>135845259</t>
+  </si>
+  <si>
+    <t>135845274</t>
+  </si>
+  <si>
+    <t>135845297</t>
+  </si>
+  <si>
+    <t>135845300</t>
+  </si>
+  <si>
+    <t>135845342</t>
+  </si>
+  <si>
+    <t>135845344</t>
+  </si>
+  <si>
+    <t>135845371</t>
+  </si>
+  <si>
+    <t>135845403</t>
+  </si>
+  <si>
+    <t>135845414</t>
+  </si>
+  <si>
+    <t>135845416</t>
+  </si>
+  <si>
+    <t>135845477</t>
+  </si>
+  <si>
+    <t>135845512</t>
+  </si>
+  <si>
+    <t>135845690</t>
+  </si>
+  <si>
+    <t>135845709</t>
+  </si>
+  <si>
+    <t>135845757</t>
+  </si>
+  <si>
+    <t>135845809</t>
+  </si>
+  <si>
+    <t>135845827</t>
+  </si>
+  <si>
+    <t>135845841</t>
+  </si>
+  <si>
+    <t>135845899</t>
+  </si>
+  <si>
+    <t>135845903</t>
+  </si>
+  <si>
+    <t>135845913</t>
+  </si>
+  <si>
+    <t>135845938</t>
+  </si>
+  <si>
+    <t>135845999</t>
+  </si>
+  <si>
+    <t>135846029</t>
+  </si>
+  <si>
+    <t>135846079</t>
+  </si>
+  <si>
+    <t>135846094</t>
+  </si>
+  <si>
+    <t>135846128</t>
+  </si>
+  <si>
+    <t>135846154</t>
+  </si>
+  <si>
+    <t>135846217</t>
+  </si>
+  <si>
+    <t>135846339</t>
+  </si>
+  <si>
+    <t>135846375</t>
+  </si>
+  <si>
+    <t>135846513</t>
+  </si>
+  <si>
+    <t>135846518</t>
+  </si>
+  <si>
+    <t>135846553</t>
+  </si>
+  <si>
+    <t>135846617</t>
+  </si>
+  <si>
+    <t>135846639</t>
+  </si>
+  <si>
+    <t>135846674</t>
+  </si>
+  <si>
+    <t>135846729</t>
+  </si>
+  <si>
+    <t>135846783</t>
+  </si>
+  <si>
+    <t>135846901</t>
+  </si>
+  <si>
+    <t>135846933</t>
+  </si>
+  <si>
+    <t>135846975</t>
+  </si>
+  <si>
+    <t>135846991</t>
+  </si>
+  <si>
+    <t>135847002</t>
+  </si>
+  <si>
+    <t>135847032</t>
+  </si>
+  <si>
+    <t>135847077</t>
+  </si>
+  <si>
+    <t>135847087</t>
+  </si>
+  <si>
+    <t>135847098</t>
+  </si>
+  <si>
+    <t>135847129</t>
+  </si>
+  <si>
+    <t>135847135</t>
+  </si>
+  <si>
+    <t>135847183</t>
+  </si>
+  <si>
+    <t>135847184</t>
+  </si>
+  <si>
+    <t>135847271</t>
+  </si>
+  <si>
+    <t>135847309</t>
+  </si>
+  <si>
+    <t>135847332</t>
+  </si>
+  <si>
+    <t>135847416</t>
+  </si>
+  <si>
+    <t>135847471</t>
+  </si>
+  <si>
+    <t>135847552</t>
+  </si>
+  <si>
+    <t>135847593</t>
+  </si>
+  <si>
+    <t>135847793</t>
+  </si>
+  <si>
+    <t>135847814</t>
+  </si>
+  <si>
+    <t>135847853</t>
+  </si>
+  <si>
+    <t>135847959</t>
   </si>
 </sst>
 </file>
@@ -2346,7 +2961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C634"/>
+  <dimension ref="A1:C839"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2368,7 +2983,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>3</v>
@@ -2379,7 +2994,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>3</v>
@@ -2390,7 +3005,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>3</v>
@@ -2401,7 +3016,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>3</v>
@@ -2412,7 +3027,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>3</v>
@@ -2423,7 +3038,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>3</v>
@@ -2434,7 +3049,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
@@ -2445,7 +3060,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>3</v>
@@ -2456,7 +3071,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>3</v>
@@ -2467,7 +3082,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>3</v>
@@ -2478,7 +3093,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>3</v>
@@ -2489,7 +3104,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>3</v>
@@ -2500,7 +3115,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>3</v>
@@ -2511,7 +3126,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>3</v>
@@ -2522,7 +3137,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>3</v>
@@ -2533,7 +3148,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>3</v>
@@ -2544,7 +3159,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>3</v>
@@ -2555,7 +3170,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>3</v>
@@ -2566,7 +3181,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>3</v>
@@ -2577,7 +3192,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>3</v>
@@ -2588,7 +3203,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>3</v>
@@ -2599,7 +3214,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>3</v>
@@ -2610,7 +3225,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>3</v>
@@ -2621,7 +3236,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>3</v>
@@ -2632,7 +3247,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>3</v>
@@ -2643,7 +3258,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>3</v>
@@ -2654,7 +3269,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>3</v>
@@ -2665,7 +3280,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>3</v>
@@ -2676,7 +3291,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>3</v>
@@ -2687,7 +3302,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>3</v>
@@ -2698,7 +3313,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>3</v>
@@ -2709,7 +3324,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>3</v>
@@ -2720,7 +3335,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>3</v>
@@ -2731,7 +3346,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>3</v>
@@ -2742,7 +3357,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>3</v>
@@ -2753,7 +3368,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>3</v>
@@ -2764,7 +3379,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>3</v>
@@ -8423,6 +9038,1646 @@
         <v>637</v>
       </c>
       <c r="B634" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A635" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B635" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A636" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B636" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A637" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B637" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A638" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B638" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A639" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B639" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A640" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B640" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A641" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B641" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A642" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B642" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A643" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B643" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A644" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B644" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A645" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B645" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A646" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B646" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A647" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B647" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A648" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B648" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A649" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B649" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A650" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B650" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A651" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="B651" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A652" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B652" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A653" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B653" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A654" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B654" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A655" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B655" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A656" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B656" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A657" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B657" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A658" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B658" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A659" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B659" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A660" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B660" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A661" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B661" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A662" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B662" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A663" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B663" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A664" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B664" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A665" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B665" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A666" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B666" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A667" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B667" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A668" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B668" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A669" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B669" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A670" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B670" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A671" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B671" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A672" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B672" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A673" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="B673" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A674" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B674" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A675" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B675" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A676" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B676" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A677" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B677" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A678" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B678" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A679" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B679" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A680" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B680" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A681" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B681" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A682" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B682" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A683" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B683" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A684" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B684" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A685" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B685" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A686" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B686" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A687" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B687" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A688" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B688" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A689" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B689" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A690" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B690" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A691" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B691" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A692" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B692" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A693" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B693" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A694" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B694" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A695" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B695" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A696" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B696" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A697" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B697" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A698" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B698" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A699" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B699" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A700" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B700" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A701" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B701" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A702" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B702" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A703" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B703" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A704" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B704" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A705" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B705" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A706" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B706" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A707" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B707" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A708" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B708" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A709" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B709" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A710" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B710" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A711" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B711" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A712" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B712" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A713" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B713" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A714" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B714" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A715" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B715" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A716" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B716" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A717" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B717" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A718" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B718" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A719" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B719" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A720" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B720" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A721" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B721" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A722" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B722" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A723" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B723" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A724" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B724" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A725" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B725" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A726" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B726" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A727" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B727" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A728" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B728" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A729" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B729" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A730" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B730" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A731" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B731" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A732" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B732" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A733" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B733" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A734" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B734" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A735" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B735" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A736" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B736" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A737" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B737" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A738" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B738" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A739" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B739" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A740" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B740" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A741" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B741" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A742" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B742" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A743" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B743" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A744" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B744" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A745" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B745" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A746" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B746" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A747" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B747" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A748" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B748" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A749" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B749" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A750" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B750" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A751" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B751" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A752" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B752" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A753" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B753" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A754" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B754" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A755" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B755" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A756" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B756" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A757" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B757" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A758" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B758" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A759" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B759" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A760" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B760" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A761" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B761" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A762" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B762" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A763" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B763" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A764" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B764" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A765" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B765" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A766" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B766" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A767" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B767" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A768" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B768" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A769" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B769" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A770" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B770" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A771" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B771" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A772" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B772" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A773" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B773" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A774" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="B774" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A775" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B775" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A776" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B776" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A777" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B777" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A778" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B778" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A779" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B779" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A780" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B780" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A781" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B781" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A782" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B782" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A783" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B783" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A784" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B784" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A785" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B785" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A786" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B786" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A787" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B787" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A788" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B788" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A789" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B789" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A790" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B790" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A791" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B791" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A792" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B792" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A793" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B793" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A794" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B794" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A795" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="B795" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A796" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B796" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A797" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B797" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A798" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B798" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A799" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B799" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A800" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B800" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A801" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B801" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A802" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B802" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A803" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B803" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A804" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B804" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A805" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B805" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A806" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B806" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A807" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B807" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A808" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B808" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A809" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B809" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A810" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="B810" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A811" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B811" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A812" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="B812" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A813" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B813" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A814" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B814" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A815" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B815" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A816" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B816" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A817" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B817" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A818" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B818" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A819" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B819" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A820" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="B820" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A821" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="B821" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A822" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B822" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A823" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B823" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A824" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B824" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A825" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="B825" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A826" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B826" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A827" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="B827" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A828" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B828" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A829" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B829" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A830" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="B830" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A831" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B831" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A832" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B832" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A833" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B833" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A834" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="B834" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A835" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="B835" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A836" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B836" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A837" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B837" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A838" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B838" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A839" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B839" s="6" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087E9F03-5463-443A-AB1E-F2FD0099627B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13EE706-A575-43F8-A6AD-84FF812D1E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="7785" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
   <sheets>
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="622">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,2518 +45,1855 @@
     <t>.</t>
   </si>
   <si>
-    <t>130830027</t>
-  </si>
-  <si>
-    <t>130871360</t>
-  </si>
-  <si>
-    <t>130946628</t>
-  </si>
-  <si>
-    <t>131013144</t>
-  </si>
-  <si>
-    <t>131073184</t>
-  </si>
-  <si>
-    <t>131086855</t>
-  </si>
-  <si>
-    <t>131202300</t>
-  </si>
-  <si>
-    <t>131249640</t>
-  </si>
-  <si>
-    <t>131688430</t>
-  </si>
-  <si>
-    <t>131793069</t>
-  </si>
-  <si>
-    <t>131925517</t>
-  </si>
-  <si>
-    <t>131945415</t>
-  </si>
-  <si>
-    <t>131967702</t>
-  </si>
-  <si>
-    <t>132072014</t>
-  </si>
-  <si>
-    <t>132118948</t>
-  </si>
-  <si>
-    <t>132156853</t>
-  </si>
-  <si>
-    <t>132184722</t>
-  </si>
-  <si>
-    <t>132204812</t>
-  </si>
-  <si>
-    <t>132217500</t>
-  </si>
-  <si>
-    <t>132217664</t>
-  </si>
-  <si>
-    <t>132350890</t>
-  </si>
-  <si>
-    <t>132356168</t>
-  </si>
-  <si>
-    <t>132417927</t>
-  </si>
-  <si>
-    <t>132459353</t>
-  </si>
-  <si>
-    <t>132492918</t>
-  </si>
-  <si>
-    <t>132557643</t>
-  </si>
-  <si>
-    <t>132596481</t>
-  </si>
-  <si>
-    <t>132599212</t>
-  </si>
-  <si>
-    <t>132664862</t>
-  </si>
-  <si>
-    <t>132678915</t>
-  </si>
-  <si>
-    <t>132723922</t>
-  </si>
-  <si>
-    <t>132725256</t>
-  </si>
-  <si>
-    <t>132793420</t>
-  </si>
-  <si>
-    <t>132809508</t>
-  </si>
-  <si>
-    <t>132883881</t>
-  </si>
-  <si>
-    <t>133014420</t>
-  </si>
-  <si>
-    <t>133061172</t>
-  </si>
-  <si>
-    <t>133078191</t>
-  </si>
-  <si>
-    <t>133212660</t>
-  </si>
-  <si>
-    <t>133297809</t>
-  </si>
-  <si>
-    <t>133346770</t>
-  </si>
-  <si>
-    <t>133367438</t>
-  </si>
-  <si>
-    <t>133432512</t>
-  </si>
-  <si>
-    <t>133515997</t>
-  </si>
-  <si>
-    <t>133617777</t>
-  </si>
-  <si>
-    <t>133622699</t>
-  </si>
-  <si>
-    <t>133654385</t>
-  </si>
-  <si>
-    <t>133669659</t>
-  </si>
-  <si>
-    <t>133673225</t>
-  </si>
-  <si>
-    <t>133755917</t>
-  </si>
-  <si>
-    <t>133799869</t>
-  </si>
-  <si>
-    <t>134144228</t>
-  </si>
-  <si>
-    <t>134154929</t>
-  </si>
-  <si>
-    <t>134247515</t>
-  </si>
-  <si>
-    <t>134294164</t>
-  </si>
-  <si>
-    <t>134356945</t>
-  </si>
-  <si>
-    <t>134414783</t>
-  </si>
-  <si>
-    <t>134437327</t>
-  </si>
-  <si>
-    <t>134482747</t>
-  </si>
-  <si>
-    <t>134509759</t>
-  </si>
-  <si>
-    <t>134539611</t>
-  </si>
-  <si>
-    <t>134585101</t>
-  </si>
-  <si>
-    <t>134609447</t>
-  </si>
-  <si>
-    <t>134618910</t>
-  </si>
-  <si>
-    <t>134636928</t>
-  </si>
-  <si>
-    <t>134637963</t>
-  </si>
-  <si>
-    <t>134775899</t>
-  </si>
-  <si>
-    <t>134907796</t>
-  </si>
-  <si>
-    <t>134924756</t>
-  </si>
-  <si>
-    <t>134998144</t>
-  </si>
-  <si>
-    <t>135189168</t>
-  </si>
-  <si>
-    <t>135197689</t>
-  </si>
-  <si>
-    <t>135285239</t>
-  </si>
-  <si>
-    <t>135287356</t>
-  </si>
-  <si>
-    <t>135404787</t>
-  </si>
-  <si>
-    <t>135460230</t>
-  </si>
-  <si>
-    <t>135477209</t>
-  </si>
-  <si>
-    <t>135486440</t>
-  </si>
-  <si>
-    <t>135526221</t>
-  </si>
-  <si>
-    <t>135782624</t>
-  </si>
-  <si>
-    <t>135782984</t>
-  </si>
-  <si>
-    <t>135783310</t>
-  </si>
-  <si>
-    <t>135783360</t>
-  </si>
-  <si>
-    <t>135783614</t>
-  </si>
-  <si>
-    <t>135783833</t>
-  </si>
-  <si>
-    <t>135784066</t>
-  </si>
-  <si>
-    <t>135784492</t>
-  </si>
-  <si>
-    <t>135784668</t>
-  </si>
-  <si>
-    <t>135784914</t>
-  </si>
-  <si>
-    <t>135784963</t>
-  </si>
-  <si>
-    <t>135785027</t>
-  </si>
-  <si>
-    <t>135785099</t>
-  </si>
-  <si>
-    <t>135785187</t>
-  </si>
-  <si>
-    <t>135785341</t>
-  </si>
-  <si>
-    <t>135785493</t>
-  </si>
-  <si>
-    <t>135785789</t>
-  </si>
-  <si>
-    <t>135785856</t>
-  </si>
-  <si>
-    <t>135786002</t>
-  </si>
-  <si>
-    <t>135786234</t>
-  </si>
-  <si>
-    <t>135786554</t>
-  </si>
-  <si>
-    <t>135786662</t>
-  </si>
-  <si>
-    <t>135786988</t>
-  </si>
-  <si>
-    <t>135786992</t>
-  </si>
-  <si>
-    <t>135787076</t>
-  </si>
-  <si>
-    <t>135787188</t>
-  </si>
-  <si>
-    <t>135787215</t>
-  </si>
-  <si>
-    <t>135787311</t>
-  </si>
-  <si>
-    <t>135787457</t>
-  </si>
-  <si>
-    <t>135787622</t>
-  </si>
-  <si>
-    <t>135787631</t>
-  </si>
-  <si>
-    <t>135787684</t>
-  </si>
-  <si>
-    <t>135787715</t>
-  </si>
-  <si>
-    <t>135787756</t>
-  </si>
-  <si>
-    <t>135788160</t>
-  </si>
-  <si>
-    <t>135788187</t>
-  </si>
-  <si>
-    <t>135788545</t>
-  </si>
-  <si>
-    <t>135788559</t>
-  </si>
-  <si>
-    <t>135788625</t>
-  </si>
-  <si>
-    <t>135788837</t>
-  </si>
-  <si>
-    <t>135788869</t>
-  </si>
-  <si>
-    <t>135789037</t>
-  </si>
-  <si>
-    <t>135789107</t>
-  </si>
-  <si>
-    <t>135789183</t>
-  </si>
-  <si>
-    <t>135789236</t>
-  </si>
-  <si>
-    <t>135789324</t>
-  </si>
-  <si>
-    <t>135789510</t>
-  </si>
-  <si>
-    <t>135789515</t>
-  </si>
-  <si>
-    <t>135789575</t>
-  </si>
-  <si>
-    <t>135789718</t>
-  </si>
-  <si>
-    <t>135789768</t>
-  </si>
-  <si>
-    <t>135789931</t>
-  </si>
-  <si>
-    <t>135790000</t>
-  </si>
-  <si>
-    <t>135790032</t>
-  </si>
-  <si>
-    <t>135790226</t>
-  </si>
-  <si>
-    <t>135790616</t>
-  </si>
-  <si>
-    <t>135790924</t>
-  </si>
-  <si>
-    <t>135790948</t>
-  </si>
-  <si>
-    <t>135790995</t>
-  </si>
-  <si>
-    <t>135790996</t>
-  </si>
-  <si>
-    <t>135791001</t>
-  </si>
-  <si>
-    <t>135791350</t>
-  </si>
-  <si>
-    <t>135791638</t>
-  </si>
-  <si>
-    <t>135791757</t>
-  </si>
-  <si>
-    <t>135792102</t>
-  </si>
-  <si>
-    <t>135792383</t>
-  </si>
-  <si>
-    <t>135792420</t>
-  </si>
-  <si>
-    <t>135792461</t>
-  </si>
-  <si>
-    <t>135792497</t>
-  </si>
-  <si>
-    <t>135792660</t>
-  </si>
-  <si>
-    <t>135792794</t>
-  </si>
-  <si>
-    <t>135792917</t>
-  </si>
-  <si>
-    <t>135792921</t>
-  </si>
-  <si>
-    <t>135793068</t>
-  </si>
-  <si>
-    <t>135793083</t>
-  </si>
-  <si>
-    <t>135793139</t>
-  </si>
-  <si>
-    <t>135794002</t>
-  </si>
-  <si>
-    <t>135794015</t>
-  </si>
-  <si>
-    <t>135794149</t>
-  </si>
-  <si>
-    <t>135794402</t>
-  </si>
-  <si>
-    <t>135794680</t>
-  </si>
-  <si>
-    <t>135794753</t>
-  </si>
-  <si>
-    <t>135794763</t>
-  </si>
-  <si>
-    <t>135794935</t>
-  </si>
-  <si>
-    <t>135795081</t>
-  </si>
-  <si>
-    <t>135795162</t>
-  </si>
-  <si>
-    <t>135795211</t>
-  </si>
-  <si>
-    <t>135795252</t>
-  </si>
-  <si>
-    <t>135795318</t>
-  </si>
-  <si>
-    <t>135795621</t>
-  </si>
-  <si>
-    <t>135795633</t>
-  </si>
-  <si>
-    <t>135795703</t>
-  </si>
-  <si>
-    <t>135795712</t>
-  </si>
-  <si>
-    <t>135795802</t>
-  </si>
-  <si>
-    <t>135796136</t>
-  </si>
-  <si>
-    <t>135796491</t>
-  </si>
-  <si>
-    <t>135796625</t>
-  </si>
-  <si>
-    <t>135796664</t>
-  </si>
-  <si>
-    <t>135796735</t>
-  </si>
-  <si>
-    <t>135796879</t>
-  </si>
-  <si>
-    <t>135796978</t>
-  </si>
-  <si>
-    <t>135797060</t>
-  </si>
-  <si>
-    <t>135797224</t>
-  </si>
-  <si>
-    <t>135797431</t>
-  </si>
-  <si>
-    <t>135797720</t>
-  </si>
-  <si>
-    <t>135797823</t>
-  </si>
-  <si>
-    <t>135797857</t>
-  </si>
-  <si>
-    <t>135797924</t>
-  </si>
-  <si>
-    <t>135797972</t>
-  </si>
-  <si>
-    <t>135798115</t>
-  </si>
-  <si>
-    <t>135798280</t>
-  </si>
-  <si>
-    <t>135798360</t>
-  </si>
-  <si>
-    <t>135798684</t>
-  </si>
-  <si>
-    <t>135798798</t>
-  </si>
-  <si>
-    <t>135798817</t>
-  </si>
-  <si>
-    <t>135798822</t>
-  </si>
-  <si>
-    <t>135798926</t>
-  </si>
-  <si>
-    <t>135798976</t>
-  </si>
-  <si>
-    <t>135799126</t>
-  </si>
-  <si>
-    <t>135799139</t>
-  </si>
-  <si>
-    <t>135799889</t>
-  </si>
-  <si>
-    <t>135800051</t>
-  </si>
-  <si>
-    <t>135800223</t>
-  </si>
-  <si>
-    <t>135800268</t>
-  </si>
-  <si>
-    <t>135800277</t>
-  </si>
-  <si>
-    <t>135800358</t>
-  </si>
-  <si>
-    <t>135800468</t>
-  </si>
-  <si>
-    <t>135800568</t>
-  </si>
-  <si>
-    <t>135800598</t>
-  </si>
-  <si>
-    <t>135800711</t>
-  </si>
-  <si>
-    <t>135800735</t>
-  </si>
-  <si>
-    <t>135800747</t>
-  </si>
-  <si>
-    <t>135801128</t>
-  </si>
-  <si>
-    <t>135801230</t>
-  </si>
-  <si>
-    <t>135801278</t>
-  </si>
-  <si>
-    <t>135801390</t>
-  </si>
-  <si>
-    <t>135801442</t>
-  </si>
-  <si>
-    <t>135801653</t>
-  </si>
-  <si>
-    <t>135801689</t>
-  </si>
-  <si>
-    <t>135801726</t>
-  </si>
-  <si>
-    <t>135801731</t>
-  </si>
-  <si>
-    <t>135801756</t>
-  </si>
-  <si>
-    <t>135801761</t>
-  </si>
-  <si>
-    <t>135801822</t>
-  </si>
-  <si>
-    <t>135802073</t>
-  </si>
-  <si>
-    <t>135802152</t>
-  </si>
-  <si>
-    <t>135802229</t>
-  </si>
-  <si>
-    <t>135802331</t>
-  </si>
-  <si>
-    <t>135802438</t>
-  </si>
-  <si>
-    <t>135802541</t>
-  </si>
-  <si>
-    <t>135802647</t>
-  </si>
-  <si>
-    <t>135802697</t>
-  </si>
-  <si>
-    <t>135802701</t>
-  </si>
-  <si>
-    <t>135802813</t>
-  </si>
-  <si>
-    <t>135802875</t>
-  </si>
-  <si>
-    <t>135803202</t>
-  </si>
-  <si>
-    <t>135803396</t>
-  </si>
-  <si>
-    <t>135803430</t>
-  </si>
-  <si>
-    <t>135803478</t>
-  </si>
-  <si>
-    <t>135803755</t>
-  </si>
-  <si>
-    <t>135803839</t>
-  </si>
-  <si>
-    <t>135803870</t>
-  </si>
-  <si>
-    <t>135804085</t>
-  </si>
-  <si>
-    <t>135804152</t>
-  </si>
-  <si>
-    <t>135804177</t>
-  </si>
-  <si>
-    <t>135804418</t>
-  </si>
-  <si>
-    <t>135805086</t>
-  </si>
-  <si>
-    <t>135805127</t>
-  </si>
-  <si>
-    <t>135805160</t>
-  </si>
-  <si>
-    <t>135805189</t>
-  </si>
-  <si>
-    <t>135805214</t>
-  </si>
-  <si>
-    <t>135805287</t>
-  </si>
-  <si>
-    <t>135805670</t>
-  </si>
-  <si>
-    <t>135805722</t>
-  </si>
-  <si>
-    <t>135806011</t>
-  </si>
-  <si>
-    <t>135806073</t>
-  </si>
-  <si>
-    <t>135806364</t>
-  </si>
-  <si>
-    <t>135806458</t>
-  </si>
-  <si>
-    <t>135806463</t>
-  </si>
-  <si>
-    <t>135806494</t>
-  </si>
-  <si>
-    <t>135806540</t>
-  </si>
-  <si>
-    <t>135806730</t>
-  </si>
-  <si>
-    <t>135806823</t>
-  </si>
-  <si>
-    <t>135806871</t>
-  </si>
-  <si>
-    <t>135806940</t>
-  </si>
-  <si>
-    <t>135807108</t>
-  </si>
-  <si>
-    <t>135807281</t>
-  </si>
-  <si>
-    <t>135807335</t>
-  </si>
-  <si>
-    <t>135807416</t>
-  </si>
-  <si>
-    <t>135807718</t>
-  </si>
-  <si>
-    <t>135807734</t>
-  </si>
-  <si>
-    <t>135807784</t>
-  </si>
-  <si>
-    <t>135807935</t>
-  </si>
-  <si>
-    <t>135807951</t>
-  </si>
-  <si>
-    <t>135808010</t>
-  </si>
-  <si>
-    <t>135808011</t>
-  </si>
-  <si>
-    <t>135808027</t>
-  </si>
-  <si>
-    <t>135808244</t>
-  </si>
-  <si>
-    <t>135808252</t>
-  </si>
-  <si>
-    <t>135808376</t>
-  </si>
-  <si>
-    <t>135808458</t>
-  </si>
-  <si>
-    <t>135808812</t>
-  </si>
-  <si>
-    <t>135808997</t>
-  </si>
-  <si>
-    <t>135809050</t>
-  </si>
-  <si>
-    <t>135809115</t>
-  </si>
-  <si>
-    <t>135809173</t>
-  </si>
-  <si>
-    <t>135809230</t>
-  </si>
-  <si>
-    <t>135809266</t>
-  </si>
-  <si>
-    <t>135809481</t>
-  </si>
-  <si>
-    <t>135809535</t>
-  </si>
-  <si>
-    <t>135809550</t>
-  </si>
-  <si>
-    <t>135809887</t>
-  </si>
-  <si>
-    <t>135810012</t>
-  </si>
-  <si>
-    <t>135810480</t>
-  </si>
-  <si>
-    <t>135810685</t>
-  </si>
-  <si>
-    <t>135810908</t>
-  </si>
-  <si>
-    <t>135810916</t>
-  </si>
-  <si>
-    <t>135810971</t>
-  </si>
-  <si>
-    <t>135811117</t>
-  </si>
-  <si>
-    <t>135811315</t>
-  </si>
-  <si>
-    <t>135811411</t>
-  </si>
-  <si>
-    <t>135811419</t>
-  </si>
-  <si>
-    <t>135811495</t>
-  </si>
-  <si>
-    <t>135811516</t>
-  </si>
-  <si>
-    <t>135811627</t>
-  </si>
-  <si>
-    <t>135811709</t>
-  </si>
-  <si>
-    <t>135811760</t>
-  </si>
-  <si>
-    <t>135811881</t>
-  </si>
-  <si>
-    <t>135811891</t>
-  </si>
-  <si>
-    <t>135811984</t>
-  </si>
-  <si>
-    <t>135811987</t>
-  </si>
-  <si>
-    <t>135812131</t>
-  </si>
-  <si>
-    <t>135812284</t>
-  </si>
-  <si>
-    <t>135812293</t>
-  </si>
-  <si>
-    <t>135812315</t>
-  </si>
-  <si>
-    <t>135812466</t>
-  </si>
-  <si>
-    <t>135812637</t>
-  </si>
-  <si>
-    <t>135812753</t>
-  </si>
-  <si>
-    <t>135812967</t>
-  </si>
-  <si>
-    <t>135813044</t>
-  </si>
-  <si>
-    <t>135813155</t>
-  </si>
-  <si>
-    <t>135813200</t>
-  </si>
-  <si>
-    <t>135813843</t>
-  </si>
-  <si>
-    <t>135814079</t>
-  </si>
-  <si>
-    <t>135814171</t>
-  </si>
-  <si>
-    <t>135814266</t>
-  </si>
-  <si>
-    <t>135814338</t>
-  </si>
-  <si>
-    <t>135814543</t>
-  </si>
-  <si>
-    <t>135814570</t>
-  </si>
-  <si>
-    <t>135814609</t>
-  </si>
-  <si>
-    <t>135814879</t>
-  </si>
-  <si>
-    <t>135814904</t>
-  </si>
-  <si>
-    <t>135814953</t>
-  </si>
-  <si>
-    <t>135815199</t>
-  </si>
-  <si>
-    <t>135815209</t>
-  </si>
-  <si>
-    <t>135815418</t>
-  </si>
-  <si>
-    <t>135815518</t>
-  </si>
-  <si>
-    <t>135815643</t>
-  </si>
-  <si>
-    <t>135815667</t>
-  </si>
-  <si>
-    <t>135815672</t>
-  </si>
-  <si>
-    <t>135815689</t>
-  </si>
-  <si>
-    <t>135815984</t>
-  </si>
-  <si>
-    <t>135816251</t>
-  </si>
-  <si>
-    <t>135816255</t>
-  </si>
-  <si>
-    <t>135816308</t>
-  </si>
-  <si>
-    <t>135816438</t>
-  </si>
-  <si>
-    <t>135816530</t>
-  </si>
-  <si>
-    <t>135816548</t>
-  </si>
-  <si>
-    <t>135816609</t>
-  </si>
-  <si>
-    <t>135816613</t>
-  </si>
-  <si>
-    <t>135816665</t>
-  </si>
-  <si>
-    <t>135817115</t>
-  </si>
-  <si>
-    <t>135817138</t>
-  </si>
-  <si>
-    <t>135817179</t>
-  </si>
-  <si>
-    <t>135817240</t>
-  </si>
-  <si>
-    <t>135817318</t>
-  </si>
-  <si>
-    <t>135817371</t>
-  </si>
-  <si>
-    <t>135817452</t>
-  </si>
-  <si>
-    <t>135817621</t>
-  </si>
-  <si>
-    <t>135817675</t>
-  </si>
-  <si>
-    <t>135817939</t>
-  </si>
-  <si>
-    <t>135817976</t>
-  </si>
-  <si>
-    <t>135817978</t>
-  </si>
-  <si>
-    <t>135818050</t>
-  </si>
-  <si>
-    <t>135818070</t>
-  </si>
-  <si>
-    <t>135818569</t>
-  </si>
-  <si>
-    <t>135818640</t>
-  </si>
-  <si>
-    <t>135818699</t>
-  </si>
-  <si>
-    <t>135818843</t>
-  </si>
-  <si>
-    <t>135818851</t>
-  </si>
-  <si>
-    <t>135818943</t>
-  </si>
-  <si>
-    <t>135818945</t>
-  </si>
-  <si>
-    <t>135818952</t>
-  </si>
-  <si>
-    <t>135818953</t>
-  </si>
-  <si>
-    <t>135818983</t>
-  </si>
-  <si>
-    <t>135818995</t>
-  </si>
-  <si>
-    <t>135819106</t>
-  </si>
-  <si>
-    <t>135819154</t>
-  </si>
-  <si>
-    <t>135819185</t>
-  </si>
-  <si>
-    <t>135819203</t>
-  </si>
-  <si>
-    <t>135819240</t>
-  </si>
-  <si>
-    <t>135819327</t>
-  </si>
-  <si>
-    <t>135819627</t>
-  </si>
-  <si>
-    <t>135819651</t>
-  </si>
-  <si>
-    <t>135819751</t>
-  </si>
-  <si>
-    <t>135819959</t>
-  </si>
-  <si>
-    <t>135820028</t>
-  </si>
-  <si>
-    <t>135820095</t>
-  </si>
-  <si>
-    <t>135820157</t>
-  </si>
-  <si>
-    <t>135820216</t>
-  </si>
-  <si>
-    <t>135820283</t>
-  </si>
-  <si>
-    <t>135820314</t>
-  </si>
-  <si>
-    <t>135820319</t>
-  </si>
-  <si>
-    <t>135820410</t>
-  </si>
-  <si>
-    <t>135820585</t>
-  </si>
-  <si>
-    <t>135820637</t>
-  </si>
-  <si>
-    <t>135820684</t>
-  </si>
-  <si>
-    <t>135820738</t>
-  </si>
-  <si>
-    <t>135820787</t>
-  </si>
-  <si>
-    <t>135820874</t>
-  </si>
-  <si>
-    <t>135820917</t>
-  </si>
-  <si>
-    <t>135821015</t>
-  </si>
-  <si>
-    <t>135821081</t>
-  </si>
-  <si>
-    <t>135821148</t>
-  </si>
-  <si>
-    <t>135821216</t>
-  </si>
-  <si>
-    <t>135821361</t>
-  </si>
-  <si>
-    <t>135821428</t>
-  </si>
-  <si>
-    <t>135821481</t>
-  </si>
-  <si>
-    <t>135821485</t>
-  </si>
-  <si>
-    <t>135821489</t>
-  </si>
-  <si>
-    <t>135821541</t>
-  </si>
-  <si>
-    <t>135821562</t>
-  </si>
-  <si>
-    <t>135821656</t>
-  </si>
-  <si>
-    <t>135821810</t>
-  </si>
-  <si>
-    <t>135821936</t>
-  </si>
-  <si>
-    <t>135821952</t>
-  </si>
-  <si>
-    <t>135821979</t>
-  </si>
-  <si>
-    <t>135822109</t>
-  </si>
-  <si>
-    <t>135822128</t>
-  </si>
-  <si>
-    <t>135822142</t>
-  </si>
-  <si>
-    <t>135822162</t>
-  </si>
-  <si>
-    <t>135822293</t>
-  </si>
-  <si>
-    <t>135822352</t>
-  </si>
-  <si>
-    <t>135822464</t>
-  </si>
-  <si>
-    <t>135822572</t>
-  </si>
-  <si>
-    <t>135822660</t>
-  </si>
-  <si>
-    <t>135822825</t>
-  </si>
-  <si>
-    <t>135822837</t>
-  </si>
-  <si>
-    <t>135822900</t>
-  </si>
-  <si>
-    <t>135822954</t>
-  </si>
-  <si>
-    <t>135823314</t>
-  </si>
-  <si>
-    <t>135823368</t>
-  </si>
-  <si>
-    <t>135823371</t>
-  </si>
-  <si>
-    <t>135823420</t>
-  </si>
-  <si>
-    <t>135823453</t>
-  </si>
-  <si>
-    <t>135823479</t>
-  </si>
-  <si>
-    <t>135823498</t>
-  </si>
-  <si>
-    <t>135823506</t>
-  </si>
-  <si>
-    <t>135823600</t>
-  </si>
-  <si>
-    <t>135823689</t>
-  </si>
-  <si>
-    <t>135823760</t>
-  </si>
-  <si>
-    <t>135823843</t>
-  </si>
-  <si>
-    <t>135823871</t>
-  </si>
-  <si>
-    <t>135823920</t>
-  </si>
-  <si>
-    <t>135823942</t>
-  </si>
-  <si>
-    <t>135823968</t>
-  </si>
-  <si>
-    <t>135824078</t>
-  </si>
-  <si>
-    <t>135824219</t>
-  </si>
-  <si>
-    <t>135824237</t>
-  </si>
-  <si>
-    <t>135824283</t>
-  </si>
-  <si>
-    <t>135824613</t>
-  </si>
-  <si>
-    <t>135824712</t>
-  </si>
-  <si>
-    <t>135824822</t>
-  </si>
-  <si>
-    <t>135824911</t>
-  </si>
-  <si>
-    <t>135824943</t>
-  </si>
-  <si>
-    <t>135824981</t>
-  </si>
-  <si>
-    <t>135825229</t>
-  </si>
-  <si>
-    <t>135825263</t>
-  </si>
-  <si>
-    <t>135825299</t>
-  </si>
-  <si>
-    <t>135825376</t>
-  </si>
-  <si>
-    <t>135825479</t>
-  </si>
-  <si>
-    <t>135825494</t>
-  </si>
-  <si>
-    <t>135825641</t>
-  </si>
-  <si>
-    <t>135825651</t>
-  </si>
-  <si>
-    <t>135825721</t>
-  </si>
-  <si>
-    <t>135825872</t>
-  </si>
-  <si>
-    <t>135825904</t>
-  </si>
-  <si>
-    <t>135825990</t>
-  </si>
-  <si>
-    <t>135826156</t>
-  </si>
-  <si>
-    <t>135826400</t>
-  </si>
-  <si>
-    <t>135826844</t>
-  </si>
-  <si>
-    <t>135826967</t>
-  </si>
-  <si>
-    <t>135827115</t>
-  </si>
-  <si>
-    <t>135827190</t>
-  </si>
-  <si>
-    <t>135827293</t>
-  </si>
-  <si>
-    <t>135827311</t>
-  </si>
-  <si>
-    <t>135827335</t>
-  </si>
-  <si>
-    <t>135827339</t>
-  </si>
-  <si>
-    <t>135827376</t>
-  </si>
-  <si>
-    <t>135827483</t>
-  </si>
-  <si>
-    <t>135827594</t>
-  </si>
-  <si>
-    <t>135827645</t>
-  </si>
-  <si>
-    <t>135827714</t>
-  </si>
-  <si>
-    <t>135827840</t>
-  </si>
-  <si>
-    <t>135827920</t>
-  </si>
-  <si>
-    <t>135827921</t>
-  </si>
-  <si>
-    <t>135827976</t>
-  </si>
-  <si>
-    <t>135828028</t>
-  </si>
-  <si>
-    <t>135828032</t>
-  </si>
-  <si>
-    <t>135828052</t>
-  </si>
-  <si>
-    <t>135828054</t>
-  </si>
-  <si>
-    <t>135828076</t>
-  </si>
-  <si>
-    <t>135828131</t>
-  </si>
-  <si>
-    <t>135828170</t>
-  </si>
-  <si>
-    <t>135828234</t>
-  </si>
-  <si>
-    <t>135828239</t>
-  </si>
-  <si>
-    <t>135828269</t>
-  </si>
-  <si>
-    <t>135828472</t>
-  </si>
-  <si>
-    <t>135828497</t>
-  </si>
-  <si>
-    <t>135828612</t>
-  </si>
-  <si>
-    <t>135828662</t>
-  </si>
-  <si>
-    <t>135828675</t>
-  </si>
-  <si>
-    <t>135828717</t>
-  </si>
-  <si>
-    <t>135828718</t>
-  </si>
-  <si>
-    <t>135828831</t>
-  </si>
-  <si>
-    <t>135828853</t>
-  </si>
-  <si>
-    <t>135828858</t>
-  </si>
-  <si>
-    <t>135828878</t>
-  </si>
-  <si>
-    <t>135829029</t>
-  </si>
-  <si>
-    <t>135829044</t>
-  </si>
-  <si>
-    <t>135829075</t>
-  </si>
-  <si>
-    <t>135829170</t>
-  </si>
-  <si>
-    <t>135829269</t>
-  </si>
-  <si>
-    <t>135829295</t>
-  </si>
-  <si>
-    <t>135829385</t>
-  </si>
-  <si>
-    <t>135829406</t>
-  </si>
-  <si>
-    <t>135829469</t>
-  </si>
-  <si>
-    <t>135829813</t>
-  </si>
-  <si>
-    <t>135829821</t>
-  </si>
-  <si>
-    <t>135829907</t>
-  </si>
-  <si>
-    <t>135830070</t>
-  </si>
-  <si>
-    <t>135830071</t>
-  </si>
-  <si>
-    <t>135830164</t>
-  </si>
-  <si>
-    <t>135830188</t>
-  </si>
-  <si>
-    <t>135830360</t>
-  </si>
-  <si>
-    <t>135830423</t>
-  </si>
-  <si>
-    <t>135830440</t>
-  </si>
-  <si>
-    <t>135830556</t>
-  </si>
-  <si>
-    <t>135830654</t>
-  </si>
-  <si>
-    <t>135830801</t>
-  </si>
-  <si>
-    <t>135830878</t>
-  </si>
-  <si>
-    <t>135830883</t>
-  </si>
-  <si>
-    <t>135830955</t>
-  </si>
-  <si>
-    <t>135831004</t>
-  </si>
-  <si>
-    <t>135831014</t>
-  </si>
-  <si>
-    <t>135831209</t>
-  </si>
-  <si>
-    <t>135831292</t>
-  </si>
-  <si>
-    <t>135831295</t>
-  </si>
-  <si>
-    <t>135831403</t>
-  </si>
-  <si>
-    <t>135831419</t>
-  </si>
-  <si>
-    <t>135831420</t>
-  </si>
-  <si>
-    <t>135831459</t>
-  </si>
-  <si>
-    <t>135831574</t>
-  </si>
-  <si>
-    <t>135831603</t>
-  </si>
-  <si>
-    <t>135831939</t>
-  </si>
-  <si>
-    <t>135831958</t>
-  </si>
-  <si>
-    <t>135831979</t>
-  </si>
-  <si>
-    <t>135832076</t>
-  </si>
-  <si>
-    <t>135832149</t>
-  </si>
-  <si>
-    <t>135832158</t>
-  </si>
-  <si>
-    <t>135832208</t>
-  </si>
-  <si>
-    <t>135832296</t>
-  </si>
-  <si>
-    <t>135832381</t>
-  </si>
-  <si>
-    <t>135832424</t>
-  </si>
-  <si>
-    <t>135832425</t>
-  </si>
-  <si>
-    <t>135832538</t>
-  </si>
-  <si>
-    <t>135832547</t>
-  </si>
-  <si>
-    <t>135832689</t>
-  </si>
-  <si>
-    <t>135832716</t>
-  </si>
-  <si>
-    <t>135832787</t>
-  </si>
-  <si>
-    <t>135832796</t>
-  </si>
-  <si>
-    <t>135833012</t>
-  </si>
-  <si>
-    <t>135833300</t>
-  </si>
-  <si>
-    <t>135833321</t>
-  </si>
-  <si>
-    <t>135833328</t>
-  </si>
-  <si>
-    <t>135833450</t>
-  </si>
-  <si>
-    <t>135833506</t>
-  </si>
-  <si>
-    <t>135833533</t>
-  </si>
-  <si>
-    <t>135833675</t>
-  </si>
-  <si>
-    <t>135833685</t>
-  </si>
-  <si>
-    <t>135833782</t>
-  </si>
-  <si>
-    <t>135833811</t>
-  </si>
-  <si>
-    <t>135833852</t>
-  </si>
-  <si>
-    <t>135833855</t>
-  </si>
-  <si>
-    <t>135833880</t>
-  </si>
-  <si>
-    <t>135833920</t>
-  </si>
-  <si>
-    <t>135834055</t>
-  </si>
-  <si>
-    <t>135834089</t>
-  </si>
-  <si>
-    <t>135834603</t>
-  </si>
-  <si>
-    <t>135834661</t>
-  </si>
-  <si>
-    <t>135834818</t>
-  </si>
-  <si>
-    <t>135834930</t>
-  </si>
-  <si>
-    <t>135834978</t>
-  </si>
-  <si>
-    <t>135835042</t>
-  </si>
-  <si>
-    <t>135835112</t>
-  </si>
-  <si>
-    <t>135835202</t>
-  </si>
-  <si>
-    <t>135835238</t>
-  </si>
-  <si>
-    <t>135835278</t>
-  </si>
-  <si>
-    <t>135835282</t>
-  </si>
-  <si>
-    <t>135835356</t>
-  </si>
-  <si>
-    <t>135835392</t>
-  </si>
-  <si>
-    <t>135835438</t>
-  </si>
-  <si>
-    <t>135835624</t>
-  </si>
-  <si>
-    <t>135835747</t>
-  </si>
-  <si>
-    <t>135835759</t>
-  </si>
-  <si>
-    <t>135835787</t>
-  </si>
-  <si>
-    <t>135835845</t>
-  </si>
-  <si>
-    <t>135836160</t>
-  </si>
-  <si>
-    <t>135836190</t>
-  </si>
-  <si>
-    <t>135836211</t>
-  </si>
-  <si>
-    <t>135836305</t>
-  </si>
-  <si>
-    <t>135836307</t>
-  </si>
-  <si>
-    <t>135836397</t>
-  </si>
-  <si>
-    <t>135836439</t>
-  </si>
-  <si>
-    <t>135836553</t>
-  </si>
-  <si>
-    <t>135836605</t>
-  </si>
-  <si>
-    <t>135836606</t>
-  </si>
-  <si>
-    <t>135836620</t>
-  </si>
-  <si>
-    <t>135836683</t>
-  </si>
-  <si>
-    <t>135836691</t>
-  </si>
-  <si>
-    <t>135836782</t>
-  </si>
-  <si>
-    <t>135836837</t>
-  </si>
-  <si>
-    <t>135836845</t>
-  </si>
-  <si>
-    <t>135836988</t>
-  </si>
-  <si>
-    <t>135837068</t>
-  </si>
-  <si>
-    <t>135837322</t>
-  </si>
-  <si>
-    <t>135837452</t>
-  </si>
-  <si>
-    <t>135837560</t>
-  </si>
-  <si>
-    <t>135837564</t>
-  </si>
-  <si>
-    <t>135837715</t>
-  </si>
-  <si>
-    <t>135837745</t>
-  </si>
-  <si>
-    <t>135837762</t>
-  </si>
-  <si>
-    <t>135837814</t>
-  </si>
-  <si>
-    <t>135837817</t>
-  </si>
-  <si>
-    <t>135837860</t>
-  </si>
-  <si>
-    <t>135837893</t>
-  </si>
-  <si>
-    <t>135837949</t>
-  </si>
-  <si>
-    <t>135838004</t>
-  </si>
-  <si>
-    <t>135838054</t>
-  </si>
-  <si>
-    <t>135838073</t>
-  </si>
-  <si>
-    <t>135838192</t>
-  </si>
-  <si>
-    <t>135838333</t>
-  </si>
-  <si>
-    <t>135838337</t>
-  </si>
-  <si>
-    <t>135838359</t>
-  </si>
-  <si>
-    <t>135838367</t>
-  </si>
-  <si>
-    <t>135838412</t>
-  </si>
-  <si>
-    <t>135838481</t>
-  </si>
-  <si>
-    <t>135838514</t>
-  </si>
-  <si>
-    <t>135838603</t>
-  </si>
-  <si>
-    <t>135838621</t>
-  </si>
-  <si>
-    <t>135838638</t>
-  </si>
-  <si>
-    <t>135838650</t>
-  </si>
-  <si>
-    <t>135838716</t>
-  </si>
-  <si>
-    <t>135838767</t>
-  </si>
-  <si>
-    <t>135838836</t>
-  </si>
-  <si>
-    <t>135838857</t>
-  </si>
-  <si>
-    <t>135838992</t>
-  </si>
-  <si>
-    <t>135839133</t>
-  </si>
-  <si>
-    <t>135839259</t>
-  </si>
-  <si>
-    <t>135839426</t>
-  </si>
-  <si>
-    <t>135839448</t>
-  </si>
-  <si>
-    <t>135839657</t>
-  </si>
-  <si>
-    <t>135839746</t>
-  </si>
-  <si>
-    <t>135839807</t>
-  </si>
-  <si>
-    <t>135839839</t>
-  </si>
-  <si>
-    <t>135839887</t>
-  </si>
-  <si>
-    <t>135839899</t>
-  </si>
-  <si>
-    <t>135839911</t>
-  </si>
-  <si>
-    <t>135839933</t>
-  </si>
-  <si>
-    <t>135839954</t>
-  </si>
-  <si>
-    <t>135840144</t>
-  </si>
-  <si>
-    <t>135840245</t>
-  </si>
-  <si>
-    <t>135840382</t>
-  </si>
-  <si>
-    <t>135840391</t>
-  </si>
-  <si>
-    <t>135840421</t>
-  </si>
-  <si>
-    <t>135840526</t>
-  </si>
-  <si>
-    <t>135840576</t>
-  </si>
-  <si>
-    <t>135840689</t>
-  </si>
-  <si>
-    <t>135840795</t>
-  </si>
-  <si>
-    <t>135840855</t>
-  </si>
-  <si>
-    <t>135840890</t>
-  </si>
-  <si>
-    <t>135840893</t>
-  </si>
-  <si>
-    <t>135840930</t>
-  </si>
-  <si>
-    <t>135841042</t>
-  </si>
-  <si>
-    <t>135841138</t>
-  </si>
-  <si>
-    <t>135841150</t>
-  </si>
-  <si>
-    <t>135841180</t>
-  </si>
-  <si>
-    <t>135841201</t>
-  </si>
-  <si>
-    <t>135841241</t>
-  </si>
-  <si>
-    <t>135841250</t>
-  </si>
-  <si>
-    <t>135841319</t>
-  </si>
-  <si>
-    <t>135841469</t>
-  </si>
-  <si>
-    <t>135841482</t>
-  </si>
-  <si>
-    <t>135841507</t>
-  </si>
-  <si>
-    <t>135841523</t>
-  </si>
-  <si>
-    <t>135841546</t>
-  </si>
-  <si>
-    <t>135841572</t>
-  </si>
-  <si>
-    <t>135841650</t>
-  </si>
-  <si>
-    <t>135841654</t>
-  </si>
-  <si>
-    <t>135841658</t>
-  </si>
-  <si>
-    <t>135841724</t>
-  </si>
-  <si>
-    <t>135841784</t>
-  </si>
-  <si>
-    <t>135841931</t>
-  </si>
-  <si>
-    <t>135841932</t>
-  </si>
-  <si>
-    <t>135841942</t>
-  </si>
-  <si>
-    <t>135842007</t>
-  </si>
-  <si>
-    <t>135842008</t>
-  </si>
-  <si>
-    <t>135842040</t>
-  </si>
-  <si>
-    <t>135842179</t>
-  </si>
-  <si>
-    <t>135842181</t>
-  </si>
-  <si>
-    <t>135842317</t>
-  </si>
-  <si>
-    <t>135842323</t>
-  </si>
-  <si>
-    <t>135842346</t>
-  </si>
-  <si>
-    <t>135842385</t>
-  </si>
-  <si>
-    <t>135842403</t>
-  </si>
-  <si>
-    <t>135842411</t>
-  </si>
-  <si>
-    <t>135842592</t>
-  </si>
-  <si>
-    <t>135842597</t>
-  </si>
-  <si>
-    <t>135842699</t>
-  </si>
-  <si>
-    <t>135842712</t>
-  </si>
-  <si>
-    <t>135842717</t>
-  </si>
-  <si>
-    <t>135842751</t>
-  </si>
-  <si>
-    <t>135842778</t>
-  </si>
-  <si>
-    <t>135842886</t>
-  </si>
-  <si>
-    <t>135842945</t>
-  </si>
-  <si>
-    <t>135843249</t>
-  </si>
-  <si>
-    <t>135843251</t>
-  </si>
-  <si>
-    <t>135843259</t>
-  </si>
-  <si>
-    <t>135843389</t>
-  </si>
-  <si>
-    <t>135843453</t>
-  </si>
-  <si>
-    <t>135843464</t>
-  </si>
-  <si>
-    <t>135843465</t>
-  </si>
-  <si>
-    <t>135843502</t>
-  </si>
-  <si>
-    <t>135843505</t>
-  </si>
-  <si>
-    <t>135843604</t>
-  </si>
-  <si>
-    <t>135843675</t>
-  </si>
-  <si>
-    <t>135843679</t>
-  </si>
-  <si>
-    <t>135843710</t>
-  </si>
-  <si>
-    <t>135843749</t>
-  </si>
-  <si>
-    <t>135843758</t>
-  </si>
-  <si>
-    <t>135843775</t>
-  </si>
-  <si>
-    <t>135843891</t>
-  </si>
-  <si>
-    <t>135843895</t>
-  </si>
-  <si>
-    <t>135843951</t>
-  </si>
-  <si>
-    <t>135844039</t>
-  </si>
-  <si>
-    <t>135844075</t>
-  </si>
-  <si>
-    <t>135844098</t>
-  </si>
-  <si>
-    <t>135844139</t>
-  </si>
-  <si>
-    <t>135844154</t>
-  </si>
-  <si>
-    <t>135844180</t>
-  </si>
-  <si>
-    <t>135844223</t>
-  </si>
-  <si>
-    <t>135844233</t>
-  </si>
-  <si>
-    <t>135844242</t>
-  </si>
-  <si>
-    <t>135844248</t>
-  </si>
-  <si>
-    <t>135844266</t>
-  </si>
-  <si>
-    <t>135844292</t>
-  </si>
-  <si>
-    <t>135844326</t>
-  </si>
-  <si>
-    <t>135844328</t>
-  </si>
-  <si>
-    <t>135844329</t>
-  </si>
-  <si>
-    <t>135844347</t>
-  </si>
-  <si>
-    <t>135844409</t>
-  </si>
-  <si>
-    <t>135844482</t>
-  </si>
-  <si>
-    <t>135844489</t>
-  </si>
-  <si>
-    <t>135844588</t>
-  </si>
-  <si>
-    <t>135844593</t>
-  </si>
-  <si>
-    <t>135844610</t>
-  </si>
-  <si>
-    <t>135844669</t>
-  </si>
-  <si>
-    <t>135844704</t>
-  </si>
-  <si>
-    <t>135844733</t>
-  </si>
-  <si>
-    <t>135844743</t>
-  </si>
-  <si>
-    <t>135844784</t>
-  </si>
-  <si>
-    <t>135844834</t>
-  </si>
-  <si>
-    <t>135844861</t>
-  </si>
-  <si>
-    <t>135844890</t>
-  </si>
-  <si>
-    <t>135844898</t>
-  </si>
-  <si>
-    <t>135844925</t>
-  </si>
-  <si>
-    <t>135844980</t>
-  </si>
-  <si>
-    <t>135845001</t>
-  </si>
-  <si>
-    <t>135845030</t>
-  </si>
-  <si>
-    <t>135845035</t>
-  </si>
-  <si>
-    <t>135845050</t>
-  </si>
-  <si>
-    <t>135845083</t>
-  </si>
-  <si>
-    <t>135845084</t>
-  </si>
-  <si>
-    <t>135845159</t>
-  </si>
-  <si>
-    <t>135845212</t>
-  </si>
-  <si>
-    <t>135845213</t>
-  </si>
-  <si>
-    <t>135845259</t>
-  </si>
-  <si>
-    <t>135845274</t>
-  </si>
-  <si>
-    <t>135845297</t>
-  </si>
-  <si>
-    <t>135845300</t>
-  </si>
-  <si>
-    <t>135845342</t>
-  </si>
-  <si>
-    <t>135845344</t>
-  </si>
-  <si>
-    <t>135845371</t>
-  </si>
-  <si>
-    <t>135845403</t>
-  </si>
-  <si>
-    <t>135845414</t>
-  </si>
-  <si>
-    <t>135845416</t>
-  </si>
-  <si>
-    <t>135845477</t>
-  </si>
-  <si>
-    <t>135845512</t>
-  </si>
-  <si>
-    <t>135845690</t>
-  </si>
-  <si>
-    <t>135845709</t>
-  </si>
-  <si>
-    <t>135845757</t>
-  </si>
-  <si>
-    <t>135845809</t>
-  </si>
-  <si>
-    <t>135845827</t>
-  </si>
-  <si>
-    <t>135845841</t>
-  </si>
-  <si>
-    <t>135845899</t>
-  </si>
-  <si>
-    <t>135845903</t>
-  </si>
-  <si>
-    <t>135845913</t>
-  </si>
-  <si>
-    <t>135845938</t>
-  </si>
-  <si>
-    <t>135845999</t>
-  </si>
-  <si>
-    <t>135846029</t>
-  </si>
-  <si>
-    <t>135846079</t>
-  </si>
-  <si>
-    <t>135846094</t>
-  </si>
-  <si>
-    <t>135846128</t>
-  </si>
-  <si>
-    <t>135846154</t>
-  </si>
-  <si>
-    <t>135846217</t>
-  </si>
-  <si>
-    <t>135846339</t>
-  </si>
-  <si>
-    <t>135846375</t>
-  </si>
-  <si>
-    <t>135846513</t>
-  </si>
-  <si>
-    <t>135846518</t>
-  </si>
-  <si>
-    <t>135846553</t>
-  </si>
-  <si>
-    <t>135846617</t>
-  </si>
-  <si>
-    <t>135846639</t>
-  </si>
-  <si>
-    <t>135846674</t>
-  </si>
-  <si>
-    <t>135846729</t>
-  </si>
-  <si>
-    <t>135846783</t>
-  </si>
-  <si>
-    <t>135846901</t>
-  </si>
-  <si>
-    <t>135846933</t>
-  </si>
-  <si>
-    <t>135846975</t>
-  </si>
-  <si>
-    <t>135846991</t>
-  </si>
-  <si>
-    <t>135847002</t>
-  </si>
-  <si>
-    <t>135847032</t>
-  </si>
-  <si>
-    <t>135847077</t>
-  </si>
-  <si>
-    <t>135847087</t>
-  </si>
-  <si>
-    <t>135847098</t>
-  </si>
-  <si>
-    <t>135847129</t>
-  </si>
-  <si>
-    <t>135847135</t>
-  </si>
-  <si>
-    <t>135847183</t>
-  </si>
-  <si>
-    <t>135847184</t>
-  </si>
-  <si>
-    <t>135847271</t>
-  </si>
-  <si>
-    <t>135847309</t>
-  </si>
-  <si>
-    <t>135847332</t>
-  </si>
-  <si>
-    <t>135847416</t>
-  </si>
-  <si>
-    <t>135847471</t>
-  </si>
-  <si>
-    <t>135847552</t>
-  </si>
-  <si>
-    <t>135847593</t>
-  </si>
-  <si>
-    <t>135847793</t>
-  </si>
-  <si>
-    <t>135847814</t>
-  </si>
-  <si>
-    <t>135847853</t>
-  </si>
-  <si>
-    <t>135847959</t>
+    <t>130908187</t>
+  </si>
+  <si>
+    <t>130970593</t>
+  </si>
+  <si>
+    <t>130977955</t>
+  </si>
+  <si>
+    <t>131006556</t>
+  </si>
+  <si>
+    <t>131173886</t>
+  </si>
+  <si>
+    <t>131187274</t>
+  </si>
+  <si>
+    <t>131310240</t>
+  </si>
+  <si>
+    <t>131444174</t>
+  </si>
+  <si>
+    <t>131581954</t>
+  </si>
+  <si>
+    <t>131638564</t>
+  </si>
+  <si>
+    <t>131714833</t>
+  </si>
+  <si>
+    <t>131731182</t>
+  </si>
+  <si>
+    <t>131770328</t>
+  </si>
+  <si>
+    <t>131783113</t>
+  </si>
+  <si>
+    <t>131785512</t>
+  </si>
+  <si>
+    <t>131846922</t>
+  </si>
+  <si>
+    <t>131852057</t>
+  </si>
+  <si>
+    <t>132019545</t>
+  </si>
+  <si>
+    <t>132184140</t>
+  </si>
+  <si>
+    <t>132240082</t>
+  </si>
+  <si>
+    <t>132241814</t>
+  </si>
+  <si>
+    <t>132279770</t>
+  </si>
+  <si>
+    <t>132300244</t>
+  </si>
+  <si>
+    <t>132348002</t>
+  </si>
+  <si>
+    <t>132371853</t>
+  </si>
+  <si>
+    <t>132461208</t>
+  </si>
+  <si>
+    <t>132518081</t>
+  </si>
+  <si>
+    <t>132535282</t>
+  </si>
+  <si>
+    <t>132595204</t>
+  </si>
+  <si>
+    <t>132663119</t>
+  </si>
+  <si>
+    <t>132696734</t>
+  </si>
+  <si>
+    <t>132697911</t>
+  </si>
+  <si>
+    <t>132919313</t>
+  </si>
+  <si>
+    <t>132953721</t>
+  </si>
+  <si>
+    <t>133249938</t>
+  </si>
+  <si>
+    <t>133272252</t>
+  </si>
+  <si>
+    <t>133309201</t>
+  </si>
+  <si>
+    <t>133316984</t>
+  </si>
+  <si>
+    <t>133494691</t>
+  </si>
+  <si>
+    <t>133531178</t>
+  </si>
+  <si>
+    <t>133537749</t>
+  </si>
+  <si>
+    <t>133586912</t>
+  </si>
+  <si>
+    <t>133704582</t>
+  </si>
+  <si>
+    <t>133710045</t>
+  </si>
+  <si>
+    <t>133827605</t>
+  </si>
+  <si>
+    <t>133837282</t>
+  </si>
+  <si>
+    <t>133885311</t>
+  </si>
+  <si>
+    <t>133911022</t>
+  </si>
+  <si>
+    <t>133964543</t>
+  </si>
+  <si>
+    <t>133981264</t>
+  </si>
+  <si>
+    <t>134013622</t>
+  </si>
+  <si>
+    <t>134061307</t>
+  </si>
+  <si>
+    <t>134214240</t>
+  </si>
+  <si>
+    <t>134225360</t>
+  </si>
+  <si>
+    <t>134246962</t>
+  </si>
+  <si>
+    <t>134251671</t>
+  </si>
+  <si>
+    <t>134253401</t>
+  </si>
+  <si>
+    <t>134292432</t>
+  </si>
+  <si>
+    <t>134342502</t>
+  </si>
+  <si>
+    <t>134396785</t>
+  </si>
+  <si>
+    <t>134503419</t>
+  </si>
+  <si>
+    <t>134543230</t>
+  </si>
+  <si>
+    <t>134556767</t>
+  </si>
+  <si>
+    <t>134892479</t>
+  </si>
+  <si>
+    <t>134927283</t>
+  </si>
+  <si>
+    <t>135031671</t>
+  </si>
+  <si>
+    <t>135087189</t>
+  </si>
+  <si>
+    <t>135284151</t>
+  </si>
+  <si>
+    <t>135404834</t>
+  </si>
+  <si>
+    <t>135579066</t>
+  </si>
+  <si>
+    <t>135709752</t>
+  </si>
+  <si>
+    <t>135722339</t>
+  </si>
+  <si>
+    <t>135850238</t>
+  </si>
+  <si>
+    <t>135850396</t>
+  </si>
+  <si>
+    <t>135850447</t>
+  </si>
+  <si>
+    <t>135850545</t>
+  </si>
+  <si>
+    <t>135850632</t>
+  </si>
+  <si>
+    <t>135850733</t>
+  </si>
+  <si>
+    <t>135851023</t>
+  </si>
+  <si>
+    <t>135851311</t>
+  </si>
+  <si>
+    <t>135851912</t>
+  </si>
+  <si>
+    <t>135851930</t>
+  </si>
+  <si>
+    <t>135852084</t>
+  </si>
+  <si>
+    <t>135852300</t>
+  </si>
+  <si>
+    <t>135852381</t>
+  </si>
+  <si>
+    <t>135852418</t>
+  </si>
+  <si>
+    <t>135852448</t>
+  </si>
+  <si>
+    <t>135852701</t>
+  </si>
+  <si>
+    <t>135852815</t>
+  </si>
+  <si>
+    <t>135852889</t>
+  </si>
+  <si>
+    <t>135852943</t>
+  </si>
+  <si>
+    <t>135853074</t>
+  </si>
+  <si>
+    <t>135853208</t>
+  </si>
+  <si>
+    <t>135853352</t>
+  </si>
+  <si>
+    <t>135853575</t>
+  </si>
+  <si>
+    <t>135853654</t>
+  </si>
+  <si>
+    <t>135853705</t>
+  </si>
+  <si>
+    <t>135853871</t>
+  </si>
+  <si>
+    <t>135854001</t>
+  </si>
+  <si>
+    <t>135854012</t>
+  </si>
+  <si>
+    <t>135854028</t>
+  </si>
+  <si>
+    <t>135854185</t>
+  </si>
+  <si>
+    <t>135854460</t>
+  </si>
+  <si>
+    <t>135854486</t>
+  </si>
+  <si>
+    <t>135854998</t>
+  </si>
+  <si>
+    <t>135855053</t>
+  </si>
+  <si>
+    <t>135855423</t>
+  </si>
+  <si>
+    <t>135855567</t>
+  </si>
+  <si>
+    <t>135855767</t>
+  </si>
+  <si>
+    <t>135856016</t>
+  </si>
+  <si>
+    <t>135856075</t>
+  </si>
+  <si>
+    <t>135856160</t>
+  </si>
+  <si>
+    <t>135856203</t>
+  </si>
+  <si>
+    <t>135856221</t>
+  </si>
+  <si>
+    <t>135856427</t>
+  </si>
+  <si>
+    <t>135856612</t>
+  </si>
+  <si>
+    <t>135856749</t>
+  </si>
+  <si>
+    <t>135856772</t>
+  </si>
+  <si>
+    <t>135856825</t>
+  </si>
+  <si>
+    <t>135856973</t>
+  </si>
+  <si>
+    <t>135857044</t>
+  </si>
+  <si>
+    <t>135857139</t>
+  </si>
+  <si>
+    <t>135857333</t>
+  </si>
+  <si>
+    <t>135857367</t>
+  </si>
+  <si>
+    <t>135857519</t>
+  </si>
+  <si>
+    <t>135857556</t>
+  </si>
+  <si>
+    <t>135857564</t>
+  </si>
+  <si>
+    <t>135857704</t>
+  </si>
+  <si>
+    <t>135857887</t>
+  </si>
+  <si>
+    <t>135857992</t>
+  </si>
+  <si>
+    <t>135858019</t>
+  </si>
+  <si>
+    <t>135858127</t>
+  </si>
+  <si>
+    <t>135858189</t>
+  </si>
+  <si>
+    <t>135858276</t>
+  </si>
+  <si>
+    <t>135858367</t>
+  </si>
+  <si>
+    <t>135858558</t>
+  </si>
+  <si>
+    <t>135858579</t>
+  </si>
+  <si>
+    <t>135858660</t>
+  </si>
+  <si>
+    <t>135858833</t>
+  </si>
+  <si>
+    <t>135858945</t>
+  </si>
+  <si>
+    <t>135858977</t>
+  </si>
+  <si>
+    <t>135859226</t>
+  </si>
+  <si>
+    <t>135859247</t>
+  </si>
+  <si>
+    <t>135859454</t>
+  </si>
+  <si>
+    <t>135859799</t>
+  </si>
+  <si>
+    <t>135859836</t>
+  </si>
+  <si>
+    <t>135859880</t>
+  </si>
+  <si>
+    <t>135859890</t>
+  </si>
+  <si>
+    <t>135859901</t>
+  </si>
+  <si>
+    <t>135859950</t>
+  </si>
+  <si>
+    <t>135860082</t>
+  </si>
+  <si>
+    <t>135860293</t>
+  </si>
+  <si>
+    <t>135860399</t>
+  </si>
+  <si>
+    <t>135860445</t>
+  </si>
+  <si>
+    <t>135860770</t>
+  </si>
+  <si>
+    <t>135860876</t>
+  </si>
+  <si>
+    <t>135860950</t>
+  </si>
+  <si>
+    <t>135861133</t>
+  </si>
+  <si>
+    <t>135861386</t>
+  </si>
+  <si>
+    <t>135861474</t>
+  </si>
+  <si>
+    <t>135861631</t>
+  </si>
+  <si>
+    <t>135861762</t>
+  </si>
+  <si>
+    <t>135861824</t>
+  </si>
+  <si>
+    <t>135861878</t>
+  </si>
+  <si>
+    <t>135862005</t>
+  </si>
+  <si>
+    <t>135862420</t>
+  </si>
+  <si>
+    <t>135862427</t>
+  </si>
+  <si>
+    <t>135862467</t>
+  </si>
+  <si>
+    <t>135862684</t>
+  </si>
+  <si>
+    <t>135862723</t>
+  </si>
+  <si>
+    <t>135862763</t>
+  </si>
+  <si>
+    <t>135862778</t>
+  </si>
+  <si>
+    <t>135862792</t>
+  </si>
+  <si>
+    <t>135862955</t>
+  </si>
+  <si>
+    <t>135862967</t>
+  </si>
+  <si>
+    <t>135863406</t>
+  </si>
+  <si>
+    <t>135863437</t>
+  </si>
+  <si>
+    <t>135863566</t>
+  </si>
+  <si>
+    <t>135863726</t>
+  </si>
+  <si>
+    <t>135864048</t>
+  </si>
+  <si>
+    <t>135864076</t>
+  </si>
+  <si>
+    <t>135864249</t>
+  </si>
+  <si>
+    <t>135864337</t>
+  </si>
+  <si>
+    <t>135864388</t>
+  </si>
+  <si>
+    <t>135864407</t>
+  </si>
+  <si>
+    <t>135864462</t>
+  </si>
+  <si>
+    <t>135864547</t>
+  </si>
+  <si>
+    <t>135864683</t>
+  </si>
+  <si>
+    <t>135865054</t>
+  </si>
+  <si>
+    <t>135865282</t>
+  </si>
+  <si>
+    <t>135865305</t>
+  </si>
+  <si>
+    <t>135865631</t>
+  </si>
+  <si>
+    <t>135865779</t>
+  </si>
+  <si>
+    <t>135865877</t>
+  </si>
+  <si>
+    <t>135865908</t>
+  </si>
+  <si>
+    <t>135865941</t>
+  </si>
+  <si>
+    <t>135866066</t>
+  </si>
+  <si>
+    <t>135866102</t>
+  </si>
+  <si>
+    <t>135866728</t>
+  </si>
+  <si>
+    <t>135866735</t>
+  </si>
+  <si>
+    <t>135866838</t>
+  </si>
+  <si>
+    <t>135866849</t>
+  </si>
+  <si>
+    <t>135866868</t>
+  </si>
+  <si>
+    <t>135867029</t>
+  </si>
+  <si>
+    <t>135867126</t>
+  </si>
+  <si>
+    <t>135867298</t>
+  </si>
+  <si>
+    <t>135867379</t>
+  </si>
+  <si>
+    <t>135867440</t>
+  </si>
+  <si>
+    <t>135867498</t>
+  </si>
+  <si>
+    <t>135867635</t>
+  </si>
+  <si>
+    <t>135867682</t>
+  </si>
+  <si>
+    <t>135867762</t>
+  </si>
+  <si>
+    <t>135867771</t>
+  </si>
+  <si>
+    <t>135867899</t>
+  </si>
+  <si>
+    <t>135868185</t>
+  </si>
+  <si>
+    <t>135868235</t>
+  </si>
+  <si>
+    <t>135868254</t>
+  </si>
+  <si>
+    <t>135868301</t>
+  </si>
+  <si>
+    <t>135868335</t>
+  </si>
+  <si>
+    <t>135868344</t>
+  </si>
+  <si>
+    <t>135868353</t>
+  </si>
+  <si>
+    <t>135868367</t>
+  </si>
+  <si>
+    <t>135868395</t>
+  </si>
+  <si>
+    <t>135868424</t>
+  </si>
+  <si>
+    <t>135868550</t>
+  </si>
+  <si>
+    <t>135868857</t>
+  </si>
+  <si>
+    <t>135869025</t>
+  </si>
+  <si>
+    <t>135869140</t>
+  </si>
+  <si>
+    <t>135869201</t>
+  </si>
+  <si>
+    <t>135869319</t>
+  </si>
+  <si>
+    <t>135869387</t>
+  </si>
+  <si>
+    <t>135869435</t>
+  </si>
+  <si>
+    <t>135869530</t>
+  </si>
+  <si>
+    <t>135869585</t>
+  </si>
+  <si>
+    <t>135869704</t>
+  </si>
+  <si>
+    <t>135869710</t>
+  </si>
+  <si>
+    <t>135869719</t>
+  </si>
+  <si>
+    <t>135869736</t>
+  </si>
+  <si>
+    <t>135869861</t>
+  </si>
+  <si>
+    <t>135869918</t>
+  </si>
+  <si>
+    <t>135870192</t>
+  </si>
+  <si>
+    <t>135870284</t>
+  </si>
+  <si>
+    <t>135870365</t>
+  </si>
+  <si>
+    <t>135870412</t>
+  </si>
+  <si>
+    <t>135870566</t>
+  </si>
+  <si>
+    <t>135870740</t>
+  </si>
+  <si>
+    <t>135870751</t>
+  </si>
+  <si>
+    <t>135870823</t>
+  </si>
+  <si>
+    <t>135870892</t>
+  </si>
+  <si>
+    <t>135870917</t>
+  </si>
+  <si>
+    <t>135871053</t>
+  </si>
+  <si>
+    <t>135871076</t>
+  </si>
+  <si>
+    <t>135871182</t>
+  </si>
+  <si>
+    <t>135871226</t>
+  </si>
+  <si>
+    <t>135871348</t>
+  </si>
+  <si>
+    <t>135871389</t>
+  </si>
+  <si>
+    <t>135871411</t>
+  </si>
+  <si>
+    <t>135871593</t>
+  </si>
+  <si>
+    <t>135871606</t>
+  </si>
+  <si>
+    <t>135871634</t>
+  </si>
+  <si>
+    <t>135871639</t>
+  </si>
+  <si>
+    <t>135871644</t>
+  </si>
+  <si>
+    <t>135871704</t>
+  </si>
+  <si>
+    <t>135871808</t>
+  </si>
+  <si>
+    <t>135871882</t>
+  </si>
+  <si>
+    <t>135872098</t>
+  </si>
+  <si>
+    <t>135872108</t>
+  </si>
+  <si>
+    <t>135872332</t>
+  </si>
+  <si>
+    <t>135872338</t>
+  </si>
+  <si>
+    <t>135872382</t>
+  </si>
+  <si>
+    <t>135872519</t>
+  </si>
+  <si>
+    <t>135872606</t>
+  </si>
+  <si>
+    <t>135872652</t>
+  </si>
+  <si>
+    <t>135872961</t>
+  </si>
+  <si>
+    <t>135872963</t>
+  </si>
+  <si>
+    <t>135872967</t>
+  </si>
+  <si>
+    <t>135872976</t>
+  </si>
+  <si>
+    <t>135872983</t>
+  </si>
+  <si>
+    <t>135873465</t>
+  </si>
+  <si>
+    <t>135873489</t>
+  </si>
+  <si>
+    <t>135873707</t>
+  </si>
+  <si>
+    <t>135873734</t>
+  </si>
+  <si>
+    <t>135873839</t>
+  </si>
+  <si>
+    <t>135873843</t>
+  </si>
+  <si>
+    <t>135873844</t>
+  </si>
+  <si>
+    <t>135873887</t>
+  </si>
+  <si>
+    <t>135873971</t>
+  </si>
+  <si>
+    <t>135873980</t>
+  </si>
+  <si>
+    <t>135874144</t>
+  </si>
+  <si>
+    <t>135874169</t>
+  </si>
+  <si>
+    <t>135874193</t>
+  </si>
+  <si>
+    <t>135874219</t>
+  </si>
+  <si>
+    <t>135874240</t>
+  </si>
+  <si>
+    <t>135874330</t>
+  </si>
+  <si>
+    <t>135874335</t>
+  </si>
+  <si>
+    <t>135874514</t>
+  </si>
+  <si>
+    <t>135874879</t>
+  </si>
+  <si>
+    <t>135874924</t>
+  </si>
+  <si>
+    <t>135874971</t>
+  </si>
+  <si>
+    <t>135874980</t>
+  </si>
+  <si>
+    <t>135875181</t>
+  </si>
+  <si>
+    <t>135875189</t>
+  </si>
+  <si>
+    <t>135875271</t>
+  </si>
+  <si>
+    <t>135875323</t>
+  </si>
+  <si>
+    <t>135875502</t>
+  </si>
+  <si>
+    <t>135875596</t>
+  </si>
+  <si>
+    <t>135875679</t>
+  </si>
+  <si>
+    <t>135875754</t>
+  </si>
+  <si>
+    <t>135875860</t>
+  </si>
+  <si>
+    <t>135875955</t>
+  </si>
+  <si>
+    <t>135876024</t>
+  </si>
+  <si>
+    <t>135876177</t>
+  </si>
+  <si>
+    <t>135876362</t>
+  </si>
+  <si>
+    <t>135876396</t>
+  </si>
+  <si>
+    <t>135876455</t>
+  </si>
+  <si>
+    <t>135876733</t>
+  </si>
+  <si>
+    <t>135876744</t>
+  </si>
+  <si>
+    <t>135876831</t>
+  </si>
+  <si>
+    <t>135876878</t>
+  </si>
+  <si>
+    <t>135876992</t>
+  </si>
+  <si>
+    <t>135876999</t>
+  </si>
+  <si>
+    <t>135877059</t>
+  </si>
+  <si>
+    <t>135877071</t>
+  </si>
+  <si>
+    <t>135877225</t>
+  </si>
+  <si>
+    <t>135877280</t>
+  </si>
+  <si>
+    <t>135877464</t>
+  </si>
+  <si>
+    <t>135877469</t>
+  </si>
+  <si>
+    <t>135877507</t>
+  </si>
+  <si>
+    <t>135877522</t>
+  </si>
+  <si>
+    <t>135877611</t>
+  </si>
+  <si>
+    <t>135877627</t>
+  </si>
+  <si>
+    <t>135877725</t>
+  </si>
+  <si>
+    <t>135877823</t>
+  </si>
+  <si>
+    <t>135877844</t>
+  </si>
+  <si>
+    <t>135877938</t>
+  </si>
+  <si>
+    <t>135878068</t>
+  </si>
+  <si>
+    <t>135878246</t>
+  </si>
+  <si>
+    <t>135878285</t>
+  </si>
+  <si>
+    <t>135878310</t>
+  </si>
+  <si>
+    <t>135878321</t>
+  </si>
+  <si>
+    <t>135878387</t>
+  </si>
+  <si>
+    <t>135878402</t>
+  </si>
+  <si>
+    <t>135878537</t>
+  </si>
+  <si>
+    <t>135878549</t>
+  </si>
+  <si>
+    <t>135878624</t>
+  </si>
+  <si>
+    <t>135878628</t>
+  </si>
+  <si>
+    <t>135878645</t>
+  </si>
+  <si>
+    <t>135878649</t>
+  </si>
+  <si>
+    <t>135878665</t>
+  </si>
+  <si>
+    <t>135878941</t>
+  </si>
+  <si>
+    <t>135879049</t>
+  </si>
+  <si>
+    <t>135879201</t>
+  </si>
+  <si>
+    <t>135879252</t>
+  </si>
+  <si>
+    <t>135879269</t>
+  </si>
+  <si>
+    <t>135879322</t>
+  </si>
+  <si>
+    <t>135879326</t>
+  </si>
+  <si>
+    <t>135879350</t>
+  </si>
+  <si>
+    <t>135879364</t>
+  </si>
+  <si>
+    <t>135879399</t>
+  </si>
+  <si>
+    <t>135879415</t>
+  </si>
+  <si>
+    <t>135879437</t>
+  </si>
+  <si>
+    <t>135879525</t>
+  </si>
+  <si>
+    <t>135879733</t>
+  </si>
+  <si>
+    <t>135879745</t>
+  </si>
+  <si>
+    <t>135879828</t>
+  </si>
+  <si>
+    <t>135880007</t>
+  </si>
+  <si>
+    <t>135880031</t>
+  </si>
+  <si>
+    <t>135880096</t>
+  </si>
+  <si>
+    <t>135880275</t>
+  </si>
+  <si>
+    <t>135880367</t>
+  </si>
+  <si>
+    <t>135880555</t>
+  </si>
+  <si>
+    <t>135880584</t>
+  </si>
+  <si>
+    <t>135880641</t>
+  </si>
+  <si>
+    <t>135880724</t>
+  </si>
+  <si>
+    <t>135880786</t>
+  </si>
+  <si>
+    <t>135880811</t>
+  </si>
+  <si>
+    <t>135880945</t>
+  </si>
+  <si>
+    <t>135880978</t>
+  </si>
+  <si>
+    <t>135881207</t>
+  </si>
+  <si>
+    <t>135881232</t>
+  </si>
+  <si>
+    <t>135881310</t>
+  </si>
+  <si>
+    <t>135881366</t>
+  </si>
+  <si>
+    <t>135881371</t>
+  </si>
+  <si>
+    <t>135881452</t>
+  </si>
+  <si>
+    <t>135881514</t>
+  </si>
+  <si>
+    <t>135881614</t>
+  </si>
+  <si>
+    <t>135881761</t>
+  </si>
+  <si>
+    <t>135881790</t>
+  </si>
+  <si>
+    <t>135882139</t>
+  </si>
+  <si>
+    <t>135882349</t>
+  </si>
+  <si>
+    <t>135882441</t>
+  </si>
+  <si>
+    <t>135882576</t>
+  </si>
+  <si>
+    <t>135882643</t>
+  </si>
+  <si>
+    <t>135882754</t>
+  </si>
+  <si>
+    <t>135882829</t>
+  </si>
+  <si>
+    <t>135882844</t>
+  </si>
+  <si>
+    <t>135882891</t>
+  </si>
+  <si>
+    <t>135882893</t>
+  </si>
+  <si>
+    <t>135882914</t>
+  </si>
+  <si>
+    <t>135882939</t>
+  </si>
+  <si>
+    <t>135883156</t>
+  </si>
+  <si>
+    <t>135883199</t>
+  </si>
+  <si>
+    <t>135883353</t>
+  </si>
+  <si>
+    <t>135883371</t>
+  </si>
+  <si>
+    <t>135883422</t>
+  </si>
+  <si>
+    <t>135883474</t>
+  </si>
+  <si>
+    <t>135883605</t>
+  </si>
+  <si>
+    <t>135883796</t>
+  </si>
+  <si>
+    <t>135883822</t>
+  </si>
+  <si>
+    <t>135883917</t>
+  </si>
+  <si>
+    <t>135883962</t>
+  </si>
+  <si>
+    <t>135884049</t>
+  </si>
+  <si>
+    <t>135884130</t>
+  </si>
+  <si>
+    <t>135884505</t>
+  </si>
+  <si>
+    <t>135884793</t>
+  </si>
+  <si>
+    <t>135884821</t>
+  </si>
+  <si>
+    <t>135884827</t>
+  </si>
+  <si>
+    <t>135884839</t>
+  </si>
+  <si>
+    <t>135884907</t>
+  </si>
+  <si>
+    <t>135884919</t>
+  </si>
+  <si>
+    <t>135884977</t>
+  </si>
+  <si>
+    <t>135885086</t>
+  </si>
+  <si>
+    <t>135885090</t>
+  </si>
+  <si>
+    <t>135885110</t>
+  </si>
+  <si>
+    <t>135885179</t>
+  </si>
+  <si>
+    <t>135885295</t>
+  </si>
+  <si>
+    <t>135885419</t>
+  </si>
+  <si>
+    <t>135885486</t>
+  </si>
+  <si>
+    <t>135885570</t>
+  </si>
+  <si>
+    <t>135885700</t>
+  </si>
+  <si>
+    <t>135885865</t>
+  </si>
+  <si>
+    <t>135885868</t>
+  </si>
+  <si>
+    <t>135886012</t>
+  </si>
+  <si>
+    <t>135886094</t>
+  </si>
+  <si>
+    <t>135886112</t>
+  </si>
+  <si>
+    <t>135886234</t>
+  </si>
+  <si>
+    <t>135886612</t>
+  </si>
+  <si>
+    <t>135886633</t>
+  </si>
+  <si>
+    <t>135886660</t>
+  </si>
+  <si>
+    <t>135886712</t>
+  </si>
+  <si>
+    <t>135886749</t>
+  </si>
+  <si>
+    <t>135886872</t>
+  </si>
+  <si>
+    <t>135887009</t>
+  </si>
+  <si>
+    <t>135887046</t>
+  </si>
+  <si>
+    <t>135887119</t>
+  </si>
+  <si>
+    <t>135887149</t>
+  </si>
+  <si>
+    <t>135887165</t>
+  </si>
+  <si>
+    <t>135887222</t>
+  </si>
+  <si>
+    <t>135887330</t>
+  </si>
+  <si>
+    <t>135887519</t>
+  </si>
+  <si>
+    <t>135887563</t>
+  </si>
+  <si>
+    <t>135887631</t>
+  </si>
+  <si>
+    <t>135887650</t>
+  </si>
+  <si>
+    <t>135887739</t>
+  </si>
+  <si>
+    <t>135887839</t>
+  </si>
+  <si>
+    <t>135887910</t>
+  </si>
+  <si>
+    <t>135887995</t>
+  </si>
+  <si>
+    <t>135888045</t>
+  </si>
+  <si>
+    <t>135888207</t>
+  </si>
+  <si>
+    <t>135888278</t>
+  </si>
+  <si>
+    <t>135888485</t>
+  </si>
+  <si>
+    <t>135888493</t>
+  </si>
+  <si>
+    <t>135888500</t>
+  </si>
+  <si>
+    <t>135888520</t>
+  </si>
+  <si>
+    <t>135888559</t>
+  </si>
+  <si>
+    <t>135888575</t>
+  </si>
+  <si>
+    <t>135888696</t>
+  </si>
+  <si>
+    <t>135888761</t>
+  </si>
+  <si>
+    <t>135888802</t>
+  </si>
+  <si>
+    <t>135888814</t>
+  </si>
+  <si>
+    <t>135888820</t>
+  </si>
+  <si>
+    <t>135888864</t>
+  </si>
+  <si>
+    <t>135888901</t>
+  </si>
+  <si>
+    <t>135888964</t>
+  </si>
+  <si>
+    <t>135889017</t>
+  </si>
+  <si>
+    <t>135889020</t>
+  </si>
+  <si>
+    <t>135889030</t>
+  </si>
+  <si>
+    <t>135889035</t>
+  </si>
+  <si>
+    <t>135889074</t>
+  </si>
+  <si>
+    <t>135889246</t>
+  </si>
+  <si>
+    <t>135889251</t>
+  </si>
+  <si>
+    <t>135889274</t>
+  </si>
+  <si>
+    <t>135889459</t>
+  </si>
+  <si>
+    <t>135889536</t>
+  </si>
+  <si>
+    <t>135889628</t>
+  </si>
+  <si>
+    <t>135889668</t>
+  </si>
+  <si>
+    <t>135889708</t>
+  </si>
+  <si>
+    <t>135889766</t>
+  </si>
+  <si>
+    <t>135889774</t>
+  </si>
+  <si>
+    <t>135889778</t>
+  </si>
+  <si>
+    <t>135889794</t>
+  </si>
+  <si>
+    <t>135889906</t>
+  </si>
+  <si>
+    <t>135889924</t>
+  </si>
+  <si>
+    <t>135890048</t>
+  </si>
+  <si>
+    <t>135890067</t>
+  </si>
+  <si>
+    <t>135890217</t>
+  </si>
+  <si>
+    <t>135890398</t>
+  </si>
+  <si>
+    <t>135890434</t>
+  </si>
+  <si>
+    <t>135890483</t>
+  </si>
+  <si>
+    <t>135890547</t>
+  </si>
+  <si>
+    <t>135890576</t>
+  </si>
+  <si>
+    <t>135890589</t>
+  </si>
+  <si>
+    <t>135890639</t>
+  </si>
+  <si>
+    <t>135890641</t>
+  </si>
+  <si>
+    <t>135890668</t>
+  </si>
+  <si>
+    <t>135890758</t>
+  </si>
+  <si>
+    <t>135890791</t>
+  </si>
+  <si>
+    <t>135890794</t>
+  </si>
+  <si>
+    <t>135890805</t>
+  </si>
+  <si>
+    <t>135890838</t>
+  </si>
+  <si>
+    <t>135890905</t>
+  </si>
+  <si>
+    <t>135890934</t>
+  </si>
+  <si>
+    <t>135890943</t>
+  </si>
+  <si>
+    <t>135891020</t>
+  </si>
+  <si>
+    <t>135891075</t>
+  </si>
+  <si>
+    <t>135891123</t>
+  </si>
+  <si>
+    <t>135891147</t>
+  </si>
+  <si>
+    <t>135891207</t>
+  </si>
+  <si>
+    <t>135891219</t>
+  </si>
+  <si>
+    <t>135891234</t>
+  </si>
+  <si>
+    <t>135891250</t>
+  </si>
+  <si>
+    <t>135891330</t>
+  </si>
+  <si>
+    <t>135891351</t>
+  </si>
+  <si>
+    <t>135891428</t>
+  </si>
+  <si>
+    <t>135891447</t>
+  </si>
+  <si>
+    <t>135891464</t>
+  </si>
+  <si>
+    <t>135891501</t>
+  </si>
+  <si>
+    <t>135891547</t>
+  </si>
+  <si>
+    <t>135891614</t>
+  </si>
+  <si>
+    <t>135891629</t>
+  </si>
+  <si>
+    <t>135891649</t>
+  </si>
+  <si>
+    <t>135891705</t>
+  </si>
+  <si>
+    <t>135891730</t>
+  </si>
+  <si>
+    <t>135891771</t>
+  </si>
+  <si>
+    <t>135891779</t>
+  </si>
+  <si>
+    <t>135891785</t>
+  </si>
+  <si>
+    <t>135891921</t>
+  </si>
+  <si>
+    <t>135891957</t>
+  </si>
+  <si>
+    <t>135891999</t>
+  </si>
+  <si>
+    <t>135892006</t>
+  </si>
+  <si>
+    <t>135892055</t>
+  </si>
+  <si>
+    <t>135892157</t>
+  </si>
+  <si>
+    <t>135892167</t>
+  </si>
+  <si>
+    <t>135892172</t>
+  </si>
+  <si>
+    <t>135892243</t>
+  </si>
+  <si>
+    <t>135892251</t>
+  </si>
+  <si>
+    <t>135892254</t>
+  </si>
+  <si>
+    <t>135892315</t>
+  </si>
+  <si>
+    <t>135892388</t>
+  </si>
+  <si>
+    <t>135892409</t>
+  </si>
+  <si>
+    <t>135892430</t>
+  </si>
+  <si>
+    <t>135892552</t>
+  </si>
+  <si>
+    <t>135892559</t>
+  </si>
+  <si>
+    <t>135892560</t>
+  </si>
+  <si>
+    <t>135892570</t>
+  </si>
+  <si>
+    <t>135892703</t>
+  </si>
+  <si>
+    <t>135892741</t>
+  </si>
+  <si>
+    <t>135892754</t>
+  </si>
+  <si>
+    <t>135892777</t>
+  </si>
+  <si>
+    <t>135892816</t>
+  </si>
+  <si>
+    <t>135892835</t>
+  </si>
+  <si>
+    <t>135892849</t>
+  </si>
+  <si>
+    <t>135892883</t>
+  </si>
+  <si>
+    <t>135892956</t>
+  </si>
+  <si>
+    <t>135892974</t>
+  </si>
+  <si>
+    <t>135892986</t>
+  </si>
+  <si>
+    <t>135893058</t>
+  </si>
+  <si>
+    <t>135893087</t>
+  </si>
+  <si>
+    <t>135893107</t>
+  </si>
+  <si>
+    <t>135893121</t>
+  </si>
+  <si>
+    <t>135893183</t>
+  </si>
+  <si>
+    <t>135893201</t>
+  </si>
+  <si>
+    <t>135893303</t>
+  </si>
+  <si>
+    <t>135893315</t>
+  </si>
+  <si>
+    <t>135893385</t>
+  </si>
+  <si>
+    <t>135893403</t>
+  </si>
+  <si>
+    <t>135893523</t>
+  </si>
+  <si>
+    <t>135893534</t>
+  </si>
+  <si>
+    <t>135893538</t>
+  </si>
+  <si>
+    <t>135893655</t>
+  </si>
+  <si>
+    <t>135893666</t>
+  </si>
+  <si>
+    <t>135893729</t>
+  </si>
+  <si>
+    <t>135893732</t>
+  </si>
+  <si>
+    <t>135893829</t>
+  </si>
+  <si>
+    <t>135893857</t>
+  </si>
+  <si>
+    <t>135893882</t>
+  </si>
+  <si>
+    <t>135893888</t>
+  </si>
+  <si>
+    <t>135893921</t>
+  </si>
+  <si>
+    <t>135893923</t>
+  </si>
+  <si>
+    <t>135893929</t>
+  </si>
+  <si>
+    <t>135893939</t>
+  </si>
+  <si>
+    <t>135894098</t>
+  </si>
+  <si>
+    <t>135894137</t>
+  </si>
+  <si>
+    <t>135894147</t>
+  </si>
+  <si>
+    <t>135894184</t>
+  </si>
+  <si>
+    <t>135894283</t>
+  </si>
+  <si>
+    <t>135894321</t>
+  </si>
+  <si>
+    <t>135894381</t>
+  </si>
+  <si>
+    <t>135894394</t>
+  </si>
+  <si>
+    <t>135894439</t>
+  </si>
+  <si>
+    <t>135894477</t>
+  </si>
+  <si>
+    <t>135894568</t>
+  </si>
+  <si>
+    <t>135894595</t>
+  </si>
+  <si>
+    <t>135894673</t>
+  </si>
+  <si>
+    <t>135894717</t>
+  </si>
+  <si>
+    <t>135894727</t>
+  </si>
+  <si>
+    <t>135894746</t>
+  </si>
+  <si>
+    <t>135894780</t>
+  </si>
+  <si>
+    <t>135894812</t>
+  </si>
+  <si>
+    <t>135894818</t>
+  </si>
+  <si>
+    <t>135894890</t>
+  </si>
+  <si>
+    <t>135894900</t>
+  </si>
+  <si>
+    <t>135894906</t>
+  </si>
+  <si>
+    <t>135894947</t>
+  </si>
+  <si>
+    <t>135894985</t>
+  </si>
+  <si>
+    <t>135895080</t>
+  </si>
+  <si>
+    <t>135895146</t>
   </si>
 </sst>
 </file>
@@ -2961,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C839"/>
+  <dimension ref="A1:C618"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -8913,1774 +8250,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A619" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="B619" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A620" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="B620" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A621" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="B621" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A622" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="B622" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A623" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="B623" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A624" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="B624" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A625" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="B625" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A626" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="B626" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A627" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="B627" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A628" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="B628" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A629" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="B629" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A630" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="B630" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A631" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="B631" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A632" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="B632" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A633" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="B633" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A634" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="B634" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A635" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="B635" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A636" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="B636" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A637" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="B637" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A638" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="B638" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A639" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="B639" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A640" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="B640" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A641" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="B641" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A642" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="B642" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A643" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="B643" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A644" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="B644" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A645" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B645" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A646" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="B646" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A647" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="B647" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A648" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="B648" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A649" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="B649" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A650" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="B650" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A651" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="B651" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A652" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="B652" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A653" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="B653" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A654" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="B654" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A655" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="B655" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A656" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="B656" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A657" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="B657" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A658" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="B658" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A659" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="B659" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A660" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="B660" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A661" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="B661" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A662" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="B662" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A663" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B663" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A664" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="B664" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A665" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="B665" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A666" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="B666" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A667" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="B667" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A668" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="B668" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A669" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="B669" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A670" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="B670" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A671" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B671" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A672" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B672" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A673" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="B673" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A674" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="B674" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A675" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="B675" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A676" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="B676" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A677" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="B677" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A678" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="B678" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A679" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="B679" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A680" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="B680" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A681" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="B681" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A682" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="B682" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A683" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="B683" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A684" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="B684" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A685" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="B685" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A686" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="B686" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A687" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="B687" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A688" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="B688" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A689" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="B689" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A690" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="B690" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A691" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="B691" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A692" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="B692" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A693" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="B693" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A694" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="B694" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A695" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="B695" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A696" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="B696" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A697" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="B697" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A698" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="B698" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A699" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="B699" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A700" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="B700" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A701" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="B701" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A702" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B702" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A703" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="B703" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A704" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="B704" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A705" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="B705" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A706" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="B706" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A707" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="B707" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A708" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="B708" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A709" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="B709" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A710" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="B710" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A711" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="B711" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A712" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="B712" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A713" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="B713" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A714" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="B714" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A715" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="B715" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A716" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="B716" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A717" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="B717" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A718" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="B718" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A719" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="B719" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A720" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="B720" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A721" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="B721" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A722" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="B722" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A723" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="B723" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A724" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="B724" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A725" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="B725" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A726" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="B726" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A727" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="B727" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A728" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="B728" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A729" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="B729" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A730" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="B730" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A731" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="B731" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A732" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="B732" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A733" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="B733" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A734" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="B734" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A735" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="B735" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A736" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="B736" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A737" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="B737" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A738" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="B738" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A739" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="B739" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A740" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="B740" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A741" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="B741" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A742" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="B742" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A743" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="B743" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A744" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="B744" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A745" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="B745" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A746" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="B746" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A747" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="B747" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A748" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="B748" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A749" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="B749" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A750" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="B750" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A751" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="B751" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A752" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="B752" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A753" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="B753" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A754" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="B754" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A755" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="B755" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A756" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="B756" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A757" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="B757" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A758" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="B758" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A759" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="B759" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A760" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="B760" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A761" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="B761" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A762" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="B762" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A763" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="B763" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A764" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="B764" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A765" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="B765" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A766" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="B766" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A767" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="B767" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A768" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="B768" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A769" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="B769" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A770" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="B770" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A771" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="B771" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A772" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="B772" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A773" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="B773" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A774" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="B774" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A775" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="B775" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A776" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="B776" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A777" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="B777" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A778" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="B778" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A779" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="B779" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A780" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="B780" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A781" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="B781" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A782" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="B782" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A783" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="B783" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A784" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="B784" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A785" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="B785" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A786" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="B786" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A787" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="B787" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A788" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="B788" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A789" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="B789" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A790" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="B790" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A791" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="B791" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A792" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="B792" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A793" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="B793" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A794" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="B794" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A795" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="B795" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A796" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="B796" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A797" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="B797" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A798" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="B798" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A799" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="B799" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A800" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="B800" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="801" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A801" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="B801" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="802" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A802" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="B802" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="803" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A803" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="B803" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="804" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A804" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="B804" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="805" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A805" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="B805" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="806" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A806" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="B806" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="807" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A807" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="B807" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="808" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A808" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="B808" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="809" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A809" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="B809" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="810" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A810" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="B810" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="811" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A811" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="B811" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="812" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A812" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="B812" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="813" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A813" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="B813" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="814" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A814" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="B814" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="815" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A815" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="B815" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="816" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A816" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="B816" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="817" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A817" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="B817" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="818" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A818" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="B818" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="819" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A819" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="B819" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="820" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A820" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="B820" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="821" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A821" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="B821" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="822" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A822" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="B822" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="823" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A823" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="B823" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="824" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A824" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="B824" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="825" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A825" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="B825" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="826" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A826" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="B826" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="827" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A827" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="B827" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="828" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A828" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="B828" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="829" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A829" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="B829" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="830" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A830" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="B830" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="831" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A831" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="B831" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="832" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A832" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="B832" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="833" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A833" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="B833" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="834" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A834" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="B834" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="835" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A835" s="1" t="s">
-        <v>838</v>
-      </c>
-      <c r="B835" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="836" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A836" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B836" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="837" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A837" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="B837" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="838" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A838" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="B838" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="839" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A839" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="B839" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:C205" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B973DF-22B1-4998-BA74-2D0FB0CD98A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2CD20A-441C-4B84-866E-098CF100AE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="RecusaProposta" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RecusaProposta!$A$1:$C$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,61 +45,25 @@
     <t>.</t>
   </si>
   <si>
-    <t>136090688</t>
-  </si>
-  <si>
-    <t>136090694</t>
-  </si>
-  <si>
-    <t>136090891</t>
-  </si>
-  <si>
-    <t>136090933</t>
-  </si>
-  <si>
-    <t>136090935</t>
-  </si>
-  <si>
-    <t>136091034</t>
-  </si>
-  <si>
-    <t>136091070</t>
-  </si>
-  <si>
-    <t>136091175</t>
-  </si>
-  <si>
-    <t>136091182</t>
-  </si>
-  <si>
-    <t>136091210</t>
-  </si>
-  <si>
-    <t>136091218</t>
-  </si>
-  <si>
-    <t>136091278</t>
-  </si>
-  <si>
-    <t>136091301</t>
-  </si>
-  <si>
-    <t>136091379</t>
-  </si>
-  <si>
-    <t>136091425</t>
-  </si>
-  <si>
-    <t>136091559</t>
-  </si>
-  <si>
-    <t>136091927</t>
-  </si>
-  <si>
-    <t>136092032</t>
-  </si>
-  <si>
-    <t>136092273</t>
+    <t>136092391</t>
+  </si>
+  <si>
+    <t>136092413</t>
+  </si>
+  <si>
+    <t>136092489</t>
+  </si>
+  <si>
+    <t>136092671</t>
+  </si>
+  <si>
+    <t>136092867</t>
+  </si>
+  <si>
+    <t>136092948</t>
+  </si>
+  <si>
+    <t>136092965</t>
   </si>
 </sst>
 </file>
@@ -504,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
@@ -601,140 +565,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C20" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
+  <autoFilter ref="A1:C8" xr:uid="{322EE45B-4BB4-4712-A0E7-8263778555CF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Treinamento/RecusaProposta.xlsx
+++ b/Treinamento/RecusaProposta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C28F12-F8E6-4E6D-9EDE-E0A3F79DAE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE7B722-47E2-414A-93E0-37CD3DDCA0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B8421E97-A918-4249-83D2-1627CFA9F642}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="150">
   <si>
     <t>PROPOSTA</t>
   </si>
@@ -45,298 +45,439 @@
     <t>.</t>
   </si>
   <si>
-    <t>132019545</t>
-  </si>
-  <si>
-    <t>132937954</t>
-  </si>
-  <si>
-    <t>133276306</t>
-  </si>
-  <si>
-    <t>133441488</t>
-  </si>
-  <si>
-    <t>133518472</t>
-  </si>
-  <si>
-    <t>134804669</t>
-  </si>
-  <si>
-    <t>135784939</t>
-  </si>
-  <si>
-    <t>136055495</t>
-  </si>
-  <si>
-    <t>136094446</t>
-  </si>
-  <si>
-    <t>136094509</t>
-  </si>
-  <si>
-    <t>136094593</t>
-  </si>
-  <si>
-    <t>136094663</t>
-  </si>
-  <si>
-    <t>136094739</t>
-  </si>
-  <si>
-    <t>136094787</t>
-  </si>
-  <si>
-    <t>136095109</t>
-  </si>
-  <si>
-    <t>136095175</t>
-  </si>
-  <si>
-    <t>136095316</t>
-  </si>
-  <si>
-    <t>136095395</t>
-  </si>
-  <si>
-    <t>136095584</t>
-  </si>
-  <si>
-    <t>136095764</t>
-  </si>
-  <si>
-    <t>136095798</t>
-  </si>
-  <si>
-    <t>136095827</t>
-  </si>
-  <si>
-    <t>136096000</t>
-  </si>
-  <si>
-    <t>136096101</t>
-  </si>
-  <si>
-    <t>136096341</t>
-  </si>
-  <si>
-    <t>136096352</t>
-  </si>
-  <si>
-    <t>136096638</t>
-  </si>
-  <si>
-    <t>136096763</t>
-  </si>
-  <si>
-    <t>136096829</t>
-  </si>
-  <si>
-    <t>136096924</t>
-  </si>
-  <si>
-    <t>136097291</t>